--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24616146087646</t>
+    <t xml:space="preserve">1.24616158008575</t>
   </si>
   <si>
     <t xml:space="preserve">AUTME.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24544668197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24330163002014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22256779670715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21541857719421</t>
+    <t xml:space="preserve">1.24544656276703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24330151081085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22256803512573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21541845798492</t>
   </si>
   <si>
     <t xml:space="preserve">1.22185289859772</t>
@@ -68,10 +68,10 @@
     <t xml:space="preserve">1.21327376365662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20683896541595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20111966133118</t>
+    <t xml:space="preserve">1.20683908462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2011194229126</t>
   </si>
   <si>
     <t xml:space="preserve">1.20040464401245</t>
@@ -80,34 +80,34 @@
     <t xml:space="preserve">1.16680181026459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1946849822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25688600540161</t>
+    <t xml:space="preserve">1.19468486309052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25688588619232</t>
   </si>
   <si>
     <t xml:space="preserve">1.25045108795166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2468763589859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25116610527039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26475012302399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23543727397919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22542774677277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21041393280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22113811969757</t>
+    <t xml:space="preserve">1.24687647819519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25116622447968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26475024223328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23543739318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22542762756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.210413813591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22113800048828</t>
   </si>
   <si>
     <t xml:space="preserve">1.19396996498108</t>
@@ -119,13 +119,13 @@
     <t xml:space="preserve">1.20469427108765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25831592082977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26546537876129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25903034210205</t>
+    <t xml:space="preserve">1.25831580162048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.265465259552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25903046131134</t>
   </si>
   <si>
     <t xml:space="preserve">1.26903998851776</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">1.21684861183167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22828781604767</t>
+    <t xml:space="preserve">1.22828769683838</t>
   </si>
   <si>
     <t xml:space="preserve">1.27404463291168</t>
@@ -143,13 +143,13 @@
     <t xml:space="preserve">1.26689493656158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27261459827423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27189970016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2790492773056</t>
+    <t xml:space="preserve">1.27261471748352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27189981937408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27904915809631</t>
   </si>
   <si>
     <t xml:space="preserve">1.26760995388031</t>
@@ -158,169 +158,169 @@
     <t xml:space="preserve">1.25545573234558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26260530948639</t>
+    <t xml:space="preserve">1.26260542869568</t>
   </si>
   <si>
     <t xml:space="preserve">1.24830627441406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24902141094208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24258649349213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23686707019806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23472237586975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23400712013245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25225353240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26176822185516</t>
+    <t xml:space="preserve">1.24902129173279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24258673191071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23686718940735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23472225666046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23400723934174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25225365161896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26176798343658</t>
   </si>
   <si>
     <t xml:space="preserve">1.26835513114929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27860128879547</t>
+    <t xml:space="preserve">1.27860140800476</t>
   </si>
   <si>
     <t xml:space="preserve">1.27640581130981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27421021461487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27494192123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26323175430298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27128267288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2668913602829</t>
+    <t xml:space="preserve">1.27420997619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27494204044342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26323187351227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27128255367279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26689124107361</t>
   </si>
   <si>
     <t xml:space="preserve">1.28445649147034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28079700469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27933323383331</t>
+    <t xml:space="preserve">1.280797123909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2793333530426</t>
   </si>
   <si>
     <t xml:space="preserve">1.27347815036774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27274608612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26615941524506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28226101398468</t>
+    <t xml:space="preserve">1.2727462053299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26615953445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28226089477539</t>
   </si>
   <si>
     <t xml:space="preserve">1.28811609745026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28738403320312</t>
+    <t xml:space="preserve">1.28738415241241</t>
   </si>
   <si>
     <t xml:space="preserve">1.28299283981323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26396358013153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24127531051636</t>
+    <t xml:space="preserve">1.26396381855011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24127542972565</t>
   </si>
   <si>
     <t xml:space="preserve">1.2434709072113</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22956526279449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23468840122223</t>
+    <t xml:space="preserve">1.22956514358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23468828201294</t>
   </si>
   <si>
     <t xml:space="preserve">1.22663772106171</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20687663555145</t>
+    <t xml:space="preserve">1.20687675476074</t>
   </si>
   <si>
     <t xml:space="preserve">1.20760858058929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18565225601196</t>
+    <t xml:space="preserve">1.18565201759338</t>
   </si>
   <si>
     <t xml:space="preserve">1.1783332824707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18784773349762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16955065727234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17101454734802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17028260231018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1893116235733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22224628925323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22151446342468</t>
+    <t xml:space="preserve">1.18784785270691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16955077648163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17101442813873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17028248310089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18931150436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22224640846252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22151458263397</t>
   </si>
   <si>
     <t xml:space="preserve">1.23981165885925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23907971382141</t>
+    <t xml:space="preserve">1.23907959461212</t>
   </si>
   <si>
     <t xml:space="preserve">1.23834776878357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23542010784149</t>
+    <t xml:space="preserve">1.23542022705078</t>
   </si>
   <si>
     <t xml:space="preserve">1.20614492893219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23102867603302</t>
+    <t xml:space="preserve">1.23102879524231</t>
   </si>
   <si>
     <t xml:space="preserve">1.19736230373383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21712303161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22297811508179</t>
+    <t xml:space="preserve">1.2171231508255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22297823429108</t>
   </si>
   <si>
     <t xml:space="preserve">1.23322463035583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23249280452728</t>
+    <t xml:space="preserve">1.23249268531799</t>
   </si>
   <si>
     <t xml:space="preserve">1.22883343696594</t>
@@ -335,25 +335,25 @@
     <t xml:space="preserve">1.30714499950409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29909431934357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32324624061584</t>
+    <t xml:space="preserve">1.29909420013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32324635982513</t>
   </si>
   <si>
     <t xml:space="preserve">1.31665933132172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32763779163361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30348563194275</t>
+    <t xml:space="preserve">1.32763767242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30348539352417</t>
   </si>
   <si>
     <t xml:space="preserve">1.31592750549316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3181232213974</t>
+    <t xml:space="preserve">1.31812298297882</t>
   </si>
   <si>
     <t xml:space="preserve">1.29763031005859</t>
@@ -362,31 +362,31 @@
     <t xml:space="preserve">1.30275356769562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29982614517212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28884780406952</t>
+    <t xml:space="preserve">1.29982602596283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28884768486023</t>
   </si>
   <si>
     <t xml:space="preserve">1.29543483257294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30055809020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29836225509644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29323887825012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29250705242157</t>
+    <t xml:space="preserve">1.30055785179138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29836237430573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29323899745941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29250729084015</t>
   </si>
   <si>
     <t xml:space="preserve">1.30128991603851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3056812286377</t>
+    <t xml:space="preserve">1.30568110942841</t>
   </si>
   <si>
     <t xml:space="preserve">1.26908695697784</t>
@@ -404,106 +404,109 @@
     <t xml:space="preserve">1.2654275894165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28006529808044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25810873508453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25005793571472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24054360389709</t>
+    <t xml:space="preserve">1.28006505966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25810861587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25005781650543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24054348468781</t>
   </si>
   <si>
     <t xml:space="preserve">1.24639856815338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24420297145844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23688387870789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24200737476349</t>
+    <t xml:space="preserve">1.24420285224915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23615205287933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23688411712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2420072555542</t>
   </si>
   <si>
     <t xml:space="preserve">1.23176074028015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20980429649353</t>
+    <t xml:space="preserve">1.20980441570282</t>
   </si>
   <si>
     <t xml:space="preserve">1.21126806735992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2185868024826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21492767333984</t>
+    <t xml:space="preserve">1.21858692169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21492755413055</t>
   </si>
   <si>
     <t xml:space="preserve">1.19004344940186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18199276924133</t>
+    <t xml:space="preserve">1.18199265003204</t>
   </si>
   <si>
     <t xml:space="preserve">1.214195728302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19297087192535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19663047790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22005081176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21639132499695</t>
+    <t xml:space="preserve">1.19297075271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19663023948669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22005069255829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21639120578766</t>
   </si>
   <si>
     <t xml:space="preserve">1.25957238674164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27786934375763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28592038154602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29470300674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29689848423004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3100723028183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32544219493866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34081161022186</t>
+    <t xml:space="preserve">1.27786946296692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28592014312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2947028875351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29689836502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31007254123688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32544207572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34081149101257</t>
   </si>
   <si>
     <t xml:space="preserve">1.33349275588989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33422458171844</t>
+    <t xml:space="preserve">1.33422446250916</t>
   </si>
   <si>
     <t xml:space="preserve">1.3320289850235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33861601352692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33934772014618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34666669368744</t>
+    <t xml:space="preserve">1.33861589431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33934783935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34666657447815</t>
   </si>
   <si>
     <t xml:space="preserve">1.34227550029755</t>
@@ -515,10 +518,10 @@
     <t xml:space="preserve">1.32690572738647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3210506439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3459347486496</t>
+    <t xml:space="preserve">1.32105076313019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34593462944031</t>
   </si>
   <si>
     <t xml:space="preserve">1.36130440235138</t>
@@ -527,34 +530,34 @@
     <t xml:space="preserve">1.36057245731354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33276081085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34959399700165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33788394927979</t>
+    <t xml:space="preserve">1.33276069164276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34959411621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33788406848907</t>
   </si>
   <si>
     <t xml:space="preserve">1.34373915195465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34520304203033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32910144329071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36349999904633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36789131164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37667381763458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38252902030945</t>
+    <t xml:space="preserve">1.34520292282104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32910132408142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36349987983704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36789119243622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37667369842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38252890110016</t>
   </si>
   <si>
     <t xml:space="preserve">1.39789855480194</t>
@@ -563,16 +566,16 @@
     <t xml:space="preserve">1.41253614425659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40668106079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40814471244812</t>
+    <t xml:space="preserve">1.40668118000031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4081449508667</t>
   </si>
   <si>
     <t xml:space="preserve">1.40887665748596</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40302181243896</t>
+    <t xml:space="preserve">1.40302193164825</t>
   </si>
   <si>
     <t xml:space="preserve">1.39277541637421</t>
@@ -581,7 +584,7 @@
     <t xml:space="preserve">1.36935496330261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37886941432953</t>
+    <t xml:space="preserve">1.37886953353882</t>
   </si>
   <si>
     <t xml:space="preserve">1.38911581039429</t>
@@ -590,40 +593,40 @@
     <t xml:space="preserve">1.40155792236328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49304354190826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47621011734009</t>
+    <t xml:space="preserve">1.49304330348969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47621023654938</t>
   </si>
   <si>
     <t xml:space="preserve">1.48206520080566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.491579413414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50328981876373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46742737293243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45864486694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4791374206543</t>
+    <t xml:space="preserve">1.49157965183258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50329005718231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46742725372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45864498615265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47913753986359</t>
   </si>
   <si>
     <t xml:space="preserve">1.49523901939392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49084782600403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48792016506195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52744174003601</t>
+    <t xml:space="preserve">1.49084794521332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48792004585266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5274418592453</t>
   </si>
   <si>
     <t xml:space="preserve">1.50987672805786</t>
@@ -635,19 +638,19 @@
     <t xml:space="preserve">1.52963769435883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53183329105377</t>
+    <t xml:space="preserve">1.53183341026306</t>
   </si>
   <si>
     <t xml:space="preserve">1.52817380428314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51499998569489</t>
+    <t xml:space="preserve">1.51500010490417</t>
   </si>
   <si>
     <t xml:space="preserve">1.49963057041168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49816644191742</t>
+    <t xml:space="preserve">1.498166680336</t>
   </si>
   <si>
     <t xml:space="preserve">1.48572468757629</t>
@@ -656,10 +659,10 @@
     <t xml:space="preserve">1.47108697891235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48426103591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46376824378967</t>
+    <t xml:space="preserve">1.4842609167099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46376812458038</t>
   </si>
   <si>
     <t xml:space="preserve">1.45498538017273</t>
@@ -671,19 +674,19 @@
     <t xml:space="preserve">1.52085506916046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53768837451935</t>
+    <t xml:space="preserve">1.53768861293793</t>
   </si>
   <si>
     <t xml:space="preserve">1.58233344554901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63126349449158</t>
+    <t xml:space="preserve">1.63126361370087</t>
   </si>
   <si>
     <t xml:space="preserve">1.63427484035492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64857757091522</t>
+    <t xml:space="preserve">1.64857745170593</t>
   </si>
   <si>
     <t xml:space="preserve">1.63578033447266</t>
@@ -692,58 +695,58 @@
     <t xml:space="preserve">1.6666442155838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6628805398941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66137444972992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76902151107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8081659078598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84429919719696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91656517982483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99485421180725</t>
+    <t xml:space="preserve">1.66288030147552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66137456893921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76902163028717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80816602706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84429907798767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91656529903412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99485385417938</t>
   </si>
   <si>
     <t xml:space="preserve">2.01367354393005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95345163345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9820568561554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93011546134949</t>
+    <t xml:space="preserve">1.95345139503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98205709457397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9301153421402</t>
   </si>
   <si>
     <t xml:space="preserve">1.83376014232635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9030157327652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90452122688293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91204881668091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93538498878479</t>
+    <t xml:space="preserve">1.90301561355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90452110767365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91204869747162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9353848695755</t>
   </si>
   <si>
     <t xml:space="preserve">1.92258787155151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9158126115799</t>
+    <t xml:space="preserve">1.91581249237061</t>
   </si>
   <si>
     <t xml:space="preserve">1.88118505477905</t>
@@ -752,13 +755,13 @@
     <t xml:space="preserve">1.92860996723175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.921835064888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9255987405777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94065427780151</t>
+    <t xml:space="preserve">1.92183494567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92559897899628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94065451622009</t>
   </si>
   <si>
     <t xml:space="preserve">1.9263516664505</t>
@@ -767,94 +770,94 @@
     <t xml:space="preserve">1.90376842021942</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91957676410675</t>
+    <t xml:space="preserve">1.91957664489746</t>
   </si>
   <si>
     <t xml:space="preserve">1.91882383823395</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93237376213074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94366538524628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91054332256317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89021861553192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9075323343277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89699327945709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89473509788513</t>
+    <t xml:space="preserve">1.93237388134003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94366550445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91054320335388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89021837711334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90753221511841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89699351787567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89473497867584</t>
   </si>
   <si>
     <t xml:space="preserve">1.87742114067078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86010730266571</t>
+    <t xml:space="preserve">1.86010718345642</t>
   </si>
   <si>
     <t xml:space="preserve">1.7705272436142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79762709140778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76826894283295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79461598396301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80741322040558</t>
+    <t xml:space="preserve">1.7976268529892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76826870441437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79461586475372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80741310119629</t>
   </si>
   <si>
     <t xml:space="preserve">1.83074915409088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84881579875946</t>
+    <t xml:space="preserve">1.84881567955017</t>
   </si>
   <si>
     <t xml:space="preserve">1.82547962665558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81042420864105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82623243331909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83601856231689</t>
+    <t xml:space="preserve">1.81042432785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82623267173767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8360184431076</t>
   </si>
   <si>
     <t xml:space="preserve">1.83902955055237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85257947444916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82171595096588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84806287288666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84655737876892</t>
+    <t xml:space="preserve">1.85257959365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82171583175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84806299209595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84655749797821</t>
   </si>
   <si>
     <t xml:space="preserve">1.83752405643463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89774596691132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91280174255371</t>
+    <t xml:space="preserve">1.8977462053299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91280150413513</t>
   </si>
   <si>
     <t xml:space="preserve">1.97377645969391</t>
@@ -863,10 +866,10 @@
     <t xml:space="preserve">1.97151815891266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93086838722229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93613767623901</t>
+    <t xml:space="preserve">1.930868268013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93613755702972</t>
   </si>
   <si>
     <t xml:space="preserve">1.9210821390152</t>
@@ -875,31 +878,31 @@
     <t xml:space="preserve">1.88796007633209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88720715045929</t>
+    <t xml:space="preserve">1.88720726966858</t>
   </si>
   <si>
     <t xml:space="preserve">1.89548778533936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89322936534882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86914050579071</t>
+    <t xml:space="preserve">1.89322948455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86914074420929</t>
   </si>
   <si>
     <t xml:space="preserve">1.85860192775726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85634326934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85709607601166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85182678699493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86688232421875</t>
+    <t xml:space="preserve">1.85634338855743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85709631443024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85182702541351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86688256263733</t>
   </si>
   <si>
     <t xml:space="preserve">1.88494908809662</t>
@@ -908,7 +911,7 @@
     <t xml:space="preserve">1.87215185165405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87064635753632</t>
+    <t xml:space="preserve">1.87064611911774</t>
   </si>
   <si>
     <t xml:space="preserve">1.86161291599274</t>
@@ -923,52 +926,52 @@
     <t xml:space="preserve">1.87365710735321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86537683010101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84505212306976</t>
+    <t xml:space="preserve">1.86537706851959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84505188465118</t>
   </si>
   <si>
     <t xml:space="preserve">1.84204065799713</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84731030464172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84279358386993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81795191764832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82397401332855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82849097251892</t>
+    <t xml:space="preserve">1.84731018543243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84279334545135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8179520368576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82397437095642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82849085330963</t>
   </si>
   <si>
     <t xml:space="preserve">1.81569373607635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82021033763885</t>
+    <t xml:space="preserve">1.82021045684814</t>
   </si>
   <si>
     <t xml:space="preserve">1.81117689609528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81644630432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81418800354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83526563644409</t>
+    <t xml:space="preserve">1.81644642353058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81418812274933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8352655172348</t>
   </si>
   <si>
     <t xml:space="preserve">1.83225464820862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82246851921082</t>
+    <t xml:space="preserve">1.82246875762939</t>
   </si>
   <si>
     <t xml:space="preserve">1.8503212928772</t>
@@ -986,16 +989,16 @@
     <t xml:space="preserve">1.97979867458344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96474325656891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94667637348175</t>
+    <t xml:space="preserve">1.96474313735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94667661190033</t>
   </si>
   <si>
     <t xml:space="preserve">1.97076547145844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96775436401367</t>
+    <t xml:space="preserve">1.96775412559509</t>
   </si>
   <si>
     <t xml:space="preserve">1.96248483657837</t>
@@ -1013,13 +1016,13 @@
     <t xml:space="preserve">1.98732626438141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99937081336975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98582077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99033761024475</t>
+    <t xml:space="preserve">1.99937069416046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98582065105438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99033749103546</t>
   </si>
   <si>
     <t xml:space="preserve">1.96624886989594</t>
@@ -1031,16 +1034,16 @@
     <t xml:space="preserve">1.96549606323242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97603464126587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98280966281891</t>
+    <t xml:space="preserve">1.97603452205658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98280990123749</t>
   </si>
   <si>
     <t xml:space="preserve">2.02496528625488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06260371208191</t>
+    <t xml:space="preserve">2.06260395050049</t>
   </si>
   <si>
     <t xml:space="preserve">2.07540082931519</t>
@@ -1058,7 +1061,7 @@
     <t xml:space="preserve">2.07765936851501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09572577476501</t>
+    <t xml:space="preserve">2.09572601318359</t>
   </si>
   <si>
     <t xml:space="preserve">2.09045648574829</t>
@@ -1088,22 +1091,22 @@
     <t xml:space="preserve">2.07615375518799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08368182182312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10400652885437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08518743515015</t>
+    <t xml:space="preserve">2.08368134498596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10400676727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08518719673157</t>
   </si>
   <si>
     <t xml:space="preserve">2.13185906410217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19057583808899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21315884590149</t>
+    <t xml:space="preserve">2.19057559967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21315908432007</t>
   </si>
   <si>
     <t xml:space="preserve">2.17552042007446</t>
@@ -1112,13 +1115,13 @@
     <t xml:space="preserve">2.16799235343933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20563125610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22068691253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31101989746094</t>
+    <t xml:space="preserve">2.20563101768494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22068667411804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31101965904236</t>
   </si>
   <si>
     <t xml:space="preserve">2.36371374130249</t>
@@ -1127,10 +1130,10 @@
     <t xml:space="preserve">2.31854724884033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33360290527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37124180793762</t>
+    <t xml:space="preserve">2.33360266685486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37124156951904</t>
   </si>
   <si>
     <t xml:space="preserve">2.32607507705688</t>
@@ -1154,10 +1157,10 @@
     <t xml:space="preserve">2.25832533836365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19810342788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18304777145386</t>
+    <t xml:space="preserve">2.19810318946838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18304800987244</t>
   </si>
   <si>
     <t xml:space="preserve">2.43899154663086</t>
@@ -1169,7 +1172,7 @@
     <t xml:space="preserve">2.55190801620483</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54437971115112</t>
+    <t xml:space="preserve">2.5443799495697</t>
   </si>
   <si>
     <t xml:space="preserve">2.61965727806091</t>
@@ -1178,13 +1181,13 @@
     <t xml:space="preserve">2.46157479286194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49168562889099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46910214424133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40135288238525</t>
+    <t xml:space="preserve">2.49168539047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46910238265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40135264396667</t>
   </si>
   <si>
     <t xml:space="preserve">2.43146371841431</t>
@@ -1193,7 +1196,7 @@
     <t xml:space="preserve">2.47663044929504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44651937484741</t>
+    <t xml:space="preserve">2.44651913642883</t>
   </si>
   <si>
     <t xml:space="preserve">2.40888047218323</t>
@@ -1211,16 +1214,16 @@
     <t xml:space="preserve">2.50674104690552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52932453155518</t>
+    <t xml:space="preserve">2.52932476997375</t>
   </si>
   <si>
     <t xml:space="preserve">2.57587671279907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59139370918274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58363485336304</t>
+    <t xml:space="preserve">2.59139394760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58363509178162</t>
   </si>
   <si>
     <t xml:space="preserve">2.56035900115967</t>
@@ -1229,13 +1232,13 @@
     <t xml:space="preserve">2.50604844093323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51380705833435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52156591415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54484152793884</t>
+    <t xml:space="preserve">2.51380729675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52156567573547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54484176635742</t>
   </si>
   <si>
     <t xml:space="preserve">2.5293242931366</t>
@@ -1244,10 +1247,10 @@
     <t xml:space="preserve">2.48277235031128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49828958511353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42846202850342</t>
+    <t xml:space="preserve">2.4982898235321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42846179008484</t>
   </si>
   <si>
     <t xml:space="preserve">2.3275990486145</t>
@@ -1262,7 +1265,7 @@
     <t xml:space="preserve">2.31208157539368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22673654556274</t>
+    <t xml:space="preserve">2.22673678398132</t>
   </si>
   <si>
     <t xml:space="preserve">2.2034604549408</t>
@@ -1313,7 +1316,7 @@
     <t xml:space="preserve">2.07156348228455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0405285358429</t>
+    <t xml:space="preserve">2.04052877426147</t>
   </si>
   <si>
     <t xml:space="preserve">2.14139127731323</t>
@@ -1322,7 +1325,7 @@
     <t xml:space="preserve">2.16466736793518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14915013313293</t>
+    <t xml:space="preserve">2.14914989471436</t>
   </si>
   <si>
     <t xml:space="preserve">2.18018460273743</t>
@@ -1337,7 +1340,7 @@
     <t xml:space="preserve">2.01725244522095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02501130104065</t>
+    <t xml:space="preserve">2.02501153945923</t>
   </si>
   <si>
     <t xml:space="preserve">2.0094940662384</t>
@@ -1346,7 +1349,7 @@
     <t xml:space="preserve">1.97070062160492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9629420042038</t>
+    <t xml:space="preserve">1.96294212341309</t>
   </si>
   <si>
     <t xml:space="preserve">1.93966591358185</t>
@@ -1355,16 +1358,16 @@
     <t xml:space="preserve">1.88535523414612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87759685516357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85432052612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86983799934387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79225146770477</t>
+    <t xml:space="preserve">1.87759673595428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85432076454163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86983811855316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79225134849548</t>
   </si>
   <si>
     <t xml:space="preserve">1.83880352973938</t>
@@ -1373,13 +1376,13 @@
     <t xml:space="preserve">1.83104491233826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86207962036133</t>
+    <t xml:space="preserve">1.86207950115204</t>
   </si>
   <si>
     <t xml:space="preserve">2.15690851211548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06380438804626</t>
+    <t xml:space="preserve">2.06380462646484</t>
   </si>
   <si>
     <t xml:space="preserve">2.04828715324402</t>
@@ -1388,34 +1391,34 @@
     <t xml:space="preserve">2.0017352104187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97845947742462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99397671222687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92414855957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8465621471405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80776870250702</t>
+    <t xml:space="preserve">1.97845935821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99397659301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9241486787796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84656202793121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80776858329773</t>
   </si>
   <si>
     <t xml:space="preserve">1.75345814228058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77673399448395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74569928646088</t>
+    <t xml:space="preserve">1.77673411369324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74569940567017</t>
   </si>
   <si>
     <t xml:space="preserve">1.82328605651855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89311408996582</t>
+    <t xml:space="preserve">1.89311397075653</t>
   </si>
   <si>
     <t xml:space="preserve">1.91638994216919</t>
@@ -1424,10 +1427,10 @@
     <t xml:space="preserve">2.2112193107605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11035680770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05604577064514</t>
+    <t xml:space="preserve">2.11035656929016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05604600906372</t>
   </si>
   <si>
     <t xml:space="preserve">2.26552987098694</t>
@@ -1439,22 +1442,22 @@
     <t xml:space="preserve">2.35087513923645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31984066963196</t>
+    <t xml:space="preserve">2.31984090805054</t>
   </si>
   <si>
     <t xml:space="preserve">2.3353579044342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35863375663757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40518593788147</t>
+    <t xml:space="preserve">2.35863399505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40518569946289</t>
   </si>
   <si>
     <t xml:space="preserve">2.3819100856781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38966846466064</t>
+    <t xml:space="preserve">2.38966822624207</t>
   </si>
   <si>
     <t xml:space="preserve">2.39742732048035</t>
@@ -1472,16 +1475,16 @@
     <t xml:space="preserve">2.34311652183533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3741512298584</t>
+    <t xml:space="preserve">2.37415099143982</t>
   </si>
   <si>
     <t xml:space="preserve">2.45173788070679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47501373291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5526008605957</t>
+    <t xml:space="preserve">2.47501397132874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55260062217712</t>
   </si>
   <si>
     <t xml:space="preserve">2.5444712638855</t>
@@ -1502,7 +1505,7 @@
     <t xml:space="preserve">2.47943687438965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48756623268127</t>
+    <t xml:space="preserve">2.4875659942627</t>
   </si>
   <si>
     <t xml:space="preserve">2.50382447242737</t>
@@ -1511,13 +1514,13 @@
     <t xml:space="preserve">2.40627312660217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43066096305847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42253184318542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36562657356262</t>
+    <t xml:space="preserve">2.43066072463989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42253160476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3656268119812</t>
   </si>
   <si>
     <t xml:space="preserve">2.39001441001892</t>
@@ -1541,28 +1544,28 @@
     <t xml:space="preserve">2.26807498931885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.357497215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32498025894165</t>
+    <t xml:space="preserve">2.35749745368958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32498002052307</t>
   </si>
   <si>
     <t xml:space="preserve">2.34123873710632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37375593185425</t>
+    <t xml:space="preserve">2.37375617027283</t>
   </si>
   <si>
     <t xml:space="preserve">2.4631781578064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51195406913757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52821278572083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53634190559387</t>
+    <t xml:space="preserve">2.51195383071899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52821254730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53634214401245</t>
   </si>
   <si>
     <t xml:space="preserve">2.58511757850647</t>
@@ -1574,7 +1577,7 @@
     <t xml:space="preserve">2.56072998046875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6013765335083</t>
+    <t xml:space="preserve">2.60137629508972</t>
   </si>
   <si>
     <t xml:space="preserve">2.60950541496277</t>
@@ -1583,10 +1586,7 @@
     <t xml:space="preserve">2.5688591003418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57698845863342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55260062217712</t>
+    <t xml:space="preserve">2.57698822021484</t>
   </si>
   <si>
     <t xml:space="preserve">2.4144024848938</t>
@@ -1601,7 +1601,7 @@
     <t xml:space="preserve">2.39814376831055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47130727767944</t>
+    <t xml:space="preserve">2.47130751609802</t>
   </si>
   <si>
     <t xml:space="preserve">2.44691967964172</t>
@@ -1619,13 +1619,13 @@
     <t xml:space="preserve">2.30059218406677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11361837387085</t>
+    <t xml:space="preserve">2.11361813545227</t>
   </si>
   <si>
     <t xml:space="preserve">2.18678212165833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1298770904541</t>
+    <t xml:space="preserve">2.12987685203552</t>
   </si>
   <si>
     <t xml:space="preserve">2.08110094070435</t>
@@ -1637,22 +1637,22 @@
     <t xml:space="preserve">2.1217474937439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04858374595642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89412701129913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65837752819061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66650676727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62586009502411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47140347957611</t>
+    <t xml:space="preserve">2.048583984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89412713050842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65837740898132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66650664806366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6258602142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4714035987854</t>
   </si>
   <si>
     <t xml:space="preserve">1.50392067432404</t>
@@ -1661,13 +1661,13 @@
     <t xml:space="preserve">1.51205003261566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61366617679596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55676102638245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5486319065094</t>
+    <t xml:space="preserve">1.61366629600525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55676090717316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54863178730011</t>
   </si>
   <si>
     <t xml:space="preserve">1.53237330913544</t>
@@ -1676,7 +1676,7 @@
     <t xml:space="preserve">1.4957914352417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58521366119385</t>
+    <t xml:space="preserve">1.58521378040314</t>
   </si>
   <si>
     <t xml:space="preserve">1.60147225856781</t>
@@ -1691,19 +1691,19 @@
     <t xml:space="preserve">1.58114922046661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5689549446106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63398957252502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69089460372925</t>
+    <t xml:space="preserve">1.56895506381989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63398969173431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69089448451996</t>
   </si>
   <si>
     <t xml:space="preserve">1.60553693771362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62179565429688</t>
+    <t xml:space="preserve">1.62179553508759</t>
   </si>
   <si>
     <t xml:space="preserve">1.58927834033966</t>
@@ -1712,16 +1712,16 @@
     <t xml:space="preserve">1.61773085594177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67463600635529</t>
+    <t xml:space="preserve">1.67463612556458</t>
   </si>
   <si>
     <t xml:space="preserve">1.7071533203125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76405835151672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73154103755951</t>
+    <t xml:space="preserve">1.76405823230743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73154127597809</t>
   </si>
   <si>
     <t xml:space="preserve">1.71528244018555</t>
@@ -1733,37 +1733,37 @@
     <t xml:space="preserve">1.6502480506897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74779987335205</t>
+    <t xml:space="preserve">1.74779975414276</t>
   </si>
   <si>
     <t xml:space="preserve">1.75592887401581</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77218747138977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78844630718231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82096362113953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87786841392517</t>
+    <t xml:space="preserve">1.77218759059906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7884464263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82096338272095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87786865234375</t>
   </si>
   <si>
     <t xml:space="preserve">1.82909286022186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80470478534698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81283414363861</t>
+    <t xml:space="preserve">1.80470490455627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81283402442932</t>
   </si>
   <si>
     <t xml:space="preserve">1.79657554626465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7803168296814</t>
+    <t xml:space="preserve">1.78031706809998</t>
   </si>
   <si>
     <t xml:space="preserve">1.72341179847717</t>
@@ -1775,10 +1775,10 @@
     <t xml:space="preserve">1.68276536464691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60960161685944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64211869239807</t>
+    <t xml:space="preserve">1.60960149765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64211881160736</t>
   </si>
   <si>
     <t xml:space="preserve">1.57708442211151</t>
@@ -1796,13 +1796,13 @@
     <t xml:space="preserve">1.48766195774078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48359751701355</t>
+    <t xml:space="preserve">1.48359739780426</t>
   </si>
   <si>
     <t xml:space="preserve">1.43075704574585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42262780666351</t>
+    <t xml:space="preserve">1.42262768745422</t>
   </si>
   <si>
     <t xml:space="preserve">1.41043376922607</t>
@@ -1817,7 +1817,7 @@
     <t xml:space="preserve">1.4144983291626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36572241783142</t>
+    <t xml:space="preserve">1.36572253704071</t>
   </si>
   <si>
     <t xml:space="preserve">1.33320534229279</t>
@@ -1838,7 +1838,7 @@
     <t xml:space="preserve">1.30881750583649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3372700214386</t>
+    <t xml:space="preserve">1.33727014064789</t>
   </si>
   <si>
     <t xml:space="preserve">1.32507598400116</t>
@@ -1847,22 +1847,22 @@
     <t xml:space="preserve">1.34946405887604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37385177612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35352873802185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39823997020721</t>
+    <t xml:space="preserve">1.37385189533234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35352861881256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39823985099792</t>
   </si>
   <si>
     <t xml:space="preserve">1.40230441093445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3860456943512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3901104927063</t>
+    <t xml:space="preserve">1.38604581356049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39011061191559</t>
   </si>
   <si>
     <t xml:space="preserve">1.37791657447815</t>
@@ -1871,22 +1871,22 @@
     <t xml:space="preserve">1.4673388004303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52017939090729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5526967048645</t>
+    <t xml:space="preserve">1.520179271698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55269658565521</t>
   </si>
   <si>
     <t xml:space="preserve">1.54456722736359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49172675609589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5242440700531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50798535346985</t>
+    <t xml:space="preserve">1.49172687530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52424395084381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50798523426056</t>
   </si>
   <si>
     <t xml:space="preserve">1.51611471176147</t>
@@ -1895,13 +1895,13 @@
     <t xml:space="preserve">1.54050266742706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47953271865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86973929405212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95103216171265</t>
+    <t xml:space="preserve">1.47953283786774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86973941326141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95103228092194</t>
   </si>
   <si>
     <t xml:space="preserve">2.07297158241272</t>
@@ -1913,13 +1913,13 @@
     <t xml:space="preserve">2.24368715286255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17865252494812</t>
+    <t xml:space="preserve">2.1786527633667</t>
   </si>
   <si>
     <t xml:space="preserve">2.14613556861877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05671310424805</t>
+    <t xml:space="preserve">2.05671334266663</t>
   </si>
   <si>
     <t xml:space="preserve">2.13800621032715</t>
@@ -1931,16 +1931,16 @@
     <t xml:space="preserve">2.21945142745972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23601460456848</t>
+    <t xml:space="preserve">2.2360143661499</t>
   </si>
   <si>
     <t xml:space="preserve">2.24429607391357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25257754325867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20288848876953</t>
+    <t xml:space="preserve">2.25257778167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20288825035095</t>
   </si>
   <si>
     <t xml:space="preserve">2.22773313522339</t>
@@ -1952,7 +1952,7 @@
     <t xml:space="preserve">2.17804384231567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34367442131042</t>
+    <t xml:space="preserve">2.343674659729</t>
   </si>
   <si>
     <t xml:space="preserve">2.36023759841919</t>
@@ -1961,7 +1961,7 @@
     <t xml:space="preserve">2.36851906776428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38508200645447</t>
+    <t xml:space="preserve">2.38508224487305</t>
   </si>
   <si>
     <t xml:space="preserve">2.40164518356323</t>
@@ -1970,7 +1970,7 @@
     <t xml:space="preserve">2.45133447647095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4761791229248</t>
+    <t xml:space="preserve">2.47617888450623</t>
   </si>
   <si>
     <t xml:space="preserve">2.4844605922699</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">2.418208360672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39336371421814</t>
+    <t xml:space="preserve">2.39336347579956</t>
   </si>
   <si>
     <t xml:space="preserve">2.37680077552795</t>
@@ -1997,7 +1997,7 @@
     <t xml:space="preserve">2.42648983001709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33539295196533</t>
+    <t xml:space="preserve">2.33539319038391</t>
   </si>
   <si>
     <t xml:space="preserve">2.32711148262024</t>
@@ -2030,7 +2030,7 @@
     <t xml:space="preserve">2.12835454940796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13663625717163</t>
+    <t xml:space="preserve">2.13663601875305</t>
   </si>
   <si>
     <t xml:space="preserve">2.18632531166077</t>
@@ -2039,7 +2039,7 @@
     <t xml:space="preserve">2.08694696426392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10351014137268</t>
+    <t xml:space="preserve">2.1035099029541</t>
   </si>
   <si>
     <t xml:space="preserve">2.07038378715515</t>
@@ -2057,7 +2057,7 @@
     <t xml:space="preserve">2.26914072036743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26085901260376</t>
+    <t xml:space="preserve">2.26085925102234</t>
   </si>
   <si>
     <t xml:space="preserve">2.4099268913269</t>
@@ -2075,10 +2075,10 @@
     <t xml:space="preserve">2.50930500030518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62524676322937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71634340286255</t>
+    <t xml:space="preserve">2.62524652481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71634364128113</t>
   </si>
   <si>
     <t xml:space="preserve">2.69978022575378</t>
@@ -2096,13 +2096,13 @@
     <t xml:space="preserve">3.01447892189026</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03104186058044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24636220932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2380805015564</t>
+    <t xml:space="preserve">3.03104162216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24636197090149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23808026313782</t>
   </si>
   <si>
     <t xml:space="preserve">3.22979879379272</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">3.3043327331543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1221387386322</t>
+    <t xml:space="preserve">3.12213897705078</t>
   </si>
   <si>
     <t xml:space="preserve">3.1635468006134</t>
@@ -2132,7 +2132,7 @@
     <t xml:space="preserve">3.18010950088501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13042020797729</t>
+    <t xml:space="preserve">3.13042044639587</t>
   </si>
   <si>
     <t xml:space="preserve">3.10557556152344</t>
@@ -2144,7 +2144,7 @@
     <t xml:space="preserve">3.08901286125183</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07244968414307</t>
+    <t xml:space="preserve">3.07244944572449</t>
   </si>
   <si>
     <t xml:space="preserve">3.11385703086853</t>
@@ -2153,7 +2153,7 @@
     <t xml:space="preserve">3.08073139190674</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06416821479797</t>
+    <t xml:space="preserve">3.06416797637939</t>
   </si>
   <si>
     <t xml:space="preserve">3.254643201828</t>
@@ -2162,22 +2162,22 @@
     <t xml:space="preserve">3.09729433059692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93994474411011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02276015281677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04760479927063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0558865070343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15526509284973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03932332992554</t>
+    <t xml:space="preserve">2.93994498252869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02276039123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04760503768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05588674545288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15526485443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03932356834412</t>
   </si>
   <si>
     <t xml:space="preserve">2.98963403701782</t>
@@ -2192,7 +2192,7 @@
     <t xml:space="preserve">2.97307133674622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20495414733887</t>
+    <t xml:space="preserve">3.20495438575745</t>
   </si>
   <si>
     <t xml:space="preserve">3.27948784828186</t>
@@ -8677,7 +8677,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G209" t="s">
-        <v>16</v>
+        <v>136</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -8703,7 +8703,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G210" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -8755,7 +8755,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G212" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -8963,7 +8963,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G220" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -9171,7 +9171,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G228" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -9197,7 +9197,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G229" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -9223,7 +9223,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G230" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -9275,7 +9275,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G232" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -9301,7 +9301,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G233" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -9327,7 +9327,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G234" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -9353,7 +9353,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G235" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -9379,7 +9379,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G236" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -9405,7 +9405,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G237" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -9483,7 +9483,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G240" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -9509,7 +9509,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G241" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -9561,7 +9561,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G243" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -9639,7 +9639,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G246" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -9665,7 +9665,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G247" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -9691,7 +9691,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G248" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -9743,7 +9743,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G250" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -9769,7 +9769,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G251" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -9847,7 +9847,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G254" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -9925,7 +9925,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G257" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -9951,7 +9951,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G258" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -9977,7 +9977,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G259" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -10003,7 +10003,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G260" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -10029,7 +10029,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G261" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -10055,7 +10055,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G262" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -10081,7 +10081,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G263" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -10107,7 +10107,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G264" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -10133,7 +10133,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G265" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -10185,7 +10185,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G267" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -10211,7 +10211,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G268" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -10237,7 +10237,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G269" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -10263,7 +10263,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G270" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -10289,7 +10289,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G271" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -10315,7 +10315,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G272" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -10341,7 +10341,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G273" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -10367,7 +10367,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G274" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -10393,7 +10393,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G275" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -10419,7 +10419,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G276" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -10445,7 +10445,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G277" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -10471,7 +10471,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G278" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -10497,7 +10497,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G279" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -10523,7 +10523,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G280" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -10549,7 +10549,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G281" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -10575,7 +10575,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G282" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -10601,7 +10601,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G283" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -10627,7 +10627,7 @@
         <v>18.6299991607666</v>
       </c>
       <c r="G284" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -10653,7 +10653,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G285" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -10679,7 +10679,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G286" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -10705,7 +10705,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G287" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -10731,7 +10731,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G288" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -10757,7 +10757,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G289" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -10783,7 +10783,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G290" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -10809,7 +10809,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G291" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -10835,7 +10835,7 @@
         <v>19.25</v>
       </c>
       <c r="G292" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -10861,7 +10861,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G293" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -10887,7 +10887,7 @@
         <v>19.0300006866455</v>
       </c>
       <c r="G294" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -10913,7 +10913,7 @@
         <v>18.7099990844727</v>
       </c>
       <c r="G295" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -10939,7 +10939,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G296" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -10965,7 +10965,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G297" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -10991,7 +10991,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G298" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -11017,7 +11017,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G299" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -11043,7 +11043,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G300" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -11069,7 +11069,7 @@
         <v>20.1700000762939</v>
       </c>
       <c r="G301" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -11095,7 +11095,7 @@
         <v>20.25</v>
       </c>
       <c r="G302" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -11121,7 +11121,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G303" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -11147,7 +11147,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G304" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -11173,7 +11173,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G305" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -11199,7 +11199,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G306" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -11225,7 +11225,7 @@
         <v>20.2099990844727</v>
       </c>
       <c r="G307" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -11251,7 +11251,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G308" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -11277,7 +11277,7 @@
         <v>20.3700008392334</v>
       </c>
       <c r="G309" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -11303,7 +11303,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G310" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -11329,7 +11329,7 @@
         <v>20.25</v>
       </c>
       <c r="G311" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -11355,7 +11355,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G312" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -11381,7 +11381,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G313" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -11407,7 +11407,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G314" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -11433,7 +11433,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G315" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -11459,7 +11459,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G316" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -11485,7 +11485,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G317" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -11511,7 +11511,7 @@
         <v>20.9300003051758</v>
       </c>
       <c r="G318" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -11537,7 +11537,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G319" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -11563,7 +11563,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G320" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -11589,7 +11589,7 @@
         <v>20.4899997711182</v>
       </c>
       <c r="G321" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -11615,7 +11615,7 @@
         <v>20.4699993133545</v>
       </c>
       <c r="G322" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -11641,7 +11641,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G323" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -11667,7 +11667,7 @@
         <v>20.25</v>
       </c>
       <c r="G324" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -11693,7 +11693,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G325" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -11719,7 +11719,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G326" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -11745,7 +11745,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G327" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -11771,7 +11771,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G328" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -11797,7 +11797,7 @@
         <v>20.25</v>
       </c>
       <c r="G329" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -11823,7 +11823,7 @@
         <v>20</v>
       </c>
       <c r="G330" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -11849,7 +11849,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G331" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -11875,7 +11875,7 @@
         <v>20.2900009155273</v>
       </c>
       <c r="G332" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -11901,7 +11901,7 @@
         <v>20.7800006866455</v>
       </c>
       <c r="G333" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -11927,7 +11927,7 @@
         <v>21.0100002288818</v>
       </c>
       <c r="G334" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -11953,7 +11953,7 @@
         <v>21.6200008392334</v>
       </c>
       <c r="G335" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -11979,7 +11979,7 @@
         <v>21.6700000762939</v>
       </c>
       <c r="G336" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -12005,7 +12005,7 @@
         <v>21.7099990844727</v>
       </c>
       <c r="G337" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -12031,7 +12031,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G338" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -12057,7 +12057,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G339" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -12083,7 +12083,7 @@
         <v>22.1399993896484</v>
       </c>
       <c r="G340" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -12109,7 +12109,7 @@
         <v>22.0900001525879</v>
       </c>
       <c r="G341" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -12135,7 +12135,7 @@
         <v>22.0699996948242</v>
       </c>
       <c r="G342" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -12161,7 +12161,7 @@
         <v>23.5</v>
       </c>
       <c r="G343" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -12187,7 +12187,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G344" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -12213,7 +12213,7 @@
         <v>24.5</v>
       </c>
       <c r="G345" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -12239,7 +12239,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G346" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -12265,7 +12265,7 @@
         <v>26.5</v>
       </c>
       <c r="G347" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -12291,7 +12291,7 @@
         <v>26.75</v>
       </c>
       <c r="G348" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -12317,7 +12317,7 @@
         <v>25.9500007629395</v>
       </c>
       <c r="G349" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -12343,7 +12343,7 @@
         <v>26.3299999237061</v>
       </c>
       <c r="G350" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -12369,7 +12369,7 @@
         <v>25.6399993896484</v>
       </c>
       <c r="G351" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -12395,7 +12395,7 @@
         <v>24.5</v>
       </c>
       <c r="G352" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -12421,7 +12421,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G353" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -12447,7 +12447,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G354" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -12473,7 +12473,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G355" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -12499,7 +12499,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G356" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -12525,7 +12525,7 @@
         <v>25.7099990844727</v>
       </c>
       <c r="G357" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -12551,7 +12551,7 @@
         <v>25.5400009155273</v>
       </c>
       <c r="G358" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -12577,7 +12577,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G359" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -12603,7 +12603,7 @@
         <v>24.9899997711182</v>
       </c>
       <c r="G360" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -12629,7 +12629,7 @@
         <v>25.6200008392334</v>
       </c>
       <c r="G361" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -12655,7 +12655,7 @@
         <v>25.5300006866455</v>
       </c>
       <c r="G362" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -12681,7 +12681,7 @@
         <v>25.5799999237061</v>
       </c>
       <c r="G363" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -12707,7 +12707,7 @@
         <v>25.7800006866455</v>
       </c>
       <c r="G364" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -12733,7 +12733,7 @@
         <v>25.5900001525879</v>
       </c>
       <c r="G365" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -12759,7 +12759,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G366" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -12785,7 +12785,7 @@
         <v>25.2900009155273</v>
       </c>
       <c r="G367" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -12811,7 +12811,7 @@
         <v>25.5</v>
       </c>
       <c r="G368" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -12837,7 +12837,7 @@
         <v>25.5799999237061</v>
       </c>
       <c r="G369" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -12863,7 +12863,7 @@
         <v>25.4899997711182</v>
       </c>
       <c r="G370" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -12889,7 +12889,7 @@
         <v>25.6700000762939</v>
       </c>
       <c r="G371" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -12915,7 +12915,7 @@
         <v>25.8199996948242</v>
       </c>
       <c r="G372" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -12941,7 +12941,7 @@
         <v>25.5400009155273</v>
       </c>
       <c r="G373" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -12967,7 +12967,7 @@
         <v>25.3799991607666</v>
       </c>
       <c r="G374" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -12993,7 +12993,7 @@
         <v>25.1100006103516</v>
       </c>
       <c r="G375" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -13019,7 +13019,7 @@
         <v>25.3400001525879</v>
       </c>
       <c r="G376" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -13045,7 +13045,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G377" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -13071,7 +13071,7 @@
         <v>25.1700000762939</v>
       </c>
       <c r="G378" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -13097,7 +13097,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G379" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -13123,7 +13123,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G380" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -13149,7 +13149,7 @@
         <v>23.5200004577637</v>
       </c>
       <c r="G381" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -13175,7 +13175,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G382" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -13201,7 +13201,7 @@
         <v>23.4899997711182</v>
       </c>
       <c r="G383" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -13227,7 +13227,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G384" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -13253,7 +13253,7 @@
         <v>24.0100002288818</v>
       </c>
       <c r="G385" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -13279,7 +13279,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G386" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -13305,7 +13305,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G387" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -13331,7 +13331,7 @@
         <v>24.25</v>
       </c>
       <c r="G388" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -13357,7 +13357,7 @@
         <v>24.0499992370605</v>
       </c>
       <c r="G389" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -13383,7 +13383,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G390" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -13409,7 +13409,7 @@
         <v>24.2600002288818</v>
       </c>
       <c r="G391" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -13435,7 +13435,7 @@
         <v>24.0499992370605</v>
       </c>
       <c r="G392" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -13461,7 +13461,7 @@
         <v>24.3899993896484</v>
       </c>
       <c r="G393" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -13487,7 +13487,7 @@
         <v>24.4300003051758</v>
       </c>
       <c r="G394" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -13513,7 +13513,7 @@
         <v>24.5</v>
       </c>
       <c r="G395" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -13539,7 +13539,7 @@
         <v>24.5</v>
       </c>
       <c r="G396" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -13565,7 +13565,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G397" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -13591,7 +13591,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G398" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -13617,7 +13617,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G399" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -13643,7 +13643,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G400" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -13669,7 +13669,7 @@
         <v>24.5300006866455</v>
       </c>
       <c r="G401" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -13695,7 +13695,7 @@
         <v>24.4099998474121</v>
       </c>
       <c r="G402" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -13721,7 +13721,7 @@
         <v>25.2099990844727</v>
       </c>
       <c r="G403" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -13747,7 +13747,7 @@
         <v>25.4099998474121</v>
       </c>
       <c r="G404" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -13773,7 +13773,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G405" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -13799,7 +13799,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G406" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -13825,7 +13825,7 @@
         <v>26.1900005340576</v>
       </c>
       <c r="G407" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -13851,7 +13851,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G408" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -13877,7 +13877,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G409" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -13903,7 +13903,7 @@
         <v>25.6700000762939</v>
       </c>
       <c r="G410" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -13929,7 +13929,7 @@
         <v>25.5200004577637</v>
       </c>
       <c r="G411" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -13955,7 +13955,7 @@
         <v>25.5</v>
       </c>
       <c r="G412" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -13981,7 +13981,7 @@
         <v>25.0799999237061</v>
       </c>
       <c r="G413" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -14007,7 +14007,7 @@
         <v>25.1100006103516</v>
       </c>
       <c r="G414" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -14033,7 +14033,7 @@
         <v>25.0699996948242</v>
       </c>
       <c r="G415" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -14059,7 +14059,7 @@
         <v>25.1800003051758</v>
       </c>
       <c r="G416" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -14085,7 +14085,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G417" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -14111,7 +14111,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G418" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -14137,7 +14137,7 @@
         <v>24.8299999237061</v>
       </c>
       <c r="G419" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -14163,7 +14163,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G420" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -14189,7 +14189,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G421" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -14215,7 +14215,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G422" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -14241,7 +14241,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G423" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -14267,7 +14267,7 @@
         <v>24.6700000762939</v>
       </c>
       <c r="G424" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -14293,7 +14293,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G425" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -14319,7 +14319,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G426" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -14345,7 +14345,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G427" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -14371,7 +14371,7 @@
         <v>25.0400009155273</v>
       </c>
       <c r="G428" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -14397,7 +14397,7 @@
         <v>24.8700008392334</v>
       </c>
       <c r="G429" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -14423,7 +14423,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G430" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -14449,7 +14449,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G431" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -14475,7 +14475,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G432" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -14501,7 +14501,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G433" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -14527,7 +14527,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G434" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -14553,7 +14553,7 @@
         <v>24.7299995422363</v>
       </c>
       <c r="G435" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -14579,7 +14579,7 @@
         <v>25</v>
       </c>
       <c r="G436" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -14605,7 +14605,7 @@
         <v>24.8099994659424</v>
       </c>
       <c r="G437" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -14631,7 +14631,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G438" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -14657,7 +14657,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G439" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -14683,7 +14683,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G440" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -14709,7 +14709,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G441" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -14735,7 +14735,7 @@
         <v>24.5100002288818</v>
       </c>
       <c r="G442" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -14761,7 +14761,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G443" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -14787,7 +14787,7 @@
         <v>24.4699993133545</v>
       </c>
       <c r="G444" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -14813,7 +14813,7 @@
         <v>24.5400009155273</v>
       </c>
       <c r="G445" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -14839,7 +14839,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G446" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -14865,7 +14865,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G447" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -14891,7 +14891,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G448" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -14917,7 +14917,7 @@
         <v>24.2299995422363</v>
       </c>
       <c r="G449" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -14943,7 +14943,7 @@
         <v>24.2900009155273</v>
       </c>
       <c r="G450" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -14969,7 +14969,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G451" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -14995,7 +14995,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G452" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15021,7 +15021,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G453" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15047,7 +15047,7 @@
         <v>24.1299991607666</v>
       </c>
       <c r="G454" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15073,7 +15073,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G455" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15099,7 +15099,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G456" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -15125,7 +15125,7 @@
         <v>24.25</v>
       </c>
       <c r="G457" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15151,7 +15151,7 @@
         <v>24.3400001525879</v>
       </c>
       <c r="G458" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15177,7 +15177,7 @@
         <v>24.2099990844727</v>
       </c>
       <c r="G459" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -15203,7 +15203,7 @@
         <v>24.25</v>
       </c>
       <c r="G460" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -15229,7 +15229,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G461" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15255,7 +15255,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G462" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15281,7 +15281,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G463" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -15307,7 +15307,7 @@
         <v>25.2199993133545</v>
       </c>
       <c r="G464" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15333,7 +15333,7 @@
         <v>25.7299995422363</v>
       </c>
       <c r="G465" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15359,7 +15359,7 @@
         <v>25.4699993133545</v>
       </c>
       <c r="G466" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15385,7 +15385,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G467" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -15411,7 +15411,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G468" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15437,7 +15437,7 @@
         <v>25.8199996948242</v>
       </c>
       <c r="G469" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15463,7 +15463,7 @@
         <v>25.8600006103516</v>
       </c>
       <c r="G470" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15489,7 +15489,7 @@
         <v>26.1800003051758</v>
       </c>
       <c r="G471" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15515,7 +15515,7 @@
         <v>26.1399993896484</v>
       </c>
       <c r="G472" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15541,7 +15541,7 @@
         <v>26.0699996948242</v>
       </c>
       <c r="G473" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15567,7 +15567,7 @@
         <v>27.9400005340576</v>
       </c>
       <c r="G474" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -15593,7 +15593,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G475" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -15619,7 +15619,7 @@
         <v>26.8899993896484</v>
       </c>
       <c r="G476" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15645,7 +15645,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G477" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15671,7 +15671,7 @@
         <v>26.5599994659424</v>
       </c>
       <c r="G478" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -15697,7 +15697,7 @@
         <v>26.3799991607666</v>
       </c>
       <c r="G479" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15723,7 +15723,7 @@
         <v>26.4400005340576</v>
       </c>
       <c r="G480" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -15749,7 +15749,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G481" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -15775,7 +15775,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G482" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -15801,7 +15801,7 @@
         <v>26.1100006103516</v>
       </c>
       <c r="G483" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -15827,7 +15827,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G484" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -15853,7 +15853,7 @@
         <v>26.25</v>
       </c>
       <c r="G485" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -15879,7 +15879,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G486" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -15905,7 +15905,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G487" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -15931,7 +15931,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G488" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -15957,7 +15957,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G489" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -15983,7 +15983,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G490" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -16009,7 +16009,7 @@
         <v>27.5699996948242</v>
       </c>
       <c r="G491" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16035,7 +16035,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G492" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -16061,7 +16061,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G493" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16087,7 +16087,7 @@
         <v>27.6599998474121</v>
       </c>
       <c r="G494" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16113,7 +16113,7 @@
         <v>27.7099990844727</v>
       </c>
       <c r="G495" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -16139,7 +16139,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G496" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -16165,7 +16165,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G497" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -16191,7 +16191,7 @@
         <v>27.8400001525879</v>
       </c>
       <c r="G498" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -16217,7 +16217,7 @@
         <v>27.7700004577637</v>
       </c>
       <c r="G499" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16243,7 +16243,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G500" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -16269,7 +16269,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G501" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16295,7 +16295,7 @@
         <v>27.7199993133545</v>
       </c>
       <c r="G502" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16321,7 +16321,7 @@
         <v>27.5</v>
       </c>
       <c r="G503" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16347,7 +16347,7 @@
         <v>27.3700008392334</v>
       </c>
       <c r="G504" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16373,7 +16373,7 @@
         <v>27.3600006103516</v>
       </c>
       <c r="G505" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16399,7 +16399,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G506" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16425,7 +16425,7 @@
         <v>27.5699996948242</v>
       </c>
       <c r="G507" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16451,7 +16451,7 @@
         <v>27.5799999237061</v>
       </c>
       <c r="G508" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16477,7 +16477,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G509" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16503,7 +16503,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G510" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16529,7 +16529,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G511" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16555,7 +16555,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G512" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -16581,7 +16581,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G513" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -16607,7 +16607,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G514" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -16633,7 +16633,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G515" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -16659,7 +16659,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G516" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16685,7 +16685,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G517" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -16711,7 +16711,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G518" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -16737,7 +16737,7 @@
         <v>29.5</v>
       </c>
       <c r="G519" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -16763,7 +16763,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G520" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -16789,7 +16789,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G521" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -16815,7 +16815,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G522" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -16841,7 +16841,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G523" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -16867,7 +16867,7 @@
         <v>31</v>
       </c>
       <c r="G524" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -16893,7 +16893,7 @@
         <v>31.5</v>
       </c>
       <c r="G525" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -16919,7 +16919,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G526" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -16945,7 +16945,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G527" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -16971,7 +16971,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G528" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -16997,7 +16997,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G529" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -17023,7 +17023,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G530" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17049,7 +17049,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G531" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17075,7 +17075,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G532" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17101,7 +17101,7 @@
         <v>30.5</v>
       </c>
       <c r="G533" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17127,7 +17127,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G534" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -17153,7 +17153,7 @@
         <v>30</v>
       </c>
       <c r="G535" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17179,7 +17179,7 @@
         <v>30</v>
       </c>
       <c r="G536" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17205,7 +17205,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G537" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17231,7 +17231,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G538" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17257,7 +17257,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G539" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17283,7 +17283,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G540" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17309,7 +17309,7 @@
         <v>29</v>
       </c>
       <c r="G541" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17335,7 +17335,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G542" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17361,7 +17361,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G543" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17387,7 +17387,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G544" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17413,7 +17413,7 @@
         <v>30</v>
       </c>
       <c r="G545" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17439,7 +17439,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G546" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17465,7 +17465,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G547" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17491,7 +17491,7 @@
         <v>31.5</v>
       </c>
       <c r="G548" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17517,7 +17517,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G549" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17543,7 +17543,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G550" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17569,7 +17569,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G551" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17595,7 +17595,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G552" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17621,7 +17621,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G553" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17647,7 +17647,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G554" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17673,7 +17673,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G555" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17699,7 +17699,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G556" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17725,7 +17725,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G557" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -17751,7 +17751,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G558" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -17777,7 +17777,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G559" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -17803,7 +17803,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G560" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -17829,7 +17829,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G561" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -17855,7 +17855,7 @@
         <v>32.5</v>
       </c>
       <c r="G562" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -17881,7 +17881,7 @@
         <v>32</v>
       </c>
       <c r="G563" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -17907,7 +17907,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G564" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -17933,7 +17933,7 @@
         <v>32.5</v>
       </c>
       <c r="G565" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -17959,7 +17959,7 @@
         <v>33</v>
       </c>
       <c r="G566" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -17985,7 +17985,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G567" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18011,7 +18011,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G568" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18037,7 +18037,7 @@
         <v>32.5</v>
       </c>
       <c r="G569" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18063,7 +18063,7 @@
         <v>32.5</v>
       </c>
       <c r="G570" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18089,7 +18089,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G571" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18115,7 +18115,7 @@
         <v>32.5</v>
       </c>
       <c r="G572" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18141,7 +18141,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G573" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18167,7 +18167,7 @@
         <v>32.5</v>
       </c>
       <c r="G574" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18193,7 +18193,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G575" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18219,7 +18219,7 @@
         <v>32.5</v>
       </c>
       <c r="G576" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18245,7 +18245,7 @@
         <v>32.5</v>
       </c>
       <c r="G577" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18271,7 +18271,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G578" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18297,7 +18297,7 @@
         <v>32.5</v>
       </c>
       <c r="G579" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18323,7 +18323,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G580" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18349,7 +18349,7 @@
         <v>32.5</v>
       </c>
       <c r="G581" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18375,7 +18375,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G582" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18401,7 +18401,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G583" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18427,7 +18427,7 @@
         <v>33</v>
       </c>
       <c r="G584" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18453,7 +18453,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G585" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18479,7 +18479,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G586" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18505,7 +18505,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G587" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18531,7 +18531,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G588" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18557,7 +18557,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G589" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18583,7 +18583,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G590" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18609,7 +18609,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G591" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18635,7 +18635,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G592" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18661,7 +18661,7 @@
         <v>33</v>
       </c>
       <c r="G593" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18687,7 +18687,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G594" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18713,7 +18713,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G595" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18739,7 +18739,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G596" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -18765,7 +18765,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G597" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -18791,7 +18791,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G598" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -18817,7 +18817,7 @@
         <v>32.5</v>
       </c>
       <c r="G599" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -18843,7 +18843,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G600" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -18869,7 +18869,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G601" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -18895,7 +18895,7 @@
         <v>32</v>
       </c>
       <c r="G602" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -18921,7 +18921,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G603" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18947,7 +18947,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G604" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -18973,7 +18973,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G605" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -18999,7 +18999,7 @@
         <v>32</v>
       </c>
       <c r="G606" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19025,7 +19025,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G607" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19051,7 +19051,7 @@
         <v>30</v>
       </c>
       <c r="G608" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19077,7 +19077,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G609" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19103,7 +19103,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G610" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19129,7 +19129,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G611" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19155,7 +19155,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G612" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19181,7 +19181,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G613" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19207,7 +19207,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G614" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19233,7 +19233,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G615" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19259,7 +19259,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G616" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19285,7 +19285,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G617" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19311,7 +19311,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G618" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19337,7 +19337,7 @@
         <v>28</v>
       </c>
       <c r="G619" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19363,7 +19363,7 @@
         <v>28</v>
       </c>
       <c r="G620" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19389,7 +19389,7 @@
         <v>28</v>
       </c>
       <c r="G621" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19415,7 +19415,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G622" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19441,7 +19441,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G623" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19467,7 +19467,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G624" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19493,7 +19493,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G625" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19519,7 +19519,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G626" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19545,7 +19545,7 @@
         <v>29</v>
       </c>
       <c r="G627" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19571,7 +19571,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G628" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19597,7 +19597,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G629" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19623,7 +19623,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G630" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19649,7 +19649,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G631" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19675,7 +19675,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G632" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19701,7 +19701,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G633" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19727,7 +19727,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G634" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19753,7 +19753,7 @@
         <v>27.5</v>
       </c>
       <c r="G635" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19779,7 +19779,7 @@
         <v>27</v>
       </c>
       <c r="G636" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19805,7 +19805,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G637" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19831,7 +19831,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G638" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19857,7 +19857,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G639" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19883,7 +19883,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G640" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19909,7 +19909,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G641" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -19935,7 +19935,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G642" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19961,7 +19961,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G643" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19987,7 +19987,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G644" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20013,7 +20013,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G645" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20039,7 +20039,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G646" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20065,7 +20065,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G647" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20091,7 +20091,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G648" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20117,7 +20117,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G649" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20143,7 +20143,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G650" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20169,7 +20169,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G651" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20195,7 +20195,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G652" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20221,7 +20221,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G653" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20247,7 +20247,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G654" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20273,7 +20273,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G655" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20299,7 +20299,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G656" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20325,7 +20325,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G657" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20351,7 +20351,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G658" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20377,7 +20377,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G659" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20403,7 +20403,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G660" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20429,7 +20429,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G661" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20455,7 +20455,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G662" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20481,7 +20481,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G663" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -20507,7 +20507,7 @@
         <v>27.5</v>
       </c>
       <c r="G664" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20533,7 +20533,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G665" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20559,7 +20559,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G666" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20585,7 +20585,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G667" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20611,7 +20611,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G668" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20637,7 +20637,7 @@
         <v>27</v>
       </c>
       <c r="G669" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20663,7 +20663,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G670" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20689,7 +20689,7 @@
         <v>27</v>
       </c>
       <c r="G671" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20715,7 +20715,7 @@
         <v>26</v>
       </c>
       <c r="G672" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20741,7 +20741,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G673" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20767,7 +20767,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G674" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20793,7 +20793,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G675" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20819,7 +20819,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G676" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20845,7 +20845,7 @@
         <v>25</v>
       </c>
       <c r="G677" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20871,7 +20871,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G678" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20897,7 +20897,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G679" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -20923,7 +20923,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G680" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -20949,7 +20949,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G681" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -20975,7 +20975,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G682" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21001,7 +21001,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G683" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21027,7 +21027,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G684" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21053,7 +21053,7 @@
         <v>24</v>
       </c>
       <c r="G685" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21079,7 +21079,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G686" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21105,7 +21105,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G687" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21131,7 +21131,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G688" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21157,7 +21157,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G689" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21183,7 +21183,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G690" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21209,7 +21209,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G691" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21235,7 +21235,7 @@
         <v>27</v>
       </c>
       <c r="G692" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21261,7 +21261,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G693" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21287,7 +21287,7 @@
         <v>26</v>
       </c>
       <c r="G694" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21313,7 +21313,7 @@
         <v>26</v>
       </c>
       <c r="G695" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21339,7 +21339,7 @@
         <v>26</v>
       </c>
       <c r="G696" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21365,7 +21365,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G697" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21391,7 +21391,7 @@
         <v>26</v>
       </c>
       <c r="G698" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21417,7 +21417,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G699" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21443,7 +21443,7 @@
         <v>26</v>
       </c>
       <c r="G700" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21469,7 +21469,7 @@
         <v>25.5</v>
       </c>
       <c r="G701" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21495,7 +21495,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G702" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -21521,7 +21521,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G703" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21547,7 +21547,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G704" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21573,7 +21573,7 @@
         <v>26</v>
       </c>
       <c r="G705" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21599,7 +21599,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G706" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21625,7 +21625,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G707" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21651,7 +21651,7 @@
         <v>25.5</v>
       </c>
       <c r="G708" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21677,7 +21677,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G709" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21703,7 +21703,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G710" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21729,7 +21729,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G711" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21755,7 +21755,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G712" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21781,7 +21781,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G713" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21807,7 +21807,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G714" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21833,7 +21833,7 @@
         <v>24</v>
       </c>
       <c r="G715" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21859,7 +21859,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G716" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21885,7 +21885,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G717" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21911,7 +21911,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G718" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -21937,7 +21937,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G719" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -21963,7 +21963,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G720" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21989,7 +21989,7 @@
         <v>22.5</v>
       </c>
       <c r="G721" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22015,7 +22015,7 @@
         <v>23.5</v>
       </c>
       <c r="G722" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22041,7 +22041,7 @@
         <v>23.5</v>
       </c>
       <c r="G723" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22067,7 +22067,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G724" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22093,7 +22093,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G725" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22119,7 +22119,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G726" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22145,7 +22145,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G727" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22171,7 +22171,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G728" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22197,7 +22197,7 @@
         <v>25</v>
       </c>
       <c r="G729" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22223,7 +22223,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G730" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22249,7 +22249,7 @@
         <v>28</v>
       </c>
       <c r="G731" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22275,7 +22275,7 @@
         <v>28.5</v>
       </c>
       <c r="G732" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22301,7 +22301,7 @@
         <v>27.5</v>
       </c>
       <c r="G733" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22327,7 +22327,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G734" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22353,7 +22353,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G735" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22379,7 +22379,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G736" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22405,7 +22405,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G737" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22431,7 +22431,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G738" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22457,7 +22457,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G739" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -22483,7 +22483,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G740" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -22509,7 +22509,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G741" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22535,7 +22535,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G742" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22561,7 +22561,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G743" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22587,7 +22587,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G744" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22613,7 +22613,7 @@
         <v>27.5</v>
       </c>
       <c r="G745" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22639,7 +22639,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G746" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22665,7 +22665,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G747" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22691,7 +22691,7 @@
         <v>27.5</v>
       </c>
       <c r="G748" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22717,7 +22717,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G749" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22743,7 +22743,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G750" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22769,7 +22769,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G751" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22795,7 +22795,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G752" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22821,7 +22821,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G753" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22847,7 +22847,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G754" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22873,7 +22873,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G755" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22899,7 +22899,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G756" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -22925,7 +22925,7 @@
         <v>26.5</v>
       </c>
       <c r="G757" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -22951,7 +22951,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G758" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -22977,7 +22977,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G759" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23003,7 +23003,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G760" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23029,7 +23029,7 @@
         <v>27</v>
       </c>
       <c r="G761" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23055,7 +23055,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G762" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23081,7 +23081,7 @@
         <v>27</v>
       </c>
       <c r="G763" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23107,7 +23107,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G764" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23133,7 +23133,7 @@
         <v>26.5</v>
       </c>
       <c r="G765" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23159,7 +23159,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G766" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23185,7 +23185,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G767" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23211,7 +23211,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G768" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23237,7 +23237,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G769" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23263,7 +23263,7 @@
         <v>28.5</v>
       </c>
       <c r="G770" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23289,7 +23289,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G771" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23315,7 +23315,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G772" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23341,7 +23341,7 @@
         <v>28</v>
       </c>
       <c r="G773" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23367,7 +23367,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G774" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23393,7 +23393,7 @@
         <v>28</v>
       </c>
       <c r="G775" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23419,7 +23419,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G776" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23445,7 +23445,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G777" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23471,7 +23471,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G778" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -23497,7 +23497,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G779" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -23523,7 +23523,7 @@
         <v>28.5</v>
       </c>
       <c r="G780" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23549,7 +23549,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G781" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23575,7 +23575,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G782" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23601,7 +23601,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G783" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23627,7 +23627,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G784" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23653,7 +23653,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G785" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23679,7 +23679,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G786" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23705,7 +23705,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G787" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23731,7 +23731,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G788" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23757,7 +23757,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G789" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23783,7 +23783,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G790" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23809,7 +23809,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G791" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23835,7 +23835,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G792" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23861,7 +23861,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G793" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23887,7 +23887,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G794" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23913,7 +23913,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G795" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -23939,7 +23939,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G796" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -23965,7 +23965,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G797" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -23991,7 +23991,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G798" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24017,7 +24017,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G799" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24043,7 +24043,7 @@
         <v>30</v>
       </c>
       <c r="G800" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24069,7 +24069,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G801" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24095,7 +24095,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G802" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24121,7 +24121,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G803" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24147,7 +24147,7 @@
         <v>31</v>
       </c>
       <c r="G804" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24173,7 +24173,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G805" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24199,7 +24199,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G806" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24225,7 +24225,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G807" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24251,7 +24251,7 @@
         <v>31</v>
       </c>
       <c r="G808" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24277,7 +24277,7 @@
         <v>31</v>
       </c>
       <c r="G809" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24303,7 +24303,7 @@
         <v>31</v>
       </c>
       <c r="G810" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24329,7 +24329,7 @@
         <v>31</v>
       </c>
       <c r="G811" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24355,7 +24355,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G812" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24381,7 +24381,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G813" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24407,7 +24407,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G814" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24433,7 +24433,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G815" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24459,7 +24459,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G816" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -24485,7 +24485,7 @@
         <v>31</v>
       </c>
       <c r="G817" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -24511,7 +24511,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G818" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24537,7 +24537,7 @@
         <v>31</v>
       </c>
       <c r="G819" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24563,7 +24563,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G820" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24589,7 +24589,7 @@
         <v>30.5</v>
       </c>
       <c r="G821" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24615,7 +24615,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G822" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24641,7 +24641,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G823" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24667,7 +24667,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G824" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24693,7 +24693,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G825" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24719,7 +24719,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G826" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24745,7 +24745,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G827" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24771,7 +24771,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G828" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24797,7 +24797,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G829" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24823,7 +24823,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G830" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24849,7 +24849,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G831" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24875,7 +24875,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G832" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24901,7 +24901,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G833" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -24927,7 +24927,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G834" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -24953,7 +24953,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G835" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -24979,7 +24979,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G836" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25005,7 +25005,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G837" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25031,7 +25031,7 @@
         <v>31</v>
       </c>
       <c r="G838" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25057,7 +25057,7 @@
         <v>31</v>
       </c>
       <c r="G839" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25083,7 +25083,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G840" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25109,7 +25109,7 @@
         <v>30</v>
       </c>
       <c r="G841" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25135,7 +25135,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G842" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25161,7 +25161,7 @@
         <v>30.5</v>
       </c>
       <c r="G843" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25187,7 +25187,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G844" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25213,7 +25213,7 @@
         <v>30.5</v>
       </c>
       <c r="G845" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25239,7 +25239,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G846" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25265,7 +25265,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G847" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25291,7 +25291,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G848" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25317,7 +25317,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G849" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25343,7 +25343,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G850" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25369,7 +25369,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G851" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25395,7 +25395,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G852" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -25421,7 +25421,7 @@
         <v>28</v>
       </c>
       <c r="G853" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -25447,7 +25447,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G854" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -25473,7 +25473,7 @@
         <v>28</v>
       </c>
       <c r="G855" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -25499,7 +25499,7 @@
         <v>27.5</v>
       </c>
       <c r="G856" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25525,7 +25525,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G857" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25551,7 +25551,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G858" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25577,7 +25577,7 @@
         <v>27.5</v>
       </c>
       <c r="G859" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25603,7 +25603,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G860" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25629,7 +25629,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G861" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25655,7 +25655,7 @@
         <v>28</v>
       </c>
       <c r="G862" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25681,7 +25681,7 @@
         <v>29</v>
       </c>
       <c r="G863" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25707,7 +25707,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G864" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25733,7 +25733,7 @@
         <v>29</v>
       </c>
       <c r="G865" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25759,7 +25759,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G866" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -25785,7 +25785,7 @@
         <v>29</v>
       </c>
       <c r="G867" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25811,7 +25811,7 @@
         <v>29</v>
       </c>
       <c r="G868" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -25837,7 +25837,7 @@
         <v>29</v>
       </c>
       <c r="G869" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -25863,7 +25863,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G870" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -25889,7 +25889,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G871" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25915,7 +25915,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G872" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -25941,7 +25941,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G873" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -25967,7 +25967,7 @@
         <v>30.5</v>
       </c>
       <c r="G874" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -25993,7 +25993,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G875" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -26019,7 +26019,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G876" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -26045,7 +26045,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G877" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -26071,7 +26071,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G878" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -26097,7 +26097,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G879" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26123,7 +26123,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G880" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -26149,7 +26149,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G881" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -26175,7 +26175,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G882" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -26201,7 +26201,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G883" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -26227,7 +26227,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G884" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -26253,7 +26253,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G885" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -26279,7 +26279,7 @@
         <v>31.5</v>
       </c>
       <c r="G886" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -26305,7 +26305,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G887" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -26331,7 +26331,7 @@
         <v>32</v>
       </c>
       <c r="G888" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -26357,7 +26357,7 @@
         <v>31.5</v>
       </c>
       <c r="G889" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -26383,7 +26383,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G890" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -26409,7 +26409,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G891" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -26435,7 +26435,7 @@
         <v>32</v>
       </c>
       <c r="G892" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -26461,7 +26461,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G893" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -26487,7 +26487,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G894" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -26513,7 +26513,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26539,7 +26539,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G896" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -26565,7 +26565,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G897" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -26591,7 +26591,7 @@
         <v>31</v>
       </c>
       <c r="G898" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -26617,7 +26617,7 @@
         <v>31</v>
       </c>
       <c r="G899" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -26643,7 +26643,7 @@
         <v>31</v>
       </c>
       <c r="G900" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -26669,7 +26669,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G901" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -26695,7 +26695,7 @@
         <v>31</v>
       </c>
       <c r="G902" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -26721,7 +26721,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G903" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -26747,7 +26747,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G904" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -26773,7 +26773,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G905" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -26799,7 +26799,7 @@
         <v>31</v>
       </c>
       <c r="G906" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -26825,7 +26825,7 @@
         <v>31</v>
       </c>
       <c r="G907" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -26851,7 +26851,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G908" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -26877,7 +26877,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G909" t="s">
-        <v>524</v>
+        <v>490</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -26903,7 +26903,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G910" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -26929,7 +26929,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G911" t="s">
-        <v>524</v>
+        <v>490</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -26955,7 +26955,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G912" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -26981,7 +26981,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G913" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -27007,7 +27007,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G914" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -27033,7 +27033,7 @@
         <v>30</v>
       </c>
       <c r="G915" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -27059,7 +27059,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G916" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -27111,7 +27111,7 @@
         <v>29</v>
       </c>
       <c r="G918" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -27163,7 +27163,7 @@
         <v>29</v>
       </c>
       <c r="G920" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -27241,7 +27241,7 @@
         <v>29</v>
       </c>
       <c r="G923" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -27267,7 +27267,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G924" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -27293,7 +27293,7 @@
         <v>29</v>
       </c>
       <c r="G925" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -27319,7 +27319,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G926" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -27345,7 +27345,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G927" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -27371,7 +27371,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G928" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -27423,7 +27423,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G930" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -27449,7 +27449,7 @@
         <v>30.5</v>
       </c>
       <c r="G931" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -27475,7 +27475,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G932" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -27579,7 +27579,7 @@
         <v>30</v>
       </c>
       <c r="G936" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -27657,7 +27657,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G939" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -27683,7 +27683,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G940" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -27709,7 +27709,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G941" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -27735,7 +27735,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G942" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -27761,7 +27761,7 @@
         <v>30</v>
       </c>
       <c r="G943" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -27787,7 +27787,7 @@
         <v>30</v>
       </c>
       <c r="G944" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -27839,7 +27839,7 @@
         <v>30</v>
       </c>
       <c r="G946" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -27865,7 +27865,7 @@
         <v>30.5</v>
       </c>
       <c r="G947" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -27891,7 +27891,7 @@
         <v>30.5</v>
       </c>
       <c r="G948" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -27917,7 +27917,7 @@
         <v>30</v>
       </c>
       <c r="G949" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -27969,7 +27969,7 @@
         <v>30</v>
       </c>
       <c r="G951" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -28021,7 +28021,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G953" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -28073,7 +28073,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G955" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -28099,7 +28099,7 @@
         <v>30</v>
       </c>
       <c r="G956" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -28125,7 +28125,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G957" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -28151,7 +28151,7 @@
         <v>30</v>
       </c>
       <c r="G958" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -28177,7 +28177,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G959" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -28203,7 +28203,7 @@
         <v>30</v>
       </c>
       <c r="G960" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -28229,7 +28229,7 @@
         <v>30</v>
       </c>
       <c r="G961" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -28255,7 +28255,7 @@
         <v>30</v>
       </c>
       <c r="G962" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -28281,7 +28281,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G963" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -28307,7 +28307,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G964" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -28333,7 +28333,7 @@
         <v>30</v>
       </c>
       <c r="G965" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -28359,7 +28359,7 @@
         <v>30</v>
       </c>
       <c r="G966" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -28411,7 +28411,7 @@
         <v>30</v>
       </c>
       <c r="G968" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -28437,7 +28437,7 @@
         <v>30</v>
       </c>
       <c r="G969" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -28515,7 +28515,7 @@
         <v>30</v>
       </c>
       <c r="G972" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -28567,7 +28567,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G974" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -28593,7 +28593,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G975" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -28645,7 +28645,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G977" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -28671,7 +28671,7 @@
         <v>31</v>
       </c>
       <c r="G978" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28697,7 +28697,7 @@
         <v>31</v>
       </c>
       <c r="G979" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -28723,7 +28723,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G980" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28749,7 +28749,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G981" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -28775,7 +28775,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G982" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -28801,7 +28801,7 @@
         <v>31</v>
       </c>
       <c r="G983" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -28827,7 +28827,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G984" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -28853,7 +28853,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G985" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28879,7 +28879,7 @@
         <v>31</v>
       </c>
       <c r="G986" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -28905,7 +28905,7 @@
         <v>31.5</v>
       </c>
       <c r="G987" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -28931,7 +28931,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G988" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -28957,7 +28957,7 @@
         <v>31.5</v>
       </c>
       <c r="G989" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -28983,7 +28983,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G990" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -29009,7 +29009,7 @@
         <v>31.5</v>
       </c>
       <c r="G991" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -29035,7 +29035,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G992" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -29061,7 +29061,7 @@
         <v>31.5</v>
       </c>
       <c r="G993" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -29087,7 +29087,7 @@
         <v>31.5</v>
       </c>
       <c r="G994" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -29113,7 +29113,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G995" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -29139,7 +29139,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G996" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -29165,7 +29165,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G997" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -29191,7 +29191,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G998" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -29217,7 +29217,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G999" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -29243,7 +29243,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1000" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -29269,7 +29269,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1001" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -29295,7 +29295,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1002" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -29321,7 +29321,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1003" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -29347,7 +29347,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1004" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -29373,7 +29373,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1005" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -29399,7 +29399,7 @@
         <v>31</v>
       </c>
       <c r="G1006" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -29425,7 +29425,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1007" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -29451,7 +29451,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1008" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -29477,7 +29477,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1009" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -29503,7 +29503,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1010" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -29529,7 +29529,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1011" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -29555,7 +29555,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1012" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -29581,7 +29581,7 @@
         <v>30.5</v>
       </c>
       <c r="G1013" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -29607,7 +29607,7 @@
         <v>30.5</v>
       </c>
       <c r="G1014" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -29659,7 +29659,7 @@
         <v>30.5</v>
       </c>
       <c r="G1016" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -29711,7 +29711,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1018" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -29737,7 +29737,7 @@
         <v>30</v>
       </c>
       <c r="G1019" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -29763,7 +29763,7 @@
         <v>30.5</v>
       </c>
       <c r="G1020" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -29789,7 +29789,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1021" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -29815,7 +29815,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1022" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -29841,7 +29841,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1023" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -29867,7 +29867,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1024" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -29893,7 +29893,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1025" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -29919,7 +29919,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1026" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -29945,7 +29945,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1027" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -29971,7 +29971,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1028" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -29997,7 +29997,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1029" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -30023,7 +30023,7 @@
         <v>30</v>
       </c>
       <c r="G1030" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -30049,7 +30049,7 @@
         <v>30</v>
       </c>
       <c r="G1031" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -30075,7 +30075,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1032" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -30257,7 +30257,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1039" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -30283,7 +30283,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1040" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -30309,7 +30309,7 @@
         <v>28</v>
       </c>
       <c r="G1041" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -30439,7 +30439,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1046" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -30491,7 +30491,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1048" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -30517,7 +30517,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1049" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -30569,7 +30569,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1051" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -30595,7 +30595,7 @@
         <v>28</v>
       </c>
       <c r="G1052" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -30673,7 +30673,7 @@
         <v>27.5</v>
       </c>
       <c r="G1055" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -36939,7 +36939,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1296" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -36965,7 +36965,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1297" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -37017,7 +37017,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1299" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -37069,7 +37069,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1301" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -37095,7 +37095,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1302" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -37121,7 +37121,7 @@
         <v>29</v>
       </c>
       <c r="G1303" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -37147,7 +37147,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1304" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -37173,7 +37173,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1305" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -37277,7 +37277,7 @@
         <v>28</v>
       </c>
       <c r="G1309" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -37303,7 +37303,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1310" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -37329,7 +37329,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1311" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -37407,7 +37407,7 @@
         <v>28</v>
       </c>
       <c r="G1314" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -37433,7 +37433,7 @@
         <v>28</v>
       </c>
       <c r="G1315" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -37459,7 +37459,7 @@
         <v>28</v>
       </c>
       <c r="G1316" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -37823,7 +37823,7 @@
         <v>27.5</v>
       </c>
       <c r="G1330" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -38005,7 +38005,7 @@
         <v>27.5</v>
       </c>
       <c r="G1337" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -67887,7 +67887,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.5283449074</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>8862</v>
@@ -67908,6 +67908,32 @@
         <v>966</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.5397916667</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>4054</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>2.79500007629395</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>2.73499989509583</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>2.79500007629395</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>954</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24616146087646</t>
+    <t xml:space="preserve">1.24616158008575</t>
   </si>
   <si>
     <t xml:space="preserve">AUTME.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24544656276703</t>
+    <t xml:space="preserve">1.24544644355774</t>
   </si>
   <si>
     <t xml:space="preserve">1.24330174922943</t>
@@ -53,28 +53,28 @@
     <t xml:space="preserve">1.22256815433502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21541845798492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22185301780701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2147034406662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23615217208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21327376365662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20683884620667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2011194229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20040464401245</t>
+    <t xml:space="preserve">1.21541857719421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22185325622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21470367908478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23615229129791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21327352523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20683920383453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20111930370331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20040452480316</t>
   </si>
   <si>
     <t xml:space="preserve">1.1668016910553</t>
@@ -83,13 +83,13 @@
     <t xml:space="preserve">1.1946849822998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25688588619232</t>
+    <t xml:space="preserve">1.25688564777374</t>
   </si>
   <si>
     <t xml:space="preserve">1.25045120716095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24687647819519</t>
+    <t xml:space="preserve">1.2468763589859</t>
   </si>
   <si>
     <t xml:space="preserve">1.25116622447968</t>
@@ -98,13 +98,13 @@
     <t xml:space="preserve">1.26475036144257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23543739318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22542786598206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21041393280029</t>
+    <t xml:space="preserve">1.23543727397919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22542774677277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.210413813591</t>
   </si>
   <si>
     <t xml:space="preserve">1.22113811969757</t>
@@ -113,40 +113,40 @@
     <t xml:space="preserve">1.19397008419037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22685790061951</t>
+    <t xml:space="preserve">1.2268580198288</t>
   </si>
   <si>
     <t xml:space="preserve">1.20469427108765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25831580162048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.265465259552</t>
+    <t xml:space="preserve">1.25831568241119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26546537876129</t>
   </si>
   <si>
     <t xml:space="preserve">1.25903058052063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26904010772705</t>
+    <t xml:space="preserve">1.26903986930847</t>
   </si>
   <si>
     <t xml:space="preserve">1.21684849262238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22828757762909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2740443944931</t>
+    <t xml:space="preserve">1.22828769683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27404463291168</t>
   </si>
   <si>
     <t xml:space="preserve">1.26689505577087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27261483669281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27189981937408</t>
+    <t xml:space="preserve">1.27261459827423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27189970016479</t>
   </si>
   <si>
     <t xml:space="preserve">1.27904915809631</t>
@@ -161,19 +161,19 @@
     <t xml:space="preserve">1.26260542869568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24830639362335</t>
+    <t xml:space="preserve">1.24830615520477</t>
   </si>
   <si>
     <t xml:space="preserve">1.2490211725235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24258685112</t>
+    <t xml:space="preserve">1.24258649349213</t>
   </si>
   <si>
     <t xml:space="preserve">1.23686695098877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23472237586975</t>
+    <t xml:space="preserve">1.23472225666046</t>
   </si>
   <si>
     <t xml:space="preserve">1.23400735855103</t>
@@ -182,13 +182,13 @@
     <t xml:space="preserve">1.25225365161896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26176798343658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26835501194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27860128879547</t>
+    <t xml:space="preserve">1.26176822185516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26835513114929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27860140800476</t>
   </si>
   <si>
     <t xml:space="preserve">1.27640581130981</t>
@@ -197,28 +197,28 @@
     <t xml:space="preserve">1.27421009540558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27494204044342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26323187351227</t>
+    <t xml:space="preserve">1.27494192123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26323175430298</t>
   </si>
   <si>
     <t xml:space="preserve">1.27128255367279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26689112186432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28445637226105</t>
+    <t xml:space="preserve">1.26689124107361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28445649147034</t>
   </si>
   <si>
     <t xml:space="preserve">1.280797123909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2793333530426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27347826957703</t>
+    <t xml:space="preserve">1.27933311462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27347815036774</t>
   </si>
   <si>
     <t xml:space="preserve">1.27274632453918</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">1.26396381855011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24127519130707</t>
+    <t xml:space="preserve">1.24127542972565</t>
   </si>
   <si>
     <t xml:space="preserve">1.2434709072113</t>
@@ -251,7 +251,7 @@
     <t xml:space="preserve">1.22956514358521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23468863964081</t>
+    <t xml:space="preserve">1.23468852043152</t>
   </si>
   <si>
     <t xml:space="preserve">1.22663772106171</t>
@@ -260,19 +260,19 @@
     <t xml:space="preserve">1.20687675476074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20760869979858</t>
+    <t xml:space="preserve">1.20760881900787</t>
   </si>
   <si>
     <t xml:space="preserve">1.18565225601196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17833340167999</t>
+    <t xml:space="preserve">1.1783332824707</t>
   </si>
   <si>
     <t xml:space="preserve">1.18784785270691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16955077648163</t>
+    <t xml:space="preserve">1.16955065727234</t>
   </si>
   <si>
     <t xml:space="preserve">1.17101454734802</t>
@@ -290,13 +290,13 @@
     <t xml:space="preserve">1.22151458263397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23981153964996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2390798330307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23834788799286</t>
+    <t xml:space="preserve">1.23981165885925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23907971382141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23834800720215</t>
   </si>
   <si>
     <t xml:space="preserve">1.23542010784149</t>
@@ -305,10 +305,10 @@
     <t xml:space="preserve">1.2061448097229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2310289144516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19736230373383</t>
+    <t xml:space="preserve">1.23102903366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19736242294312</t>
   </si>
   <si>
     <t xml:space="preserve">1.2171231508255</t>
@@ -317,28 +317,28 @@
     <t xml:space="preserve">1.22297823429108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23322463035583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23249280452728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22883343696594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28518843650818</t>
+    <t xml:space="preserve">1.23322474956512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23249268531799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22883331775665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28518831729889</t>
   </si>
   <si>
     <t xml:space="preserve">1.25884056091309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3071448802948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29909431934357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32324624061584</t>
+    <t xml:space="preserve">1.30714499950409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29909420013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32324635982513</t>
   </si>
   <si>
     <t xml:space="preserve">1.31665945053101</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">1.32763755321503</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30348539352417</t>
+    <t xml:space="preserve">1.30348551273346</t>
   </si>
   <si>
     <t xml:space="preserve">1.31592750549316</t>
@@ -356,22 +356,22 @@
     <t xml:space="preserve">1.3181232213974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29763031005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30275368690491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29982590675354</t>
+    <t xml:space="preserve">1.29763042926788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30275344848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29982614517212</t>
   </si>
   <si>
     <t xml:space="preserve">1.28884780406952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29543471336365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30055797100067</t>
+    <t xml:space="preserve">1.29543483257294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30055809020996</t>
   </si>
   <si>
     <t xml:space="preserve">1.29836225509644</t>
@@ -380,13 +380,13 @@
     <t xml:space="preserve">1.2932391166687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29250729084015</t>
+    <t xml:space="preserve">1.29250717163086</t>
   </si>
   <si>
     <t xml:space="preserve">1.30128991603851</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30568099021912</t>
+    <t xml:space="preserve">1.3056812286377</t>
   </si>
   <si>
     <t xml:space="preserve">1.26908695697784</t>
@@ -395,43 +395,46 @@
     <t xml:space="preserve">1.26762318611145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24786233901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25518095493317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2654275894165</t>
+    <t xml:space="preserve">1.24786221981049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25518119335175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26542747020721</t>
   </si>
   <si>
     <t xml:space="preserve">1.28006517887115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25810873508453</t>
+    <t xml:space="preserve">1.25810861587524</t>
   </si>
   <si>
     <t xml:space="preserve">1.25005793571472</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24054360389709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24639856815338</t>
+    <t xml:space="preserve">1.24054336547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24639868736267</t>
   </si>
   <si>
     <t xml:space="preserve">1.24420285224915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23688399791718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24200737476349</t>
+    <t xml:space="preserve">1.23615205287933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23688411712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24200713634491</t>
   </si>
   <si>
     <t xml:space="preserve">1.23176085948944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20980453491211</t>
+    <t xml:space="preserve">1.20980441570282</t>
   </si>
   <si>
     <t xml:space="preserve">1.21126806735992</t>
@@ -446,13 +449,13 @@
     <t xml:space="preserve">1.19004333019257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18199276924133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21419560909271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19297087192535</t>
+    <t xml:space="preserve">1.18199265003204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.214195728302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19297099113464</t>
   </si>
   <si>
     <t xml:space="preserve">1.19663047790527</t>
@@ -461,22 +464,22 @@
     <t xml:space="preserve">1.22005069255829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21639132499695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25957238674164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27786958217621</t>
+    <t xml:space="preserve">1.21639144420624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25957226753235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27786946296692</t>
   </si>
   <si>
     <t xml:space="preserve">1.28592026233673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29470300674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29689848423004</t>
+    <t xml:space="preserve">1.29470276832581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29689836502075</t>
   </si>
   <si>
     <t xml:space="preserve">1.31007242202759</t>
@@ -485,19 +488,19 @@
     <t xml:space="preserve">1.32544195652008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34081149101257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33349275588989</t>
+    <t xml:space="preserve">1.34081161022186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3334926366806</t>
   </si>
   <si>
     <t xml:space="preserve">1.33422458171844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3320289850235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33861589431763</t>
+    <t xml:space="preserve">1.33202910423279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33861601352692</t>
   </si>
   <si>
     <t xml:space="preserve">1.33934772014618</t>
@@ -506,16 +509,16 @@
     <t xml:space="preserve">1.34666669368744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34227538108826</t>
+    <t xml:space="preserve">1.34227526187897</t>
   </si>
   <si>
     <t xml:space="preserve">1.34007966518402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32690560817719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3210506439209</t>
+    <t xml:space="preserve">1.32690572738647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32105088233948</t>
   </si>
   <si>
     <t xml:space="preserve">1.34593486785889</t>
@@ -524,91 +527,91 @@
     <t xml:space="preserve">1.36130428314209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36057245731354</t>
+    <t xml:space="preserve">1.36057257652283</t>
   </si>
   <si>
     <t xml:space="preserve">1.33276081085205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34959411621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33788406848907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34373915195465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34520292282104</t>
+    <t xml:space="preserve">1.34959423542023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33788418769836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34373903274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34520280361176</t>
   </si>
   <si>
     <t xml:space="preserve">1.32910144329071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36349999904633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3678914308548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37667393684387</t>
+    <t xml:space="preserve">1.36349987983704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36789131164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37667381763458</t>
   </si>
   <si>
     <t xml:space="preserve">1.38252890110016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39789867401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41253614425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40668118000031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40814471244812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40887665748596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40302169322968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39277541637421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36935484409332</t>
+    <t xml:space="preserve">1.39789855480194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4125360250473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40668106079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40814483165741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40887689590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40302181243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39277529716492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36935496330261</t>
   </si>
   <si>
     <t xml:space="preserve">1.37886953353882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38911592960358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40155804157257</t>
+    <t xml:space="preserve">1.38911581039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40155780315399</t>
   </si>
   <si>
     <t xml:space="preserve">1.49304342269897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47621011734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48206508159637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49157977104187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50328993797302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46742749214172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45864510536194</t>
+    <t xml:space="preserve">1.47621023654938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48206532001495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49157989025116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50328969955444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46742761135101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45864474773407</t>
   </si>
   <si>
     <t xml:space="preserve">1.47913765907288</t>
@@ -617,10 +620,10 @@
     <t xml:space="preserve">1.49523901939392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49084782600403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48792028427124</t>
+    <t xml:space="preserve">1.49084794521332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48792040348053</t>
   </si>
   <si>
     <t xml:space="preserve">1.52744209766388</t>
@@ -632,25 +635,25 @@
     <t xml:space="preserve">1.53256523609161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52963757514954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53183341026306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52817404270172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51500010490417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4996303319931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49816644191742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.485724568367</t>
+    <t xml:space="preserve">1.52963781356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53183329105377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52817392349243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5149998664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49963057041168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.498166680336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48572444915771</t>
   </si>
   <si>
     <t xml:space="preserve">1.47108697891235</t>
@@ -659,16 +662,16 @@
     <t xml:space="preserve">1.4842609167099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46376812458038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45498561859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48499286174774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52085494995117</t>
+    <t xml:space="preserve">1.46376800537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45498538017273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48499274253845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52085518836975</t>
   </si>
   <si>
     <t xml:space="preserve">1.53768837451935</t>
@@ -677,73 +680,73 @@
     <t xml:space="preserve">1.58233344554901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63126361370087</t>
+    <t xml:space="preserve">1.63126385211945</t>
   </si>
   <si>
     <t xml:space="preserve">1.63427472114563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64857733249664</t>
+    <t xml:space="preserve">1.64857757091522</t>
   </si>
   <si>
     <t xml:space="preserve">1.63578033447266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66664397716522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66288042068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66137456893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76902151107788</t>
+    <t xml:space="preserve">1.6666442155838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66288018226624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66137480735779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76902163028717</t>
   </si>
   <si>
     <t xml:space="preserve">1.8081659078598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84429907798767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91656529903412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99485409259796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01367330551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95345139503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98205709457397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93011546134949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83376026153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90301549434662</t>
+    <t xml:space="preserve">1.84429919719696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9165655374527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99485397338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01367378234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95345163345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98205697536469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9301153421402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83376014232635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90301585197449</t>
   </si>
   <si>
     <t xml:space="preserve">1.90452086925507</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91204881668091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93538498878479</t>
+    <t xml:space="preserve">1.91204869747162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93538475036621</t>
   </si>
   <si>
     <t xml:space="preserve">1.92258775234222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91581284999847</t>
+    <t xml:space="preserve">1.91581273078918</t>
   </si>
   <si>
     <t xml:space="preserve">1.88118493556976</t>
@@ -752,10 +755,10 @@
     <t xml:space="preserve">1.92860996723175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92183530330658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92559885978699</t>
+    <t xml:space="preserve">1.92183518409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9255987405777</t>
   </si>
   <si>
     <t xml:space="preserve">1.94065427780151</t>
@@ -764,37 +767,37 @@
     <t xml:space="preserve">1.9263516664505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.903768658638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91957664489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91882371902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93237364292145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94366562366486</t>
+    <t xml:space="preserve">1.90376830101013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91957676410675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91882395744324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93237376213074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94366550445557</t>
   </si>
   <si>
     <t xml:space="preserve">1.91054332256317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89021849632263</t>
+    <t xml:space="preserve">1.89021825790405</t>
   </si>
   <si>
     <t xml:space="preserve">1.90753221511841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89699351787567</t>
+    <t xml:space="preserve">1.8969931602478</t>
   </si>
   <si>
     <t xml:space="preserve">1.89473509788513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87742137908936</t>
+    <t xml:space="preserve">1.87742114067078</t>
   </si>
   <si>
     <t xml:space="preserve">1.86010730266571</t>
@@ -803,52 +806,52 @@
     <t xml:space="preserve">1.77052700519562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79762721061707</t>
+    <t xml:space="preserve">1.79762697219849</t>
   </si>
   <si>
     <t xml:space="preserve">1.76826870441437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79461586475372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80741310119629</t>
+    <t xml:space="preserve">1.79461598396301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80741322040558</t>
   </si>
   <si>
     <t xml:space="preserve">1.83074915409088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84881579875946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82547950744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81042408943176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82623243331909</t>
+    <t xml:space="preserve">1.84881591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82547962665558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81042397022247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82623267173767</t>
   </si>
   <si>
     <t xml:space="preserve">1.83601856231689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83902955055237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85257971286774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82171607017517</t>
+    <t xml:space="preserve">1.83902978897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85257983207703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82171595096588</t>
   </si>
   <si>
     <t xml:space="preserve">1.84806287288666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84655749797821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83752417564392</t>
+    <t xml:space="preserve">1.84655737876892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83752393722534</t>
   </si>
   <si>
     <t xml:space="preserve">1.89774608612061</t>
@@ -857,16 +860,16 @@
     <t xml:space="preserve">1.91280174255371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97377645969391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97151803970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.930868268013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93613743782043</t>
+    <t xml:space="preserve">1.9737765789032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97151815891266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93086814880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93613755702972</t>
   </si>
   <si>
     <t xml:space="preserve">1.9210821390152</t>
@@ -875,88 +878,88 @@
     <t xml:space="preserve">1.8879599571228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88720715045929</t>
+    <t xml:space="preserve">1.88720738887787</t>
   </si>
   <si>
     <t xml:space="preserve">1.89548778533936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8932296037674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.869140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85860192775726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85634326934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85709631443024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85182690620422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86688232421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88494884967804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87215161323547</t>
+    <t xml:space="preserve">1.89322948455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86914050579071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85860180854797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8563437461853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85709607601166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85182702541351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86688208580017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88494896888733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87215197086334</t>
   </si>
   <si>
     <t xml:space="preserve">1.87064635753632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86161303520203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88193798065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86763525009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8736572265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86537671089172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84505188465118</t>
+    <t xml:space="preserve">1.86161291599274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88193786144257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86763513088226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87365710735321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86537683010101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84505200386047</t>
   </si>
   <si>
     <t xml:space="preserve">1.84204077720642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84731018543243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84279334545135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8179520368576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82397425174713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82849085330963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81569361686707</t>
+    <t xml:space="preserve">1.84731042385101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84279358386993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81795179843903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82397413253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82849109172821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81569385528564</t>
   </si>
   <si>
     <t xml:space="preserve">1.82021033763885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81117713451385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.816446185112</t>
+    <t xml:space="preserve">1.81117689609528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81644630432129</t>
   </si>
   <si>
     <t xml:space="preserve">1.81418812274933</t>
@@ -965,22 +968,22 @@
     <t xml:space="preserve">1.83526575565338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83225464820862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82246840000153</t>
+    <t xml:space="preserve">1.83225476741791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82246851921082</t>
   </si>
   <si>
     <t xml:space="preserve">1.8503212928772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89849865436554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93689024448395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9173184633255</t>
+    <t xml:space="preserve">1.89849877357483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93689036369324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91731810569763</t>
   </si>
   <si>
     <t xml:space="preserve">1.97979867458344</t>
@@ -989,40 +992,40 @@
     <t xml:space="preserve">1.96474313735962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94667649269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97076535224915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96775424480438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96248471736908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10325384140015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04378437995911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0242121219635</t>
+    <t xml:space="preserve">1.94667661190033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97076523303986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9677540063858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96248483657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10325360298157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04378461837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02421236038208</t>
   </si>
   <si>
     <t xml:space="preserve">1.9873263835907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99937069416046</t>
+    <t xml:space="preserve">1.99937057495117</t>
   </si>
   <si>
     <t xml:space="preserve">1.98582077026367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99033749103546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96624875068665</t>
+    <t xml:space="preserve">1.99033761024475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96624898910522</t>
   </si>
   <si>
     <t xml:space="preserve">1.99861788749695</t>
@@ -1031,73 +1034,73 @@
     <t xml:space="preserve">1.96549594402313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97603464126587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98280966281891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0249650478363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06260371208191</t>
+    <t xml:space="preserve">1.97603476047516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98280990123749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02496528625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06260395050049</t>
   </si>
   <si>
     <t xml:space="preserve">2.07540106773376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08142328262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08217573165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08594012260437</t>
+    <t xml:space="preserve">2.08142304420471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08217597007751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08593988418579</t>
   </si>
   <si>
     <t xml:space="preserve">2.07765936851501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09572577476501</t>
+    <t xml:space="preserve">2.09572601318359</t>
   </si>
   <si>
     <t xml:space="preserve">2.09045672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11153435707092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10024237632751</t>
+    <t xml:space="preserve">2.11153411865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10024261474609</t>
   </si>
   <si>
     <t xml:space="preserve">2.08669257164001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07013130187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06034541130066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05959272384644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05884027481079</t>
+    <t xml:space="preserve">2.07013177871704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06034564971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05959296226501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05884003639221</t>
   </si>
   <si>
     <t xml:space="preserve">2.07615375518799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08368158340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10400652885437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08518719673157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13185930252075</t>
+    <t xml:space="preserve">2.08368182182312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10400676727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08518695831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13185906410217</t>
   </si>
   <si>
     <t xml:space="preserve">2.19057559967041</t>
@@ -1106,7 +1109,7 @@
     <t xml:space="preserve">2.21315884590149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17552018165588</t>
+    <t xml:space="preserve">2.1755199432373</t>
   </si>
   <si>
     <t xml:space="preserve">2.16799259185791</t>
@@ -1121,13 +1124,13 @@
     <t xml:space="preserve">2.31101965904236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36371421813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31854724884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33360314369202</t>
+    <t xml:space="preserve">2.36371397972107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31854748725891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33360266685486</t>
   </si>
   <si>
     <t xml:space="preserve">2.37124156951904</t>
@@ -1139,19 +1142,19 @@
     <t xml:space="preserve">2.28843641281128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26585340499878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28090858459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30349183082581</t>
+    <t xml:space="preserve">2.2658531665802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28090882301331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30349206924438</t>
   </si>
   <si>
     <t xml:space="preserve">2.29596424102783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25832557678223</t>
+    <t xml:space="preserve">2.25832533836365</t>
   </si>
   <si>
     <t xml:space="preserve">2.19810342788696</t>
@@ -1166,10 +1169,10 @@
     <t xml:space="preserve">2.38629722595215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55190801620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5443799495697</t>
+    <t xml:space="preserve">2.55190777778625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54437971115112</t>
   </si>
   <si>
     <t xml:space="preserve">2.61965751647949</t>
@@ -1181,13 +1184,13 @@
     <t xml:space="preserve">2.49168562889099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46910214424133</t>
+    <t xml:space="preserve">2.46910238265991</t>
   </si>
   <si>
     <t xml:space="preserve">2.40135264396667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43146371841431</t>
+    <t xml:space="preserve">2.43146347999573</t>
   </si>
   <si>
     <t xml:space="preserve">2.47663044929504</t>
@@ -1199,13 +1202,13 @@
     <t xml:space="preserve">2.40888047218323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48415803909302</t>
+    <t xml:space="preserve">2.48415780067444</t>
   </si>
   <si>
     <t xml:space="preserve">2.45404672622681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41640782356262</t>
+    <t xml:space="preserve">2.4164080619812</t>
   </si>
   <si>
     <t xml:space="preserve">2.5067412853241</t>
@@ -1214,22 +1217,22 @@
     <t xml:space="preserve">2.5293242931366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57587647438049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59139394760132</t>
+    <t xml:space="preserve">2.57587671279907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59139370918274</t>
   </si>
   <si>
     <t xml:space="preserve">2.58363509178162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56035923957825</t>
+    <t xml:space="preserve">2.56035900115967</t>
   </si>
   <si>
     <t xml:space="preserve">2.50604844093323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51380729675293</t>
+    <t xml:space="preserve">2.51380753517151</t>
   </si>
   <si>
     <t xml:space="preserve">2.52156567573547</t>
@@ -1238,7 +1241,7 @@
     <t xml:space="preserve">2.54484176635742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48277258872986</t>
+    <t xml:space="preserve">2.48277235031128</t>
   </si>
   <si>
     <t xml:space="preserve">2.4982898235321</t>
@@ -1250,22 +1253,22 @@
     <t xml:space="preserve">2.32759928703308</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30432343482971</t>
+    <t xml:space="preserve">2.30432295799255</t>
   </si>
   <si>
     <t xml:space="preserve">2.28104710578918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31208181381226</t>
+    <t xml:space="preserve">2.31208157539368</t>
   </si>
   <si>
     <t xml:space="preserve">2.22673678398132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20346069335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19570183753967</t>
+    <t xml:space="preserve">2.2034604549408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19570207595825</t>
   </si>
   <si>
     <t xml:space="preserve">2.21897792816162</t>
@@ -1280,13 +1283,13 @@
     <t xml:space="preserve">2.1724259853363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11811542510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18794322013855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25001263618469</t>
+    <t xml:space="preserve">2.11811518669128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18794345855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25001239776611</t>
   </si>
   <si>
     <t xml:space="preserve">2.12587404251099</t>
@@ -1295,19 +1298,19 @@
     <t xml:space="preserve">2.10259795188904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13363242149353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09483909606934</t>
+    <t xml:space="preserve">2.13363265991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09483933448792</t>
   </si>
   <si>
     <t xml:space="preserve">2.08708071708679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07932186126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07156348228455</t>
+    <t xml:space="preserve">2.07932209968567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07156324386597</t>
   </si>
   <si>
     <t xml:space="preserve">2.04052877426147</t>
@@ -1319,61 +1322,61 @@
     <t xml:space="preserve">2.1646671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14915013313293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18018484115601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29656457901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03276991844177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01725268363953</t>
+    <t xml:space="preserve">2.14914989471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18018460273743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29656481742859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03277015686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01725244522095</t>
   </si>
   <si>
     <t xml:space="preserve">2.02501130104065</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00949382781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97070062160492</t>
+    <t xml:space="preserve">2.0094940662384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97070050239563</t>
   </si>
   <si>
     <t xml:space="preserve">1.96294176578522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93966603279114</t>
+    <t xml:space="preserve">1.93966615200043</t>
   </si>
   <si>
     <t xml:space="preserve">1.88535535335541</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87759685516357</t>
+    <t xml:space="preserve">1.877596616745</t>
   </si>
   <si>
     <t xml:space="preserve">1.85432076454163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86983788013458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79225134849548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83880341053009</t>
+    <t xml:space="preserve">1.86983799934387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79225146770477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8388032913208</t>
   </si>
   <si>
     <t xml:space="preserve">1.83104467391968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86207950115204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15690851211548</t>
+    <t xml:space="preserve">1.86207926273346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15690875053406</t>
   </si>
   <si>
     <t xml:space="preserve">2.06380438804626</t>
@@ -1382,40 +1385,40 @@
     <t xml:space="preserve">2.0482873916626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0017352104187</t>
+    <t xml:space="preserve">2.00173544883728</t>
   </si>
   <si>
     <t xml:space="preserve">1.97845947742462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99397671222687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9241486787796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84656190872192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80776882171631</t>
+    <t xml:space="preserve">1.99397683143616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92414855957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84656202793121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80776870250702</t>
   </si>
   <si>
     <t xml:space="preserve">1.75345814228058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77673399448395</t>
+    <t xml:space="preserve">1.77673387527466</t>
   </si>
   <si>
     <t xml:space="preserve">1.74569952487946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82328593730927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89311385154724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91638994216919</t>
+    <t xml:space="preserve">1.82328605651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89311397075653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91639018058777</t>
   </si>
   <si>
     <t xml:space="preserve">2.21121907234192</t>
@@ -1427,49 +1430,49 @@
     <t xml:space="preserve">2.05604600906372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26552987098694</t>
+    <t xml:space="preserve">2.26553010940552</t>
   </si>
   <si>
     <t xml:space="preserve">2.24225378036499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35087490081787</t>
+    <t xml:space="preserve">2.35087513923645</t>
   </si>
   <si>
     <t xml:space="preserve">2.31984043121338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33535814285278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35863375663757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40518593788147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3819100856781</t>
+    <t xml:space="preserve">2.3353579044342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35863399505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40518569946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38190984725952</t>
   </si>
   <si>
     <t xml:space="preserve">2.38966846466064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39742708206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41294431686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42070293426514</t>
+    <t xml:space="preserve">2.39742732048035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41294455528259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42070317268372</t>
   </si>
   <si>
     <t xml:space="preserve">2.36639261245728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34311652183533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3741512298584</t>
+    <t xml:space="preserve">2.34311628341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37415146827698</t>
   </si>
   <si>
     <t xml:space="preserve">2.45173788070679</t>
@@ -1484,13 +1487,13 @@
     <t xml:space="preserve">2.54447102546692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5200834274292</t>
+    <t xml:space="preserve">2.52008318901062</t>
   </si>
   <si>
     <t xml:space="preserve">2.4956955909729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4387903213501</t>
+    <t xml:space="preserve">2.43879008293152</t>
   </si>
   <si>
     <t xml:space="preserve">2.45504903793335</t>
@@ -1514,16 +1517,16 @@
     <t xml:space="preserve">2.42253160476685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36562657356262</t>
+    <t xml:space="preserve">2.3656268119812</t>
   </si>
   <si>
     <t xml:space="preserve">2.3900146484375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28433346748352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27620434761047</t>
+    <t xml:space="preserve">2.2843337059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27620410919189</t>
   </si>
   <si>
     <t xml:space="preserve">2.2274284362793</t>
@@ -1532,13 +1535,13 @@
     <t xml:space="preserve">2.23555779457092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25181651115417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26807498931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.357497215271</t>
+    <t xml:space="preserve">2.2518162727356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26807522773743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35749697685242</t>
   </si>
   <si>
     <t xml:space="preserve">2.32498002052307</t>
@@ -1559,7 +1562,7 @@
     <t xml:space="preserve">2.52821254730225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53634214401245</t>
+    <t xml:space="preserve">2.53634190559387</t>
   </si>
   <si>
     <t xml:space="preserve">2.58511781692505</t>
@@ -1568,7 +1571,7 @@
     <t xml:space="preserve">2.5932469367981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56072998046875</t>
+    <t xml:space="preserve">2.56072974205017</t>
   </si>
   <si>
     <t xml:space="preserve">2.60137629508972</t>
@@ -1580,13 +1583,10 @@
     <t xml:space="preserve">2.5688591003418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57698845863342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55260038375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41440272331238</t>
+    <t xml:space="preserve">2.576988697052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4144024848938</t>
   </si>
   <si>
     <t xml:space="preserve">2.3331093788147</t>
@@ -1598,7 +1598,7 @@
     <t xml:space="preserve">2.39814376831055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47130727767944</t>
+    <t xml:space="preserve">2.47130751609802</t>
   </si>
   <si>
     <t xml:space="preserve">2.44691967964172</t>
@@ -1616,7 +1616,7 @@
     <t xml:space="preserve">2.30059218406677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11361837387085</t>
+    <t xml:space="preserve">2.11361813545227</t>
   </si>
   <si>
     <t xml:space="preserve">2.18678212165833</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">2.12987685203552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08110094070435</t>
+    <t xml:space="preserve">2.08110117912292</t>
   </si>
   <si>
     <t xml:space="preserve">2.10548901557922</t>
@@ -1637,16 +1637,16 @@
     <t xml:space="preserve">2.048583984375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89412724971771</t>
+    <t xml:space="preserve">1.89412713050842</t>
   </si>
   <si>
     <t xml:space="preserve">1.65837728977203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66650664806366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6258602142334</t>
+    <t xml:space="preserve">1.66650652885437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62586009502411</t>
   </si>
   <si>
     <t xml:space="preserve">1.47140347957611</t>
@@ -1655,7 +1655,7 @@
     <t xml:space="preserve">1.50392067432404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51205015182495</t>
+    <t xml:space="preserve">1.51205003261566</t>
   </si>
   <si>
     <t xml:space="preserve">1.61366641521454</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">1.53237330913544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49579131603241</t>
+    <t xml:space="preserve">1.4957914352417</t>
   </si>
   <si>
     <t xml:space="preserve">1.58521366119385</t>
@@ -1679,31 +1679,31 @@
     <t xml:space="preserve">1.6014723777771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57301986217499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56082582473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58114922046661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5689549446106</t>
+    <t xml:space="preserve">1.5730197429657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56082570552826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58114898204803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56895506381989</t>
   </si>
   <si>
     <t xml:space="preserve">1.63398957252502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69089460372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60553693771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62179565429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58927834033966</t>
+    <t xml:space="preserve">1.69089472293854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60553705692291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62179553508759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58927845954895</t>
   </si>
   <si>
     <t xml:space="preserve">1.61773085594177</t>
@@ -1718,16 +1718,16 @@
     <t xml:space="preserve">1.76405835151672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73154103755951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71528255939484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69902384281158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65024816989899</t>
+    <t xml:space="preserve">1.7315411567688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71528267860413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69902396202087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6502480506897</t>
   </si>
   <si>
     <t xml:space="preserve">1.74779963493347</t>
@@ -1736,16 +1736,16 @@
     <t xml:space="preserve">1.75592911243439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77218759059906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78844618797302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82096350193024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87786865234375</t>
+    <t xml:space="preserve">1.77218747138977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78844630718231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82096338272095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87786829471588</t>
   </si>
   <si>
     <t xml:space="preserve">1.82909274101257</t>
@@ -1754,25 +1754,25 @@
     <t xml:space="preserve">1.80470490455627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81283414363861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79657566547394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78031671047211</t>
+    <t xml:space="preserve">1.81283402442932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79657578468323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78031694889069</t>
   </si>
   <si>
     <t xml:space="preserve">1.72341191768646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73967027664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6827654838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60960149765015</t>
+    <t xml:space="preserve">1.73967039585114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68276524543762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60960161685944</t>
   </si>
   <si>
     <t xml:space="preserve">1.64211881160736</t>
@@ -1781,13 +1781,13 @@
     <t xml:space="preserve">1.57708418369293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52830851078033</t>
+    <t xml:space="preserve">1.52830862998962</t>
   </si>
   <si>
     <t xml:space="preserve">1.53643774986267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49985599517822</t>
+    <t xml:space="preserve">1.49985611438751</t>
   </si>
   <si>
     <t xml:space="preserve">1.48766207695007</t>
@@ -1802,25 +1802,25 @@
     <t xml:space="preserve">1.42262768745422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41043388843536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40636909008026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43482160568237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41449844837189</t>
+    <t xml:space="preserve">1.41043376922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40636897087097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43482172489166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4144983291626</t>
   </si>
   <si>
     <t xml:space="preserve">1.36572241783142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33320534229279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38198113441467</t>
+    <t xml:space="preserve">1.33320546150208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38198125362396</t>
   </si>
   <si>
     <t xml:space="preserve">1.35759329795837</t>
@@ -1835,7 +1835,7 @@
     <t xml:space="preserve">1.30881750583649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33727014064789</t>
+    <t xml:space="preserve">1.3372700214386</t>
   </si>
   <si>
     <t xml:space="preserve">1.32507598400116</t>
@@ -1856,28 +1856,28 @@
     <t xml:space="preserve">1.40230441093445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3860456943512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39011061191559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37791657447815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46733868122101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52017939090729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5526967048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54456722736359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49172687530518</t>
+    <t xml:space="preserve">1.38604581356049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3901104927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37791645526886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4673388004303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.520179271698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55269658565521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5445671081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49172675609589</t>
   </si>
   <si>
     <t xml:space="preserve">1.52424395084381</t>
@@ -1892,19 +1892,19 @@
     <t xml:space="preserve">1.54050254821777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47953295707703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86973929405212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95103216171265</t>
+    <t xml:space="preserve">1.47953283786774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86973917484283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95103228092194</t>
   </si>
   <si>
     <t xml:space="preserve">2.0729718208313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25994563102722</t>
+    <t xml:space="preserve">2.2599458694458</t>
   </si>
   <si>
     <t xml:space="preserve">2.24368715286255</t>
@@ -1913,7 +1913,7 @@
     <t xml:space="preserve">2.1786527633667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14613556861877</t>
+    <t xml:space="preserve">2.1461353302002</t>
   </si>
   <si>
     <t xml:space="preserve">2.05671310424805</t>
@@ -1934,10 +1934,10 @@
     <t xml:space="preserve">2.24429607391357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25257754325867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20288848876953</t>
+    <t xml:space="preserve">2.25257778167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20288825035095</t>
   </si>
   <si>
     <t xml:space="preserve">2.22773313522339</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">2.19460678100586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17804360389709</t>
+    <t xml:space="preserve">2.17804384231567</t>
   </si>
   <si>
     <t xml:space="preserve">2.34367442131042</t>
@@ -1973,7 +1973,7 @@
     <t xml:space="preserve">2.4844605922699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49274230003357</t>
+    <t xml:space="preserve">2.49274206161499</t>
   </si>
   <si>
     <t xml:space="preserve">2.41820859909058</t>
@@ -1997,28 +1997,28 @@
     <t xml:space="preserve">2.33539295196533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32711124420166</t>
+    <t xml:space="preserve">2.32711172103882</t>
   </si>
   <si>
     <t xml:space="preserve">2.30226683616638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31882977485657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31054830551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3519561290741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29398536682129</t>
+    <t xml:space="preserve">2.31883001327515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31054854393005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35195589065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29398512840271</t>
   </si>
   <si>
     <t xml:space="preserve">2.28570365905762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2774224281311</t>
+    <t xml:space="preserve">2.27742218971252</t>
   </si>
   <si>
     <t xml:space="preserve">2.15319919586182</t>
@@ -2054,13 +2054,13 @@
     <t xml:space="preserve">2.26914072036743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26085925102234</t>
+    <t xml:space="preserve">2.26085901260376</t>
   </si>
   <si>
     <t xml:space="preserve">2.4099268913269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46789717674255</t>
+    <t xml:space="preserve">2.46789765357971</t>
   </si>
   <si>
     <t xml:space="preserve">2.50102376937866</t>
@@ -2084,28 +2084,28 @@
     <t xml:space="preserve">2.81572198867798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84884834289551</t>
+    <t xml:space="preserve">2.84884810447693</t>
   </si>
   <si>
     <t xml:space="preserve">2.86541104316711</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01447892189026</t>
+    <t xml:space="preserve">3.01447916030884</t>
   </si>
   <si>
     <t xml:space="preserve">3.03104186058044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24636197090149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23808002471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22979879379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3043327331543</t>
+    <t xml:space="preserve">3.24636220932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23808026313782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22979855537415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30433297157288</t>
   </si>
   <si>
     <t xml:space="preserve">3.12213897705078</t>
@@ -2117,7 +2117,7 @@
     <t xml:space="preserve">3.17182803153992</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21323585510254</t>
+    <t xml:space="preserve">3.21323561668396</t>
   </si>
   <si>
     <t xml:space="preserve">3.1883909702301</t>
@@ -2135,25 +2135,25 @@
     <t xml:space="preserve">3.10557579994202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13870215415955</t>
+    <t xml:space="preserve">3.13870191574097</t>
   </si>
   <si>
     <t xml:space="preserve">3.08901262283325</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07244968414307</t>
+    <t xml:space="preserve">3.07244944572449</t>
   </si>
   <si>
     <t xml:space="preserve">3.11385726928711</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08073115348816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06416821479797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.254643201828</t>
+    <t xml:space="preserve">3.08073091506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06416797637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25464344024658</t>
   </si>
   <si>
     <t xml:space="preserve">3.09729433059692</t>
@@ -2168,13 +2168,13 @@
     <t xml:space="preserve">3.04760479927063</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0558865070343</t>
+    <t xml:space="preserve">3.05588674545288</t>
   </si>
   <si>
     <t xml:space="preserve">3.15526485443115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03932332992554</t>
+    <t xml:space="preserve">3.03932356834412</t>
   </si>
   <si>
     <t xml:space="preserve">2.98963403701782</t>
@@ -2189,7 +2189,7 @@
     <t xml:space="preserve">2.97307133674622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20495438575745</t>
+    <t xml:space="preserve">3.20495414733887</t>
   </si>
   <si>
     <t xml:space="preserve">3.27948784828186</t>
@@ -8677,7 +8677,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G209" t="s">
-        <v>16</v>
+        <v>136</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -8703,7 +8703,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G210" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -8755,7 +8755,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G212" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -8963,7 +8963,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G220" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -9171,7 +9171,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G228" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -9197,7 +9197,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G229" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -9223,7 +9223,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G230" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -9275,7 +9275,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G232" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -9301,7 +9301,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G233" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -9327,7 +9327,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G234" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -9353,7 +9353,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G235" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -9379,7 +9379,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G236" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -9405,7 +9405,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G237" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -9483,7 +9483,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G240" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -9509,7 +9509,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G241" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -9561,7 +9561,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G243" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -9639,7 +9639,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G246" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -9665,7 +9665,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G247" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -9691,7 +9691,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G248" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -9743,7 +9743,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G250" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -9769,7 +9769,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G251" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -9847,7 +9847,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G254" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -9925,7 +9925,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G257" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -9951,7 +9951,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G258" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -9977,7 +9977,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G259" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -10003,7 +10003,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G260" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -10029,7 +10029,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G261" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -10055,7 +10055,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G262" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -10081,7 +10081,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G263" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -10107,7 +10107,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G264" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -10133,7 +10133,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G265" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -10185,7 +10185,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G267" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -10211,7 +10211,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G268" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -10237,7 +10237,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G269" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -10263,7 +10263,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G270" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -10289,7 +10289,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G271" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -10315,7 +10315,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G272" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -10341,7 +10341,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G273" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -10367,7 +10367,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G274" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -10393,7 +10393,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G275" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -10419,7 +10419,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G276" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -10445,7 +10445,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G277" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -10471,7 +10471,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G278" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -10497,7 +10497,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G279" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -10523,7 +10523,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G280" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -10549,7 +10549,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G281" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -10575,7 +10575,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G282" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -10601,7 +10601,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G283" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -10627,7 +10627,7 @@
         <v>18.6299991607666</v>
       </c>
       <c r="G284" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -10653,7 +10653,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G285" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -10679,7 +10679,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G286" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -10705,7 +10705,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G287" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -10731,7 +10731,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G288" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -10757,7 +10757,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G289" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -10783,7 +10783,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G290" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -10809,7 +10809,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G291" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -10835,7 +10835,7 @@
         <v>19.25</v>
       </c>
       <c r="G292" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -10861,7 +10861,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G293" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -10887,7 +10887,7 @@
         <v>19.0300006866455</v>
       </c>
       <c r="G294" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -10913,7 +10913,7 @@
         <v>18.7099990844727</v>
       </c>
       <c r="G295" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -10939,7 +10939,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G296" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -10965,7 +10965,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G297" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -10991,7 +10991,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G298" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -11017,7 +11017,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G299" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -11043,7 +11043,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G300" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -11069,7 +11069,7 @@
         <v>20.1700000762939</v>
       </c>
       <c r="G301" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -11095,7 +11095,7 @@
         <v>20.25</v>
       </c>
       <c r="G302" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -11121,7 +11121,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G303" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -11147,7 +11147,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G304" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -11173,7 +11173,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G305" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -11199,7 +11199,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G306" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -11225,7 +11225,7 @@
         <v>20.2099990844727</v>
       </c>
       <c r="G307" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -11251,7 +11251,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G308" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -11277,7 +11277,7 @@
         <v>20.3700008392334</v>
       </c>
       <c r="G309" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -11303,7 +11303,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G310" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -11329,7 +11329,7 @@
         <v>20.25</v>
       </c>
       <c r="G311" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -11355,7 +11355,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G312" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -11381,7 +11381,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G313" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -11407,7 +11407,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G314" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -11433,7 +11433,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G315" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -11459,7 +11459,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G316" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -11485,7 +11485,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G317" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -11511,7 +11511,7 @@
         <v>20.9300003051758</v>
       </c>
       <c r="G318" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -11537,7 +11537,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G319" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -11563,7 +11563,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G320" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -11589,7 +11589,7 @@
         <v>20.4899997711182</v>
       </c>
       <c r="G321" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -11615,7 +11615,7 @@
         <v>20.4699993133545</v>
       </c>
       <c r="G322" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -11641,7 +11641,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G323" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -11667,7 +11667,7 @@
         <v>20.25</v>
       </c>
       <c r="G324" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -11693,7 +11693,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G325" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -11719,7 +11719,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G326" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -11745,7 +11745,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G327" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -11771,7 +11771,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G328" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -11797,7 +11797,7 @@
         <v>20.25</v>
       </c>
       <c r="G329" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -11823,7 +11823,7 @@
         <v>20</v>
       </c>
       <c r="G330" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -11849,7 +11849,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G331" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -11875,7 +11875,7 @@
         <v>20.2900009155273</v>
       </c>
       <c r="G332" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -11901,7 +11901,7 @@
         <v>20.7800006866455</v>
       </c>
       <c r="G333" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -11927,7 +11927,7 @@
         <v>21.0100002288818</v>
       </c>
       <c r="G334" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -11953,7 +11953,7 @@
         <v>21.6200008392334</v>
       </c>
       <c r="G335" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -11979,7 +11979,7 @@
         <v>21.6700000762939</v>
       </c>
       <c r="G336" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -12005,7 +12005,7 @@
         <v>21.7099990844727</v>
       </c>
       <c r="G337" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -12031,7 +12031,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G338" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -12057,7 +12057,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G339" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -12083,7 +12083,7 @@
         <v>22.1399993896484</v>
       </c>
       <c r="G340" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -12109,7 +12109,7 @@
         <v>22.0900001525879</v>
       </c>
       <c r="G341" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -12135,7 +12135,7 @@
         <v>22.0699996948242</v>
       </c>
       <c r="G342" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -12161,7 +12161,7 @@
         <v>23.5</v>
       </c>
       <c r="G343" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -12187,7 +12187,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G344" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -12213,7 +12213,7 @@
         <v>24.5</v>
       </c>
       <c r="G345" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -12239,7 +12239,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G346" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -12265,7 +12265,7 @@
         <v>26.5</v>
       </c>
       <c r="G347" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -12291,7 +12291,7 @@
         <v>26.75</v>
       </c>
       <c r="G348" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -12317,7 +12317,7 @@
         <v>25.9500007629395</v>
       </c>
       <c r="G349" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -12343,7 +12343,7 @@
         <v>26.3299999237061</v>
       </c>
       <c r="G350" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -12369,7 +12369,7 @@
         <v>25.6399993896484</v>
       </c>
       <c r="G351" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -12395,7 +12395,7 @@
         <v>24.5</v>
       </c>
       <c r="G352" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -12421,7 +12421,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G353" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -12447,7 +12447,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G354" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -12473,7 +12473,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G355" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -12499,7 +12499,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G356" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -12525,7 +12525,7 @@
         <v>25.7099990844727</v>
       </c>
       <c r="G357" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -12551,7 +12551,7 @@
         <v>25.5400009155273</v>
       </c>
       <c r="G358" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -12577,7 +12577,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G359" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -12603,7 +12603,7 @@
         <v>24.9899997711182</v>
       </c>
       <c r="G360" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -12629,7 +12629,7 @@
         <v>25.6200008392334</v>
       </c>
       <c r="G361" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -12655,7 +12655,7 @@
         <v>25.5300006866455</v>
       </c>
       <c r="G362" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -12681,7 +12681,7 @@
         <v>25.5799999237061</v>
       </c>
       <c r="G363" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -12707,7 +12707,7 @@
         <v>25.7800006866455</v>
       </c>
       <c r="G364" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -12733,7 +12733,7 @@
         <v>25.5900001525879</v>
       </c>
       <c r="G365" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -12759,7 +12759,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G366" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -12785,7 +12785,7 @@
         <v>25.2900009155273</v>
       </c>
       <c r="G367" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -12811,7 +12811,7 @@
         <v>25.5</v>
       </c>
       <c r="G368" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -12837,7 +12837,7 @@
         <v>25.5799999237061</v>
       </c>
       <c r="G369" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -12863,7 +12863,7 @@
         <v>25.4899997711182</v>
       </c>
       <c r="G370" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -12889,7 +12889,7 @@
         <v>25.6700000762939</v>
       </c>
       <c r="G371" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -12915,7 +12915,7 @@
         <v>25.8199996948242</v>
       </c>
       <c r="G372" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -12941,7 +12941,7 @@
         <v>25.5400009155273</v>
       </c>
       <c r="G373" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -12967,7 +12967,7 @@
         <v>25.3799991607666</v>
       </c>
       <c r="G374" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -12993,7 +12993,7 @@
         <v>25.1100006103516</v>
       </c>
       <c r="G375" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -13019,7 +13019,7 @@
         <v>25.3400001525879</v>
       </c>
       <c r="G376" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -13045,7 +13045,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G377" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -13071,7 +13071,7 @@
         <v>25.1700000762939</v>
       </c>
       <c r="G378" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -13097,7 +13097,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G379" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -13123,7 +13123,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G380" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -13149,7 +13149,7 @@
         <v>23.5200004577637</v>
       </c>
       <c r="G381" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -13175,7 +13175,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G382" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -13201,7 +13201,7 @@
         <v>23.4899997711182</v>
       </c>
       <c r="G383" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -13227,7 +13227,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G384" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -13253,7 +13253,7 @@
         <v>24.0100002288818</v>
       </c>
       <c r="G385" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -13279,7 +13279,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G386" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -13305,7 +13305,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G387" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -13331,7 +13331,7 @@
         <v>24.25</v>
       </c>
       <c r="G388" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -13357,7 +13357,7 @@
         <v>24.0499992370605</v>
       </c>
       <c r="G389" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -13383,7 +13383,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G390" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -13409,7 +13409,7 @@
         <v>24.2600002288818</v>
       </c>
       <c r="G391" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -13435,7 +13435,7 @@
         <v>24.0499992370605</v>
       </c>
       <c r="G392" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -13461,7 +13461,7 @@
         <v>24.3899993896484</v>
       </c>
       <c r="G393" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -13487,7 +13487,7 @@
         <v>24.4300003051758</v>
       </c>
       <c r="G394" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -13513,7 +13513,7 @@
         <v>24.5</v>
       </c>
       <c r="G395" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -13539,7 +13539,7 @@
         <v>24.5</v>
       </c>
       <c r="G396" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -13565,7 +13565,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G397" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -13591,7 +13591,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G398" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -13617,7 +13617,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G399" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -13643,7 +13643,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G400" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -13669,7 +13669,7 @@
         <v>24.5300006866455</v>
       </c>
       <c r="G401" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -13695,7 +13695,7 @@
         <v>24.4099998474121</v>
       </c>
       <c r="G402" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -13721,7 +13721,7 @@
         <v>25.2099990844727</v>
       </c>
       <c r="G403" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -13747,7 +13747,7 @@
         <v>25.4099998474121</v>
       </c>
       <c r="G404" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -13773,7 +13773,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G405" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -13799,7 +13799,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G406" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -13825,7 +13825,7 @@
         <v>26.1900005340576</v>
       </c>
       <c r="G407" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -13851,7 +13851,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G408" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -13877,7 +13877,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G409" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -13903,7 +13903,7 @@
         <v>25.6700000762939</v>
       </c>
       <c r="G410" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -13929,7 +13929,7 @@
         <v>25.5200004577637</v>
       </c>
       <c r="G411" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -13955,7 +13955,7 @@
         <v>25.5</v>
       </c>
       <c r="G412" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -13981,7 +13981,7 @@
         <v>25.0799999237061</v>
       </c>
       <c r="G413" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -14007,7 +14007,7 @@
         <v>25.1100006103516</v>
       </c>
       <c r="G414" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -14033,7 +14033,7 @@
         <v>25.0699996948242</v>
       </c>
       <c r="G415" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -14059,7 +14059,7 @@
         <v>25.1800003051758</v>
       </c>
       <c r="G416" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -14085,7 +14085,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G417" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -14111,7 +14111,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G418" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -14137,7 +14137,7 @@
         <v>24.8299999237061</v>
       </c>
       <c r="G419" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -14163,7 +14163,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G420" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -14189,7 +14189,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G421" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -14215,7 +14215,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G422" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -14241,7 +14241,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G423" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -14267,7 +14267,7 @@
         <v>24.6700000762939</v>
       </c>
       <c r="G424" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -14293,7 +14293,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G425" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -14319,7 +14319,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G426" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -14345,7 +14345,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G427" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -14371,7 +14371,7 @@
         <v>25.0400009155273</v>
       </c>
       <c r="G428" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -14397,7 +14397,7 @@
         <v>24.8700008392334</v>
       </c>
       <c r="G429" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -14423,7 +14423,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G430" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -14449,7 +14449,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G431" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -14475,7 +14475,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G432" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -14501,7 +14501,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G433" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -14527,7 +14527,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G434" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -14553,7 +14553,7 @@
         <v>24.7299995422363</v>
       </c>
       <c r="G435" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -14579,7 +14579,7 @@
         <v>25</v>
       </c>
       <c r="G436" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -14605,7 +14605,7 @@
         <v>24.8099994659424</v>
       </c>
       <c r="G437" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -14631,7 +14631,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G438" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -14657,7 +14657,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G439" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -14683,7 +14683,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G440" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -14709,7 +14709,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G441" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -14735,7 +14735,7 @@
         <v>24.5100002288818</v>
       </c>
       <c r="G442" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -14761,7 +14761,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G443" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -14787,7 +14787,7 @@
         <v>24.4699993133545</v>
       </c>
       <c r="G444" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -14813,7 +14813,7 @@
         <v>24.5400009155273</v>
       </c>
       <c r="G445" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -14839,7 +14839,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G446" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -14865,7 +14865,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G447" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -14891,7 +14891,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G448" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -14917,7 +14917,7 @@
         <v>24.2299995422363</v>
       </c>
       <c r="G449" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -14943,7 +14943,7 @@
         <v>24.2900009155273</v>
       </c>
       <c r="G450" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -14969,7 +14969,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G451" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -14995,7 +14995,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G452" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15021,7 +15021,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G453" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15047,7 +15047,7 @@
         <v>24.1299991607666</v>
       </c>
       <c r="G454" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15073,7 +15073,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G455" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15099,7 +15099,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G456" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -15125,7 +15125,7 @@
         <v>24.25</v>
       </c>
       <c r="G457" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15151,7 +15151,7 @@
         <v>24.3400001525879</v>
       </c>
       <c r="G458" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15177,7 +15177,7 @@
         <v>24.2099990844727</v>
       </c>
       <c r="G459" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -15203,7 +15203,7 @@
         <v>24.25</v>
       </c>
       <c r="G460" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -15229,7 +15229,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G461" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15255,7 +15255,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G462" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15281,7 +15281,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G463" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -15307,7 +15307,7 @@
         <v>25.2199993133545</v>
       </c>
       <c r="G464" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15333,7 +15333,7 @@
         <v>25.7299995422363</v>
       </c>
       <c r="G465" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15359,7 +15359,7 @@
         <v>25.4699993133545</v>
       </c>
       <c r="G466" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15385,7 +15385,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G467" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -15411,7 +15411,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G468" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15437,7 +15437,7 @@
         <v>25.8199996948242</v>
       </c>
       <c r="G469" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15463,7 +15463,7 @@
         <v>25.8600006103516</v>
       </c>
       <c r="G470" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15489,7 +15489,7 @@
         <v>26.1800003051758</v>
       </c>
       <c r="G471" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15515,7 +15515,7 @@
         <v>26.1399993896484</v>
       </c>
       <c r="G472" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15541,7 +15541,7 @@
         <v>26.0699996948242</v>
       </c>
       <c r="G473" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15567,7 +15567,7 @@
         <v>27.9400005340576</v>
       </c>
       <c r="G474" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -15593,7 +15593,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G475" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -15619,7 +15619,7 @@
         <v>26.8899993896484</v>
       </c>
       <c r="G476" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15645,7 +15645,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G477" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15671,7 +15671,7 @@
         <v>26.5599994659424</v>
       </c>
       <c r="G478" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -15697,7 +15697,7 @@
         <v>26.3799991607666</v>
       </c>
       <c r="G479" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15723,7 +15723,7 @@
         <v>26.4400005340576</v>
       </c>
       <c r="G480" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -15749,7 +15749,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G481" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -15775,7 +15775,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G482" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -15801,7 +15801,7 @@
         <v>26.1100006103516</v>
       </c>
       <c r="G483" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -15827,7 +15827,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G484" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -15853,7 +15853,7 @@
         <v>26.25</v>
       </c>
       <c r="G485" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -15879,7 +15879,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G486" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -15905,7 +15905,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G487" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -15931,7 +15931,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G488" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -15957,7 +15957,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G489" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -15983,7 +15983,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G490" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -16009,7 +16009,7 @@
         <v>27.5699996948242</v>
       </c>
       <c r="G491" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16035,7 +16035,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G492" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -16061,7 +16061,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G493" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16087,7 +16087,7 @@
         <v>27.6599998474121</v>
       </c>
       <c r="G494" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16113,7 +16113,7 @@
         <v>27.7099990844727</v>
       </c>
       <c r="G495" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -16139,7 +16139,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G496" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -16165,7 +16165,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G497" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -16191,7 +16191,7 @@
         <v>27.8400001525879</v>
       </c>
       <c r="G498" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -16217,7 +16217,7 @@
         <v>27.7700004577637</v>
       </c>
       <c r="G499" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16243,7 +16243,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G500" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -16269,7 +16269,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G501" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16295,7 +16295,7 @@
         <v>27.7199993133545</v>
       </c>
       <c r="G502" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16321,7 +16321,7 @@
         <v>27.5</v>
       </c>
       <c r="G503" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16347,7 +16347,7 @@
         <v>27.3700008392334</v>
       </c>
       <c r="G504" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16373,7 +16373,7 @@
         <v>27.3600006103516</v>
       </c>
       <c r="G505" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16399,7 +16399,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G506" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16425,7 +16425,7 @@
         <v>27.5699996948242</v>
       </c>
       <c r="G507" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16451,7 +16451,7 @@
         <v>27.5799999237061</v>
       </c>
       <c r="G508" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16477,7 +16477,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G509" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16503,7 +16503,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G510" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16529,7 +16529,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G511" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16555,7 +16555,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G512" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -16581,7 +16581,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G513" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -16607,7 +16607,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G514" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -16633,7 +16633,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G515" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -16659,7 +16659,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G516" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16685,7 +16685,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G517" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -16711,7 +16711,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G518" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -16737,7 +16737,7 @@
         <v>29.5</v>
       </c>
       <c r="G519" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -16763,7 +16763,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G520" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -16789,7 +16789,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G521" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -16815,7 +16815,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G522" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -16841,7 +16841,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G523" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -16867,7 +16867,7 @@
         <v>31</v>
       </c>
       <c r="G524" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -16893,7 +16893,7 @@
         <v>31.5</v>
       </c>
       <c r="G525" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -16919,7 +16919,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G526" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -16945,7 +16945,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G527" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -16971,7 +16971,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G528" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -16997,7 +16997,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G529" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -17023,7 +17023,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G530" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17049,7 +17049,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G531" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17075,7 +17075,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G532" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17101,7 +17101,7 @@
         <v>30.5</v>
       </c>
       <c r="G533" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17127,7 +17127,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G534" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -17153,7 +17153,7 @@
         <v>30</v>
       </c>
       <c r="G535" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17179,7 +17179,7 @@
         <v>30</v>
       </c>
       <c r="G536" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17205,7 +17205,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G537" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17231,7 +17231,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G538" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17257,7 +17257,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G539" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17283,7 +17283,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G540" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17309,7 +17309,7 @@
         <v>29</v>
       </c>
       <c r="G541" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17335,7 +17335,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G542" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17361,7 +17361,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G543" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17387,7 +17387,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G544" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17413,7 +17413,7 @@
         <v>30</v>
       </c>
       <c r="G545" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17439,7 +17439,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G546" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17465,7 +17465,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G547" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17491,7 +17491,7 @@
         <v>31.5</v>
       </c>
       <c r="G548" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17517,7 +17517,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G549" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17543,7 +17543,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G550" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17569,7 +17569,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G551" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17595,7 +17595,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G552" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17621,7 +17621,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G553" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17647,7 +17647,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G554" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17673,7 +17673,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G555" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17699,7 +17699,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G556" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17725,7 +17725,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G557" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -17751,7 +17751,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G558" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -17777,7 +17777,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G559" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -17803,7 +17803,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G560" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -17829,7 +17829,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G561" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -17855,7 +17855,7 @@
         <v>32.5</v>
       </c>
       <c r="G562" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -17881,7 +17881,7 @@
         <v>32</v>
       </c>
       <c r="G563" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -17907,7 +17907,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G564" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -17933,7 +17933,7 @@
         <v>32.5</v>
       </c>
       <c r="G565" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -17959,7 +17959,7 @@
         <v>33</v>
       </c>
       <c r="G566" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -17985,7 +17985,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G567" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18011,7 +18011,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G568" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18037,7 +18037,7 @@
         <v>32.5</v>
       </c>
       <c r="G569" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18063,7 +18063,7 @@
         <v>32.5</v>
       </c>
       <c r="G570" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18089,7 +18089,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G571" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18115,7 +18115,7 @@
         <v>32.5</v>
       </c>
       <c r="G572" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18141,7 +18141,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G573" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18167,7 +18167,7 @@
         <v>32.5</v>
       </c>
       <c r="G574" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18193,7 +18193,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G575" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18219,7 +18219,7 @@
         <v>32.5</v>
       </c>
       <c r="G576" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18245,7 +18245,7 @@
         <v>32.5</v>
       </c>
       <c r="G577" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18271,7 +18271,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G578" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18297,7 +18297,7 @@
         <v>32.5</v>
       </c>
       <c r="G579" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18323,7 +18323,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G580" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18349,7 +18349,7 @@
         <v>32.5</v>
       </c>
       <c r="G581" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18375,7 +18375,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G582" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18401,7 +18401,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G583" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18427,7 +18427,7 @@
         <v>33</v>
       </c>
       <c r="G584" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18453,7 +18453,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G585" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18479,7 +18479,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G586" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18505,7 +18505,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G587" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18531,7 +18531,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G588" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18557,7 +18557,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G589" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18583,7 +18583,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G590" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18609,7 +18609,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G591" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18635,7 +18635,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G592" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18661,7 +18661,7 @@
         <v>33</v>
       </c>
       <c r="G593" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18687,7 +18687,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G594" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18713,7 +18713,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G595" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18739,7 +18739,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G596" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -18765,7 +18765,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G597" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -18791,7 +18791,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G598" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -18817,7 +18817,7 @@
         <v>32.5</v>
       </c>
       <c r="G599" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -18843,7 +18843,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G600" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -18869,7 +18869,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G601" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -18895,7 +18895,7 @@
         <v>32</v>
       </c>
       <c r="G602" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -18921,7 +18921,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G603" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18947,7 +18947,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G604" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -18973,7 +18973,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G605" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -18999,7 +18999,7 @@
         <v>32</v>
       </c>
       <c r="G606" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19025,7 +19025,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G607" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19051,7 +19051,7 @@
         <v>30</v>
       </c>
       <c r="G608" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19077,7 +19077,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G609" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19103,7 +19103,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G610" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19129,7 +19129,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G611" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19155,7 +19155,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G612" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19181,7 +19181,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G613" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19207,7 +19207,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G614" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19233,7 +19233,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G615" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19259,7 +19259,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G616" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19285,7 +19285,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G617" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19311,7 +19311,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G618" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19337,7 +19337,7 @@
         <v>28</v>
       </c>
       <c r="G619" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19363,7 +19363,7 @@
         <v>28</v>
       </c>
       <c r="G620" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19389,7 +19389,7 @@
         <v>28</v>
       </c>
       <c r="G621" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19415,7 +19415,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G622" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19441,7 +19441,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G623" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19467,7 +19467,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G624" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19493,7 +19493,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G625" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19519,7 +19519,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G626" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19545,7 +19545,7 @@
         <v>29</v>
       </c>
       <c r="G627" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19571,7 +19571,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G628" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19597,7 +19597,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G629" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19623,7 +19623,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G630" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19649,7 +19649,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G631" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19675,7 +19675,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G632" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19701,7 +19701,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G633" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19727,7 +19727,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G634" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19753,7 +19753,7 @@
         <v>27.5</v>
       </c>
       <c r="G635" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19779,7 +19779,7 @@
         <v>27</v>
       </c>
       <c r="G636" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19805,7 +19805,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G637" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19831,7 +19831,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G638" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19857,7 +19857,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G639" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19883,7 +19883,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G640" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19909,7 +19909,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G641" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -19935,7 +19935,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G642" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19961,7 +19961,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G643" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19987,7 +19987,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G644" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20013,7 +20013,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G645" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20039,7 +20039,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G646" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20065,7 +20065,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G647" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20091,7 +20091,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G648" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20117,7 +20117,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G649" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20143,7 +20143,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G650" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20169,7 +20169,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G651" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20195,7 +20195,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G652" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20221,7 +20221,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G653" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20247,7 +20247,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G654" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20273,7 +20273,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G655" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20299,7 +20299,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G656" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20325,7 +20325,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G657" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20351,7 +20351,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G658" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20377,7 +20377,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G659" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20403,7 +20403,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G660" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20429,7 +20429,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G661" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20455,7 +20455,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G662" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20481,7 +20481,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G663" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -20507,7 +20507,7 @@
         <v>27.5</v>
       </c>
       <c r="G664" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20533,7 +20533,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G665" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20559,7 +20559,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G666" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20585,7 +20585,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G667" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20611,7 +20611,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G668" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20637,7 +20637,7 @@
         <v>27</v>
       </c>
       <c r="G669" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20663,7 +20663,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G670" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20689,7 +20689,7 @@
         <v>27</v>
       </c>
       <c r="G671" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20715,7 +20715,7 @@
         <v>26</v>
       </c>
       <c r="G672" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20741,7 +20741,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G673" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20767,7 +20767,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G674" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20793,7 +20793,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G675" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20819,7 +20819,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G676" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20845,7 +20845,7 @@
         <v>25</v>
       </c>
       <c r="G677" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20871,7 +20871,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G678" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20897,7 +20897,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G679" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -20923,7 +20923,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G680" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -20949,7 +20949,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G681" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -20975,7 +20975,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G682" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21001,7 +21001,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G683" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21027,7 +21027,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G684" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21053,7 +21053,7 @@
         <v>24</v>
       </c>
       <c r="G685" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21079,7 +21079,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G686" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21105,7 +21105,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G687" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21131,7 +21131,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G688" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21157,7 +21157,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G689" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21183,7 +21183,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G690" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21209,7 +21209,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G691" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21235,7 +21235,7 @@
         <v>27</v>
       </c>
       <c r="G692" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21261,7 +21261,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G693" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21287,7 +21287,7 @@
         <v>26</v>
       </c>
       <c r="G694" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21313,7 +21313,7 @@
         <v>26</v>
       </c>
       <c r="G695" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21339,7 +21339,7 @@
         <v>26</v>
       </c>
       <c r="G696" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21365,7 +21365,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G697" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21391,7 +21391,7 @@
         <v>26</v>
       </c>
       <c r="G698" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21417,7 +21417,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G699" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21443,7 +21443,7 @@
         <v>26</v>
       </c>
       <c r="G700" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21469,7 +21469,7 @@
         <v>25.5</v>
       </c>
       <c r="G701" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21495,7 +21495,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G702" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -21521,7 +21521,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G703" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21547,7 +21547,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G704" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21573,7 +21573,7 @@
         <v>26</v>
       </c>
       <c r="G705" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21599,7 +21599,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G706" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21625,7 +21625,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G707" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21651,7 +21651,7 @@
         <v>25.5</v>
       </c>
       <c r="G708" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21677,7 +21677,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G709" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21703,7 +21703,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G710" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21729,7 +21729,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G711" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21755,7 +21755,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G712" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21781,7 +21781,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G713" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21807,7 +21807,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G714" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21833,7 +21833,7 @@
         <v>24</v>
       </c>
       <c r="G715" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21859,7 +21859,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G716" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21885,7 +21885,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G717" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21911,7 +21911,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G718" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -21937,7 +21937,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G719" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -21963,7 +21963,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G720" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21989,7 +21989,7 @@
         <v>22.5</v>
       </c>
       <c r="G721" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22015,7 +22015,7 @@
         <v>23.5</v>
       </c>
       <c r="G722" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22041,7 +22041,7 @@
         <v>23.5</v>
       </c>
       <c r="G723" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22067,7 +22067,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G724" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22093,7 +22093,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G725" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22119,7 +22119,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G726" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22145,7 +22145,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G727" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22171,7 +22171,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G728" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22197,7 +22197,7 @@
         <v>25</v>
       </c>
       <c r="G729" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22223,7 +22223,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G730" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22249,7 +22249,7 @@
         <v>28</v>
       </c>
       <c r="G731" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22275,7 +22275,7 @@
         <v>28.5</v>
       </c>
       <c r="G732" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22301,7 +22301,7 @@
         <v>27.5</v>
       </c>
       <c r="G733" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22327,7 +22327,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G734" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22353,7 +22353,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G735" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22379,7 +22379,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G736" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22405,7 +22405,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G737" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22431,7 +22431,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G738" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22457,7 +22457,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G739" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -22483,7 +22483,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G740" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -22509,7 +22509,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G741" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22535,7 +22535,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G742" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22561,7 +22561,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G743" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22587,7 +22587,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G744" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22613,7 +22613,7 @@
         <v>27.5</v>
       </c>
       <c r="G745" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22639,7 +22639,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G746" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22665,7 +22665,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G747" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22691,7 +22691,7 @@
         <v>27.5</v>
       </c>
       <c r="G748" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22717,7 +22717,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G749" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22743,7 +22743,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G750" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22769,7 +22769,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G751" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22795,7 +22795,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G752" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22821,7 +22821,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G753" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22847,7 +22847,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G754" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22873,7 +22873,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G755" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22899,7 +22899,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G756" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -22925,7 +22925,7 @@
         <v>26.5</v>
       </c>
       <c r="G757" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -22951,7 +22951,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G758" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -22977,7 +22977,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G759" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23003,7 +23003,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G760" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23029,7 +23029,7 @@
         <v>27</v>
       </c>
       <c r="G761" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23055,7 +23055,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G762" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23081,7 +23081,7 @@
         <v>27</v>
       </c>
       <c r="G763" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23107,7 +23107,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G764" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23133,7 +23133,7 @@
         <v>26.5</v>
       </c>
       <c r="G765" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23159,7 +23159,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G766" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23185,7 +23185,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G767" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23211,7 +23211,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G768" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23237,7 +23237,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G769" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23263,7 +23263,7 @@
         <v>28.5</v>
       </c>
       <c r="G770" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23289,7 +23289,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G771" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23315,7 +23315,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G772" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23341,7 +23341,7 @@
         <v>28</v>
       </c>
       <c r="G773" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23367,7 +23367,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G774" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23393,7 +23393,7 @@
         <v>28</v>
       </c>
       <c r="G775" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23419,7 +23419,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G776" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23445,7 +23445,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G777" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23471,7 +23471,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G778" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -23497,7 +23497,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G779" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -23523,7 +23523,7 @@
         <v>28.5</v>
       </c>
       <c r="G780" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23549,7 +23549,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G781" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23575,7 +23575,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G782" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23601,7 +23601,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G783" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23627,7 +23627,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G784" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23653,7 +23653,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G785" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23679,7 +23679,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G786" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23705,7 +23705,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G787" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23731,7 +23731,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G788" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23757,7 +23757,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G789" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23783,7 +23783,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G790" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23809,7 +23809,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G791" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23835,7 +23835,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G792" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23861,7 +23861,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G793" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23887,7 +23887,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G794" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23913,7 +23913,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G795" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -23939,7 +23939,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G796" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -23965,7 +23965,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G797" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -23991,7 +23991,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G798" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24017,7 +24017,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G799" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24043,7 +24043,7 @@
         <v>30</v>
       </c>
       <c r="G800" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24069,7 +24069,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G801" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24095,7 +24095,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G802" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24121,7 +24121,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G803" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24147,7 +24147,7 @@
         <v>31</v>
       </c>
       <c r="G804" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24173,7 +24173,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G805" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24199,7 +24199,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G806" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24225,7 +24225,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G807" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24251,7 +24251,7 @@
         <v>31</v>
       </c>
       <c r="G808" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24277,7 +24277,7 @@
         <v>31</v>
       </c>
       <c r="G809" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24303,7 +24303,7 @@
         <v>31</v>
       </c>
       <c r="G810" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24329,7 +24329,7 @@
         <v>31</v>
       </c>
       <c r="G811" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24355,7 +24355,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G812" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24381,7 +24381,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G813" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24407,7 +24407,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G814" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24433,7 +24433,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G815" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24459,7 +24459,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G816" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -24485,7 +24485,7 @@
         <v>31</v>
       </c>
       <c r="G817" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -24511,7 +24511,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G818" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24537,7 +24537,7 @@
         <v>31</v>
       </c>
       <c r="G819" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24563,7 +24563,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G820" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24589,7 +24589,7 @@
         <v>30.5</v>
       </c>
       <c r="G821" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24615,7 +24615,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G822" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24641,7 +24641,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G823" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24667,7 +24667,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G824" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24693,7 +24693,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G825" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24719,7 +24719,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G826" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24745,7 +24745,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G827" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24771,7 +24771,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G828" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24797,7 +24797,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G829" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24823,7 +24823,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G830" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24849,7 +24849,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G831" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24875,7 +24875,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G832" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24901,7 +24901,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G833" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -24927,7 +24927,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G834" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -24953,7 +24953,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G835" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -24979,7 +24979,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G836" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25005,7 +25005,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G837" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25031,7 +25031,7 @@
         <v>31</v>
       </c>
       <c r="G838" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25057,7 +25057,7 @@
         <v>31</v>
       </c>
       <c r="G839" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25083,7 +25083,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G840" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25109,7 +25109,7 @@
         <v>30</v>
       </c>
       <c r="G841" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25135,7 +25135,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G842" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25161,7 +25161,7 @@
         <v>30.5</v>
       </c>
       <c r="G843" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25187,7 +25187,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G844" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25213,7 +25213,7 @@
         <v>30.5</v>
       </c>
       <c r="G845" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25239,7 +25239,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G846" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25265,7 +25265,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G847" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25291,7 +25291,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G848" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25317,7 +25317,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G849" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25343,7 +25343,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G850" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25369,7 +25369,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G851" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25395,7 +25395,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G852" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -25421,7 +25421,7 @@
         <v>28</v>
       </c>
       <c r="G853" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -25447,7 +25447,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G854" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -25473,7 +25473,7 @@
         <v>28</v>
       </c>
       <c r="G855" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -25499,7 +25499,7 @@
         <v>27.5</v>
       </c>
       <c r="G856" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25525,7 +25525,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G857" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25551,7 +25551,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G858" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25577,7 +25577,7 @@
         <v>27.5</v>
       </c>
       <c r="G859" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25603,7 +25603,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G860" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25629,7 +25629,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G861" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25655,7 +25655,7 @@
         <v>28</v>
       </c>
       <c r="G862" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25681,7 +25681,7 @@
         <v>29</v>
       </c>
       <c r="G863" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25707,7 +25707,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G864" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25733,7 +25733,7 @@
         <v>29</v>
       </c>
       <c r="G865" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25759,7 +25759,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G866" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -25785,7 +25785,7 @@
         <v>29</v>
       </c>
       <c r="G867" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25811,7 +25811,7 @@
         <v>29</v>
       </c>
       <c r="G868" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -25837,7 +25837,7 @@
         <v>29</v>
       </c>
       <c r="G869" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -25863,7 +25863,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G870" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -25889,7 +25889,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G871" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25915,7 +25915,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G872" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -25941,7 +25941,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G873" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -25967,7 +25967,7 @@
         <v>30.5</v>
       </c>
       <c r="G874" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -25993,7 +25993,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G875" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -26019,7 +26019,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G876" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -26045,7 +26045,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G877" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -26071,7 +26071,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G878" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -26097,7 +26097,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G879" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26123,7 +26123,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G880" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -26149,7 +26149,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G881" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -26175,7 +26175,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G882" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -26201,7 +26201,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G883" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -26227,7 +26227,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G884" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -26253,7 +26253,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G885" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -26279,7 +26279,7 @@
         <v>31.5</v>
       </c>
       <c r="G886" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -26305,7 +26305,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G887" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -26331,7 +26331,7 @@
         <v>32</v>
       </c>
       <c r="G888" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -26357,7 +26357,7 @@
         <v>31.5</v>
       </c>
       <c r="G889" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -26383,7 +26383,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G890" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -26409,7 +26409,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G891" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -26435,7 +26435,7 @@
         <v>32</v>
       </c>
       <c r="G892" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -26461,7 +26461,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G893" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -26487,7 +26487,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G894" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -26513,7 +26513,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26539,7 +26539,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G896" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -26565,7 +26565,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G897" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -26591,7 +26591,7 @@
         <v>31</v>
       </c>
       <c r="G898" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -26617,7 +26617,7 @@
         <v>31</v>
       </c>
       <c r="G899" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -26643,7 +26643,7 @@
         <v>31</v>
       </c>
       <c r="G900" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -26669,7 +26669,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G901" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -26695,7 +26695,7 @@
         <v>31</v>
       </c>
       <c r="G902" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -26721,7 +26721,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G903" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -26747,7 +26747,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G904" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -26773,7 +26773,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G905" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -26799,7 +26799,7 @@
         <v>31</v>
       </c>
       <c r="G906" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -26825,7 +26825,7 @@
         <v>31</v>
       </c>
       <c r="G907" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -26851,7 +26851,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G908" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -26877,7 +26877,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G909" t="s">
-        <v>523</v>
+        <v>489</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -26903,7 +26903,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G910" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -26929,7 +26929,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G911" t="s">
-        <v>523</v>
+        <v>489</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -26955,7 +26955,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G912" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -26981,7 +26981,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G913" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -27007,7 +27007,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G914" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -27033,7 +27033,7 @@
         <v>30</v>
       </c>
       <c r="G915" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -27059,7 +27059,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G916" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -27111,7 +27111,7 @@
         <v>29</v>
       </c>
       <c r="G918" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -27163,7 +27163,7 @@
         <v>29</v>
       </c>
       <c r="G920" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -27241,7 +27241,7 @@
         <v>29</v>
       </c>
       <c r="G923" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -27267,7 +27267,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G924" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -27293,7 +27293,7 @@
         <v>29</v>
       </c>
       <c r="G925" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -27319,7 +27319,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G926" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -27345,7 +27345,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G927" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -27371,7 +27371,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G928" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -27423,7 +27423,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G930" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -27449,7 +27449,7 @@
         <v>30.5</v>
       </c>
       <c r="G931" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -27475,7 +27475,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G932" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -27579,7 +27579,7 @@
         <v>30</v>
       </c>
       <c r="G936" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -27657,7 +27657,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G939" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -27683,7 +27683,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G940" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -27709,7 +27709,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G941" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -27735,7 +27735,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G942" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -27761,7 +27761,7 @@
         <v>30</v>
       </c>
       <c r="G943" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -27787,7 +27787,7 @@
         <v>30</v>
       </c>
       <c r="G944" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -27839,7 +27839,7 @@
         <v>30</v>
       </c>
       <c r="G946" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -27865,7 +27865,7 @@
         <v>30.5</v>
       </c>
       <c r="G947" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -27891,7 +27891,7 @@
         <v>30.5</v>
       </c>
       <c r="G948" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -27917,7 +27917,7 @@
         <v>30</v>
       </c>
       <c r="G949" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -27969,7 +27969,7 @@
         <v>30</v>
       </c>
       <c r="G951" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -28021,7 +28021,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G953" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -28073,7 +28073,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G955" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -28099,7 +28099,7 @@
         <v>30</v>
       </c>
       <c r="G956" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -28125,7 +28125,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G957" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -28151,7 +28151,7 @@
         <v>30</v>
       </c>
       <c r="G958" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -28177,7 +28177,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G959" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -28203,7 +28203,7 @@
         <v>30</v>
       </c>
       <c r="G960" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -28229,7 +28229,7 @@
         <v>30</v>
       </c>
       <c r="G961" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -28255,7 +28255,7 @@
         <v>30</v>
       </c>
       <c r="G962" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -28281,7 +28281,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G963" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -28307,7 +28307,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G964" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -28333,7 +28333,7 @@
         <v>30</v>
       </c>
       <c r="G965" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -28359,7 +28359,7 @@
         <v>30</v>
       </c>
       <c r="G966" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -28411,7 +28411,7 @@
         <v>30</v>
       </c>
       <c r="G968" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -28437,7 +28437,7 @@
         <v>30</v>
       </c>
       <c r="G969" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -28515,7 +28515,7 @@
         <v>30</v>
       </c>
       <c r="G972" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -28567,7 +28567,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G974" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -28593,7 +28593,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G975" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -28645,7 +28645,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G977" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -28671,7 +28671,7 @@
         <v>31</v>
       </c>
       <c r="G978" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28697,7 +28697,7 @@
         <v>31</v>
       </c>
       <c r="G979" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -28723,7 +28723,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G980" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28749,7 +28749,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G981" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -28775,7 +28775,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G982" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -28801,7 +28801,7 @@
         <v>31</v>
       </c>
       <c r="G983" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -28827,7 +28827,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G984" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -28853,7 +28853,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G985" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28879,7 +28879,7 @@
         <v>31</v>
       </c>
       <c r="G986" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -28905,7 +28905,7 @@
         <v>31.5</v>
       </c>
       <c r="G987" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -28931,7 +28931,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G988" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -28957,7 +28957,7 @@
         <v>31.5</v>
       </c>
       <c r="G989" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -28983,7 +28983,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G990" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -29009,7 +29009,7 @@
         <v>31.5</v>
       </c>
       <c r="G991" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -29035,7 +29035,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G992" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -29061,7 +29061,7 @@
         <v>31.5</v>
       </c>
       <c r="G993" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -29087,7 +29087,7 @@
         <v>31.5</v>
       </c>
       <c r="G994" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -29113,7 +29113,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G995" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -29139,7 +29139,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G996" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -29165,7 +29165,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G997" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -29191,7 +29191,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G998" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -29217,7 +29217,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G999" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -29243,7 +29243,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1000" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -29269,7 +29269,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1001" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -29295,7 +29295,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1002" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -29321,7 +29321,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1003" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -29347,7 +29347,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1004" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -29373,7 +29373,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1005" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -29399,7 +29399,7 @@
         <v>31</v>
       </c>
       <c r="G1006" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -29425,7 +29425,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1007" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -29451,7 +29451,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1008" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -29477,7 +29477,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1009" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -29503,7 +29503,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1010" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -29529,7 +29529,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1011" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -29555,7 +29555,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1012" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -29581,7 +29581,7 @@
         <v>30.5</v>
       </c>
       <c r="G1013" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -29607,7 +29607,7 @@
         <v>30.5</v>
       </c>
       <c r="G1014" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -29659,7 +29659,7 @@
         <v>30.5</v>
       </c>
       <c r="G1016" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -29711,7 +29711,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1018" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -29737,7 +29737,7 @@
         <v>30</v>
       </c>
       <c r="G1019" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -29763,7 +29763,7 @@
         <v>30.5</v>
       </c>
       <c r="G1020" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -29789,7 +29789,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1021" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -29815,7 +29815,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1022" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -29841,7 +29841,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1023" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -29867,7 +29867,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1024" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -29893,7 +29893,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1025" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -29919,7 +29919,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1026" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -29945,7 +29945,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1027" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -29971,7 +29971,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1028" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -29997,7 +29997,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1029" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -30023,7 +30023,7 @@
         <v>30</v>
       </c>
       <c r="G1030" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -30049,7 +30049,7 @@
         <v>30</v>
       </c>
       <c r="G1031" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -30075,7 +30075,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1032" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -30257,7 +30257,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1039" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -30283,7 +30283,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1040" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -30309,7 +30309,7 @@
         <v>28</v>
       </c>
       <c r="G1041" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -30439,7 +30439,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1046" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -30491,7 +30491,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1048" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -30517,7 +30517,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1049" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -30569,7 +30569,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1051" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -30595,7 +30595,7 @@
         <v>28</v>
       </c>
       <c r="G1052" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -30673,7 +30673,7 @@
         <v>27.5</v>
       </c>
       <c r="G1055" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -36939,7 +36939,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1296" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -36965,7 +36965,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1297" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -37017,7 +37017,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1299" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -37069,7 +37069,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1301" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -37095,7 +37095,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1302" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -37121,7 +37121,7 @@
         <v>29</v>
       </c>
       <c r="G1303" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -37147,7 +37147,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1304" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -37173,7 +37173,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1305" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -37277,7 +37277,7 @@
         <v>28</v>
       </c>
       <c r="G1309" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -37303,7 +37303,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1310" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -37329,7 +37329,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1311" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -37407,7 +37407,7 @@
         <v>28</v>
       </c>
       <c r="G1314" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -37433,7 +37433,7 @@
         <v>28</v>
       </c>
       <c r="G1315" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -37459,7 +37459,7 @@
         <v>28</v>
       </c>
       <c r="G1316" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -37823,7 +37823,7 @@
         <v>27.5</v>
       </c>
       <c r="G1330" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -38005,7 +38005,7 @@
         <v>27.5</v>
       </c>
       <c r="G1337" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -68017,7 +68017,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6366435185</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>14205</v>
@@ -68038,6 +68038,32 @@
         <v>902</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.5367939815</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>128</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>2.61500000953674</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>2.61500000953674</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>926</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24616169929504</t>
+    <t xml:space="preserve">1.24616158008575</t>
   </si>
   <si>
     <t xml:space="preserve">AUTME.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24544668197632</t>
+    <t xml:space="preserve">1.24544656276703</t>
   </si>
   <si>
     <t xml:space="preserve">1.24330163002014</t>
@@ -53,19 +53,19 @@
     <t xml:space="preserve">1.22256803512573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21541857719421</t>
+    <t xml:space="preserve">1.21541845798492</t>
   </si>
   <si>
     <t xml:space="preserve">1.2218531370163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21470367908478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23615229129791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21327352523804</t>
+    <t xml:space="preserve">1.21470355987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23615205287933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21327364444733</t>
   </si>
   <si>
     <t xml:space="preserve">1.20683908462524</t>
@@ -74,52 +74,52 @@
     <t xml:space="preserve">1.20111930370331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20040452480316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16680181026459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1946849822998</t>
+    <t xml:space="preserve">1.20040464401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1668016910553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19468474388123</t>
   </si>
   <si>
     <t xml:space="preserve">1.25688564777374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25045120716095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2468763589859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25116634368896</t>
+    <t xml:space="preserve">1.25045132637024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24687647819519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25116622447968</t>
   </si>
   <si>
     <t xml:space="preserve">1.26475024223328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23543727397919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22542774677277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.210413813591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22113823890686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19397008419037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22685790061951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20469450950623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25831580162048</t>
+    <t xml:space="preserve">1.2354371547699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22542786598206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21041393280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22113800048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19396984577179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22685778141022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20469427108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2583155632019</t>
   </si>
   <si>
     <t xml:space="preserve">1.265465259552</t>
@@ -131,55 +131,55 @@
     <t xml:space="preserve">1.26903986930847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21684861183167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22828769683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27404463291168</t>
+    <t xml:space="preserve">1.21684837341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22828757762909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27404451370239</t>
   </si>
   <si>
     <t xml:space="preserve">1.26689493656158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27261471748352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27189981937408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27904915809631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26761019229889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25545585155487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26260554790497</t>
+    <t xml:space="preserve">1.27261459827423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27189993858337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2790492773056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2676100730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25545573234558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2626051902771</t>
   </si>
   <si>
     <t xml:space="preserve">1.24830627441406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2490211725235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24258661270142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23686707019806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23472213745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23400735855103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25225365161896</t>
+    <t xml:space="preserve">1.24902129173279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24258649349213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23686695098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23472225666046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23400723934174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25225353240967</t>
   </si>
   <si>
     <t xml:space="preserve">1.26176798343658</t>
@@ -191,7 +191,7 @@
     <t xml:space="preserve">1.27860140800476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2764059305191</t>
+    <t xml:space="preserve">1.27640581130981</t>
   </si>
   <si>
     <t xml:space="preserve">1.27421009540558</t>
@@ -203,28 +203,28 @@
     <t xml:space="preserve">1.26323187351227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27128267288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26689124107361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28445637226105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28079700469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2793333530426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27347815036774</t>
+    <t xml:space="preserve">1.27128279209137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26689112186432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28445649147034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.280797123909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27933323383331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27347826957703</t>
   </si>
   <si>
     <t xml:space="preserve">1.27274632453918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26615941524506</t>
+    <t xml:space="preserve">1.26615929603577</t>
   </si>
   <si>
     <t xml:space="preserve">1.2822607755661</t>
@@ -233,10 +233,10 @@
     <t xml:space="preserve">1.28811585903168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28738415241241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28299283981323</t>
+    <t xml:space="preserve">1.28738403320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28299272060394</t>
   </si>
   <si>
     <t xml:space="preserve">1.26396381855011</t>
@@ -245,16 +245,16 @@
     <t xml:space="preserve">1.24127519130707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2434709072113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22956514358521</t>
+    <t xml:space="preserve">1.24347102642059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22956502437592</t>
   </si>
   <si>
     <t xml:space="preserve">1.23468852043152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22663772106171</t>
+    <t xml:space="preserve">1.22663760185242</t>
   </si>
   <si>
     <t xml:space="preserve">1.20687675476074</t>
@@ -263,28 +263,28 @@
     <t xml:space="preserve">1.20760869979858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18565201759338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1783332824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18784773349762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16955065727234</t>
+    <t xml:space="preserve">1.18565225601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17833340167999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18784785270691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16955077648163</t>
   </si>
   <si>
     <t xml:space="preserve">1.17101442813873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17028248310089</t>
+    <t xml:space="preserve">1.17028260231018</t>
   </si>
   <si>
     <t xml:space="preserve">1.18931150436401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22224640846252</t>
+    <t xml:space="preserve">1.22224628925323</t>
   </si>
   <si>
     <t xml:space="preserve">1.22151446342468</t>
@@ -293,13 +293,13 @@
     <t xml:space="preserve">1.23981153964996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23907959461212</t>
+    <t xml:space="preserve">1.23907971382141</t>
   </si>
   <si>
     <t xml:space="preserve">1.23834764957428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23542034626007</t>
+    <t xml:space="preserve">1.23542022705078</t>
   </si>
   <si>
     <t xml:space="preserve">1.2061448097229</t>
@@ -317,37 +317,37 @@
     <t xml:space="preserve">1.22297811508179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23322474956512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23249268531799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22883331775665</t>
+    <t xml:space="preserve">1.23322463035583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23249280452728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22883343696594</t>
   </si>
   <si>
     <t xml:space="preserve">1.28518831729889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25884056091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30714499950409</t>
+    <t xml:space="preserve">1.25884068012238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3071448802948</t>
   </si>
   <si>
     <t xml:space="preserve">1.29909408092499</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32324624061584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31665933132172</t>
+    <t xml:space="preserve">1.32324635982513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31665945053101</t>
   </si>
   <si>
     <t xml:space="preserve">1.32763767242432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30348539352417</t>
+    <t xml:space="preserve">1.30348551273346</t>
   </si>
   <si>
     <t xml:space="preserve">1.31592738628387</t>
@@ -359,19 +359,19 @@
     <t xml:space="preserve">1.29763042926788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30275356769562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29982602596283</t>
+    <t xml:space="preserve">1.30275344848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29982614517212</t>
   </si>
   <si>
     <t xml:space="preserve">1.28884780406952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29543495178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30055785179138</t>
+    <t xml:space="preserve">1.29543483257294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30055809020996</t>
   </si>
   <si>
     <t xml:space="preserve">1.29836225509644</t>
@@ -380,43 +380,43 @@
     <t xml:space="preserve">1.2932391166687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29250717163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30128979682922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30568110942841</t>
+    <t xml:space="preserve">1.29250705242157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30128991603851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30568099021912</t>
   </si>
   <si>
     <t xml:space="preserve">1.26908695697784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26762318611145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24786233901978</t>
+    <t xml:space="preserve">1.26762306690216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24786221981049</t>
   </si>
   <si>
     <t xml:space="preserve">1.25518119335175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2654275894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28006505966187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25810861587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25005793571472</t>
+    <t xml:space="preserve">1.26542747020721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28006529808044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25810885429382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25005781650543</t>
   </si>
   <si>
     <t xml:space="preserve">1.24054348468781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24639856815338</t>
+    <t xml:space="preserve">1.24639868736267</t>
   </si>
   <si>
     <t xml:space="preserve">1.24420285224915</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">1.23615217208862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23688411712646</t>
+    <t xml:space="preserve">1.23688399791718</t>
   </si>
   <si>
     <t xml:space="preserve">1.24200713634491</t>
@@ -437,25 +437,25 @@
     <t xml:space="preserve">1.20980441570282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21126806735992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21858704090118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21492767333984</t>
+    <t xml:space="preserve">1.21126794815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21858692169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21492755413055</t>
   </si>
   <si>
     <t xml:space="preserve">1.19004344940186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18199265003204</t>
+    <t xml:space="preserve">1.18199276924133</t>
   </si>
   <si>
     <t xml:space="preserve">1.214195728302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19297087192535</t>
+    <t xml:space="preserve">1.19297099113464</t>
   </si>
   <si>
     <t xml:space="preserve">1.19663035869598</t>
@@ -464,43 +464,43 @@
     <t xml:space="preserve">1.220050573349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21639132499695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25957226753235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27786934375763</t>
+    <t xml:space="preserve">1.21639108657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25957250595093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27786946296692</t>
   </si>
   <si>
     <t xml:space="preserve">1.28592026233673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29470300674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29689848423004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31007254123688</t>
+    <t xml:space="preserve">1.2947028875351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29689836502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31007242202759</t>
   </si>
   <si>
     <t xml:space="preserve">1.32544207572937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34081149101257</t>
+    <t xml:space="preserve">1.34081161022186</t>
   </si>
   <si>
     <t xml:space="preserve">1.3334926366806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33422470092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33202910423279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33861613273621</t>
+    <t xml:space="preserve">1.33422458171844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3320289850235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33861601352692</t>
   </si>
   <si>
     <t xml:space="preserve">1.33934772014618</t>
@@ -515,58 +515,58 @@
     <t xml:space="preserve">1.34007966518402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32690572738647</t>
+    <t xml:space="preserve">1.32690584659576</t>
   </si>
   <si>
     <t xml:space="preserve">1.3210506439209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34593462944031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36130440235138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36057257652283</t>
+    <t xml:space="preserve">1.3459347486496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36130428314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36057245731354</t>
   </si>
   <si>
     <t xml:space="preserve">1.33276081085205</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34959435462952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33788406848907</t>
+    <t xml:space="preserve">1.34959411621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33788394927979</t>
   </si>
   <si>
     <t xml:space="preserve">1.34373915195465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34520268440247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32910144329071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36349987983704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3678914308548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37667369842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38252890110016</t>
+    <t xml:space="preserve">1.34520292282104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32910132408142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36349999904633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36789155006409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37667393684387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38252902030945</t>
   </si>
   <si>
     <t xml:space="preserve">1.39789855480194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41253614425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40668106079102</t>
+    <t xml:space="preserve">1.41253626346588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40668118000031</t>
   </si>
   <si>
     <t xml:space="preserve">1.4081449508667</t>
@@ -575,76 +575,76 @@
     <t xml:space="preserve">1.40887689590454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40302169322968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39277529716492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36935520172119</t>
+    <t xml:space="preserve">1.40302193164825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3927755355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3693550825119</t>
   </si>
   <si>
     <t xml:space="preserve">1.37886953353882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38911604881287</t>
+    <t xml:space="preserve">1.38911581039429</t>
   </si>
   <si>
     <t xml:space="preserve">1.40155792236328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49304330348969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4762099981308</t>
+    <t xml:space="preserve">1.49304354190826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47621023654938</t>
   </si>
   <si>
     <t xml:space="preserve">1.48206520080566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49157965183258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50329005718231</t>
+    <t xml:space="preserve">1.49157977104187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50328981876373</t>
   </si>
   <si>
     <t xml:space="preserve">1.46742749214172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45864474773407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47913753986359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4952392578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49084794521332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48792016506195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5274418592453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50987660884857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53256523609161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52963757514954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53183329105377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52817368507385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51500010490417</t>
+    <t xml:space="preserve">1.45864498615265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47913789749146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49523901939392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49084806442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48792040348053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52744209766388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50987684726715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53256511688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52963745594025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53183341026306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52817392349243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51500022411346</t>
   </si>
   <si>
     <t xml:space="preserve">1.49963045120239</t>
@@ -656,103 +656,103 @@
     <t xml:space="preserve">1.485724568367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47108697891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48426103591919</t>
+    <t xml:space="preserve">1.47108709812164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4842609167099</t>
   </si>
   <si>
     <t xml:space="preserve">1.46376812458038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45498538017273</t>
+    <t xml:space="preserve">1.45498549938202</t>
   </si>
   <si>
     <t xml:space="preserve">1.48499286174774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52085506916046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53768849372864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58233332633972</t>
+    <t xml:space="preserve">1.52085494995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53768825531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58233344554901</t>
   </si>
   <si>
     <t xml:space="preserve">1.63126361370087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63427472114563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64857745170593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63578045368195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66664409637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66288030147552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66137456893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76902174949646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80816602706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84429919719696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91656565666199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99485409259796</t>
+    <t xml:space="preserve">1.63427460193634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64857757091522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63578033447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6666442155838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6628805398941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6613746881485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76902151107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80816614627838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84429907798767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91656541824341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99485397338867</t>
   </si>
   <si>
     <t xml:space="preserve">2.01367354393005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95345139503479</t>
+    <t xml:space="preserve">1.95345163345337</t>
   </si>
   <si>
     <t xml:space="preserve">1.9820568561554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93011522293091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83376049995422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90301561355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90452086925507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9120489358902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9353848695755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92258787155151</t>
+    <t xml:space="preserve">1.93011546134949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83376038074493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9030157327652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90452098846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91204857826233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93538498878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9225879907608</t>
   </si>
   <si>
     <t xml:space="preserve">1.9158126115799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88118505477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92860996723175</t>
+    <t xml:space="preserve">1.88118481636047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92861008644104</t>
   </si>
   <si>
     <t xml:space="preserve">1.92183494567871</t>
@@ -761,85 +761,85 @@
     <t xml:space="preserve">1.9255987405777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94065451622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9263516664505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90376842021942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91957688331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91882383823395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93237376213074</t>
+    <t xml:space="preserve">1.94065427780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92635154724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90376830101013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91957652568817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91882395744324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93237364292145</t>
   </si>
   <si>
     <t xml:space="preserve">1.94366526603699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91054320335388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89021813869476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90753221511841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89699351787567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89473497867584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87742114067078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86010718345642</t>
+    <t xml:space="preserve">1.91054332256317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89021861553192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9075323343277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89699327945709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89473509788513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87742102146149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.860107421875</t>
   </si>
   <si>
     <t xml:space="preserve">1.77052700519562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79762709140778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76826858520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79461586475372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.807412981987</t>
+    <t xml:space="preserve">1.79762721061707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76826882362366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79461574554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80741286277771</t>
   </si>
   <si>
     <t xml:space="preserve">1.83074915409088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84881567955017</t>
+    <t xml:space="preserve">1.84881579875946</t>
   </si>
   <si>
     <t xml:space="preserve">1.82547962665558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81042408943176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82623267173767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8360184431076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83902978897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85257959365845</t>
+    <t xml:space="preserve">1.81042420864105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82623255252838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83601868152618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83902966976166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85257983207703</t>
   </si>
   <si>
     <t xml:space="preserve">1.82171583175659</t>
@@ -848,28 +848,28 @@
     <t xml:space="preserve">1.84806287288666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84655737876892</t>
+    <t xml:space="preserve">1.8465576171875</t>
   </si>
   <si>
     <t xml:space="preserve">1.83752405643463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8977462053299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91280150413513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97377645969391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97151815891266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.930868268013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93613767623901</t>
+    <t xml:space="preserve">1.89774596691132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91280174255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97377622127533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97151803970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93086838722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93613755702972</t>
   </si>
   <si>
     <t xml:space="preserve">1.9210821390152</t>
@@ -878,61 +878,61 @@
     <t xml:space="preserve">1.88796007633209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88720703125</t>
+    <t xml:space="preserve">1.88720726966858</t>
   </si>
   <si>
     <t xml:space="preserve">1.89548802375793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89322948455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86914050579071</t>
+    <t xml:space="preserve">1.89322936534882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.869140625</t>
   </si>
   <si>
     <t xml:space="preserve">1.85860192775726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85634338855743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85709631443024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85182702541351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86688220500946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88494908809662</t>
+    <t xml:space="preserve">1.85634362697601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85709607601166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85182678699493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86688232421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88494896888733</t>
   </si>
   <si>
     <t xml:space="preserve">1.87215185165405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87064611911774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86161291599274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88193798065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86763501167297</t>
+    <t xml:space="preserve">1.87064635753632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86161279678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88193774223328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86763525009155</t>
   </si>
   <si>
     <t xml:space="preserve">1.87365710735321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86537706851959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84505188465118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84204089641571</t>
+    <t xml:space="preserve">1.86537683010101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84505200386047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84204065799713</t>
   </si>
   <si>
     <t xml:space="preserve">1.84731018543243</t>
@@ -947,109 +947,109 @@
     <t xml:space="preserve">1.82397413253784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82849061489105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81569361686707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82021021842957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81117689609528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81644642353058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81418788433075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83526575565338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83225476741791</t>
+    <t xml:space="preserve">1.82849097251892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81569385528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82021045684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81117677688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81644630432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81418800354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83526563644409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83225464820862</t>
   </si>
   <si>
     <t xml:space="preserve">1.82246875762939</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85032117366791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89849877357483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93689036369324</t>
+    <t xml:space="preserve">1.85032153129578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89849889278412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93689024448395</t>
   </si>
   <si>
     <t xml:space="preserve">1.91731810569763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97979867458344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96474301815033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94667649269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97076523303986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96775388717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96248483657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10325360298157</t>
+    <t xml:space="preserve">1.97979855537415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96474325656891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94667673110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97076547145844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96775412559509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96248459815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10325384140015</t>
   </si>
   <si>
     <t xml:space="preserve">2.04378437995911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0242121219635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98732614517212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99937093257904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9858204126358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99033749103546</t>
+    <t xml:space="preserve">2.02421236038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98732626438141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99937057495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98582077026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99033737182617</t>
   </si>
   <si>
     <t xml:space="preserve">1.96624863147736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99861812591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96549582481384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97603476047516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98281013965607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02496528625488</t>
+    <t xml:space="preserve">1.99861788749695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96549606323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97603487968445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9828097820282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0249650478363</t>
   </si>
   <si>
     <t xml:space="preserve">2.06260395050049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07540106773376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08142328262329</t>
+    <t xml:space="preserve">2.07540130615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08142304420471</t>
   </si>
   <si>
     <t xml:space="preserve">2.08217597007751</t>
@@ -1058,25 +1058,25 @@
     <t xml:space="preserve">2.08593988418579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07765936851501</t>
+    <t xml:space="preserve">2.07765960693359</t>
   </si>
   <si>
     <t xml:space="preserve">2.09572601318359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09045648574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11153435707092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10024261474609</t>
+    <t xml:space="preserve">2.09045672416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11153411865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10024285316467</t>
   </si>
   <si>
     <t xml:space="preserve">2.08669257164001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07013154029846</t>
+    <t xml:space="preserve">2.07013177871704</t>
   </si>
   <si>
     <t xml:space="preserve">2.06034564971924</t>
@@ -1088,64 +1088,64 @@
     <t xml:space="preserve">2.05883979797363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07615375518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08368158340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10400652885437</t>
+    <t xml:space="preserve">2.07615399360657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08368182182312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10400676727295</t>
   </si>
   <si>
     <t xml:space="preserve">2.08518719673157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13185906410217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19057536125183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21315908432007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17552042007446</t>
+    <t xml:space="preserve">2.13185930252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19057583808899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21315884590149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17552018165588</t>
   </si>
   <si>
     <t xml:space="preserve">2.16799235343933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20563101768494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22068667411804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31101965904236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36371374130249</t>
+    <t xml:space="preserve">2.20563125610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22068691253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31101989746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36371397972107</t>
   </si>
   <si>
     <t xml:space="preserve">2.31854748725891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33360266685486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37124156951904</t>
+    <t xml:space="preserve">2.33360290527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37124180793762</t>
   </si>
   <si>
     <t xml:space="preserve">2.32607507705688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2884361743927</t>
+    <t xml:space="preserve">2.28843641281128</t>
   </si>
   <si>
     <t xml:space="preserve">2.26585340499878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28090858459473</t>
+    <t xml:space="preserve">2.28090882301331</t>
   </si>
   <si>
     <t xml:space="preserve">2.30349206924438</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">2.29596424102783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25832557678223</t>
+    <t xml:space="preserve">2.25832533836365</t>
   </si>
   <si>
     <t xml:space="preserve">2.19810366630554</t>
@@ -1163,19 +1163,19 @@
     <t xml:space="preserve">2.18304800987244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43899130821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38629746437073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55190801620483</t>
+    <t xml:space="preserve">2.43899154663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38629722595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55190753936768</t>
   </si>
   <si>
     <t xml:space="preserve">2.5443799495697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61965751647949</t>
+    <t xml:space="preserve">2.61965727806091</t>
   </si>
   <si>
     <t xml:space="preserve">2.46157479286194</t>
@@ -1184,22 +1184,22 @@
     <t xml:space="preserve">2.49168562889099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46910238265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4013524055481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43146371841431</t>
+    <t xml:space="preserve">2.46910262107849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40135264396667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43146347999573</t>
   </si>
   <si>
     <t xml:space="preserve">2.47663044929504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44651937484741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40888071060181</t>
+    <t xml:space="preserve">2.44651913642883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40888047218323</t>
   </si>
   <si>
     <t xml:space="preserve">2.48415780067444</t>
@@ -1208,10 +1208,10 @@
     <t xml:space="preserve">2.45404696464539</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41640830039978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5067412853241</t>
+    <t xml:space="preserve">2.4164080619812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50674104690552</t>
   </si>
   <si>
     <t xml:space="preserve">2.5293242931366</t>
@@ -1220,22 +1220,22 @@
     <t xml:space="preserve">2.57587647438049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59139370918274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58363509178162</t>
+    <t xml:space="preserve">2.59139394760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58363485336304</t>
   </si>
   <si>
     <t xml:space="preserve">2.56035900115967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50604867935181</t>
+    <t xml:space="preserve">2.50604820251465</t>
   </si>
   <si>
     <t xml:space="preserve">2.51380729675293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52156591415405</t>
+    <t xml:space="preserve">2.52156567573547</t>
   </si>
   <si>
     <t xml:space="preserve">2.54484176635742</t>
@@ -1262,10 +1262,10 @@
     <t xml:space="preserve">2.31208181381226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22673678398132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2034604549408</t>
+    <t xml:space="preserve">2.22673654556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20346069335938</t>
   </si>
   <si>
     <t xml:space="preserve">2.19570183753967</t>
@@ -1277,19 +1277,19 @@
     <t xml:space="preserve">2.23449516296387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25777101516724</t>
+    <t xml:space="preserve">2.25777125358582</t>
   </si>
   <si>
     <t xml:space="preserve">2.1724259853363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11811542510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18794322013855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25001263618469</t>
+    <t xml:space="preserve">2.11811518669128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18794345855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25001239776611</t>
   </si>
   <si>
     <t xml:space="preserve">2.12587380409241</t>
@@ -1298,16 +1298,16 @@
     <t xml:space="preserve">2.10259819030762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13363289833069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09483933448792</t>
+    <t xml:space="preserve">2.13363265991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09483909606934</t>
   </si>
   <si>
     <t xml:space="preserve">2.08708071708679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07932186126709</t>
+    <t xml:space="preserve">2.07932209968567</t>
   </si>
   <si>
     <t xml:space="preserve">2.07156324386597</t>
@@ -1328,22 +1328,22 @@
     <t xml:space="preserve">2.18018460273743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29656434059143</t>
+    <t xml:space="preserve">2.29656457901001</t>
   </si>
   <si>
     <t xml:space="preserve">2.03276991844177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01725268363953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02501153945923</t>
+    <t xml:space="preserve">2.01725244522095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02501130104065</t>
   </si>
   <si>
     <t xml:space="preserve">2.00949382781982</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97070074081421</t>
+    <t xml:space="preserve">1.97070062160492</t>
   </si>
   <si>
     <t xml:space="preserve">1.96294188499451</t>
@@ -1352,19 +1352,19 @@
     <t xml:space="preserve">1.93966591358185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88535523414612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87759685516357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85432076454163</t>
+    <t xml:space="preserve">1.8853554725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.877596616745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85432052612305</t>
   </si>
   <si>
     <t xml:space="preserve">1.86983799934387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79225134849548</t>
+    <t xml:space="preserve">1.79225122928619</t>
   </si>
   <si>
     <t xml:space="preserve">1.83880352973938</t>
@@ -1373,10 +1373,10 @@
     <t xml:space="preserve">1.83104491233826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86207926273346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15690851211548</t>
+    <t xml:space="preserve">1.86207938194275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15690875053406</t>
   </si>
   <si>
     <t xml:space="preserve">2.06380462646484</t>
@@ -1388,43 +1388,43 @@
     <t xml:space="preserve">2.0017352104187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97845935821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99397671222687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92414844036102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84656202793121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80776858329773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.753457903862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77673411369324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74569940567017</t>
+    <t xml:space="preserve">1.97845947742462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99397683143616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9241486787796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84656190872192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80776882171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75345814228058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77673399448395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74569928646088</t>
   </si>
   <si>
     <t xml:space="preserve">1.82328605651855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89311397075653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91639018058777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21121954917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11035633087158</t>
+    <t xml:space="preserve">1.89311408996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91639029979706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2112193107605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11035680770874</t>
   </si>
   <si>
     <t xml:space="preserve">2.05604600906372</t>
@@ -1436,13 +1436,13 @@
     <t xml:space="preserve">2.24225378036499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35087513923645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31984090805054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3353579044342</t>
+    <t xml:space="preserve">2.35087537765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31984066963196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33535766601562</t>
   </si>
   <si>
     <t xml:space="preserve">2.35863399505615</t>
@@ -1457,142 +1457,145 @@
     <t xml:space="preserve">2.38966846466064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39742732048035</t>
+    <t xml:space="preserve">2.39742708206177</t>
   </si>
   <si>
     <t xml:space="preserve">2.41294455528259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42070341110229</t>
+    <t xml:space="preserve">2.42070317268372</t>
   </si>
   <si>
     <t xml:space="preserve">2.36639261245728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34311652183533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37415099143982</t>
+    <t xml:space="preserve">2.34311628341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37415146827698</t>
   </si>
   <si>
     <t xml:space="preserve">2.45173788070679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47501397132874</t>
+    <t xml:space="preserve">2.47501373291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5526008605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54447102546692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52008318901062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4956955909729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4387903213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45504879951477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47943687438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48756623268127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50382471084595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40627312660217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43066120147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42253160476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36562657356262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39001441001892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28433346748352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27620434761047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2274284362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23555779457092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25181651115417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26807522773743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.357497215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32498025894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34123849868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37375617027283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4631781578064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51195406913757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52821254730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53634190559387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58511781692505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5932469367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56072998046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60137629508972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60950541496277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5688591003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.576988697052</t>
   </si>
   <si>
     <t xml:space="preserve">2.55260062217712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5444712638855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5200834274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4956955909729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4387903213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45504903793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47943687438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4875659942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50382471084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40627312660217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43066096305847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42253160476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36562657356262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39001441001892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2843337059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27620434761047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2274284362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23555779457092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25181651115417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26807522773743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35749745368958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32498025894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34123873710632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37375617027283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4631781578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51195383071899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52821254730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53634214401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58511781692505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59324717521667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56072974205017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60137629508972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60950541496277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5688591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57698845863342</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.4144024848938</t>
   </si>
   <si>
     <t xml:space="preserve">2.3331093788147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34936785697937</t>
+    <t xml:space="preserve">2.34936809539795</t>
   </si>
   <si>
     <t xml:space="preserve">2.39814376831055</t>
@@ -1601,22 +1604,22 @@
     <t xml:space="preserve">2.47130751609802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44691967964172</t>
+    <t xml:space="preserve">2.44691944122314</t>
   </si>
   <si>
     <t xml:space="preserve">2.38188529014587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29246282577515</t>
+    <t xml:space="preserve">2.29246306419373</t>
   </si>
   <si>
     <t xml:space="preserve">2.30872130393982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30059194564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11361837387085</t>
+    <t xml:space="preserve">2.30059218406677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11361813545227</t>
   </si>
   <si>
     <t xml:space="preserve">2.18678212165833</t>
@@ -1634,19 +1637,19 @@
     <t xml:space="preserve">2.1217474937439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.048583984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89412689208984</t>
+    <t xml:space="preserve">2.04858374595642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89412713050842</t>
   </si>
   <si>
     <t xml:space="preserve">1.65837728977203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66650664806366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6258602142334</t>
+    <t xml:space="preserve">1.66650676727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62586009502411</t>
   </si>
   <si>
     <t xml:space="preserve">1.47140347957611</t>
@@ -1664,19 +1667,19 @@
     <t xml:space="preserve">1.55676102638245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54863178730011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53237330913544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4957914352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58521378040314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6014723777771</t>
+    <t xml:space="preserve">1.54863166809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53237318992615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49579131603241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58521366119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60147249698639</t>
   </si>
   <si>
     <t xml:space="preserve">1.5730197429657</t>
@@ -1685,25 +1688,25 @@
     <t xml:space="preserve">1.56082582473755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58114922046661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56895506381989</t>
+    <t xml:space="preserve">1.58114910125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5689549446106</t>
   </si>
   <si>
     <t xml:space="preserve">1.63398957252502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69089448451996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60553693771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62179553508759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58927822113037</t>
+    <t xml:space="preserve">1.69089484214783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60553705692291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62179565429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58927834033966</t>
   </si>
   <si>
     <t xml:space="preserve">1.61773085594177</t>
@@ -1712,13 +1715,13 @@
     <t xml:space="preserve">1.67463600635529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7071533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76405847072601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73154127597809</t>
+    <t xml:space="preserve">1.70715320110321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76405835151672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73154103755951</t>
   </si>
   <si>
     <t xml:space="preserve">1.71528244018555</t>
@@ -1730,40 +1733,40 @@
     <t xml:space="preserve">1.6502480506897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74779975414276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75592887401581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77218759059906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78844618797302</t>
+    <t xml:space="preserve">1.74779987335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75592911243439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77218747138977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78844630718231</t>
   </si>
   <si>
     <t xml:space="preserve">1.82096338272095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87786865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82909286022186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8047046661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81283402442932</t>
+    <t xml:space="preserve">1.87786841392517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82909274101257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80470502376556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81283414363861</t>
   </si>
   <si>
     <t xml:space="preserve">1.79657554626465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78031706809998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72341179847717</t>
+    <t xml:space="preserve">1.78031694889069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72341191768646</t>
   </si>
   <si>
     <t xml:space="preserve">1.73967039585114</t>
@@ -1772,7 +1775,7 @@
     <t xml:space="preserve">1.68276536464691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60960149765015</t>
+    <t xml:space="preserve">1.60960161685944</t>
   </si>
   <si>
     <t xml:space="preserve">1.64211893081665</t>
@@ -1784,13 +1787,13 @@
     <t xml:space="preserve">1.52830851078033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53643786907196</t>
+    <t xml:space="preserve">1.53643774986267</t>
   </si>
   <si>
     <t xml:space="preserve">1.49985611438751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48766195774078</t>
+    <t xml:space="preserve">1.48766207695007</t>
   </si>
   <si>
     <t xml:space="preserve">1.48359739780426</t>
@@ -1799,10 +1802,10 @@
     <t xml:space="preserve">1.43075704574585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42262768745422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41043365001678</t>
+    <t xml:space="preserve">1.42262780666351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41043376922607</t>
   </si>
   <si>
     <t xml:space="preserve">1.40636897087097</t>
@@ -1814,16 +1817,16 @@
     <t xml:space="preserve">1.4144983291626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36572253704071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3332052230835</t>
+    <t xml:space="preserve">1.36572241783142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33320546150208</t>
   </si>
   <si>
     <t xml:space="preserve">1.38198125362396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35759329795837</t>
+    <t xml:space="preserve">1.35759341716766</t>
   </si>
   <si>
     <t xml:space="preserve">1.30475270748138</t>
@@ -1832,10 +1835,10 @@
     <t xml:space="preserve">1.29255890846252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3088173866272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33727025985718</t>
+    <t xml:space="preserve">1.30881750583649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33727014064789</t>
   </si>
   <si>
     <t xml:space="preserve">1.32507598400116</t>
@@ -1856,10 +1859,10 @@
     <t xml:space="preserve">1.40230441093445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3860456943512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39011061191559</t>
+    <t xml:space="preserve">1.38604581356049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3901104927063</t>
   </si>
   <si>
     <t xml:space="preserve">1.37791657447815</t>
@@ -1871,16 +1874,16 @@
     <t xml:space="preserve">1.52017939090729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55269646644592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54456722736359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49172687530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52424395084381</t>
+    <t xml:space="preserve">1.55269658565521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5445671081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49172675609589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5242440700531</t>
   </si>
   <si>
     <t xml:space="preserve">1.50798523426056</t>
@@ -1889,22 +1892,22 @@
     <t xml:space="preserve">1.51611471176147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54050278663635</t>
+    <t xml:space="preserve">1.54050266742706</t>
   </si>
   <si>
     <t xml:space="preserve">1.47953283786774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86973941326141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95103228092194</t>
+    <t xml:space="preserve">1.86973917484283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95103216171265</t>
   </si>
   <si>
     <t xml:space="preserve">2.0729718208313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25994563102722</t>
+    <t xml:space="preserve">2.2599458694458</t>
   </si>
   <si>
     <t xml:space="preserve">2.24368715286255</t>
@@ -1916,22 +1919,19 @@
     <t xml:space="preserve">2.14613556861877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05671310424805</t>
+    <t xml:space="preserve">2.05671286582947</t>
   </si>
   <si>
     <t xml:space="preserve">2.13800597190857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21116971969604</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.21116995811462</t>
   </si>
   <si>
     <t xml:space="preserve">2.21945142745972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2360143661499</t>
+    <t xml:space="preserve">2.23601460456848</t>
   </si>
   <si>
     <t xml:space="preserve">2.24429607391357</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">2.25257754325867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20288825035095</t>
+    <t xml:space="preserve">2.20288848876953</t>
   </si>
   <si>
     <t xml:space="preserve">2.22773313522339</t>
@@ -1958,10 +1958,10 @@
     <t xml:space="preserve">2.36023759841919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36851930618286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38508224487305</t>
+    <t xml:space="preserve">2.36851906776428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38508200645447</t>
   </si>
   <si>
     <t xml:space="preserve">2.40164518356323</t>
@@ -1973,16 +1973,16 @@
     <t xml:space="preserve">2.4761791229248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4844605922699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49274230003357</t>
+    <t xml:space="preserve">2.48446035385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49274206161499</t>
   </si>
   <si>
     <t xml:space="preserve">2.418208360672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39336347579956</t>
+    <t xml:space="preserve">2.39336371421814</t>
   </si>
   <si>
     <t xml:space="preserve">2.37680077552795</t>
@@ -2009,7 +2009,7 @@
     <t xml:space="preserve">2.31882977485657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31054830551147</t>
+    <t xml:space="preserve">2.31054854393005</t>
   </si>
   <si>
     <t xml:space="preserve">2.35195589065552</t>
@@ -2024,22 +2024,22 @@
     <t xml:space="preserve">2.27742218971252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1531994342804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12835454940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13663601875305</t>
+    <t xml:space="preserve">2.15319919586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12835478782654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13663625717163</t>
   </si>
   <si>
     <t xml:space="preserve">2.18632531166077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08694672584534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10351014137268</t>
+    <t xml:space="preserve">2.08694696426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1035099029541</t>
   </si>
   <si>
     <t xml:space="preserve">2.07038378715515</t>
@@ -2057,10 +2057,10 @@
     <t xml:space="preserve">2.26914072036743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26085925102234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40992665290833</t>
+    <t xml:space="preserve">2.26085901260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4099268913269</t>
   </si>
   <si>
     <t xml:space="preserve">2.46789741516113</t>
@@ -2072,19 +2072,19 @@
     <t xml:space="preserve">2.52586841583252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50930500030518</t>
+    <t xml:space="preserve">2.50930523872375</t>
   </si>
   <si>
     <t xml:space="preserve">2.62524676322937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71634340286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69978022575378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81572198867798</t>
+    <t xml:space="preserve">2.71634364128113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69978046417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81572222709656</t>
   </si>
   <si>
     <t xml:space="preserve">2.84884834289551</t>
@@ -2096,13 +2096,13 @@
     <t xml:space="preserve">3.01447892189026</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03104162216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24636197090149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23808002471924</t>
+    <t xml:space="preserve">3.03104186058044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24636220932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2380805015564</t>
   </si>
   <si>
     <t xml:space="preserve">3.22979879379272</t>
@@ -2111,13 +2111,13 @@
     <t xml:space="preserve">3.3043327331543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12213897705078</t>
+    <t xml:space="preserve">3.1221387386322</t>
   </si>
   <si>
     <t xml:space="preserve">3.16354656219482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17182803153992</t>
+    <t xml:space="preserve">3.17182779312134</t>
   </si>
   <si>
     <t xml:space="preserve">3.21323561668396</t>
@@ -2135,16 +2135,16 @@
     <t xml:space="preserve">3.13042020797729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10557579994202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13870215415955</t>
+    <t xml:space="preserve">3.1055760383606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13870191574097</t>
   </si>
   <si>
     <t xml:space="preserve">3.08901286125183</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07244944572449</t>
+    <t xml:space="preserve">3.07244920730591</t>
   </si>
   <si>
     <t xml:space="preserve">3.11385703086853</t>
@@ -2156,28 +2156,28 @@
     <t xml:space="preserve">3.06416797637939</t>
   </si>
   <si>
-    <t xml:space="preserve">3.254643201828</t>
+    <t xml:space="preserve">3.25464367866516</t>
   </si>
   <si>
     <t xml:space="preserve">3.09729433059692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93994522094727</t>
+    <t xml:space="preserve">2.93994498252869</t>
   </si>
   <si>
     <t xml:space="preserve">3.02276039123535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04760503768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05588674545288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15526485443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03932356834412</t>
+    <t xml:space="preserve">3.04760479927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0558865070343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15526461601257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03932332992554</t>
   </si>
   <si>
     <t xml:space="preserve">2.98963403701782</t>
@@ -2192,13 +2192,13 @@
     <t xml:space="preserve">2.97307133674622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20495438575745</t>
+    <t xml:space="preserve">3.20495414733887</t>
   </si>
   <si>
     <t xml:space="preserve">3.27948784828186</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27120637893677</t>
+    <t xml:space="preserve">3.27120661735535</t>
   </si>
   <si>
     <t xml:space="preserve">3.29605102539062</t>
@@ -2228,13 +2228,13 @@
     <t xml:space="preserve">4.95042657852173</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01585054397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5828595161438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36477899551392</t>
+    <t xml:space="preserve">5.01585006713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58285999298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36477947235107</t>
   </si>
   <si>
     <t xml:space="preserve">5.05946683883667</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">4.97223424911499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14669847488403</t>
+    <t xml:space="preserve">5.14669895172119</t>
   </si>
   <si>
     <t xml:space="preserve">5.08127450942993</t>
@@ -2252,7 +2252,7 @@
     <t xml:space="preserve">5.19031476974487</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21212291717529</t>
+    <t xml:space="preserve">5.21212244033813</t>
   </si>
   <si>
     <t xml:space="preserve">5.27754688262939</t>
@@ -2267,22 +2267,22 @@
     <t xml:space="preserve">5.47381925582886</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53924369812012</t>
+    <t xml:space="preserve">5.53924322128296</t>
   </si>
   <si>
     <t xml:space="preserve">5.45201110839844</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43020343780518</t>
+    <t xml:space="preserve">5.43020296096802</t>
   </si>
   <si>
     <t xml:space="preserve">5.40839529037476</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3429708480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38658714294434</t>
+    <t xml:space="preserve">5.34297132492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38658761978149</t>
   </si>
   <si>
     <t xml:space="preserve">5.32116317749023</t>
@@ -2294,19 +2294,19 @@
     <t xml:space="preserve">5.99721240997314</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82591819763184</t>
+    <t xml:space="preserve">6.82591772079468</t>
   </si>
   <si>
     <t xml:space="preserve">7.32750272750854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93495798110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78230237960815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73868560791016</t>
+    <t xml:space="preserve">6.93495845794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.782301902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73868608474731</t>
   </si>
   <si>
     <t xml:space="preserve">6.67326211929321</t>
@@ -2321,7 +2321,7 @@
     <t xml:space="preserve">6.25890922546387</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32433319091797</t>
+    <t xml:space="preserve">6.32433271408081</t>
   </si>
   <si>
     <t xml:space="preserve">6.23710107803345</t>
@@ -2336,28 +2336,28 @@
     <t xml:space="preserve">6.41156530380249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62964534759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76049423217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02219104766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0658073425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04399871826172</t>
+    <t xml:space="preserve">6.62964582443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76049375534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0221905708313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06580686569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04399824142456</t>
   </si>
   <si>
     <t xml:space="preserve">7.0876145362854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45835208892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52377510070801</t>
+    <t xml:space="preserve">7.45835161209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52377557754517</t>
   </si>
   <si>
     <t xml:space="preserve">7.78547239303589</t>
@@ -2369,7 +2369,7 @@
     <t xml:space="preserve">8.19982433319092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11259365081787</t>
+    <t xml:space="preserve">8.11259269714355</t>
   </si>
   <si>
     <t xml:space="preserve">8.37428951263428</t>
@@ -26883,7 +26883,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G909" t="s">
-        <v>489</v>
+        <v>524</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -26935,7 +26935,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G911" t="s">
-        <v>489</v>
+        <v>524</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -27091,7 +27091,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G917" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -27143,7 +27143,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G919" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -27195,7 +27195,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G921" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -27221,7 +27221,7 @@
         <v>29.5</v>
       </c>
       <c r="G922" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -27403,7 +27403,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G929" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -27507,7 +27507,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G933" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -27533,7 +27533,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G934" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -27559,7 +27559,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G935" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -27611,7 +27611,7 @@
         <v>29.5</v>
       </c>
       <c r="G937" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -27637,7 +27637,7 @@
         <v>29.5</v>
       </c>
       <c r="G938" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -27819,7 +27819,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G945" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -27949,7 +27949,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G950" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -28001,7 +28001,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G952" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -28053,7 +28053,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G954" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -28391,7 +28391,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G967" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -28469,7 +28469,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G970" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -28495,7 +28495,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G971" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -28547,7 +28547,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G973" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -28625,7 +28625,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G976" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -29639,7 +29639,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1015" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -29691,7 +29691,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1017" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -30107,7 +30107,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1033" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -30133,7 +30133,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1034" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -30159,7 +30159,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1035" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -30185,7 +30185,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1036" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -30211,7 +30211,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1037" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -30237,7 +30237,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1038" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -30341,7 +30341,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1042" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -30367,7 +30367,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1043" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -30393,7 +30393,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1044" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -30419,7 +30419,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1045" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -30471,7 +30471,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1047" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -30549,7 +30549,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1050" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -30627,7 +30627,7 @@
         <v>26</v>
       </c>
       <c r="G1053" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -30653,7 +30653,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1054" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -30705,7 +30705,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1056" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -30731,7 +30731,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1057" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -30757,7 +30757,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1058" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -30783,7 +30783,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1059" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -30809,7 +30809,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1060" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -30835,7 +30835,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1061" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -30861,7 +30861,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1062" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -30887,7 +30887,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1063" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -30913,7 +30913,7 @@
         <v>20.5</v>
       </c>
       <c r="G1064" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -30939,7 +30939,7 @@
         <v>20</v>
       </c>
       <c r="G1065" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -30965,7 +30965,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1066" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -30991,7 +30991,7 @@
         <v>18.5</v>
       </c>
       <c r="G1067" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -31017,7 +31017,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1068" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -31043,7 +31043,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1069" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -31069,7 +31069,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G1070" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -31095,7 +31095,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G1071" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -31121,7 +31121,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1072" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -31147,7 +31147,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1073" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -31173,7 +31173,7 @@
         <v>19.5</v>
       </c>
       <c r="G1074" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -31199,7 +31199,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1075" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -31225,7 +31225,7 @@
         <v>20.5</v>
       </c>
       <c r="G1076" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -31251,7 +31251,7 @@
         <v>19.5</v>
       </c>
       <c r="G1077" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -31277,7 +31277,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G1078" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -31303,7 +31303,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1079" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -31329,7 +31329,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1080" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -31355,7 +31355,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1081" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -31381,7 +31381,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1082" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -31407,7 +31407,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1083" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -31433,7 +31433,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1084" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -31459,7 +31459,7 @@
         <v>19.5</v>
       </c>
       <c r="G1085" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -31485,7 +31485,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1086" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -31511,7 +31511,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1087" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -31537,7 +31537,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1088" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -31563,7 +31563,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1089" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -31589,7 +31589,7 @@
         <v>19.75</v>
       </c>
       <c r="G1090" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -31615,7 +31615,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G1091" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -31641,7 +31641,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1092" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -31667,7 +31667,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1093" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -31693,7 +31693,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1094" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -31719,7 +31719,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1095" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -31745,7 +31745,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1096" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -31771,7 +31771,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1097" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -31797,7 +31797,7 @@
         <v>21</v>
       </c>
       <c r="G1098" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -31823,7 +31823,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1099" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -31849,7 +31849,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1100" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -31875,7 +31875,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1101" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -31901,7 +31901,7 @@
         <v>21</v>
       </c>
       <c r="G1102" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -31927,7 +31927,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1103" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -31953,7 +31953,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1104" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -31979,7 +31979,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1105" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -32005,7 +32005,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1106" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -32031,7 +32031,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1107" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -32057,7 +32057,7 @@
         <v>20.5</v>
       </c>
       <c r="G1108" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -32083,7 +32083,7 @@
         <v>20.5</v>
       </c>
       <c r="G1109" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -32109,7 +32109,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1110" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -32135,7 +32135,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1111" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -32161,7 +32161,7 @@
         <v>20.5</v>
       </c>
       <c r="G1112" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -32187,7 +32187,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1113" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -32213,7 +32213,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1114" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -32239,7 +32239,7 @@
         <v>20.5</v>
       </c>
       <c r="G1115" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -32265,7 +32265,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1116" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -32291,7 +32291,7 @@
         <v>21</v>
       </c>
       <c r="G1117" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -32317,7 +32317,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1118" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -32343,7 +32343,7 @@
         <v>21</v>
       </c>
       <c r="G1119" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -32369,7 +32369,7 @@
         <v>21.5</v>
       </c>
       <c r="G1120" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -32395,7 +32395,7 @@
         <v>21.5</v>
       </c>
       <c r="G1121" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -32421,7 +32421,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1122" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -32447,7 +32447,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1123" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -32473,7 +32473,7 @@
         <v>22</v>
       </c>
       <c r="G1124" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -32499,7 +32499,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1125" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -32525,7 +32525,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1126" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -32551,7 +32551,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1127" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -32577,7 +32577,7 @@
         <v>21.5</v>
       </c>
       <c r="G1128" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -32603,7 +32603,7 @@
         <v>22</v>
       </c>
       <c r="G1129" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -32629,7 +32629,7 @@
         <v>22</v>
       </c>
       <c r="G1130" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -32655,7 +32655,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1131" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -32681,7 +32681,7 @@
         <v>22.5</v>
       </c>
       <c r="G1132" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -32707,7 +32707,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1133" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -32733,7 +32733,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1134" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -32759,7 +32759,7 @@
         <v>22</v>
       </c>
       <c r="G1135" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -32785,7 +32785,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1136" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -32811,7 +32811,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1137" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -32837,7 +32837,7 @@
         <v>22</v>
       </c>
       <c r="G1138" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -32863,7 +32863,7 @@
         <v>22</v>
       </c>
       <c r="G1139" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -32889,7 +32889,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1140" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -32915,7 +32915,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1141" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -32941,7 +32941,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1142" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -32967,7 +32967,7 @@
         <v>22</v>
       </c>
       <c r="G1143" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -32993,7 +32993,7 @@
         <v>22</v>
       </c>
       <c r="G1144" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -33019,7 +33019,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1145" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -33045,7 +33045,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1146" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -33071,7 +33071,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1147" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -33097,7 +33097,7 @@
         <v>21.5</v>
       </c>
       <c r="G1148" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -33123,7 +33123,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1149" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -33149,7 +33149,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1150" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -33175,7 +33175,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1151" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -33201,7 +33201,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1152" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -33227,7 +33227,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1153" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -33253,7 +33253,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1154" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -33279,7 +33279,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1155" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -33305,7 +33305,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1156" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -33331,7 +33331,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1157" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -33357,7 +33357,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1158" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -33383,7 +33383,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1159" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -33409,7 +33409,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1160" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -33435,7 +33435,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1161" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -33461,7 +33461,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1162" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -33487,7 +33487,7 @@
         <v>20.5</v>
       </c>
       <c r="G1163" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -33513,7 +33513,7 @@
         <v>20.5</v>
       </c>
       <c r="G1164" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -33539,7 +33539,7 @@
         <v>21</v>
       </c>
       <c r="G1165" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -33565,7 +33565,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1166" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -33591,7 +33591,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1167" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -33617,7 +33617,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1168" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -33643,7 +33643,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1169" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -33669,7 +33669,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1170" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -33695,7 +33695,7 @@
         <v>21.5</v>
       </c>
       <c r="G1171" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -33721,7 +33721,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1172" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -33747,7 +33747,7 @@
         <v>21.5</v>
       </c>
       <c r="G1173" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -33773,7 +33773,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1174" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -33799,7 +33799,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1175" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -33825,7 +33825,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1176" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -33851,7 +33851,7 @@
         <v>21.5</v>
       </c>
       <c r="G1177" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -33877,7 +33877,7 @@
         <v>21.5</v>
       </c>
       <c r="G1178" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33903,7 +33903,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1179" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -33929,7 +33929,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1180" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -33955,7 +33955,7 @@
         <v>21.5</v>
       </c>
       <c r="G1181" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -33981,7 +33981,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1182" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -34007,7 +34007,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1183" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -34033,7 +34033,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1184" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -34059,7 +34059,7 @@
         <v>21</v>
       </c>
       <c r="G1185" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -34085,7 +34085,7 @@
         <v>21</v>
       </c>
       <c r="G1186" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -34111,7 +34111,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1187" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -34137,7 +34137,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1188" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -34163,7 +34163,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1189" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -34189,7 +34189,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1190" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -34215,7 +34215,7 @@
         <v>20</v>
       </c>
       <c r="G1191" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -34241,7 +34241,7 @@
         <v>20</v>
       </c>
       <c r="G1192" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -34267,7 +34267,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1193" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -34293,7 +34293,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1194" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -34319,7 +34319,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1195" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -34345,7 +34345,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1196" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -34371,7 +34371,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1197" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -34397,7 +34397,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1198" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -34423,7 +34423,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1199" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -34449,7 +34449,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1200" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -34475,7 +34475,7 @@
         <v>19.75</v>
       </c>
       <c r="G1201" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -34501,7 +34501,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1202" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -34527,7 +34527,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1203" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -34553,7 +34553,7 @@
         <v>19.75</v>
       </c>
       <c r="G1204" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -34579,7 +34579,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1205" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -34605,7 +34605,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1206" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -34631,7 +34631,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1207" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -34657,7 +34657,7 @@
         <v>18.5</v>
       </c>
       <c r="G1208" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -34683,7 +34683,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1209" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -34709,7 +34709,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1210" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -34735,7 +34735,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1211" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -34761,7 +34761,7 @@
         <v>18.5</v>
       </c>
       <c r="G1212" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -34787,7 +34787,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1213" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -34813,7 +34813,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1214" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -34839,7 +34839,7 @@
         <v>18.25</v>
       </c>
       <c r="G1215" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -34865,7 +34865,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1216" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -34891,7 +34891,7 @@
         <v>17.5</v>
       </c>
       <c r="G1217" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -34917,7 +34917,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1218" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -34943,7 +34943,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1219" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -34969,7 +34969,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1220" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -34995,7 +34995,7 @@
         <v>17.5</v>
       </c>
       <c r="G1221" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -35021,7 +35021,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1222" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -35047,7 +35047,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1223" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -35073,7 +35073,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1224" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -35099,7 +35099,7 @@
         <v>17</v>
       </c>
       <c r="G1225" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -35125,7 +35125,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1226" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -35151,7 +35151,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1227" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -35177,7 +35177,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1228" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -35203,7 +35203,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1229" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -35229,7 +35229,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1230" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -35255,7 +35255,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1231" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -35281,7 +35281,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1232" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -35307,7 +35307,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1233" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -35333,7 +35333,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1234" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -35359,7 +35359,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1235" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -35385,7 +35385,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1236" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -35411,7 +35411,7 @@
         <v>17.25</v>
       </c>
       <c r="G1237" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -35437,7 +35437,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1238" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -35463,7 +35463,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1239" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -35489,7 +35489,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1240" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -35515,7 +35515,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1241" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -35541,7 +35541,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1242" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -35567,7 +35567,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1243" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -35593,7 +35593,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1244" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -35619,7 +35619,7 @@
         <v>17.5</v>
       </c>
       <c r="G1245" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -35645,7 +35645,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1246" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -35671,7 +35671,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1247" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -35697,7 +35697,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1248" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -35723,7 +35723,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1249" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -35749,7 +35749,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1250" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -35775,7 +35775,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1251" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -35801,7 +35801,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1252" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -35827,7 +35827,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1253" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -35853,7 +35853,7 @@
         <v>19</v>
       </c>
       <c r="G1254" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -35879,7 +35879,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1255" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -35905,7 +35905,7 @@
         <v>18.5</v>
       </c>
       <c r="G1256" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -35931,7 +35931,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1257" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -35957,7 +35957,7 @@
         <v>18.25</v>
       </c>
       <c r="G1258" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -35983,7 +35983,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1259" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -36009,7 +36009,7 @@
         <v>18.5</v>
       </c>
       <c r="G1260" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -36035,7 +36035,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1261" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -36061,7 +36061,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1262" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -36087,7 +36087,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1263" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -36113,7 +36113,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1264" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -36139,7 +36139,7 @@
         <v>18.75</v>
       </c>
       <c r="G1265" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -36165,7 +36165,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1266" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -36191,7 +36191,7 @@
         <v>18.5</v>
       </c>
       <c r="G1267" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -36217,7 +36217,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G1268" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -36243,7 +36243,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G1269" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -36269,7 +36269,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1270" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -36295,7 +36295,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1271" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -36321,7 +36321,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1272" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -36347,7 +36347,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1273" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -36373,7 +36373,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1274" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -36399,7 +36399,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1275" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -36425,7 +36425,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1276" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -36451,7 +36451,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1277" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -36477,7 +36477,7 @@
         <v>19</v>
       </c>
       <c r="G1278" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -36503,7 +36503,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1279" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -36529,7 +36529,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G1280" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -36555,7 +36555,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1281" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -36581,7 +36581,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1282" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -36607,7 +36607,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1283" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -36633,7 +36633,7 @@
         <v>18.5</v>
       </c>
       <c r="G1284" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -36659,7 +36659,7 @@
         <v>18.5</v>
       </c>
       <c r="G1285" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -36685,7 +36685,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1286" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -36711,7 +36711,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1287" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -36737,7 +36737,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1288" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -36763,7 +36763,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1289" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -36789,7 +36789,7 @@
         <v>18.25</v>
       </c>
       <c r="G1290" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -36815,7 +36815,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1291" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -36841,7 +36841,7 @@
         <v>19</v>
       </c>
       <c r="G1292" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -36867,7 +36867,7 @@
         <v>23</v>
       </c>
       <c r="G1293" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -36893,7 +36893,7 @@
         <v>24</v>
       </c>
       <c r="G1294" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -36919,7 +36919,7 @@
         <v>25.5</v>
       </c>
       <c r="G1295" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -36997,7 +36997,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1298" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -37049,7 +37049,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1300" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -37205,7 +37205,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1306" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -37231,7 +37231,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1307" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -37257,7 +37257,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1308" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -37361,7 +37361,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1312" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -37387,7 +37387,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1313" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -37491,7 +37491,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1317" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -37517,7 +37517,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1318" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -37543,7 +37543,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1319" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -37569,7 +37569,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1320" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -37595,7 +37595,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1321" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -37621,7 +37621,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1322" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -37647,7 +37647,7 @@
         <v>26</v>
       </c>
       <c r="G1323" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -37673,7 +37673,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1324" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -37699,7 +37699,7 @@
         <v>25.5</v>
       </c>
       <c r="G1325" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -37725,7 +37725,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1326" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -37751,7 +37751,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1327" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -37777,7 +37777,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1328" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -37803,7 +37803,7 @@
         <v>26</v>
       </c>
       <c r="G1329" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -37855,7 +37855,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1331" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -37881,7 +37881,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1332" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -37907,7 +37907,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1333" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -37933,7 +37933,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1334" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -37959,7 +37959,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1335" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -37985,7 +37985,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1336" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -38037,7 +38037,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1338" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -68075,7 +68075,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.6357986111</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>1118</v>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -44,58 +44,58 @@
     <t xml:space="preserve">AUTME.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24544644355774</t>
+    <t xml:space="preserve">1.24544656276703</t>
   </si>
   <si>
     <t xml:space="preserve">1.24330163002014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22256803512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21541845798492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22185325622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21470355987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23615229129791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21327364444733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20683920383453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2011194229126</t>
+    <t xml:space="preserve">1.22256815433502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2154186964035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2218531370163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2147034406662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23615217208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21327352523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20683896541595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20111954212189</t>
   </si>
   <si>
     <t xml:space="preserve">1.20040452480316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16680181026459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19468474388123</t>
+    <t xml:space="preserve">1.1668016910553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19468486309052</t>
   </si>
   <si>
     <t xml:space="preserve">1.25688564777374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25045108795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24687659740448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25116610527039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26475024223328</t>
+    <t xml:space="preserve">1.25045120716095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2468763589859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25116622447968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26475012302399</t>
   </si>
   <si>
     <t xml:space="preserve">1.2354371547699</t>
@@ -107,13 +107,13 @@
     <t xml:space="preserve">1.21041393280029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22113823890686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19396996498108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22685790061951</t>
+    <t xml:space="preserve">1.22113811969757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19397008419037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2268580198288</t>
   </si>
   <si>
     <t xml:space="preserve">1.20469439029694</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">1.25831568241119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.265465259552</t>
+    <t xml:space="preserve">1.26546537876129</t>
   </si>
   <si>
     <t xml:space="preserve">1.25903069972992</t>
@@ -131,16 +131,16 @@
     <t xml:space="preserve">1.26903998851776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21684837341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22828757762909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27404463291168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26689505577087</t>
+    <t xml:space="preserve">1.21684849262238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22828769683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27404451370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26689493656158</t>
   </si>
   <si>
     <t xml:space="preserve">1.27261471748352</t>
@@ -149,28 +149,28 @@
     <t xml:space="preserve">1.27189981937408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2790492773056</t>
+    <t xml:space="preserve">1.27904915809631</t>
   </si>
   <si>
     <t xml:space="preserve">1.26760995388031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25545573234558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26260530948639</t>
+    <t xml:space="preserve">1.25545585155487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26260542869568</t>
   </si>
   <si>
     <t xml:space="preserve">1.24830627441406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2490211725235</t>
+    <t xml:space="preserve">1.24902129173279</t>
   </si>
   <si>
     <t xml:space="preserve">1.24258661270142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23686695098877</t>
+    <t xml:space="preserve">1.23686707019806</t>
   </si>
   <si>
     <t xml:space="preserve">1.23472225666046</t>
@@ -185,25 +185,25 @@
     <t xml:space="preserve">1.26176810264587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26835513114929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27860128879547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2764059305191</t>
+    <t xml:space="preserve">1.26835501194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27860140800476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27640581130981</t>
   </si>
   <si>
     <t xml:space="preserve">1.27421021461487</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27494192123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26323175430298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27128267288208</t>
+    <t xml:space="preserve">1.27494215965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26323187351227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27128255367279</t>
   </si>
   <si>
     <t xml:space="preserve">1.26689124107361</t>
@@ -212,31 +212,31 @@
     <t xml:space="preserve">1.28445649147034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28079700469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2793333530426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27347826957703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27274632453918</t>
+    <t xml:space="preserve">1.280797123909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27933323383331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27347815036774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27274644374847</t>
   </si>
   <si>
     <t xml:space="preserve">1.26615929603577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28226089477539</t>
+    <t xml:space="preserve">1.28226101398468</t>
   </si>
   <si>
     <t xml:space="preserve">1.28811597824097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28738403320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28299272060394</t>
+    <t xml:space="preserve">1.28738391399384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28299283981323</t>
   </si>
   <si>
     <t xml:space="preserve">1.26396381855011</t>
@@ -248,37 +248,37 @@
     <t xml:space="preserve">1.24347102642059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22956514358521</t>
+    <t xml:space="preserve">1.22956502437592</t>
   </si>
   <si>
     <t xml:space="preserve">1.23468852043152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22663772106171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20687663555145</t>
+    <t xml:space="preserve">1.22663760185242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20687675476074</t>
   </si>
   <si>
     <t xml:space="preserve">1.20760869979858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18565213680267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17833340167999</t>
+    <t xml:space="preserve">1.18565225601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1783332824707</t>
   </si>
   <si>
     <t xml:space="preserve">1.18784773349762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16955065727234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17101442813873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17028260231018</t>
+    <t xml:space="preserve">1.16955077648163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17101430892944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17028248310089</t>
   </si>
   <si>
     <t xml:space="preserve">1.1893116235733</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">1.22151434421539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23981153964996</t>
+    <t xml:space="preserve">1.23981165885925</t>
   </si>
   <si>
     <t xml:space="preserve">1.23907971382141</t>
@@ -299,25 +299,25 @@
     <t xml:space="preserve">1.23834776878357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23542034626007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2061448097229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23102903366089</t>
+    <t xml:space="preserve">1.23542022705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20614504814148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2310289144516</t>
   </si>
   <si>
     <t xml:space="preserve">1.19736242294312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21712303161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22297811508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23322474956512</t>
+    <t xml:space="preserve">1.2171231508255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22297823429108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23322463035583</t>
   </si>
   <si>
     <t xml:space="preserve">1.23249280452728</t>
@@ -326,10 +326,10 @@
     <t xml:space="preserve">1.22883331775665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28518831729889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25884068012238</t>
+    <t xml:space="preserve">1.2851881980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25884056091309</t>
   </si>
   <si>
     <t xml:space="preserve">1.30714499950409</t>
@@ -344,10 +344,10 @@
     <t xml:space="preserve">1.31665933132172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32763767242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30348539352417</t>
+    <t xml:space="preserve">1.32763755321503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30348551273346</t>
   </si>
   <si>
     <t xml:space="preserve">1.31592738628387</t>
@@ -356,16 +356,16 @@
     <t xml:space="preserve">1.31812310218811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29763031005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30275356769562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29982602596283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28884792327881</t>
+    <t xml:space="preserve">1.29763054847717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30275344848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29982626438141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28884780406952</t>
   </si>
   <si>
     <t xml:space="preserve">1.29543483257294</t>
@@ -380,10 +380,10 @@
     <t xml:space="preserve">1.2932391166687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29250717163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30128991603851</t>
+    <t xml:space="preserve">1.29250729084015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3012900352478</t>
   </si>
   <si>
     <t xml:space="preserve">1.30568110942841</t>
@@ -392,7 +392,7 @@
     <t xml:space="preserve">1.26908695697784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26762318611145</t>
+    <t xml:space="preserve">1.26762306690216</t>
   </si>
   <si>
     <t xml:space="preserve">1.24786233901978</t>
@@ -401,37 +401,37 @@
     <t xml:space="preserve">1.25518119335175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26542770862579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28006505966187</t>
+    <t xml:space="preserve">1.2654275894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28006517887115</t>
   </si>
   <si>
     <t xml:space="preserve">1.25810861587524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25005805492401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24054348468781</t>
+    <t xml:space="preserve">1.25005793571472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24054336547852</t>
   </si>
   <si>
     <t xml:space="preserve">1.24639856815338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24420285224915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23615217208862</t>
+    <t xml:space="preserve">1.24420297145844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23615205287933</t>
   </si>
   <si>
     <t xml:space="preserve">1.23688399791718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24200713634491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23176085948944</t>
+    <t xml:space="preserve">1.2420072555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23176074028015</t>
   </si>
   <si>
     <t xml:space="preserve">1.20980441570282</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">1.19004344940186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18199276924133</t>
+    <t xml:space="preserve">1.18199265003204</t>
   </si>
   <si>
     <t xml:space="preserve">1.214195728302</t>
@@ -458,7 +458,7 @@
     <t xml:space="preserve">1.19297099113464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19663035869598</t>
+    <t xml:space="preserve">1.19663059711456</t>
   </si>
   <si>
     <t xml:space="preserve">1.22005069255829</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">1.21639144420624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25957238674164</t>
+    <t xml:space="preserve">1.25957250595093</t>
   </si>
   <si>
     <t xml:space="preserve">1.27786946296692</t>
@@ -479,7 +479,7 @@
     <t xml:space="preserve">1.2947028875351</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29689848423004</t>
+    <t xml:space="preserve">1.29689836502075</t>
   </si>
   <si>
     <t xml:space="preserve">1.31007242202759</t>
@@ -503,22 +503,22 @@
     <t xml:space="preserve">1.33861601352692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33934772014618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34666645526886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34227538108826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34007966518402</t>
+    <t xml:space="preserve">1.33934783935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34666669368744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34227550029755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34007978439331</t>
   </si>
   <si>
     <t xml:space="preserve">1.32690572738647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32105052471161</t>
+    <t xml:space="preserve">1.3210506439209</t>
   </si>
   <si>
     <t xml:space="preserve">1.3459347486496</t>
@@ -527,28 +527,28 @@
     <t xml:space="preserve">1.36130428314209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36057257652283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33276081085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34959423542023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3378838300705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34373915195465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34520292282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32910132408142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36349987983704</t>
+    <t xml:space="preserve">1.36057245731354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33276069164276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34959411621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33788418769836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34373903274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34520268440247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32910144329071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36349976062775</t>
   </si>
   <si>
     <t xml:space="preserve">1.36789131164551</t>
@@ -557,10 +557,10 @@
     <t xml:space="preserve">1.37667381763458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38252902030945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39789867401123</t>
+    <t xml:space="preserve">1.38252890110016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39789855480194</t>
   </si>
   <si>
     <t xml:space="preserve">1.41253614425659</t>
@@ -575,46 +575,46 @@
     <t xml:space="preserve">1.40887689590454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40302181243896</t>
+    <t xml:space="preserve">1.40302169322968</t>
   </si>
   <si>
     <t xml:space="preserve">1.39277541637421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36935520172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37886941432953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38911592960358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40155792236328</t>
+    <t xml:space="preserve">1.36935496330261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37886965274811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38911581039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40155780315399</t>
   </si>
   <si>
     <t xml:space="preserve">1.49304330348969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47621011734009</t>
+    <t xml:space="preserve">1.47621035575867</t>
   </si>
   <si>
     <t xml:space="preserve">1.48206520080566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49157953262329</t>
+    <t xml:space="preserve">1.49157977104187</t>
   </si>
   <si>
     <t xml:space="preserve">1.50328993797302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46742749214172</t>
+    <t xml:space="preserve">1.46742761135101</t>
   </si>
   <si>
     <t xml:space="preserve">1.45864486694336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47913753986359</t>
+    <t xml:space="preserve">1.4791374206543</t>
   </si>
   <si>
     <t xml:space="preserve">1.49523913860321</t>
@@ -623,82 +623,82 @@
     <t xml:space="preserve">1.49084782600403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48792004585266</t>
+    <t xml:space="preserve">1.48792028427124</t>
   </si>
   <si>
     <t xml:space="preserve">1.52744209766388</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50987660884857</t>
+    <t xml:space="preserve">1.50987684726715</t>
   </si>
   <si>
     <t xml:space="preserve">1.53256523609161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52963757514954</t>
+    <t xml:space="preserve">1.52963769435883</t>
   </si>
   <si>
     <t xml:space="preserve">1.53183329105377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52817380428314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51499998569489</t>
+    <t xml:space="preserve">1.52817368507385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5149998664856</t>
   </si>
   <si>
     <t xml:space="preserve">1.49963045120239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.498166680336</t>
+    <t xml:space="preserve">1.49816656112671</t>
   </si>
   <si>
     <t xml:space="preserve">1.485724568367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47108685970306</t>
+    <t xml:space="preserve">1.47108697891235</t>
   </si>
   <si>
     <t xml:space="preserve">1.48426103591919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46376824378967</t>
+    <t xml:space="preserve">1.4637678861618</t>
   </si>
   <si>
     <t xml:space="preserve">1.45498538017273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48499274253845</t>
+    <t xml:space="preserve">1.48499286174774</t>
   </si>
   <si>
     <t xml:space="preserve">1.52085506916046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53768849372864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58233344554901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63126361370087</t>
+    <t xml:space="preserve">1.53768837451935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58233332633972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63126373291016</t>
   </si>
   <si>
     <t xml:space="preserve">1.63427472114563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64857745170593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63578045368195</t>
+    <t xml:space="preserve">1.64857757091522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63578033447266</t>
   </si>
   <si>
     <t xml:space="preserve">1.66664409637451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66288030147552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66137456893921</t>
+    <t xml:space="preserve">1.66288042068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6613746881485</t>
   </si>
   <si>
     <t xml:space="preserve">1.76902174949646</t>
@@ -707,28 +707,28 @@
     <t xml:space="preserve">1.8081659078598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84429931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91656541824341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99485421180725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01367378234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95345139503479</t>
+    <t xml:space="preserve">1.84429919719696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9165655374527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99485409259796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01367354393005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95345151424408</t>
   </si>
   <si>
     <t xml:space="preserve">1.98205709457397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93011546134949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83376038074493</t>
+    <t xml:space="preserve">1.93011522293091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83376014232635</t>
   </si>
   <si>
     <t xml:space="preserve">1.9030157327652</t>
@@ -737,76 +737,76 @@
     <t xml:space="preserve">1.90452110767365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91204869747162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93538475036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92258775234222</t>
+    <t xml:space="preserve">1.91204881668091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93538510799408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92258787155151</t>
   </si>
   <si>
     <t xml:space="preserve">1.91581284999847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88118493556976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92860996723175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92183482646942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92559885978699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94065451622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92635142803192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90376842021942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91957676410675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91882395744324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93237364292145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94366526603699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91054320335388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89021813869476</t>
+    <t xml:space="preserve">1.88118505477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92860984802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92183494567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9255987405777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94065427780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9263516664505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90376818180084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91957664489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91882407665253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93237376213074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94366538524628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91054308414459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89021825790405</t>
   </si>
   <si>
     <t xml:space="preserve">1.90753221511841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89699339866638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89473509788513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87742125988007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86010730266571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77052712440491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79762697219849</t>
+    <t xml:space="preserve">1.89699351787567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89473485946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87742114067078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.860107421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77052700519562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79762709140778</t>
   </si>
   <si>
     <t xml:space="preserve">1.76826882362366</t>
@@ -815,127 +815,127 @@
     <t xml:space="preserve">1.79461586475372</t>
   </si>
   <si>
-    <t xml:space="preserve">1.807412981987</t>
+    <t xml:space="preserve">1.80741310119629</t>
   </si>
   <si>
     <t xml:space="preserve">1.83074903488159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84881544113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82547974586487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81042432785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82623267173767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8360184431076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83902966976166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85257971286774</t>
+    <t xml:space="preserve">1.84881579875946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82547962665558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81042420864105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82623243331909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83601856231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83902978897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85257959365845</t>
   </si>
   <si>
     <t xml:space="preserve">1.82171583175659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84806275367737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84655725955963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83752393722534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8977462053299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91280162334442</t>
+    <t xml:space="preserve">1.84806299209595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84655737876892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83752417564392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89774608612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91280150413513</t>
   </si>
   <si>
     <t xml:space="preserve">1.97377645969391</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97151827812195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93086850643158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9361377954483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9210821390152</t>
+    <t xml:space="preserve">1.97151803970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.930868268013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93613743782043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92108225822449</t>
   </si>
   <si>
     <t xml:space="preserve">1.88796019554138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88720726966858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89548766613007</t>
+    <t xml:space="preserve">1.88720715045929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89548790454865</t>
   </si>
   <si>
     <t xml:space="preserve">1.89322948455811</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86914038658142</t>
+    <t xml:space="preserve">1.86914050579071</t>
   </si>
   <si>
     <t xml:space="preserve">1.85860180854797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85634350776672</t>
+    <t xml:space="preserve">1.8563437461853</t>
   </si>
   <si>
     <t xml:space="preserve">1.85709631443024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85182702541351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86688208580017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88494908809662</t>
+    <t xml:space="preserve">1.85182678699493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86688220500946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88494896888733</t>
   </si>
   <si>
     <t xml:space="preserve">1.87215173244476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87064611911774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86161291599274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88193798065186</t>
+    <t xml:space="preserve">1.87064635753632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86161303520203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88193786144257</t>
   </si>
   <si>
     <t xml:space="preserve">1.86763501167297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87365734577179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86537706851959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84505176544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84204089641571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84731030464172</t>
+    <t xml:space="preserve">1.8736572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86537683010101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84505188465118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84204053878784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84731018543243</t>
   </si>
   <si>
     <t xml:space="preserve">1.84279358386993</t>
@@ -947,7 +947,7 @@
     <t xml:space="preserve">1.82397413253784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82849073410034</t>
+    <t xml:space="preserve">1.82849109172821</t>
   </si>
   <si>
     <t xml:space="preserve">1.81569361686707</t>
@@ -956,13 +956,13 @@
     <t xml:space="preserve">1.82021045684814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81117701530457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81644630432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81418800354004</t>
+    <t xml:space="preserve">1.81117689609528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.816446185112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81418788433075</t>
   </si>
   <si>
     <t xml:space="preserve">1.83526575565338</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">1.83225464820862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8224686384201</t>
+    <t xml:space="preserve">1.82246851921082</t>
   </si>
   <si>
     <t xml:space="preserve">1.85032117366791</t>
@@ -980,28 +980,28 @@
     <t xml:space="preserve">1.89849901199341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93689036369324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91731822490692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97979843616486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96474289894104</t>
+    <t xml:space="preserve">1.93689060211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91731834411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97979879379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96474313735962</t>
   </si>
   <si>
     <t xml:space="preserve">1.94667661190033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97076535224915</t>
+    <t xml:space="preserve">1.97076511383057</t>
   </si>
   <si>
     <t xml:space="preserve">1.9677540063858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96248507499695</t>
+    <t xml:space="preserve">1.96248471736908</t>
   </si>
   <si>
     <t xml:space="preserve">2.10325384140015</t>
@@ -1016,28 +1016,28 @@
     <t xml:space="preserve">1.98732626438141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99937057495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9858204126358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99033749103546</t>
+    <t xml:space="preserve">1.99937069416046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98582077026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99033737182617</t>
   </si>
   <si>
     <t xml:space="preserve">1.96624875068665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99861800670624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96549582481384</t>
+    <t xml:space="preserve">1.99861776828766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96549606323242</t>
   </si>
   <si>
     <t xml:space="preserve">1.97603487968445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98281002044678</t>
+    <t xml:space="preserve">1.98280966281891</t>
   </si>
   <si>
     <t xml:space="preserve">2.02496528625488</t>
@@ -1046,13 +1046,13 @@
     <t xml:space="preserve">2.06260371208191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07540082931519</t>
+    <t xml:space="preserve">2.07540106773376</t>
   </si>
   <si>
     <t xml:space="preserve">2.08142328262329</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08217597007751</t>
+    <t xml:space="preserve">2.08217620849609</t>
   </si>
   <si>
     <t xml:space="preserve">2.08593988418579</t>
@@ -1067,31 +1067,31 @@
     <t xml:space="preserve">2.09045672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11153411865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10024261474609</t>
+    <t xml:space="preserve">2.11153435707092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10024285316467</t>
   </si>
   <si>
     <t xml:space="preserve">2.08669257164001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07013154029846</t>
+    <t xml:space="preserve">2.07013177871704</t>
   </si>
   <si>
     <t xml:space="preserve">2.06034588813782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05959296226501</t>
+    <t xml:space="preserve">2.05959272384644</t>
   </si>
   <si>
     <t xml:space="preserve">2.05884003639221</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07615375518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08368134498596</t>
+    <t xml:space="preserve">2.07615399360657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08368182182312</t>
   </si>
   <si>
     <t xml:space="preserve">2.10400629043579</t>
@@ -1103,37 +1103,37 @@
     <t xml:space="preserve">2.13185930252075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19057559967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21315884590149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17552042007446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16799211502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20563101768494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22068691253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31101965904236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36371374130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31854701042175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33360314369202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37124180793762</t>
+    <t xml:space="preserve">2.19057583808899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21315908432007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17552018165588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16799259185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20563125610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22068667411804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31101989746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36371397972107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31854724884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33360266685486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37124156951904</t>
   </si>
   <si>
     <t xml:space="preserve">2.32607507705688</t>
@@ -1142,34 +1142,34 @@
     <t xml:space="preserve">2.28843641281128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26585292816162</t>
+    <t xml:space="preserve">2.2658531665802</t>
   </si>
   <si>
     <t xml:space="preserve">2.28090858459473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30349183082581</t>
+    <t xml:space="preserve">2.30349206924438</t>
   </si>
   <si>
     <t xml:space="preserve">2.29596424102783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25832557678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19810366630554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18304777145386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43899130821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38629722595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55190777778625</t>
+    <t xml:space="preserve">2.25832533836365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19810342788696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18304753303528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43899154663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38629746437073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55190753936768</t>
   </si>
   <si>
     <t xml:space="preserve">2.5443799495697</t>
@@ -1178,13 +1178,13 @@
     <t xml:space="preserve">2.61965751647949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46157455444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49168539047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46910238265991</t>
+    <t xml:space="preserve">2.46157503128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49168562889099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46910262107849</t>
   </si>
   <si>
     <t xml:space="preserve">2.40135264396667</t>
@@ -1193,7 +1193,7 @@
     <t xml:space="preserve">2.43146371841431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47663044929504</t>
+    <t xml:space="preserve">2.47663021087646</t>
   </si>
   <si>
     <t xml:space="preserve">2.44651937484741</t>
@@ -1205,7 +1205,7 @@
     <t xml:space="preserve">2.48415803909302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45404696464539</t>
+    <t xml:space="preserve">2.45404672622681</t>
   </si>
   <si>
     <t xml:space="preserve">2.4164080619812</t>
@@ -1214,52 +1214,55 @@
     <t xml:space="preserve">2.5067412853241</t>
   </si>
   <si>
+    <t xml:space="preserve">2.52932405471802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57587671279907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59139394760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58363509178162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56035923957825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50604844093323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51380729675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52156591415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.544842004776</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.5293242931366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57587647438049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59139370918274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58363509178162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56035900115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50604867935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51380729675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52156567573547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54484176635742</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.48277235031128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49829006195068</t>
+    <t xml:space="preserve">2.4982898235321</t>
   </si>
   <si>
     <t xml:space="preserve">2.42846155166626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32759928703308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30432367324829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28104710578918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31208157539368</t>
+    <t xml:space="preserve">2.3275990486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30432319641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28104734420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31208181381226</t>
   </si>
   <si>
     <t xml:space="preserve">2.22673654556274</t>
@@ -1268,28 +1271,28 @@
     <t xml:space="preserve">2.20346069335938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19570159912109</t>
+    <t xml:space="preserve">2.19570183753967</t>
   </si>
   <si>
     <t xml:space="preserve">2.21897792816162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23449516296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25777125358582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1724259853363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11811518669128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18794322013855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25001263618469</t>
+    <t xml:space="preserve">2.23449540138245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25777149200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17242574691772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11811542510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18794345855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25001215934753</t>
   </si>
   <si>
     <t xml:space="preserve">2.12587380409241</t>
@@ -1307,19 +1310,19 @@
     <t xml:space="preserve">2.08708071708679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07932186126709</t>
+    <t xml:space="preserve">2.07932209968567</t>
   </si>
   <si>
     <t xml:space="preserve">2.07156324386597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0405285358429</t>
+    <t xml:space="preserve">2.04052877426147</t>
   </si>
   <si>
     <t xml:space="preserve">2.14139127731323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1646671295166</t>
+    <t xml:space="preserve">2.16466760635376</t>
   </si>
   <si>
     <t xml:space="preserve">2.14914989471436</t>
@@ -1328,13 +1331,13 @@
     <t xml:space="preserve">2.18018460273743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29656434059143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03277015686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01725268363953</t>
+    <t xml:space="preserve">2.29656457901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03276991844177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01725244522095</t>
   </si>
   <si>
     <t xml:space="preserve">2.02501130104065</t>
@@ -1343,7 +1346,7 @@
     <t xml:space="preserve">2.0094940662384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97070074081421</t>
+    <t xml:space="preserve">1.97070062160492</t>
   </si>
   <si>
     <t xml:space="preserve">1.9629420042038</t>
@@ -1352,10 +1355,10 @@
     <t xml:space="preserve">1.93966603279114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88535523414612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87759685516357</t>
+    <t xml:space="preserve">1.8853554725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87759673595428</t>
   </si>
   <si>
     <t xml:space="preserve">1.85432064533234</t>
@@ -1364,16 +1367,16 @@
     <t xml:space="preserve">1.86983788013458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79225146770477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83880341053009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83104491233826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86207950115204</t>
+    <t xml:space="preserve">1.7922511100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83880352973938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83104467391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86207938194275</t>
   </si>
   <si>
     <t xml:space="preserve">2.15690875053406</t>
@@ -1388,7 +1391,7 @@
     <t xml:space="preserve">2.0017352104187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97845923900604</t>
+    <t xml:space="preserve">1.97845935821533</t>
   </si>
   <si>
     <t xml:space="preserve">1.99397683143616</t>
@@ -1397,31 +1400,31 @@
     <t xml:space="preserve">1.92414855957031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84656202793121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80776858329773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75345802307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77673411369324</t>
+    <t xml:space="preserve">1.84656190872192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80776870250702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75345826148987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77673399448395</t>
   </si>
   <si>
     <t xml:space="preserve">1.74569940567017</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82328605651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89311385154724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91639018058777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2112193107605</t>
+    <t xml:space="preserve">1.82328617572784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89311420917511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91639029979706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21121907234192</t>
   </si>
   <si>
     <t xml:space="preserve">2.11035680770874</t>
@@ -1430,10 +1433,10 @@
     <t xml:space="preserve">2.05604600906372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26553010940552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24225378036499</t>
+    <t xml:space="preserve">2.26552987098694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24225401878357</t>
   </si>
   <si>
     <t xml:space="preserve">2.35087513923645</t>
@@ -1445,10 +1448,10 @@
     <t xml:space="preserve">2.3353579044342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35863399505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40518593788147</t>
+    <t xml:space="preserve">2.35863375663757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40518569946289</t>
   </si>
   <si>
     <t xml:space="preserve">2.3819100856781</t>
@@ -1457,46 +1460,46 @@
     <t xml:space="preserve">2.38966846466064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39742732048035</t>
+    <t xml:space="preserve">2.39742708206177</t>
   </si>
   <si>
     <t xml:space="preserve">2.41294455528259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42070341110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3663923740387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34311652183533</t>
+    <t xml:space="preserve">2.42070317268372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36639261245728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34311676025391</t>
   </si>
   <si>
     <t xml:space="preserve">2.3741512298584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45173811912537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47501397132874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5526008605957</t>
+    <t xml:space="preserve">2.45173788070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47501373291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55260038375854</t>
   </si>
   <si>
     <t xml:space="preserve">2.54447102546692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52008366584778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49569535255432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4387903213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45504879951477</t>
+    <t xml:space="preserve">2.52008318901062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4956955909729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43879008293152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45504903793335</t>
   </si>
   <si>
     <t xml:space="preserve">2.47943687438965</t>
@@ -1511,16 +1514,16 @@
     <t xml:space="preserve">2.40627312660217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43066096305847</t>
+    <t xml:space="preserve">2.43066120147705</t>
   </si>
   <si>
     <t xml:space="preserve">2.42253160476685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36562657356262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39001441001892</t>
+    <t xml:space="preserve">2.3656268119812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3900146484375</t>
   </si>
   <si>
     <t xml:space="preserve">2.2843337059021</t>
@@ -1535,16 +1538,16 @@
     <t xml:space="preserve">2.23555779457092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25181651115417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26807498931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.357497215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32498025894165</t>
+    <t xml:space="preserve">2.2518162727356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26807522773743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35749697685242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32498002052307</t>
   </si>
   <si>
     <t xml:space="preserve">2.34123873710632</t>
@@ -1553,7 +1556,7 @@
     <t xml:space="preserve">2.37375593185425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46317791938782</t>
+    <t xml:space="preserve">2.4631781578064</t>
   </si>
   <si>
     <t xml:space="preserve">2.51195383071899</t>
@@ -1562,13 +1565,13 @@
     <t xml:space="preserve">2.52821254730225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53634214401245</t>
+    <t xml:space="preserve">2.53634190559387</t>
   </si>
   <si>
     <t xml:space="preserve">2.58511781692505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59324717521667</t>
+    <t xml:space="preserve">2.5932469367981</t>
   </si>
   <si>
     <t xml:space="preserve">2.56072974205017</t>
@@ -1583,7 +1586,7 @@
     <t xml:space="preserve">2.5688591003418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57698845863342</t>
+    <t xml:space="preserve">2.576988697052</t>
   </si>
   <si>
     <t xml:space="preserve">2.55260062217712</t>
@@ -1592,13 +1595,13 @@
     <t xml:space="preserve">2.4144024848938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33310961723328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34936785697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39814400672913</t>
+    <t xml:space="preserve">2.3331093788147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34936809539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39814376831055</t>
   </si>
   <si>
     <t xml:space="preserve">2.47130751609802</t>
@@ -1610,46 +1613,46 @@
     <t xml:space="preserve">2.38188529014587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29246282577515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30872130393982</t>
+    <t xml:space="preserve">2.29246306419373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3087215423584</t>
   </si>
   <si>
     <t xml:space="preserve">2.30059218406677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11361861228943</t>
+    <t xml:space="preserve">2.11361813545227</t>
   </si>
   <si>
     <t xml:space="preserve">2.18678212165833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1298770904541</t>
+    <t xml:space="preserve">2.12987685203552</t>
   </si>
   <si>
     <t xml:space="preserve">2.08110117912292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10548877716064</t>
+    <t xml:space="preserve">2.10548901557922</t>
   </si>
   <si>
     <t xml:space="preserve">2.1217474937439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04858374595642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89412689208984</t>
+    <t xml:space="preserve">2.048583984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89412713050842</t>
   </si>
   <si>
     <t xml:space="preserve">1.65837728977203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66650664806366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6258602142334</t>
+    <t xml:space="preserve">1.66650652885437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62586009502411</t>
   </si>
   <si>
     <t xml:space="preserve">1.47140347957611</t>
@@ -1661,10 +1664,10 @@
     <t xml:space="preserve">1.51205003261566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61366629600525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55676114559174</t>
+    <t xml:space="preserve">1.61366641521454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55676102638245</t>
   </si>
   <si>
     <t xml:space="preserve">1.54863178730011</t>
@@ -1682,49 +1685,49 @@
     <t xml:space="preserve">1.6014723777771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57301986217499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56082582473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58114910125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56895518302917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63398945331573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69089448451996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60553693771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62179565429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58927822113037</t>
+    <t xml:space="preserve">1.5730197429657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56082570552826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58114898204803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56895506381989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63398957252502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69089472293854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60553705692291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62179553508759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58927845954895</t>
   </si>
   <si>
     <t xml:space="preserve">1.61773085594177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.674635887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7071533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7640585899353</t>
+    <t xml:space="preserve">1.67463612556458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70715320110321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76405835151672</t>
   </si>
   <si>
     <t xml:space="preserve">1.7315411567688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71528255939484</t>
+    <t xml:space="preserve">1.71528267860413</t>
   </si>
   <si>
     <t xml:space="preserve">1.69902396202087</t>
@@ -1733,34 +1736,34 @@
     <t xml:space="preserve">1.6502480506897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74779975414276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7559289932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77218759059906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78844618797302</t>
+    <t xml:space="preserve">1.74779963493347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75592911243439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77218747138977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78844630718231</t>
   </si>
   <si>
     <t xml:space="preserve">1.82096338272095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87786853313446</t>
+    <t xml:space="preserve">1.87786829471588</t>
   </si>
   <si>
     <t xml:space="preserve">1.82909274101257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80470478534698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8128342628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79657554626465</t>
+    <t xml:space="preserve">1.80470490455627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81283402442932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79657578468323</t>
   </si>
   <si>
     <t xml:space="preserve">1.78031694889069</t>
@@ -1772,34 +1775,34 @@
     <t xml:space="preserve">1.73967039585114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68276536464691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60960149765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64211893081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57708442211151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52830851078033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53643786907196</t>
+    <t xml:space="preserve">1.68276524543762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60960161685944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64211881160736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57708418369293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52830862998962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53643774986267</t>
   </si>
   <si>
     <t xml:space="preserve">1.49985611438751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48766195774078</t>
+    <t xml:space="preserve">1.48766207695007</t>
   </si>
   <si>
     <t xml:space="preserve">1.48359739780426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43075692653656</t>
+    <t xml:space="preserve">1.43075704574585</t>
   </si>
   <si>
     <t xml:space="preserve">1.42262768745422</t>
@@ -1811,22 +1814,22 @@
     <t xml:space="preserve">1.40636897087097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43482160568237</t>
+    <t xml:space="preserve">1.43482172489166</t>
   </si>
   <si>
     <t xml:space="preserve">1.4144983291626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36572253704071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33320534229279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38198113441467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35759317874908</t>
+    <t xml:space="preserve">1.36572241783142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33320546150208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38198125362396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35759329795837</t>
   </si>
   <si>
     <t xml:space="preserve">1.30475270748138</t>
@@ -1838,46 +1841,46 @@
     <t xml:space="preserve">1.30881750583649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33727014064789</t>
+    <t xml:space="preserve">1.3372700214386</t>
   </si>
   <si>
     <t xml:space="preserve">1.32507598400116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34946393966675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37385177612305</t>
+    <t xml:space="preserve">1.34946405887604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37385189533234</t>
   </si>
   <si>
     <t xml:space="preserve">1.35352861881256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39823985099792</t>
+    <t xml:space="preserve">1.39823973178864</t>
   </si>
   <si>
     <t xml:space="preserve">1.40230441093445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3860456943512</t>
+    <t xml:space="preserve">1.38604581356049</t>
   </si>
   <si>
     <t xml:space="preserve">1.3901104927063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37791657447815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46733868122101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52017939090729</t>
+    <t xml:space="preserve">1.37791645526886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4673388004303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.520179271698</t>
   </si>
   <si>
     <t xml:space="preserve">1.55269658565521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54456722736359</t>
+    <t xml:space="preserve">1.5445671081543</t>
   </si>
   <si>
     <t xml:space="preserve">1.49172675609589</t>
@@ -1892,40 +1895,37 @@
     <t xml:space="preserve">1.51611471176147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54050266742706</t>
+    <t xml:space="preserve">1.54050254821777</t>
   </si>
   <si>
     <t xml:space="preserve">1.47953283786774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86973929405212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95103216171265</t>
+    <t xml:space="preserve">1.86973917484283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95103228092194</t>
   </si>
   <si>
     <t xml:space="preserve">2.0729718208313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25994563102722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24368691444397</t>
+    <t xml:space="preserve">2.2599458694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24368715286255</t>
   </si>
   <si>
     <t xml:space="preserve">2.1786527633667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14613556861877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05671286582947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13800597190857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21116971969604</t>
+    <t xml:space="preserve">2.1461353302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05671310424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13800621032715</t>
   </si>
   <si>
     <t xml:space="preserve">2.21116995811462</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">2.24429607391357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25257754325867</t>
+    <t xml:space="preserve">2.25257778167725</t>
   </si>
   <si>
     <t xml:space="preserve">2.20288825035095</t>
@@ -1952,7 +1952,7 @@
     <t xml:space="preserve">2.19460678100586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17804360389709</t>
+    <t xml:space="preserve">2.17804384231567</t>
   </si>
   <si>
     <t xml:space="preserve">2.34367442131042</t>
@@ -1964,7 +1964,7 @@
     <t xml:space="preserve">2.36851930618286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38508224487305</t>
+    <t xml:space="preserve">2.38508200645447</t>
   </si>
   <si>
     <t xml:space="preserve">2.40164518356323</t>
@@ -1973,22 +1973,22 @@
     <t xml:space="preserve">2.45133447647095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4761791229248</t>
+    <t xml:space="preserve">2.47617888450623</t>
   </si>
   <si>
     <t xml:space="preserve">2.4844605922699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49274230003357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.418208360672</t>
+    <t xml:space="preserve">2.49274206161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41820859909058</t>
   </si>
   <si>
     <t xml:space="preserve">2.39336347579956</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37680077552795</t>
+    <t xml:space="preserve">2.37680053710938</t>
   </si>
   <si>
     <t xml:space="preserve">2.44305300712585</t>
@@ -2003,22 +2003,22 @@
     <t xml:space="preserve">2.33539295196533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32711148262024</t>
+    <t xml:space="preserve">2.32711172103882</t>
   </si>
   <si>
     <t xml:space="preserve">2.30226683616638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31882977485657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31054830551147</t>
+    <t xml:space="preserve">2.31883001327515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31054854393005</t>
   </si>
   <si>
     <t xml:space="preserve">2.35195589065552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29398536682129</t>
+    <t xml:space="preserve">2.29398512840271</t>
   </si>
   <si>
     <t xml:space="preserve">2.28570365905762</t>
@@ -2027,22 +2027,22 @@
     <t xml:space="preserve">2.27742218971252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1531994342804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12835454940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13663601875305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18632531166077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08694672584534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10351014137268</t>
+    <t xml:space="preserve">2.15319919586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12835478782654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13663625717163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18632507324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08694696426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1035099029541</t>
   </si>
   <si>
     <t xml:space="preserve">2.07038378715515</t>
@@ -2060,22 +2060,22 @@
     <t xml:space="preserve">2.26914072036743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26085925102234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40992665290833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46789741516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50102353096008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52586841583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50930500030518</t>
+    <t xml:space="preserve">2.26085901260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4099268913269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46789765357971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50102376937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52586817741394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50930523872375</t>
   </si>
   <si>
     <t xml:space="preserve">2.62524676322937</t>
@@ -2084,34 +2084,34 @@
     <t xml:space="preserve">2.71634340286255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69978022575378</t>
+    <t xml:space="preserve">2.69978046417236</t>
   </si>
   <si>
     <t xml:space="preserve">2.81572198867798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84884834289551</t>
+    <t xml:space="preserve">2.84884810447693</t>
   </si>
   <si>
     <t xml:space="preserve">2.86541104316711</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01447892189026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03104162216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24636197090149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23808002471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22979879379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3043327331543</t>
+    <t xml:space="preserve">3.01447916030884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03104186058044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24636220932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23808026313782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22979855537415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30433297157288</t>
   </si>
   <si>
     <t xml:space="preserve">3.12213897705078</t>
@@ -2141,37 +2141,37 @@
     <t xml:space="preserve">3.10557579994202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13870215415955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08901286125183</t>
+    <t xml:space="preserve">3.13870191574097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08901262283325</t>
   </si>
   <si>
     <t xml:space="preserve">3.07244944572449</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11385703086853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08073115348816</t>
+    <t xml:space="preserve">3.11385726928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08073091506958</t>
   </si>
   <si>
     <t xml:space="preserve">3.06416797637939</t>
   </si>
   <si>
-    <t xml:space="preserve">3.254643201828</t>
+    <t xml:space="preserve">3.25464344024658</t>
   </si>
   <si>
     <t xml:space="preserve">3.09729433059692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93994522094727</t>
+    <t xml:space="preserve">2.93994498252869</t>
   </si>
   <si>
     <t xml:space="preserve">3.02276039123535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04760503768921</t>
+    <t xml:space="preserve">3.04760479927063</t>
   </si>
   <si>
     <t xml:space="preserve">3.05588674545288</t>
@@ -2195,7 +2195,7 @@
     <t xml:space="preserve">2.97307133674622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20495438575745</t>
+    <t xml:space="preserve">3.20495414733887</t>
   </si>
   <si>
     <t xml:space="preserve">3.27948784828186</t>
@@ -2231,13 +2231,13 @@
     <t xml:space="preserve">4.95042657852173</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01585054397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5828595161438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36477899551392</t>
+    <t xml:space="preserve">5.01585006713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58285999298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36477947235107</t>
   </si>
   <si>
     <t xml:space="preserve">5.05946683883667</t>
@@ -2246,7 +2246,7 @@
     <t xml:space="preserve">4.97223424911499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14669847488403</t>
+    <t xml:space="preserve">5.14669895172119</t>
   </si>
   <si>
     <t xml:space="preserve">5.08127450942993</t>
@@ -2255,7 +2255,7 @@
     <t xml:space="preserve">5.19031476974487</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21212291717529</t>
+    <t xml:space="preserve">5.21212244033813</t>
   </si>
   <si>
     <t xml:space="preserve">5.27754688262939</t>
@@ -2270,22 +2270,22 @@
     <t xml:space="preserve">5.47381925582886</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53924369812012</t>
+    <t xml:space="preserve">5.53924322128296</t>
   </si>
   <si>
     <t xml:space="preserve">5.45201110839844</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43020343780518</t>
+    <t xml:space="preserve">5.43020296096802</t>
   </si>
   <si>
     <t xml:space="preserve">5.40839529037476</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3429708480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38658714294434</t>
+    <t xml:space="preserve">5.34297132492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38658761978149</t>
   </si>
   <si>
     <t xml:space="preserve">5.32116317749023</t>
@@ -2297,19 +2297,19 @@
     <t xml:space="preserve">5.99721240997314</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82591819763184</t>
+    <t xml:space="preserve">6.82591772079468</t>
   </si>
   <si>
     <t xml:space="preserve">7.32750272750854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93495798110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78230237960815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73868560791016</t>
+    <t xml:space="preserve">6.93495845794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.782301902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73868608474731</t>
   </si>
   <si>
     <t xml:space="preserve">6.67326211929321</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">6.25890922546387</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32433319091797</t>
+    <t xml:space="preserve">6.32433271408081</t>
   </si>
   <si>
     <t xml:space="preserve">6.23710107803345</t>
@@ -2339,28 +2339,28 @@
     <t xml:space="preserve">6.41156530380249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62964534759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76049423217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02219104766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0658073425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04399871826172</t>
+    <t xml:space="preserve">6.62964582443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76049375534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0221905708313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06580686569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04399824142456</t>
   </si>
   <si>
     <t xml:space="preserve">7.0876145362854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45835208892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52377510070801</t>
+    <t xml:space="preserve">7.45835161209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52377557754517</t>
   </si>
   <si>
     <t xml:space="preserve">7.78547239303589</t>
@@ -2372,7 +2372,7 @@
     <t xml:space="preserve">8.19982433319092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11259365081787</t>
+    <t xml:space="preserve">8.11259269714355</t>
   </si>
   <si>
     <t xml:space="preserve">8.37428951263428</t>
@@ -18878,7 +18878,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G601" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -18904,7 +18904,7 @@
         <v>32</v>
       </c>
       <c r="G602" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -18930,7 +18930,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G603" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18956,7 +18956,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G604" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19008,7 +19008,7 @@
         <v>32</v>
       </c>
       <c r="G606" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19034,7 +19034,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G607" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19060,7 +19060,7 @@
         <v>30</v>
       </c>
       <c r="G608" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19086,7 +19086,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G609" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19112,7 +19112,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G610" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19138,7 +19138,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G611" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19164,7 +19164,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G612" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19190,7 +19190,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G613" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19216,7 +19216,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G614" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19242,7 +19242,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G615" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19268,7 +19268,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G616" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19294,7 +19294,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G617" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19320,7 +19320,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G618" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19346,7 +19346,7 @@
         <v>28</v>
       </c>
       <c r="G619" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19372,7 +19372,7 @@
         <v>28</v>
       </c>
       <c r="G620" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19398,7 +19398,7 @@
         <v>28</v>
       </c>
       <c r="G621" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19424,7 +19424,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G622" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19450,7 +19450,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G623" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19476,7 +19476,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G624" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19502,7 +19502,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G625" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19528,7 +19528,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G626" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19554,7 +19554,7 @@
         <v>29</v>
       </c>
       <c r="G627" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19580,7 +19580,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G628" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19606,7 +19606,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G629" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19632,7 +19632,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G630" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19658,7 +19658,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G631" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19684,7 +19684,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G632" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19710,7 +19710,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G633" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19736,7 +19736,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G634" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19762,7 +19762,7 @@
         <v>27.5</v>
       </c>
       <c r="G635" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19788,7 +19788,7 @@
         <v>27</v>
       </c>
       <c r="G636" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19814,7 +19814,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G637" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19840,7 +19840,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G638" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19866,7 +19866,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G639" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19892,7 +19892,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G640" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19918,7 +19918,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G641" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -19944,7 +19944,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G642" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19970,7 +19970,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G643" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19996,7 +19996,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G644" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20022,7 +20022,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G645" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20048,7 +20048,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G646" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20074,7 +20074,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G647" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20100,7 +20100,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G648" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20126,7 +20126,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G649" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20152,7 +20152,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G650" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20178,7 +20178,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G651" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20204,7 +20204,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G652" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20230,7 +20230,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G653" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20256,7 +20256,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G654" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20282,7 +20282,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G655" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20308,7 +20308,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G656" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20334,7 +20334,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G657" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20360,7 +20360,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G658" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20386,7 +20386,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G659" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20412,7 +20412,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G660" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20438,7 +20438,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G661" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20464,7 +20464,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G662" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20490,7 +20490,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G663" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -20516,7 +20516,7 @@
         <v>27.5</v>
       </c>
       <c r="G664" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20542,7 +20542,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G665" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20568,7 +20568,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G666" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20594,7 +20594,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G667" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20620,7 +20620,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G668" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20646,7 +20646,7 @@
         <v>27</v>
       </c>
       <c r="G669" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20672,7 +20672,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G670" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20698,7 +20698,7 @@
         <v>27</v>
       </c>
       <c r="G671" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20724,7 +20724,7 @@
         <v>26</v>
       </c>
       <c r="G672" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20750,7 +20750,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G673" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20776,7 +20776,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G674" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20802,7 +20802,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G675" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20828,7 +20828,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G676" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20854,7 +20854,7 @@
         <v>25</v>
       </c>
       <c r="G677" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20880,7 +20880,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G678" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20906,7 +20906,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G679" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -20932,7 +20932,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G680" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -20958,7 +20958,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G681" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -20984,7 +20984,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G682" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21010,7 +21010,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G683" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21036,7 +21036,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G684" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21062,7 +21062,7 @@
         <v>24</v>
       </c>
       <c r="G685" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21088,7 +21088,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G686" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21114,7 +21114,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G687" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21140,7 +21140,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G688" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21166,7 +21166,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G689" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21192,7 +21192,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G690" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21218,7 +21218,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G691" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21244,7 +21244,7 @@
         <v>27</v>
       </c>
       <c r="G692" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21270,7 +21270,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G693" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21296,7 +21296,7 @@
         <v>26</v>
       </c>
       <c r="G694" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21322,7 +21322,7 @@
         <v>26</v>
       </c>
       <c r="G695" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21348,7 +21348,7 @@
         <v>26</v>
       </c>
       <c r="G696" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21374,7 +21374,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G697" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21400,7 +21400,7 @@
         <v>26</v>
       </c>
       <c r="G698" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21426,7 +21426,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G699" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21452,7 +21452,7 @@
         <v>26</v>
       </c>
       <c r="G700" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21478,7 +21478,7 @@
         <v>25.5</v>
       </c>
       <c r="G701" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21504,7 +21504,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G702" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -21530,7 +21530,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G703" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21556,7 +21556,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G704" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21582,7 +21582,7 @@
         <v>26</v>
       </c>
       <c r="G705" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21608,7 +21608,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G706" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21634,7 +21634,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G707" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21660,7 +21660,7 @@
         <v>25.5</v>
       </c>
       <c r="G708" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21686,7 +21686,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G709" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21712,7 +21712,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G710" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21738,7 +21738,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G711" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21764,7 +21764,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G712" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21790,7 +21790,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G713" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21816,7 +21816,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G714" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21842,7 +21842,7 @@
         <v>24</v>
       </c>
       <c r="G715" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21868,7 +21868,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G716" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21894,7 +21894,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G717" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21920,7 +21920,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G718" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -21946,7 +21946,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G719" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -21972,7 +21972,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G720" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21998,7 +21998,7 @@
         <v>22.5</v>
       </c>
       <c r="G721" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22024,7 +22024,7 @@
         <v>23.5</v>
       </c>
       <c r="G722" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22050,7 +22050,7 @@
         <v>23.5</v>
       </c>
       <c r="G723" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22076,7 +22076,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G724" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22102,7 +22102,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G725" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22128,7 +22128,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G726" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22154,7 +22154,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G727" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22180,7 +22180,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G728" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22206,7 +22206,7 @@
         <v>25</v>
       </c>
       <c r="G729" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22232,7 +22232,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G730" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22258,7 +22258,7 @@
         <v>28</v>
       </c>
       <c r="G731" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22284,7 +22284,7 @@
         <v>28.5</v>
       </c>
       <c r="G732" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22310,7 +22310,7 @@
         <v>27.5</v>
       </c>
       <c r="G733" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22336,7 +22336,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G734" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22362,7 +22362,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G735" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22388,7 +22388,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G736" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22414,7 +22414,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G737" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22440,7 +22440,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G738" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22466,7 +22466,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G739" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -22492,7 +22492,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G740" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -22518,7 +22518,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G741" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22544,7 +22544,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G742" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22570,7 +22570,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G743" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22596,7 +22596,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G744" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22622,7 +22622,7 @@
         <v>27.5</v>
       </c>
       <c r="G745" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22648,7 +22648,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G746" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22674,7 +22674,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G747" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22700,7 +22700,7 @@
         <v>27.5</v>
       </c>
       <c r="G748" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22726,7 +22726,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G749" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22752,7 +22752,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G750" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22778,7 +22778,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G751" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22804,7 +22804,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G752" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22830,7 +22830,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G753" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22856,7 +22856,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G754" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22882,7 +22882,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G755" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22908,7 +22908,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G756" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -22934,7 +22934,7 @@
         <v>26.5</v>
       </c>
       <c r="G757" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -22960,7 +22960,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G758" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -22986,7 +22986,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G759" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23012,7 +23012,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G760" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23038,7 +23038,7 @@
         <v>27</v>
       </c>
       <c r="G761" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23064,7 +23064,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G762" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23090,7 +23090,7 @@
         <v>27</v>
       </c>
       <c r="G763" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23116,7 +23116,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G764" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23142,7 +23142,7 @@
         <v>26.5</v>
       </c>
       <c r="G765" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23168,7 +23168,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G766" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23194,7 +23194,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G767" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23220,7 +23220,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G768" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23246,7 +23246,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G769" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23272,7 +23272,7 @@
         <v>28.5</v>
       </c>
       <c r="G770" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23298,7 +23298,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G771" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23324,7 +23324,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G772" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23350,7 +23350,7 @@
         <v>28</v>
       </c>
       <c r="G773" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23376,7 +23376,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G774" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23402,7 +23402,7 @@
         <v>28</v>
       </c>
       <c r="G775" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23428,7 +23428,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G776" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23454,7 +23454,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G777" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23480,7 +23480,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G778" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -23506,7 +23506,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G779" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -23532,7 +23532,7 @@
         <v>28.5</v>
       </c>
       <c r="G780" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23558,7 +23558,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G781" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23584,7 +23584,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G782" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23610,7 +23610,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G783" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23636,7 +23636,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G784" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23662,7 +23662,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G785" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23688,7 +23688,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G786" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23714,7 +23714,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G787" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23740,7 +23740,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G788" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23766,7 +23766,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G789" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23792,7 +23792,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G790" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23818,7 +23818,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G791" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23844,7 +23844,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G792" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23870,7 +23870,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G793" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23896,7 +23896,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G794" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23922,7 +23922,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G795" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -23948,7 +23948,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G796" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -23974,7 +23974,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G797" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24000,7 +24000,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G798" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24026,7 +24026,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G799" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24052,7 +24052,7 @@
         <v>30</v>
       </c>
       <c r="G800" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24078,7 +24078,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G801" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24104,7 +24104,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G802" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24130,7 +24130,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G803" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24156,7 +24156,7 @@
         <v>31</v>
       </c>
       <c r="G804" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24182,7 +24182,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G805" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24208,7 +24208,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G806" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24234,7 +24234,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G807" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24260,7 +24260,7 @@
         <v>31</v>
       </c>
       <c r="G808" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24286,7 +24286,7 @@
         <v>31</v>
       </c>
       <c r="G809" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24312,7 +24312,7 @@
         <v>31</v>
       </c>
       <c r="G810" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24338,7 +24338,7 @@
         <v>31</v>
       </c>
       <c r="G811" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24364,7 +24364,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G812" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24390,7 +24390,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G813" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24416,7 +24416,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G814" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24442,7 +24442,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G815" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24468,7 +24468,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G816" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -24494,7 +24494,7 @@
         <v>31</v>
       </c>
       <c r="G817" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -24520,7 +24520,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G818" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24546,7 +24546,7 @@
         <v>31</v>
       </c>
       <c r="G819" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24572,7 +24572,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G820" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24598,7 +24598,7 @@
         <v>30.5</v>
       </c>
       <c r="G821" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24624,7 +24624,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G822" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24650,7 +24650,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G823" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24676,7 +24676,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G824" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24702,7 +24702,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G825" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24728,7 +24728,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G826" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24754,7 +24754,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G827" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24780,7 +24780,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G828" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24806,7 +24806,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G829" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24832,7 +24832,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G830" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24858,7 +24858,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G831" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24884,7 +24884,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G832" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24910,7 +24910,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G833" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -24936,7 +24936,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G834" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -24962,7 +24962,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G835" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -24988,7 +24988,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G836" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25014,7 +25014,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G837" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25040,7 +25040,7 @@
         <v>31</v>
       </c>
       <c r="G838" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25066,7 +25066,7 @@
         <v>31</v>
       </c>
       <c r="G839" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25092,7 +25092,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G840" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25118,7 +25118,7 @@
         <v>30</v>
       </c>
       <c r="G841" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25144,7 +25144,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G842" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25170,7 +25170,7 @@
         <v>30.5</v>
       </c>
       <c r="G843" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25196,7 +25196,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G844" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25222,7 +25222,7 @@
         <v>30.5</v>
       </c>
       <c r="G845" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25248,7 +25248,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G846" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25274,7 +25274,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G847" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25300,7 +25300,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G848" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25326,7 +25326,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G849" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25352,7 +25352,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G850" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25378,7 +25378,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G851" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25404,7 +25404,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G852" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -25430,7 +25430,7 @@
         <v>28</v>
       </c>
       <c r="G853" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -25456,7 +25456,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G854" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -25482,7 +25482,7 @@
         <v>28</v>
       </c>
       <c r="G855" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -25508,7 +25508,7 @@
         <v>27.5</v>
       </c>
       <c r="G856" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25534,7 +25534,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G857" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25560,7 +25560,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G858" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25586,7 +25586,7 @@
         <v>27.5</v>
       </c>
       <c r="G859" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25612,7 +25612,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G860" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25638,7 +25638,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G861" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25664,7 +25664,7 @@
         <v>28</v>
       </c>
       <c r="G862" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25690,7 +25690,7 @@
         <v>29</v>
       </c>
       <c r="G863" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25716,7 +25716,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G864" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25742,7 +25742,7 @@
         <v>29</v>
       </c>
       <c r="G865" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25768,7 +25768,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G866" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -25794,7 +25794,7 @@
         <v>29</v>
       </c>
       <c r="G867" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25820,7 +25820,7 @@
         <v>29</v>
       </c>
       <c r="G868" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -25846,7 +25846,7 @@
         <v>29</v>
       </c>
       <c r="G869" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -25872,7 +25872,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G870" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -25898,7 +25898,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G871" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25924,7 +25924,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G872" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -25950,7 +25950,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G873" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -25976,7 +25976,7 @@
         <v>30.5</v>
       </c>
       <c r="G874" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -26002,7 +26002,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G875" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -26028,7 +26028,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G876" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -26054,7 +26054,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G877" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -26080,7 +26080,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G878" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -26106,7 +26106,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G879" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26132,7 +26132,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G880" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -26158,7 +26158,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G881" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -26184,7 +26184,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G882" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -26210,7 +26210,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G883" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -26236,7 +26236,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G884" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -26262,7 +26262,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G885" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -26288,7 +26288,7 @@
         <v>31.5</v>
       </c>
       <c r="G886" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -26314,7 +26314,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G887" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -26340,7 +26340,7 @@
         <v>32</v>
       </c>
       <c r="G888" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -26366,7 +26366,7 @@
         <v>31.5</v>
       </c>
       <c r="G889" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -26392,7 +26392,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G890" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -26418,7 +26418,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G891" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -26444,7 +26444,7 @@
         <v>32</v>
       </c>
       <c r="G892" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -26470,7 +26470,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G893" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -26496,7 +26496,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G894" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -26522,7 +26522,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26548,7 +26548,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G896" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -26574,7 +26574,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G897" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -26600,7 +26600,7 @@
         <v>31</v>
       </c>
       <c r="G898" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -26626,7 +26626,7 @@
         <v>31</v>
       </c>
       <c r="G899" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -26652,7 +26652,7 @@
         <v>31</v>
       </c>
       <c r="G900" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -26678,7 +26678,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G901" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -26704,7 +26704,7 @@
         <v>31</v>
       </c>
       <c r="G902" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -26730,7 +26730,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G903" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -26756,7 +26756,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G904" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -26782,7 +26782,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G905" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -26808,7 +26808,7 @@
         <v>31</v>
       </c>
       <c r="G906" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -26834,7 +26834,7 @@
         <v>31</v>
       </c>
       <c r="G907" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -26860,7 +26860,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G908" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -26886,7 +26886,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G909" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -26912,7 +26912,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G910" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -26938,7 +26938,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G911" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -26964,7 +26964,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G912" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -26990,7 +26990,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G913" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -27016,7 +27016,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G914" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -27042,7 +27042,7 @@
         <v>30</v>
       </c>
       <c r="G915" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -27068,7 +27068,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G916" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -27094,7 +27094,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G917" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -27120,7 +27120,7 @@
         <v>29</v>
       </c>
       <c r="G918" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -27146,7 +27146,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G919" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -27172,7 +27172,7 @@
         <v>29</v>
       </c>
       <c r="G920" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -27198,7 +27198,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G921" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -27224,7 +27224,7 @@
         <v>29.5</v>
       </c>
       <c r="G922" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -27250,7 +27250,7 @@
         <v>29</v>
       </c>
       <c r="G923" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -27276,7 +27276,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G924" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -27302,7 +27302,7 @@
         <v>29</v>
       </c>
       <c r="G925" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -27328,7 +27328,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G926" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -27354,7 +27354,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G927" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -27380,7 +27380,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G928" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -27406,7 +27406,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G929" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -27432,7 +27432,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G930" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -27458,7 +27458,7 @@
         <v>30.5</v>
       </c>
       <c r="G931" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -27484,7 +27484,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G932" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -27510,7 +27510,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G933" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -27536,7 +27536,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G934" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -27562,7 +27562,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G935" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -27588,7 +27588,7 @@
         <v>30</v>
       </c>
       <c r="G936" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -27614,7 +27614,7 @@
         <v>29.5</v>
       </c>
       <c r="G937" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -27640,7 +27640,7 @@
         <v>29.5</v>
       </c>
       <c r="G938" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -27666,7 +27666,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G939" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -27692,7 +27692,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G940" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -27718,7 +27718,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G941" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -27744,7 +27744,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G942" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -27770,7 +27770,7 @@
         <v>30</v>
       </c>
       <c r="G943" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -27796,7 +27796,7 @@
         <v>30</v>
       </c>
       <c r="G944" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -27822,7 +27822,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G945" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -27848,7 +27848,7 @@
         <v>30</v>
       </c>
       <c r="G946" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -27874,7 +27874,7 @@
         <v>30.5</v>
       </c>
       <c r="G947" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -27900,7 +27900,7 @@
         <v>30.5</v>
       </c>
       <c r="G948" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -27926,7 +27926,7 @@
         <v>30</v>
       </c>
       <c r="G949" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -27952,7 +27952,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G950" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -27978,7 +27978,7 @@
         <v>30</v>
       </c>
       <c r="G951" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -28004,7 +28004,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G952" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -28030,7 +28030,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G953" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -28056,7 +28056,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G954" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -28082,7 +28082,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G955" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -28108,7 +28108,7 @@
         <v>30</v>
       </c>
       <c r="G956" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -28134,7 +28134,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G957" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -28160,7 +28160,7 @@
         <v>30</v>
       </c>
       <c r="G958" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -28186,7 +28186,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G959" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -28212,7 +28212,7 @@
         <v>30</v>
       </c>
       <c r="G960" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -28238,7 +28238,7 @@
         <v>30</v>
       </c>
       <c r="G961" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -28264,7 +28264,7 @@
         <v>30</v>
       </c>
       <c r="G962" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -28290,7 +28290,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G963" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -28316,7 +28316,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G964" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -28342,7 +28342,7 @@
         <v>30</v>
       </c>
       <c r="G965" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -28368,7 +28368,7 @@
         <v>30</v>
       </c>
       <c r="G966" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -28394,7 +28394,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G967" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -28420,7 +28420,7 @@
         <v>30</v>
       </c>
       <c r="G968" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -28446,7 +28446,7 @@
         <v>30</v>
       </c>
       <c r="G969" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -28472,7 +28472,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G970" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -28498,7 +28498,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G971" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -28524,7 +28524,7 @@
         <v>30</v>
       </c>
       <c r="G972" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -28550,7 +28550,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G973" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -28576,7 +28576,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G974" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -28602,7 +28602,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G975" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -28628,7 +28628,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G976" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -28654,7 +28654,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G977" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -28680,7 +28680,7 @@
         <v>31</v>
       </c>
       <c r="G978" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28706,7 +28706,7 @@
         <v>31</v>
       </c>
       <c r="G979" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -28732,7 +28732,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G980" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28758,7 +28758,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G981" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -28784,7 +28784,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G982" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -28810,7 +28810,7 @@
         <v>31</v>
       </c>
       <c r="G983" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -28836,7 +28836,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G984" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -28862,7 +28862,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G985" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28888,7 +28888,7 @@
         <v>31</v>
       </c>
       <c r="G986" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -28914,7 +28914,7 @@
         <v>31.5</v>
       </c>
       <c r="G987" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -28940,7 +28940,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G988" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -28966,7 +28966,7 @@
         <v>31.5</v>
       </c>
       <c r="G989" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -28992,7 +28992,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G990" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -29018,7 +29018,7 @@
         <v>31.5</v>
       </c>
       <c r="G991" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -29044,7 +29044,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G992" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -29070,7 +29070,7 @@
         <v>31.5</v>
       </c>
       <c r="G993" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -29096,7 +29096,7 @@
         <v>31.5</v>
       </c>
       <c r="G994" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -29122,7 +29122,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G995" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -29148,7 +29148,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G996" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -29174,7 +29174,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G997" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -29200,7 +29200,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G998" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -29226,7 +29226,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G999" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -29252,7 +29252,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1000" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -29278,7 +29278,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1001" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -29304,7 +29304,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1002" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -29330,7 +29330,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1003" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -29356,7 +29356,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1004" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -29382,7 +29382,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1005" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -29408,7 +29408,7 @@
         <v>31</v>
       </c>
       <c r="G1006" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -29434,7 +29434,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1007" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -29460,7 +29460,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1008" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -29486,7 +29486,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1009" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -29512,7 +29512,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1010" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -29538,7 +29538,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1011" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -29564,7 +29564,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1012" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -29590,7 +29590,7 @@
         <v>30.5</v>
       </c>
       <c r="G1013" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -29616,7 +29616,7 @@
         <v>30.5</v>
       </c>
       <c r="G1014" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -29642,7 +29642,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1015" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -29668,7 +29668,7 @@
         <v>30.5</v>
       </c>
       <c r="G1016" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -29694,7 +29694,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1017" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -29720,7 +29720,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1018" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -29746,7 +29746,7 @@
         <v>30</v>
       </c>
       <c r="G1019" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -29772,7 +29772,7 @@
         <v>30.5</v>
       </c>
       <c r="G1020" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -29798,7 +29798,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1021" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -29824,7 +29824,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1022" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -29850,7 +29850,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1023" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -29876,7 +29876,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1024" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -29902,7 +29902,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1025" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -29928,7 +29928,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1026" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -29954,7 +29954,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1027" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -29980,7 +29980,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1028" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -30006,7 +30006,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1029" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -30032,7 +30032,7 @@
         <v>30</v>
       </c>
       <c r="G1030" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -30058,7 +30058,7 @@
         <v>30</v>
       </c>
       <c r="G1031" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -30084,7 +30084,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1032" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -30110,7 +30110,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1033" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -30136,7 +30136,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1034" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -30162,7 +30162,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1035" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -30188,7 +30188,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1036" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -30214,7 +30214,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1037" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -30240,7 +30240,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1038" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -30266,7 +30266,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1039" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -30292,7 +30292,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1040" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -30318,7 +30318,7 @@
         <v>28</v>
       </c>
       <c r="G1041" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -30344,7 +30344,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1042" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -30370,7 +30370,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1043" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -30396,7 +30396,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1044" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -30422,7 +30422,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1045" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -30448,7 +30448,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1046" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -30474,7 +30474,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1047" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -30500,7 +30500,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1048" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -30526,7 +30526,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1049" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -30552,7 +30552,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1050" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -30578,7 +30578,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1051" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -30604,7 +30604,7 @@
         <v>28</v>
       </c>
       <c r="G1052" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -30630,7 +30630,7 @@
         <v>26</v>
       </c>
       <c r="G1053" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -30656,7 +30656,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1054" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -30682,7 +30682,7 @@
         <v>27.5</v>
       </c>
       <c r="G1055" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -30708,7 +30708,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1056" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -30734,7 +30734,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1057" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -30760,7 +30760,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1058" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -30786,7 +30786,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1059" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -30812,7 +30812,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1060" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -30838,7 +30838,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1061" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -30864,7 +30864,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1062" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -30890,7 +30890,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1063" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -30916,7 +30916,7 @@
         <v>20.5</v>
       </c>
       <c r="G1064" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -30942,7 +30942,7 @@
         <v>20</v>
       </c>
       <c r="G1065" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -30968,7 +30968,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1066" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -30994,7 +30994,7 @@
         <v>18.5</v>
       </c>
       <c r="G1067" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -31020,7 +31020,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1068" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -31046,7 +31046,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1069" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -31072,7 +31072,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G1070" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -31098,7 +31098,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G1071" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -31124,7 +31124,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1072" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -31150,7 +31150,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1073" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -31176,7 +31176,7 @@
         <v>19.5</v>
       </c>
       <c r="G1074" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -31202,7 +31202,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1075" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -31228,7 +31228,7 @@
         <v>20.5</v>
       </c>
       <c r="G1076" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -31254,7 +31254,7 @@
         <v>19.5</v>
       </c>
       <c r="G1077" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -31280,7 +31280,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G1078" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -31306,7 +31306,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1079" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -31332,7 +31332,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1080" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -31358,7 +31358,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1081" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -31384,7 +31384,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1082" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -31410,7 +31410,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1083" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -31436,7 +31436,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1084" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -31462,7 +31462,7 @@
         <v>19.5</v>
       </c>
       <c r="G1085" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -31488,7 +31488,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1086" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -31514,7 +31514,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1087" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -31540,7 +31540,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1088" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -31566,7 +31566,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1089" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -31592,7 +31592,7 @@
         <v>19.75</v>
       </c>
       <c r="G1090" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -31618,7 +31618,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G1091" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -31644,7 +31644,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1092" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -31670,7 +31670,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1093" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -31696,7 +31696,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1094" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -31722,7 +31722,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1095" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -31748,7 +31748,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1096" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -31774,7 +31774,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1097" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -31800,7 +31800,7 @@
         <v>21</v>
       </c>
       <c r="G1098" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -31826,7 +31826,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1099" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -31852,7 +31852,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1100" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -31878,7 +31878,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1101" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -31904,7 +31904,7 @@
         <v>21</v>
       </c>
       <c r="G1102" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -31930,7 +31930,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1103" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -31956,7 +31956,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1104" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -31982,7 +31982,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1105" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -32008,7 +32008,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1106" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -32034,7 +32034,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1107" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -32060,7 +32060,7 @@
         <v>20.5</v>
       </c>
       <c r="G1108" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -32086,7 +32086,7 @@
         <v>20.5</v>
       </c>
       <c r="G1109" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -32112,7 +32112,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1110" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -32138,7 +32138,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1111" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -32164,7 +32164,7 @@
         <v>20.5</v>
       </c>
       <c r="G1112" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -32190,7 +32190,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1113" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -32216,7 +32216,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1114" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -32242,7 +32242,7 @@
         <v>20.5</v>
       </c>
       <c r="G1115" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -32268,7 +32268,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1116" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -32294,7 +32294,7 @@
         <v>21</v>
       </c>
       <c r="G1117" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -32320,7 +32320,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1118" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -32346,7 +32346,7 @@
         <v>21</v>
       </c>
       <c r="G1119" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -32372,7 +32372,7 @@
         <v>21.5</v>
       </c>
       <c r="G1120" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -32398,7 +32398,7 @@
         <v>21.5</v>
       </c>
       <c r="G1121" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -32424,7 +32424,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1122" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -32450,7 +32450,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1123" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -32476,7 +32476,7 @@
         <v>22</v>
       </c>
       <c r="G1124" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -32502,7 +32502,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1125" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -32528,7 +32528,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1126" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -32554,7 +32554,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1127" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -32580,7 +32580,7 @@
         <v>21.5</v>
       </c>
       <c r="G1128" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -32606,7 +32606,7 @@
         <v>22</v>
       </c>
       <c r="G1129" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -32632,7 +32632,7 @@
         <v>22</v>
       </c>
       <c r="G1130" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -32658,7 +32658,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1131" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -32684,7 +32684,7 @@
         <v>22.5</v>
       </c>
       <c r="G1132" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -32710,7 +32710,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1133" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -32736,7 +32736,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1134" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -32762,7 +32762,7 @@
         <v>22</v>
       </c>
       <c r="G1135" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -32788,7 +32788,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1136" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -32814,7 +32814,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1137" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -32840,7 +32840,7 @@
         <v>22</v>
       </c>
       <c r="G1138" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -32866,7 +32866,7 @@
         <v>22</v>
       </c>
       <c r="G1139" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -32892,7 +32892,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1140" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -32918,7 +32918,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1141" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -32944,7 +32944,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1142" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -32970,7 +32970,7 @@
         <v>22</v>
       </c>
       <c r="G1143" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -32996,7 +32996,7 @@
         <v>22</v>
       </c>
       <c r="G1144" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -33022,7 +33022,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1145" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -33048,7 +33048,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1146" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -33074,7 +33074,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1147" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -33100,7 +33100,7 @@
         <v>21.5</v>
       </c>
       <c r="G1148" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -33126,7 +33126,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1149" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -33152,7 +33152,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1150" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -33178,7 +33178,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1151" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -33204,7 +33204,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1152" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -33230,7 +33230,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1153" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -33256,7 +33256,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1154" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -33282,7 +33282,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1155" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -33308,7 +33308,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1156" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -33334,7 +33334,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1157" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -33360,7 +33360,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1158" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -33386,7 +33386,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1159" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -33412,7 +33412,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1160" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -33438,7 +33438,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1161" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -33464,7 +33464,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1162" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -33490,7 +33490,7 @@
         <v>20.5</v>
       </c>
       <c r="G1163" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -33516,7 +33516,7 @@
         <v>20.5</v>
       </c>
       <c r="G1164" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -33542,7 +33542,7 @@
         <v>21</v>
       </c>
       <c r="G1165" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -33568,7 +33568,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1166" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -33594,7 +33594,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1167" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -33620,7 +33620,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1168" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -33646,7 +33646,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1169" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -33672,7 +33672,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1170" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -33698,7 +33698,7 @@
         <v>21.5</v>
       </c>
       <c r="G1171" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -33724,7 +33724,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1172" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -33750,7 +33750,7 @@
         <v>21.5</v>
       </c>
       <c r="G1173" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -33776,7 +33776,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1174" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -33802,7 +33802,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1175" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -33828,7 +33828,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1176" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -33854,7 +33854,7 @@
         <v>21.5</v>
       </c>
       <c r="G1177" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -33880,7 +33880,7 @@
         <v>21.5</v>
       </c>
       <c r="G1178" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33906,7 +33906,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1179" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -33932,7 +33932,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1180" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -33958,7 +33958,7 @@
         <v>21.5</v>
       </c>
       <c r="G1181" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -33984,7 +33984,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1182" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -34010,7 +34010,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1183" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -34036,7 +34036,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1184" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -34062,7 +34062,7 @@
         <v>21</v>
       </c>
       <c r="G1185" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -34088,7 +34088,7 @@
         <v>21</v>
       </c>
       <c r="G1186" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -34114,7 +34114,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1187" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -34140,7 +34140,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1188" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -34166,7 +34166,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1189" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -34192,7 +34192,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1190" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -34218,7 +34218,7 @@
         <v>20</v>
       </c>
       <c r="G1191" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -34244,7 +34244,7 @@
         <v>20</v>
       </c>
       <c r="G1192" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -34270,7 +34270,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1193" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -34296,7 +34296,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1194" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -34322,7 +34322,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1195" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -34348,7 +34348,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1196" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -34374,7 +34374,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1197" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -34400,7 +34400,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1198" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -34426,7 +34426,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1199" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -34452,7 +34452,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1200" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -34478,7 +34478,7 @@
         <v>19.75</v>
       </c>
       <c r="G1201" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -34504,7 +34504,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1202" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -34530,7 +34530,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1203" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -34556,7 +34556,7 @@
         <v>19.75</v>
       </c>
       <c r="G1204" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -34582,7 +34582,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1205" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -34608,7 +34608,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1206" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -34634,7 +34634,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1207" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -34660,7 +34660,7 @@
         <v>18.5</v>
       </c>
       <c r="G1208" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -34686,7 +34686,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1209" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -34712,7 +34712,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1210" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -34738,7 +34738,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1211" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -34764,7 +34764,7 @@
         <v>18.5</v>
       </c>
       <c r="G1212" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -34790,7 +34790,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1213" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -34816,7 +34816,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1214" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -34842,7 +34842,7 @@
         <v>18.25</v>
       </c>
       <c r="G1215" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -34868,7 +34868,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1216" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -34894,7 +34894,7 @@
         <v>17.5</v>
       </c>
       <c r="G1217" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -34920,7 +34920,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1218" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -34946,7 +34946,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1219" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -34972,7 +34972,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1220" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -34998,7 +34998,7 @@
         <v>17.5</v>
       </c>
       <c r="G1221" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -35024,7 +35024,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1222" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -35050,7 +35050,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1223" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -35076,7 +35076,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1224" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -35102,7 +35102,7 @@
         <v>17</v>
       </c>
       <c r="G1225" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -35128,7 +35128,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1226" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -35154,7 +35154,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1227" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -35180,7 +35180,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1228" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -35206,7 +35206,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1229" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -35232,7 +35232,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1230" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -35258,7 +35258,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1231" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -35284,7 +35284,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1232" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -35310,7 +35310,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1233" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -35336,7 +35336,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1234" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -35362,7 +35362,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1235" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -35388,7 +35388,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1236" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -35414,7 +35414,7 @@
         <v>17.25</v>
       </c>
       <c r="G1237" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -35440,7 +35440,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1238" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -35466,7 +35466,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1239" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -35492,7 +35492,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1240" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -35518,7 +35518,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1241" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -35544,7 +35544,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1242" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -35570,7 +35570,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1243" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -35596,7 +35596,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1244" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -35622,7 +35622,7 @@
         <v>17.5</v>
       </c>
       <c r="G1245" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -35648,7 +35648,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1246" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -35674,7 +35674,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1247" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -35700,7 +35700,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1248" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -35726,7 +35726,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1249" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -35752,7 +35752,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1250" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -35778,7 +35778,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1251" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -35804,7 +35804,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1252" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -35830,7 +35830,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1253" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -35856,7 +35856,7 @@
         <v>19</v>
       </c>
       <c r="G1254" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -35882,7 +35882,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1255" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -35908,7 +35908,7 @@
         <v>18.5</v>
       </c>
       <c r="G1256" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -35934,7 +35934,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1257" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -35960,7 +35960,7 @@
         <v>18.25</v>
       </c>
       <c r="G1258" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -35986,7 +35986,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1259" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -36012,7 +36012,7 @@
         <v>18.5</v>
       </c>
       <c r="G1260" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -36038,7 +36038,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1261" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -36064,7 +36064,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1262" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -36090,7 +36090,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1263" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -36116,7 +36116,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1264" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -36142,7 +36142,7 @@
         <v>18.75</v>
       </c>
       <c r="G1265" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -36168,7 +36168,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1266" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -36194,7 +36194,7 @@
         <v>18.5</v>
       </c>
       <c r="G1267" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -36220,7 +36220,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G1268" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -36246,7 +36246,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G1269" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -36272,7 +36272,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1270" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -36298,7 +36298,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1271" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -36324,7 +36324,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1272" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -36350,7 +36350,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1273" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -36376,7 +36376,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1274" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -36402,7 +36402,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1275" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -36428,7 +36428,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1276" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -36454,7 +36454,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1277" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -36480,7 +36480,7 @@
         <v>19</v>
       </c>
       <c r="G1278" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -36506,7 +36506,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1279" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -36532,7 +36532,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G1280" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -36558,7 +36558,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1281" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -36584,7 +36584,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1282" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -36610,7 +36610,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1283" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -36636,7 +36636,7 @@
         <v>18.5</v>
       </c>
       <c r="G1284" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -36662,7 +36662,7 @@
         <v>18.5</v>
       </c>
       <c r="G1285" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -36688,7 +36688,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1286" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -36714,7 +36714,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1287" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -36740,7 +36740,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1288" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -36766,7 +36766,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1289" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -36792,7 +36792,7 @@
         <v>18.25</v>
       </c>
       <c r="G1290" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -36818,7 +36818,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1291" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -36844,7 +36844,7 @@
         <v>19</v>
       </c>
       <c r="G1292" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -36870,7 +36870,7 @@
         <v>23</v>
       </c>
       <c r="G1293" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -36896,7 +36896,7 @@
         <v>24</v>
       </c>
       <c r="G1294" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -36922,7 +36922,7 @@
         <v>25.5</v>
       </c>
       <c r="G1295" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -36948,7 +36948,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1296" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -36974,7 +36974,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1297" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -37000,7 +37000,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1298" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -37026,7 +37026,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1299" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -37052,7 +37052,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1300" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -37078,7 +37078,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1301" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -37104,7 +37104,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1302" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -37130,7 +37130,7 @@
         <v>29</v>
       </c>
       <c r="G1303" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -37156,7 +37156,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1304" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -37182,7 +37182,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1305" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -37208,7 +37208,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1306" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -37234,7 +37234,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1307" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -37260,7 +37260,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1308" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -37286,7 +37286,7 @@
         <v>28</v>
       </c>
       <c r="G1309" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -37312,7 +37312,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1310" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -37338,7 +37338,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1311" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -37364,7 +37364,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1312" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -37390,7 +37390,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1313" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -37416,7 +37416,7 @@
         <v>28</v>
       </c>
       <c r="G1314" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -37442,7 +37442,7 @@
         <v>28</v>
       </c>
       <c r="G1315" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -37468,7 +37468,7 @@
         <v>28</v>
       </c>
       <c r="G1316" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -37494,7 +37494,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1317" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -37520,7 +37520,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1318" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -37546,7 +37546,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1319" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -37572,7 +37572,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1320" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -37598,7 +37598,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1321" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -37624,7 +37624,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1322" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -37650,7 +37650,7 @@
         <v>26</v>
       </c>
       <c r="G1323" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -37676,7 +37676,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1324" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -37702,7 +37702,7 @@
         <v>25.5</v>
       </c>
       <c r="G1325" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -37728,7 +37728,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1326" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -37754,7 +37754,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1327" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -37780,7 +37780,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1328" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -37806,7 +37806,7 @@
         <v>26</v>
       </c>
       <c r="G1329" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -37832,7 +37832,7 @@
         <v>27.5</v>
       </c>
       <c r="G1330" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -37858,7 +37858,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1331" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -37884,7 +37884,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1332" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -37910,7 +37910,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1333" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -37936,7 +37936,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1334" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -37962,7 +37962,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1335" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -37988,7 +37988,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1336" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -38014,7 +38014,7 @@
         <v>27.5</v>
       </c>
       <c r="G1337" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -38040,7 +38040,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1338" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -68156,7 +68156,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.5368518519</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>300</v>
@@ -68177,6 +68177,32 @@
         <v>920</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6245138889</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>964</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -44,22 +44,22 @@
     <t xml:space="preserve">AUTME.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24544656276703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24330163002014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22256815433502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2154186964035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2218531370163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2147034406662</t>
+    <t xml:space="preserve">1.24544644355774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24330174922943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22256803512573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21541857719421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22185289859772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21470367908478</t>
   </si>
   <si>
     <t xml:space="preserve">1.23615217208862</t>
@@ -68,13 +68,13 @@
     <t xml:space="preserve">1.21327352523804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20683896541595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20111954212189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20040452480316</t>
+    <t xml:space="preserve">1.20683908462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20111918449402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20040464401245</t>
   </si>
   <si>
     <t xml:space="preserve">1.1668016910553</t>
@@ -83,37 +83,37 @@
     <t xml:space="preserve">1.19468486309052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25688564777374</t>
+    <t xml:space="preserve">1.25688576698303</t>
   </si>
   <si>
     <t xml:space="preserve">1.25045120716095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2468763589859</t>
+    <t xml:space="preserve">1.24687623977661</t>
   </si>
   <si>
     <t xml:space="preserve">1.25116622447968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26475012302399</t>
+    <t xml:space="preserve">1.26475036144257</t>
   </si>
   <si>
     <t xml:space="preserve">1.2354371547699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22542774677277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21041393280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22113811969757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19397008419037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2268580198288</t>
+    <t xml:space="preserve">1.22542786598206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.210413813591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22113800048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19396984577179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22685778141022</t>
   </si>
   <si>
     <t xml:space="preserve">1.20469439029694</t>
@@ -122,28 +122,28 @@
     <t xml:space="preserve">1.25831568241119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26546537876129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25903069972992</t>
+    <t xml:space="preserve">1.265465259552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25903046131134</t>
   </si>
   <si>
     <t xml:space="preserve">1.26903998851776</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21684849262238</t>
+    <t xml:space="preserve">1.21684837341309</t>
   </si>
   <si>
     <t xml:space="preserve">1.22828769683838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27404451370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26689493656158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27261471748352</t>
+    <t xml:space="preserve">1.27404463291168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26689505577087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27261447906494</t>
   </si>
   <si>
     <t xml:space="preserve">1.27189981937408</t>
@@ -152,40 +152,40 @@
     <t xml:space="preserve">1.27904915809631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26760995388031</t>
+    <t xml:space="preserve">1.2676100730896</t>
   </si>
   <si>
     <t xml:space="preserve">1.25545585155487</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26260542869568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24830627441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24902129173279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24258661270142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23686707019806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23472225666046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23400723934174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25225365161896</t>
+    <t xml:space="preserve">1.26260530948639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24830615520477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2490211725235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24258649349213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23686695098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23472237586975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23400735855103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25225377082825</t>
   </si>
   <si>
     <t xml:space="preserve">1.26176810264587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26835501194</t>
+    <t xml:space="preserve">1.26835513114929</t>
   </si>
   <si>
     <t xml:space="preserve">1.27860140800476</t>
@@ -194,61 +194,61 @@
     <t xml:space="preserve">1.27640581130981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27421021461487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27494215965271</t>
+    <t xml:space="preserve">1.27421009540558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27494180202484</t>
   </si>
   <si>
     <t xml:space="preserve">1.26323187351227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27128255367279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26689124107361</t>
+    <t xml:space="preserve">1.27128279209137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26689112186432</t>
   </si>
   <si>
     <t xml:space="preserve">1.28445649147034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.280797123909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27933323383331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27347815036774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27274644374847</t>
+    <t xml:space="preserve">1.28079700469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27933311462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27347826957703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27274632453918</t>
   </si>
   <si>
     <t xml:space="preserve">1.26615929603577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28226101398468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28811597824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28738391399384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28299283981323</t>
+    <t xml:space="preserve">1.2822607755661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28811585903168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28738403320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28299307823181</t>
   </si>
   <si>
     <t xml:space="preserve">1.26396381855011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24127531051636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24347102642059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22956502437592</t>
+    <t xml:space="preserve">1.24127542972565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2434709072113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22956514358521</t>
   </si>
   <si>
     <t xml:space="preserve">1.23468852043152</t>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">1.22663760185242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20687675476074</t>
+    <t xml:space="preserve">1.20687687397003</t>
   </si>
   <si>
     <t xml:space="preserve">1.20760869979858</t>
@@ -272,52 +272,52 @@
     <t xml:space="preserve">1.18784773349762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16955077648163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17101430892944</t>
+    <t xml:space="preserve">1.16955065727234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17101442813873</t>
   </si>
   <si>
     <t xml:space="preserve">1.17028248310089</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1893116235733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22224640846252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22151434421539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23981165885925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23907971382141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23834776878357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23542022705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20614504814148</t>
+    <t xml:space="preserve">1.18931150436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22224652767181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22151470184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23981153964996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2390798330307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23834764957428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23542010784149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2061448097229</t>
   </si>
   <si>
     <t xml:space="preserve">1.2310289144516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19736242294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2171231508255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22297823429108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23322463035583</t>
+    <t xml:space="preserve">1.19736218452454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21712303161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22297835350037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23322474956512</t>
   </si>
   <si>
     <t xml:space="preserve">1.23249280452728</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">1.25884056091309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30714499950409</t>
+    <t xml:space="preserve">1.3071448802948</t>
   </si>
   <si>
     <t xml:space="preserve">1.29909420013428</t>
@@ -344,25 +344,25 @@
     <t xml:space="preserve">1.31665933132172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32763755321503</t>
+    <t xml:space="preserve">1.32763743400574</t>
   </si>
   <si>
     <t xml:space="preserve">1.30348551273346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31592738628387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31812310218811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29763054847717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30275344848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29982626438141</t>
+    <t xml:space="preserve">1.31592750549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3181232213974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29763042926788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30275356769562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29982602596283</t>
   </si>
   <si>
     <t xml:space="preserve">1.28884780406952</t>
@@ -371,31 +371,31 @@
     <t xml:space="preserve">1.29543483257294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30055785179138</t>
+    <t xml:space="preserve">1.30055809020996</t>
   </si>
   <si>
     <t xml:space="preserve">1.29836225509644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2932391166687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29250729084015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3012900352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30568110942841</t>
+    <t xml:space="preserve">1.29323923587799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29250717163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30128991603851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30568099021912</t>
   </si>
   <si>
     <t xml:space="preserve">1.26908695697784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26762306690216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24786233901978</t>
+    <t xml:space="preserve">1.26762294769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24786221981049</t>
   </si>
   <si>
     <t xml:space="preserve">1.25518119335175</t>
@@ -410,43 +410,43 @@
     <t xml:space="preserve">1.25810861587524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25005793571472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24054336547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24639856815338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24420297145844</t>
+    <t xml:space="preserve">1.25005781650543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24054348468781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24639868736267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24420285224915</t>
   </si>
   <si>
     <t xml:space="preserve">1.23615205287933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23688399791718</t>
+    <t xml:space="preserve">1.23688411712646</t>
   </si>
   <si>
     <t xml:space="preserve">1.2420072555542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23176074028015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20980441570282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21126794815063</t>
+    <t xml:space="preserve">1.23176097869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20980429649353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21126818656921</t>
   </si>
   <si>
     <t xml:space="preserve">1.21858692169189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21492767333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19004344940186</t>
+    <t xml:space="preserve">1.21492755413055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19004333019257</t>
   </si>
   <si>
     <t xml:space="preserve">1.18199265003204</t>
@@ -458,25 +458,25 @@
     <t xml:space="preserve">1.19297099113464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19663059711456</t>
+    <t xml:space="preserve">1.19663035869598</t>
   </si>
   <si>
     <t xml:space="preserve">1.22005069255829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21639144420624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25957250595093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27786946296692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28592026233673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2947028875351</t>
+    <t xml:space="preserve">1.21639132499695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25957226753235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27786922454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28592038154602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29470300674438</t>
   </si>
   <si>
     <t xml:space="preserve">1.29689836502075</t>
@@ -491,34 +491,34 @@
     <t xml:space="preserve">1.34081149101257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33349275588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33422470092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3320289850235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33861601352692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33934783935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34666669368744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34227550029755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34007978439331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32690572738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3210506439209</t>
+    <t xml:space="preserve">1.3334926366806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33422446250916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33202910423279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33861589431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33934772014618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34666645526886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34227526187897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34007966518402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3269054889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32105076313019</t>
   </si>
   <si>
     <t xml:space="preserve">1.3459347486496</t>
@@ -527,28 +527,28 @@
     <t xml:space="preserve">1.36130428314209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36057245731354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33276069164276</t>
+    <t xml:space="preserve">1.36057257652283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33276081085205</t>
   </si>
   <si>
     <t xml:space="preserve">1.34959411621094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33788418769836</t>
+    <t xml:space="preserve">1.33788394927979</t>
   </si>
   <si>
     <t xml:space="preserve">1.34373903274536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34520268440247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32910144329071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36349976062775</t>
+    <t xml:space="preserve">1.34520280361176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32910132408142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36349987983704</t>
   </si>
   <si>
     <t xml:space="preserve">1.36789131164551</t>
@@ -557,22 +557,22 @@
     <t xml:space="preserve">1.37667381763458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38252890110016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39789855480194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41253614425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40668118000031</t>
+    <t xml:space="preserve">1.38252902030945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39789843559265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4125360250473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40668106079102</t>
   </si>
   <si>
     <t xml:space="preserve">1.4081449508667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40887689590454</t>
+    <t xml:space="preserve">1.40887677669525</t>
   </si>
   <si>
     <t xml:space="preserve">1.40302169322968</t>
@@ -584,28 +584,28 @@
     <t xml:space="preserve">1.36935496330261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37886965274811</t>
+    <t xml:space="preserve">1.37886953353882</t>
   </si>
   <si>
     <t xml:space="preserve">1.38911581039429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40155780315399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49304330348969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47621035575867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48206520080566</t>
+    <t xml:space="preserve">1.40155804157257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49304342269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47621011734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48206543922424</t>
   </si>
   <si>
     <t xml:space="preserve">1.49157977104187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50328993797302</t>
+    <t xml:space="preserve">1.50328981876373</t>
   </si>
   <si>
     <t xml:space="preserve">1.46742761135101</t>
@@ -614,19 +614,19 @@
     <t xml:space="preserve">1.45864486694336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4791374206543</t>
+    <t xml:space="preserve">1.47913753986359</t>
   </si>
   <si>
     <t xml:space="preserve">1.49523913860321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49084782600403</t>
+    <t xml:space="preserve">1.49084794521332</t>
   </si>
   <si>
     <t xml:space="preserve">1.48792028427124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52744209766388</t>
+    <t xml:space="preserve">1.52744197845459</t>
   </si>
   <si>
     <t xml:space="preserve">1.50987684726715</t>
@@ -635,16 +635,16 @@
     <t xml:space="preserve">1.53256523609161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52963769435883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53183329105377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52817368507385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5149998664856</t>
+    <t xml:space="preserve">1.52963757514954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53183341026306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52817356586456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51499998569489</t>
   </si>
   <si>
     <t xml:space="preserve">1.49963045120239</t>
@@ -662,13 +662,13 @@
     <t xml:space="preserve">1.48426103591919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4637678861618</t>
+    <t xml:space="preserve">1.46376800537109</t>
   </si>
   <si>
     <t xml:space="preserve">1.45498538017273</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48499286174774</t>
+    <t xml:space="preserve">1.48499298095703</t>
   </si>
   <si>
     <t xml:space="preserve">1.52085506916046</t>
@@ -677,19 +677,19 @@
     <t xml:space="preserve">1.53768837451935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58233332633972</t>
+    <t xml:space="preserve">1.58233344554901</t>
   </si>
   <si>
     <t xml:space="preserve">1.63126373291016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63427472114563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64857757091522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63578033447266</t>
+    <t xml:space="preserve">1.63427484035492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64857733249664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63578045368195</t>
   </si>
   <si>
     <t xml:space="preserve">1.66664409637451</t>
@@ -698,19 +698,19 @@
     <t xml:space="preserve">1.66288042068481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6613746881485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76902174949646</t>
+    <t xml:space="preserve">1.66137480735779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76902151107788</t>
   </si>
   <si>
     <t xml:space="preserve">1.8081659078598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84429919719696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9165655374527</t>
+    <t xml:space="preserve">1.84429907798767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91656541824341</t>
   </si>
   <si>
     <t xml:space="preserve">1.99485409259796</t>
@@ -722,61 +722,61 @@
     <t xml:space="preserve">1.95345151424408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98205709457397</t>
+    <t xml:space="preserve">1.98205697536469</t>
   </si>
   <si>
     <t xml:space="preserve">1.93011522293091</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83376014232635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9030157327652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90452110767365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91204881668091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93538510799408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92258787155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91581284999847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88118505477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92860984802246</t>
+    <t xml:space="preserve">1.83376038074493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90301561355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90452075004578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9120489358902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93538475036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92258763313293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91581296920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88118517398834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92860996723175</t>
   </si>
   <si>
     <t xml:space="preserve">1.92183494567871</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9255987405777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94065427780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9263516664505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90376818180084</t>
+    <t xml:space="preserve">1.92559885978699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9406543970108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92635154724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90376853942871</t>
   </si>
   <si>
     <t xml:space="preserve">1.91957664489746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91882407665253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93237376213074</t>
+    <t xml:space="preserve">1.91882371902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93237364292145</t>
   </si>
   <si>
     <t xml:space="preserve">1.94366538524628</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">1.91054308414459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89021825790405</t>
+    <t xml:space="preserve">1.89021849632263</t>
   </si>
   <si>
     <t xml:space="preserve">1.90753221511841</t>
@@ -794,7 +794,7 @@
     <t xml:space="preserve">1.89699351787567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89473485946655</t>
+    <t xml:space="preserve">1.89473497867584</t>
   </si>
   <si>
     <t xml:space="preserve">1.87742114067078</t>
@@ -803,22 +803,22 @@
     <t xml:space="preserve">1.860107421875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77052700519562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79762709140778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76826882362366</t>
+    <t xml:space="preserve">1.77052712440491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7976268529892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76826858520508</t>
   </si>
   <si>
     <t xml:space="preserve">1.79461586475372</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80741310119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83074903488159</t>
+    <t xml:space="preserve">1.807412981987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83074927330017</t>
   </si>
   <si>
     <t xml:space="preserve">1.84881579875946</t>
@@ -827,22 +827,22 @@
     <t xml:space="preserve">1.82547962665558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81042420864105</t>
+    <t xml:space="preserve">1.81042397022247</t>
   </si>
   <si>
     <t xml:space="preserve">1.82623243331909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83601856231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83902978897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85257959365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82171583175659</t>
+    <t xml:space="preserve">1.83601868152618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83902966976166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85257947444916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82171607017517</t>
   </si>
   <si>
     <t xml:space="preserve">1.84806299209595</t>
@@ -851,43 +851,43 @@
     <t xml:space="preserve">1.84655737876892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83752417564392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89774608612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91280150413513</t>
+    <t xml:space="preserve">1.83752429485321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89774596691132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91280174255371</t>
   </si>
   <si>
     <t xml:space="preserve">1.97377645969391</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97151803970337</t>
+    <t xml:space="preserve">1.97151815891266</t>
   </si>
   <si>
     <t xml:space="preserve">1.930868268013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93613743782043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92108225822449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88796019554138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88720715045929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89548790454865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89322948455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86914050579071</t>
+    <t xml:space="preserve">1.93613755702972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92108201980591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88796007633209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88720726966858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89548766613007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89322936534882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.869140625</t>
   </si>
   <si>
     <t xml:space="preserve">1.85860180854797</t>
@@ -899,46 +899,46 @@
     <t xml:space="preserve">1.85709631443024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85182678699493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86688220500946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88494896888733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87215173244476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87064635753632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86161303520203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88193786144257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86763501167297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8736572265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86537683010101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84505188465118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84204053878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84731018543243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84279358386993</t>
+    <t xml:space="preserve">1.85182702541351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86688232421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88494884967804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87215185165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87064623832703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86161279678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88193774223328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86763513088226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87365746498108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8653769493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84505200386047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84204077720642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84731030464172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84279346466064</t>
   </si>
   <si>
     <t xml:space="preserve">1.81795191764832</t>
@@ -947,22 +947,22 @@
     <t xml:space="preserve">1.82397413253784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82849109172821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81569361686707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82021045684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81117689609528</t>
+    <t xml:space="preserve">1.82849085330963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81569373607635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82021033763885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81117701530457</t>
   </si>
   <si>
     <t xml:space="preserve">1.816446185112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81418788433075</t>
+    <t xml:space="preserve">1.81418800354004</t>
   </si>
   <si>
     <t xml:space="preserve">1.83526575565338</t>
@@ -974,34 +974,34 @@
     <t xml:space="preserve">1.82246851921082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85032117366791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89849901199341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93689060211182</t>
+    <t xml:space="preserve">1.8503212928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89849889278412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93689024448395</t>
   </si>
   <si>
     <t xml:space="preserve">1.91731834411621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97979879379272</t>
+    <t xml:space="preserve">1.97979843616486</t>
   </si>
   <si>
     <t xml:space="preserve">1.96474313735962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94667661190033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97076511383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9677540063858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96248471736908</t>
+    <t xml:space="preserve">1.94667649269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97076523303986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96775436401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96248459815979</t>
   </si>
   <si>
     <t xml:space="preserve">2.10325384140015</t>
@@ -1016,19 +1016,19 @@
     <t xml:space="preserve">1.98732626438141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99937069416046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98582077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99033737182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96624875068665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99861776828766</t>
+    <t xml:space="preserve">1.99937081336975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98582100868225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99033749103546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96624863147736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99861788749695</t>
   </si>
   <si>
     <t xml:space="preserve">1.96549606323242</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">1.98280966281891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02496528625488</t>
+    <t xml:space="preserve">2.0249650478363</t>
   </si>
   <si>
     <t xml:space="preserve">2.06260371208191</t>
@@ -1052,10 +1052,10 @@
     <t xml:space="preserve">2.08142328262329</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08217620849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08593988418579</t>
+    <t xml:space="preserve">2.08217573165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08594012260437</t>
   </si>
   <si>
     <t xml:space="preserve">2.07765936851501</t>
@@ -1067,19 +1067,19 @@
     <t xml:space="preserve">2.09045672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11153435707092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10024285316467</t>
+    <t xml:space="preserve">2.11153411865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10024237632751</t>
   </si>
   <si>
     <t xml:space="preserve">2.08669257164001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07013177871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06034588813782</t>
+    <t xml:space="preserve">2.07013154029846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06034564971924</t>
   </si>
   <si>
     <t xml:space="preserve">2.05959272384644</t>
@@ -1088,13 +1088,13 @@
     <t xml:space="preserve">2.05884003639221</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07615399360657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08368182182312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10400629043579</t>
+    <t xml:space="preserve">2.07615375518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08368158340454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10400700569153</t>
   </si>
   <si>
     <t xml:space="preserve">2.08518719673157</t>
@@ -1103,16 +1103,16 @@
     <t xml:space="preserve">2.13185930252075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19057583808899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21315908432007</t>
+    <t xml:space="preserve">2.19057559967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21315884590149</t>
   </si>
   <si>
     <t xml:space="preserve">2.17552018165588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16799259185791</t>
+    <t xml:space="preserve">2.16799235343933</t>
   </si>
   <si>
     <t xml:space="preserve">2.20563125610352</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">2.22068667411804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31101989746094</t>
+    <t xml:space="preserve">2.31101965904236</t>
   </si>
   <si>
     <t xml:space="preserve">2.36371397972107</t>
@@ -1130,61 +1130,61 @@
     <t xml:space="preserve">2.31854724884033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33360266685486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37124156951904</t>
+    <t xml:space="preserve">2.33360290527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37124180793762</t>
   </si>
   <si>
     <t xml:space="preserve">2.32607507705688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28843641281128</t>
+    <t xml:space="preserve">2.2884361743927</t>
   </si>
   <si>
     <t xml:space="preserve">2.2658531665802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28090858459473</t>
+    <t xml:space="preserve">2.28090882301331</t>
   </si>
   <si>
     <t xml:space="preserve">2.30349206924438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29596424102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25832533836365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19810342788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18304753303528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43899154663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38629746437073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55190753936768</t>
+    <t xml:space="preserve">2.29596447944641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25832557678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19810318946838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18304777145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43899130821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38629698753357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55190801620483</t>
   </si>
   <si>
     <t xml:space="preserve">2.5443799495697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61965751647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46157503128052</t>
+    <t xml:space="preserve">2.61965775489807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46157479286194</t>
   </si>
   <si>
     <t xml:space="preserve">2.49168562889099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46910262107849</t>
+    <t xml:space="preserve">2.46910238265991</t>
   </si>
   <si>
     <t xml:space="preserve">2.40135264396667</t>
@@ -1193,25 +1193,25 @@
     <t xml:space="preserve">2.43146371841431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47663021087646</t>
+    <t xml:space="preserve">2.47663044929504</t>
   </si>
   <si>
     <t xml:space="preserve">2.44651937484741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40888023376465</t>
+    <t xml:space="preserve">2.40888047218323</t>
   </si>
   <si>
     <t xml:space="preserve">2.48415803909302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45404672622681</t>
+    <t xml:space="preserve">2.45404648780823</t>
   </si>
   <si>
     <t xml:space="preserve">2.4164080619812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5067412853241</t>
+    <t xml:space="preserve">2.50674104690552</t>
   </si>
   <si>
     <t xml:space="preserve">2.52932405471802</t>
@@ -1238,7 +1238,7 @@
     <t xml:space="preserve">2.52156591415405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.544842004776</t>
+    <t xml:space="preserve">2.54484176635742</t>
   </si>
   <si>
     <t xml:space="preserve">2.5293242931366</t>
@@ -1253,22 +1253,22 @@
     <t xml:space="preserve">2.42846155166626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3275990486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30432319641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28104734420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31208181381226</t>
+    <t xml:space="preserve">2.32759928703308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30432367324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28104710578918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31208157539368</t>
   </si>
   <si>
     <t xml:space="preserve">2.22673654556274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20346069335938</t>
+    <t xml:space="preserve">2.2034604549408</t>
   </si>
   <si>
     <t xml:space="preserve">2.19570183753967</t>
@@ -1277,22 +1277,22 @@
     <t xml:space="preserve">2.21897792816162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23449540138245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25777149200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17242574691772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11811542510986</t>
+    <t xml:space="preserve">2.23449516296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25777125358582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1724259853363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11811518669128</t>
   </si>
   <si>
     <t xml:space="preserve">2.18794345855713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25001215934753</t>
+    <t xml:space="preserve">2.25001263618469</t>
   </si>
   <si>
     <t xml:space="preserve">2.12587380409241</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">2.07932209968567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07156324386597</t>
+    <t xml:space="preserve">2.07156348228455</t>
   </si>
   <si>
     <t xml:space="preserve">2.04052877426147</t>
@@ -1322,10 +1322,10 @@
     <t xml:space="preserve">2.14139127731323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16466760635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14914989471436</t>
+    <t xml:space="preserve">2.1646671295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14915013313293</t>
   </si>
   <si>
     <t xml:space="preserve">2.18018460273743</t>
@@ -1337,76 +1337,76 @@
     <t xml:space="preserve">2.03276991844177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01725244522095</t>
+    <t xml:space="preserve">2.01725292205811</t>
   </si>
   <si>
     <t xml:space="preserve">2.02501130104065</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0094940662384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97070062160492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9629420042038</t>
+    <t xml:space="preserve">2.00949382781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9707008600235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96294188499451</t>
   </si>
   <si>
     <t xml:space="preserve">1.93966603279114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8853554725647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87759673595428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85432064533234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86983788013458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7922511100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83880352973938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83104467391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86207938194275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15690875053406</t>
+    <t xml:space="preserve">1.88535535335541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87759685516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85432076454163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86983799934387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79225146770477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83880364894867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83104479312897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86207926273346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15690851211548</t>
   </si>
   <si>
     <t xml:space="preserve">2.06380462646484</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04828715324402</t>
+    <t xml:space="preserve">2.0482873916626</t>
   </si>
   <si>
     <t xml:space="preserve">2.0017352104187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97845935821533</t>
+    <t xml:space="preserve">1.97845947742462</t>
   </si>
   <si>
     <t xml:space="preserve">1.99397683143616</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92414855957031</t>
+    <t xml:space="preserve">1.9241486787796</t>
   </si>
   <si>
     <t xml:space="preserve">1.84656190872192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80776870250702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75345826148987</t>
+    <t xml:space="preserve">1.80776882171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75345802307129</t>
   </si>
   <si>
     <t xml:space="preserve">1.77673399448395</t>
@@ -1415,28 +1415,28 @@
     <t xml:space="preserve">1.74569940567017</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82328617572784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89311420917511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91639029979706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21121907234192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11035680770874</t>
+    <t xml:space="preserve">1.82328581809998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89311385154724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91639006137848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2112193107605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11035656929016</t>
   </si>
   <si>
     <t xml:space="preserve">2.05604600906372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26552987098694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24225401878357</t>
+    <t xml:space="preserve">2.26553010940552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24225378036499</t>
   </si>
   <si>
     <t xml:space="preserve">2.35087513923645</t>
@@ -1445,16 +1445,16 @@
     <t xml:space="preserve">2.31984066963196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3353579044342</t>
+    <t xml:space="preserve">2.33535814285278</t>
   </si>
   <si>
     <t xml:space="preserve">2.35863375663757</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40518569946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3819100856781</t>
+    <t xml:space="preserve">2.40518617630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38190984725952</t>
   </si>
   <si>
     <t xml:space="preserve">2.38966846466064</t>
@@ -1463,136 +1463,136 @@
     <t xml:space="preserve">2.39742708206177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41294455528259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42070317268372</t>
+    <t xml:space="preserve">2.41294431686401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42070341110229</t>
   </si>
   <si>
     <t xml:space="preserve">2.36639261245728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34311676025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3741512298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45173788070679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47501373291016</t>
+    <t xml:space="preserve">2.34311652183533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37415146827698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45173764228821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47501397132874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55260062217712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54447102546692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5200834274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4956955909729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4387903213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45504903793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47943687438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48756623268127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50382471084595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40627312660217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43066120147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42253160476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36562657356262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3900146484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28433346748352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27620434761047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2274284362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23555779457092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25181651115417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26807498931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.357497215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32498002052307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34123873710632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37375593185425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4631781578064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51195383071899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52821254730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53634214401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58511781692505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5932469367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56072998046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60137629508972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60950541496277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5688591003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57698845863342</t>
   </si>
   <si>
     <t xml:space="preserve">2.55260038375854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54447102546692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52008318901062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4956955909729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43879008293152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45504903793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47943687438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48756623268127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50382471084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40627312660217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43066120147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42253160476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3656268119812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3900146484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2843337059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27620410919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2274284362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23555779457092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2518162727356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26807522773743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35749697685242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32498002052307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34123873710632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37375593185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4631781578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51195383071899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52821254730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53634190559387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58511781692505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5932469367981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56072974205017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60137629508972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60950541496277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5688591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.576988697052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55260062217712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4144024848938</t>
+    <t xml:space="preserve">2.41440272331238</t>
   </si>
   <si>
     <t xml:space="preserve">2.3331093788147</t>
@@ -1604,7 +1604,7 @@
     <t xml:space="preserve">2.39814376831055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47130751609802</t>
+    <t xml:space="preserve">2.47130727767944</t>
   </si>
   <si>
     <t xml:space="preserve">2.44691967964172</t>
@@ -1622,7 +1622,7 @@
     <t xml:space="preserve">2.30059218406677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11361813545227</t>
+    <t xml:space="preserve">2.11361837387085</t>
   </si>
   <si>
     <t xml:space="preserve">2.18678212165833</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">2.12987685203552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08110117912292</t>
+    <t xml:space="preserve">2.08110094070435</t>
   </si>
   <si>
     <t xml:space="preserve">2.10548901557922</t>
@@ -1643,16 +1643,16 @@
     <t xml:space="preserve">2.048583984375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89412713050842</t>
+    <t xml:space="preserve">1.89412724971771</t>
   </si>
   <si>
     <t xml:space="preserve">1.65837728977203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66650652885437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62586009502411</t>
+    <t xml:space="preserve">1.66650664806366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6258602142334</t>
   </si>
   <si>
     <t xml:space="preserve">1.47140347957611</t>
@@ -1661,7 +1661,7 @@
     <t xml:space="preserve">1.50392067432404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51205003261566</t>
+    <t xml:space="preserve">1.51205015182495</t>
   </si>
   <si>
     <t xml:space="preserve">1.61366641521454</t>
@@ -1676,7 +1676,7 @@
     <t xml:space="preserve">1.53237330913544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4957914352417</t>
+    <t xml:space="preserve">1.49579131603241</t>
   </si>
   <si>
     <t xml:space="preserve">1.58521366119385</t>
@@ -1685,31 +1685,31 @@
     <t xml:space="preserve">1.6014723777771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5730197429657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56082570552826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58114898204803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56895506381989</t>
+    <t xml:space="preserve">1.57301986217499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56082582473755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58114922046661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5689549446106</t>
   </si>
   <si>
     <t xml:space="preserve">1.63398957252502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69089472293854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60553705692291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62179553508759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58927845954895</t>
+    <t xml:space="preserve">1.69089460372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60553693771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62179565429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58927834033966</t>
   </si>
   <si>
     <t xml:space="preserve">1.61773085594177</t>
@@ -1724,16 +1724,16 @@
     <t xml:space="preserve">1.76405835151672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7315411567688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71528267860413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69902396202087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6502480506897</t>
+    <t xml:space="preserve">1.73154103755951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71528255939484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69902384281158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65024816989899</t>
   </si>
   <si>
     <t xml:space="preserve">1.74779963493347</t>
@@ -1742,16 +1742,16 @@
     <t xml:space="preserve">1.75592911243439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77218747138977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78844630718231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82096338272095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87786829471588</t>
+    <t xml:space="preserve">1.77218759059906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78844618797302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82096350193024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87786865234375</t>
   </si>
   <si>
     <t xml:space="preserve">1.82909274101257</t>
@@ -1760,25 +1760,25 @@
     <t xml:space="preserve">1.80470490455627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81283402442932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79657578468323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78031694889069</t>
+    <t xml:space="preserve">1.81283414363861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79657566547394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78031671047211</t>
   </si>
   <si>
     <t xml:space="preserve">1.72341191768646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73967039585114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68276524543762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60960161685944</t>
+    <t xml:space="preserve">1.73967027664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6827654838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60960149765015</t>
   </si>
   <si>
     <t xml:space="preserve">1.64211881160736</t>
@@ -1787,13 +1787,13 @@
     <t xml:space="preserve">1.57708418369293</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52830862998962</t>
+    <t xml:space="preserve">1.52830851078033</t>
   </si>
   <si>
     <t xml:space="preserve">1.53643774986267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49985611438751</t>
+    <t xml:space="preserve">1.49985599517822</t>
   </si>
   <si>
     <t xml:space="preserve">1.48766207695007</t>
@@ -1808,25 +1808,25 @@
     <t xml:space="preserve">1.42262768745422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41043376922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40636897087097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43482172489166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4144983291626</t>
+    <t xml:space="preserve">1.41043388843536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40636909008026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43482160568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41449844837189</t>
   </si>
   <si>
     <t xml:space="preserve">1.36572241783142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33320546150208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38198125362396</t>
+    <t xml:space="preserve">1.33320534229279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38198113441467</t>
   </si>
   <si>
     <t xml:space="preserve">1.35759329795837</t>
@@ -1841,7 +1841,7 @@
     <t xml:space="preserve">1.30881750583649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3372700214386</t>
+    <t xml:space="preserve">1.33727014064789</t>
   </si>
   <si>
     <t xml:space="preserve">1.32507598400116</t>
@@ -1862,28 +1862,28 @@
     <t xml:space="preserve">1.40230441093445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38604581356049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3901104927063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37791645526886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4673388004303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.520179271698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55269658565521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5445671081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49172675609589</t>
+    <t xml:space="preserve">1.3860456943512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39011061191559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37791657447815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46733868122101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52017939090729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5526967048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54456722736359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49172687530518</t>
   </si>
   <si>
     <t xml:space="preserve">1.52424395084381</t>
@@ -1898,19 +1898,19 @@
     <t xml:space="preserve">1.54050254821777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47953283786774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86973917484283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95103228092194</t>
+    <t xml:space="preserve">1.47953295707703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86973929405212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95103216171265</t>
   </si>
   <si>
     <t xml:space="preserve">2.0729718208313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2599458694458</t>
+    <t xml:space="preserve">2.25994563102722</t>
   </si>
   <si>
     <t xml:space="preserve">2.24368715286255</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">2.1786527633667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1461353302002</t>
+    <t xml:space="preserve">2.14613556861877</t>
   </si>
   <si>
     <t xml:space="preserve">2.05671310424805</t>
@@ -1940,10 +1940,10 @@
     <t xml:space="preserve">2.24429607391357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25257778167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20288825035095</t>
+    <t xml:space="preserve">2.25257754325867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20288848876953</t>
   </si>
   <si>
     <t xml:space="preserve">2.22773313522339</t>
@@ -1952,7 +1952,7 @@
     <t xml:space="preserve">2.19460678100586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17804384231567</t>
+    <t xml:space="preserve">2.17804360389709</t>
   </si>
   <si>
     <t xml:space="preserve">2.34367442131042</t>
@@ -1979,7 +1979,7 @@
     <t xml:space="preserve">2.4844605922699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49274206161499</t>
+    <t xml:space="preserve">2.49274230003357</t>
   </si>
   <si>
     <t xml:space="preserve">2.41820859909058</t>
@@ -2003,28 +2003,28 @@
     <t xml:space="preserve">2.33539295196533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32711172103882</t>
+    <t xml:space="preserve">2.32711124420166</t>
   </si>
   <si>
     <t xml:space="preserve">2.30226683616638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31883001327515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31054854393005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35195589065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29398512840271</t>
+    <t xml:space="preserve">2.31882977485657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31054830551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3519561290741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29398536682129</t>
   </si>
   <si>
     <t xml:space="preserve">2.28570365905762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27742218971252</t>
+    <t xml:space="preserve">2.2774224281311</t>
   </si>
   <si>
     <t xml:space="preserve">2.15319919586182</t>
@@ -2060,13 +2060,13 @@
     <t xml:space="preserve">2.26914072036743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26085901260376</t>
+    <t xml:space="preserve">2.26085925102234</t>
   </si>
   <si>
     <t xml:space="preserve">2.4099268913269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46789765357971</t>
+    <t xml:space="preserve">2.46789717674255</t>
   </si>
   <si>
     <t xml:space="preserve">2.50102376937866</t>
@@ -2090,28 +2090,28 @@
     <t xml:space="preserve">2.81572198867798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84884810447693</t>
+    <t xml:space="preserve">2.84884834289551</t>
   </si>
   <si>
     <t xml:space="preserve">2.86541104316711</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01447916030884</t>
+    <t xml:space="preserve">3.01447892189026</t>
   </si>
   <si>
     <t xml:space="preserve">3.03104186058044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24636220932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23808026313782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22979855537415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30433297157288</t>
+    <t xml:space="preserve">3.24636197090149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23808002471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22979879379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3043327331543</t>
   </si>
   <si>
     <t xml:space="preserve">3.12213897705078</t>
@@ -2123,7 +2123,7 @@
     <t xml:space="preserve">3.17182803153992</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21323561668396</t>
+    <t xml:space="preserve">3.21323585510254</t>
   </si>
   <si>
     <t xml:space="preserve">3.1883909702301</t>
@@ -2141,25 +2141,25 @@
     <t xml:space="preserve">3.10557579994202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13870191574097</t>
+    <t xml:space="preserve">3.13870215415955</t>
   </si>
   <si>
     <t xml:space="preserve">3.08901262283325</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07244944572449</t>
+    <t xml:space="preserve">3.07244968414307</t>
   </si>
   <si>
     <t xml:space="preserve">3.11385726928711</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08073091506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06416797637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25464344024658</t>
+    <t xml:space="preserve">3.08073115348816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06416821479797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.254643201828</t>
   </si>
   <si>
     <t xml:space="preserve">3.09729433059692</t>
@@ -2174,13 +2174,13 @@
     <t xml:space="preserve">3.04760479927063</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05588674545288</t>
+    <t xml:space="preserve">3.0558865070343</t>
   </si>
   <si>
     <t xml:space="preserve">3.15526485443115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03932356834412</t>
+    <t xml:space="preserve">3.03932332992554</t>
   </si>
   <si>
     <t xml:space="preserve">2.98963403701782</t>
@@ -2195,7 +2195,7 @@
     <t xml:space="preserve">2.97307133674622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20495414733887</t>
+    <t xml:space="preserve">3.20495438575745</t>
   </si>
   <si>
     <t xml:space="preserve">3.27948784828186</t>
@@ -68182,7 +68182,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6245138889</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>4</v>
@@ -68203,6 +68203,32 @@
         <v>964</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.6912268518</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>6500</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>2.68499994277954</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>2.68499994277954</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>904</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24616158008575</t>
+    <t xml:space="preserve">1.24616146087646</t>
   </si>
   <si>
     <t xml:space="preserve">AUTME.MI</t>
@@ -47,19 +47,19 @@
     <t xml:space="preserve">1.24544656276703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24330163002014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22256815433502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21541857719421</t>
+    <t xml:space="preserve">1.24330174922943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22256803512573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21541845798492</t>
   </si>
   <si>
     <t xml:space="preserve">1.22185301780701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21470367908478</t>
+    <t xml:space="preserve">1.21470355987549</t>
   </si>
   <si>
     <t xml:space="preserve">1.23615217208862</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">1.21327364444733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20683896541595</t>
+    <t xml:space="preserve">1.20683920383453</t>
   </si>
   <si>
     <t xml:space="preserve">1.2011194229126</t>
@@ -77,28 +77,28 @@
     <t xml:space="preserve">1.20040452480316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1668016910553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1946849822998</t>
+    <t xml:space="preserve">1.16680181026459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19468474388123</t>
   </si>
   <si>
     <t xml:space="preserve">1.25688576698303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25045120716095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24687659740448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25116610527039</t>
+    <t xml:space="preserve">1.25045108795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2468763589859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2511659860611</t>
   </si>
   <si>
     <t xml:space="preserve">1.26475036144257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23543739318848</t>
+    <t xml:space="preserve">1.2354371547699</t>
   </si>
   <si>
     <t xml:space="preserve">1.22542774677277</t>
@@ -110,13 +110,13 @@
     <t xml:space="preserve">1.22113811969757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19396996498108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22685778141022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20469439029694</t>
+    <t xml:space="preserve">1.19397020339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22685766220093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20469427108765</t>
   </si>
   <si>
     <t xml:space="preserve">1.25831580162048</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">1.265465259552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25903058052063</t>
+    <t xml:space="preserve">1.25903069972992</t>
   </si>
   <si>
     <t xml:space="preserve">1.26903998851776</t>
@@ -134,22 +134,22 @@
     <t xml:space="preserve">1.21684849262238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22828769683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27404451370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26689481735229</t>
+    <t xml:space="preserve">1.22828781604767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2740443944931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26689493656158</t>
   </si>
   <si>
     <t xml:space="preserve">1.27261459827423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27189981937408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27904915809631</t>
+    <t xml:space="preserve">1.27189958095551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2790492773056</t>
   </si>
   <si>
     <t xml:space="preserve">1.2676100730896</t>
@@ -161,100 +161,100 @@
     <t xml:space="preserve">1.26260530948639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24830627441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2490211725235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24258673191071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23686707019806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23472225666046</t>
+    <t xml:space="preserve">1.24830615520477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24902129173279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24258661270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23686683177948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23472213745117</t>
   </si>
   <si>
     <t xml:space="preserve">1.23400723934174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25225365161896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26176798343658</t>
+    <t xml:space="preserve">1.25225377082825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26176810264587</t>
   </si>
   <si>
     <t xml:space="preserve">1.26835501194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27860128879547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2764059305191</t>
+    <t xml:space="preserve">1.27860140800476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27640581130981</t>
   </si>
   <si>
     <t xml:space="preserve">1.27421021461487</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27494204044342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26323187351227</t>
+    <t xml:space="preserve">1.27494215965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26323175430298</t>
   </si>
   <si>
     <t xml:space="preserve">1.27128267288208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26689112186432</t>
+    <t xml:space="preserve">1.2668913602829</t>
   </si>
   <si>
     <t xml:space="preserve">1.28445649147034</t>
   </si>
   <si>
-    <t xml:space="preserve">1.280797123909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2793333530426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27347826957703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27274632453918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26615941524506</t>
+    <t xml:space="preserve">1.28079700469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27933323383331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27347815036774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27274644374847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26615917682648</t>
   </si>
   <si>
     <t xml:space="preserve">1.28226101398468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28811597824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28738403320312</t>
+    <t xml:space="preserve">1.28811609745026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28738415241241</t>
   </si>
   <si>
     <t xml:space="preserve">1.28299272060394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26396369934082</t>
+    <t xml:space="preserve">1.26396358013153</t>
   </si>
   <si>
     <t xml:space="preserve">1.24127531051636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24347114562988</t>
+    <t xml:space="preserve">1.24347102642059</t>
   </si>
   <si>
     <t xml:space="preserve">1.22956514358521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23468852043152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22663772106171</t>
+    <t xml:space="preserve">1.23468840122223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22663760185242</t>
   </si>
   <si>
     <t xml:space="preserve">1.20687675476074</t>
@@ -266,10 +266,10 @@
     <t xml:space="preserve">1.18565225601196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17833340167999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18784773349762</t>
+    <t xml:space="preserve">1.17833352088928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1878479719162</t>
   </si>
   <si>
     <t xml:space="preserve">1.16955065727234</t>
@@ -278,16 +278,16 @@
     <t xml:space="preserve">1.17101454734802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17028260231018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18931150436401</t>
+    <t xml:space="preserve">1.17028248310089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18931138515472</t>
   </si>
   <si>
     <t xml:space="preserve">1.22224640846252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22151434421539</t>
+    <t xml:space="preserve">1.22151470184326</t>
   </si>
   <si>
     <t xml:space="preserve">1.23981153964996</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">1.2310289144516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19736242294312</t>
+    <t xml:space="preserve">1.19736230373383</t>
   </si>
   <si>
     <t xml:space="preserve">1.2171231508255</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">1.22297811508179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23322474956512</t>
+    <t xml:space="preserve">1.23322463035583</t>
   </si>
   <si>
     <t xml:space="preserve">1.23249268531799</t>
@@ -326,16 +326,16 @@
     <t xml:space="preserve">1.22883331775665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28518843650818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25884068012238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30714499950409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29909408092499</t>
+    <t xml:space="preserve">1.28518831729889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25884079933167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3071448802948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29909420013428</t>
   </si>
   <si>
     <t xml:space="preserve">1.32324635982513</t>
@@ -347,31 +347,31 @@
     <t xml:space="preserve">1.32763767242432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30348539352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31592726707458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3181232213974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29763042926788</t>
+    <t xml:space="preserve">1.30348527431488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31592750549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31812310218811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29763054847717</t>
   </si>
   <si>
     <t xml:space="preserve">1.30275344848633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29982590675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28884792327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29543483257294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30055797100067</t>
+    <t xml:space="preserve">1.29982614517212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28884780406952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29543495178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30055809020996</t>
   </si>
   <si>
     <t xml:space="preserve">1.29836225509644</t>
@@ -383,7 +383,7 @@
     <t xml:space="preserve">1.29250717163086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30128979682922</t>
+    <t xml:space="preserve">1.30128991603851</t>
   </si>
   <si>
     <t xml:space="preserve">1.30568110942841</t>
@@ -395,22 +395,22 @@
     <t xml:space="preserve">1.26762318611145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24786245822906</t>
+    <t xml:space="preserve">1.24786233901978</t>
   </si>
   <si>
     <t xml:space="preserve">1.25518107414246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2654275894165</t>
+    <t xml:space="preserve">1.26542747020721</t>
   </si>
   <si>
     <t xml:space="preserve">1.28006517887115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25810861587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25005793571472</t>
+    <t xml:space="preserve">1.25810873508453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25005781650543</t>
   </si>
   <si>
     <t xml:space="preserve">1.24054348468781</t>
@@ -419,16 +419,19 @@
     <t xml:space="preserve">1.24639868736267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24420285224915</t>
+    <t xml:space="preserve">1.24420297145844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23615205287933</t>
   </si>
   <si>
     <t xml:space="preserve">1.23688399791718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24200713634491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23176097869873</t>
+    <t xml:space="preserve">1.2420072555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23176085948944</t>
   </si>
   <si>
     <t xml:space="preserve">1.20980429649353</t>
@@ -437,7 +440,7 @@
     <t xml:space="preserve">1.21126806735992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21858704090118</t>
+    <t xml:space="preserve">1.21858716011047</t>
   </si>
   <si>
     <t xml:space="preserve">1.21492755413055</t>
@@ -449,127 +452,127 @@
     <t xml:space="preserve">1.18199276924133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21419560909271</t>
+    <t xml:space="preserve">1.214195728302</t>
   </si>
   <si>
     <t xml:space="preserve">1.19297087192535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19663047790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22005081176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21639132499695</t>
+    <t xml:space="preserve">1.19663023948669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22005069255829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21639144420624</t>
   </si>
   <si>
     <t xml:space="preserve">1.25957238674164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27786958217621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28592026233673</t>
+    <t xml:space="preserve">1.27786946296692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28592038154602</t>
   </si>
   <si>
     <t xml:space="preserve">1.2947028875351</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29689824581146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31007254123688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32544219493866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34081149101257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33349275588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33422470092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33202922344208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33861601352692</t>
+    <t xml:space="preserve">1.29689836502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31007242202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32544207572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34081161022186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3334926366806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33422446250916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33202886581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33861613273621</t>
   </si>
   <si>
     <t xml:space="preserve">1.33934772014618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34666669368744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34227538108826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34007954597473</t>
+    <t xml:space="preserve">1.34666657447815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34227526187897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34007966518402</t>
   </si>
   <si>
     <t xml:space="preserve">1.32690584659576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3210506439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34593462944031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36130428314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36057245731354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33276093006134</t>
+    <t xml:space="preserve">1.32105076313019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3459347486496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36130452156067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36057257652283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33276069164276</t>
   </si>
   <si>
     <t xml:space="preserve">1.34959423542023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33788394927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34373927116394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34520292282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32910132408142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36349976062775</t>
+    <t xml:space="preserve">1.33788406848907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34373915195465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34520280361176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32910144329071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36349999904633</t>
   </si>
   <si>
     <t xml:space="preserve">1.36789131164551</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37667381763458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38252890110016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39789855480194</t>
+    <t xml:space="preserve">1.37667393684387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38252878189087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39789843559265</t>
   </si>
   <si>
     <t xml:space="preserve">1.41253614425659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40668106079102</t>
+    <t xml:space="preserve">1.40668118000031</t>
   </si>
   <si>
     <t xml:space="preserve">1.40814471244812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40887689590454</t>
+    <t xml:space="preserve">1.40887665748596</t>
   </si>
   <si>
     <t xml:space="preserve">1.40302181243896</t>
@@ -578,64 +581,64 @@
     <t xml:space="preserve">1.39277541637421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3693550825119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37886965274811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38911581039429</t>
+    <t xml:space="preserve">1.36935484409332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37886953353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38911592960358</t>
   </si>
   <si>
     <t xml:space="preserve">1.40155792236328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49304342269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4762099981308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48206532001495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49157953262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50328981876373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46742761135101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45864510536194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47913753986359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49523913860321</t>
+    <t xml:space="preserve">1.49304354190826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47621011734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48206508159637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49157965183258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50328993797302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46742749214172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45864498615265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4791374206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4952392578125</t>
   </si>
   <si>
     <t xml:space="preserve">1.49084782600403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48792016506195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52744209766388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50987672805786</t>
+    <t xml:space="preserve">1.48792028427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5274418592453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50987660884857</t>
   </si>
   <si>
     <t xml:space="preserve">1.53256523609161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52963757514954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53183329105377</t>
+    <t xml:space="preserve">1.52963769435883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53183341026306</t>
   </si>
   <si>
     <t xml:space="preserve">1.52817380428314</t>
@@ -650,64 +653,64 @@
     <t xml:space="preserve">1.498166680336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48572444915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47108674049377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4842609167099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46376812458038</t>
+    <t xml:space="preserve">1.48572468757629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47108697891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48426079750061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46376800537109</t>
   </si>
   <si>
     <t xml:space="preserve">1.45498549938202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48499286174774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52085506916046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53768837451935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58233344554901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63126373291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63427472114563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64857769012451</t>
+    <t xml:space="preserve">1.48499274253845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52085518836975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53768849372864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58233320713043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63126385211945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63427484035492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64857745170593</t>
   </si>
   <si>
     <t xml:space="preserve">1.63578033447266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6666442155838</t>
+    <t xml:space="preserve">1.66664397716522</t>
   </si>
   <si>
     <t xml:space="preserve">1.66288018226624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66137456893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76902163028717</t>
+    <t xml:space="preserve">1.6613746881485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76902174949646</t>
   </si>
   <si>
     <t xml:space="preserve">1.80816578865051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84429907798767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91656529903412</t>
+    <t xml:space="preserve">1.84429895877838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9165655374527</t>
   </si>
   <si>
     <t xml:space="preserve">1.99485421180725</t>
@@ -716,10 +719,10 @@
     <t xml:space="preserve">2.01367354393005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95345163345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98205721378326</t>
+    <t xml:space="preserve">1.95345139503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98205697536469</t>
   </si>
   <si>
     <t xml:space="preserve">1.9301153421402</t>
@@ -731,13 +734,13 @@
     <t xml:space="preserve">1.90301561355591</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90452110767365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91204869747162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93538475036621</t>
+    <t xml:space="preserve">1.90452098846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9120489358902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9353848695755</t>
   </si>
   <si>
     <t xml:space="preserve">1.92258787155151</t>
@@ -746,7 +749,7 @@
     <t xml:space="preserve">1.91581284999847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88118505477905</t>
+    <t xml:space="preserve">1.88118517398834</t>
   </si>
   <si>
     <t xml:space="preserve">1.92860984802246</t>
@@ -758,22 +761,22 @@
     <t xml:space="preserve">1.9255987405777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94065451622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92635142803192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90376853942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91957664489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91882395744324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93237352371216</t>
+    <t xml:space="preserve">1.94065427780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9263516664505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90376842021942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91957640647888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91882371902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93237376213074</t>
   </si>
   <si>
     <t xml:space="preserve">1.94366538524628</t>
@@ -782,13 +785,13 @@
     <t xml:space="preserve">1.91054320335388</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89021849632263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9075323343277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89699339866638</t>
+    <t xml:space="preserve">1.89021837711334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90753221511841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89699327945709</t>
   </si>
   <si>
     <t xml:space="preserve">1.89473497867584</t>
@@ -800,16 +803,16 @@
     <t xml:space="preserve">1.86010718345642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7705272436142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7976268529892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76826870441437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79461586475372</t>
+    <t xml:space="preserve">1.77052700519562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79762709140778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76826894283295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79461598396301</t>
   </si>
   <si>
     <t xml:space="preserve">1.80741310119629</t>
@@ -821,34 +824,34 @@
     <t xml:space="preserve">1.84881556034088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82547986507416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81042420864105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82623267173767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83601856231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83902955055237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85257947444916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82171583175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84806275367737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84655725955963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83752393722534</t>
+    <t xml:space="preserve">1.82547962665558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81042408943176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82623243331909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83601868152618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83902990818024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85257959365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82171595096588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84806287288666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84655749797821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83752429485321</t>
   </si>
   <si>
     <t xml:space="preserve">1.89774596691132</t>
@@ -860,7 +863,7 @@
     <t xml:space="preserve">1.97377622127533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97151803970337</t>
+    <t xml:space="preserve">1.97151827812195</t>
   </si>
   <si>
     <t xml:space="preserve">1.93086802959442</t>
@@ -869,31 +872,31 @@
     <t xml:space="preserve">1.93613767623901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92108237743378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88795983791351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88720726966858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89548778533936</t>
+    <t xml:space="preserve">1.9210821390152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88796007633209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88720715045929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89548790454865</t>
   </si>
   <si>
     <t xml:space="preserve">1.89322936534882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86914050579071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85860204696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85634362697601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85709631443024</t>
+    <t xml:space="preserve">1.86914074420929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85860180854797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85634350776672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85709619522095</t>
   </si>
   <si>
     <t xml:space="preserve">1.85182690620422</t>
@@ -902,94 +905,94 @@
     <t xml:space="preserve">1.86688232421875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88494896888733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87215185165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87064623832703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86161291599274</t>
+    <t xml:space="preserve">1.88494884967804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87215197086334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87064599990845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86161303520203</t>
   </si>
   <si>
     <t xml:space="preserve">1.88193786144257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86763501167297</t>
+    <t xml:space="preserve">1.86763525009155</t>
   </si>
   <si>
     <t xml:space="preserve">1.87365734577179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86537718772888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84505200386047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84204065799713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84731018543243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84279370307922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8179520368576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82397425174713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82849073410034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81569361686707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82021009922028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81117689609528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81644654273987</t>
+    <t xml:space="preserve">1.8653769493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84505176544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84204089641571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84731030464172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84279346466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81795191764832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82397413253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82849085330963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81569337844849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82021021842957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81117677688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81644642353058</t>
   </si>
   <si>
     <t xml:space="preserve">1.81418812274933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83526563644409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83225464820862</t>
+    <t xml:space="preserve">1.83526575565338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83225476741791</t>
   </si>
   <si>
     <t xml:space="preserve">1.82246851921082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85032141208649</t>
+    <t xml:space="preserve">1.85032117366791</t>
   </si>
   <si>
     <t xml:space="preserve">1.89849889278412</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93689036369324</t>
+    <t xml:space="preserve">1.93689060211182</t>
   </si>
   <si>
     <t xml:space="preserve">1.91731822490692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97979855537415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96474325656891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94667661190033</t>
+    <t xml:space="preserve">1.97979879379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96474301815033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94667673110962</t>
   </si>
   <si>
     <t xml:space="preserve">1.97076547145844</t>
@@ -1004,31 +1007,31 @@
     <t xml:space="preserve">2.10325384140015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04378437995911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02421236038208</t>
+    <t xml:space="preserve">2.04378461837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02421259880066</t>
   </si>
   <si>
     <t xml:space="preserve">1.98732626438141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99937057495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98582053184509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99033737182617</t>
+    <t xml:space="preserve">1.99937081336975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98582077026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99033761024475</t>
   </si>
   <si>
     <t xml:space="preserve">1.96624863147736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99861812591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96549570560455</t>
+    <t xml:space="preserve">1.99861788749695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96549594402313</t>
   </si>
   <si>
     <t xml:space="preserve">1.97603487968445</t>
@@ -1037,40 +1040,40 @@
     <t xml:space="preserve">1.98280966281891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0249650478363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06260395050049</t>
+    <t xml:space="preserve">2.02496528625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06260371208191</t>
   </si>
   <si>
     <t xml:space="preserve">2.07540082931519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08142352104187</t>
+    <t xml:space="preserve">2.08142328262329</t>
   </si>
   <si>
     <t xml:space="preserve">2.08217597007751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08593988418579</t>
+    <t xml:space="preserve">2.08594012260437</t>
   </si>
   <si>
     <t xml:space="preserve">2.07765936851501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09572601318359</t>
+    <t xml:space="preserve">2.09572625160217</t>
   </si>
   <si>
     <t xml:space="preserve">2.09045672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11153411865234</t>
+    <t xml:space="preserve">2.11153435707092</t>
   </si>
   <si>
     <t xml:space="preserve">2.10024261474609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08669257164001</t>
+    <t xml:space="preserve">2.08669281005859</t>
   </si>
   <si>
     <t xml:space="preserve">2.07013154029846</t>
@@ -1082,13 +1085,13 @@
     <t xml:space="preserve">2.05959296226501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05884003639221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07615375518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08368134498596</t>
+    <t xml:space="preserve">2.05884027481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07615399360657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08368158340454</t>
   </si>
   <si>
     <t xml:space="preserve">2.10400652885437</t>
@@ -1100,16 +1103,16 @@
     <t xml:space="preserve">2.13185906410217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19057559967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21315908432007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17552018165588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16799235343933</t>
+    <t xml:space="preserve">2.19057536125183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21315884590149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1755199432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16799259185791</t>
   </si>
   <si>
     <t xml:space="preserve">2.20563101768494</t>
@@ -1124,13 +1127,13 @@
     <t xml:space="preserve">2.36371397972107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31854748725891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33360314369202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37124156951904</t>
+    <t xml:space="preserve">2.31854701042175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33360290527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37124180793762</t>
   </si>
   <si>
     <t xml:space="preserve">2.32607507705688</t>
@@ -1145,10 +1148,10 @@
     <t xml:space="preserve">2.28090858459473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30349183082581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29596424102783</t>
+    <t xml:space="preserve">2.30349206924438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29596400260925</t>
   </si>
   <si>
     <t xml:space="preserve">2.25832533836365</t>
@@ -1160,7 +1163,7 @@
     <t xml:space="preserve">2.18304800987244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43899154663086</t>
+    <t xml:space="preserve">2.43899178504944</t>
   </si>
   <si>
     <t xml:space="preserve">2.38629722595215</t>
@@ -1175,13 +1178,13 @@
     <t xml:space="preserve">2.61965751647949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46157479286194</t>
+    <t xml:space="preserve">2.46157455444336</t>
   </si>
   <si>
     <t xml:space="preserve">2.49168562889099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46910238265991</t>
+    <t xml:space="preserve">2.46910214424133</t>
   </si>
   <si>
     <t xml:space="preserve">2.40135264396667</t>
@@ -1190,13 +1193,13 @@
     <t xml:space="preserve">2.43146371841431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47663044929504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44651913642883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40888047218323</t>
+    <t xml:space="preserve">2.47663021087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44651889801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40888071060181</t>
   </si>
   <si>
     <t xml:space="preserve">2.48415803909302</t>
@@ -1205,7 +1208,7 @@
     <t xml:space="preserve">2.45404672622681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41640830039978</t>
+    <t xml:space="preserve">2.4164080619812</t>
   </si>
   <si>
     <t xml:space="preserve">2.50674152374268</t>
@@ -1220,31 +1223,31 @@
     <t xml:space="preserve">2.5913941860199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58363485336304</t>
+    <t xml:space="preserve">2.58363509178162</t>
   </si>
   <si>
     <t xml:space="preserve">2.56035923957825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50604820251465</t>
+    <t xml:space="preserve">2.50604867935181</t>
   </si>
   <si>
     <t xml:space="preserve">2.51380729675293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52156567573547</t>
+    <t xml:space="preserve">2.52156591415405</t>
   </si>
   <si>
     <t xml:space="preserve">2.54484176635742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48277258872986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49828958511353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42846155166626</t>
+    <t xml:space="preserve">2.48277235031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4982898235321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42846179008484</t>
   </si>
   <si>
     <t xml:space="preserve">2.32759928703308</t>
@@ -1253,7 +1256,7 @@
     <t xml:space="preserve">2.30432319641113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28104734420776</t>
+    <t xml:space="preserve">2.28104710578918</t>
   </si>
   <si>
     <t xml:space="preserve">2.31208181381226</t>
@@ -1262,19 +1265,19 @@
     <t xml:space="preserve">2.22673654556274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20346069335938</t>
+    <t xml:space="preserve">2.2034604549408</t>
   </si>
   <si>
     <t xml:space="preserve">2.19570183753967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2189781665802</t>
+    <t xml:space="preserve">2.21897792816162</t>
   </si>
   <si>
     <t xml:space="preserve">2.23449540138245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25777125358582</t>
+    <t xml:space="preserve">2.25777149200439</t>
   </si>
   <si>
     <t xml:space="preserve">2.1724259853363</t>
@@ -1286,7 +1289,7 @@
     <t xml:space="preserve">2.18794345855713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25001239776611</t>
+    <t xml:space="preserve">2.25001263618469</t>
   </si>
   <si>
     <t xml:space="preserve">2.12587380409241</t>
@@ -1301,10 +1304,10 @@
     <t xml:space="preserve">2.09483933448792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08708047866821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07932186126709</t>
+    <t xml:space="preserve">2.08708071708679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07932209968567</t>
   </si>
   <si>
     <t xml:space="preserve">2.07156324386597</t>
@@ -1331,7 +1334,7 @@
     <t xml:space="preserve">2.03276991844177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01725268363953</t>
+    <t xml:space="preserve">2.01725244522095</t>
   </si>
   <si>
     <t xml:space="preserve">2.02501130104065</t>
@@ -1343,13 +1346,13 @@
     <t xml:space="preserve">1.97070062160492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96294176578522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93966603279114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88535535335541</t>
+    <t xml:space="preserve">1.96294212341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93966579437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8853554725647</t>
   </si>
   <si>
     <t xml:space="preserve">1.87759685516357</t>
@@ -1358,7 +1361,7 @@
     <t xml:space="preserve">1.85432064533234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86983799934387</t>
+    <t xml:space="preserve">1.86983811855316</t>
   </si>
   <si>
     <t xml:space="preserve">1.79225146770477</t>
@@ -1367,10 +1370,10 @@
     <t xml:space="preserve">1.83880352973938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83104479312897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86207926273346</t>
+    <t xml:space="preserve">1.83104467391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86207938194275</t>
   </si>
   <si>
     <t xml:space="preserve">2.15690851211548</t>
@@ -1388,7 +1391,7 @@
     <t xml:space="preserve">1.97845911979675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99397659301758</t>
+    <t xml:space="preserve">1.99397683143616</t>
   </si>
   <si>
     <t xml:space="preserve">1.92414855957031</t>
@@ -1400,7 +1403,7 @@
     <t xml:space="preserve">1.80776870250702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75345826148987</t>
+    <t xml:space="preserve">1.75345802307129</t>
   </si>
   <si>
     <t xml:space="preserve">1.77673423290253</t>
@@ -1409,7 +1412,7 @@
     <t xml:space="preserve">1.74569952487946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82328605651855</t>
+    <t xml:space="preserve">1.82328617572784</t>
   </si>
   <si>
     <t xml:space="preserve">1.89311397075653</t>
@@ -1427,16 +1430,16 @@
     <t xml:space="preserve">2.05604600906372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26552987098694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24225401878357</t>
+    <t xml:space="preserve">2.26553010940552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24225378036499</t>
   </si>
   <si>
     <t xml:space="preserve">2.35087513923645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31984043121338</t>
+    <t xml:space="preserve">2.3198401927948</t>
   </si>
   <si>
     <t xml:space="preserve">2.3353579044342</t>
@@ -1448,28 +1451,28 @@
     <t xml:space="preserve">2.40518569946289</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38190984725952</t>
+    <t xml:space="preserve">2.3819100856781</t>
   </si>
   <si>
     <t xml:space="preserve">2.38966822624207</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39742732048035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41294479370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42070317268372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3663923740387</t>
+    <t xml:space="preserve">2.39742708206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41294455528259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42070341110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36639261245728</t>
   </si>
   <si>
     <t xml:space="preserve">2.34311676025391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3741512298584</t>
+    <t xml:space="preserve">2.37415099143982</t>
   </si>
   <si>
     <t xml:space="preserve">2.45173788070679</t>
@@ -1478,16 +1481,16 @@
     <t xml:space="preserve">2.47501397132874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55260038375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54447102546692</t>
+    <t xml:space="preserve">2.55260062217712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5444712638855</t>
   </si>
   <si>
     <t xml:space="preserve">2.52008318901062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49569535255432</t>
+    <t xml:space="preserve">2.4956955909729</t>
   </si>
   <si>
     <t xml:space="preserve">2.4387903213501</t>
@@ -1496,10 +1499,10 @@
     <t xml:space="preserve">2.45504903793335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47943663597107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48756623268127</t>
+    <t xml:space="preserve">2.47943687438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4875659942627</t>
   </si>
   <si>
     <t xml:space="preserve">2.50382447242737</t>
@@ -1508,16 +1511,16 @@
     <t xml:space="preserve">2.40627312660217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43066096305847</t>
+    <t xml:space="preserve">2.43066072463989</t>
   </si>
   <si>
     <t xml:space="preserve">2.42253160476685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36562657356262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3900146484375</t>
+    <t xml:space="preserve">2.3656268119812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39001441001892</t>
   </si>
   <si>
     <t xml:space="preserve">2.2843337059021</t>
@@ -1538,31 +1541,31 @@
     <t xml:space="preserve">2.26807498931885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.357497215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32498025894165</t>
+    <t xml:space="preserve">2.35749745368958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32498002052307</t>
   </si>
   <si>
     <t xml:space="preserve">2.34123873710632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37375593185425</t>
+    <t xml:space="preserve">2.37375617027283</t>
   </si>
   <si>
     <t xml:space="preserve">2.4631781578064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51195406913757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52821278572083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53634190559387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58511781692505</t>
+    <t xml:space="preserve">2.51195383071899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52821254730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53634214401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58511757850647</t>
   </si>
   <si>
     <t xml:space="preserve">2.59324717521667</t>
@@ -1571,7 +1574,7 @@
     <t xml:space="preserve">2.56072998046875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6013765335083</t>
+    <t xml:space="preserve">2.60137629508972</t>
   </si>
   <si>
     <t xml:space="preserve">2.60950541496277</t>
@@ -1580,10 +1583,7 @@
     <t xml:space="preserve">2.5688591003418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57698845863342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55260062217712</t>
+    <t xml:space="preserve">2.57698822021484</t>
   </si>
   <si>
     <t xml:space="preserve">2.4144024848938</t>
@@ -1592,13 +1592,13 @@
     <t xml:space="preserve">2.3331093788147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34936809539795</t>
+    <t xml:space="preserve">2.34936785697937</t>
   </si>
   <si>
     <t xml:space="preserve">2.39814376831055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47130727767944</t>
+    <t xml:space="preserve">2.47130751609802</t>
   </si>
   <si>
     <t xml:space="preserve">2.44691967964172</t>
@@ -1610,16 +1610,16 @@
     <t xml:space="preserve">2.29246306419373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3087215423584</t>
+    <t xml:space="preserve">2.30872130393982</t>
   </si>
   <si>
     <t xml:space="preserve">2.30059218406677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11361837387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18678188323975</t>
+    <t xml:space="preserve">2.11361813545227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18678212165833</t>
   </si>
   <si>
     <t xml:space="preserve">2.12987685203552</t>
@@ -1634,37 +1634,37 @@
     <t xml:space="preserve">2.1217474937439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04858374595642</t>
+    <t xml:space="preserve">2.048583984375</t>
   </si>
   <si>
     <t xml:space="preserve">1.89412713050842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65837752819061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66650676727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62586009502411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47140347957611</t>
+    <t xml:space="preserve">1.65837740898132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66650664806366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6258602142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4714035987854</t>
   </si>
   <si>
     <t xml:space="preserve">1.50392067432404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51205015182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61366641521454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55676114559174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5486319065094</t>
+    <t xml:space="preserve">1.51205003261566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61366629600525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55676090717316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54863178730011</t>
   </si>
   <si>
     <t xml:space="preserve">1.53237330913544</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">1.4957914352417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58521366119385</t>
+    <t xml:space="preserve">1.58521378040314</t>
   </si>
   <si>
     <t xml:space="preserve">1.60147225856781</t>
@@ -1688,19 +1688,19 @@
     <t xml:space="preserve">1.58114922046661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5689549446106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63398945331573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69089460372925</t>
+    <t xml:space="preserve">1.56895506381989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63398969173431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69089448451996</t>
   </si>
   <si>
     <t xml:space="preserve">1.60553693771362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62179565429688</t>
+    <t xml:space="preserve">1.62179553508759</t>
   </si>
   <si>
     <t xml:space="preserve">1.58927834033966</t>
@@ -1709,16 +1709,16 @@
     <t xml:space="preserve">1.61773085594177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67463600635529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70715320110321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76405835151672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73154103755951</t>
+    <t xml:space="preserve">1.67463612556458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7071533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76405823230743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73154127597809</t>
   </si>
   <si>
     <t xml:space="preserve">1.71528244018555</t>
@@ -1730,19 +1730,19 @@
     <t xml:space="preserve">1.6502480506897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74779963493347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75592911243439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77218747138977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78844630718231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82096362113953</t>
+    <t xml:space="preserve">1.74779975414276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75592887401581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77218759059906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7884464263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82096338272095</t>
   </si>
   <si>
     <t xml:space="preserve">1.87786865234375</t>
@@ -1751,70 +1751,70 @@
     <t xml:space="preserve">1.82909286022186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80470478534698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81283414363861</t>
+    <t xml:space="preserve">1.80470490455627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81283402442932</t>
   </si>
   <si>
     <t xml:space="preserve">1.79657554626465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7803168296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72341191768646</t>
+    <t xml:space="preserve">1.78031706809998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72341179847717</t>
   </si>
   <si>
     <t xml:space="preserve">1.73967039585114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6827654838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60960137844086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64211869239807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57708418369293</t>
+    <t xml:space="preserve">1.68276536464691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60960149765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64211881160736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57708442211151</t>
   </si>
   <si>
     <t xml:space="preserve">1.52830851078033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53643774986267</t>
+    <t xml:space="preserve">1.53643798828125</t>
   </si>
   <si>
     <t xml:space="preserve">1.49985611438751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48766219615936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48359751701355</t>
+    <t xml:space="preserve">1.48766195774078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48359739780426</t>
   </si>
   <si>
     <t xml:space="preserve">1.43075704574585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42262780666351</t>
+    <t xml:space="preserve">1.42262768745422</t>
   </si>
   <si>
     <t xml:space="preserve">1.41043376922607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40636909008026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43482148647308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41449844837189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36572241783142</t>
+    <t xml:space="preserve">1.40636897087097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43482172489166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4144983291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36572253704071</t>
   </si>
   <si>
     <t xml:space="preserve">1.33320534229279</t>
@@ -1829,13 +1829,13 @@
     <t xml:space="preserve">1.30475270748138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29255890846252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3088173866272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3372700214386</t>
+    <t xml:space="preserve">1.29255878925323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30881750583649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33727014064789</t>
   </si>
   <si>
     <t xml:space="preserve">1.32507598400116</t>
@@ -1847,7 +1847,7 @@
     <t xml:space="preserve">1.37385189533234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35352849960327</t>
+    <t xml:space="preserve">1.35352861881256</t>
   </si>
   <si>
     <t xml:space="preserve">1.39823985099792</t>
@@ -1856,10 +1856,10 @@
     <t xml:space="preserve">1.40230441093445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3860456943512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3901104927063</t>
+    <t xml:space="preserve">1.38604581356049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39011061191559</t>
   </si>
   <si>
     <t xml:space="preserve">1.37791657447815</t>
@@ -1868,7 +1868,7 @@
     <t xml:space="preserve">1.4673388004303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52017939090729</t>
+    <t xml:space="preserve">1.520179271698</t>
   </si>
   <si>
     <t xml:space="preserve">1.55269658565521</t>
@@ -1877,10 +1877,10 @@
     <t xml:space="preserve">1.54456722736359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49172675609589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5242440700531</t>
+    <t xml:space="preserve">1.49172687530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52424395084381</t>
   </si>
   <si>
     <t xml:space="preserve">1.50798523426056</t>
@@ -1892,13 +1892,13 @@
     <t xml:space="preserve">1.54050266742706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47953295707703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86973929405212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95103216171265</t>
+    <t xml:space="preserve">1.47953283786774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86973941326141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95103228092194</t>
   </si>
   <si>
     <t xml:space="preserve">2.07297158241272</t>
@@ -1910,13 +1910,13 @@
     <t xml:space="preserve">2.24368715286255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17865252494812</t>
+    <t xml:space="preserve">2.1786527633667</t>
   </si>
   <si>
     <t xml:space="preserve">2.14613556861877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05671286582947</t>
+    <t xml:space="preserve">2.05671334266663</t>
   </si>
   <si>
     <t xml:space="preserve">2.13800621032715</t>
@@ -1928,16 +1928,16 @@
     <t xml:space="preserve">2.21945142745972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23601460456848</t>
+    <t xml:space="preserve">2.2360143661499</t>
   </si>
   <si>
     <t xml:space="preserve">2.24429607391357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25257754325867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20288848876953</t>
+    <t xml:space="preserve">2.25257778167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20288825035095</t>
   </si>
   <si>
     <t xml:space="preserve">2.22773313522339</t>
@@ -1949,7 +1949,7 @@
     <t xml:space="preserve">2.17804384231567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34367442131042</t>
+    <t xml:space="preserve">2.343674659729</t>
   </si>
   <si>
     <t xml:space="preserve">2.36023759841919</t>
@@ -1958,7 +1958,7 @@
     <t xml:space="preserve">2.36851906776428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38508200645447</t>
+    <t xml:space="preserve">2.38508224487305</t>
   </si>
   <si>
     <t xml:space="preserve">2.40164518356323</t>
@@ -1967,7 +1967,7 @@
     <t xml:space="preserve">2.45133447647095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4761791229248</t>
+    <t xml:space="preserve">2.47617888450623</t>
   </si>
   <si>
     <t xml:space="preserve">2.4844605922699</t>
@@ -1979,7 +1979,7 @@
     <t xml:space="preserve">2.418208360672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39336371421814</t>
+    <t xml:space="preserve">2.39336347579956</t>
   </si>
   <si>
     <t xml:space="preserve">2.37680077552795</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">2.42648983001709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33539295196533</t>
+    <t xml:space="preserve">2.33539319038391</t>
   </si>
   <si>
     <t xml:space="preserve">2.32711148262024</t>
@@ -2027,7 +2027,7 @@
     <t xml:space="preserve">2.12835454940796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13663625717163</t>
+    <t xml:space="preserve">2.13663601875305</t>
   </si>
   <si>
     <t xml:space="preserve">2.18632531166077</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">2.08694696426392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10351014137268</t>
+    <t xml:space="preserve">2.1035099029541</t>
   </si>
   <si>
     <t xml:space="preserve">2.07038378715515</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">2.26914072036743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26085901260376</t>
+    <t xml:space="preserve">2.26085925102234</t>
   </si>
   <si>
     <t xml:space="preserve">2.4099268913269</t>
@@ -2072,10 +2072,10 @@
     <t xml:space="preserve">2.50930500030518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62524676322937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71634340286255</t>
+    <t xml:space="preserve">2.62524652481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71634364128113</t>
   </si>
   <si>
     <t xml:space="preserve">2.69978022575378</t>
@@ -2093,13 +2093,13 @@
     <t xml:space="preserve">3.01447892189026</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03104186058044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24636220932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2380805015564</t>
+    <t xml:space="preserve">3.03104162216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24636197090149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23808026313782</t>
   </si>
   <si>
     <t xml:space="preserve">3.22979879379272</t>
@@ -2108,7 +2108,7 @@
     <t xml:space="preserve">3.3043327331543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1221387386322</t>
+    <t xml:space="preserve">3.12213897705078</t>
   </si>
   <si>
     <t xml:space="preserve">3.1635468006134</t>
@@ -2129,7 +2129,7 @@
     <t xml:space="preserve">3.18010950088501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13042020797729</t>
+    <t xml:space="preserve">3.13042044639587</t>
   </si>
   <si>
     <t xml:space="preserve">3.10557556152344</t>
@@ -2141,7 +2141,7 @@
     <t xml:space="preserve">3.08901286125183</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07244968414307</t>
+    <t xml:space="preserve">3.07244944572449</t>
   </si>
   <si>
     <t xml:space="preserve">3.11385703086853</t>
@@ -2150,7 +2150,7 @@
     <t xml:space="preserve">3.08073139190674</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06416821479797</t>
+    <t xml:space="preserve">3.06416797637939</t>
   </si>
   <si>
     <t xml:space="preserve">3.254643201828</t>
@@ -2159,22 +2159,22 @@
     <t xml:space="preserve">3.09729433059692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93994474411011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02276015281677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04760479927063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0558865070343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15526509284973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03932332992554</t>
+    <t xml:space="preserve">2.93994498252869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02276039123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04760503768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05588674545288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15526485443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03932356834412</t>
   </si>
   <si>
     <t xml:space="preserve">2.98963403701782</t>
@@ -2189,7 +2189,7 @@
     <t xml:space="preserve">2.97307133674622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20495414733887</t>
+    <t xml:space="preserve">3.20495438575745</t>
   </si>
   <si>
     <t xml:space="preserve">3.27948784828186</t>
@@ -8683,7 +8683,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G209" t="s">
-        <v>16</v>
+        <v>136</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -8709,7 +8709,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G210" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -8761,7 +8761,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G212" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -8969,7 +8969,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G220" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -9177,7 +9177,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G228" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -9203,7 +9203,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G229" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -9229,7 +9229,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G230" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -9281,7 +9281,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G232" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -9307,7 +9307,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G233" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -9333,7 +9333,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G234" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -9359,7 +9359,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G235" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -9385,7 +9385,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G236" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -9411,7 +9411,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G237" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -9489,7 +9489,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G240" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -9515,7 +9515,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G241" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -9567,7 +9567,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G243" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -9645,7 +9645,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G246" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -9671,7 +9671,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G247" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -9697,7 +9697,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G248" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -9749,7 +9749,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G250" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -9775,7 +9775,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G251" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -9853,7 +9853,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G254" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -9931,7 +9931,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G257" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -9957,7 +9957,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G258" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -9983,7 +9983,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G259" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -10009,7 +10009,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G260" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -10035,7 +10035,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G261" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -10061,7 +10061,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G262" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -10087,7 +10087,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G263" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -10113,7 +10113,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G264" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -10139,7 +10139,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G265" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -10191,7 +10191,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G267" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -10217,7 +10217,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G268" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -10243,7 +10243,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G269" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -10269,7 +10269,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G270" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -10295,7 +10295,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G271" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -10321,7 +10321,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G272" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -10347,7 +10347,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G273" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -10373,7 +10373,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G274" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -10399,7 +10399,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G275" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -10425,7 +10425,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G276" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -10451,7 +10451,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G277" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -10477,7 +10477,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G278" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -10503,7 +10503,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G279" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -10529,7 +10529,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G280" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -10555,7 +10555,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G281" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -10581,7 +10581,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G282" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -10607,7 +10607,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G283" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -10633,7 +10633,7 @@
         <v>18.6299991607666</v>
       </c>
       <c r="G284" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -10659,7 +10659,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G285" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -10685,7 +10685,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G286" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -10711,7 +10711,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G287" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -10737,7 +10737,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G288" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -10763,7 +10763,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G289" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -10789,7 +10789,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G290" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -10815,7 +10815,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G291" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -10841,7 +10841,7 @@
         <v>19.25</v>
       </c>
       <c r="G292" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -10867,7 +10867,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G293" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -10893,7 +10893,7 @@
         <v>19.0300006866455</v>
       </c>
       <c r="G294" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -10919,7 +10919,7 @@
         <v>18.7099990844727</v>
       </c>
       <c r="G295" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -10945,7 +10945,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G296" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -10971,7 +10971,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G297" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -10997,7 +10997,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G298" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -11023,7 +11023,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G299" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -11049,7 +11049,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G300" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -11075,7 +11075,7 @@
         <v>20.1700000762939</v>
       </c>
       <c r="G301" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -11101,7 +11101,7 @@
         <v>20.25</v>
       </c>
       <c r="G302" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -11127,7 +11127,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G303" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -11153,7 +11153,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G304" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -11179,7 +11179,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G305" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -11205,7 +11205,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G306" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -11231,7 +11231,7 @@
         <v>20.2099990844727</v>
       </c>
       <c r="G307" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -11257,7 +11257,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G308" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -11283,7 +11283,7 @@
         <v>20.3700008392334</v>
       </c>
       <c r="G309" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -11309,7 +11309,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G310" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -11335,7 +11335,7 @@
         <v>20.25</v>
       </c>
       <c r="G311" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -11361,7 +11361,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G312" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -11387,7 +11387,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G313" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -11413,7 +11413,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G314" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -11439,7 +11439,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G315" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -11465,7 +11465,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G316" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -11491,7 +11491,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G317" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -11517,7 +11517,7 @@
         <v>20.9300003051758</v>
       </c>
       <c r="G318" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -11543,7 +11543,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G319" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -11569,7 +11569,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G320" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -11595,7 +11595,7 @@
         <v>20.4899997711182</v>
       </c>
       <c r="G321" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -11621,7 +11621,7 @@
         <v>20.4699993133545</v>
       </c>
       <c r="G322" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -11647,7 +11647,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G323" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -11673,7 +11673,7 @@
         <v>20.25</v>
       </c>
       <c r="G324" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -11699,7 +11699,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G325" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -11725,7 +11725,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G326" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -11751,7 +11751,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G327" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -11777,7 +11777,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G328" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -11803,7 +11803,7 @@
         <v>20.25</v>
       </c>
       <c r="G329" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -11829,7 +11829,7 @@
         <v>20</v>
       </c>
       <c r="G330" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -11855,7 +11855,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G331" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -11881,7 +11881,7 @@
         <v>20.2900009155273</v>
       </c>
       <c r="G332" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -11907,7 +11907,7 @@
         <v>20.7800006866455</v>
       </c>
       <c r="G333" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -11933,7 +11933,7 @@
         <v>21.0100002288818</v>
       </c>
       <c r="G334" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -11959,7 +11959,7 @@
         <v>21.6200008392334</v>
       </c>
       <c r="G335" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -11985,7 +11985,7 @@
         <v>21.6700000762939</v>
       </c>
       <c r="G336" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -12011,7 +12011,7 @@
         <v>21.7099990844727</v>
       </c>
       <c r="G337" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -12037,7 +12037,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G338" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -12063,7 +12063,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G339" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -12089,7 +12089,7 @@
         <v>22.1399993896484</v>
       </c>
       <c r="G340" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -12115,7 +12115,7 @@
         <v>22.0900001525879</v>
       </c>
       <c r="G341" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -12141,7 +12141,7 @@
         <v>22.0699996948242</v>
       </c>
       <c r="G342" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -12167,7 +12167,7 @@
         <v>23.5</v>
       </c>
       <c r="G343" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -12193,7 +12193,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G344" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -12219,7 +12219,7 @@
         <v>24.5</v>
       </c>
       <c r="G345" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -12245,7 +12245,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G346" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -12271,7 +12271,7 @@
         <v>26.5</v>
       </c>
       <c r="G347" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -12297,7 +12297,7 @@
         <v>26.75</v>
       </c>
       <c r="G348" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -12323,7 +12323,7 @@
         <v>25.9500007629395</v>
       </c>
       <c r="G349" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -12349,7 +12349,7 @@
         <v>26.3299999237061</v>
       </c>
       <c r="G350" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -12375,7 +12375,7 @@
         <v>25.6399993896484</v>
       </c>
       <c r="G351" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -12401,7 +12401,7 @@
         <v>24.5</v>
       </c>
       <c r="G352" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -12427,7 +12427,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G353" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -12453,7 +12453,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G354" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -12479,7 +12479,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G355" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -12505,7 +12505,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G356" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -12531,7 +12531,7 @@
         <v>25.7099990844727</v>
       </c>
       <c r="G357" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -12557,7 +12557,7 @@
         <v>25.5400009155273</v>
       </c>
       <c r="G358" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -12583,7 +12583,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G359" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -12609,7 +12609,7 @@
         <v>24.9899997711182</v>
       </c>
       <c r="G360" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -12635,7 +12635,7 @@
         <v>25.6200008392334</v>
       </c>
       <c r="G361" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -12661,7 +12661,7 @@
         <v>25.5300006866455</v>
       </c>
       <c r="G362" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -12687,7 +12687,7 @@
         <v>25.5799999237061</v>
       </c>
       <c r="G363" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -12713,7 +12713,7 @@
         <v>25.7800006866455</v>
       </c>
       <c r="G364" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -12739,7 +12739,7 @@
         <v>25.5900001525879</v>
       </c>
       <c r="G365" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -12765,7 +12765,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G366" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -12791,7 +12791,7 @@
         <v>25.2900009155273</v>
       </c>
       <c r="G367" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -12817,7 +12817,7 @@
         <v>25.5</v>
       </c>
       <c r="G368" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -12843,7 +12843,7 @@
         <v>25.5799999237061</v>
       </c>
       <c r="G369" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -12869,7 +12869,7 @@
         <v>25.4899997711182</v>
       </c>
       <c r="G370" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -12895,7 +12895,7 @@
         <v>25.6700000762939</v>
       </c>
       <c r="G371" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -12921,7 +12921,7 @@
         <v>25.8199996948242</v>
       </c>
       <c r="G372" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -12947,7 +12947,7 @@
         <v>25.5400009155273</v>
       </c>
       <c r="G373" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -12973,7 +12973,7 @@
         <v>25.3799991607666</v>
       </c>
       <c r="G374" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -12999,7 +12999,7 @@
         <v>25.1100006103516</v>
       </c>
       <c r="G375" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -13025,7 +13025,7 @@
         <v>25.3400001525879</v>
       </c>
       <c r="G376" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -13051,7 +13051,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G377" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -13077,7 +13077,7 @@
         <v>25.1700000762939</v>
       </c>
       <c r="G378" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -13103,7 +13103,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G379" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -13129,7 +13129,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G380" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -13155,7 +13155,7 @@
         <v>23.5200004577637</v>
       </c>
       <c r="G381" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -13181,7 +13181,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G382" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -13207,7 +13207,7 @@
         <v>23.4899997711182</v>
       </c>
       <c r="G383" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -13233,7 +13233,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G384" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -13259,7 +13259,7 @@
         <v>24.0100002288818</v>
       </c>
       <c r="G385" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -13285,7 +13285,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G386" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -13311,7 +13311,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G387" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -13337,7 +13337,7 @@
         <v>24.25</v>
       </c>
       <c r="G388" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -13363,7 +13363,7 @@
         <v>24.0499992370605</v>
       </c>
       <c r="G389" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -13389,7 +13389,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G390" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -13415,7 +13415,7 @@
         <v>24.2600002288818</v>
       </c>
       <c r="G391" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -13441,7 +13441,7 @@
         <v>24.0499992370605</v>
       </c>
       <c r="G392" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -13467,7 +13467,7 @@
         <v>24.3899993896484</v>
       </c>
       <c r="G393" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -13493,7 +13493,7 @@
         <v>24.4300003051758</v>
       </c>
       <c r="G394" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -13519,7 +13519,7 @@
         <v>24.5</v>
       </c>
       <c r="G395" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -13545,7 +13545,7 @@
         <v>24.5</v>
       </c>
       <c r="G396" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -13571,7 +13571,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G397" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -13597,7 +13597,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G398" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -13623,7 +13623,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G399" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -13649,7 +13649,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G400" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -13675,7 +13675,7 @@
         <v>24.5300006866455</v>
       </c>
       <c r="G401" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -13701,7 +13701,7 @@
         <v>24.4099998474121</v>
       </c>
       <c r="G402" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -13727,7 +13727,7 @@
         <v>25.2099990844727</v>
       </c>
       <c r="G403" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -13753,7 +13753,7 @@
         <v>25.4099998474121</v>
       </c>
       <c r="G404" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -13779,7 +13779,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G405" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -13805,7 +13805,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G406" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -13831,7 +13831,7 @@
         <v>26.1900005340576</v>
       </c>
       <c r="G407" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -13857,7 +13857,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G408" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -13883,7 +13883,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G409" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -13909,7 +13909,7 @@
         <v>25.6700000762939</v>
       </c>
       <c r="G410" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -13935,7 +13935,7 @@
         <v>25.5200004577637</v>
       </c>
       <c r="G411" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -13961,7 +13961,7 @@
         <v>25.5</v>
       </c>
       <c r="G412" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -13987,7 +13987,7 @@
         <v>25.0799999237061</v>
       </c>
       <c r="G413" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -14013,7 +14013,7 @@
         <v>25.1100006103516</v>
       </c>
       <c r="G414" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -14039,7 +14039,7 @@
         <v>25.0699996948242</v>
       </c>
       <c r="G415" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -14065,7 +14065,7 @@
         <v>25.1800003051758</v>
       </c>
       <c r="G416" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -14091,7 +14091,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G417" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -14117,7 +14117,7 @@
         <v>25.1499996185303</v>
       </c>
       <c r="G418" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -14143,7 +14143,7 @@
         <v>24.8299999237061</v>
       </c>
       <c r="G419" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -14169,7 +14169,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G420" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -14195,7 +14195,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G421" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -14221,7 +14221,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G422" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -14247,7 +14247,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G423" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -14273,7 +14273,7 @@
         <v>24.6700000762939</v>
       </c>
       <c r="G424" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -14299,7 +14299,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G425" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -14325,7 +14325,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G426" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -14351,7 +14351,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G427" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -14377,7 +14377,7 @@
         <v>25.0400009155273</v>
       </c>
       <c r="G428" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -14403,7 +14403,7 @@
         <v>24.8700008392334</v>
       </c>
       <c r="G429" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -14429,7 +14429,7 @@
         <v>24.6900005340576</v>
       </c>
       <c r="G430" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -14455,7 +14455,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G431" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -14481,7 +14481,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G432" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -14507,7 +14507,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G433" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -14533,7 +14533,7 @@
         <v>24.8500003814697</v>
       </c>
       <c r="G434" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -14559,7 +14559,7 @@
         <v>24.7299995422363</v>
       </c>
       <c r="G435" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -14585,7 +14585,7 @@
         <v>25</v>
       </c>
       <c r="G436" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -14611,7 +14611,7 @@
         <v>24.8099994659424</v>
       </c>
       <c r="G437" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -14637,7 +14637,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G438" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -14663,7 +14663,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G439" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -14689,7 +14689,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G440" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -14715,7 +14715,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G441" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -14741,7 +14741,7 @@
         <v>24.5100002288818</v>
       </c>
       <c r="G442" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -14767,7 +14767,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G443" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -14793,7 +14793,7 @@
         <v>24.4699993133545</v>
       </c>
       <c r="G444" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -14819,7 +14819,7 @@
         <v>24.5400009155273</v>
       </c>
       <c r="G445" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -14845,7 +14845,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G446" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -14871,7 +14871,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G447" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -14897,7 +14897,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G448" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -14923,7 +14923,7 @@
         <v>24.2299995422363</v>
       </c>
       <c r="G449" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -14949,7 +14949,7 @@
         <v>24.2900009155273</v>
       </c>
       <c r="G450" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -14975,7 +14975,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G451" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15001,7 +15001,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G452" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15027,7 +15027,7 @@
         <v>24.0599994659424</v>
       </c>
       <c r="G453" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15053,7 +15053,7 @@
         <v>24.1299991607666</v>
       </c>
       <c r="G454" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15079,7 +15079,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G455" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15105,7 +15105,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G456" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -15131,7 +15131,7 @@
         <v>24.25</v>
       </c>
       <c r="G457" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15157,7 +15157,7 @@
         <v>24.3400001525879</v>
       </c>
       <c r="G458" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15183,7 +15183,7 @@
         <v>24.2099990844727</v>
       </c>
       <c r="G459" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -15209,7 +15209,7 @@
         <v>24.25</v>
       </c>
       <c r="G460" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -15235,7 +15235,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G461" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15261,7 +15261,7 @@
         <v>24.3799991607666</v>
       </c>
       <c r="G462" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15287,7 +15287,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G463" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -15313,7 +15313,7 @@
         <v>25.2199993133545</v>
       </c>
       <c r="G464" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15339,7 +15339,7 @@
         <v>25.7299995422363</v>
       </c>
       <c r="G465" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15365,7 +15365,7 @@
         <v>25.4699993133545</v>
       </c>
       <c r="G466" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15391,7 +15391,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G467" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -15417,7 +15417,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G468" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15443,7 +15443,7 @@
         <v>25.8199996948242</v>
       </c>
       <c r="G469" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15469,7 +15469,7 @@
         <v>25.8600006103516</v>
       </c>
       <c r="G470" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15495,7 +15495,7 @@
         <v>26.1800003051758</v>
       </c>
       <c r="G471" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15521,7 +15521,7 @@
         <v>26.1399993896484</v>
       </c>
       <c r="G472" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15547,7 +15547,7 @@
         <v>26.0699996948242</v>
       </c>
       <c r="G473" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15573,7 +15573,7 @@
         <v>27.9400005340576</v>
       </c>
       <c r="G474" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -15599,7 +15599,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G475" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -15625,7 +15625,7 @@
         <v>26.8899993896484</v>
       </c>
       <c r="G476" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15651,7 +15651,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G477" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15677,7 +15677,7 @@
         <v>26.5599994659424</v>
       </c>
       <c r="G478" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -15703,7 +15703,7 @@
         <v>26.3799991607666</v>
       </c>
       <c r="G479" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15729,7 +15729,7 @@
         <v>26.4400005340576</v>
       </c>
       <c r="G480" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -15755,7 +15755,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G481" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -15781,7 +15781,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G482" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -15807,7 +15807,7 @@
         <v>26.1100006103516</v>
       </c>
       <c r="G483" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -15833,7 +15833,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G484" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -15859,7 +15859,7 @@
         <v>26.25</v>
       </c>
       <c r="G485" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -15885,7 +15885,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G486" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -15911,7 +15911,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G487" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -15937,7 +15937,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G488" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -15963,7 +15963,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G489" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -15989,7 +15989,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G490" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -16015,7 +16015,7 @@
         <v>27.5699996948242</v>
       </c>
       <c r="G491" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16041,7 +16041,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G492" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -16067,7 +16067,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G493" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16093,7 +16093,7 @@
         <v>27.6599998474121</v>
       </c>
       <c r="G494" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16119,7 +16119,7 @@
         <v>27.7099990844727</v>
       </c>
       <c r="G495" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -16145,7 +16145,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G496" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -16171,7 +16171,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G497" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -16197,7 +16197,7 @@
         <v>27.8400001525879</v>
       </c>
       <c r="G498" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -16223,7 +16223,7 @@
         <v>27.7700004577637</v>
       </c>
       <c r="G499" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16249,7 +16249,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G500" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -16275,7 +16275,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G501" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16301,7 +16301,7 @@
         <v>27.7199993133545</v>
       </c>
       <c r="G502" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16327,7 +16327,7 @@
         <v>27.5</v>
       </c>
       <c r="G503" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16353,7 +16353,7 @@
         <v>27.3700008392334</v>
       </c>
       <c r="G504" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16379,7 +16379,7 @@
         <v>27.3600006103516</v>
       </c>
       <c r="G505" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16405,7 +16405,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G506" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16431,7 +16431,7 @@
         <v>27.5699996948242</v>
       </c>
       <c r="G507" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16457,7 +16457,7 @@
         <v>27.5799999237061</v>
       </c>
       <c r="G508" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16483,7 +16483,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G509" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16509,7 +16509,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G510" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16535,7 +16535,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G511" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16561,7 +16561,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G512" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -16587,7 +16587,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G513" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -16613,7 +16613,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G514" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -16639,7 +16639,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G515" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -16665,7 +16665,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G516" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16691,7 +16691,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G517" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -16717,7 +16717,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G518" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -16743,7 +16743,7 @@
         <v>29.5</v>
       </c>
       <c r="G519" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -16769,7 +16769,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G520" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -16795,7 +16795,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G521" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -16821,7 +16821,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G522" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -16847,7 +16847,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G523" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -16873,7 +16873,7 @@
         <v>31</v>
       </c>
       <c r="G524" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -16899,7 +16899,7 @@
         <v>31.5</v>
       </c>
       <c r="G525" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -16925,7 +16925,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G526" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -16951,7 +16951,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G527" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -16977,7 +16977,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G528" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -17003,7 +17003,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G529" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -17029,7 +17029,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G530" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17055,7 +17055,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G531" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17081,7 +17081,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G532" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17107,7 +17107,7 @@
         <v>30.5</v>
       </c>
       <c r="G533" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17133,7 +17133,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G534" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -17159,7 +17159,7 @@
         <v>30</v>
       </c>
       <c r="G535" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17185,7 +17185,7 @@
         <v>30</v>
       </c>
       <c r="G536" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17211,7 +17211,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G537" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17237,7 +17237,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G538" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17263,7 +17263,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G539" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17289,7 +17289,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G540" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17315,7 +17315,7 @@
         <v>29</v>
       </c>
       <c r="G541" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17341,7 +17341,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G542" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17367,7 +17367,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G543" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17393,7 +17393,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G544" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17419,7 +17419,7 @@
         <v>30</v>
       </c>
       <c r="G545" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17445,7 +17445,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G546" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17471,7 +17471,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G547" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17497,7 +17497,7 @@
         <v>31.5</v>
       </c>
       <c r="G548" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17523,7 +17523,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G549" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17549,7 +17549,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G550" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17575,7 +17575,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G551" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17601,7 +17601,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G552" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17627,7 +17627,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G553" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17653,7 +17653,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G554" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17679,7 +17679,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G555" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17705,7 +17705,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G556" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17731,7 +17731,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G557" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -17757,7 +17757,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G558" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -17783,7 +17783,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G559" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -17809,7 +17809,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G560" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -17835,7 +17835,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G561" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -17861,7 +17861,7 @@
         <v>32.5</v>
       </c>
       <c r="G562" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -17887,7 +17887,7 @@
         <v>32</v>
       </c>
       <c r="G563" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -17913,7 +17913,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G564" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -17939,7 +17939,7 @@
         <v>32.5</v>
       </c>
       <c r="G565" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -17965,7 +17965,7 @@
         <v>33</v>
       </c>
       <c r="G566" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -17991,7 +17991,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G567" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18017,7 +18017,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G568" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18043,7 +18043,7 @@
         <v>32.5</v>
       </c>
       <c r="G569" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18069,7 +18069,7 @@
         <v>32.5</v>
       </c>
       <c r="G570" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18095,7 +18095,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G571" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18121,7 +18121,7 @@
         <v>32.5</v>
       </c>
       <c r="G572" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18147,7 +18147,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G573" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18173,7 +18173,7 @@
         <v>32.5</v>
       </c>
       <c r="G574" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18199,7 +18199,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G575" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18225,7 +18225,7 @@
         <v>32.5</v>
       </c>
       <c r="G576" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18251,7 +18251,7 @@
         <v>32.5</v>
       </c>
       <c r="G577" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18277,7 +18277,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G578" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18303,7 +18303,7 @@
         <v>32.5</v>
       </c>
       <c r="G579" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18329,7 +18329,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G580" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18355,7 +18355,7 @@
         <v>32.5</v>
       </c>
       <c r="G581" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18381,7 +18381,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G582" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18407,7 +18407,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G583" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18433,7 +18433,7 @@
         <v>33</v>
       </c>
       <c r="G584" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18459,7 +18459,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G585" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18485,7 +18485,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G586" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18511,7 +18511,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G587" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18537,7 +18537,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G588" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18563,7 +18563,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G589" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18589,7 +18589,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G590" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18615,7 +18615,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G591" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18641,7 +18641,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G592" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18667,7 +18667,7 @@
         <v>33</v>
       </c>
       <c r="G593" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18693,7 +18693,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G594" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18719,7 +18719,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G595" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18745,7 +18745,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G596" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -18771,7 +18771,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G597" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -18797,7 +18797,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G598" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -18823,7 +18823,7 @@
         <v>32.5</v>
       </c>
       <c r="G599" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -18849,7 +18849,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G600" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -18875,7 +18875,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G601" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -18901,7 +18901,7 @@
         <v>32</v>
       </c>
       <c r="G602" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -18927,7 +18927,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G603" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18953,7 +18953,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G604" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -18979,7 +18979,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G605" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19005,7 +19005,7 @@
         <v>32</v>
       </c>
       <c r="G606" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19031,7 +19031,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G607" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19057,7 +19057,7 @@
         <v>30</v>
       </c>
       <c r="G608" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19083,7 +19083,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G609" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19109,7 +19109,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G610" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19135,7 +19135,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G611" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19161,7 +19161,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G612" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19187,7 +19187,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G613" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19213,7 +19213,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G614" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19239,7 +19239,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G615" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19265,7 +19265,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G616" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19291,7 +19291,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G617" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19317,7 +19317,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G618" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19343,7 +19343,7 @@
         <v>28</v>
       </c>
       <c r="G619" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19369,7 +19369,7 @@
         <v>28</v>
       </c>
       <c r="G620" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19395,7 +19395,7 @@
         <v>28</v>
       </c>
       <c r="G621" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19421,7 +19421,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G622" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19447,7 +19447,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G623" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19473,7 +19473,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G624" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19499,7 +19499,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G625" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19525,7 +19525,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G626" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19551,7 +19551,7 @@
         <v>29</v>
       </c>
       <c r="G627" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19577,7 +19577,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G628" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19603,7 +19603,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G629" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19629,7 +19629,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G630" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19655,7 +19655,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G631" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19681,7 +19681,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G632" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19707,7 +19707,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G633" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19733,7 +19733,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G634" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19759,7 +19759,7 @@
         <v>27.5</v>
       </c>
       <c r="G635" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19785,7 +19785,7 @@
         <v>27</v>
       </c>
       <c r="G636" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19811,7 +19811,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G637" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19837,7 +19837,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G638" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19863,7 +19863,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G639" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19889,7 +19889,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G640" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19915,7 +19915,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G641" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -19941,7 +19941,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G642" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19967,7 +19967,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G643" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19993,7 +19993,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G644" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20019,7 +20019,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G645" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20045,7 +20045,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G646" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20071,7 +20071,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G647" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20097,7 +20097,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G648" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20123,7 +20123,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G649" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20149,7 +20149,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G650" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20175,7 +20175,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G651" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20201,7 +20201,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G652" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20227,7 +20227,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G653" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20253,7 +20253,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G654" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20279,7 +20279,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G655" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20305,7 +20305,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G656" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20331,7 +20331,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G657" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20357,7 +20357,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G658" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20383,7 +20383,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G659" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20409,7 +20409,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G660" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20435,7 +20435,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G661" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20461,7 +20461,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G662" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20487,7 +20487,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G663" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -20513,7 +20513,7 @@
         <v>27.5</v>
       </c>
       <c r="G664" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20539,7 +20539,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G665" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20565,7 +20565,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G666" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20591,7 +20591,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G667" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20617,7 +20617,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G668" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20643,7 +20643,7 @@
         <v>27</v>
       </c>
       <c r="G669" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20669,7 +20669,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G670" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20695,7 +20695,7 @@
         <v>27</v>
       </c>
       <c r="G671" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20721,7 +20721,7 @@
         <v>26</v>
       </c>
       <c r="G672" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20747,7 +20747,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G673" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20773,7 +20773,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G674" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20799,7 +20799,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G675" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20825,7 +20825,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G676" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20851,7 +20851,7 @@
         <v>25</v>
       </c>
       <c r="G677" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20877,7 +20877,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G678" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20903,7 +20903,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G679" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -20929,7 +20929,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G680" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -20955,7 +20955,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G681" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -20981,7 +20981,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G682" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21007,7 +21007,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G683" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21033,7 +21033,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G684" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21059,7 +21059,7 @@
         <v>24</v>
       </c>
       <c r="G685" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21085,7 +21085,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G686" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21111,7 +21111,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G687" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21137,7 +21137,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G688" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21163,7 +21163,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G689" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21189,7 +21189,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G690" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21215,7 +21215,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G691" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21241,7 +21241,7 @@
         <v>27</v>
       </c>
       <c r="G692" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21267,7 +21267,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G693" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21293,7 +21293,7 @@
         <v>26</v>
       </c>
       <c r="G694" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21319,7 +21319,7 @@
         <v>26</v>
       </c>
       <c r="G695" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21345,7 +21345,7 @@
         <v>26</v>
       </c>
       <c r="G696" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21371,7 +21371,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G697" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21397,7 +21397,7 @@
         <v>26</v>
       </c>
       <c r="G698" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21423,7 +21423,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G699" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21449,7 +21449,7 @@
         <v>26</v>
       </c>
       <c r="G700" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21475,7 +21475,7 @@
         <v>25.5</v>
       </c>
       <c r="G701" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21501,7 +21501,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G702" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -21527,7 +21527,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G703" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21553,7 +21553,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G704" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21579,7 +21579,7 @@
         <v>26</v>
       </c>
       <c r="G705" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21605,7 +21605,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G706" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21631,7 +21631,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G707" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21657,7 +21657,7 @@
         <v>25.5</v>
       </c>
       <c r="G708" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21683,7 +21683,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G709" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21709,7 +21709,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G710" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21735,7 +21735,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G711" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21761,7 +21761,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G712" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21787,7 +21787,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G713" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21813,7 +21813,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G714" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21839,7 +21839,7 @@
         <v>24</v>
       </c>
       <c r="G715" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21865,7 +21865,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G716" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21891,7 +21891,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G717" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21917,7 +21917,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G718" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -21943,7 +21943,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G719" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -21969,7 +21969,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G720" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21995,7 +21995,7 @@
         <v>22.5</v>
       </c>
       <c r="G721" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22021,7 +22021,7 @@
         <v>23.5</v>
       </c>
       <c r="G722" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22047,7 +22047,7 @@
         <v>23.5</v>
       </c>
       <c r="G723" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22073,7 +22073,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G724" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22099,7 +22099,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G725" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22125,7 +22125,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G726" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22151,7 +22151,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G727" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22177,7 +22177,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G728" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22203,7 +22203,7 @@
         <v>25</v>
       </c>
       <c r="G729" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22229,7 +22229,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G730" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22255,7 +22255,7 @@
         <v>28</v>
       </c>
       <c r="G731" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22281,7 +22281,7 @@
         <v>28.5</v>
       </c>
       <c r="G732" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22307,7 +22307,7 @@
         <v>27.5</v>
       </c>
       <c r="G733" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22333,7 +22333,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G734" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22359,7 +22359,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G735" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22385,7 +22385,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G736" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22411,7 +22411,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G737" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22437,7 +22437,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G738" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22463,7 +22463,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G739" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -22489,7 +22489,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G740" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -22515,7 +22515,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G741" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22541,7 +22541,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G742" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22567,7 +22567,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G743" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22593,7 +22593,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G744" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22619,7 +22619,7 @@
         <v>27.5</v>
       </c>
       <c r="G745" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22645,7 +22645,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G746" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22671,7 +22671,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G747" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22697,7 +22697,7 @@
         <v>27.5</v>
       </c>
       <c r="G748" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22723,7 +22723,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G749" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22749,7 +22749,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G750" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22775,7 +22775,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G751" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22801,7 +22801,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G752" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22827,7 +22827,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G753" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22853,7 +22853,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G754" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22879,7 +22879,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G755" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22905,7 +22905,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G756" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -22931,7 +22931,7 @@
         <v>26.5</v>
       </c>
       <c r="G757" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -22957,7 +22957,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G758" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -22983,7 +22983,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G759" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23009,7 +23009,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G760" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23035,7 +23035,7 @@
         <v>27</v>
       </c>
       <c r="G761" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23061,7 +23061,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G762" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23087,7 +23087,7 @@
         <v>27</v>
       </c>
       <c r="G763" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23113,7 +23113,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G764" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23139,7 +23139,7 @@
         <v>26.5</v>
       </c>
       <c r="G765" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23165,7 +23165,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G766" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23191,7 +23191,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G767" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23217,7 +23217,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G768" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23243,7 +23243,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G769" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23269,7 +23269,7 @@
         <v>28.5</v>
       </c>
       <c r="G770" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23295,7 +23295,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G771" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23321,7 +23321,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G772" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23347,7 +23347,7 @@
         <v>28</v>
       </c>
       <c r="G773" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23373,7 +23373,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G774" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23399,7 +23399,7 @@
         <v>28</v>
       </c>
       <c r="G775" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23425,7 +23425,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G776" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23451,7 +23451,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G777" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23477,7 +23477,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G778" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -23503,7 +23503,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G779" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -23529,7 +23529,7 @@
         <v>28.5</v>
       </c>
       <c r="G780" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23555,7 +23555,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G781" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23581,7 +23581,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G782" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23607,7 +23607,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G783" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23633,7 +23633,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G784" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23659,7 +23659,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G785" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23685,7 +23685,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G786" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23711,7 +23711,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G787" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23737,7 +23737,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G788" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23763,7 +23763,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G789" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23789,7 +23789,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G790" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23815,7 +23815,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G791" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23841,7 +23841,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G792" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23867,7 +23867,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G793" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23893,7 +23893,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G794" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23919,7 +23919,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G795" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -23945,7 +23945,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G796" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -23971,7 +23971,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G797" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -23997,7 +23997,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G798" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24023,7 +24023,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G799" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24049,7 +24049,7 @@
         <v>30</v>
       </c>
       <c r="G800" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24075,7 +24075,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G801" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24101,7 +24101,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G802" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24127,7 +24127,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G803" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24153,7 +24153,7 @@
         <v>31</v>
       </c>
       <c r="G804" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24179,7 +24179,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G805" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24205,7 +24205,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G806" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24231,7 +24231,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G807" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24257,7 +24257,7 @@
         <v>31</v>
       </c>
       <c r="G808" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24283,7 +24283,7 @@
         <v>31</v>
       </c>
       <c r="G809" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24309,7 +24309,7 @@
         <v>31</v>
       </c>
       <c r="G810" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24335,7 +24335,7 @@
         <v>31</v>
       </c>
       <c r="G811" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24361,7 +24361,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G812" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24387,7 +24387,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G813" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24413,7 +24413,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G814" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24439,7 +24439,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G815" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24465,7 +24465,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G816" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -24491,7 +24491,7 @@
         <v>31</v>
       </c>
       <c r="G817" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -24517,7 +24517,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G818" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24543,7 +24543,7 @@
         <v>31</v>
       </c>
       <c r="G819" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24569,7 +24569,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G820" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24595,7 +24595,7 @@
         <v>30.5</v>
       </c>
       <c r="G821" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24621,7 +24621,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G822" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24647,7 +24647,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G823" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24673,7 +24673,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G824" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24699,7 +24699,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G825" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24725,7 +24725,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G826" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24751,7 +24751,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G827" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24777,7 +24777,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G828" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24803,7 +24803,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G829" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24829,7 +24829,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G830" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24855,7 +24855,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G831" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24881,7 +24881,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G832" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24907,7 +24907,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G833" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -24933,7 +24933,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G834" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -24959,7 +24959,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G835" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -24985,7 +24985,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G836" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25011,7 +25011,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G837" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25037,7 +25037,7 @@
         <v>31</v>
       </c>
       <c r="G838" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25063,7 +25063,7 @@
         <v>31</v>
       </c>
       <c r="G839" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25089,7 +25089,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G840" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25115,7 +25115,7 @@
         <v>30</v>
       </c>
       <c r="G841" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25141,7 +25141,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G842" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25167,7 +25167,7 @@
         <v>30.5</v>
       </c>
       <c r="G843" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25193,7 +25193,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G844" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25219,7 +25219,7 @@
         <v>30.5</v>
       </c>
       <c r="G845" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25245,7 +25245,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G846" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25271,7 +25271,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G847" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25297,7 +25297,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G848" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25323,7 +25323,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G849" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25349,7 +25349,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G850" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25375,7 +25375,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G851" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25401,7 +25401,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G852" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -25427,7 +25427,7 @@
         <v>28</v>
       </c>
       <c r="G853" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -25453,7 +25453,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G854" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -25479,7 +25479,7 @@
         <v>28</v>
       </c>
       <c r="G855" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -25505,7 +25505,7 @@
         <v>27.5</v>
       </c>
       <c r="G856" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25531,7 +25531,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G857" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25557,7 +25557,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G858" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25583,7 +25583,7 @@
         <v>27.5</v>
       </c>
       <c r="G859" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25609,7 +25609,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G860" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25635,7 +25635,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G861" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25661,7 +25661,7 @@
         <v>28</v>
       </c>
       <c r="G862" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25687,7 +25687,7 @@
         <v>29</v>
       </c>
       <c r="G863" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25713,7 +25713,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G864" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25739,7 +25739,7 @@
         <v>29</v>
       </c>
       <c r="G865" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25765,7 +25765,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G866" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -25791,7 +25791,7 @@
         <v>29</v>
       </c>
       <c r="G867" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25817,7 +25817,7 @@
         <v>29</v>
       </c>
       <c r="G868" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -25843,7 +25843,7 @@
         <v>29</v>
       </c>
       <c r="G869" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -25869,7 +25869,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G870" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -25895,7 +25895,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G871" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25921,7 +25921,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G872" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -25947,7 +25947,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G873" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -25973,7 +25973,7 @@
         <v>30.5</v>
       </c>
       <c r="G874" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -25999,7 +25999,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G875" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -26025,7 +26025,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G876" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -26051,7 +26051,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G877" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -26077,7 +26077,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G878" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -26103,7 +26103,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G879" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26129,7 +26129,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G880" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -26155,7 +26155,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G881" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -26181,7 +26181,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G882" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -26207,7 +26207,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G883" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -26233,7 +26233,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G884" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -26259,7 +26259,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G885" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -26285,7 +26285,7 @@
         <v>31.5</v>
       </c>
       <c r="G886" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -26311,7 +26311,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G887" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -26337,7 +26337,7 @@
         <v>32</v>
       </c>
       <c r="G888" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -26363,7 +26363,7 @@
         <v>31.5</v>
       </c>
       <c r="G889" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -26389,7 +26389,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G890" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -26415,7 +26415,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G891" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -26441,7 +26441,7 @@
         <v>32</v>
       </c>
       <c r="G892" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -26467,7 +26467,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G893" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -26493,7 +26493,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G894" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -26519,7 +26519,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26545,7 +26545,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G896" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -26571,7 +26571,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G897" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -26597,7 +26597,7 @@
         <v>31</v>
       </c>
       <c r="G898" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -26623,7 +26623,7 @@
         <v>31</v>
       </c>
       <c r="G899" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -26649,7 +26649,7 @@
         <v>31</v>
       </c>
       <c r="G900" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -26675,7 +26675,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G901" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -26701,7 +26701,7 @@
         <v>31</v>
       </c>
       <c r="G902" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -26727,7 +26727,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G903" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -26753,7 +26753,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G904" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -26779,7 +26779,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G905" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -26805,7 +26805,7 @@
         <v>31</v>
       </c>
       <c r="G906" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -26831,7 +26831,7 @@
         <v>31</v>
       </c>
       <c r="G907" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -26857,7 +26857,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G908" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -26883,7 +26883,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G909" t="s">
-        <v>523</v>
+        <v>489</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -26909,7 +26909,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G910" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -26935,7 +26935,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G911" t="s">
-        <v>523</v>
+        <v>489</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -26961,7 +26961,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G912" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -26987,7 +26987,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G913" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -27013,7 +27013,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G914" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -27039,7 +27039,7 @@
         <v>30</v>
       </c>
       <c r="G915" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -27065,7 +27065,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G916" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -27117,7 +27117,7 @@
         <v>29</v>
       </c>
       <c r="G918" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -27169,7 +27169,7 @@
         <v>29</v>
       </c>
       <c r="G920" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -27247,7 +27247,7 @@
         <v>29</v>
       </c>
       <c r="G923" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -27273,7 +27273,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G924" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -27299,7 +27299,7 @@
         <v>29</v>
       </c>
       <c r="G925" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -27325,7 +27325,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G926" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -27351,7 +27351,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G927" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -27377,7 +27377,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G928" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -27429,7 +27429,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G930" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -27455,7 +27455,7 @@
         <v>30.5</v>
       </c>
       <c r="G931" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -27481,7 +27481,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G932" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -27585,7 +27585,7 @@
         <v>30</v>
       </c>
       <c r="G936" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -27663,7 +27663,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G939" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -27689,7 +27689,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G940" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -27715,7 +27715,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G941" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -27741,7 +27741,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G942" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -27767,7 +27767,7 @@
         <v>30</v>
       </c>
       <c r="G943" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -27793,7 +27793,7 @@
         <v>30</v>
       </c>
       <c r="G944" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -27845,7 +27845,7 @@
         <v>30</v>
       </c>
       <c r="G946" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -27871,7 +27871,7 @@
         <v>30.5</v>
       </c>
       <c r="G947" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -27897,7 +27897,7 @@
         <v>30.5</v>
       </c>
       <c r="G948" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -27923,7 +27923,7 @@
         <v>30</v>
       </c>
       <c r="G949" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -27975,7 +27975,7 @@
         <v>30</v>
       </c>
       <c r="G951" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -28027,7 +28027,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G953" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -28079,7 +28079,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G955" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -28105,7 +28105,7 @@
         <v>30</v>
       </c>
       <c r="G956" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -28131,7 +28131,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G957" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -28157,7 +28157,7 @@
         <v>30</v>
       </c>
       <c r="G958" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -28183,7 +28183,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G959" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -28209,7 +28209,7 @@
         <v>30</v>
       </c>
       <c r="G960" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -28235,7 +28235,7 @@
         <v>30</v>
       </c>
       <c r="G961" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -28261,7 +28261,7 @@
         <v>30</v>
       </c>
       <c r="G962" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -28287,7 +28287,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G963" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -28313,7 +28313,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G964" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -28339,7 +28339,7 @@
         <v>30</v>
       </c>
       <c r="G965" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -28365,7 +28365,7 @@
         <v>30</v>
       </c>
       <c r="G966" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -28417,7 +28417,7 @@
         <v>30</v>
       </c>
       <c r="G968" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -28443,7 +28443,7 @@
         <v>30</v>
       </c>
       <c r="G969" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -28521,7 +28521,7 @@
         <v>30</v>
       </c>
       <c r="G972" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -28573,7 +28573,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G974" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -28599,7 +28599,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G975" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -28651,7 +28651,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G977" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -28677,7 +28677,7 @@
         <v>31</v>
       </c>
       <c r="G978" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28703,7 +28703,7 @@
         <v>31</v>
       </c>
       <c r="G979" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -28729,7 +28729,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G980" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28755,7 +28755,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G981" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -28781,7 +28781,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G982" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -28807,7 +28807,7 @@
         <v>31</v>
       </c>
       <c r="G983" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -28833,7 +28833,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G984" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -28859,7 +28859,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G985" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28885,7 +28885,7 @@
         <v>31</v>
       </c>
       <c r="G986" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -28911,7 +28911,7 @@
         <v>31.5</v>
       </c>
       <c r="G987" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -28937,7 +28937,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G988" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -28963,7 +28963,7 @@
         <v>31.5</v>
       </c>
       <c r="G989" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -28989,7 +28989,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G990" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -29015,7 +29015,7 @@
         <v>31.5</v>
       </c>
       <c r="G991" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -29041,7 +29041,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G992" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -29067,7 +29067,7 @@
         <v>31.5</v>
       </c>
       <c r="G993" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -29093,7 +29093,7 @@
         <v>31.5</v>
       </c>
       <c r="G994" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -29119,7 +29119,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G995" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -29145,7 +29145,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G996" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -29171,7 +29171,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G997" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -29197,7 +29197,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G998" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -29223,7 +29223,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G999" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -29249,7 +29249,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1000" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -29275,7 +29275,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1001" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -29301,7 +29301,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1002" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -29327,7 +29327,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1003" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -29353,7 +29353,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1004" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -29379,7 +29379,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1005" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -29405,7 +29405,7 @@
         <v>31</v>
       </c>
       <c r="G1006" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -29431,7 +29431,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1007" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -29457,7 +29457,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1008" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -29483,7 +29483,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1009" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -29509,7 +29509,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1010" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -29535,7 +29535,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1011" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -29561,7 +29561,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1012" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -29587,7 +29587,7 @@
         <v>30.5</v>
       </c>
       <c r="G1013" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -29613,7 +29613,7 @@
         <v>30.5</v>
       </c>
       <c r="G1014" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -29665,7 +29665,7 @@
         <v>30.5</v>
       </c>
       <c r="G1016" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -29717,7 +29717,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1018" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -29743,7 +29743,7 @@
         <v>30</v>
       </c>
       <c r="G1019" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -29769,7 +29769,7 @@
         <v>30.5</v>
       </c>
       <c r="G1020" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -29795,7 +29795,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1021" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -29821,7 +29821,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1022" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -29847,7 +29847,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1023" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -29873,7 +29873,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1024" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -29899,7 +29899,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1025" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -29925,7 +29925,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1026" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -29951,7 +29951,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1027" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -29977,7 +29977,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1028" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -30003,7 +30003,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1029" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -30029,7 +30029,7 @@
         <v>30</v>
       </c>
       <c r="G1030" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -30055,7 +30055,7 @@
         <v>30</v>
       </c>
       <c r="G1031" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -30081,7 +30081,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1032" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -30263,7 +30263,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1039" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -30289,7 +30289,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1040" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -30315,7 +30315,7 @@
         <v>28</v>
       </c>
       <c r="G1041" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -30445,7 +30445,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1046" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -30497,7 +30497,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1048" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -30523,7 +30523,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1049" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -30575,7 +30575,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1051" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -30601,7 +30601,7 @@
         <v>28</v>
       </c>
       <c r="G1052" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -30679,7 +30679,7 @@
         <v>27.5</v>
       </c>
       <c r="G1055" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -36945,7 +36945,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1296" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -36971,7 +36971,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1297" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -37023,7 +37023,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1299" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -37075,7 +37075,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1301" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -37101,7 +37101,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1302" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -37127,7 +37127,7 @@
         <v>29</v>
       </c>
       <c r="G1303" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -37153,7 +37153,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1304" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -37179,7 +37179,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1305" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -37283,7 +37283,7 @@
         <v>28</v>
       </c>
       <c r="G1309" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -37309,7 +37309,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1310" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -37335,7 +37335,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1311" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -37413,7 +37413,7 @@
         <v>28</v>
       </c>
       <c r="G1314" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -37439,7 +37439,7 @@
         <v>28</v>
       </c>
       <c r="G1315" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -37465,7 +37465,7 @@
         <v>28</v>
       </c>
       <c r="G1316" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -37829,7 +37829,7 @@
         <v>27.5</v>
       </c>
       <c r="G1330" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -38011,7 +38011,7 @@
         <v>27.5</v>
       </c>
       <c r="G1337" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -68361,19 +68361,19 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45967.3336574074</v>
+        <v>45968.5628240741</v>
       </c>
       <c r="B2505" t="n">
-        <v>18</v>
+        <v>1555</v>
       </c>
       <c r="C2505" t="n">
-        <v>2.6800000667572</v>
+        <v>2.68499994277954</v>
       </c>
       <c r="D2505" t="n">
         <v>2.6800000667572</v>
       </c>
       <c r="E2505" t="n">
-        <v>2.6800000667572</v>
+        <v>2.68499994277954</v>
       </c>
       <c r="F2505" t="n">
         <v>2.6800000667572</v>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24616169929504</t>
+    <t xml:space="preserve">1.24616146087646</t>
   </si>
   <si>
     <t xml:space="preserve">AUTME.MI</t>
@@ -50,25 +50,25 @@
     <t xml:space="preserve">1.24330163002014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22256815433502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21541845798492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2218531370163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2147034406662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23615229129791</t>
+    <t xml:space="preserve">1.22256803512573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2154186964035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22185289859772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21470367908478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23615205287933</t>
   </si>
   <si>
     <t xml:space="preserve">1.21327364444733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20683908462524</t>
+    <t xml:space="preserve">1.20683896541595</t>
   </si>
   <si>
     <t xml:space="preserve">1.20111954212189</t>
@@ -77,91 +77,91 @@
     <t xml:space="preserve">1.20040464401245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1668016910553</t>
+    <t xml:space="preserve">1.16680181026459</t>
   </si>
   <si>
     <t xml:space="preserve">1.19468486309052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25688564777374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25045132637024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24687647819519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25116622447968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26475024223328</t>
+    <t xml:space="preserve">1.25688576698303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25045108795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2468763589859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25116634368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26475012302399</t>
   </si>
   <si>
     <t xml:space="preserve">1.23543727397919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22542786598206</t>
+    <t xml:space="preserve">1.22542774677277</t>
   </si>
   <si>
     <t xml:space="preserve">1.210413813591</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22113823890686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19396996498108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22685790061951</t>
+    <t xml:space="preserve">1.22113800048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19397008419037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22685766220093</t>
   </si>
   <si>
     <t xml:space="preserve">1.20469427108765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25831568241119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.265465259552</t>
+    <t xml:space="preserve">1.25831592082977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26546549797058</t>
   </si>
   <si>
     <t xml:space="preserve">1.25903058052063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26903986930847</t>
+    <t xml:space="preserve">1.26903998851776</t>
   </si>
   <si>
     <t xml:space="preserve">1.21684849262238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22828781604767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27404475212097</t>
+    <t xml:space="preserve">1.22828757762909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27404463291168</t>
   </si>
   <si>
     <t xml:space="preserve">1.26689493656158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27261471748352</t>
+    <t xml:space="preserve">1.27261459827423</t>
   </si>
   <si>
     <t xml:space="preserve">1.27189981937408</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2790492773056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26760995388031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25545597076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26260530948639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24830639362335</t>
+    <t xml:space="preserve">1.27904903888702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2676100730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25545585155487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26260542869568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24830627441406</t>
   </si>
   <si>
     <t xml:space="preserve">1.2490211725235</t>
@@ -173,37 +173,37 @@
     <t xml:space="preserve">1.23686707019806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23472225666046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23400735855103</t>
+    <t xml:space="preserve">1.23472237586975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23400712013245</t>
   </si>
   <si>
     <t xml:space="preserve">1.25225353240967</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26176810264587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26835501194</t>
+    <t xml:space="preserve">1.26176798343658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26835513114929</t>
   </si>
   <si>
     <t xml:space="preserve">1.27860140800476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27640569210052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27421009540558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27494204044342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26323175430298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27128267288208</t>
+    <t xml:space="preserve">1.2764059305191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27420997619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27494215965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26323199272156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27128255367279</t>
   </si>
   <si>
     <t xml:space="preserve">1.26689124107361</t>
@@ -221,34 +221,34 @@
     <t xml:space="preserve">1.27347815036774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27274644374847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26615941524506</t>
+    <t xml:space="preserve">1.2727462053299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26615929603577</t>
   </si>
   <si>
     <t xml:space="preserve">1.28226089477539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28811597824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28738403320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28299272060394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2639639377594</t>
+    <t xml:space="preserve">1.28811609745026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28738415241241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28299295902252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26396369934082</t>
   </si>
   <si>
     <t xml:space="preserve">1.24127531051636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2434709072113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22956514358521</t>
+    <t xml:space="preserve">1.24347102642059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22956526279449</t>
   </si>
   <si>
     <t xml:space="preserve">1.23468840122223</t>
@@ -257,22 +257,22 @@
     <t xml:space="preserve">1.22663772106171</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20687663555145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20760858058929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18565213680267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17833340167999</t>
+    <t xml:space="preserve">1.20687675476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20760869979858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18565225601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1783332824707</t>
   </si>
   <si>
     <t xml:space="preserve">1.18784785270691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16955077648163</t>
+    <t xml:space="preserve">1.16955065727234</t>
   </si>
   <si>
     <t xml:space="preserve">1.17101442813873</t>
@@ -281,136 +281,136 @@
     <t xml:space="preserve">1.17028260231018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1893116235733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22224628925323</t>
+    <t xml:space="preserve">1.18931150436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22224640846252</t>
   </si>
   <si>
     <t xml:space="preserve">1.22151446342468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23981165885925</t>
+    <t xml:space="preserve">1.23981153964996</t>
   </si>
   <si>
     <t xml:space="preserve">1.23907971382141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23834788799286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23542034626007</t>
+    <t xml:space="preserve">1.23834776878357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23542022705078</t>
   </si>
   <si>
     <t xml:space="preserve">1.2061448097229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23102879524231</t>
+    <t xml:space="preserve">1.2310289144516</t>
   </si>
   <si>
     <t xml:space="preserve">1.19736230373383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2171231508255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22297823429108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23322451114655</t>
+    <t xml:space="preserve">1.21712303161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22297811508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23322463035583</t>
   </si>
   <si>
     <t xml:space="preserve">1.23249268531799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22883319854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28518831729889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25884079933167</t>
+    <t xml:space="preserve">1.22883343696594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28518843650818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25884068012238</t>
   </si>
   <si>
     <t xml:space="preserve">1.3071448802948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29909420013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32324624061584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31665933132172</t>
+    <t xml:space="preserve">1.29909408092499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32324647903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3166595697403</t>
   </si>
   <si>
     <t xml:space="preserve">1.32763767242432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30348539352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31592738628387</t>
+    <t xml:space="preserve">1.30348551273346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31592750549316</t>
   </si>
   <si>
     <t xml:space="preserve">1.3181232213974</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29763042926788</t>
+    <t xml:space="preserve">1.29763031005859</t>
   </si>
   <si>
     <t xml:space="preserve">1.30275356769562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29982614517212</t>
+    <t xml:space="preserve">1.29982602596283</t>
   </si>
   <si>
     <t xml:space="preserve">1.28884792327881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29543483257294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30055797100067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29836225509644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29323923587799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29250729084015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30128979682922</t>
+    <t xml:space="preserve">1.29543471336365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30055809020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29836213588715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2932391166687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29250717163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30128991603851</t>
   </si>
   <si>
     <t xml:space="preserve">1.3056812286377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26908683776855</t>
+    <t xml:space="preserve">1.26908695697784</t>
   </si>
   <si>
     <t xml:space="preserve">1.26762306690216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24786221981049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25518107414246</t>
+    <t xml:space="preserve">1.24786233901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25518119335175</t>
   </si>
   <si>
     <t xml:space="preserve">1.2654275894165</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28006517887115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25810873508453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25005805492401</t>
+    <t xml:space="preserve">1.28006529808044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25810861587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25005781650543</t>
   </si>
   <si>
     <t xml:space="preserve">1.24054348468781</t>
@@ -422,7 +422,7 @@
     <t xml:space="preserve">1.24420285224915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23688399791718</t>
+    <t xml:space="preserve">1.23688387870789</t>
   </si>
   <si>
     <t xml:space="preserve">1.2420072555542</t>
@@ -431,10 +431,10 @@
     <t xml:space="preserve">1.23176074028015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20980441570282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21126794815063</t>
+    <t xml:space="preserve">1.20980429649353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21126806735992</t>
   </si>
   <si>
     <t xml:space="preserve">1.21858692169189</t>
@@ -449,22 +449,22 @@
     <t xml:space="preserve">1.18199276924133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21419560909271</t>
+    <t xml:space="preserve">1.214195728302</t>
   </si>
   <si>
     <t xml:space="preserve">1.19297099113464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19663047790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.220050573349</t>
+    <t xml:space="preserve">1.19663035869598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22005069255829</t>
   </si>
   <si>
     <t xml:space="preserve">1.21639132499695</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25957250595093</t>
+    <t xml:space="preserve">1.25957238674164</t>
   </si>
   <si>
     <t xml:space="preserve">1.27786946296692</t>
@@ -473,40 +473,40 @@
     <t xml:space="preserve">1.28592026233673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29470300674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29689860343933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31007242202759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32544207572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34081149101257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33349287509918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33422458171844</t>
+    <t xml:space="preserve">1.2947028875351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29689848423004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31007218360901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32544195652008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34081161022186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3334926366806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33422446250916</t>
   </si>
   <si>
     <t xml:space="preserve">1.3320289850235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33861577510834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33934783935547</t>
+    <t xml:space="preserve">1.33861589431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33934772014618</t>
   </si>
   <si>
     <t xml:space="preserve">1.34666657447815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34227538108826</t>
+    <t xml:space="preserve">1.34227526187897</t>
   </si>
   <si>
     <t xml:space="preserve">1.34007966518402</t>
@@ -515,16 +515,16 @@
     <t xml:space="preserve">1.32690572738647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3210506439209</t>
+    <t xml:space="preserve">1.32105076313019</t>
   </si>
   <si>
     <t xml:space="preserve">1.3459347486496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36130428314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36057233810425</t>
+    <t xml:space="preserve">1.36130440235138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36057257652283</t>
   </si>
   <si>
     <t xml:space="preserve">1.33276081085205</t>
@@ -533,37 +533,37 @@
     <t xml:space="preserve">1.34959411621094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33788394927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34373915195465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34520280361176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36349987983704</t>
+    <t xml:space="preserve">1.33788406848907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34373927116394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34520292282104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32910132408142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36350011825562</t>
   </si>
   <si>
     <t xml:space="preserve">1.36789131164551</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37667369842529</t>
+    <t xml:space="preserve">1.37667381763458</t>
   </si>
   <si>
     <t xml:space="preserve">1.38252902030945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39789867401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41253626346588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40668118000031</t>
+    <t xml:space="preserve">1.39789843559265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41253614425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40668129920959</t>
   </si>
   <si>
     <t xml:space="preserve">1.40814483165741</t>
@@ -572,43 +572,43 @@
     <t xml:space="preserve">1.40887677669525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40302169322968</t>
+    <t xml:space="preserve">1.40302193164825</t>
   </si>
   <si>
     <t xml:space="preserve">1.39277529716492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36935496330261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37886941432953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38911604881287</t>
+    <t xml:space="preserve">1.36935484409332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37886965274811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38911581039429</t>
   </si>
   <si>
     <t xml:space="preserve">1.40155792236328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49304330348969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47621023654938</t>
+    <t xml:space="preserve">1.49304354190826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4762099981308</t>
   </si>
   <si>
     <t xml:space="preserve">1.48206520080566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49157965183258</t>
+    <t xml:space="preserve">1.49157953262329</t>
   </si>
   <si>
     <t xml:space="preserve">1.50328981876373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46742749214172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45864486694336</t>
+    <t xml:space="preserve">1.46742725372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45864498615265</t>
   </si>
   <si>
     <t xml:space="preserve">1.47913753986359</t>
@@ -617,79 +617,79 @@
     <t xml:space="preserve">1.49523913860321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49084782600403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48792028427124</t>
+    <t xml:space="preserve">1.49084770679474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48792016506195</t>
   </si>
   <si>
     <t xml:space="preserve">1.52744209766388</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50987684726715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53256511688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52963769435883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53183329105377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52817392349243</t>
+    <t xml:space="preserve">1.50987672805786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53256523609161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52963757514954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53183341026306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52817380428314</t>
   </si>
   <si>
     <t xml:space="preserve">1.51499998569489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4996303319931</t>
+    <t xml:space="preserve">1.49963045120239</t>
   </si>
   <si>
     <t xml:space="preserve">1.498166680336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48572444915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47108697891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48426079750061</t>
+    <t xml:space="preserve">1.48572480678558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47108685970306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4842609167099</t>
   </si>
   <si>
     <t xml:space="preserve">1.46376812458038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45498538017273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48499286174774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52085506916046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53768837451935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58233332633972</t>
+    <t xml:space="preserve">1.45498549938202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48499298095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52085494995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53768849372864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58233344554901</t>
   </si>
   <si>
     <t xml:space="preserve">1.63126361370087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63427484035492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64857745170593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63578045368195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66664397716522</t>
+    <t xml:space="preserve">1.63427460193634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64857757091522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63578033447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6666442155838</t>
   </si>
   <si>
     <t xml:space="preserve">1.66288030147552</t>
@@ -698,10 +698,10 @@
     <t xml:space="preserve">1.66137480735779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76902163028717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8081659078598</t>
+    <t xml:space="preserve">1.76902174949646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80816578865051</t>
   </si>
   <si>
     <t xml:space="preserve">1.84429907798767</t>
@@ -710,34 +710,34 @@
     <t xml:space="preserve">1.9165655374527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99485409259796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01367330551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95345151424408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98205709457397</t>
+    <t xml:space="preserve">1.99485397338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01367378234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95345115661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98205673694611</t>
   </si>
   <si>
     <t xml:space="preserve">1.93011546134949</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83376026153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90301585197449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90452122688293</t>
+    <t xml:space="preserve">1.83376038074493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9030157327652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90452098846436</t>
   </si>
   <si>
     <t xml:space="preserve">1.9120489358902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9353848695755</t>
+    <t xml:space="preserve">1.93538475036621</t>
   </si>
   <si>
     <t xml:space="preserve">1.92258763313293</t>
@@ -749,49 +749,49 @@
     <t xml:space="preserve">1.88118505477905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92860984802246</t>
+    <t xml:space="preserve">1.92861008644104</t>
   </si>
   <si>
     <t xml:space="preserve">1.92183494567871</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92559885978699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94065427780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9263516664505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90376830101013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91957664489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91882371902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93237364292145</t>
+    <t xml:space="preserve">1.9255987405777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94065451622009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92635154724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90376842021942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91957676410675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91882395744324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93237400054932</t>
   </si>
   <si>
     <t xml:space="preserve">1.94366538524628</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91054320335388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89021837711334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90753221511841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89699339866638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89473497867584</t>
+    <t xml:space="preserve">1.91054332256317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89021849632263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9075323343277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89699327945709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89473509788513</t>
   </si>
   <si>
     <t xml:space="preserve">1.87742114067078</t>
@@ -800,97 +800,97 @@
     <t xml:space="preserve">1.86010730266571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77052700519562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7976268529892</t>
+    <t xml:space="preserve">1.7705272436142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79762709140778</t>
   </si>
   <si>
     <t xml:space="preserve">1.76826882362366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79461586475372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80741333961487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83074915409088</t>
+    <t xml:space="preserve">1.79461598396301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80741322040558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83074939250946</t>
   </si>
   <si>
     <t xml:space="preserve">1.84881567955017</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82547974586487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81042408943176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82623243331909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8360184431076</t>
+    <t xml:space="preserve">1.82547962665558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81042420864105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82623255252838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83601856231689</t>
   </si>
   <si>
     <t xml:space="preserve">1.83902966976166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85257959365845</t>
+    <t xml:space="preserve">1.85257947444916</t>
   </si>
   <si>
     <t xml:space="preserve">1.82171595096588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84806299209595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84655749797821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83752393722534</t>
+    <t xml:space="preserve">1.84806311130524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8465576171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83752417564392</t>
   </si>
   <si>
     <t xml:space="preserve">1.89774596691132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.912801861763</t>
+    <t xml:space="preserve">1.91280150413513</t>
   </si>
   <si>
     <t xml:space="preserve">1.97377645969391</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97151827812195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93086802959442</t>
+    <t xml:space="preserve">1.97151815891266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93086838722229</t>
   </si>
   <si>
     <t xml:space="preserve">1.93613767623901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92108225822449</t>
+    <t xml:space="preserve">1.9210821390152</t>
   </si>
   <si>
     <t xml:space="preserve">1.88796019554138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88720738887787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89548754692078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89322948455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86914074420929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85860204696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85634362697601</t>
+    <t xml:space="preserve">1.88720726966858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89548778533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89322924613953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86914050579071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85860180854797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85634326934814</t>
   </si>
   <si>
     <t xml:space="preserve">1.85709631443024</t>
@@ -899,37 +899,37 @@
     <t xml:space="preserve">1.85182690620422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86688208580017</t>
+    <t xml:space="preserve">1.86688232421875</t>
   </si>
   <si>
     <t xml:space="preserve">1.88494896888733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87215197086334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87064623832703</t>
+    <t xml:space="preserve">1.87215185165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87064635753632</t>
   </si>
   <si>
     <t xml:space="preserve">1.86161291599274</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88193774223328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86763489246368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87365746498108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86537683010101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84505212306976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84204065799713</t>
+    <t xml:space="preserve">1.88193798065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86763501167297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87365734577179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86537659168243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84505176544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84204077720642</t>
   </si>
   <si>
     <t xml:space="preserve">1.84731030464172</t>
@@ -938,25 +938,25 @@
     <t xml:space="preserve">1.84279358386993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81795179843903</t>
+    <t xml:space="preserve">1.81795191764832</t>
   </si>
   <si>
     <t xml:space="preserve">1.82397401332855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82849073410034</t>
+    <t xml:space="preserve">1.82849097251892</t>
   </si>
   <si>
     <t xml:space="preserve">1.81569373607635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82021033763885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81117677688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81644654273987</t>
+    <t xml:space="preserve">1.82021009922028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81117713451385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81644630432129</t>
   </si>
   <si>
     <t xml:space="preserve">1.81418800354004</t>
@@ -965,22 +965,22 @@
     <t xml:space="preserve">1.83526575565338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83225464820862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82246828079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85032141208649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89849889278412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93689024448395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91731822490692</t>
+    <t xml:space="preserve">1.83225452899933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82246851921082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85032153129578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89849877357483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93689036369324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91731810569763</t>
   </si>
   <si>
     <t xml:space="preserve">1.97979855537415</t>
@@ -989,52 +989,52 @@
     <t xml:space="preserve">1.9647433757782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94667661190033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97076535224915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96775424480438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96248471736908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10325384140015</t>
+    <t xml:space="preserve">1.94667637348175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97076523303986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96775436401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96248483657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10325360298157</t>
   </si>
   <si>
     <t xml:space="preserve">2.04378437995911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02421259880066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98732626438141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99937093257904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98582053184509</t>
+    <t xml:space="preserve">2.02421236038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98732650279999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99937057495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98582065105438</t>
   </si>
   <si>
     <t xml:space="preserve">1.99033737182617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96624875068665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99861776828766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96549582481384</t>
+    <t xml:space="preserve">1.96624863147736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99861764907837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96549594402313</t>
   </si>
   <si>
     <t xml:space="preserve">1.97603487968445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98280990123749</t>
+    <t xml:space="preserve">1.98280966281891</t>
   </si>
   <si>
     <t xml:space="preserve">2.02496528625488</t>
@@ -1052,19 +1052,19 @@
     <t xml:space="preserve">2.08217597007751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08593988418579</t>
+    <t xml:space="preserve">2.08594012260437</t>
   </si>
   <si>
     <t xml:space="preserve">2.07765936851501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09572625160217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09045648574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11153435707092</t>
+    <t xml:space="preserve">2.09572577476501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09045672416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11153411865234</t>
   </si>
   <si>
     <t xml:space="preserve">2.10024261474609</t>
@@ -1079,10 +1079,10 @@
     <t xml:space="preserve">2.06034564971924</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05959296226501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05884003639221</t>
+    <t xml:space="preserve">2.05959272384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05883979797363</t>
   </si>
   <si>
     <t xml:space="preserve">2.07615375518799</t>
@@ -1103,19 +1103,19 @@
     <t xml:space="preserve">2.19057559967041</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21315860748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1755199432373</t>
+    <t xml:space="preserve">2.21315884590149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17552018165588</t>
   </si>
   <si>
     <t xml:space="preserve">2.16799235343933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20563125610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22068691253662</t>
+    <t xml:space="preserve">2.20563101768494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22068667411804</t>
   </si>
   <si>
     <t xml:space="preserve">2.31101989746094</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">2.37124156951904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32607531547546</t>
+    <t xml:space="preserve">2.32607507705688</t>
   </si>
   <si>
     <t xml:space="preserve">2.28843665122986</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">2.25832533836365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19810366630554</t>
+    <t xml:space="preserve">2.19810342788696</t>
   </si>
   <si>
     <t xml:space="preserve">2.18304800987244</t>
@@ -1172,100 +1172,103 @@
     <t xml:space="preserve">2.5443799495697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61965751647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46157503128052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49168586730957</t>
+    <t xml:space="preserve">2.61965727806091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46157455444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49168562889099</t>
   </si>
   <si>
     <t xml:space="preserve">2.46910238265991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40135288238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43146395683289</t>
+    <t xml:space="preserve">2.40135264396667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43146371841431</t>
   </si>
   <si>
     <t xml:space="preserve">2.47663044929504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44651937484741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40888023376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48415780067444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45404672622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41640830039978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50674152374268</t>
+    <t xml:space="preserve">2.44651913642883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40888047218323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48415803909302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45404696464539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4164080619812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50674104690552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52932453155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57587671279907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59139394760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58363509178162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56035923957825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50604844093323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51380729675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52156591415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54484176635742</t>
   </si>
   <si>
     <t xml:space="preserve">2.5293242931366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57587623596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59139370918274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5836353302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56035900115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50604867935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51380729675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52156591415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54484176635742</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.48277235031128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4982898235321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42846155166626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3275990486145</t>
+    <t xml:space="preserve">2.49828958511353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42846179008484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32759928703308</t>
   </si>
   <si>
     <t xml:space="preserve">2.30432343482971</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28104686737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31208157539368</t>
+    <t xml:space="preserve">2.28104710578918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31208181381226</t>
   </si>
   <si>
     <t xml:space="preserve">2.22673654556274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2034604549408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19570183753967</t>
+    <t xml:space="preserve">2.20346069335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19570207595825</t>
   </si>
   <si>
     <t xml:space="preserve">2.21897792816162</t>
@@ -1280,7 +1283,7 @@
     <t xml:space="preserve">2.1724259853363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11811542510986</t>
+    <t xml:space="preserve">2.11811518669128</t>
   </si>
   <si>
     <t xml:space="preserve">2.18794322013855</t>
@@ -1289,10 +1292,10 @@
     <t xml:space="preserve">2.25001263618469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12587380409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10259819030762</t>
+    <t xml:space="preserve">2.12587404251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10259795188904</t>
   </si>
   <si>
     <t xml:space="preserve">2.13363265991211</t>
@@ -1307,7 +1310,7 @@
     <t xml:space="preserve">2.07932186126709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07156324386597</t>
+    <t xml:space="preserve">2.07156348228455</t>
   </si>
   <si>
     <t xml:space="preserve">2.0405285358429</t>
@@ -1316,7 +1319,7 @@
     <t xml:space="preserve">2.14139127731323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1646671295166</t>
+    <t xml:space="preserve">2.16466736793518</t>
   </si>
   <si>
     <t xml:space="preserve">2.14914989471436</t>
@@ -1325,34 +1328,34 @@
     <t xml:space="preserve">2.18018460273743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29656434059143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03276991844177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01725244522095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02501153945923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0094940662384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97070074081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96294212341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93966591358185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88535523414612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87759685516357</t>
+    <t xml:space="preserve">2.29656457901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03277015686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01725268363953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02501130104065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00949382781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97070062160492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9629420042038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93966615200043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8853554725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.877596616745</t>
   </si>
   <si>
     <t xml:space="preserve">1.85432076454163</t>
@@ -1361,16 +1364,16 @@
     <t xml:space="preserve">1.86983799934387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79225134849548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83880352973938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83104491233826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86207950115204</t>
+    <t xml:space="preserve">1.79225122928619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8388032913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83104467391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86207938194275</t>
   </si>
   <si>
     <t xml:space="preserve">2.15690875053406</t>
@@ -1379,64 +1382,64 @@
     <t xml:space="preserve">2.06380462646484</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04828715324402</t>
+    <t xml:space="preserve">2.0482873916626</t>
   </si>
   <si>
     <t xml:space="preserve">2.0017352104187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97845935821533</t>
+    <t xml:space="preserve">1.97845947742462</t>
   </si>
   <si>
     <t xml:space="preserve">1.99397671222687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92414844036102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84656202793121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80776858329773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.753457903862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77673411369324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74569940567017</t>
+    <t xml:space="preserve">1.9241486787796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84656190872192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80776870250702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75345814228058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77673423290253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74569928646088</t>
   </si>
   <si>
     <t xml:space="preserve">1.82328605651855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89311397075653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91639018058777</t>
+    <t xml:space="preserve">1.89311408996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91638994216919</t>
   </si>
   <si>
     <t xml:space="preserve">2.2112193107605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11035656929016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05604600906372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26553010940552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24225378036499</t>
+    <t xml:space="preserve">2.11035680770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05604577064514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26552987098694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24225401878357</t>
   </si>
   <si>
     <t xml:space="preserve">2.35087513923645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31984090805054</t>
+    <t xml:space="preserve">2.31984066963196</t>
   </si>
   <si>
     <t xml:space="preserve">2.3353579044342</t>
@@ -1460,28 +1463,28 @@
     <t xml:space="preserve">2.41294455528259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42070341110229</t>
+    <t xml:space="preserve">2.42070317268372</t>
   </si>
   <si>
     <t xml:space="preserve">2.36639261245728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34311652183533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37415099143982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45173811912537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47501397132874</t>
+    <t xml:space="preserve">2.34311676025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37415146827698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45173788070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47501373291016</t>
   </si>
   <si>
     <t xml:space="preserve">2.55260062217712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5444712638855</t>
+    <t xml:space="preserve">2.54447102546692</t>
   </si>
   <si>
     <t xml:space="preserve">2.5200834274292</t>
@@ -1496,13 +1499,13 @@
     <t xml:space="preserve">2.45504903793335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47943687438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4875659942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50382471084595</t>
+    <t xml:space="preserve">2.47943663597107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48756623268127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50382447242737</t>
   </si>
   <si>
     <t xml:space="preserve">2.40627312660217</t>
@@ -1511,7 +1514,7 @@
     <t xml:space="preserve">2.43066096305847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42253160476685</t>
+    <t xml:space="preserve">2.42253184318542</t>
   </si>
   <si>
     <t xml:space="preserve">2.36562657356262</t>
@@ -1529,25 +1532,25 @@
     <t xml:space="preserve">2.2274284362793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23555779457092</t>
+    <t xml:space="preserve">2.23555755615234</t>
   </si>
   <si>
     <t xml:space="preserve">2.25181651115417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26807522773743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35749745368958</t>
+    <t xml:space="preserve">2.26807475090027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.357497215271</t>
   </si>
   <si>
     <t xml:space="preserve">2.32498025894165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34123873710632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37375617027283</t>
+    <t xml:space="preserve">2.34123849868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37375593185425</t>
   </si>
   <si>
     <t xml:space="preserve">2.4631781578064</t>
@@ -1556,19 +1559,19 @@
     <t xml:space="preserve">2.51195383071899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52821254730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53634214401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58511781692505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59324717521667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56072974205017</t>
+    <t xml:space="preserve">2.52821278572083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53634190559387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58511757850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5932469367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56072998046875</t>
   </si>
   <si>
     <t xml:space="preserve">2.60137629508972</t>
@@ -1589,13 +1592,13 @@
     <t xml:space="preserve">2.3331093788147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34936785697937</t>
+    <t xml:space="preserve">2.34936809539795</t>
   </si>
   <si>
     <t xml:space="preserve">2.39814376831055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47130751609802</t>
+    <t xml:space="preserve">2.47130727767944</t>
   </si>
   <si>
     <t xml:space="preserve">2.44691967964172</t>
@@ -1604,7 +1607,7 @@
     <t xml:space="preserve">2.38188529014587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29246282577515</t>
+    <t xml:space="preserve">2.29246306419373</t>
   </si>
   <si>
     <t xml:space="preserve">2.30872130393982</t>
@@ -1616,7 +1619,7 @@
     <t xml:space="preserve">2.11361837387085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18678212165833</t>
+    <t xml:space="preserve">2.18678188323975</t>
   </si>
   <si>
     <t xml:space="preserve">2.12987685203552</t>
@@ -1634,16 +1637,16 @@
     <t xml:space="preserve">2.048583984375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89412689208984</t>
+    <t xml:space="preserve">1.89412701129913</t>
   </si>
   <si>
     <t xml:space="preserve">1.65837728977203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66650664806366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6258602142334</t>
+    <t xml:space="preserve">1.66650676727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62586009502411</t>
   </si>
   <si>
     <t xml:space="preserve">1.47140347957611</t>
@@ -1652,40 +1655,40 @@
     <t xml:space="preserve">1.50392067432404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51204991340637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61366617679596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55676102638245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54863178730011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53237330913544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4957914352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58521378040314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6014723777771</t>
+    <t xml:space="preserve">1.51205015182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61366641521454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55676114559174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54863166809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53237318992615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49579131603241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58521366119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60147249698639</t>
   </si>
   <si>
     <t xml:space="preserve">1.5730197429657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56082582473755</t>
+    <t xml:space="preserve">1.56082606315613</t>
   </si>
   <si>
     <t xml:space="preserve">1.58114922046661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56895506381989</t>
+    <t xml:space="preserve">1.5689549446106</t>
   </si>
   <si>
     <t xml:space="preserve">1.63398957252502</t>
@@ -1697,10 +1700,10 @@
     <t xml:space="preserve">1.60553693771362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62179553508759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58927822113037</t>
+    <t xml:space="preserve">1.62179565429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58927810192108</t>
   </si>
   <si>
     <t xml:space="preserve">1.61773085594177</t>
@@ -1709,13 +1712,13 @@
     <t xml:space="preserve">1.67463600635529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7071533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76405847072601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73154127597809</t>
+    <t xml:space="preserve">1.70715320110321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76405835151672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73154103755951</t>
   </si>
   <si>
     <t xml:space="preserve">1.71528244018555</t>
@@ -1727,16 +1730,16 @@
     <t xml:space="preserve">1.6502480506897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74779975414276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75592887401581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77218759059906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78844618797302</t>
+    <t xml:space="preserve">1.74779963493347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75592911243439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77218747138977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78844630718231</t>
   </si>
   <si>
     <t xml:space="preserve">1.82096338272095</t>
@@ -1745,52 +1748,52 @@
     <t xml:space="preserve">1.87786865234375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82909286022186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8047046661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81283402442932</t>
+    <t xml:space="preserve">1.82909274101257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80470502376556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81283390522003</t>
   </si>
   <si>
     <t xml:space="preserve">1.79657554626465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78031706809998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72341179847717</t>
+    <t xml:space="preserve">1.7803168296814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72341191768646</t>
   </si>
   <si>
     <t xml:space="preserve">1.73967039585114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68276536464691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60960149765015</t>
+    <t xml:space="preserve">1.6827654838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60960137844086</t>
   </si>
   <si>
     <t xml:space="preserve">1.64211893081665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57708442211151</t>
+    <t xml:space="preserve">1.57708418369293</t>
   </si>
   <si>
     <t xml:space="preserve">1.52830851078033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53643786907196</t>
+    <t xml:space="preserve">1.53643774986267</t>
   </si>
   <si>
     <t xml:space="preserve">1.49985611438751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48766195774078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48359739780426</t>
+    <t xml:space="preserve">1.48766207695007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48359751701355</t>
   </si>
   <si>
     <t xml:space="preserve">1.43075704574585</t>
@@ -1799,19 +1802,19 @@
     <t xml:space="preserve">1.42262768745422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41043365001678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40636897087097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43482160568237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4144983291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36572253704071</t>
+    <t xml:space="preserve">1.41043376922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40636909008026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43482148647308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41449844837189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36572241783142</t>
   </si>
   <si>
     <t xml:space="preserve">1.3332052230835</t>
@@ -1826,25 +1829,25 @@
     <t xml:space="preserve">1.30475270748138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29255890846252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3088173866272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33727025985718</t>
+    <t xml:space="preserve">1.29255878925323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30881750583649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33727014064789</t>
   </si>
   <si>
     <t xml:space="preserve">1.32507598400116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34946393966675</t>
+    <t xml:space="preserve">1.34946405887604</t>
   </si>
   <si>
     <t xml:space="preserve">1.37385189533234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35352849960327</t>
+    <t xml:space="preserve">1.35352861881256</t>
   </si>
   <si>
     <t xml:space="preserve">1.39823985099792</t>
@@ -1853,10 +1856,10 @@
     <t xml:space="preserve">1.40230441093445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3860456943512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39011061191559</t>
+    <t xml:space="preserve">1.38604581356049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3901104927063</t>
   </si>
   <si>
     <t xml:space="preserve">1.37791657447815</t>
@@ -1868,16 +1871,16 @@
     <t xml:space="preserve">1.52017939090729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55269646644592</t>
+    <t xml:space="preserve">1.55269658565521</t>
   </si>
   <si>
     <t xml:space="preserve">1.54456722736359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49172687530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52424395084381</t>
+    <t xml:space="preserve">1.49172675609589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5242440700531</t>
   </si>
   <si>
     <t xml:space="preserve">1.50798523426056</t>
@@ -1886,49 +1889,46 @@
     <t xml:space="preserve">1.51611471176147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54050278663635</t>
+    <t xml:space="preserve">1.54050266742706</t>
   </si>
   <si>
     <t xml:space="preserve">1.47953283786774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86973941326141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95103228092194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0729718208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25994563102722</t>
+    <t xml:space="preserve">1.86973929405212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95103216171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07297158241272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25994539260864</t>
   </si>
   <si>
     <t xml:space="preserve">2.24368715286255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1786527633667</t>
+    <t xml:space="preserve">2.17865252494812</t>
   </si>
   <si>
     <t xml:space="preserve">2.14613556861877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05671310424805</t>
+    <t xml:space="preserve">2.05671286582947</t>
   </si>
   <si>
     <t xml:space="preserve">2.13800597190857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21116971969604</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.21116995811462</t>
   </si>
   <si>
     <t xml:space="preserve">2.21945142745972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2360143661499</t>
+    <t xml:space="preserve">2.23601460456848</t>
   </si>
   <si>
     <t xml:space="preserve">2.24429607391357</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">2.25257754325867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20288825035095</t>
+    <t xml:space="preserve">2.20288848876953</t>
   </si>
   <si>
     <t xml:space="preserve">2.22773313522339</t>
@@ -1955,10 +1955,10 @@
     <t xml:space="preserve">2.36023759841919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36851930618286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38508224487305</t>
+    <t xml:space="preserve">2.36851906776428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38508200645447</t>
   </si>
   <si>
     <t xml:space="preserve">2.40164518356323</t>
@@ -1970,16 +1970,16 @@
     <t xml:space="preserve">2.4761791229248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4844605922699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49274230003357</t>
+    <t xml:space="preserve">2.48446035385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49274206161499</t>
   </si>
   <si>
     <t xml:space="preserve">2.418208360672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39336347579956</t>
+    <t xml:space="preserve">2.39336371421814</t>
   </si>
   <si>
     <t xml:space="preserve">2.37680077552795</t>
@@ -2006,7 +2006,7 @@
     <t xml:space="preserve">2.31882977485657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31054830551147</t>
+    <t xml:space="preserve">2.31054854393005</t>
   </si>
   <si>
     <t xml:space="preserve">2.35195589065552</t>
@@ -2021,22 +2021,22 @@
     <t xml:space="preserve">2.27742218971252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1531994342804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12835454940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13663601875305</t>
+    <t xml:space="preserve">2.15319919586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12835478782654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13663625717163</t>
   </si>
   <si>
     <t xml:space="preserve">2.18632531166077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08694672584534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10351014137268</t>
+    <t xml:space="preserve">2.08694696426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1035099029541</t>
   </si>
   <si>
     <t xml:space="preserve">2.07038378715515</t>
@@ -2054,10 +2054,10 @@
     <t xml:space="preserve">2.26914072036743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26085925102234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40992665290833</t>
+    <t xml:space="preserve">2.26085901260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4099268913269</t>
   </si>
   <si>
     <t xml:space="preserve">2.46789741516113</t>
@@ -2069,19 +2069,19 @@
     <t xml:space="preserve">2.52586841583252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50930500030518</t>
+    <t xml:space="preserve">2.50930523872375</t>
   </si>
   <si>
     <t xml:space="preserve">2.62524676322937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71634340286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69978022575378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81572198867798</t>
+    <t xml:space="preserve">2.71634364128113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69978046417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81572222709656</t>
   </si>
   <si>
     <t xml:space="preserve">2.84884834289551</t>
@@ -2093,13 +2093,13 @@
     <t xml:space="preserve">3.01447892189026</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03104162216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24636197090149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23808002471924</t>
+    <t xml:space="preserve">3.03104186058044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24636220932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2380805015564</t>
   </si>
   <si>
     <t xml:space="preserve">3.22979879379272</t>
@@ -2108,13 +2108,13 @@
     <t xml:space="preserve">3.3043327331543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12213897705078</t>
+    <t xml:space="preserve">3.1221387386322</t>
   </si>
   <si>
     <t xml:space="preserve">3.16354656219482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17182803153992</t>
+    <t xml:space="preserve">3.17182779312134</t>
   </si>
   <si>
     <t xml:space="preserve">3.21323561668396</t>
@@ -2132,16 +2132,16 @@
     <t xml:space="preserve">3.13042020797729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10557579994202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13870215415955</t>
+    <t xml:space="preserve">3.1055760383606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13870191574097</t>
   </si>
   <si>
     <t xml:space="preserve">3.08901286125183</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07244944572449</t>
+    <t xml:space="preserve">3.07244920730591</t>
   </si>
   <si>
     <t xml:space="preserve">3.11385703086853</t>
@@ -2153,28 +2153,28 @@
     <t xml:space="preserve">3.06416797637939</t>
   </si>
   <si>
-    <t xml:space="preserve">3.254643201828</t>
+    <t xml:space="preserve">3.25464367866516</t>
   </si>
   <si>
     <t xml:space="preserve">3.09729433059692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93994522094727</t>
+    <t xml:space="preserve">2.93994498252869</t>
   </si>
   <si>
     <t xml:space="preserve">3.02276039123535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04760503768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05588674545288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15526485443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03932356834412</t>
+    <t xml:space="preserve">3.04760479927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0558865070343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15526461601257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03932332992554</t>
   </si>
   <si>
     <t xml:space="preserve">2.98963403701782</t>
@@ -2189,13 +2189,13 @@
     <t xml:space="preserve">2.97307133674622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20495438575745</t>
+    <t xml:space="preserve">3.20495414733887</t>
   </si>
   <si>
     <t xml:space="preserve">3.27948784828186</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27120637893677</t>
+    <t xml:space="preserve">3.27120661735535</t>
   </si>
   <si>
     <t xml:space="preserve">3.29605102539062</t>
@@ -2225,13 +2225,13 @@
     <t xml:space="preserve">4.95042657852173</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01585054397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5828595161438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36477899551392</t>
+    <t xml:space="preserve">5.01585006713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58285999298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36477947235107</t>
   </si>
   <si>
     <t xml:space="preserve">5.05946683883667</t>
@@ -2240,7 +2240,7 @@
     <t xml:space="preserve">4.97223424911499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14669847488403</t>
+    <t xml:space="preserve">5.14669895172119</t>
   </si>
   <si>
     <t xml:space="preserve">5.08127450942993</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">5.19031476974487</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21212291717529</t>
+    <t xml:space="preserve">5.21212244033813</t>
   </si>
   <si>
     <t xml:space="preserve">5.27754688262939</t>
@@ -2264,22 +2264,22 @@
     <t xml:space="preserve">5.47381925582886</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53924369812012</t>
+    <t xml:space="preserve">5.53924322128296</t>
   </si>
   <si>
     <t xml:space="preserve">5.45201110839844</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43020343780518</t>
+    <t xml:space="preserve">5.43020296096802</t>
   </si>
   <si>
     <t xml:space="preserve">5.40839529037476</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3429708480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38658714294434</t>
+    <t xml:space="preserve">5.34297132492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38658761978149</t>
   </si>
   <si>
     <t xml:space="preserve">5.32116317749023</t>
@@ -2291,19 +2291,19 @@
     <t xml:space="preserve">5.99721240997314</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82591819763184</t>
+    <t xml:space="preserve">6.82591772079468</t>
   </si>
   <si>
     <t xml:space="preserve">7.32750272750854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93495798110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78230237960815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73868560791016</t>
+    <t xml:space="preserve">6.93495845794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.782301902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73868608474731</t>
   </si>
   <si>
     <t xml:space="preserve">6.67326211929321</t>
@@ -2318,7 +2318,7 @@
     <t xml:space="preserve">6.25890922546387</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32433319091797</t>
+    <t xml:space="preserve">6.32433271408081</t>
   </si>
   <si>
     <t xml:space="preserve">6.23710107803345</t>
@@ -2333,28 +2333,28 @@
     <t xml:space="preserve">6.41156530380249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62964534759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76049423217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02219104766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0658073425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04399871826172</t>
+    <t xml:space="preserve">6.62964582443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76049375534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0221905708313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06580686569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04399824142456</t>
   </si>
   <si>
     <t xml:space="preserve">7.0876145362854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45835208892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52377510070801</t>
+    <t xml:space="preserve">7.45835161209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52377557754517</t>
   </si>
   <si>
     <t xml:space="preserve">7.78547239303589</t>
@@ -2366,7 +2366,7 @@
     <t xml:space="preserve">8.19982433319092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11259365081787</t>
+    <t xml:space="preserve">8.11259269714355</t>
   </si>
   <si>
     <t xml:space="preserve">8.37428951263428</t>
@@ -18875,7 +18875,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G601" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -18901,7 +18901,7 @@
         <v>32</v>
       </c>
       <c r="G602" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -18927,7 +18927,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G603" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18953,7 +18953,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G604" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19005,7 +19005,7 @@
         <v>32</v>
       </c>
       <c r="G606" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19031,7 +19031,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G607" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19057,7 +19057,7 @@
         <v>30</v>
       </c>
       <c r="G608" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19083,7 +19083,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G609" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19109,7 +19109,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G610" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19135,7 +19135,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G611" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19161,7 +19161,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G612" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19187,7 +19187,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G613" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19213,7 +19213,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G614" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19239,7 +19239,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G615" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19265,7 +19265,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G616" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19291,7 +19291,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G617" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19317,7 +19317,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G618" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19343,7 +19343,7 @@
         <v>28</v>
       </c>
       <c r="G619" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19369,7 +19369,7 @@
         <v>28</v>
       </c>
       <c r="G620" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19395,7 +19395,7 @@
         <v>28</v>
       </c>
       <c r="G621" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19421,7 +19421,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G622" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19447,7 +19447,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G623" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19473,7 +19473,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G624" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19499,7 +19499,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G625" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19525,7 +19525,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G626" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19551,7 +19551,7 @@
         <v>29</v>
       </c>
       <c r="G627" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19577,7 +19577,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G628" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19603,7 +19603,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G629" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19629,7 +19629,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G630" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19655,7 +19655,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G631" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19681,7 +19681,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G632" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19707,7 +19707,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G633" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19733,7 +19733,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G634" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19759,7 +19759,7 @@
         <v>27.5</v>
       </c>
       <c r="G635" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19785,7 +19785,7 @@
         <v>27</v>
       </c>
       <c r="G636" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19811,7 +19811,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G637" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19837,7 +19837,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G638" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19863,7 +19863,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G639" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19889,7 +19889,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G640" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19915,7 +19915,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G641" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -19941,7 +19941,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G642" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19967,7 +19967,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G643" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19993,7 +19993,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G644" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20019,7 +20019,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G645" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20045,7 +20045,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G646" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20071,7 +20071,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G647" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20097,7 +20097,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G648" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20123,7 +20123,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G649" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20149,7 +20149,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G650" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20175,7 +20175,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G651" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20201,7 +20201,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G652" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20227,7 +20227,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G653" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20253,7 +20253,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G654" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20279,7 +20279,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G655" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20305,7 +20305,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G656" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20331,7 +20331,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G657" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20357,7 +20357,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G658" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20383,7 +20383,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G659" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20409,7 +20409,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G660" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20435,7 +20435,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G661" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20461,7 +20461,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G662" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20487,7 +20487,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G663" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -20513,7 +20513,7 @@
         <v>27.5</v>
       </c>
       <c r="G664" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20539,7 +20539,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G665" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20565,7 +20565,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G666" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20591,7 +20591,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G667" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20617,7 +20617,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G668" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20643,7 +20643,7 @@
         <v>27</v>
       </c>
       <c r="G669" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20669,7 +20669,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G670" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20695,7 +20695,7 @@
         <v>27</v>
       </c>
       <c r="G671" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20721,7 +20721,7 @@
         <v>26</v>
       </c>
       <c r="G672" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20747,7 +20747,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G673" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20773,7 +20773,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G674" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20799,7 +20799,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G675" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20825,7 +20825,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G676" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20851,7 +20851,7 @@
         <v>25</v>
       </c>
       <c r="G677" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20877,7 +20877,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G678" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20903,7 +20903,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G679" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -20929,7 +20929,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G680" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -20955,7 +20955,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G681" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -20981,7 +20981,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G682" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21007,7 +21007,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G683" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21033,7 +21033,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G684" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21059,7 +21059,7 @@
         <v>24</v>
       </c>
       <c r="G685" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21085,7 +21085,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G686" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21111,7 +21111,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G687" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21137,7 +21137,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G688" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21163,7 +21163,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G689" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21189,7 +21189,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G690" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21215,7 +21215,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G691" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21241,7 +21241,7 @@
         <v>27</v>
       </c>
       <c r="G692" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21267,7 +21267,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G693" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21293,7 +21293,7 @@
         <v>26</v>
       </c>
       <c r="G694" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21319,7 +21319,7 @@
         <v>26</v>
       </c>
       <c r="G695" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21345,7 +21345,7 @@
         <v>26</v>
       </c>
       <c r="G696" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21371,7 +21371,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G697" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21397,7 +21397,7 @@
         <v>26</v>
       </c>
       <c r="G698" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21423,7 +21423,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G699" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21449,7 +21449,7 @@
         <v>26</v>
       </c>
       <c r="G700" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21475,7 +21475,7 @@
         <v>25.5</v>
       </c>
       <c r="G701" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21501,7 +21501,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G702" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -21527,7 +21527,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G703" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21553,7 +21553,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G704" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21579,7 +21579,7 @@
         <v>26</v>
       </c>
       <c r="G705" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21605,7 +21605,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G706" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21631,7 +21631,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G707" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21657,7 +21657,7 @@
         <v>25.5</v>
       </c>
       <c r="G708" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21683,7 +21683,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G709" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21709,7 +21709,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G710" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21735,7 +21735,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G711" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21761,7 +21761,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G712" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21787,7 +21787,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G713" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21813,7 +21813,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G714" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21839,7 +21839,7 @@
         <v>24</v>
       </c>
       <c r="G715" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21865,7 +21865,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G716" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21891,7 +21891,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G717" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21917,7 +21917,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G718" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -21943,7 +21943,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G719" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -21969,7 +21969,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G720" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21995,7 +21995,7 @@
         <v>22.5</v>
       </c>
       <c r="G721" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22021,7 +22021,7 @@
         <v>23.5</v>
       </c>
       <c r="G722" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22047,7 +22047,7 @@
         <v>23.5</v>
       </c>
       <c r="G723" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22073,7 +22073,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G724" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22099,7 +22099,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G725" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22125,7 +22125,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G726" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22151,7 +22151,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G727" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22177,7 +22177,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G728" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22203,7 +22203,7 @@
         <v>25</v>
       </c>
       <c r="G729" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22229,7 +22229,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G730" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22255,7 +22255,7 @@
         <v>28</v>
       </c>
       <c r="G731" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22281,7 +22281,7 @@
         <v>28.5</v>
       </c>
       <c r="G732" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22307,7 +22307,7 @@
         <v>27.5</v>
       </c>
       <c r="G733" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22333,7 +22333,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G734" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22359,7 +22359,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G735" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22385,7 +22385,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G736" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22411,7 +22411,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G737" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22437,7 +22437,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G738" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22463,7 +22463,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G739" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -22489,7 +22489,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G740" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -22515,7 +22515,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G741" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22541,7 +22541,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G742" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22567,7 +22567,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G743" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22593,7 +22593,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G744" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22619,7 +22619,7 @@
         <v>27.5</v>
       </c>
       <c r="G745" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22645,7 +22645,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G746" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22671,7 +22671,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G747" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22697,7 +22697,7 @@
         <v>27.5</v>
       </c>
       <c r="G748" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22723,7 +22723,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G749" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22749,7 +22749,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G750" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22775,7 +22775,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G751" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22801,7 +22801,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G752" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22827,7 +22827,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G753" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22853,7 +22853,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G754" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22879,7 +22879,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G755" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22905,7 +22905,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G756" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -22931,7 +22931,7 @@
         <v>26.5</v>
       </c>
       <c r="G757" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -22957,7 +22957,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G758" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -22983,7 +22983,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G759" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23009,7 +23009,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G760" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23035,7 +23035,7 @@
         <v>27</v>
       </c>
       <c r="G761" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23061,7 +23061,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G762" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23087,7 +23087,7 @@
         <v>27</v>
       </c>
       <c r="G763" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23113,7 +23113,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G764" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23139,7 +23139,7 @@
         <v>26.5</v>
       </c>
       <c r="G765" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23165,7 +23165,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G766" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23191,7 +23191,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G767" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23217,7 +23217,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G768" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23243,7 +23243,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G769" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23269,7 +23269,7 @@
         <v>28.5</v>
       </c>
       <c r="G770" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23295,7 +23295,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G771" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23321,7 +23321,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G772" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23347,7 +23347,7 @@
         <v>28</v>
       </c>
       <c r="G773" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23373,7 +23373,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G774" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23399,7 +23399,7 @@
         <v>28</v>
       </c>
       <c r="G775" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23425,7 +23425,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G776" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23451,7 +23451,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G777" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23477,7 +23477,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G778" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -23503,7 +23503,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G779" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -23529,7 +23529,7 @@
         <v>28.5</v>
       </c>
       <c r="G780" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23555,7 +23555,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G781" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23581,7 +23581,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G782" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23607,7 +23607,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G783" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23633,7 +23633,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G784" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23659,7 +23659,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G785" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23685,7 +23685,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G786" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23711,7 +23711,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G787" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23737,7 +23737,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G788" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23763,7 +23763,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G789" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23789,7 +23789,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G790" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23815,7 +23815,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G791" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23841,7 +23841,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G792" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23867,7 +23867,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G793" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23893,7 +23893,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G794" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23919,7 +23919,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G795" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -23945,7 +23945,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G796" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -23971,7 +23971,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G797" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -23997,7 +23997,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G798" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24023,7 +24023,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G799" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24049,7 +24049,7 @@
         <v>30</v>
       </c>
       <c r="G800" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24075,7 +24075,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G801" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24101,7 +24101,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G802" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24127,7 +24127,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G803" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24153,7 +24153,7 @@
         <v>31</v>
       </c>
       <c r="G804" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24179,7 +24179,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G805" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24205,7 +24205,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G806" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24231,7 +24231,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G807" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24257,7 +24257,7 @@
         <v>31</v>
       </c>
       <c r="G808" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24283,7 +24283,7 @@
         <v>31</v>
       </c>
       <c r="G809" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24309,7 +24309,7 @@
         <v>31</v>
       </c>
       <c r="G810" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24335,7 +24335,7 @@
         <v>31</v>
       </c>
       <c r="G811" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24361,7 +24361,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G812" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24387,7 +24387,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G813" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24413,7 +24413,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G814" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24439,7 +24439,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G815" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24465,7 +24465,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G816" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -24491,7 +24491,7 @@
         <v>31</v>
       </c>
       <c r="G817" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -24517,7 +24517,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G818" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24543,7 +24543,7 @@
         <v>31</v>
       </c>
       <c r="G819" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24569,7 +24569,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G820" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24595,7 +24595,7 @@
         <v>30.5</v>
       </c>
       <c r="G821" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24621,7 +24621,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G822" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24647,7 +24647,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G823" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24673,7 +24673,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G824" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24699,7 +24699,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G825" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24725,7 +24725,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G826" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24751,7 +24751,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G827" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24777,7 +24777,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G828" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24803,7 +24803,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G829" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24829,7 +24829,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G830" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24855,7 +24855,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G831" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24881,7 +24881,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G832" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24907,7 +24907,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G833" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -24933,7 +24933,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G834" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -24959,7 +24959,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G835" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -24985,7 +24985,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G836" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25011,7 +25011,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G837" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25037,7 +25037,7 @@
         <v>31</v>
       </c>
       <c r="G838" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25063,7 +25063,7 @@
         <v>31</v>
       </c>
       <c r="G839" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25089,7 +25089,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G840" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25115,7 +25115,7 @@
         <v>30</v>
       </c>
       <c r="G841" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25141,7 +25141,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G842" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25167,7 +25167,7 @@
         <v>30.5</v>
       </c>
       <c r="G843" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25193,7 +25193,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G844" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25219,7 +25219,7 @@
         <v>30.5</v>
       </c>
       <c r="G845" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25245,7 +25245,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G846" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25271,7 +25271,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G847" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25297,7 +25297,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G848" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25323,7 +25323,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G849" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25349,7 +25349,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G850" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25375,7 +25375,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G851" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25401,7 +25401,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G852" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -25427,7 +25427,7 @@
         <v>28</v>
       </c>
       <c r="G853" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -25453,7 +25453,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G854" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -25479,7 +25479,7 @@
         <v>28</v>
       </c>
       <c r="G855" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -25505,7 +25505,7 @@
         <v>27.5</v>
       </c>
       <c r="G856" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25531,7 +25531,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G857" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25557,7 +25557,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G858" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25583,7 +25583,7 @@
         <v>27.5</v>
       </c>
       <c r="G859" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25609,7 +25609,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G860" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25635,7 +25635,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G861" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25661,7 +25661,7 @@
         <v>28</v>
       </c>
       <c r="G862" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25687,7 +25687,7 @@
         <v>29</v>
       </c>
       <c r="G863" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25713,7 +25713,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G864" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25739,7 +25739,7 @@
         <v>29</v>
       </c>
       <c r="G865" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25765,7 +25765,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G866" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -25791,7 +25791,7 @@
         <v>29</v>
       </c>
       <c r="G867" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25817,7 +25817,7 @@
         <v>29</v>
       </c>
       <c r="G868" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -25843,7 +25843,7 @@
         <v>29</v>
       </c>
       <c r="G869" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -25869,7 +25869,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G870" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -25895,7 +25895,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G871" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25921,7 +25921,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G872" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -25947,7 +25947,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G873" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -25973,7 +25973,7 @@
         <v>30.5</v>
       </c>
       <c r="G874" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -25999,7 +25999,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G875" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -26025,7 +26025,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G876" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -26051,7 +26051,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G877" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -26077,7 +26077,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G878" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -26103,7 +26103,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G879" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26129,7 +26129,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G880" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -26155,7 +26155,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G881" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -26181,7 +26181,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G882" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -26207,7 +26207,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G883" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -26233,7 +26233,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G884" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -26259,7 +26259,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G885" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -26285,7 +26285,7 @@
         <v>31.5</v>
       </c>
       <c r="G886" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -26311,7 +26311,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G887" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -26337,7 +26337,7 @@
         <v>32</v>
       </c>
       <c r="G888" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -26363,7 +26363,7 @@
         <v>31.5</v>
       </c>
       <c r="G889" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -26389,7 +26389,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G890" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -26415,7 +26415,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G891" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -26441,7 +26441,7 @@
         <v>32</v>
       </c>
       <c r="G892" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -26467,7 +26467,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G893" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -26493,7 +26493,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G894" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -26519,7 +26519,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26545,7 +26545,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G896" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -26571,7 +26571,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G897" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -26597,7 +26597,7 @@
         <v>31</v>
       </c>
       <c r="G898" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -26623,7 +26623,7 @@
         <v>31</v>
       </c>
       <c r="G899" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -26649,7 +26649,7 @@
         <v>31</v>
       </c>
       <c r="G900" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -26675,7 +26675,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G901" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -26701,7 +26701,7 @@
         <v>31</v>
       </c>
       <c r="G902" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -26727,7 +26727,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G903" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -26753,7 +26753,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G904" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -26779,7 +26779,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G905" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -26805,7 +26805,7 @@
         <v>31</v>
       </c>
       <c r="G906" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -26831,7 +26831,7 @@
         <v>31</v>
       </c>
       <c r="G907" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -26857,7 +26857,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G908" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -26883,7 +26883,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G909" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -26909,7 +26909,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G910" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -26935,7 +26935,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G911" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -26961,7 +26961,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G912" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -26987,7 +26987,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G913" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -27013,7 +27013,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G914" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -27039,7 +27039,7 @@
         <v>30</v>
       </c>
       <c r="G915" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -27065,7 +27065,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G916" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -27091,7 +27091,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G917" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -27117,7 +27117,7 @@
         <v>29</v>
       </c>
       <c r="G918" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -27143,7 +27143,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G919" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -27169,7 +27169,7 @@
         <v>29</v>
       </c>
       <c r="G920" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -27195,7 +27195,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G921" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -27221,7 +27221,7 @@
         <v>29.5</v>
       </c>
       <c r="G922" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -27247,7 +27247,7 @@
         <v>29</v>
       </c>
       <c r="G923" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -27273,7 +27273,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G924" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -27299,7 +27299,7 @@
         <v>29</v>
       </c>
       <c r="G925" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -27325,7 +27325,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G926" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -27351,7 +27351,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G927" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -27377,7 +27377,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G928" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -27403,7 +27403,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G929" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -27429,7 +27429,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G930" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -27455,7 +27455,7 @@
         <v>30.5</v>
       </c>
       <c r="G931" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -27481,7 +27481,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G932" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -27507,7 +27507,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G933" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -27533,7 +27533,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G934" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -27559,7 +27559,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G935" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -27585,7 +27585,7 @@
         <v>30</v>
       </c>
       <c r="G936" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -27611,7 +27611,7 @@
         <v>29.5</v>
       </c>
       <c r="G937" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -27637,7 +27637,7 @@
         <v>29.5</v>
       </c>
       <c r="G938" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -27663,7 +27663,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G939" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -27689,7 +27689,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G940" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -27715,7 +27715,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G941" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -27741,7 +27741,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G942" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -27767,7 +27767,7 @@
         <v>30</v>
       </c>
       <c r="G943" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -27793,7 +27793,7 @@
         <v>30</v>
       </c>
       <c r="G944" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -27819,7 +27819,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G945" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -27845,7 +27845,7 @@
         <v>30</v>
       </c>
       <c r="G946" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -27871,7 +27871,7 @@
         <v>30.5</v>
       </c>
       <c r="G947" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -27897,7 +27897,7 @@
         <v>30.5</v>
       </c>
       <c r="G948" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -27923,7 +27923,7 @@
         <v>30</v>
       </c>
       <c r="G949" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -27949,7 +27949,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G950" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -27975,7 +27975,7 @@
         <v>30</v>
       </c>
       <c r="G951" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -28001,7 +28001,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G952" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -28027,7 +28027,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G953" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -28053,7 +28053,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G954" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -28079,7 +28079,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G955" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -28105,7 +28105,7 @@
         <v>30</v>
       </c>
       <c r="G956" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -28131,7 +28131,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G957" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -28157,7 +28157,7 @@
         <v>30</v>
       </c>
       <c r="G958" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -28183,7 +28183,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G959" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -28209,7 +28209,7 @@
         <v>30</v>
       </c>
       <c r="G960" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -28235,7 +28235,7 @@
         <v>30</v>
       </c>
       <c r="G961" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -28261,7 +28261,7 @@
         <v>30</v>
       </c>
       <c r="G962" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -28287,7 +28287,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G963" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -28313,7 +28313,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G964" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -28339,7 +28339,7 @@
         <v>30</v>
       </c>
       <c r="G965" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -28365,7 +28365,7 @@
         <v>30</v>
       </c>
       <c r="G966" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -28391,7 +28391,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G967" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -28417,7 +28417,7 @@
         <v>30</v>
       </c>
       <c r="G968" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -28443,7 +28443,7 @@
         <v>30</v>
       </c>
       <c r="G969" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -28469,7 +28469,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G970" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -28495,7 +28495,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G971" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -28521,7 +28521,7 @@
         <v>30</v>
       </c>
       <c r="G972" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -28547,7 +28547,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G973" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -28573,7 +28573,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G974" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -28599,7 +28599,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G975" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -28625,7 +28625,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G976" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -28651,7 +28651,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G977" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -28677,7 +28677,7 @@
         <v>31</v>
       </c>
       <c r="G978" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28703,7 +28703,7 @@
         <v>31</v>
       </c>
       <c r="G979" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -28729,7 +28729,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G980" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28755,7 +28755,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G981" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -28781,7 +28781,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G982" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -28807,7 +28807,7 @@
         <v>31</v>
       </c>
       <c r="G983" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -28833,7 +28833,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G984" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -28859,7 +28859,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G985" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28885,7 +28885,7 @@
         <v>31</v>
       </c>
       <c r="G986" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -28911,7 +28911,7 @@
         <v>31.5</v>
       </c>
       <c r="G987" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -28937,7 +28937,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G988" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -28963,7 +28963,7 @@
         <v>31.5</v>
       </c>
       <c r="G989" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -28989,7 +28989,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G990" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -29015,7 +29015,7 @@
         <v>31.5</v>
       </c>
       <c r="G991" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -29041,7 +29041,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G992" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -29067,7 +29067,7 @@
         <v>31.5</v>
       </c>
       <c r="G993" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -29093,7 +29093,7 @@
         <v>31.5</v>
       </c>
       <c r="G994" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -29119,7 +29119,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G995" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -29145,7 +29145,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G996" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -29171,7 +29171,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G997" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -29197,7 +29197,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G998" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -29223,7 +29223,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G999" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -29249,7 +29249,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1000" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -29275,7 +29275,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1001" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -29301,7 +29301,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1002" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -29327,7 +29327,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1003" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -29353,7 +29353,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1004" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -29379,7 +29379,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1005" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -29405,7 +29405,7 @@
         <v>31</v>
       </c>
       <c r="G1006" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -29431,7 +29431,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1007" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -29457,7 +29457,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1008" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -29483,7 +29483,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1009" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -29509,7 +29509,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1010" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -29535,7 +29535,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1011" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -29561,7 +29561,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1012" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -29587,7 +29587,7 @@
         <v>30.5</v>
       </c>
       <c r="G1013" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -29613,7 +29613,7 @@
         <v>30.5</v>
       </c>
       <c r="G1014" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -29639,7 +29639,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1015" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -29665,7 +29665,7 @@
         <v>30.5</v>
       </c>
       <c r="G1016" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -29691,7 +29691,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1017" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -29717,7 +29717,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1018" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -29743,7 +29743,7 @@
         <v>30</v>
       </c>
       <c r="G1019" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -29769,7 +29769,7 @@
         <v>30.5</v>
       </c>
       <c r="G1020" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -29795,7 +29795,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1021" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -29821,7 +29821,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1022" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -29847,7 +29847,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1023" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -29873,7 +29873,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1024" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -29899,7 +29899,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1025" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -29925,7 +29925,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1026" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -29951,7 +29951,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1027" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -29977,7 +29977,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1028" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -30003,7 +30003,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1029" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -30029,7 +30029,7 @@
         <v>30</v>
       </c>
       <c r="G1030" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -30055,7 +30055,7 @@
         <v>30</v>
       </c>
       <c r="G1031" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -30081,7 +30081,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1032" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -30107,7 +30107,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1033" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -30133,7 +30133,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1034" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -30159,7 +30159,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1035" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -30185,7 +30185,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1036" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -30211,7 +30211,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1037" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -30237,7 +30237,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1038" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -30263,7 +30263,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1039" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -30289,7 +30289,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1040" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -30315,7 +30315,7 @@
         <v>28</v>
       </c>
       <c r="G1041" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -30341,7 +30341,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1042" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -30367,7 +30367,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1043" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -30393,7 +30393,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1044" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -30419,7 +30419,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1045" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -30445,7 +30445,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1046" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -30471,7 +30471,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1047" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -30497,7 +30497,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1048" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -30523,7 +30523,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1049" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -30549,7 +30549,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1050" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -30575,7 +30575,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1051" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -30601,7 +30601,7 @@
         <v>28</v>
       </c>
       <c r="G1052" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -30627,7 +30627,7 @@
         <v>26</v>
       </c>
       <c r="G1053" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -30653,7 +30653,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1054" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -30679,7 +30679,7 @@
         <v>27.5</v>
       </c>
       <c r="G1055" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -30705,7 +30705,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1056" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -30731,7 +30731,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1057" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -30757,7 +30757,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1058" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -30783,7 +30783,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1059" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -30809,7 +30809,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1060" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -30835,7 +30835,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1061" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -30861,7 +30861,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1062" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -30887,7 +30887,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1063" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -30913,7 +30913,7 @@
         <v>20.5</v>
       </c>
       <c r="G1064" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -30939,7 +30939,7 @@
         <v>20</v>
       </c>
       <c r="G1065" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -30965,7 +30965,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1066" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -30991,7 +30991,7 @@
         <v>18.5</v>
       </c>
       <c r="G1067" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -31017,7 +31017,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1068" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -31043,7 +31043,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1069" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -31069,7 +31069,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G1070" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -31095,7 +31095,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G1071" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -31121,7 +31121,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1072" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -31147,7 +31147,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1073" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -31173,7 +31173,7 @@
         <v>19.5</v>
       </c>
       <c r="G1074" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -31199,7 +31199,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1075" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -31225,7 +31225,7 @@
         <v>20.5</v>
       </c>
       <c r="G1076" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -31251,7 +31251,7 @@
         <v>19.5</v>
       </c>
       <c r="G1077" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -31277,7 +31277,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G1078" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -31303,7 +31303,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1079" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -31329,7 +31329,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1080" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -31355,7 +31355,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1081" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -31381,7 +31381,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1082" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -31407,7 +31407,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1083" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -31433,7 +31433,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1084" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -31459,7 +31459,7 @@
         <v>19.5</v>
       </c>
       <c r="G1085" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -31485,7 +31485,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1086" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -31511,7 +31511,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1087" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -31537,7 +31537,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1088" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -31563,7 +31563,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1089" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -31589,7 +31589,7 @@
         <v>19.75</v>
       </c>
       <c r="G1090" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -31615,7 +31615,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G1091" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -31641,7 +31641,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1092" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -31667,7 +31667,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1093" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -31693,7 +31693,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1094" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -31719,7 +31719,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1095" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -31745,7 +31745,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1096" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -31771,7 +31771,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1097" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -31797,7 +31797,7 @@
         <v>21</v>
       </c>
       <c r="G1098" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -31823,7 +31823,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1099" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -31849,7 +31849,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1100" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -31875,7 +31875,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1101" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -31901,7 +31901,7 @@
         <v>21</v>
       </c>
       <c r="G1102" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -31927,7 +31927,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1103" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -31953,7 +31953,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1104" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -31979,7 +31979,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1105" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -32005,7 +32005,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1106" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -32031,7 +32031,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1107" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -32057,7 +32057,7 @@
         <v>20.5</v>
       </c>
       <c r="G1108" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -32083,7 +32083,7 @@
         <v>20.5</v>
       </c>
       <c r="G1109" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -32109,7 +32109,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1110" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -32135,7 +32135,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1111" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -32161,7 +32161,7 @@
         <v>20.5</v>
       </c>
       <c r="G1112" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -32187,7 +32187,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1113" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -32213,7 +32213,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1114" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -32239,7 +32239,7 @@
         <v>20.5</v>
       </c>
       <c r="G1115" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -32265,7 +32265,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1116" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -32291,7 +32291,7 @@
         <v>21</v>
       </c>
       <c r="G1117" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -32317,7 +32317,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1118" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -32343,7 +32343,7 @@
         <v>21</v>
       </c>
       <c r="G1119" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -32369,7 +32369,7 @@
         <v>21.5</v>
       </c>
       <c r="G1120" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -32395,7 +32395,7 @@
         <v>21.5</v>
       </c>
       <c r="G1121" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -32421,7 +32421,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1122" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -32447,7 +32447,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1123" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -32473,7 +32473,7 @@
         <v>22</v>
       </c>
       <c r="G1124" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -32499,7 +32499,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1125" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -32525,7 +32525,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1126" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -32551,7 +32551,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1127" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -32577,7 +32577,7 @@
         <v>21.5</v>
       </c>
       <c r="G1128" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -32603,7 +32603,7 @@
         <v>22</v>
       </c>
       <c r="G1129" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -32629,7 +32629,7 @@
         <v>22</v>
       </c>
       <c r="G1130" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -32655,7 +32655,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1131" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -32681,7 +32681,7 @@
         <v>22.5</v>
       </c>
       <c r="G1132" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -32707,7 +32707,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1133" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -32733,7 +32733,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1134" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -32759,7 +32759,7 @@
         <v>22</v>
       </c>
       <c r="G1135" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -32785,7 +32785,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1136" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -32811,7 +32811,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1137" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -32837,7 +32837,7 @@
         <v>22</v>
       </c>
       <c r="G1138" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -32863,7 +32863,7 @@
         <v>22</v>
       </c>
       <c r="G1139" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -32889,7 +32889,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1140" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -32915,7 +32915,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1141" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -32941,7 +32941,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1142" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -32967,7 +32967,7 @@
         <v>22</v>
       </c>
       <c r="G1143" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -32993,7 +32993,7 @@
         <v>22</v>
       </c>
       <c r="G1144" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -33019,7 +33019,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1145" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -33045,7 +33045,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1146" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -33071,7 +33071,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1147" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -33097,7 +33097,7 @@
         <v>21.5</v>
       </c>
       <c r="G1148" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -33123,7 +33123,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1149" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -33149,7 +33149,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1150" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -33175,7 +33175,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1151" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -33201,7 +33201,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1152" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -33227,7 +33227,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1153" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -33253,7 +33253,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1154" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -33279,7 +33279,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1155" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -33305,7 +33305,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1156" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -33331,7 +33331,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1157" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -33357,7 +33357,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1158" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -33383,7 +33383,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1159" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -33409,7 +33409,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1160" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -33435,7 +33435,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1161" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -33461,7 +33461,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1162" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -33487,7 +33487,7 @@
         <v>20.5</v>
       </c>
       <c r="G1163" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -33513,7 +33513,7 @@
         <v>20.5</v>
       </c>
       <c r="G1164" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -33539,7 +33539,7 @@
         <v>21</v>
       </c>
       <c r="G1165" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -33565,7 +33565,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1166" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -33591,7 +33591,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1167" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -33617,7 +33617,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1168" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -33643,7 +33643,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1169" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -33669,7 +33669,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1170" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -33695,7 +33695,7 @@
         <v>21.5</v>
       </c>
       <c r="G1171" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -33721,7 +33721,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1172" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -33747,7 +33747,7 @@
         <v>21.5</v>
       </c>
       <c r="G1173" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -33773,7 +33773,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1174" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -33799,7 +33799,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1175" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -33825,7 +33825,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1176" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -33851,7 +33851,7 @@
         <v>21.5</v>
       </c>
       <c r="G1177" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -33877,7 +33877,7 @@
         <v>21.5</v>
       </c>
       <c r="G1178" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33903,7 +33903,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1179" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -33929,7 +33929,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1180" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -33955,7 +33955,7 @@
         <v>21.5</v>
       </c>
       <c r="G1181" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -33981,7 +33981,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1182" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -34007,7 +34007,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1183" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -34033,7 +34033,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1184" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -34059,7 +34059,7 @@
         <v>21</v>
       </c>
       <c r="G1185" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -34085,7 +34085,7 @@
         <v>21</v>
       </c>
       <c r="G1186" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -34111,7 +34111,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1187" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -34137,7 +34137,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1188" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -34163,7 +34163,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1189" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -34189,7 +34189,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1190" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -34215,7 +34215,7 @@
         <v>20</v>
       </c>
       <c r="G1191" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -34241,7 +34241,7 @@
         <v>20</v>
       </c>
       <c r="G1192" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -34267,7 +34267,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1193" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -34293,7 +34293,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1194" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -34319,7 +34319,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1195" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -34345,7 +34345,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1196" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -34371,7 +34371,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1197" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -34397,7 +34397,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G1198" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -34423,7 +34423,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1199" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -34449,7 +34449,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1200" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -34475,7 +34475,7 @@
         <v>19.75</v>
       </c>
       <c r="G1201" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -34501,7 +34501,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1202" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -34527,7 +34527,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1203" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -34553,7 +34553,7 @@
         <v>19.75</v>
       </c>
       <c r="G1204" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -34579,7 +34579,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1205" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -34605,7 +34605,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1206" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -34631,7 +34631,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1207" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -34657,7 +34657,7 @@
         <v>18.5</v>
       </c>
       <c r="G1208" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -34683,7 +34683,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1209" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -34709,7 +34709,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1210" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -34735,7 +34735,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1211" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -34761,7 +34761,7 @@
         <v>18.5</v>
       </c>
       <c r="G1212" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -34787,7 +34787,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1213" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -34813,7 +34813,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1214" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -34839,7 +34839,7 @@
         <v>18.25</v>
       </c>
       <c r="G1215" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -34865,7 +34865,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1216" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -34891,7 +34891,7 @@
         <v>17.5</v>
       </c>
       <c r="G1217" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -34917,7 +34917,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1218" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -34943,7 +34943,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1219" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -34969,7 +34969,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1220" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -34995,7 +34995,7 @@
         <v>17.5</v>
       </c>
       <c r="G1221" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -35021,7 +35021,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1222" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -35047,7 +35047,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1223" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -35073,7 +35073,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1224" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -35099,7 +35099,7 @@
         <v>17</v>
       </c>
       <c r="G1225" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -35125,7 +35125,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1226" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -35151,7 +35151,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1227" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -35177,7 +35177,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1228" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -35203,7 +35203,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1229" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -35229,7 +35229,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1230" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -35255,7 +35255,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1231" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -35281,7 +35281,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1232" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -35307,7 +35307,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1233" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -35333,7 +35333,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1234" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -35359,7 +35359,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1235" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -35385,7 +35385,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1236" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -35411,7 +35411,7 @@
         <v>17.25</v>
       </c>
       <c r="G1237" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -35437,7 +35437,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1238" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -35463,7 +35463,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1239" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -35489,7 +35489,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1240" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -35515,7 +35515,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1241" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -35541,7 +35541,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1242" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -35567,7 +35567,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1243" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -35593,7 +35593,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1244" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -35619,7 +35619,7 @@
         <v>17.5</v>
       </c>
       <c r="G1245" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -35645,7 +35645,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1246" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -35671,7 +35671,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1247" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -35697,7 +35697,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1248" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -35723,7 +35723,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1249" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -35749,7 +35749,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1250" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -35775,7 +35775,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1251" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -35801,7 +35801,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1252" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -35827,7 +35827,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1253" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -35853,7 +35853,7 @@
         <v>19</v>
       </c>
       <c r="G1254" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -35879,7 +35879,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G1255" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -35905,7 +35905,7 @@
         <v>18.5</v>
       </c>
       <c r="G1256" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -35931,7 +35931,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1257" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -35957,7 +35957,7 @@
         <v>18.25</v>
       </c>
       <c r="G1258" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -35983,7 +35983,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1259" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -36009,7 +36009,7 @@
         <v>18.5</v>
       </c>
       <c r="G1260" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -36035,7 +36035,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1261" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -36061,7 +36061,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1262" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -36087,7 +36087,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1263" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -36113,7 +36113,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1264" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -36139,7 +36139,7 @@
         <v>18.75</v>
       </c>
       <c r="G1265" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -36165,7 +36165,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1266" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -36191,7 +36191,7 @@
         <v>18.5</v>
       </c>
       <c r="G1267" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -36217,7 +36217,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G1268" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -36243,7 +36243,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G1269" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -36269,7 +36269,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1270" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -36295,7 +36295,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1271" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -36321,7 +36321,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1272" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -36347,7 +36347,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1273" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -36373,7 +36373,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1274" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -36399,7 +36399,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1275" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -36425,7 +36425,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1276" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -36451,7 +36451,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1277" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -36477,7 +36477,7 @@
         <v>19</v>
       </c>
       <c r="G1278" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -36503,7 +36503,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1279" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -36529,7 +36529,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G1280" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -36555,7 +36555,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1281" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -36581,7 +36581,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1282" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -36607,7 +36607,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1283" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -36633,7 +36633,7 @@
         <v>18.5</v>
       </c>
       <c r="G1284" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -36659,7 +36659,7 @@
         <v>18.5</v>
       </c>
       <c r="G1285" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -36685,7 +36685,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1286" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -36711,7 +36711,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1287" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -36737,7 +36737,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1288" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -36763,7 +36763,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1289" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -36789,7 +36789,7 @@
         <v>18.25</v>
       </c>
       <c r="G1290" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -36815,7 +36815,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1291" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -36841,7 +36841,7 @@
         <v>19</v>
       </c>
       <c r="G1292" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -36867,7 +36867,7 @@
         <v>23</v>
       </c>
       <c r="G1293" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -36893,7 +36893,7 @@
         <v>24</v>
       </c>
       <c r="G1294" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -36919,7 +36919,7 @@
         <v>25.5</v>
       </c>
       <c r="G1295" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -36945,7 +36945,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1296" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -36971,7 +36971,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1297" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -36997,7 +36997,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1298" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -37023,7 +37023,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1299" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -37049,7 +37049,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1300" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -37075,7 +37075,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1301" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -37101,7 +37101,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1302" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -37127,7 +37127,7 @@
         <v>29</v>
       </c>
       <c r="G1303" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -37153,7 +37153,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1304" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -37179,7 +37179,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1305" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -37205,7 +37205,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1306" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -37231,7 +37231,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1307" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -37257,7 +37257,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1308" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -37283,7 +37283,7 @@
         <v>28</v>
       </c>
       <c r="G1309" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -37309,7 +37309,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1310" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -37335,7 +37335,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1311" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -37361,7 +37361,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1312" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -37387,7 +37387,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1313" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -37413,7 +37413,7 @@
         <v>28</v>
       </c>
       <c r="G1314" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -37439,7 +37439,7 @@
         <v>28</v>
       </c>
       <c r="G1315" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -37465,7 +37465,7 @@
         <v>28</v>
       </c>
       <c r="G1316" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -37491,7 +37491,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1317" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -37517,7 +37517,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1318" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -37543,7 +37543,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1319" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -37569,7 +37569,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1320" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -37595,7 +37595,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1321" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -37621,7 +37621,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1322" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -37647,7 +37647,7 @@
         <v>26</v>
       </c>
       <c r="G1323" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -37673,7 +37673,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1324" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -37699,7 +37699,7 @@
         <v>25.5</v>
       </c>
       <c r="G1325" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -37725,7 +37725,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1326" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -37751,7 +37751,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1327" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -37777,7 +37777,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1328" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -37803,7 +37803,7 @@
         <v>26</v>
       </c>
       <c r="G1329" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -37829,7 +37829,7 @@
         <v>27.5</v>
       </c>
       <c r="G1330" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -37855,7 +37855,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1331" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -37881,7 +37881,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1332" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -37907,7 +37907,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1333" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -37933,7 +37933,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1334" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -37959,7 +37959,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1335" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -37985,7 +37985,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1336" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -38011,7 +38011,7 @@
         <v>27.5</v>
       </c>
       <c r="G1337" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -38037,7 +38037,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1338" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -68491,7 +68491,7 @@
     </row>
     <row r="2510">
       <c r="A2510" s="1" t="n">
-        <v>45973.6874537037</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B2510" t="n">
         <v>9014</v>
@@ -68512,6 +68512,32 @@
         <v>967</v>
       </c>
       <c r="H2510" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2511">
+      <c r="A2511" s="1" t="n">
+        <v>45974.5940740741</v>
+      </c>
+      <c r="B2511" t="n">
+        <v>2301</v>
+      </c>
+      <c r="C2511" t="n">
+        <v>2.77500009536743</v>
+      </c>
+      <c r="D2511" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="E2511" t="n">
+        <v>2.67499995231628</v>
+      </c>
+      <c r="F2511" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="G2511" t="s">
+        <v>948</v>
+      </c>
+      <c r="H2511" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -38,43 +38,43 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24616158008575</t>
+    <t xml:space="preserve">1.24616146087646</t>
   </si>
   <si>
     <t xml:space="preserve">AUTME.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24544668197632</t>
+    <t xml:space="preserve">1.24544656276703</t>
   </si>
   <si>
     <t xml:space="preserve">1.24330163002014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22256791591644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2154186964035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22185301780701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21470367908478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23615229129791</t>
+    <t xml:space="preserve">1.22256803512573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21541845798492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2218531370163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21470355987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23615217208862</t>
   </si>
   <si>
     <t xml:space="preserve">1.21327364444733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20683908462524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20111954212189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20040476322174</t>
+    <t xml:space="preserve">1.20683896541595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20111930370331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20040452480316</t>
   </si>
   <si>
     <t xml:space="preserve">1.16680181026459</t>
@@ -83,16 +83,16 @@
     <t xml:space="preserve">1.1946849822998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25688600540161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25045120716095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24687659740448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25116634368896</t>
+    <t xml:space="preserve">1.25688576698303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25045108795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2468763589859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25116622447968</t>
   </si>
   <si>
     <t xml:space="preserve">1.26475024223328</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">1.2354371547699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22542774677277</t>
+    <t xml:space="preserve">1.22542798519135</t>
   </si>
   <si>
     <t xml:space="preserve">1.21041393280029</t>
@@ -113,124 +113,124 @@
     <t xml:space="preserve">1.19397008419037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22685766220093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20469427108765</t>
+    <t xml:space="preserve">1.22685790061951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20469439029694</t>
   </si>
   <si>
     <t xml:space="preserve">1.25831580162048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26546514034271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25903069972992</t>
+    <t xml:space="preserve">1.265465259552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25903081893921</t>
   </si>
   <si>
     <t xml:space="preserve">1.26903986930847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21684861183167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22828757762909</t>
+    <t xml:space="preserve">1.21684849262238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22828781604767</t>
   </si>
   <si>
     <t xml:space="preserve">1.27404463291168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26689493656158</t>
+    <t xml:space="preserve">1.26689505577087</t>
   </si>
   <si>
     <t xml:space="preserve">1.27261459827423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27189981937408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27904903888702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26760983467102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25545597076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2626051902771</t>
+    <t xml:space="preserve">1.27189970016479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2790492773056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26760995388031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25545573234558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26260554790497</t>
   </si>
   <si>
     <t xml:space="preserve">1.24830627441406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24902129173279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24258661270142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23686718940735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23472225666046</t>
+    <t xml:space="preserve">1.2490211725235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24258673191071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23686695098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23472213745117</t>
   </si>
   <si>
     <t xml:space="preserve">1.23400735855103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25225353240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26176822185516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26835525035858</t>
+    <t xml:space="preserve">1.25225365161896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26176810264587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26835501194</t>
   </si>
   <si>
     <t xml:space="preserve">1.27860140800476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2764059305191</t>
+    <t xml:space="preserve">1.27640581130981</t>
   </si>
   <si>
     <t xml:space="preserve">1.27420997619629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27494204044342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26323187351227</t>
+    <t xml:space="preserve">1.27494192123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26323199272156</t>
   </si>
   <si>
     <t xml:space="preserve">1.27128267288208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2668913602829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28445672988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28079724311829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27933347225189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27347815036774</t>
+    <t xml:space="preserve">1.26689112186432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28445637226105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.280797123909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2793333530426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27347826957703</t>
   </si>
   <si>
     <t xml:space="preserve">1.27274632453918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26615941524506</t>
+    <t xml:space="preserve">1.26615929603577</t>
   </si>
   <si>
     <t xml:space="preserve">1.28226089477539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28811609745026</t>
+    <t xml:space="preserve">1.28811597824097</t>
   </si>
   <si>
     <t xml:space="preserve">1.28738415241241</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">1.28299283981323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26396381855011</t>
+    <t xml:space="preserve">1.26396369934082</t>
   </si>
   <si>
     <t xml:space="preserve">1.24127531051636</t>
@@ -248,10 +248,10 @@
     <t xml:space="preserve">1.24347102642059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22956526279449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23468852043152</t>
+    <t xml:space="preserve">1.22956514358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23468840122223</t>
   </si>
   <si>
     <t xml:space="preserve">1.22663760185242</t>
@@ -260,16 +260,16 @@
     <t xml:space="preserve">1.20687675476074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20760869979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18565213680267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1783332824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18784773349762</t>
+    <t xml:space="preserve">1.20760858058929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18565237522125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17833340167999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18784785270691</t>
   </si>
   <si>
     <t xml:space="preserve">1.16955065727234</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">1.17101442813873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17028248310089</t>
+    <t xml:space="preserve">1.17028260231018</t>
   </si>
   <si>
     <t xml:space="preserve">1.18931150436401</t>
@@ -296,7 +296,7 @@
     <t xml:space="preserve">1.23907971382141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23834776878357</t>
+    <t xml:space="preserve">1.23834764957428</t>
   </si>
   <si>
     <t xml:space="preserve">1.23542022705078</t>
@@ -305,16 +305,16 @@
     <t xml:space="preserve">1.20614492893219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23102879524231</t>
+    <t xml:space="preserve">1.2310289144516</t>
   </si>
   <si>
     <t xml:space="preserve">1.19736230373383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2171231508255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22297823429108</t>
+    <t xml:space="preserve">1.21712327003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22297811508179</t>
   </si>
   <si>
     <t xml:space="preserve">1.23322451114655</t>
@@ -335,13 +335,13 @@
     <t xml:space="preserve">1.30714499950409</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29909408092499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32324635982513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31665933132172</t>
+    <t xml:space="preserve">1.29909420013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32324647903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31665945053101</t>
   </si>
   <si>
     <t xml:space="preserve">1.32763767242432</t>
@@ -350,19 +350,19 @@
     <t xml:space="preserve">1.30348539352417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31592738628387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3181232213974</t>
+    <t xml:space="preserve">1.31592750549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31812310218811</t>
   </si>
   <si>
     <t xml:space="preserve">1.29763031005859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30275344848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29982590675354</t>
+    <t xml:space="preserve">1.30275356769562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29982602596283</t>
   </si>
   <si>
     <t xml:space="preserve">1.28884792327881</t>
@@ -371,88 +371,88 @@
     <t xml:space="preserve">1.29543483257294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30055797100067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29836237430573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29323887825012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29250705242157</t>
+    <t xml:space="preserve">1.30055785179138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29836225509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29323923587799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29250729084015</t>
   </si>
   <si>
     <t xml:space="preserve">1.30128979682922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30568110942841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26908707618713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26762330532074</t>
+    <t xml:space="preserve">1.30568099021912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26908683776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26762318611145</t>
   </si>
   <si>
     <t xml:space="preserve">1.24786233901978</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25518107414246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26542782783508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28006529808044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25810861587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25005793571472</t>
+    <t xml:space="preserve">1.25518119335175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2654275894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28006517887115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25810885429382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25005781650543</t>
   </si>
   <si>
     <t xml:space="preserve">1.24054348468781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24639880657196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24420297145844</t>
+    <t xml:space="preserve">1.24639868736267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24420285224915</t>
   </si>
   <si>
     <t xml:space="preserve">1.23615205287933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23688411712646</t>
+    <t xml:space="preserve">1.23688399791718</t>
   </si>
   <si>
     <t xml:space="preserve">1.2420072555542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23176074028015</t>
+    <t xml:space="preserve">1.23176085948944</t>
   </si>
   <si>
     <t xml:space="preserve">1.20980441570282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21126806735992</t>
+    <t xml:space="preserve">1.21126818656921</t>
   </si>
   <si>
     <t xml:space="preserve">1.21858692169189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21492767333984</t>
+    <t xml:space="preserve">1.21492755413055</t>
   </si>
   <si>
     <t xml:space="preserve">1.19004344940186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18199276924133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.214195728302</t>
+    <t xml:space="preserve">1.18199265003204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21419560909271</t>
   </si>
   <si>
     <t xml:space="preserve">1.19297087192535</t>
@@ -464,25 +464,25 @@
     <t xml:space="preserve">1.22005069255829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21639132499695</t>
+    <t xml:space="preserve">1.21639144420624</t>
   </si>
   <si>
     <t xml:space="preserve">1.25957238674164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27786958217621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28592050075531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2947028875351</t>
+    <t xml:space="preserve">1.27786946296692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28592026233673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29470300674438</t>
   </si>
   <si>
     <t xml:space="preserve">1.29689848423004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3100723028183</t>
+    <t xml:space="preserve">1.31007242202759</t>
   </si>
   <si>
     <t xml:space="preserve">1.32544207572937</t>
@@ -494,10 +494,10 @@
     <t xml:space="preserve">1.3334926366806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33422458171844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33202886581421</t>
+    <t xml:space="preserve">1.33422446250916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3320289850235</t>
   </si>
   <si>
     <t xml:space="preserve">1.33861601352692</t>
@@ -506,10 +506,10 @@
     <t xml:space="preserve">1.33934772014618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34666669368744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34227550029755</t>
+    <t xml:space="preserve">1.34666657447815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34227526187897</t>
   </si>
   <si>
     <t xml:space="preserve">1.34007966518402</t>
@@ -521,94 +521,94 @@
     <t xml:space="preserve">1.3210506439209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34593486785889</t>
+    <t xml:space="preserve">1.3459347486496</t>
   </si>
   <si>
     <t xml:space="preserve">1.36130440235138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36057233810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33276093006134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34959411621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33788406848907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34373939037323</t>
+    <t xml:space="preserve">1.36057257652283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33276081085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34959423542023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33788394927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34373915195465</t>
   </si>
   <si>
     <t xml:space="preserve">1.34520292282104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32910144329071</t>
+    <t xml:space="preserve">1.3291015625</t>
   </si>
   <si>
     <t xml:space="preserve">1.36349999904633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36789131164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37667369842529</t>
+    <t xml:space="preserve">1.36789119243622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37667393684387</t>
   </si>
   <si>
     <t xml:space="preserve">1.38252902030945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39789855480194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4125360250473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40668118000031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40814471244812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40887665748596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40302181243896</t>
+    <t xml:space="preserve">1.39789879322052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41253614425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40668106079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40814483165741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40887677669525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4030214548111</t>
   </si>
   <si>
     <t xml:space="preserve">1.39277541637421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36935496330261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37886953353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.389115691185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40155792236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49304342269897</t>
+    <t xml:space="preserve">1.36935484409332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37886965274811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38911581039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40155780315399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49304330348969</t>
   </si>
   <si>
     <t xml:space="preserve">1.47621011734009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48206520080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49157953262329</t>
+    <t xml:space="preserve">1.48206508159637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49157965183258</t>
   </si>
   <si>
     <t xml:space="preserve">1.50328993797302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46742749214172</t>
+    <t xml:space="preserve">1.46742761135101</t>
   </si>
   <si>
     <t xml:space="preserve">1.45864498615265</t>
@@ -617,34 +617,34 @@
     <t xml:space="preserve">1.47913765907288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4952392578125</t>
+    <t xml:space="preserve">1.49523901939392</t>
   </si>
   <si>
     <t xml:space="preserve">1.49084794521332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48792016506195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52744209766388</t>
+    <t xml:space="preserve">1.48792040348053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52744221687317</t>
   </si>
   <si>
     <t xml:space="preserve">1.50987672805786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53256523609161</t>
+    <t xml:space="preserve">1.53256547451019</t>
   </si>
   <si>
     <t xml:space="preserve">1.52963757514954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53183317184448</t>
+    <t xml:space="preserve">1.53183341026306</t>
   </si>
   <si>
     <t xml:space="preserve">1.52817380428314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51500010490417</t>
+    <t xml:space="preserve">1.5149998664856</t>
   </si>
   <si>
     <t xml:space="preserve">1.49963045120239</t>
@@ -653,19 +653,19 @@
     <t xml:space="preserve">1.498166680336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.485724568367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47108674049377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4842609167099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46376812458038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45498538017273</t>
+    <t xml:space="preserve">1.48572444915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47108709812164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48426079750061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46376800537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45498549938202</t>
   </si>
   <si>
     <t xml:space="preserve">1.48499274253845</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">1.52085518836975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53768849372864</t>
+    <t xml:space="preserve">1.53768825531006</t>
   </si>
   <si>
     <t xml:space="preserve">1.58233332633972</t>
@@ -683,94 +683,94 @@
     <t xml:space="preserve">1.63126361370087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63427472114563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64857769012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63578033447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6666442155838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66288030147552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66137492656708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76902163028717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80816602706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84429907798767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9165655374527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99485409259796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01367354393005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95345139503479</t>
+    <t xml:space="preserve">1.63427460193634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64857757091522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63578045368195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66664397716522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66288018226624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6613746881485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76902151107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80816578865051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84429883956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91656541824341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99485421180725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01367330551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95345163345337</t>
   </si>
   <si>
     <t xml:space="preserve">1.9820568561554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9301153421402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83376026153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90301561355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90452086925507</t>
+    <t xml:space="preserve">1.93011546134949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83376038074493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9030157327652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90452122688293</t>
   </si>
   <si>
     <t xml:space="preserve">1.9120489358902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93538463115692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92258787155151</t>
+    <t xml:space="preserve">1.93538475036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92258763313293</t>
   </si>
   <si>
     <t xml:space="preserve">1.91581284999847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88118493556976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92861008644104</t>
+    <t xml:space="preserve">1.88118505477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92860996723175</t>
   </si>
   <si>
     <t xml:space="preserve">1.92183494567871</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92559897899628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94065415859222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92635178565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90376842021942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91957664489746</t>
+    <t xml:space="preserve">1.9255987405777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94065427780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92635154724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90376830101013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91957652568817</t>
   </si>
   <si>
     <t xml:space="preserve">1.91882383823395</t>
@@ -779,64 +779,64 @@
     <t xml:space="preserve">1.93237376213074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94366526603699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91054344177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89021861553192</t>
+    <t xml:space="preserve">1.94366538524628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91054332256317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89021849632263</t>
   </si>
   <si>
     <t xml:space="preserve">1.90753221511841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89699351787567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89473474025726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87742125988007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86010718345642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7705272436142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7976268529892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76826894283295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79461586475372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80741310119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83074939250946</t>
+    <t xml:space="preserve">1.89699339866638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89473509788513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87742114067078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86010730266571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77052700519562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79762721061707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76826882362366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7946161031723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80741322040558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83074915409088</t>
   </si>
   <si>
     <t xml:space="preserve">1.84881567955017</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82547962665558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81042432785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82623267173767</t>
+    <t xml:space="preserve">1.82547986507416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81042397022247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82623255252838</t>
   </si>
   <si>
     <t xml:space="preserve">1.83601856231689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83902978897095</t>
+    <t xml:space="preserve">1.83902990818024</t>
   </si>
   <si>
     <t xml:space="preserve">1.85257947444916</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">1.82171583175659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84806299209595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84655749797821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83752429485321</t>
+    <t xml:space="preserve">1.84806287288666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84655737876892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83752417564392</t>
   </si>
   <si>
     <t xml:space="preserve">1.89774596691132</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">1.91280174255371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97377622127533</t>
+    <t xml:space="preserve">1.9737765789032</t>
   </si>
   <si>
     <t xml:space="preserve">1.97151815891266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93086802959442</t>
+    <t xml:space="preserve">1.93086814880371</t>
   </si>
   <si>
     <t xml:space="preserve">1.93613767623901</t>
@@ -878,22 +878,22 @@
     <t xml:space="preserve">1.88796007633209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88720738887787</t>
+    <t xml:space="preserve">1.88720715045929</t>
   </si>
   <si>
     <t xml:space="preserve">1.89548778533936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89322936534882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86914074420929</t>
+    <t xml:space="preserve">1.89322924613953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.869140625</t>
   </si>
   <si>
     <t xml:space="preserve">1.85860180854797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85634338855743</t>
+    <t xml:space="preserve">1.85634362697601</t>
   </si>
   <si>
     <t xml:space="preserve">1.85709631443024</t>
@@ -902,10 +902,10 @@
     <t xml:space="preserve">1.85182678699493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86688220500946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88494884967804</t>
+    <t xml:space="preserve">1.86688244342804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88494896888733</t>
   </si>
   <si>
     <t xml:space="preserve">1.87215185165405</t>
@@ -914,34 +914,34 @@
     <t xml:space="preserve">1.87064635753632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86161267757416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88193798065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86763525009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87365710735321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8653769493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8450516462326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84204053878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84731042385101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84279334545135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8179520368576</t>
+    <t xml:space="preserve">1.86161279678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88193774223328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86763501167297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87365734577179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86537683010101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84505200386047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84204077720642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84731030464172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84279358386993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81795191764832</t>
   </si>
   <si>
     <t xml:space="preserve">1.82397401332855</t>
@@ -950,19 +950,19 @@
     <t xml:space="preserve">1.82849097251892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81569361686707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82021045684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81117713451385</t>
+    <t xml:space="preserve">1.81569373607635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82021009922028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81117689609528</t>
   </si>
   <si>
     <t xml:space="preserve">1.81644642353058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81418788433075</t>
+    <t xml:space="preserve">1.81418800354004</t>
   </si>
   <si>
     <t xml:space="preserve">1.83526575565338</t>
@@ -971,43 +971,43 @@
     <t xml:space="preserve">1.83225464820862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82246851921082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85032117366791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89849901199341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93689036369324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91731834411621</t>
+    <t xml:space="preserve">1.82246840000153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8503212928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89849889278412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93689024448395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91731810569763</t>
   </si>
   <si>
     <t xml:space="preserve">1.97979855537415</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96474313735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94667661190033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97076547145844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96775436401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96248483657837</t>
+    <t xml:space="preserve">1.96474325656891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94667637348175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97076523303986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96775412559509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96248459815979</t>
   </si>
   <si>
     <t xml:space="preserve">2.10325384140015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04378461837769</t>
+    <t xml:space="preserve">2.04378437995911</t>
   </si>
   <si>
     <t xml:space="preserve">2.02421236038208</t>
@@ -1016,28 +1016,28 @@
     <t xml:space="preserve">1.98732650279999</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99937069416046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98582088947296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99033749103546</t>
+    <t xml:space="preserve">1.99937057495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98582077026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99033737182617</t>
   </si>
   <si>
     <t xml:space="preserve">1.96624886989594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99861812591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96549606323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97603476047516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98280966281891</t>
+    <t xml:space="preserve">1.99861788749695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96549594402313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97603487968445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9828097820282</t>
   </si>
   <si>
     <t xml:space="preserve">2.02496528625488</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">2.06260371208191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07540106773376</t>
+    <t xml:space="preserve">2.07540082931519</t>
   </si>
   <si>
     <t xml:space="preserve">2.08142328262329</t>
@@ -1058,64 +1058,64 @@
     <t xml:space="preserve">2.08593988418579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07765960693359</t>
+    <t xml:space="preserve">2.07765936851501</t>
   </si>
   <si>
     <t xml:space="preserve">2.09572601318359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09045648574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11153411865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10024237632751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08669281005859</t>
+    <t xml:space="preserve">2.09045672416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11153435707092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10024261474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08669257164001</t>
   </si>
   <si>
     <t xml:space="preserve">2.07013177871704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06034564971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05959272384644</t>
+    <t xml:space="preserve">2.06034588813782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05959296226501</t>
   </si>
   <si>
     <t xml:space="preserve">2.05884003639221</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07615375518799</t>
+    <t xml:space="preserve">2.07615399360657</t>
   </si>
   <si>
     <t xml:space="preserve">2.08368158340454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10400676727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08518719673157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13185906410217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19057536125183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21315908432007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17552042007446</t>
+    <t xml:space="preserve">2.10400629043579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08518695831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13185930252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19057559967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21315884590149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17552018165588</t>
   </si>
   <si>
     <t xml:space="preserve">2.16799235343933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20563101768494</t>
+    <t xml:space="preserve">2.20563125610352</t>
   </si>
   <si>
     <t xml:space="preserve">2.22068643569946</t>
@@ -1130,7 +1130,7 @@
     <t xml:space="preserve">2.31854724884033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33360290527344</t>
+    <t xml:space="preserve">2.33360314369202</t>
   </si>
   <si>
     <t xml:space="preserve">2.37124156951904</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">2.28843641281128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26585340499878</t>
+    <t xml:space="preserve">2.2658531665802</t>
   </si>
   <si>
     <t xml:space="preserve">2.28090858459473</t>
@@ -1157,34 +1157,34 @@
     <t xml:space="preserve">2.25832533836365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19810342788696</t>
+    <t xml:space="preserve">2.19810366630554</t>
   </si>
   <si>
     <t xml:space="preserve">2.18304800987244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43899154663086</t>
+    <t xml:space="preserve">2.43899178504944</t>
   </si>
   <si>
     <t xml:space="preserve">2.38629722595215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55190801620483</t>
+    <t xml:space="preserve">2.55190777778625</t>
   </si>
   <si>
     <t xml:space="preserve">2.5443799495697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61965727806091</t>
+    <t xml:space="preserve">2.61965751647949</t>
   </si>
   <si>
     <t xml:space="preserve">2.46157479286194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49168562889099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46910238265991</t>
+    <t xml:space="preserve">2.49168586730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46910214424133</t>
   </si>
   <si>
     <t xml:space="preserve">2.40135264396667</t>
@@ -1202,7 +1202,7 @@
     <t xml:space="preserve">2.40888047218323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48415803909302</t>
+    <t xml:space="preserve">2.48415780067444</t>
   </si>
   <si>
     <t xml:space="preserve">2.45404672622681</t>
@@ -1214,13 +1214,13 @@
     <t xml:space="preserve">2.50674104690552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52932453155518</t>
+    <t xml:space="preserve">2.5293242931366</t>
   </si>
   <si>
     <t xml:space="preserve">2.57587671279907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59139370918274</t>
+    <t xml:space="preserve">2.5913941860199</t>
   </si>
   <si>
     <t xml:space="preserve">2.58363509178162</t>
@@ -1229,21 +1229,18 @@
     <t xml:space="preserve">2.56035900115967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50604867935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51380729675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52156591415405</t>
+    <t xml:space="preserve">2.50604844093323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51380753517151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52156567573547</t>
   </si>
   <si>
     <t xml:space="preserve">2.54484152793884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5293242931366</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.48277235031128</t>
   </si>
   <si>
@@ -1253,7 +1250,7 @@
     <t xml:space="preserve">2.42846202850342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3275990486145</t>
+    <t xml:space="preserve">2.32759928703308</t>
   </si>
   <si>
     <t xml:space="preserve">2.30432343482971</t>
@@ -1262,16 +1259,16 @@
     <t xml:space="preserve">2.28104710578918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31208157539368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22673678398132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2034604549408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19570207595825</t>
+    <t xml:space="preserve">2.31208181381226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22673654556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20346069335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19570183753967</t>
   </si>
   <si>
     <t xml:space="preserve">2.21897792816162</t>
@@ -1280,7 +1277,7 @@
     <t xml:space="preserve">2.23449516296387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25777149200439</t>
+    <t xml:space="preserve">2.25777125358582</t>
   </si>
   <si>
     <t xml:space="preserve">2.1724259853363</t>
@@ -1289,7 +1286,7 @@
     <t xml:space="preserve">2.11811518669128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18794322013855</t>
+    <t xml:space="preserve">2.18794345855713</t>
   </si>
   <si>
     <t xml:space="preserve">2.25001239776611</t>
@@ -1301,7 +1298,7 @@
     <t xml:space="preserve">2.10259819030762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13363289833069</t>
+    <t xml:space="preserve">2.13363265991211</t>
   </si>
   <si>
     <t xml:space="preserve">2.09483909606934</t>
@@ -1310,13 +1307,13 @@
     <t xml:space="preserve">2.08708071708679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07932162284851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07156348228455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04052877426147</t>
+    <t xml:space="preserve">2.07932209968567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07156324386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0405285358429</t>
   </si>
   <si>
     <t xml:space="preserve">2.14139127731323</t>
@@ -1325,7 +1322,7 @@
     <t xml:space="preserve">2.16466736793518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14915013313293</t>
+    <t xml:space="preserve">2.14914989471436</t>
   </si>
   <si>
     <t xml:space="preserve">2.18018460273743</t>
@@ -1340,58 +1337,58 @@
     <t xml:space="preserve">2.01725244522095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02501153945923</t>
+    <t xml:space="preserve">2.02501130104065</t>
   </si>
   <si>
     <t xml:space="preserve">2.0094940662384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97070062160492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96294188499451</t>
+    <t xml:space="preserve">1.9707008600235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9629420042038</t>
   </si>
   <si>
     <t xml:space="preserve">1.93966591358185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88535523414612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87759685516357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85432052612305</t>
+    <t xml:space="preserve">1.8853554725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.877596616745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85432076454163</t>
   </si>
   <si>
     <t xml:space="preserve">1.86983799934387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79225134849548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83880352973938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83104479312897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86207950115204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15690851211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06380438804626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04828715324402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00173497200012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97845935821533</t>
+    <t xml:space="preserve">1.79225122928619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8388032913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83104467391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86207938194275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15690875053406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06380462646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0482873916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0017352104187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97845923900604</t>
   </si>
   <si>
     <t xml:space="preserve">1.99397671222687</t>
@@ -1400,46 +1397,46 @@
     <t xml:space="preserve">1.9241486787796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84656202793121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80776858329773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75345814228058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77673411369324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74569940567017</t>
+    <t xml:space="preserve">1.84656190872192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80776882171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.753457903862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77673423290253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74569928646088</t>
   </si>
   <si>
     <t xml:space="preserve">1.82328605651855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89311420917511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91638994216919</t>
+    <t xml:space="preserve">1.89311408996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91639006137848</t>
   </si>
   <si>
     <t xml:space="preserve">2.2112193107605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11035656929016</t>
+    <t xml:space="preserve">2.11035680770874</t>
   </si>
   <si>
     <t xml:space="preserve">2.05604600906372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26552987098694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24225401878357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35087537765503</t>
+    <t xml:space="preserve">2.26553010940552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24225378036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35087513923645</t>
   </si>
   <si>
     <t xml:space="preserve">2.31984066963196</t>
@@ -1451,7 +1448,7 @@
     <t xml:space="preserve">2.35863375663757</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40518569946289</t>
+    <t xml:space="preserve">2.40518593788147</t>
   </si>
   <si>
     <t xml:space="preserve">2.3819100856781</t>
@@ -1460,10 +1457,10 @@
     <t xml:space="preserve">2.38966822624207</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39742732048035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41294479370117</t>
+    <t xml:space="preserve">2.39742708206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41294455528259</t>
   </si>
   <si>
     <t xml:space="preserve">2.42070317268372</t>
@@ -1475,13 +1472,13 @@
     <t xml:space="preserve">2.34311652183533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37415099143982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45173764228821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47501397132874</t>
+    <t xml:space="preserve">2.37415146827698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45173788070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47501373291016</t>
   </si>
   <si>
     <t xml:space="preserve">2.55260062217712</t>
@@ -1490,7 +1487,7 @@
     <t xml:space="preserve">2.5444712638855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52008318901062</t>
+    <t xml:space="preserve">2.5200834274292</t>
   </si>
   <si>
     <t xml:space="preserve">2.4956955909729</t>
@@ -1514,19 +1511,19 @@
     <t xml:space="preserve">2.40627312660217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43066072463989</t>
+    <t xml:space="preserve">2.43066120147705</t>
   </si>
   <si>
     <t xml:space="preserve">2.42253160476685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3656268119812</t>
+    <t xml:space="preserve">2.36562657356262</t>
   </si>
   <si>
     <t xml:space="preserve">2.39001441001892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2843337059021</t>
+    <t xml:space="preserve">2.28433346748352</t>
   </si>
   <si>
     <t xml:space="preserve">2.27620434761047</t>
@@ -1535,7 +1532,7 @@
     <t xml:space="preserve">2.2274284362793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23555755615234</t>
+    <t xml:space="preserve">2.23555779457092</t>
   </si>
   <si>
     <t xml:space="preserve">2.25181651115417</t>
@@ -1547,13 +1544,13 @@
     <t xml:space="preserve">2.357497215271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32498002052307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34123873710632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37375593185425</t>
+    <t xml:space="preserve">2.32498025894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34123849868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37375617027283</t>
   </si>
   <si>
     <t xml:space="preserve">2.4631781578064</t>
@@ -1562,25 +1559,25 @@
     <t xml:space="preserve">2.51195383071899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52821254730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53634214401245</t>
+    <t xml:space="preserve">2.52821278572083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53634190559387</t>
   </si>
   <si>
     <t xml:space="preserve">2.58511757850647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59324717521667</t>
+    <t xml:space="preserve">2.5932469367981</t>
   </si>
   <si>
     <t xml:space="preserve">2.56072998046875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6013765335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60950541496277</t>
+    <t xml:space="preserve">2.60137629508972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60950565338135</t>
   </si>
   <si>
     <t xml:space="preserve">2.5688591003418</t>
@@ -1589,6 +1586,9 @@
     <t xml:space="preserve">2.57698845863342</t>
   </si>
   <si>
+    <t xml:space="preserve">2.55260038375854</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.4144024848938</t>
   </si>
   <si>
@@ -1601,7 +1601,7 @@
     <t xml:space="preserve">2.39814376831055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47130751609802</t>
+    <t xml:space="preserve">2.47130727767944</t>
   </si>
   <si>
     <t xml:space="preserve">2.44691967964172</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">2.12987685203552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08110117912292</t>
+    <t xml:space="preserve">2.08110094070435</t>
   </si>
   <si>
     <t xml:space="preserve">2.10548901557922</t>
@@ -1637,46 +1637,46 @@
     <t xml:space="preserve">2.1217474937439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.048583984375</t>
+    <t xml:space="preserve">2.04858374595642</t>
   </si>
   <si>
     <t xml:space="preserve">1.89412713050842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65837740898132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66650664806366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6258602142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47140347957611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50392067432404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51205003261566</t>
+    <t xml:space="preserve">1.65837728977203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66650676727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62586009502411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4714035987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50392079353333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51205015182495</t>
   </si>
   <si>
     <t xml:space="preserve">1.61366617679596</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55676090717316</t>
+    <t xml:space="preserve">1.55676102638245</t>
   </si>
   <si>
     <t xml:space="preserve">1.5486319065094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53237330913544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4957914352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58521378040314</t>
+    <t xml:space="preserve">1.53237318992615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49579131603241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58521366119385</t>
   </si>
   <si>
     <t xml:space="preserve">1.60147225856781</t>
@@ -1688,13 +1688,13 @@
     <t xml:space="preserve">1.56082582473755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58114922046661</t>
+    <t xml:space="preserve">1.58114910125732</t>
   </si>
   <si>
     <t xml:space="preserve">1.5689549446106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63398969173431</t>
+    <t xml:space="preserve">1.6339898109436</t>
   </si>
   <si>
     <t xml:space="preserve">1.69089460372925</t>
@@ -1712,13 +1712,13 @@
     <t xml:space="preserve">1.61773085594177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67463612556458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7071533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76405847072601</t>
+    <t xml:space="preserve">1.67463600635529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70715320110321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76405835151672</t>
   </si>
   <si>
     <t xml:space="preserve">1.73154103755951</t>
@@ -1727,22 +1727,22 @@
     <t xml:space="preserve">1.71528244018555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69902384281158</t>
+    <t xml:space="preserve">1.69902396202087</t>
   </si>
   <si>
     <t xml:space="preserve">1.6502480506897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74779975414276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75592887401581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77218759059906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7884464263916</t>
+    <t xml:space="preserve">1.74779987335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75592911243439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77218747138977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78844630718231</t>
   </si>
   <si>
     <t xml:space="preserve">1.82096338272095</t>
@@ -1751,22 +1751,22 @@
     <t xml:space="preserve">1.87786841392517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82909286022186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80470490455627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81283402442932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79657554626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7803168296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72341179847717</t>
+    <t xml:space="preserve">1.82909274101257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80470502376556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81283414363861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79657530784607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78031694889069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72341191768646</t>
   </si>
   <si>
     <t xml:space="preserve">1.73967039585114</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">1.60960161685944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64211881160736</t>
+    <t xml:space="preserve">1.64211893081665</t>
   </si>
   <si>
     <t xml:space="preserve">1.57708442211151</t>
@@ -1787,16 +1787,16 @@
     <t xml:space="preserve">1.52830851078033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53643798828125</t>
+    <t xml:space="preserve">1.53643774986267</t>
   </si>
   <si>
     <t xml:space="preserve">1.49985611438751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48766195774078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48359751701355</t>
+    <t xml:space="preserve">1.48766207695007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48359727859497</t>
   </si>
   <si>
     <t xml:space="preserve">1.43075704574585</t>
@@ -1817,19 +1817,19 @@
     <t xml:space="preserve">1.4144983291626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36572253704071</t>
+    <t xml:space="preserve">1.36572241783142</t>
   </si>
   <si>
     <t xml:space="preserve">1.33320534229279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38198125362396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35759329795837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30475270748138</t>
+    <t xml:space="preserve">1.38198113441467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35759341716766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30475282669067</t>
   </si>
   <si>
     <t xml:space="preserve">1.29255878925323</t>
@@ -1838,7 +1838,7 @@
     <t xml:space="preserve">1.30881750583649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33727014064789</t>
+    <t xml:space="preserve">1.3372700214386</t>
   </si>
   <si>
     <t xml:space="preserve">1.32507598400116</t>
@@ -1847,19 +1847,19 @@
     <t xml:space="preserve">1.34946405887604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37385177612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35352873802185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39823997020721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40230429172516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3860456943512</t>
+    <t xml:space="preserve">1.37385189533234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35352861881256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39823985099792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40230441093445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38604581356049</t>
   </si>
   <si>
     <t xml:space="preserve">1.39011061191559</t>
@@ -1871,40 +1871,40 @@
     <t xml:space="preserve">1.4673388004303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.520179271698</t>
+    <t xml:space="preserve">1.52017939090729</t>
   </si>
   <si>
     <t xml:space="preserve">1.5526967048645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54456722736359</t>
+    <t xml:space="preserve">1.5445671081543</t>
   </si>
   <si>
     <t xml:space="preserve">1.49172675609589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52424395084381</t>
+    <t xml:space="preserve">1.52424383163452</t>
   </si>
   <si>
     <t xml:space="preserve">1.50798535346985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51611459255219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54050254821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47953283786774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86973917484283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95103204250336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0729718208313</t>
+    <t xml:space="preserve">1.51611471176147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54050266742706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47953271865845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86973929405212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95103216171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07297158241272</t>
   </si>
   <si>
     <t xml:space="preserve">2.25994563102722</t>
@@ -1919,10 +1919,10 @@
     <t xml:space="preserve">2.14613556861877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05671334266663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13800597190857</t>
+    <t xml:space="preserve">2.05671310424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13800621032715</t>
   </si>
   <si>
     <t xml:space="preserve">2.21116995811462</t>
@@ -1931,16 +1931,16 @@
     <t xml:space="preserve">2.21945142745972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2360143661499</t>
+    <t xml:space="preserve">2.23601460456848</t>
   </si>
   <si>
     <t xml:space="preserve">2.24429607391357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25257778167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20288825035095</t>
+    <t xml:space="preserve">2.25257754325867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20288848876953</t>
   </si>
   <si>
     <t xml:space="preserve">2.22773313522339</t>
@@ -1952,7 +1952,7 @@
     <t xml:space="preserve">2.17804384231567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.343674659729</t>
+    <t xml:space="preserve">2.34367442131042</t>
   </si>
   <si>
     <t xml:space="preserve">2.36023759841919</t>
@@ -1961,7 +1961,7 @@
     <t xml:space="preserve">2.36851906776428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38508224487305</t>
+    <t xml:space="preserve">2.38508200645447</t>
   </si>
   <si>
     <t xml:space="preserve">2.40164518356323</t>
@@ -1970,7 +1970,7 @@
     <t xml:space="preserve">2.45133447647095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47617888450623</t>
+    <t xml:space="preserve">2.4761791229248</t>
   </si>
   <si>
     <t xml:space="preserve">2.4844605922699</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">2.418208360672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39336347579956</t>
+    <t xml:space="preserve">2.39336371421814</t>
   </si>
   <si>
     <t xml:space="preserve">2.37680077552795</t>
@@ -1997,7 +1997,7 @@
     <t xml:space="preserve">2.42648983001709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33539319038391</t>
+    <t xml:space="preserve">2.33539295196533</t>
   </si>
   <si>
     <t xml:space="preserve">2.32711148262024</t>
@@ -2030,7 +2030,7 @@
     <t xml:space="preserve">2.12835454940796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13663601875305</t>
+    <t xml:space="preserve">2.13663625717163</t>
   </si>
   <si>
     <t xml:space="preserve">2.18632531166077</t>
@@ -2039,7 +2039,7 @@
     <t xml:space="preserve">2.08694696426392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1035099029541</t>
+    <t xml:space="preserve">2.10351014137268</t>
   </si>
   <si>
     <t xml:space="preserve">2.07038378715515</t>
@@ -2057,7 +2057,7 @@
     <t xml:space="preserve">2.26914072036743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26085925102234</t>
+    <t xml:space="preserve">2.26085901260376</t>
   </si>
   <si>
     <t xml:space="preserve">2.4099268913269</t>
@@ -2075,10 +2075,10 @@
     <t xml:space="preserve">2.50930500030518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62524652481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71634364128113</t>
+    <t xml:space="preserve">2.62524676322937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71634340286255</t>
   </si>
   <si>
     <t xml:space="preserve">2.69978022575378</t>
@@ -2096,13 +2096,13 @@
     <t xml:space="preserve">3.01447892189026</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03104162216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24636197090149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23808026313782</t>
+    <t xml:space="preserve">3.03104186058044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24636220932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2380805015564</t>
   </si>
   <si>
     <t xml:space="preserve">3.22979879379272</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">3.3043327331543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12213897705078</t>
+    <t xml:space="preserve">3.1221387386322</t>
   </si>
   <si>
     <t xml:space="preserve">3.1635468006134</t>
@@ -2132,7 +2132,7 @@
     <t xml:space="preserve">3.18010950088501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13042044639587</t>
+    <t xml:space="preserve">3.13042020797729</t>
   </si>
   <si>
     <t xml:space="preserve">3.10557556152344</t>
@@ -2144,7 +2144,7 @@
     <t xml:space="preserve">3.08901286125183</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07244944572449</t>
+    <t xml:space="preserve">3.07244968414307</t>
   </si>
   <si>
     <t xml:space="preserve">3.11385703086853</t>
@@ -2153,7 +2153,7 @@
     <t xml:space="preserve">3.08073139190674</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06416797637939</t>
+    <t xml:space="preserve">3.06416821479797</t>
   </si>
   <si>
     <t xml:space="preserve">3.254643201828</t>
@@ -2162,22 +2162,22 @@
     <t xml:space="preserve">3.09729433059692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93994498252869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02276039123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04760503768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05588674545288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15526485443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03932356834412</t>
+    <t xml:space="preserve">2.93994474411011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02276015281677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04760479927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0558865070343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15526509284973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03932332992554</t>
   </si>
   <si>
     <t xml:space="preserve">2.98963403701782</t>
@@ -2192,7 +2192,7 @@
     <t xml:space="preserve">2.97307133674622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20495438575745</t>
+    <t xml:space="preserve">3.20495414733887</t>
   </si>
   <si>
     <t xml:space="preserve">3.27948784828186</t>
@@ -18878,7 +18878,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G601" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -18904,7 +18904,7 @@
         <v>32</v>
       </c>
       <c r="G602" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -18930,7 +18930,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G603" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18956,7 +18956,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G604" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19008,7 +19008,7 @@
         <v>32</v>
       </c>
       <c r="G606" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19034,7 +19034,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G607" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19060,7 +19060,7 @@
         <v>30</v>
       </c>
       <c r="G608" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19086,7 +19086,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G609" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19112,7 +19112,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G610" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19138,7 +19138,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G611" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19164,7 +19164,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G612" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19190,7 +19190,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G613" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19216,7 +19216,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G614" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19242,7 +19242,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G615" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19268,7 +19268,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G616" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19294,7 +19294,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G617" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19320,7 +19320,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G618" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19346,7 +19346,7 @@
         <v>28</v>
       </c>
       <c r="G619" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19372,7 +19372,7 @@
         <v>28</v>
       </c>
       <c r="G620" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19398,7 +19398,7 @@
         <v>28</v>
       </c>
       <c r="G621" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19424,7 +19424,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G622" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19450,7 +19450,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G623" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19476,7 +19476,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G624" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19502,7 +19502,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G625" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19528,7 +19528,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G626" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19554,7 +19554,7 @@
         <v>29</v>
       </c>
       <c r="G627" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19580,7 +19580,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G628" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19606,7 +19606,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G629" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19632,7 +19632,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G630" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19658,7 +19658,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G631" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19684,7 +19684,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G632" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19710,7 +19710,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G633" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19736,7 +19736,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G634" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19762,7 +19762,7 @@
         <v>27.5</v>
       </c>
       <c r="G635" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19788,7 +19788,7 @@
         <v>27</v>
       </c>
       <c r="G636" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19814,7 +19814,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G637" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19840,7 +19840,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G638" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19866,7 +19866,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G639" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19892,7 +19892,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G640" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19918,7 +19918,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G641" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -19944,7 +19944,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G642" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19970,7 +19970,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G643" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19996,7 +19996,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G644" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20022,7 +20022,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G645" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20048,7 +20048,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G646" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20074,7 +20074,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G647" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20100,7 +20100,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G648" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20126,7 +20126,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G649" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20152,7 +20152,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G650" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20178,7 +20178,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G651" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20204,7 +20204,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G652" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20230,7 +20230,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G653" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20256,7 +20256,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G654" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20282,7 +20282,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G655" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20308,7 +20308,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G656" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20334,7 +20334,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G657" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20360,7 +20360,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G658" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20386,7 +20386,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G659" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20412,7 +20412,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G660" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20438,7 +20438,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G661" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20464,7 +20464,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G662" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20490,7 +20490,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G663" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -20516,7 +20516,7 @@
         <v>27.5</v>
       </c>
       <c r="G664" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20542,7 +20542,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G665" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20568,7 +20568,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G666" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20594,7 +20594,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G667" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20620,7 +20620,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G668" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20646,7 +20646,7 @@
         <v>27</v>
       </c>
       <c r="G669" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20672,7 +20672,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G670" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20698,7 +20698,7 @@
         <v>27</v>
       </c>
       <c r="G671" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20724,7 +20724,7 @@
         <v>26</v>
       </c>
       <c r="G672" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20750,7 +20750,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G673" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20776,7 +20776,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G674" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20802,7 +20802,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G675" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20828,7 +20828,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G676" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20854,7 +20854,7 @@
         <v>25</v>
       </c>
       <c r="G677" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20880,7 +20880,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G678" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20906,7 +20906,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G679" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -20932,7 +20932,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G680" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -20958,7 +20958,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G681" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -20984,7 +20984,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G682" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21010,7 +21010,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G683" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21036,7 +21036,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G684" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21062,7 +21062,7 @@
         <v>24</v>
       </c>
       <c r="G685" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21088,7 +21088,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G686" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21114,7 +21114,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G687" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21140,7 +21140,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G688" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21166,7 +21166,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G689" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21192,7 +21192,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G690" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21218,7 +21218,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G691" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21244,7 +21244,7 @@
         <v>27</v>
       </c>
       <c r="G692" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21270,7 +21270,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G693" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21296,7 +21296,7 @@
         <v>26</v>
       </c>
       <c r="G694" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21322,7 +21322,7 @@
         <v>26</v>
       </c>
       <c r="G695" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21348,7 +21348,7 @@
         <v>26</v>
       </c>
       <c r="G696" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21374,7 +21374,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G697" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21400,7 +21400,7 @@
         <v>26</v>
       </c>
       <c r="G698" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21426,7 +21426,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G699" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21452,7 +21452,7 @@
         <v>26</v>
       </c>
       <c r="G700" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21478,7 +21478,7 @@
         <v>25.5</v>
       </c>
       <c r="G701" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21504,7 +21504,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G702" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -21530,7 +21530,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G703" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21556,7 +21556,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G704" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21582,7 +21582,7 @@
         <v>26</v>
       </c>
       <c r="G705" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21608,7 +21608,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G706" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21634,7 +21634,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G707" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21660,7 +21660,7 @@
         <v>25.5</v>
       </c>
       <c r="G708" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21686,7 +21686,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G709" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21712,7 +21712,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G710" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21738,7 +21738,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G711" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21764,7 +21764,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G712" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21790,7 +21790,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G713" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21816,7 +21816,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G714" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21842,7 +21842,7 @@
         <v>24</v>
       </c>
       <c r="G715" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21868,7 +21868,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G716" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21894,7 +21894,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G717" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21920,7 +21920,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G718" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -21946,7 +21946,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G719" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -21972,7 +21972,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G720" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21998,7 +21998,7 @@
         <v>22.5</v>
       </c>
       <c r="G721" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22024,7 +22024,7 @@
         <v>23.5</v>
       </c>
       <c r="G722" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22050,7 +22050,7 @@
         <v>23.5</v>
       </c>
       <c r="G723" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22076,7 +22076,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G724" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22102,7 +22102,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G725" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22128,7 +22128,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G726" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22154,7 +22154,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G727" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22180,7 +22180,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G728" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22206,7 +22206,7 @@
         <v>25</v>
       </c>
       <c r="G729" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22232,7 +22232,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G730" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22258,7 +22258,7 @@
         <v>28</v>
       </c>
       <c r="G731" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22284,7 +22284,7 @@
         <v>28.5</v>
       </c>
       <c r="G732" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22310,7 +22310,7 @@
         <v>27.5</v>
       </c>
       <c r="G733" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22336,7 +22336,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G734" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22362,7 +22362,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G735" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22388,7 +22388,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G736" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22414,7 +22414,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G737" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22440,7 +22440,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G738" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22466,7 +22466,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G739" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -22492,7 +22492,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G740" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -22518,7 +22518,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G741" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22544,7 +22544,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G742" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22570,7 +22570,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G743" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22596,7 +22596,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G744" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22622,7 +22622,7 @@
         <v>27.5</v>
       </c>
       <c r="G745" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22648,7 +22648,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G746" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22674,7 +22674,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G747" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22700,7 +22700,7 @@
         <v>27.5</v>
       </c>
       <c r="G748" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22726,7 +22726,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G749" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22752,7 +22752,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G750" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22778,7 +22778,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G751" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22804,7 +22804,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G752" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22830,7 +22830,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G753" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22856,7 +22856,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G754" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22882,7 +22882,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G755" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22908,7 +22908,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G756" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -22934,7 +22934,7 @@
         <v>26.5</v>
       </c>
       <c r="G757" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -22960,7 +22960,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G758" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -22986,7 +22986,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G759" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23012,7 +23012,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G760" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23038,7 +23038,7 @@
         <v>27</v>
       </c>
       <c r="G761" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23064,7 +23064,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G762" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23090,7 +23090,7 @@
         <v>27</v>
       </c>
       <c r="G763" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23116,7 +23116,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G764" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23142,7 +23142,7 @@
         <v>26.5</v>
       </c>
       <c r="G765" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23168,7 +23168,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G766" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23194,7 +23194,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G767" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23220,7 +23220,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G768" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23246,7 +23246,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G769" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23272,7 +23272,7 @@
         <v>28.5</v>
       </c>
       <c r="G770" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23298,7 +23298,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G771" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23324,7 +23324,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G772" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23350,7 +23350,7 @@
         <v>28</v>
       </c>
       <c r="G773" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23376,7 +23376,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G774" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23402,7 +23402,7 @@
         <v>28</v>
       </c>
       <c r="G775" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23428,7 +23428,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G776" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23454,7 +23454,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G777" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23480,7 +23480,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G778" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -23506,7 +23506,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G779" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -23532,7 +23532,7 @@
         <v>28.5</v>
       </c>
       <c r="G780" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23558,7 +23558,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G781" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23584,7 +23584,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G782" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23610,7 +23610,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G783" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23636,7 +23636,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G784" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23662,7 +23662,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G785" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23688,7 +23688,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G786" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23714,7 +23714,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G787" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23740,7 +23740,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G788" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23766,7 +23766,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G789" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23792,7 +23792,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G790" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23818,7 +23818,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G791" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23844,7 +23844,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G792" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23870,7 +23870,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G793" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23896,7 +23896,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G794" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23922,7 +23922,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G795" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -23948,7 +23948,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G796" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -23974,7 +23974,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G797" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24000,7 +24000,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G798" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24026,7 +24026,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G799" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24052,7 +24052,7 @@
         <v>30</v>
       </c>
       <c r="G800" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24078,7 +24078,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G801" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24104,7 +24104,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G802" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24130,7 +24130,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G803" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24156,7 +24156,7 @@
         <v>31</v>
       </c>
       <c r="G804" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24182,7 +24182,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G805" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24208,7 +24208,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G806" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24234,7 +24234,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G807" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24260,7 +24260,7 @@
         <v>31</v>
       </c>
       <c r="G808" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24286,7 +24286,7 @@
         <v>31</v>
       </c>
       <c r="G809" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24312,7 +24312,7 @@
         <v>31</v>
       </c>
       <c r="G810" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24338,7 +24338,7 @@
         <v>31</v>
       </c>
       <c r="G811" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24364,7 +24364,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G812" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24390,7 +24390,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G813" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24416,7 +24416,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G814" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24442,7 +24442,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G815" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24468,7 +24468,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G816" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -24494,7 +24494,7 @@
         <v>31</v>
       </c>
       <c r="G817" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -24520,7 +24520,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G818" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24546,7 +24546,7 @@
         <v>31</v>
       </c>
       <c r="G819" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24572,7 +24572,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G820" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24598,7 +24598,7 @@
         <v>30.5</v>
       </c>
       <c r="G821" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24624,7 +24624,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G822" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24650,7 +24650,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G823" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24676,7 +24676,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G824" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24702,7 +24702,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G825" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24728,7 +24728,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G826" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24754,7 +24754,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G827" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24780,7 +24780,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G828" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24806,7 +24806,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G829" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24832,7 +24832,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G830" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24858,7 +24858,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G831" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24884,7 +24884,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G832" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24910,7 +24910,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G833" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -24936,7 +24936,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G834" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -24962,7 +24962,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G835" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -24988,7 +24988,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G836" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25014,7 +25014,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G837" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25040,7 +25040,7 @@
         <v>31</v>
       </c>
       <c r="G838" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25066,7 +25066,7 @@
         <v>31</v>
       </c>
       <c r="G839" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25092,7 +25092,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G840" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25118,7 +25118,7 @@
         <v>30</v>
       </c>
       <c r="G841" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25144,7 +25144,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G842" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25170,7 +25170,7 @@
         <v>30.5</v>
       </c>
       <c r="G843" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25196,7 +25196,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G844" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25222,7 +25222,7 @@
         <v>30.5</v>
       </c>
       <c r="G845" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25248,7 +25248,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G846" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25274,7 +25274,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G847" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25300,7 +25300,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G848" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25326,7 +25326,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G849" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25352,7 +25352,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G850" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25378,7 +25378,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G851" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25404,7 +25404,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G852" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -25430,7 +25430,7 @@
         <v>28</v>
       </c>
       <c r="G853" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -25456,7 +25456,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G854" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -25482,7 +25482,7 @@
         <v>28</v>
       </c>
       <c r="G855" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -25508,7 +25508,7 @@
         <v>27.5</v>
       </c>
       <c r="G856" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25534,7 +25534,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G857" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25560,7 +25560,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G858" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25586,7 +25586,7 @@
         <v>27.5</v>
       </c>
       <c r="G859" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25612,7 +25612,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G860" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25638,7 +25638,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G861" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25664,7 +25664,7 @@
         <v>28</v>
       </c>
       <c r="G862" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25690,7 +25690,7 @@
         <v>29</v>
       </c>
       <c r="G863" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25716,7 +25716,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G864" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25742,7 +25742,7 @@
         <v>29</v>
       </c>
       <c r="G865" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25768,7 +25768,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G866" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -25794,7 +25794,7 @@
         <v>29</v>
       </c>
       <c r="G867" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25820,7 +25820,7 @@
         <v>29</v>
       </c>
       <c r="G868" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -25846,7 +25846,7 @@
         <v>29</v>
       </c>
       <c r="G869" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -25872,7 +25872,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G870" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -25898,7 +25898,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G871" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25924,7 +25924,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G872" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -25950,7 +25950,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G873" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -25976,7 +25976,7 @@
         <v>30.5</v>
       </c>
       <c r="G874" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -26002,7 +26002,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G875" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -26028,7 +26028,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G876" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -26054,7 +26054,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G877" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -26080,7 +26080,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G878" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -26106,7 +26106,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G879" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26132,7 +26132,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G880" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -26158,7 +26158,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G881" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -26184,7 +26184,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G882" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -26210,7 +26210,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G883" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -26236,7 +26236,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G884" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -26262,7 +26262,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G885" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -26288,7 +26288,7 @@
         <v>31.5</v>
       </c>
       <c r="G886" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -26314,7 +26314,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G887" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -26340,7 +26340,7 @@
         <v>32</v>
       </c>
       <c r="G888" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -26366,7 +26366,7 @@
         <v>31.5</v>
       </c>
       <c r="G889" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -26392,7 +26392,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G890" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -26418,7 +26418,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G891" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -26444,7 +26444,7 @@
         <v>32</v>
       </c>
       <c r="G892" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -26470,7 +26470,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G893" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -26496,7 +26496,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G894" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -26522,7 +26522,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26548,7 +26548,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G896" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -26574,7 +26574,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G897" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -26600,7 +26600,7 @@
         <v>31</v>
       </c>
       <c r="G898" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -26626,7 +26626,7 @@
         <v>31</v>
       </c>
       <c r="G899" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -26652,7 +26652,7 @@
         <v>31</v>
       </c>
       <c r="G900" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -26678,7 +26678,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G901" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -26704,7 +26704,7 @@
         <v>31</v>
       </c>
       <c r="G902" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -26730,7 +26730,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G903" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -26756,7 +26756,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G904" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -26782,7 +26782,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G905" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -26808,7 +26808,7 @@
         <v>31</v>
       </c>
       <c r="G906" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -26834,7 +26834,7 @@
         <v>31</v>
       </c>
       <c r="G907" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -26860,7 +26860,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G908" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -26886,7 +26886,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G909" t="s">
-        <v>490</v>
+        <v>524</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -26912,7 +26912,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G910" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -26938,7 +26938,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G911" t="s">
-        <v>490</v>
+        <v>524</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -26964,7 +26964,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G912" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -26990,7 +26990,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G913" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -27016,7 +27016,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G914" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -27042,7 +27042,7 @@
         <v>30</v>
       </c>
       <c r="G915" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -27068,7 +27068,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G916" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -27120,7 +27120,7 @@
         <v>29</v>
       </c>
       <c r="G918" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -27172,7 +27172,7 @@
         <v>29</v>
       </c>
       <c r="G920" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -27250,7 +27250,7 @@
         <v>29</v>
       </c>
       <c r="G923" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -27276,7 +27276,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G924" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -27302,7 +27302,7 @@
         <v>29</v>
       </c>
       <c r="G925" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -27328,7 +27328,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G926" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -27354,7 +27354,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G927" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -27380,7 +27380,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G928" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -27432,7 +27432,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G930" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -27458,7 +27458,7 @@
         <v>30.5</v>
       </c>
       <c r="G931" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -27484,7 +27484,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G932" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -27588,7 +27588,7 @@
         <v>30</v>
       </c>
       <c r="G936" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -27666,7 +27666,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G939" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -27692,7 +27692,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G940" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -27718,7 +27718,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G941" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -27744,7 +27744,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G942" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -27770,7 +27770,7 @@
         <v>30</v>
       </c>
       <c r="G943" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -27796,7 +27796,7 @@
         <v>30</v>
       </c>
       <c r="G944" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -27848,7 +27848,7 @@
         <v>30</v>
       </c>
       <c r="G946" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -27874,7 +27874,7 @@
         <v>30.5</v>
       </c>
       <c r="G947" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -27900,7 +27900,7 @@
         <v>30.5</v>
       </c>
       <c r="G948" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -27926,7 +27926,7 @@
         <v>30</v>
       </c>
       <c r="G949" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -27978,7 +27978,7 @@
         <v>30</v>
       </c>
       <c r="G951" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -28030,7 +28030,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G953" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -28082,7 +28082,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G955" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -28108,7 +28108,7 @@
         <v>30</v>
       </c>
       <c r="G956" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -28134,7 +28134,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G957" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -28160,7 +28160,7 @@
         <v>30</v>
       </c>
       <c r="G958" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -28186,7 +28186,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G959" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -28212,7 +28212,7 @@
         <v>30</v>
       </c>
       <c r="G960" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -28238,7 +28238,7 @@
         <v>30</v>
       </c>
       <c r="G961" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -28264,7 +28264,7 @@
         <v>30</v>
       </c>
       <c r="G962" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -28290,7 +28290,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G963" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -28316,7 +28316,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G964" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -28342,7 +28342,7 @@
         <v>30</v>
       </c>
       <c r="G965" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -28368,7 +28368,7 @@
         <v>30</v>
       </c>
       <c r="G966" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -28420,7 +28420,7 @@
         <v>30</v>
       </c>
       <c r="G968" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -28446,7 +28446,7 @@
         <v>30</v>
       </c>
       <c r="G969" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -28524,7 +28524,7 @@
         <v>30</v>
       </c>
       <c r="G972" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -28576,7 +28576,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G974" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -28602,7 +28602,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G975" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -28654,7 +28654,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G977" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -28680,7 +28680,7 @@
         <v>31</v>
       </c>
       <c r="G978" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28706,7 +28706,7 @@
         <v>31</v>
       </c>
       <c r="G979" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -28732,7 +28732,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G980" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28758,7 +28758,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G981" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -28784,7 +28784,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G982" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -28810,7 +28810,7 @@
         <v>31</v>
       </c>
       <c r="G983" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -28836,7 +28836,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G984" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -28862,7 +28862,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G985" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28888,7 +28888,7 @@
         <v>31</v>
       </c>
       <c r="G986" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -28914,7 +28914,7 @@
         <v>31.5</v>
       </c>
       <c r="G987" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -28940,7 +28940,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G988" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -28966,7 +28966,7 @@
         <v>31.5</v>
       </c>
       <c r="G989" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -28992,7 +28992,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G990" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -29018,7 +29018,7 @@
         <v>31.5</v>
       </c>
       <c r="G991" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -29044,7 +29044,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G992" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -29070,7 +29070,7 @@
         <v>31.5</v>
       </c>
       <c r="G993" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -29096,7 +29096,7 @@
         <v>31.5</v>
       </c>
       <c r="G994" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -29122,7 +29122,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G995" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -29148,7 +29148,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G996" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -29174,7 +29174,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G997" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -29200,7 +29200,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G998" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -29226,7 +29226,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G999" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -29252,7 +29252,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1000" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -29278,7 +29278,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1001" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -29304,7 +29304,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1002" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -29330,7 +29330,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1003" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -29356,7 +29356,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1004" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -29382,7 +29382,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1005" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -29408,7 +29408,7 @@
         <v>31</v>
       </c>
       <c r="G1006" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -29434,7 +29434,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1007" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -29460,7 +29460,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1008" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -29486,7 +29486,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1009" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -29512,7 +29512,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1010" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -29538,7 +29538,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1011" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -29564,7 +29564,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1012" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -29590,7 +29590,7 @@
         <v>30.5</v>
       </c>
       <c r="G1013" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -29616,7 +29616,7 @@
         <v>30.5</v>
       </c>
       <c r="G1014" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -29668,7 +29668,7 @@
         <v>30.5</v>
       </c>
       <c r="G1016" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -29720,7 +29720,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1018" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -29746,7 +29746,7 @@
         <v>30</v>
       </c>
       <c r="G1019" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -29772,7 +29772,7 @@
         <v>30.5</v>
       </c>
       <c r="G1020" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -29798,7 +29798,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1021" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -29824,7 +29824,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1022" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -29850,7 +29850,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1023" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -29876,7 +29876,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1024" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -29902,7 +29902,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1025" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -29928,7 +29928,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1026" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -29954,7 +29954,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1027" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -29980,7 +29980,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1028" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -30006,7 +30006,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1029" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -30032,7 +30032,7 @@
         <v>30</v>
       </c>
       <c r="G1030" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -30058,7 +30058,7 @@
         <v>30</v>
       </c>
       <c r="G1031" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -30084,7 +30084,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1032" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -30266,7 +30266,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1039" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -30292,7 +30292,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1040" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -30318,7 +30318,7 @@
         <v>28</v>
       </c>
       <c r="G1041" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -30448,7 +30448,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1046" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -30500,7 +30500,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1048" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -30526,7 +30526,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1049" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -30578,7 +30578,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1051" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -30604,7 +30604,7 @@
         <v>28</v>
       </c>
       <c r="G1052" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -30682,7 +30682,7 @@
         <v>27.5</v>
       </c>
       <c r="G1055" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -36948,7 +36948,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1296" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -36974,7 +36974,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1297" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -37026,7 +37026,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1299" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -37078,7 +37078,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1301" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -37104,7 +37104,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1302" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -37130,7 +37130,7 @@
         <v>29</v>
       </c>
       <c r="G1303" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -37156,7 +37156,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1304" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -37182,7 +37182,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1305" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -37286,7 +37286,7 @@
         <v>28</v>
       </c>
       <c r="G1309" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -37312,7 +37312,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1310" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -37338,7 +37338,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1311" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -37416,7 +37416,7 @@
         <v>28</v>
       </c>
       <c r="G1314" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -37442,7 +37442,7 @@
         <v>28</v>
       </c>
       <c r="G1315" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -37468,7 +37468,7 @@
         <v>28</v>
       </c>
       <c r="G1316" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -37832,7 +37832,7 @@
         <v>27.5</v>
       </c>
       <c r="G1330" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -38014,7 +38014,7 @@
         <v>27.5</v>
       </c>
       <c r="G1337" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -68546,7 +68546,7 @@
     </row>
     <row r="2512">
       <c r="A2512" s="1" t="n">
-        <v>45975.6710532407</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B2512" t="n">
         <v>2730</v>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -47,31 +47,31 @@
     <t xml:space="preserve">1.24544656276703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24330163002014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22256803512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21541845798492</t>
+    <t xml:space="preserve">1.24330174922943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22256815433502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21541857719421</t>
   </si>
   <si>
     <t xml:space="preserve">1.2218531370163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21470355987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23615217208862</t>
+    <t xml:space="preserve">1.21470367908478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23615229129791</t>
   </si>
   <si>
     <t xml:space="preserve">1.21327364444733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20683896541595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20111930370331</t>
+    <t xml:space="preserve">1.20683920383453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2011194229126</t>
   </si>
   <si>
     <t xml:space="preserve">1.20040452480316</t>
@@ -92,19 +92,19 @@
     <t xml:space="preserve">1.2468763589859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25116622447968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26475024223328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2354371547699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22542798519135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21041393280029</t>
+    <t xml:space="preserve">1.25116610527039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26475036144257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23543727397919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22542774677277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.210413813591</t>
   </si>
   <si>
     <t xml:space="preserve">1.22113811969757</t>
@@ -113,22 +113,22 @@
     <t xml:space="preserve">1.19397008419037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22685790061951</t>
+    <t xml:space="preserve">1.22685778141022</t>
   </si>
   <si>
     <t xml:space="preserve">1.20469439029694</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25831580162048</t>
+    <t xml:space="preserve">1.25831568241119</t>
   </si>
   <si>
     <t xml:space="preserve">1.265465259552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25903081893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26903986930847</t>
+    <t xml:space="preserve">1.25903058052063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26904010772705</t>
   </si>
   <si>
     <t xml:space="preserve">1.21684849262238</t>
@@ -149,19 +149,19 @@
     <t xml:space="preserve">1.27189970016479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2790492773056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26760995388031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25545573234558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26260554790497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24830627441406</t>
+    <t xml:space="preserve">1.27904903888702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2676100730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25545585155487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26260530948639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24830603599548</t>
   </si>
   <si>
     <t xml:space="preserve">1.2490211725235</t>
@@ -170,13 +170,13 @@
     <t xml:space="preserve">1.24258673191071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23686695098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23472213745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23400735855103</t>
+    <t xml:space="preserve">1.23686718940735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23472225666046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23400723934174</t>
   </si>
   <si>
     <t xml:space="preserve">1.25225365161896</t>
@@ -185,10 +185,10 @@
     <t xml:space="preserve">1.26176810264587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26835501194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27860140800476</t>
+    <t xml:space="preserve">1.26835513114929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27860128879547</t>
   </si>
   <si>
     <t xml:space="preserve">1.27640581130981</t>
@@ -197,10 +197,10 @@
     <t xml:space="preserve">1.27420997619629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27494192123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26323199272156</t>
+    <t xml:space="preserve">1.27494215965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26323187351227</t>
   </si>
   <si>
     <t xml:space="preserve">1.27128267288208</t>
@@ -209,46 +209,46 @@
     <t xml:space="preserve">1.26689112186432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28445637226105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.280797123909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2793333530426</t>
+    <t xml:space="preserve">1.28445649147034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28079700469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27933323383331</t>
   </si>
   <si>
     <t xml:space="preserve">1.27347826957703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27274632453918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26615929603577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28226089477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28811597824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28738415241241</t>
+    <t xml:space="preserve">1.27274644374847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26615941524506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2822607755661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28811585903168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28738403320312</t>
   </si>
   <si>
     <t xml:space="preserve">1.28299283981323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26396369934082</t>
+    <t xml:space="preserve">1.26396381855011</t>
   </si>
   <si>
     <t xml:space="preserve">1.24127531051636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24347102642059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22956514358521</t>
+    <t xml:space="preserve">1.2434709072113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22956526279449</t>
   </si>
   <si>
     <t xml:space="preserve">1.23468840122223</t>
@@ -260,25 +260,25 @@
     <t xml:space="preserve">1.20687675476074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20760858058929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18565237522125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17833340167999</t>
+    <t xml:space="preserve">1.20760869979858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18565213680267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1783332824707</t>
   </si>
   <si>
     <t xml:space="preserve">1.18784785270691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16955065727234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17101442813873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17028260231018</t>
+    <t xml:space="preserve">1.16955077648163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17101454734802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17028272151947</t>
   </si>
   <si>
     <t xml:space="preserve">1.18931150436401</t>
@@ -296,13 +296,13 @@
     <t xml:space="preserve">1.23907971382141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23834764957428</t>
+    <t xml:space="preserve">1.23834776878357</t>
   </si>
   <si>
     <t xml:space="preserve">1.23542022705078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20614492893219</t>
+    <t xml:space="preserve">1.20614469051361</t>
   </si>
   <si>
     <t xml:space="preserve">1.2310289144516</t>
@@ -311,22 +311,22 @@
     <t xml:space="preserve">1.19736230373383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21712327003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22297811508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23322451114655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23249268531799</t>
+    <t xml:space="preserve">1.2171231508255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22297835350037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23322463035583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23249280452728</t>
   </si>
   <si>
     <t xml:space="preserve">1.22883331775665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28518843650818</t>
+    <t xml:space="preserve">1.28518831729889</t>
   </si>
   <si>
     <t xml:space="preserve">1.25884068012238</t>
@@ -338,79 +338,79 @@
     <t xml:space="preserve">1.29909420013428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32324647903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31665945053101</t>
+    <t xml:space="preserve">1.32324635982513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31665933132172</t>
   </si>
   <si>
     <t xml:space="preserve">1.32763767242432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30348539352417</t>
+    <t xml:space="preserve">1.30348551273346</t>
   </si>
   <si>
     <t xml:space="preserve">1.31592750549316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31812310218811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29763031005859</t>
+    <t xml:space="preserve">1.3181232213974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29763042926788</t>
   </si>
   <si>
     <t xml:space="preserve">1.30275356769562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29982602596283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28884792327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29543483257294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30055785179138</t>
+    <t xml:space="preserve">1.29982614517212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28884768486023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29543471336365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30055809020996</t>
   </si>
   <si>
     <t xml:space="preserve">1.29836225509644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29323923587799</t>
+    <t xml:space="preserve">1.2932391166687</t>
   </si>
   <si>
     <t xml:space="preserve">1.29250729084015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30128979682922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30568099021912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26908683776855</t>
+    <t xml:space="preserve">1.30128991603851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3056812286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26908695697784</t>
   </si>
   <si>
     <t xml:space="preserve">1.26762318611145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24786233901978</t>
+    <t xml:space="preserve">1.24786221981049</t>
   </si>
   <si>
     <t xml:space="preserve">1.25518119335175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2654275894165</t>
+    <t xml:space="preserve">1.26542770862579</t>
   </si>
   <si>
     <t xml:space="preserve">1.28006517887115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25810885429382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25005781650543</t>
+    <t xml:space="preserve">1.25810873508453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25005805492401</t>
   </si>
   <si>
     <t xml:space="preserve">1.24054348468781</t>
@@ -425,25 +425,25 @@
     <t xml:space="preserve">1.23615205287933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23688399791718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2420072555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23176085948944</t>
+    <t xml:space="preserve">1.23688387870789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24200713634491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23176074028015</t>
   </si>
   <si>
     <t xml:space="preserve">1.20980441570282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21126818656921</t>
+    <t xml:space="preserve">1.21126806735992</t>
   </si>
   <si>
     <t xml:space="preserve">1.21858692169189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21492755413055</t>
+    <t xml:space="preserve">1.21492767333984</t>
   </si>
   <si>
     <t xml:space="preserve">1.19004344940186</t>
@@ -458,37 +458,37 @@
     <t xml:space="preserve">1.19297087192535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19663047790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22005069255829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21639144420624</t>
+    <t xml:space="preserve">1.19663035869598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22005081176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21639132499695</t>
   </si>
   <si>
     <t xml:space="preserve">1.25957238674164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27786946296692</t>
+    <t xml:space="preserve">1.27786934375763</t>
   </si>
   <si>
     <t xml:space="preserve">1.28592026233673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29470300674438</t>
+    <t xml:space="preserve">1.2947028875351</t>
   </si>
   <si>
     <t xml:space="preserve">1.29689848423004</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31007242202759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32544207572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34081149101257</t>
+    <t xml:space="preserve">1.31007254123688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32544219493866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34081161022186</t>
   </si>
   <si>
     <t xml:space="preserve">1.3334926366806</t>
@@ -518,10 +518,10 @@
     <t xml:space="preserve">1.32690572738647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3210506439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3459347486496</t>
+    <t xml:space="preserve">1.32105076313019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34593462944031</t>
   </si>
   <si>
     <t xml:space="preserve">1.36130440235138</t>
@@ -530,58 +530,58 @@
     <t xml:space="preserve">1.36057257652283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33276081085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34959423542023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33788394927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34373915195465</t>
+    <t xml:space="preserve">1.33276069164276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34959411621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33788406848907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34373903274536</t>
   </si>
   <si>
     <t xml:space="preserve">1.34520292282104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36349999904633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36789119243622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37667393684387</t>
+    <t xml:space="preserve">1.32910132408142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36349987983704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3678914308548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37667381763458</t>
   </si>
   <si>
     <t xml:space="preserve">1.38252902030945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39789879322052</t>
+    <t xml:space="preserve">1.39789855480194</t>
   </si>
   <si>
     <t xml:space="preserve">1.41253614425659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40668106079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40814483165741</t>
+    <t xml:space="preserve">1.40668118000031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4081449508667</t>
   </si>
   <si>
     <t xml:space="preserve">1.40887677669525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4030214548111</t>
+    <t xml:space="preserve">1.40302181243896</t>
   </si>
   <si>
     <t xml:space="preserve">1.39277541637421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36935484409332</t>
+    <t xml:space="preserve">1.36935496330261</t>
   </si>
   <si>
     <t xml:space="preserve">1.37886965274811</t>
@@ -593,16 +593,16 @@
     <t xml:space="preserve">1.40155780315399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49304330348969</t>
+    <t xml:space="preserve">1.49304342269897</t>
   </si>
   <si>
     <t xml:space="preserve">1.47621011734009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48206508159637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49157965183258</t>
+    <t xml:space="preserve">1.48206532001495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49157953262329</t>
   </si>
   <si>
     <t xml:space="preserve">1.50328993797302</t>
@@ -611,46 +611,46 @@
     <t xml:space="preserve">1.46742761135101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45864498615265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47913765907288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49523901939392</t>
+    <t xml:space="preserve">1.45864474773407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47913753986359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49523913860321</t>
   </si>
   <si>
     <t xml:space="preserve">1.49084794521332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48792040348053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52744221687317</t>
+    <t xml:space="preserve">1.48792028427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52744197845459</t>
   </si>
   <si>
     <t xml:space="preserve">1.50987672805786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53256547451019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52963757514954</t>
+    <t xml:space="preserve">1.53256523609161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52963769435883</t>
   </si>
   <si>
     <t xml:space="preserve">1.53183341026306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52817380428314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5149998664856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49963045120239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.498166680336</t>
+    <t xml:space="preserve">1.52817404270172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51500010490417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4996303319931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49816656112671</t>
   </si>
   <si>
     <t xml:space="preserve">1.48572444915771</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">1.47108709812164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48426079750061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46376800537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45498549938202</t>
+    <t xml:space="preserve">1.4842609167099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46376812458038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45498538017273</t>
   </si>
   <si>
     <t xml:space="preserve">1.48499274253845</t>
@@ -674,52 +674,52 @@
     <t xml:space="preserve">1.52085518836975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53768825531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58233332633972</t>
+    <t xml:space="preserve">1.53768837451935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58233344554901</t>
   </si>
   <si>
     <t xml:space="preserve">1.63126361370087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63427460193634</t>
+    <t xml:space="preserve">1.63427472114563</t>
   </si>
   <si>
     <t xml:space="preserve">1.64857757091522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63578045368195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66664397716522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66288018226624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6613746881485</t>
+    <t xml:space="preserve">1.63578033447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66664409637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66288042068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66137480735779</t>
   </si>
   <si>
     <t xml:space="preserve">1.76902151107788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80816578865051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84429883956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91656541824341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99485421180725</t>
+    <t xml:space="preserve">1.80816602706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84429907798767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91656529903412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99485409259796</t>
   </si>
   <si>
     <t xml:space="preserve">2.01367330551147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95345163345337</t>
+    <t xml:space="preserve">1.95345151424408</t>
   </si>
   <si>
     <t xml:space="preserve">1.9820568561554</t>
@@ -728,55 +728,55 @@
     <t xml:space="preserve">1.93011546134949</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83376038074493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9030157327652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90452122688293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9120489358902</t>
+    <t xml:space="preserve">1.83376049995422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90301549434662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90452110767365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91204905509949</t>
   </si>
   <si>
     <t xml:space="preserve">1.93538475036621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92258763313293</t>
+    <t xml:space="preserve">1.92258775234222</t>
   </si>
   <si>
     <t xml:space="preserve">1.91581284999847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88118505477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92860996723175</t>
+    <t xml:space="preserve">1.88118517398834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92861008644104</t>
   </si>
   <si>
     <t xml:space="preserve">1.92183494567871</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9255987405777</t>
+    <t xml:space="preserve">1.92559885978699</t>
   </si>
   <si>
     <t xml:space="preserve">1.94065427780151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92635154724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90376830101013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91957652568817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91882383823395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93237376213074</t>
+    <t xml:space="preserve">1.9263516664505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90376842021942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91957664489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91882371902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93237364292145</t>
   </si>
   <si>
     <t xml:space="preserve">1.94366538524628</t>
@@ -791,10 +791,10 @@
     <t xml:space="preserve">1.90753221511841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89699339866638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89473509788513</t>
+    <t xml:space="preserve">1.89699351787567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89473497867584</t>
   </si>
   <si>
     <t xml:space="preserve">1.87742114067078</t>
@@ -806,37 +806,37 @@
     <t xml:space="preserve">1.77052700519562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79762721061707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76826882362366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7946161031723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80741322040558</t>
+    <t xml:space="preserve">1.7976268529892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76826870441437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79461586475372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80741310119629</t>
   </si>
   <si>
     <t xml:space="preserve">1.83074915409088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84881567955017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82547986507416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81042397022247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82623255252838</t>
+    <t xml:space="preserve">1.84881579875946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82547950744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81042408943176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82623243331909</t>
   </si>
   <si>
     <t xml:space="preserve">1.83601856231689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83902990818024</t>
+    <t xml:space="preserve">1.83902955055237</t>
   </si>
   <si>
     <t xml:space="preserve">1.85257947444916</t>
@@ -848,25 +848,25 @@
     <t xml:space="preserve">1.84806287288666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84655737876892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83752417564392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89774596691132</t>
+    <t xml:space="preserve">1.84655749797821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83752393722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89774608612061</t>
   </si>
   <si>
     <t xml:space="preserve">1.91280174255371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9737765789032</t>
+    <t xml:space="preserve">1.97377622127533</t>
   </si>
   <si>
     <t xml:space="preserve">1.97151815891266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93086814880371</t>
+    <t xml:space="preserve">1.930868268013</t>
   </si>
   <si>
     <t xml:space="preserve">1.93613767623901</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">1.9210821390152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88796007633209</t>
+    <t xml:space="preserve">1.88796019554138</t>
   </si>
   <si>
     <t xml:space="preserve">1.88720715045929</t>
@@ -884,34 +884,34 @@
     <t xml:space="preserve">1.89548778533936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89322924613953</t>
+    <t xml:space="preserve">1.89322936534882</t>
   </si>
   <si>
     <t xml:space="preserve">1.869140625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85860180854797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85634362697601</t>
+    <t xml:space="preserve">1.85860204696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8563437461853</t>
   </si>
   <si>
     <t xml:space="preserve">1.85709631443024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85182678699493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86688244342804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88494896888733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87215185165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87064635753632</t>
+    <t xml:space="preserve">1.85182690620422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86688232421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88494884967804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87215209007263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87064611911774</t>
   </si>
   <si>
     <t xml:space="preserve">1.86161279678345</t>
@@ -923,52 +923,52 @@
     <t xml:space="preserve">1.86763501167297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87365734577179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86537683010101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84505200386047</t>
+    <t xml:space="preserve">1.87365746498108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8653769493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84505188465118</t>
   </si>
   <si>
     <t xml:space="preserve">1.84204077720642</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84731030464172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84279358386993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81795191764832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82397401332855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82849097251892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81569373607635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82021009922028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81117689609528</t>
+    <t xml:space="preserve">1.84731042385101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84279382228851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8179520368576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82397425174713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82849085330963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81569385528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82021045684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81117701530457</t>
   </si>
   <si>
     <t xml:space="preserve">1.81644642353058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81418800354004</t>
+    <t xml:space="preserve">1.81418788433075</t>
   </si>
   <si>
     <t xml:space="preserve">1.83526575565338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83225464820862</t>
+    <t xml:space="preserve">1.8322548866272</t>
   </si>
   <si>
     <t xml:space="preserve">1.82246840000153</t>
@@ -986,22 +986,22 @@
     <t xml:space="preserve">1.91731810569763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97979855537415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96474325656891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94667637348175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97076523303986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96775412559509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96248459815979</t>
+    <t xml:space="preserve">1.97979831695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96474313735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94667673110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97076535224915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96775424480438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96248471736908</t>
   </si>
   <si>
     <t xml:space="preserve">2.10325384140015</t>
@@ -1013,19 +1013,19 @@
     <t xml:space="preserve">2.02421236038208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98732650279999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99937057495117</t>
+    <t xml:space="preserve">1.9873263835907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99937069416046</t>
   </si>
   <si>
     <t xml:space="preserve">1.98582077026367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99033737182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96624886989594</t>
+    <t xml:space="preserve">1.99033749103546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96624851226807</t>
   </si>
   <si>
     <t xml:space="preserve">1.99861788749695</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">1.97603487968445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9828097820282</t>
+    <t xml:space="preserve">1.98280966281891</t>
   </si>
   <si>
     <t xml:space="preserve">2.02496528625488</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">2.06260371208191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07540082931519</t>
+    <t xml:space="preserve">2.07540106773376</t>
   </si>
   <si>
     <t xml:space="preserve">2.08142328262329</t>
@@ -1061,46 +1061,46 @@
     <t xml:space="preserve">2.07765936851501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09572601318359</t>
+    <t xml:space="preserve">2.09572577476501</t>
   </si>
   <si>
     <t xml:space="preserve">2.09045672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11153435707092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10024261474609</t>
+    <t xml:space="preserve">2.11153411865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10024237632751</t>
   </si>
   <si>
     <t xml:space="preserve">2.08669257164001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07013177871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06034588813782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05959296226501</t>
+    <t xml:space="preserve">2.07013130187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06034564971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05959272384644</t>
   </si>
   <si>
     <t xml:space="preserve">2.05884003639221</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07615399360657</t>
+    <t xml:space="preserve">2.07615375518799</t>
   </si>
   <si>
     <t xml:space="preserve">2.08368158340454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10400629043579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08518695831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13185930252075</t>
+    <t xml:space="preserve">2.10400676727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08518719673157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13185906410217</t>
   </si>
   <si>
     <t xml:space="preserve">2.19057559967041</t>
@@ -1109,28 +1109,28 @@
     <t xml:space="preserve">2.21315884590149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17552018165588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16799235343933</t>
+    <t xml:space="preserve">2.1755199432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16799259185791</t>
   </si>
   <si>
     <t xml:space="preserve">2.20563125610352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22068643569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31101989746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36371374130249</t>
+    <t xml:space="preserve">2.22068691253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31101942062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36371397972107</t>
   </si>
   <si>
     <t xml:space="preserve">2.31854724884033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33360314369202</t>
+    <t xml:space="preserve">2.33360290527344</t>
   </si>
   <si>
     <t xml:space="preserve">2.37124156951904</t>
@@ -1142,31 +1142,31 @@
     <t xml:space="preserve">2.28843641281128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2658531665802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28090858459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30349206924438</t>
+    <t xml:space="preserve">2.26585340499878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28090882301331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30349183082581</t>
   </si>
   <si>
     <t xml:space="preserve">2.29596424102783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25832533836365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19810366630554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18304800987244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43899178504944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38629722595215</t>
+    <t xml:space="preserve">2.25832557678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19810342788696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18304777145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43899130821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38629698753357</t>
   </si>
   <si>
     <t xml:space="preserve">2.55190777778625</t>
@@ -1181,22 +1181,22 @@
     <t xml:space="preserve">2.46157479286194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49168586730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46910214424133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40135264396667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43146371841431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47663021087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44651913642883</t>
+    <t xml:space="preserve">2.49168562889099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46910238265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40135288238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43146347999573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47663044929504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44651937484741</t>
   </si>
   <si>
     <t xml:space="preserve">2.40888047218323</t>
@@ -1211,19 +1211,19 @@
     <t xml:space="preserve">2.4164080619812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50674104690552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5293242931366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57587671279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5913941860199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58363509178162</t>
+    <t xml:space="preserve">2.5067412853241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52932453155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57587647438049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59139394760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5836353302002</t>
   </si>
   <si>
     <t xml:space="preserve">2.56035900115967</t>
@@ -1232,13 +1232,13 @@
     <t xml:space="preserve">2.50604844093323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51380753517151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52156567573547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54484152793884</t>
+    <t xml:space="preserve">2.51380729675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52156591415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54484176635742</t>
   </si>
   <si>
     <t xml:space="preserve">2.48277235031128</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">2.4982898235321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42846202850342</t>
+    <t xml:space="preserve">2.42846179008484</t>
   </si>
   <si>
     <t xml:space="preserve">2.32759928703308</t>
@@ -1256,16 +1256,16 @@
     <t xml:space="preserve">2.30432343482971</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28104710578918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31208181381226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22673654556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20346069335938</t>
+    <t xml:space="preserve">2.28104734420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31208157539368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22673678398132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2034604549408</t>
   </si>
   <si>
     <t xml:space="preserve">2.19570183753967</t>
@@ -1280,22 +1280,22 @@
     <t xml:space="preserve">2.25777125358582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1724259853363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11811518669128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18794345855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25001239776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12587380409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10259819030762</t>
+    <t xml:space="preserve">2.17242574691772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11811542510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18794322013855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25001263618469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12587404251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10259795188904</t>
   </si>
   <si>
     <t xml:space="preserve">2.13363265991211</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">2.08708071708679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07932209968567</t>
+    <t xml:space="preserve">2.07932186126709</t>
   </si>
   <si>
     <t xml:space="preserve">2.07156324386597</t>
@@ -1319,7 +1319,7 @@
     <t xml:space="preserve">2.14139127731323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16466736793518</t>
+    <t xml:space="preserve">2.1646671295166</t>
   </si>
   <si>
     <t xml:space="preserve">2.14914989471436</t>
@@ -1328,19 +1328,19 @@
     <t xml:space="preserve">2.18018460273743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29656457901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03276991844177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01725244522095</t>
+    <t xml:space="preserve">2.29656481742859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03277015686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01725268363953</t>
   </si>
   <si>
     <t xml:space="preserve">2.02501130104065</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0094940662384</t>
+    <t xml:space="preserve">2.00949382781982</t>
   </si>
   <si>
     <t xml:space="preserve">1.9707008600235</t>
@@ -1349,34 +1349,34 @@
     <t xml:space="preserve">1.9629420042038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93966591358185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8853554725647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.877596616745</t>
+    <t xml:space="preserve">1.93966603279114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88535535335541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87759673595428</t>
   </si>
   <si>
     <t xml:space="preserve">1.85432076454163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86983799934387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79225122928619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8388032913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83104467391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86207938194275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15690875053406</t>
+    <t xml:space="preserve">1.86983788013458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79225134849548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83880317211151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83104491233826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86207926273346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15690851211548</t>
   </si>
   <si>
     <t xml:space="preserve">2.06380462646484</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">2.0017352104187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97845923900604</t>
+    <t xml:space="preserve">1.97845947742462</t>
   </si>
   <si>
     <t xml:space="preserve">1.99397671222687</t>
@@ -1400,31 +1400,31 @@
     <t xml:space="preserve">1.84656190872192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80776882171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.753457903862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77673423290253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74569928646088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82328605651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89311408996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91639006137848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2112193107605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11035680770874</t>
+    <t xml:space="preserve">1.80776858329773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75345814228058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77673399448395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74569952487946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82328593730927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89311385154724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91638994216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21121907234192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11035656929016</t>
   </si>
   <si>
     <t xml:space="preserve">2.05604600906372</t>
@@ -1439,10 +1439,10 @@
     <t xml:space="preserve">2.35087513923645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31984066963196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3353579044342</t>
+    <t xml:space="preserve">2.31984043121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33535814285278</t>
   </si>
   <si>
     <t xml:space="preserve">2.35863375663757</t>
@@ -1451,16 +1451,16 @@
     <t xml:space="preserve">2.40518593788147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3819100856781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38966822624207</t>
+    <t xml:space="preserve">2.38190984725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38966846466064</t>
   </si>
   <si>
     <t xml:space="preserve">2.39742708206177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41294455528259</t>
+    <t xml:space="preserve">2.41294431686401</t>
   </si>
   <si>
     <t xml:space="preserve">2.42070317268372</t>
@@ -1472,19 +1472,19 @@
     <t xml:space="preserve">2.34311652183533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37415146827698</t>
+    <t xml:space="preserve">2.3741512298584</t>
   </si>
   <si>
     <t xml:space="preserve">2.45173788070679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47501373291016</t>
+    <t xml:space="preserve">2.47501397132874</t>
   </si>
   <si>
     <t xml:space="preserve">2.55260062217712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5444712638855</t>
+    <t xml:space="preserve">2.54447102546692</t>
   </si>
   <si>
     <t xml:space="preserve">2.5200834274292</t>
@@ -1502,10 +1502,10 @@
     <t xml:space="preserve">2.47943687438965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48756623268127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50382447242737</t>
+    <t xml:space="preserve">2.4875659942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50382471084595</t>
   </si>
   <si>
     <t xml:space="preserve">2.40627312660217</t>
@@ -1520,13 +1520,13 @@
     <t xml:space="preserve">2.36562657356262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39001441001892</t>
+    <t xml:space="preserve">2.3900146484375</t>
   </si>
   <si>
     <t xml:space="preserve">2.28433346748352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27620434761047</t>
+    <t xml:space="preserve">2.27620410919189</t>
   </si>
   <si>
     <t xml:space="preserve">2.2274284362793</t>
@@ -1541,13 +1541,13 @@
     <t xml:space="preserve">2.26807498931885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.357497215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32498025894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34123849868774</t>
+    <t xml:space="preserve">2.35749745368958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32498002052307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34123873710632</t>
   </si>
   <si>
     <t xml:space="preserve">2.37375617027283</t>
@@ -1559,10 +1559,10 @@
     <t xml:space="preserve">2.51195383071899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52821278572083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53634190559387</t>
+    <t xml:space="preserve">2.52821254730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53634214401245</t>
   </si>
   <si>
     <t xml:space="preserve">2.58511757850647</t>
@@ -1571,13 +1571,13 @@
     <t xml:space="preserve">2.5932469367981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56072998046875</t>
+    <t xml:space="preserve">2.56072974205017</t>
   </si>
   <si>
     <t xml:space="preserve">2.60137629508972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60950565338135</t>
+    <t xml:space="preserve">2.60950541496277</t>
   </si>
   <si>
     <t xml:space="preserve">2.5688591003418</t>
@@ -1589,10 +1589,10 @@
     <t xml:space="preserve">2.55260038375854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4144024848938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3331093788147</t>
+    <t xml:space="preserve">2.41440272331238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33310961723328</t>
   </si>
   <si>
     <t xml:space="preserve">2.34936809539795</t>
@@ -1610,25 +1610,25 @@
     <t xml:space="preserve">2.38188529014587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29246306419373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30872130393982</t>
+    <t xml:space="preserve">2.29246282577515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3087215423584</t>
   </si>
   <si>
     <t xml:space="preserve">2.30059218406677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11361813545227</t>
+    <t xml:space="preserve">2.11361837387085</t>
   </si>
   <si>
     <t xml:space="preserve">2.18678212165833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12987685203552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08110094070435</t>
+    <t xml:space="preserve">2.1298770904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08110117912292</t>
   </si>
   <si>
     <t xml:space="preserve">2.10548901557922</t>
@@ -1637,52 +1637,52 @@
     <t xml:space="preserve">2.1217474937439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04858374595642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89412713050842</t>
+    <t xml:space="preserve">2.048583984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89412701129913</t>
   </si>
   <si>
     <t xml:space="preserve">1.65837728977203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66650676727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62586009502411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4714035987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50392079353333</t>
+    <t xml:space="preserve">1.66650664806366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6258602142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47140347957611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50392067432404</t>
   </si>
   <si>
     <t xml:space="preserve">1.51205015182495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61366617679596</t>
+    <t xml:space="preserve">1.61366629600525</t>
   </si>
   <si>
     <t xml:space="preserve">1.55676102638245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5486319065094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53237318992615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49579131603241</t>
+    <t xml:space="preserve">1.54863178730011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53237342834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4957914352417</t>
   </si>
   <si>
     <t xml:space="preserve">1.58521366119385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60147225856781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5730197429657</t>
+    <t xml:space="preserve">1.6014723777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57301986217499</t>
   </si>
   <si>
     <t xml:space="preserve">1.56082582473755</t>
@@ -1691,10 +1691,10 @@
     <t xml:space="preserve">1.58114910125732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5689549446106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6339898109436</t>
+    <t xml:space="preserve">1.56895506381989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63398969173431</t>
   </si>
   <si>
     <t xml:space="preserve">1.69089460372925</t>
@@ -1703,31 +1703,31 @@
     <t xml:space="preserve">1.60553693771362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62179565429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58927834033966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61773085594177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67463600635529</t>
+    <t xml:space="preserve">1.62179553508759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58927822113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61773073673248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67463612556458</t>
   </si>
   <si>
     <t xml:space="preserve">1.70715320110321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76405835151672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73154103755951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71528244018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69902396202087</t>
+    <t xml:space="preserve">1.76405847072601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7315411567688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71528255939484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69902384281158</t>
   </si>
   <si>
     <t xml:space="preserve">1.6502480506897</t>
@@ -1739,28 +1739,28 @@
     <t xml:space="preserve">1.75592911243439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77218747138977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78844630718231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82096338272095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87786841392517</t>
+    <t xml:space="preserve">1.77218759059906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78844618797302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82096326351166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87786865234375</t>
   </si>
   <si>
     <t xml:space="preserve">1.82909274101257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80470502376556</t>
+    <t xml:space="preserve">1.80470490455627</t>
   </si>
   <si>
     <t xml:space="preserve">1.81283414363861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79657530784607</t>
+    <t xml:space="preserve">1.79657566547394</t>
   </si>
   <si>
     <t xml:space="preserve">1.78031694889069</t>
@@ -1769,19 +1769,19 @@
     <t xml:space="preserve">1.72341191768646</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73967039585114</t>
+    <t xml:space="preserve">1.73967027664185</t>
   </si>
   <si>
     <t xml:space="preserve">1.68276536464691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60960161685944</t>
+    <t xml:space="preserve">1.60960149765015</t>
   </si>
   <si>
     <t xml:space="preserve">1.64211893081665</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57708442211151</t>
+    <t xml:space="preserve">1.57708430290222</t>
   </si>
   <si>
     <t xml:space="preserve">1.52830851078033</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">1.48766207695007</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48359727859497</t>
+    <t xml:space="preserve">1.48359739780426</t>
   </si>
   <si>
     <t xml:space="preserve">1.43075704574585</t>
@@ -1811,13 +1811,13 @@
     <t xml:space="preserve">1.40636897087097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43482172489166</t>
+    <t xml:space="preserve">1.43482160568237</t>
   </si>
   <si>
     <t xml:space="preserve">1.4144983291626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36572241783142</t>
+    <t xml:space="preserve">1.36572253704071</t>
   </si>
   <si>
     <t xml:space="preserve">1.33320534229279</t>
@@ -1826,10 +1826,10 @@
     <t xml:space="preserve">1.38198113441467</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35759341716766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30475282669067</t>
+    <t xml:space="preserve">1.35759329795837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30475270748138</t>
   </si>
   <si>
     <t xml:space="preserve">1.29255878925323</t>
@@ -1838,7 +1838,7 @@
     <t xml:space="preserve">1.30881750583649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3372700214386</t>
+    <t xml:space="preserve">1.33727014064789</t>
   </si>
   <si>
     <t xml:space="preserve">1.32507598400116</t>
@@ -1859,7 +1859,7 @@
     <t xml:space="preserve">1.40230441093445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38604581356049</t>
+    <t xml:space="preserve">1.3860456943512</t>
   </si>
   <si>
     <t xml:space="preserve">1.39011061191559</t>
@@ -1868,22 +1868,22 @@
     <t xml:space="preserve">1.37791657447815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4673388004303</t>
+    <t xml:space="preserve">1.46733868122101</t>
   </si>
   <si>
     <t xml:space="preserve">1.52017939090729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5526967048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5445671081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49172675609589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52424383163452</t>
+    <t xml:space="preserve">1.55269658565521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54456722736359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49172687530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52424395084381</t>
   </si>
   <si>
     <t xml:space="preserve">1.50798535346985</t>
@@ -1895,7 +1895,7 @@
     <t xml:space="preserve">1.54050266742706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47953271865845</t>
+    <t xml:space="preserve">1.47953283786774</t>
   </si>
   <si>
     <t xml:space="preserve">1.86973929405212</t>
@@ -1904,13 +1904,13 @@
     <t xml:space="preserve">1.95103216171265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07297158241272</t>
+    <t xml:space="preserve">2.0729718208313</t>
   </si>
   <si>
     <t xml:space="preserve">2.25994563102722</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24368715286255</t>
+    <t xml:space="preserve">2.24368691444397</t>
   </si>
   <si>
     <t xml:space="preserve">2.1786527633667</t>
@@ -1931,7 +1931,7 @@
     <t xml:space="preserve">2.21945142745972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23601460456848</t>
+    <t xml:space="preserve">2.2360143661499</t>
   </si>
   <si>
     <t xml:space="preserve">2.24429607391357</t>
@@ -1949,7 +1949,7 @@
     <t xml:space="preserve">2.19460678100586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17804384231567</t>
+    <t xml:space="preserve">2.17804360389709</t>
   </si>
   <si>
     <t xml:space="preserve">2.34367442131042</t>
@@ -1958,7 +1958,7 @@
     <t xml:space="preserve">2.36023759841919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36851906776428</t>
+    <t xml:space="preserve">2.36851930618286</t>
   </si>
   <si>
     <t xml:space="preserve">2.38508200645447</t>
@@ -1970,7 +1970,7 @@
     <t xml:space="preserve">2.45133447647095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4761791229248</t>
+    <t xml:space="preserve">2.47617888450623</t>
   </si>
   <si>
     <t xml:space="preserve">2.4844605922699</t>
@@ -1979,13 +1979,13 @@
     <t xml:space="preserve">2.49274230003357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.418208360672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39336371421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37680077552795</t>
+    <t xml:space="preserve">2.41820859909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39336347579956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37680053710938</t>
   </si>
   <si>
     <t xml:space="preserve">2.44305300712585</t>
@@ -2000,7 +2000,7 @@
     <t xml:space="preserve">2.33539295196533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32711148262024</t>
+    <t xml:space="preserve">2.32711124420166</t>
   </si>
   <si>
     <t xml:space="preserve">2.30226683616638</t>
@@ -2012,7 +2012,7 @@
     <t xml:space="preserve">2.31054830551147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35195589065552</t>
+    <t xml:space="preserve">2.3519561290741</t>
   </si>
   <si>
     <t xml:space="preserve">2.29398536682129</t>
@@ -2021,25 +2021,25 @@
     <t xml:space="preserve">2.28570365905762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27742218971252</t>
+    <t xml:space="preserve">2.2774224281311</t>
   </si>
   <si>
     <t xml:space="preserve">2.15319919586182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12835454940796</t>
+    <t xml:space="preserve">2.12835478782654</t>
   </si>
   <si>
     <t xml:space="preserve">2.13663625717163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18632531166077</t>
+    <t xml:space="preserve">2.18632507324219</t>
   </si>
   <si>
     <t xml:space="preserve">2.08694696426392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10351014137268</t>
+    <t xml:space="preserve">2.1035099029541</t>
   </si>
   <si>
     <t xml:space="preserve">2.07038378715515</t>
@@ -2048,7 +2048,7 @@
     <t xml:space="preserve">2.16976237297058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14491772651672</t>
+    <t xml:space="preserve">2.14491748809814</t>
   </si>
   <si>
     <t xml:space="preserve">2.16148066520691</t>
@@ -2057,22 +2057,22 @@
     <t xml:space="preserve">2.26914072036743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26085901260376</t>
+    <t xml:space="preserve">2.26085925102234</t>
   </si>
   <si>
     <t xml:space="preserve">2.4099268913269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46789741516113</t>
+    <t xml:space="preserve">2.46789717674255</t>
   </si>
   <si>
     <t xml:space="preserve">2.50102376937866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52586841583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50930500030518</t>
+    <t xml:space="preserve">2.52586817741394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50930523872375</t>
   </si>
   <si>
     <t xml:space="preserve">2.62524676322937</t>
@@ -2081,7 +2081,7 @@
     <t xml:space="preserve">2.71634340286255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69978022575378</t>
+    <t xml:space="preserve">2.69978046417236</t>
   </si>
   <si>
     <t xml:space="preserve">2.81572198867798</t>
@@ -2099,10 +2099,10 @@
     <t xml:space="preserve">3.03104186058044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24636220932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2380805015564</t>
+    <t xml:space="preserve">3.24636197090149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23808002471924</t>
   </si>
   <si>
     <t xml:space="preserve">3.22979879379272</t>
@@ -2111,16 +2111,16 @@
     <t xml:space="preserve">3.3043327331543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1221387386322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1635468006134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17182779312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21323561668396</t>
+    <t xml:space="preserve">3.12213897705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16354656219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17182803153992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21323585510254</t>
   </si>
   <si>
     <t xml:space="preserve">3.1883909702301</t>
@@ -2135,22 +2135,22 @@
     <t xml:space="preserve">3.13042020797729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10557556152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13870191574097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08901286125183</t>
+    <t xml:space="preserve">3.10557579994202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13870215415955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08901262283325</t>
   </si>
   <si>
     <t xml:space="preserve">3.07244968414307</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11385703086853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08073139190674</t>
+    <t xml:space="preserve">3.11385726928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08073115348816</t>
   </si>
   <si>
     <t xml:space="preserve">3.06416821479797</t>
@@ -2162,10 +2162,10 @@
     <t xml:space="preserve">3.09729433059692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93994474411011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02276015281677</t>
+    <t xml:space="preserve">2.93994498252869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02276039123535</t>
   </si>
   <si>
     <t xml:space="preserve">3.04760479927063</t>
@@ -2174,7 +2174,7 @@
     <t xml:space="preserve">3.0558865070343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15526509284973</t>
+    <t xml:space="preserve">3.15526485443115</t>
   </si>
   <si>
     <t xml:space="preserve">3.03932332992554</t>
@@ -2183,7 +2183,7 @@
     <t xml:space="preserve">2.98963403701782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00619745254517</t>
+    <t xml:space="preserve">3.00619721412659</t>
   </si>
   <si>
     <t xml:space="preserve">2.98135280609131</t>
@@ -2192,7 +2192,7 @@
     <t xml:space="preserve">2.97307133674622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20495414733887</t>
+    <t xml:space="preserve">3.20495438575745</t>
   </si>
   <si>
     <t xml:space="preserve">3.27948784828186</t>
@@ -2228,13 +2228,13 @@
     <t xml:space="preserve">4.95042657852173</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01585054397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5828595161438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36477899551392</t>
+    <t xml:space="preserve">5.01585006713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58285999298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36477947235107</t>
   </si>
   <si>
     <t xml:space="preserve">5.05946683883667</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">4.97223424911499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14669847488403</t>
+    <t xml:space="preserve">5.14669895172119</t>
   </si>
   <si>
     <t xml:space="preserve">5.08127450942993</t>
@@ -2252,7 +2252,7 @@
     <t xml:space="preserve">5.19031476974487</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21212291717529</t>
+    <t xml:space="preserve">5.21212244033813</t>
   </si>
   <si>
     <t xml:space="preserve">5.27754688262939</t>
@@ -2267,22 +2267,22 @@
     <t xml:space="preserve">5.47381925582886</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53924369812012</t>
+    <t xml:space="preserve">5.53924322128296</t>
   </si>
   <si>
     <t xml:space="preserve">5.45201110839844</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43020343780518</t>
+    <t xml:space="preserve">5.43020296096802</t>
   </si>
   <si>
     <t xml:space="preserve">5.40839529037476</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3429708480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38658714294434</t>
+    <t xml:space="preserve">5.34297132492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38658761978149</t>
   </si>
   <si>
     <t xml:space="preserve">5.32116317749023</t>
@@ -2294,19 +2294,19 @@
     <t xml:space="preserve">5.99721240997314</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82591819763184</t>
+    <t xml:space="preserve">6.82591772079468</t>
   </si>
   <si>
     <t xml:space="preserve">7.32750272750854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93495798110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78230237960815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73868560791016</t>
+    <t xml:space="preserve">6.93495845794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.782301902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73868608474731</t>
   </si>
   <si>
     <t xml:space="preserve">6.67326211929321</t>
@@ -2321,7 +2321,7 @@
     <t xml:space="preserve">6.25890922546387</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32433319091797</t>
+    <t xml:space="preserve">6.32433271408081</t>
   </si>
   <si>
     <t xml:space="preserve">6.23710107803345</t>
@@ -2336,28 +2336,28 @@
     <t xml:space="preserve">6.41156530380249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62964534759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76049423217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02219104766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0658073425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04399871826172</t>
+    <t xml:space="preserve">6.62964582443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76049375534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0221905708313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06580686569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04399824142456</t>
   </si>
   <si>
     <t xml:space="preserve">7.0876145362854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45835208892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52377510070801</t>
+    <t xml:space="preserve">7.45835161209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52377557754517</t>
   </si>
   <si>
     <t xml:space="preserve">7.78547239303589</t>
@@ -2369,7 +2369,7 @@
     <t xml:space="preserve">8.19982433319092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11259365081787</t>
+    <t xml:space="preserve">8.11259269714355</t>
   </si>
   <si>
     <t xml:space="preserve">8.37428951263428</t>
@@ -68570,6 +68570,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2513">
+      <c r="A2513" s="1" t="n">
+        <v>45978.3333333333</v>
+      </c>
+      <c r="B2513" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2513" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="D2513" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="E2513" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="F2513" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="G2513" t="s">
+        <v>893</v>
+      </c>
+      <c r="H2513" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" s="1" t="n">
+        <v>45979.4653819444</v>
+      </c>
+      <c r="B2514" t="n">
+        <v>1180</v>
+      </c>
+      <c r="C2514" t="n">
+        <v>2.60500001907349</v>
+      </c>
+      <c r="D2514" t="n">
+        <v>2.54500007629395</v>
+      </c>
+      <c r="E2514" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="F2514" t="n">
+        <v>2.60500001907349</v>
+      </c>
+      <c r="G2514" t="s">
+        <v>929</v>
+      </c>
+      <c r="H2514" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -44,46 +44,46 @@
     <t xml:space="preserve">AUTME.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24544656276703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24330174922943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22256815433502</t>
+    <t xml:space="preserve">1.24544668197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24330151081085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22256803512573</t>
   </si>
   <si>
     <t xml:space="preserve">1.21541857719421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2218531370163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21470367908478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23615229129791</t>
+    <t xml:space="preserve">1.22185301780701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2147034406662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23615217208862</t>
   </si>
   <si>
     <t xml:space="preserve">1.21327364444733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20683920383453</t>
+    <t xml:space="preserve">1.20683908462524</t>
   </si>
   <si>
     <t xml:space="preserve">1.2011194229126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20040452480316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16680181026459</t>
+    <t xml:space="preserve">1.20040464401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1668016910553</t>
   </si>
   <si>
     <t xml:space="preserve">1.1946849822998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25688576698303</t>
+    <t xml:space="preserve">1.25688564777374</t>
   </si>
   <si>
     <t xml:space="preserve">1.25045108795166</t>
@@ -95,25 +95,25 @@
     <t xml:space="preserve">1.25116610527039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26475036144257</t>
+    <t xml:space="preserve">1.26475012302399</t>
   </si>
   <si>
     <t xml:space="preserve">1.23543727397919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22542774677277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.210413813591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22113811969757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19397008419037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22685778141022</t>
+    <t xml:space="preserve">1.22542786598206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21041369438171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22113835811615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19396996498108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22685766220093</t>
   </si>
   <si>
     <t xml:space="preserve">1.20469439029694</t>
@@ -122,52 +122,52 @@
     <t xml:space="preserve">1.25831568241119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.265465259552</t>
+    <t xml:space="preserve">1.26546514034271</t>
   </si>
   <si>
     <t xml:space="preserve">1.25903058052063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26904010772705</t>
+    <t xml:space="preserve">1.26903986930847</t>
   </si>
   <si>
     <t xml:space="preserve">1.21684849262238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22828781604767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27404463291168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26689505577087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27261459827423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27189970016479</t>
+    <t xml:space="preserve">1.22828769683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27404451370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26689493656158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27261447906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27189993858337</t>
   </si>
   <si>
     <t xml:space="preserve">1.27904903888702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2676100730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25545585155487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26260530948639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24830603599548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2490211725235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24258673191071</t>
+    <t xml:space="preserve">1.26761019229889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25545608997345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26260542869568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24830627441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24902129173279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24258661270142</t>
   </si>
   <si>
     <t xml:space="preserve">1.23686718940735</t>
@@ -185,19 +185,19 @@
     <t xml:space="preserve">1.26176810264587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26835513114929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27860128879547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27640581130981</t>
+    <t xml:space="preserve">1.26835489273071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27860140800476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27640569210052</t>
   </si>
   <si>
     <t xml:space="preserve">1.27420997619629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27494215965271</t>
+    <t xml:space="preserve">1.27494204044342</t>
   </si>
   <si>
     <t xml:space="preserve">1.26323187351227</t>
@@ -206,34 +206,34 @@
     <t xml:space="preserve">1.27128267288208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26689112186432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28445649147034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28079700469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27933323383331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27347826957703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27274644374847</t>
+    <t xml:space="preserve">1.26689124107361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28445637226105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.280797123909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2793333530426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27347803115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27274632453918</t>
   </si>
   <si>
     <t xml:space="preserve">1.26615941524506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2822607755661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28811585903168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28738403320312</t>
+    <t xml:space="preserve">1.28226089477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28811597824097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28738415241241</t>
   </si>
   <si>
     <t xml:space="preserve">1.28299283981323</t>
@@ -242,13 +242,13 @@
     <t xml:space="preserve">1.26396381855011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24127531051636</t>
+    <t xml:space="preserve">1.24127519130707</t>
   </si>
   <si>
     <t xml:space="preserve">1.2434709072113</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22956526279449</t>
+    <t xml:space="preserve">1.22956514358521</t>
   </si>
   <si>
     <t xml:space="preserve">1.23468840122223</t>
@@ -260,25 +260,25 @@
     <t xml:space="preserve">1.20687675476074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20760869979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18565213680267</t>
+    <t xml:space="preserve">1.20760881900787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18565225601196</t>
   </si>
   <si>
     <t xml:space="preserve">1.1783332824707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18784785270691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16955077648163</t>
+    <t xml:space="preserve">1.18784773349762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16955065727234</t>
   </si>
   <si>
     <t xml:space="preserve">1.17101454734802</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17028272151947</t>
+    <t xml:space="preserve">1.17028248310089</t>
   </si>
   <si>
     <t xml:space="preserve">1.18931150436401</t>
@@ -290,19 +290,19 @@
     <t xml:space="preserve">1.22151458263397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23981165885925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23907971382141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23834776878357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23542022705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20614469051361</t>
+    <t xml:space="preserve">1.23981153964996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23907959461212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23834800720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23542010784149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2061448097229</t>
   </si>
   <si>
     <t xml:space="preserve">1.2310289144516</t>
@@ -314,7 +314,7 @@
     <t xml:space="preserve">1.2171231508255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22297835350037</t>
+    <t xml:space="preserve">1.22297823429108</t>
   </si>
   <si>
     <t xml:space="preserve">1.23322463035583</t>
@@ -323,13 +323,13 @@
     <t xml:space="preserve">1.23249280452728</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22883331775665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28518831729889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25884068012238</t>
+    <t xml:space="preserve">1.22883343696594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28518843650818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2588404417038</t>
   </si>
   <si>
     <t xml:space="preserve">1.30714499950409</t>
@@ -338,13 +338,13 @@
     <t xml:space="preserve">1.29909420013428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32324635982513</t>
+    <t xml:space="preserve">1.32324624061584</t>
   </si>
   <si>
     <t xml:space="preserve">1.31665933132172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32763767242432</t>
+    <t xml:space="preserve">1.32763743400574</t>
   </si>
   <si>
     <t xml:space="preserve">1.30348551273346</t>
@@ -359,31 +359,31 @@
     <t xml:space="preserve">1.29763042926788</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30275356769562</t>
+    <t xml:space="preserve">1.30275344848633</t>
   </si>
   <si>
     <t xml:space="preserve">1.29982614517212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28884768486023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29543471336365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30055809020996</t>
+    <t xml:space="preserve">1.28884780406952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29543483257294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30055797100067</t>
   </si>
   <si>
     <t xml:space="preserve">1.29836225509644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2932391166687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29250729084015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30128991603851</t>
+    <t xml:space="preserve">1.29323923587799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29250717163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30128979682922</t>
   </si>
   <si>
     <t xml:space="preserve">1.3056812286377</t>
@@ -395,28 +395,28 @@
     <t xml:space="preserve">1.26762318611145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24786221981049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25518119335175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26542770862579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28006517887115</t>
+    <t xml:space="preserve">1.24786233901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25518107414246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26542735099792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28006505966187</t>
   </si>
   <si>
     <t xml:space="preserve">1.25810873508453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25005805492401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24054348468781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24639868736267</t>
+    <t xml:space="preserve">1.2500581741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24054360389709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24639856815338</t>
   </si>
   <si>
     <t xml:space="preserve">1.24420285224915</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">1.23615205287933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23688387870789</t>
+    <t xml:space="preserve">1.23688411712646</t>
   </si>
   <si>
     <t xml:space="preserve">1.24200713634491</t>
@@ -440,28 +440,28 @@
     <t xml:space="preserve">1.21126806735992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21858692169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21492767333984</t>
+    <t xml:space="preserve">1.2185868024826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21492755413055</t>
   </si>
   <si>
     <t xml:space="preserve">1.19004344940186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18199265003204</t>
+    <t xml:space="preserve">1.18199276924133</t>
   </si>
   <si>
     <t xml:space="preserve">1.21419560909271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19297087192535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19663035869598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22005081176758</t>
+    <t xml:space="preserve">1.19297075271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19663047790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.220050573349</t>
   </si>
   <si>
     <t xml:space="preserve">1.21639132499695</t>
@@ -473,34 +473,34 @@
     <t xml:space="preserve">1.27786934375763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28592026233673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2947028875351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29689848423004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31007254123688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32544219493866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34081161022186</t>
+    <t xml:space="preserve">1.28592014312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29470300674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29689836502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31007242202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32544207572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34081172943115</t>
   </si>
   <si>
     <t xml:space="preserve">1.3334926366806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33422446250916</t>
+    <t xml:space="preserve">1.33422470092773</t>
   </si>
   <si>
     <t xml:space="preserve">1.3320289850235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33861601352692</t>
+    <t xml:space="preserve">1.33861589431763</t>
   </si>
   <si>
     <t xml:space="preserve">1.33934772014618</t>
@@ -512,46 +512,46 @@
     <t xml:space="preserve">1.34227526187897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34007966518402</t>
+    <t xml:space="preserve">1.34007954597473</t>
   </si>
   <si>
     <t xml:space="preserve">1.32690572738647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32105076313019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34593462944031</t>
+    <t xml:space="preserve">1.32105052471161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34593486785889</t>
   </si>
   <si>
     <t xml:space="preserve">1.36130440235138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36057257652283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33276069164276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34959411621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33788406848907</t>
+    <t xml:space="preserve">1.36057233810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33276093006134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34959435462952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33788418769836</t>
   </si>
   <si>
     <t xml:space="preserve">1.34373903274536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34520292282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32910132408142</t>
+    <t xml:space="preserve">1.34520280361176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32910144329071</t>
   </si>
   <si>
     <t xml:space="preserve">1.36349987983704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3678914308548</t>
+    <t xml:space="preserve">1.36789119243622</t>
   </si>
   <si>
     <t xml:space="preserve">1.37667381763458</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">1.41253614425659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40668118000031</t>
+    <t xml:space="preserve">1.40668094158173</t>
   </si>
   <si>
     <t xml:space="preserve">1.4081449508667</t>
@@ -575,19 +575,19 @@
     <t xml:space="preserve">1.40887677669525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40302181243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39277541637421</t>
+    <t xml:space="preserve">1.40302169322968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39277529716492</t>
   </si>
   <si>
     <t xml:space="preserve">1.36935496330261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37886965274811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38911581039429</t>
+    <t xml:space="preserve">1.37886953353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.389115691185</t>
   </si>
   <si>
     <t xml:space="preserve">1.40155780315399</t>
@@ -599,64 +599,64 @@
     <t xml:space="preserve">1.47621011734009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48206532001495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49157953262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50328993797302</t>
+    <t xml:space="preserve">1.48206520080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49157965183258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50329005718231</t>
   </si>
   <si>
     <t xml:space="preserve">1.46742761135101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45864474773407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47913753986359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49523913860321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49084794521332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48792028427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52744197845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50987672805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53256523609161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52963769435883</t>
+    <t xml:space="preserve">1.45864486694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47913765907288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4952392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49084782600403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48792016506195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52744209766388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50987660884857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53256511688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52963781356812</t>
   </si>
   <si>
     <t xml:space="preserve">1.53183341026306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52817404270172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51500010490417</t>
+    <t xml:space="preserve">1.52817392349243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51500022411346</t>
   </si>
   <si>
     <t xml:space="preserve">1.4996303319931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49816656112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48572444915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47108709812164</t>
+    <t xml:space="preserve">1.498166680336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.485724568367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47108697891235</t>
   </si>
   <si>
     <t xml:space="preserve">1.4842609167099</t>
@@ -665,31 +665,31 @@
     <t xml:space="preserve">1.46376812458038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45498538017273</t>
+    <t xml:space="preserve">1.45498549938202</t>
   </si>
   <si>
     <t xml:space="preserve">1.48499274253845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52085518836975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53768837451935</t>
+    <t xml:space="preserve">1.52085506916046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53768861293793</t>
   </si>
   <si>
     <t xml:space="preserve">1.58233344554901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63126361370087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63427472114563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64857757091522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63578033447266</t>
+    <t xml:space="preserve">1.63126373291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63427484035492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64857745170593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63578045368195</t>
   </si>
   <si>
     <t xml:space="preserve">1.66664409637451</t>
@@ -701,64 +701,64 @@
     <t xml:space="preserve">1.66137480735779</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76902151107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80816602706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84429907798767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91656529903412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99485409259796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01367330551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95345151424408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9820568561554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93011546134949</t>
+    <t xml:space="preserve">1.76902163028717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80816578865051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84429883956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9165655374527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99485433101654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01367354393005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95345163345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98205709457397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93011522293091</t>
   </si>
   <si>
     <t xml:space="preserve">1.83376049995422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90301549434662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90452110767365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91204905509949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93538475036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92258775234222</t>
+    <t xml:space="preserve">1.90301561355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90452086925507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91204869747162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9353848695755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92258763313293</t>
   </si>
   <si>
     <t xml:space="preserve">1.91581284999847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88118517398834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92861008644104</t>
+    <t xml:space="preserve">1.88118505477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92860996723175</t>
   </si>
   <si>
     <t xml:space="preserve">1.92183494567871</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92559885978699</t>
+    <t xml:space="preserve">1.92559897899628</t>
   </si>
   <si>
     <t xml:space="preserve">1.94065427780151</t>
@@ -773,25 +773,25 @@
     <t xml:space="preserve">1.91957664489746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91882371902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93237364292145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94366538524628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91054332256317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89021849632263</t>
+    <t xml:space="preserve">1.91882383823395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93237388134003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94366526603699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91054320335388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89021837711334</t>
   </si>
   <si>
     <t xml:space="preserve">1.90753221511841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89699351787567</t>
+    <t xml:space="preserve">1.89699327945709</t>
   </si>
   <si>
     <t xml:space="preserve">1.89473497867584</t>
@@ -800,22 +800,22 @@
     <t xml:space="preserve">1.87742114067078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86010730266571</t>
+    <t xml:space="preserve">1.860107421875</t>
   </si>
   <si>
     <t xml:space="preserve">1.77052700519562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7976268529892</t>
+    <t xml:space="preserve">1.79762709140778</t>
   </si>
   <si>
     <t xml:space="preserve">1.76826870441437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79461586475372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80741310119629</t>
+    <t xml:space="preserve">1.7946161031723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80741333961487</t>
   </si>
   <si>
     <t xml:space="preserve">1.83074915409088</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">1.84881579875946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82547950744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81042408943176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82623243331909</t>
+    <t xml:space="preserve">1.82547962665558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81042385101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82623255252838</t>
   </si>
   <si>
     <t xml:space="preserve">1.83601856231689</t>
@@ -842,199 +842,199 @@
     <t xml:space="preserve">1.85257947444916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82171583175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84806287288666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84655749797821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83752393722534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89774608612061</t>
+    <t xml:space="preserve">1.82171607017517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84806299209595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84655737876892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83752405643463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8977462053299</t>
   </si>
   <si>
     <t xml:space="preserve">1.91280174255371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97377622127533</t>
+    <t xml:space="preserve">1.9737765789032</t>
   </si>
   <si>
     <t xml:space="preserve">1.97151815891266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.930868268013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93613767623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9210821390152</t>
+    <t xml:space="preserve">1.93086802959442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93613755702972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92108237743378</t>
   </si>
   <si>
     <t xml:space="preserve">1.88796019554138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88720715045929</t>
+    <t xml:space="preserve">1.88720738887787</t>
   </si>
   <si>
     <t xml:space="preserve">1.89548778533936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89322936534882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.869140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85860204696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8563437461853</t>
+    <t xml:space="preserve">1.89322972297668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86914074420929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85860180854797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85634338855743</t>
   </si>
   <si>
     <t xml:space="preserve">1.85709631443024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85182690620422</t>
+    <t xml:space="preserve">1.85182702541351</t>
   </si>
   <si>
     <t xml:space="preserve">1.86688232421875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88494884967804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87215209007263</t>
+    <t xml:space="preserve">1.88494908809662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87215161323547</t>
   </si>
   <si>
     <t xml:space="preserve">1.87064611911774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86161279678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88193774223328</t>
+    <t xml:space="preserve">1.86161315441132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88193798065186</t>
   </si>
   <si>
     <t xml:space="preserve">1.86763501167297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87365746498108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8653769493103</t>
+    <t xml:space="preserve">1.87365734577179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86537671089172</t>
   </si>
   <si>
     <t xml:space="preserve">1.84505188465118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84204077720642</t>
+    <t xml:space="preserve">1.84204065799713</t>
   </si>
   <si>
     <t xml:space="preserve">1.84731042385101</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84279382228851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8179520368576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82397425174713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82849085330963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81569385528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82021045684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81117701530457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81644642353058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81418788433075</t>
+    <t xml:space="preserve">1.84279358386993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81795191764832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82397413253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82849097251892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81569373607635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82021021842957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81117689609528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.816446185112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81418812274933</t>
   </si>
   <si>
     <t xml:space="preserve">1.83526575565338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8322548866272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82246840000153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8503212928772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89849889278412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93689024448395</t>
+    <t xml:space="preserve">1.83225464820862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82246851921082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85032117366791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89849877357483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93689036369324</t>
   </si>
   <si>
     <t xml:space="preserve">1.91731810569763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97979831695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96474313735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94667673110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97076535224915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96775424480438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96248471736908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10325384140015</t>
+    <t xml:space="preserve">1.97979867458344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96474301815033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94667661190033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97076523303986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96775436401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96248459815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10325360298157</t>
   </si>
   <si>
     <t xml:space="preserve">2.04378437995911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02421236038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9873263835907</t>
+    <t xml:space="preserve">2.0242121219635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98732626438141</t>
   </si>
   <si>
     <t xml:space="preserve">1.99937069416046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98582077026367</t>
+    <t xml:space="preserve">1.98582088947296</t>
   </si>
   <si>
     <t xml:space="preserve">1.99033749103546</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96624851226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99861788749695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96549594402313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97603487968445</t>
+    <t xml:space="preserve">1.96624863147736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99861812591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96549618244171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97603476047516</t>
   </si>
   <si>
     <t xml:space="preserve">1.98280966281891</t>
@@ -1058,19 +1058,19 @@
     <t xml:space="preserve">2.08593988418579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07765936851501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09572577476501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09045672416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11153411865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10024237632751</t>
+    <t xml:space="preserve">2.07765960693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09572601318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09045648574829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11153435707092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10024261474609</t>
   </si>
   <si>
     <t xml:space="preserve">2.08669257164001</t>
@@ -1091,7 +1091,7 @@
     <t xml:space="preserve">2.07615375518799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08368158340454</t>
+    <t xml:space="preserve">2.08368134498596</t>
   </si>
   <si>
     <t xml:space="preserve">2.10400676727295</t>
@@ -1100,7 +1100,7 @@
     <t xml:space="preserve">2.08518719673157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13185906410217</t>
+    <t xml:space="preserve">2.13185930252075</t>
   </si>
   <si>
     <t xml:space="preserve">2.19057559967041</t>
@@ -1118,19 +1118,19 @@
     <t xml:space="preserve">2.20563125610352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22068691253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31101942062378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36371397972107</t>
+    <t xml:space="preserve">2.22068667411804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31101989746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36371421813965</t>
   </si>
   <si>
     <t xml:space="preserve">2.31854724884033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33360290527344</t>
+    <t xml:space="preserve">2.33360266685486</t>
   </si>
   <si>
     <t xml:space="preserve">2.37124156951904</t>
@@ -1139,16 +1139,16 @@
     <t xml:space="preserve">2.32607507705688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28843641281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26585340499878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28090882301331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30349183082581</t>
+    <t xml:space="preserve">2.2884361743927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2658531665802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28090858459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30349206924438</t>
   </si>
   <si>
     <t xml:space="preserve">2.29596424102783</t>
@@ -1160,76 +1160,76 @@
     <t xml:space="preserve">2.19810342788696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18304777145386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43899130821228</t>
+    <t xml:space="preserve">2.18304800987244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43899154663086</t>
   </si>
   <si>
     <t xml:space="preserve">2.38629698753357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55190777778625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5443799495697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61965751647949</t>
+    <t xml:space="preserve">2.55190801620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54438018798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61965727806091</t>
   </si>
   <si>
     <t xml:space="preserve">2.46157479286194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49168562889099</t>
+    <t xml:space="preserve">2.49168539047241</t>
   </si>
   <si>
     <t xml:space="preserve">2.46910238265991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40135288238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43146347999573</t>
+    <t xml:space="preserve">2.40135264396667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43146371841431</t>
   </si>
   <si>
     <t xml:space="preserve">2.47663044929504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44651937484741</t>
+    <t xml:space="preserve">2.44651913642883</t>
   </si>
   <si>
     <t xml:space="preserve">2.40888047218323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48415780067444</t>
+    <t xml:space="preserve">2.48415803909302</t>
   </si>
   <si>
     <t xml:space="preserve">2.45404672622681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4164080619812</t>
+    <t xml:space="preserve">2.41640830039978</t>
   </si>
   <si>
     <t xml:space="preserve">2.5067412853241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52932453155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57587647438049</t>
+    <t xml:space="preserve">2.5293242931366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57587671279907</t>
   </si>
   <si>
     <t xml:space="preserve">2.59139394760132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5836353302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56035900115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50604844093323</t>
+    <t xml:space="preserve">2.58363509178162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56035923957825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50604867935181</t>
   </si>
   <si>
     <t xml:space="preserve">2.51380729675293</t>
@@ -1241,6 +1241,9 @@
     <t xml:space="preserve">2.54484176635742</t>
   </si>
   <si>
+    <t xml:space="preserve">2.52932405471802</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.48277235031128</t>
   </si>
   <si>
@@ -1256,16 +1259,16 @@
     <t xml:space="preserve">2.30432343482971</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28104734420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31208157539368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22673678398132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2034604549408</t>
+    <t xml:space="preserve">2.28104710578918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31208181381226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22673654556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20346069335938</t>
   </si>
   <si>
     <t xml:space="preserve">2.19570183753967</t>
@@ -1274,16 +1277,16 @@
     <t xml:space="preserve">2.21897792816162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23449516296387</t>
+    <t xml:space="preserve">2.23449540138245</t>
   </si>
   <si>
     <t xml:space="preserve">2.25777125358582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17242574691772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11811542510986</t>
+    <t xml:space="preserve">2.1724259853363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11811518669128</t>
   </si>
   <si>
     <t xml:space="preserve">2.18794322013855</t>
@@ -1292,13 +1295,13 @@
     <t xml:space="preserve">2.25001263618469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12587404251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10259795188904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13363265991211</t>
+    <t xml:space="preserve">2.12587380409241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10259819030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13363242149353</t>
   </si>
   <si>
     <t xml:space="preserve">2.09483909606934</t>
@@ -1307,31 +1310,31 @@
     <t xml:space="preserve">2.08708071708679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07932186126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07156324386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0405285358429</t>
+    <t xml:space="preserve">2.07932162284851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07156348228455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04052877426147</t>
   </si>
   <si>
     <t xml:space="preserve">2.14139127731323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1646671295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14914989471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18018460273743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29656481742859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03277015686035</t>
+    <t xml:space="preserve">2.16466736793518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14915013313293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18018484115601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29656434059143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03276991844177</t>
   </si>
   <si>
     <t xml:space="preserve">2.01725268363953</t>
@@ -1340,55 +1343,55 @@
     <t xml:space="preserve">2.02501130104065</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00949382781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9707008600235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9629420042038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93966603279114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88535535335541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87759673595428</t>
+    <t xml:space="preserve">2.0094940662384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97070062160492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96294188499451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93966615200043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88535523414612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87759685516357</t>
   </si>
   <si>
     <t xml:space="preserve">1.85432076454163</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86983788013458</t>
+    <t xml:space="preserve">1.86983799934387</t>
   </si>
   <si>
     <t xml:space="preserve">1.79225134849548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83880317211151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83104491233826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86207926273346</t>
+    <t xml:space="preserve">1.83880364894867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83104479312897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86207950115204</t>
   </si>
   <si>
     <t xml:space="preserve">2.15690851211548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06380462646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0482873916626</t>
+    <t xml:space="preserve">2.06380438804626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04828715324402</t>
   </si>
   <si>
     <t xml:space="preserve">2.0017352104187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97845947742462</t>
+    <t xml:space="preserve">1.97845935821533</t>
   </si>
   <si>
     <t xml:space="preserve">1.99397671222687</t>
@@ -1397,40 +1400,40 @@
     <t xml:space="preserve">1.9241486787796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84656190872192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80776858329773</t>
+    <t xml:space="preserve">1.84656202793121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80776882171631</t>
   </si>
   <si>
     <t xml:space="preserve">1.75345814228058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77673399448395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74569952487946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82328593730927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89311385154724</t>
+    <t xml:space="preserve">1.77673411369324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74569964408875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82328605651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89311420917511</t>
   </si>
   <si>
     <t xml:space="preserve">1.91638994216919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21121907234192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11035656929016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05604600906372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26553010940552</t>
+    <t xml:space="preserve">2.2112193107605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11035680770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0560462474823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26552987098694</t>
   </si>
   <si>
     <t xml:space="preserve">2.24225378036499</t>
@@ -1439,37 +1442,37 @@
     <t xml:space="preserve">2.35087513923645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31984043121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33535814285278</t>
+    <t xml:space="preserve">2.31984066963196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3353579044342</t>
   </si>
   <si>
     <t xml:space="preserve">2.35863375663757</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40518593788147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38190984725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38966846466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39742708206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41294431686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42070317268372</t>
+    <t xml:space="preserve">2.40518569946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3819100856781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38966822624207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39742732048035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41294479370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42070293426514</t>
   </si>
   <si>
     <t xml:space="preserve">2.36639261245728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34311652183533</t>
+    <t xml:space="preserve">2.34311676025391</t>
   </si>
   <si>
     <t xml:space="preserve">2.3741512298584</t>
@@ -1478,19 +1481,19 @@
     <t xml:space="preserve">2.45173788070679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47501397132874</t>
+    <t xml:space="preserve">2.47501373291016</t>
   </si>
   <si>
     <t xml:space="preserve">2.55260062217712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54447102546692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5200834274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4956955909729</t>
+    <t xml:space="preserve">2.5444712638855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52008318901062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49569535255432</t>
   </si>
   <si>
     <t xml:space="preserve">2.4387903213501</t>
@@ -1499,40 +1502,40 @@
     <t xml:space="preserve">2.45504903793335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47943687438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4875659942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50382471084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40627312660217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43066120147705</t>
+    <t xml:space="preserve">2.47943663597107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48756623268127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50382447242737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40627288818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43066072463989</t>
   </si>
   <si>
     <t xml:space="preserve">2.42253160476685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36562657356262</t>
+    <t xml:space="preserve">2.3656268119812</t>
   </si>
   <si>
     <t xml:space="preserve">2.3900146484375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28433346748352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27620410919189</t>
+    <t xml:space="preserve">2.2843337059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27620434761047</t>
   </si>
   <si>
     <t xml:space="preserve">2.2274284362793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23555779457092</t>
+    <t xml:space="preserve">2.23555755615234</t>
   </si>
   <si>
     <t xml:space="preserve">2.25181651115417</t>
@@ -1550,7 +1553,7 @@
     <t xml:space="preserve">2.34123873710632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37375617027283</t>
+    <t xml:space="preserve">2.37375593185425</t>
   </si>
   <si>
     <t xml:space="preserve">2.4631781578064</t>
@@ -1562,19 +1565,19 @@
     <t xml:space="preserve">2.52821254730225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53634214401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58511757850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5932469367981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56072974205017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60137629508972</t>
+    <t xml:space="preserve">2.53634190559387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58511805534363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59324717521667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56072998046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6013765335083</t>
   </si>
   <si>
     <t xml:space="preserve">2.60950541496277</t>
@@ -1586,13 +1589,10 @@
     <t xml:space="preserve">2.57698845863342</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55260038375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41440272331238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33310961723328</t>
+    <t xml:space="preserve">2.4144024848938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3331093788147</t>
   </si>
   <si>
     <t xml:space="preserve">2.34936809539795</t>
@@ -1601,7 +1601,7 @@
     <t xml:space="preserve">2.39814376831055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47130727767944</t>
+    <t xml:space="preserve">2.47130751609802</t>
   </si>
   <si>
     <t xml:space="preserve">2.44691967964172</t>
@@ -1610,7 +1610,7 @@
     <t xml:space="preserve">2.38188529014587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29246282577515</t>
+    <t xml:space="preserve">2.29246306419373</t>
   </si>
   <si>
     <t xml:space="preserve">2.3087215423584</t>
@@ -1619,13 +1619,13 @@
     <t xml:space="preserve">2.30059218406677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11361837387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18678212165833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1298770904541</t>
+    <t xml:space="preserve">2.11361813545227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18678188323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12987685203552</t>
   </si>
   <si>
     <t xml:space="preserve">2.08110117912292</t>
@@ -1640,10 +1640,10 @@
     <t xml:space="preserve">2.048583984375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89412701129913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65837728977203</t>
+    <t xml:space="preserve">1.89412713050842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65837740898132</t>
   </si>
   <si>
     <t xml:space="preserve">1.66650664806366</t>
@@ -1661,40 +1661,40 @@
     <t xml:space="preserve">1.51205015182495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61366629600525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55676102638245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54863178730011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53237342834473</t>
+    <t xml:space="preserve">1.61366641521454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55676114559174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5486319065094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53237330913544</t>
   </si>
   <si>
     <t xml:space="preserve">1.4957914352417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58521366119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6014723777771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57301986217499</t>
+    <t xml:space="preserve">1.58521378040314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60147225856781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5730197429657</t>
   </si>
   <si>
     <t xml:space="preserve">1.56082582473755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58114910125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56895506381989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63398969173431</t>
+    <t xml:space="preserve">1.58114922046661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5689549446106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63398957252502</t>
   </si>
   <si>
     <t xml:space="preserve">1.69089460372925</t>
@@ -1703,28 +1703,28 @@
     <t xml:space="preserve">1.60553693771362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62179553508759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58927822113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61773073673248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67463612556458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70715320110321</t>
+    <t xml:space="preserve">1.62179565429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58927834033966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61773085594177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67463600635529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70715308189392</t>
   </si>
   <si>
     <t xml:space="preserve">1.76405847072601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7315411567688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71528255939484</t>
+    <t xml:space="preserve">1.73154103755951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71528244018555</t>
   </si>
   <si>
     <t xml:space="preserve">1.69902384281158</t>
@@ -1733,7 +1733,7 @@
     <t xml:space="preserve">1.6502480506897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74779987335205</t>
+    <t xml:space="preserve">1.74779975414276</t>
   </si>
   <si>
     <t xml:space="preserve">1.75592911243439</t>
@@ -1742,43 +1742,43 @@
     <t xml:space="preserve">1.77218759059906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78844618797302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82096326351166</t>
+    <t xml:space="preserve">1.7884464263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82096338272095</t>
   </si>
   <si>
     <t xml:space="preserve">1.87786865234375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82909274101257</t>
+    <t xml:space="preserve">1.82909286022186</t>
   </si>
   <si>
     <t xml:space="preserve">1.80470490455627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81283414363861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79657566547394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78031694889069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72341191768646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73967027664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68276536464691</t>
+    <t xml:space="preserve">1.81283402442932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79657554626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7803168296814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72341179847717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73967039585114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6827654838562</t>
   </si>
   <si>
     <t xml:space="preserve">1.60960149765015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64211893081665</t>
+    <t xml:space="preserve">1.64211881160736</t>
   </si>
   <si>
     <t xml:space="preserve">1.57708430290222</t>
@@ -1793,10 +1793,10 @@
     <t xml:space="preserve">1.49985611438751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48766207695007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48359739780426</t>
+    <t xml:space="preserve">1.48766219615936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48359751701355</t>
   </si>
   <si>
     <t xml:space="preserve">1.43075704574585</t>
@@ -1808,13 +1808,13 @@
     <t xml:space="preserve">1.41043376922607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40636897087097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43482160568237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4144983291626</t>
+    <t xml:space="preserve">1.40636909008026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43482148647308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41449844837189</t>
   </si>
   <si>
     <t xml:space="preserve">1.36572253704071</t>
@@ -1823,7 +1823,7 @@
     <t xml:space="preserve">1.33320534229279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38198113441467</t>
+    <t xml:space="preserve">1.38198125362396</t>
   </si>
   <si>
     <t xml:space="preserve">1.35759329795837</t>
@@ -1832,10 +1832,10 @@
     <t xml:space="preserve">1.30475270748138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29255878925323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30881750583649</t>
+    <t xml:space="preserve">1.29255902767181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3088173866272</t>
   </si>
   <si>
     <t xml:space="preserve">1.33727014064789</t>
@@ -1850,13 +1850,13 @@
     <t xml:space="preserve">1.37385189533234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35352861881256</t>
+    <t xml:space="preserve">1.35352849960327</t>
   </si>
   <si>
     <t xml:space="preserve">1.39823985099792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40230441093445</t>
+    <t xml:space="preserve">1.40230429172516</t>
   </si>
   <si>
     <t xml:space="preserve">1.3860456943512</t>
@@ -1868,40 +1868,40 @@
     <t xml:space="preserve">1.37791657447815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46733868122101</t>
+    <t xml:space="preserve">1.4673388004303</t>
   </si>
   <si>
     <t xml:space="preserve">1.52017939090729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55269658565521</t>
+    <t xml:space="preserve">1.55269646644592</t>
   </si>
   <si>
     <t xml:space="preserve">1.54456722736359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49172687530518</t>
+    <t xml:space="preserve">1.49172675609589</t>
   </si>
   <si>
     <t xml:space="preserve">1.52424395084381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50798535346985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51611471176147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54050266742706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47953283786774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86973929405212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95103216171265</t>
+    <t xml:space="preserve">1.50798511505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51611459255219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54050254821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47953295707703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86973917484283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95103228092194</t>
   </si>
   <si>
     <t xml:space="preserve">2.0729718208313</t>
@@ -1910,7 +1910,7 @@
     <t xml:space="preserve">2.25994563102722</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24368691444397</t>
+    <t xml:space="preserve">2.24368715286255</t>
   </si>
   <si>
     <t xml:space="preserve">2.1786527633667</t>
@@ -1922,7 +1922,7 @@
     <t xml:space="preserve">2.05671310424805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13800621032715</t>
+    <t xml:space="preserve">2.13800597190857</t>
   </si>
   <si>
     <t xml:space="preserve">2.21116995811462</t>
@@ -1937,10 +1937,10 @@
     <t xml:space="preserve">2.24429607391357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25257754325867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20288848876953</t>
+    <t xml:space="preserve">2.25257778167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20288825035095</t>
   </si>
   <si>
     <t xml:space="preserve">2.22773313522339</t>
@@ -1949,19 +1949,19 @@
     <t xml:space="preserve">2.19460678100586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17804360389709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34367442131042</t>
+    <t xml:space="preserve">2.17804384231567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.343674659729</t>
   </si>
   <si>
     <t xml:space="preserve">2.36023759841919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36851930618286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38508200645447</t>
+    <t xml:space="preserve">2.36851906776428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38508224487305</t>
   </si>
   <si>
     <t xml:space="preserve">2.40164518356323</t>
@@ -1979,13 +1979,13 @@
     <t xml:space="preserve">2.49274230003357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41820859909058</t>
+    <t xml:space="preserve">2.418208360672</t>
   </si>
   <si>
     <t xml:space="preserve">2.39336347579956</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37680053710938</t>
+    <t xml:space="preserve">2.37680077552795</t>
   </si>
   <si>
     <t xml:space="preserve">2.44305300712585</t>
@@ -1997,10 +1997,10 @@
     <t xml:space="preserve">2.42648983001709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33539295196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32711124420166</t>
+    <t xml:space="preserve">2.33539319038391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32711148262024</t>
   </si>
   <si>
     <t xml:space="preserve">2.30226683616638</t>
@@ -2012,7 +2012,7 @@
     <t xml:space="preserve">2.31054830551147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3519561290741</t>
+    <t xml:space="preserve">2.35195589065552</t>
   </si>
   <si>
     <t xml:space="preserve">2.29398536682129</t>
@@ -2021,19 +2021,19 @@
     <t xml:space="preserve">2.28570365905762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2774224281311</t>
+    <t xml:space="preserve">2.27742218971252</t>
   </si>
   <si>
     <t xml:space="preserve">2.15319919586182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12835478782654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13663625717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18632507324219</t>
+    <t xml:space="preserve">2.12835454940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13663601875305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18632531166077</t>
   </si>
   <si>
     <t xml:space="preserve">2.08694696426392</t>
@@ -2048,7 +2048,7 @@
     <t xml:space="preserve">2.16976237297058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14491748809814</t>
+    <t xml:space="preserve">2.14491772651672</t>
   </si>
   <si>
     <t xml:space="preserve">2.16148066520691</t>
@@ -2063,25 +2063,25 @@
     <t xml:space="preserve">2.4099268913269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46789717674255</t>
+    <t xml:space="preserve">2.46789741516113</t>
   </si>
   <si>
     <t xml:space="preserve">2.50102376937866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52586817741394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50930523872375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62524676322937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71634340286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69978046417236</t>
+    <t xml:space="preserve">2.52586841583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50930500030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62524652481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71634364128113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69978022575378</t>
   </si>
   <si>
     <t xml:space="preserve">2.81572198867798</t>
@@ -2096,13 +2096,13 @@
     <t xml:space="preserve">3.01447892189026</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03104186058044</t>
+    <t xml:space="preserve">3.03104162216187</t>
   </si>
   <si>
     <t xml:space="preserve">3.24636197090149</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23808002471924</t>
+    <t xml:space="preserve">3.23808026313782</t>
   </si>
   <si>
     <t xml:space="preserve">3.22979879379272</t>
@@ -2114,13 +2114,13 @@
     <t xml:space="preserve">3.12213897705078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16354656219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17182803153992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21323585510254</t>
+    <t xml:space="preserve">3.1635468006134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17182779312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21323561668396</t>
   </si>
   <si>
     <t xml:space="preserve">3.1883909702301</t>
@@ -2132,28 +2132,28 @@
     <t xml:space="preserve">3.18010950088501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13042020797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10557579994202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13870215415955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08901262283325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07244968414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11385726928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08073115348816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06416821479797</t>
+    <t xml:space="preserve">3.13042044639587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10557556152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13870191574097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08901286125183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07244944572449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11385703086853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08073139190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06416797637939</t>
   </si>
   <si>
     <t xml:space="preserve">3.254643201828</t>
@@ -2168,22 +2168,22 @@
     <t xml:space="preserve">3.02276039123535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04760479927063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0558865070343</t>
+    <t xml:space="preserve">3.04760503768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05588674545288</t>
   </si>
   <si>
     <t xml:space="preserve">3.15526485443115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03932332992554</t>
+    <t xml:space="preserve">3.03932356834412</t>
   </si>
   <si>
     <t xml:space="preserve">2.98963403701782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00619721412659</t>
+    <t xml:space="preserve">3.00619745254517</t>
   </si>
   <si>
     <t xml:space="preserve">2.98135280609131</t>
@@ -2228,13 +2228,13 @@
     <t xml:space="preserve">4.95042657852173</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01585006713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58285999298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36477947235107</t>
+    <t xml:space="preserve">5.01585054397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5828595161438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36477899551392</t>
   </si>
   <si>
     <t xml:space="preserve">5.05946683883667</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">4.97223424911499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14669895172119</t>
+    <t xml:space="preserve">5.14669847488403</t>
   </si>
   <si>
     <t xml:space="preserve">5.08127450942993</t>
@@ -2252,7 +2252,7 @@
     <t xml:space="preserve">5.19031476974487</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21212244033813</t>
+    <t xml:space="preserve">5.21212291717529</t>
   </si>
   <si>
     <t xml:space="preserve">5.27754688262939</t>
@@ -2267,22 +2267,22 @@
     <t xml:space="preserve">5.47381925582886</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53924322128296</t>
+    <t xml:space="preserve">5.53924369812012</t>
   </si>
   <si>
     <t xml:space="preserve">5.45201110839844</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43020296096802</t>
+    <t xml:space="preserve">5.43020343780518</t>
   </si>
   <si>
     <t xml:space="preserve">5.40839529037476</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34297132492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38658761978149</t>
+    <t xml:space="preserve">5.3429708480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38658714294434</t>
   </si>
   <si>
     <t xml:space="preserve">5.32116317749023</t>
@@ -2294,19 +2294,19 @@
     <t xml:space="preserve">5.99721240997314</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82591772079468</t>
+    <t xml:space="preserve">6.82591819763184</t>
   </si>
   <si>
     <t xml:space="preserve">7.32750272750854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93495845794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.782301902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73868608474731</t>
+    <t xml:space="preserve">6.93495798110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78230237960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73868560791016</t>
   </si>
   <si>
     <t xml:space="preserve">6.67326211929321</t>
@@ -2321,7 +2321,7 @@
     <t xml:space="preserve">6.25890922546387</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32433271408081</t>
+    <t xml:space="preserve">6.32433319091797</t>
   </si>
   <si>
     <t xml:space="preserve">6.23710107803345</t>
@@ -2336,28 +2336,28 @@
     <t xml:space="preserve">6.41156530380249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62964582443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76049375534058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0221905708313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06580686569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04399824142456</t>
+    <t xml:space="preserve">6.62964534759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76049423217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02219104766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0658073425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04399871826172</t>
   </si>
   <si>
     <t xml:space="preserve">7.0876145362854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45835161209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52377557754517</t>
+    <t xml:space="preserve">7.45835208892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52377510070801</t>
   </si>
   <si>
     <t xml:space="preserve">7.78547239303589</t>
@@ -2369,7 +2369,7 @@
     <t xml:space="preserve">8.19982433319092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11259269714355</t>
+    <t xml:space="preserve">8.11259365081787</t>
   </si>
   <si>
     <t xml:space="preserve">8.37428951263428</t>
@@ -18878,7 +18878,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G601" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -18904,7 +18904,7 @@
         <v>32</v>
       </c>
       <c r="G602" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -18930,7 +18930,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G603" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18956,7 +18956,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G604" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19008,7 +19008,7 @@
         <v>32</v>
       </c>
       <c r="G606" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19034,7 +19034,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G607" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19060,7 +19060,7 @@
         <v>30</v>
       </c>
       <c r="G608" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19086,7 +19086,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G609" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19112,7 +19112,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G610" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19138,7 +19138,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G611" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19164,7 +19164,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G612" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19190,7 +19190,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G613" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19216,7 +19216,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G614" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19242,7 +19242,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G615" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19268,7 +19268,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G616" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19294,7 +19294,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G617" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19320,7 +19320,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G618" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19346,7 +19346,7 @@
         <v>28</v>
       </c>
       <c r="G619" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19372,7 +19372,7 @@
         <v>28</v>
       </c>
       <c r="G620" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19398,7 +19398,7 @@
         <v>28</v>
       </c>
       <c r="G621" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19424,7 +19424,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G622" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19450,7 +19450,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G623" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19476,7 +19476,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G624" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19502,7 +19502,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G625" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19528,7 +19528,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G626" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19554,7 +19554,7 @@
         <v>29</v>
       </c>
       <c r="G627" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19580,7 +19580,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G628" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19606,7 +19606,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G629" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19632,7 +19632,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G630" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19658,7 +19658,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G631" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19684,7 +19684,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G632" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19710,7 +19710,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G633" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19736,7 +19736,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G634" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19762,7 +19762,7 @@
         <v>27.5</v>
       </c>
       <c r="G635" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19788,7 +19788,7 @@
         <v>27</v>
       </c>
       <c r="G636" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19814,7 +19814,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G637" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19840,7 +19840,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G638" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19866,7 +19866,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G639" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19892,7 +19892,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G640" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19918,7 +19918,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G641" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -19944,7 +19944,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G642" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19970,7 +19970,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G643" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19996,7 +19996,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G644" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20022,7 +20022,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G645" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20048,7 +20048,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G646" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20074,7 +20074,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G647" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20100,7 +20100,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G648" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20126,7 +20126,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G649" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20152,7 +20152,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G650" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20178,7 +20178,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G651" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20204,7 +20204,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G652" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20230,7 +20230,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G653" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20256,7 +20256,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G654" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20282,7 +20282,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G655" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20308,7 +20308,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G656" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20334,7 +20334,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G657" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20360,7 +20360,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G658" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20386,7 +20386,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G659" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20412,7 +20412,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G660" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20438,7 +20438,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G661" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20464,7 +20464,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G662" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20490,7 +20490,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G663" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -20516,7 +20516,7 @@
         <v>27.5</v>
       </c>
       <c r="G664" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20542,7 +20542,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G665" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20568,7 +20568,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G666" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20594,7 +20594,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G667" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20620,7 +20620,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G668" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20646,7 +20646,7 @@
         <v>27</v>
       </c>
       <c r="G669" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20672,7 +20672,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G670" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20698,7 +20698,7 @@
         <v>27</v>
       </c>
       <c r="G671" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20724,7 +20724,7 @@
         <v>26</v>
       </c>
       <c r="G672" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20750,7 +20750,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G673" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20776,7 +20776,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G674" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20802,7 +20802,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G675" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20828,7 +20828,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G676" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20854,7 +20854,7 @@
         <v>25</v>
       </c>
       <c r="G677" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20880,7 +20880,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G678" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20906,7 +20906,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G679" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -20932,7 +20932,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G680" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -20958,7 +20958,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G681" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -20984,7 +20984,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G682" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21010,7 +21010,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G683" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21036,7 +21036,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G684" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21062,7 +21062,7 @@
         <v>24</v>
       </c>
       <c r="G685" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21088,7 +21088,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G686" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21114,7 +21114,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G687" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21140,7 +21140,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G688" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21166,7 +21166,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G689" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21192,7 +21192,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G690" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21218,7 +21218,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G691" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21244,7 +21244,7 @@
         <v>27</v>
       </c>
       <c r="G692" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21270,7 +21270,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G693" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21296,7 +21296,7 @@
         <v>26</v>
       </c>
       <c r="G694" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21322,7 +21322,7 @@
         <v>26</v>
       </c>
       <c r="G695" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21348,7 +21348,7 @@
         <v>26</v>
       </c>
       <c r="G696" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21374,7 +21374,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G697" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21400,7 +21400,7 @@
         <v>26</v>
       </c>
       <c r="G698" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21426,7 +21426,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G699" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21452,7 +21452,7 @@
         <v>26</v>
       </c>
       <c r="G700" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21478,7 +21478,7 @@
         <v>25.5</v>
       </c>
       <c r="G701" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21504,7 +21504,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G702" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -21530,7 +21530,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G703" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21556,7 +21556,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G704" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21582,7 +21582,7 @@
         <v>26</v>
       </c>
       <c r="G705" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21608,7 +21608,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G706" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21634,7 +21634,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G707" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21660,7 +21660,7 @@
         <v>25.5</v>
       </c>
       <c r="G708" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21686,7 +21686,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G709" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21712,7 +21712,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G710" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21738,7 +21738,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G711" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21764,7 +21764,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G712" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21790,7 +21790,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G713" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21816,7 +21816,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G714" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21842,7 +21842,7 @@
         <v>24</v>
       </c>
       <c r="G715" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21868,7 +21868,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G716" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21894,7 +21894,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G717" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21920,7 +21920,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G718" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -21946,7 +21946,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G719" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -21972,7 +21972,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G720" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21998,7 +21998,7 @@
         <v>22.5</v>
       </c>
       <c r="G721" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22024,7 +22024,7 @@
         <v>23.5</v>
       </c>
       <c r="G722" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22050,7 +22050,7 @@
         <v>23.5</v>
       </c>
       <c r="G723" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22076,7 +22076,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G724" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22102,7 +22102,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G725" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22128,7 +22128,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G726" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22154,7 +22154,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G727" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22180,7 +22180,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G728" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22206,7 +22206,7 @@
         <v>25</v>
       </c>
       <c r="G729" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22232,7 +22232,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G730" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22258,7 +22258,7 @@
         <v>28</v>
       </c>
       <c r="G731" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22284,7 +22284,7 @@
         <v>28.5</v>
       </c>
       <c r="G732" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22310,7 +22310,7 @@
         <v>27.5</v>
       </c>
       <c r="G733" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22336,7 +22336,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G734" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22362,7 +22362,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G735" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22388,7 +22388,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G736" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22414,7 +22414,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G737" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22440,7 +22440,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G738" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22466,7 +22466,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G739" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -22492,7 +22492,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G740" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -22518,7 +22518,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G741" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22544,7 +22544,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G742" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22570,7 +22570,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G743" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22596,7 +22596,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G744" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22622,7 +22622,7 @@
         <v>27.5</v>
       </c>
       <c r="G745" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22648,7 +22648,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G746" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22674,7 +22674,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G747" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22700,7 +22700,7 @@
         <v>27.5</v>
       </c>
       <c r="G748" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22726,7 +22726,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G749" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22752,7 +22752,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G750" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22778,7 +22778,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G751" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22804,7 +22804,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G752" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22830,7 +22830,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G753" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22856,7 +22856,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G754" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22882,7 +22882,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G755" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22908,7 +22908,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G756" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -22934,7 +22934,7 @@
         <v>26.5</v>
       </c>
       <c r="G757" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -22960,7 +22960,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G758" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -22986,7 +22986,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G759" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23012,7 +23012,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G760" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23038,7 +23038,7 @@
         <v>27</v>
       </c>
       <c r="G761" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23064,7 +23064,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G762" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23090,7 +23090,7 @@
         <v>27</v>
       </c>
       <c r="G763" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23116,7 +23116,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G764" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23142,7 +23142,7 @@
         <v>26.5</v>
       </c>
       <c r="G765" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23168,7 +23168,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G766" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23194,7 +23194,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G767" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23220,7 +23220,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G768" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23246,7 +23246,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G769" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23272,7 +23272,7 @@
         <v>28.5</v>
       </c>
       <c r="G770" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23298,7 +23298,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G771" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23324,7 +23324,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G772" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23350,7 +23350,7 @@
         <v>28</v>
       </c>
       <c r="G773" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23376,7 +23376,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G774" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23402,7 +23402,7 @@
         <v>28</v>
       </c>
       <c r="G775" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23428,7 +23428,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G776" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23454,7 +23454,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G777" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23480,7 +23480,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G778" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -23506,7 +23506,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G779" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -23532,7 +23532,7 @@
         <v>28.5</v>
       </c>
       <c r="G780" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23558,7 +23558,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G781" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23584,7 +23584,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G782" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23610,7 +23610,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G783" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23636,7 +23636,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G784" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23662,7 +23662,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G785" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23688,7 +23688,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G786" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23714,7 +23714,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G787" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23740,7 +23740,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G788" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23766,7 +23766,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G789" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23792,7 +23792,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G790" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23818,7 +23818,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G791" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23844,7 +23844,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G792" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23870,7 +23870,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G793" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23896,7 +23896,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G794" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23922,7 +23922,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G795" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -23948,7 +23948,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G796" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -23974,7 +23974,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G797" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24000,7 +24000,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G798" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24026,7 +24026,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G799" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24052,7 +24052,7 @@
         <v>30</v>
       </c>
       <c r="G800" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24078,7 +24078,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G801" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24104,7 +24104,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G802" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24130,7 +24130,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G803" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24156,7 +24156,7 @@
         <v>31</v>
       </c>
       <c r="G804" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24182,7 +24182,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G805" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24208,7 +24208,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G806" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24234,7 +24234,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G807" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24260,7 +24260,7 @@
         <v>31</v>
       </c>
       <c r="G808" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24286,7 +24286,7 @@
         <v>31</v>
       </c>
       <c r="G809" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24312,7 +24312,7 @@
         <v>31</v>
       </c>
       <c r="G810" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24338,7 +24338,7 @@
         <v>31</v>
       </c>
       <c r="G811" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24364,7 +24364,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G812" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24390,7 +24390,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G813" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24416,7 +24416,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G814" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24442,7 +24442,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G815" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24468,7 +24468,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G816" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -24494,7 +24494,7 @@
         <v>31</v>
       </c>
       <c r="G817" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -24520,7 +24520,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G818" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24546,7 +24546,7 @@
         <v>31</v>
       </c>
       <c r="G819" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24572,7 +24572,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G820" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24598,7 +24598,7 @@
         <v>30.5</v>
       </c>
       <c r="G821" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24624,7 +24624,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G822" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24650,7 +24650,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G823" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24676,7 +24676,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G824" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24702,7 +24702,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G825" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24728,7 +24728,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G826" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24754,7 +24754,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G827" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24780,7 +24780,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G828" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24806,7 +24806,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G829" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24832,7 +24832,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G830" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24858,7 +24858,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G831" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24884,7 +24884,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G832" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24910,7 +24910,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G833" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -24936,7 +24936,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G834" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -24962,7 +24962,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G835" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -24988,7 +24988,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G836" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25014,7 +25014,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G837" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25040,7 +25040,7 @@
         <v>31</v>
       </c>
       <c r="G838" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25066,7 +25066,7 @@
         <v>31</v>
       </c>
       <c r="G839" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25092,7 +25092,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G840" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25118,7 +25118,7 @@
         <v>30</v>
       </c>
       <c r="G841" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25144,7 +25144,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G842" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25170,7 +25170,7 @@
         <v>30.5</v>
       </c>
       <c r="G843" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25196,7 +25196,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G844" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25222,7 +25222,7 @@
         <v>30.5</v>
       </c>
       <c r="G845" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25248,7 +25248,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G846" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25274,7 +25274,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G847" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25300,7 +25300,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G848" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25326,7 +25326,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G849" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25352,7 +25352,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G850" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25378,7 +25378,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G851" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25404,7 +25404,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G852" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -25430,7 +25430,7 @@
         <v>28</v>
       </c>
       <c r="G853" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -25456,7 +25456,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G854" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -25482,7 +25482,7 @@
         <v>28</v>
       </c>
       <c r="G855" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -25508,7 +25508,7 @@
         <v>27.5</v>
       </c>
       <c r="G856" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25534,7 +25534,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G857" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25560,7 +25560,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G858" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25586,7 +25586,7 @@
         <v>27.5</v>
       </c>
       <c r="G859" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25612,7 +25612,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G860" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25638,7 +25638,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G861" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25664,7 +25664,7 @@
         <v>28</v>
       </c>
       <c r="G862" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25690,7 +25690,7 @@
         <v>29</v>
       </c>
       <c r="G863" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25716,7 +25716,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G864" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25742,7 +25742,7 @@
         <v>29</v>
       </c>
       <c r="G865" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25768,7 +25768,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G866" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -25794,7 +25794,7 @@
         <v>29</v>
       </c>
       <c r="G867" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25820,7 +25820,7 @@
         <v>29</v>
       </c>
       <c r="G868" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -25846,7 +25846,7 @@
         <v>29</v>
       </c>
       <c r="G869" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -25872,7 +25872,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G870" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -25898,7 +25898,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G871" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25924,7 +25924,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G872" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -25950,7 +25950,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G873" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -25976,7 +25976,7 @@
         <v>30.5</v>
       </c>
       <c r="G874" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -26002,7 +26002,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G875" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -26028,7 +26028,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G876" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -26054,7 +26054,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G877" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -26080,7 +26080,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G878" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -26106,7 +26106,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G879" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26132,7 +26132,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G880" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -26158,7 +26158,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G881" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -26184,7 +26184,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G882" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -26210,7 +26210,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G883" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -26236,7 +26236,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G884" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -26262,7 +26262,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G885" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -26288,7 +26288,7 @@
         <v>31.5</v>
       </c>
       <c r="G886" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -26314,7 +26314,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G887" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -26340,7 +26340,7 @@
         <v>32</v>
       </c>
       <c r="G888" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -26366,7 +26366,7 @@
         <v>31.5</v>
       </c>
       <c r="G889" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -26392,7 +26392,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G890" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -26418,7 +26418,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G891" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -26444,7 +26444,7 @@
         <v>32</v>
       </c>
       <c r="G892" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -26470,7 +26470,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G893" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -26496,7 +26496,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G894" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -26522,7 +26522,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26548,7 +26548,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G896" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -26574,7 +26574,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G897" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -26600,7 +26600,7 @@
         <v>31</v>
       </c>
       <c r="G898" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -26626,7 +26626,7 @@
         <v>31</v>
       </c>
       <c r="G899" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -26652,7 +26652,7 @@
         <v>31</v>
       </c>
       <c r="G900" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -26678,7 +26678,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G901" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -26704,7 +26704,7 @@
         <v>31</v>
       </c>
       <c r="G902" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -26730,7 +26730,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G903" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -26756,7 +26756,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G904" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -26782,7 +26782,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G905" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -26808,7 +26808,7 @@
         <v>31</v>
       </c>
       <c r="G906" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -26834,7 +26834,7 @@
         <v>31</v>
       </c>
       <c r="G907" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -26860,7 +26860,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G908" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -26886,7 +26886,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G909" t="s">
-        <v>524</v>
+        <v>490</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -26912,7 +26912,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G910" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -26938,7 +26938,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G911" t="s">
-        <v>524</v>
+        <v>490</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -26964,7 +26964,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G912" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -26990,7 +26990,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G913" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -27016,7 +27016,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G914" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -27042,7 +27042,7 @@
         <v>30</v>
       </c>
       <c r="G915" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -27068,7 +27068,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G916" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -27120,7 +27120,7 @@
         <v>29</v>
       </c>
       <c r="G918" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -27172,7 +27172,7 @@
         <v>29</v>
       </c>
       <c r="G920" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -27250,7 +27250,7 @@
         <v>29</v>
       </c>
       <c r="G923" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -27276,7 +27276,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G924" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -27302,7 +27302,7 @@
         <v>29</v>
       </c>
       <c r="G925" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -27328,7 +27328,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G926" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -27354,7 +27354,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G927" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -27380,7 +27380,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G928" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -27432,7 +27432,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G930" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -27458,7 +27458,7 @@
         <v>30.5</v>
       </c>
       <c r="G931" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -27484,7 +27484,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G932" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -27588,7 +27588,7 @@
         <v>30</v>
       </c>
       <c r="G936" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -27666,7 +27666,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G939" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -27692,7 +27692,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G940" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -27718,7 +27718,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G941" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -27744,7 +27744,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G942" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -27770,7 +27770,7 @@
         <v>30</v>
       </c>
       <c r="G943" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -27796,7 +27796,7 @@
         <v>30</v>
       </c>
       <c r="G944" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -27848,7 +27848,7 @@
         <v>30</v>
       </c>
       <c r="G946" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -27874,7 +27874,7 @@
         <v>30.5</v>
       </c>
       <c r="G947" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -27900,7 +27900,7 @@
         <v>30.5</v>
       </c>
       <c r="G948" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -27926,7 +27926,7 @@
         <v>30</v>
       </c>
       <c r="G949" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -27978,7 +27978,7 @@
         <v>30</v>
       </c>
       <c r="G951" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -28030,7 +28030,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G953" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -28082,7 +28082,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G955" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -28108,7 +28108,7 @@
         <v>30</v>
       </c>
       <c r="G956" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -28134,7 +28134,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G957" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -28160,7 +28160,7 @@
         <v>30</v>
       </c>
       <c r="G958" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -28186,7 +28186,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G959" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -28212,7 +28212,7 @@
         <v>30</v>
       </c>
       <c r="G960" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -28238,7 +28238,7 @@
         <v>30</v>
       </c>
       <c r="G961" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -28264,7 +28264,7 @@
         <v>30</v>
       </c>
       <c r="G962" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -28290,7 +28290,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G963" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -28316,7 +28316,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G964" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -28342,7 +28342,7 @@
         <v>30</v>
       </c>
       <c r="G965" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -28368,7 +28368,7 @@
         <v>30</v>
       </c>
       <c r="G966" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -28420,7 +28420,7 @@
         <v>30</v>
       </c>
       <c r="G968" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -28446,7 +28446,7 @@
         <v>30</v>
       </c>
       <c r="G969" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -28524,7 +28524,7 @@
         <v>30</v>
       </c>
       <c r="G972" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -28576,7 +28576,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G974" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -28602,7 +28602,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G975" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -28654,7 +28654,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G977" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -28680,7 +28680,7 @@
         <v>31</v>
       </c>
       <c r="G978" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28706,7 +28706,7 @@
         <v>31</v>
       </c>
       <c r="G979" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -28732,7 +28732,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G980" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28758,7 +28758,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G981" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -28784,7 +28784,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G982" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -28810,7 +28810,7 @@
         <v>31</v>
       </c>
       <c r="G983" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -28836,7 +28836,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G984" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -28862,7 +28862,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G985" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28888,7 +28888,7 @@
         <v>31</v>
       </c>
       <c r="G986" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -28914,7 +28914,7 @@
         <v>31.5</v>
       </c>
       <c r="G987" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -28940,7 +28940,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G988" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -28966,7 +28966,7 @@
         <v>31.5</v>
       </c>
       <c r="G989" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -28992,7 +28992,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G990" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -29018,7 +29018,7 @@
         <v>31.5</v>
       </c>
       <c r="G991" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -29044,7 +29044,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G992" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -29070,7 +29070,7 @@
         <v>31.5</v>
       </c>
       <c r="G993" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -29096,7 +29096,7 @@
         <v>31.5</v>
       </c>
       <c r="G994" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -29122,7 +29122,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G995" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -29148,7 +29148,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G996" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -29174,7 +29174,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G997" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -29200,7 +29200,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G998" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -29226,7 +29226,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G999" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -29252,7 +29252,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1000" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -29278,7 +29278,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1001" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -29304,7 +29304,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1002" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -29330,7 +29330,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1003" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -29356,7 +29356,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1004" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -29382,7 +29382,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1005" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -29408,7 +29408,7 @@
         <v>31</v>
       </c>
       <c r="G1006" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -29434,7 +29434,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1007" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -29460,7 +29460,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1008" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -29486,7 +29486,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1009" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -29512,7 +29512,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1010" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -29538,7 +29538,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1011" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -29564,7 +29564,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1012" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -29590,7 +29590,7 @@
         <v>30.5</v>
       </c>
       <c r="G1013" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -29616,7 +29616,7 @@
         <v>30.5</v>
       </c>
       <c r="G1014" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -29668,7 +29668,7 @@
         <v>30.5</v>
       </c>
       <c r="G1016" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -29720,7 +29720,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1018" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -29746,7 +29746,7 @@
         <v>30</v>
       </c>
       <c r="G1019" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -29772,7 +29772,7 @@
         <v>30.5</v>
       </c>
       <c r="G1020" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -29798,7 +29798,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1021" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -29824,7 +29824,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1022" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -29850,7 +29850,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1023" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -29876,7 +29876,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1024" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -29902,7 +29902,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1025" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -29928,7 +29928,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1026" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -29954,7 +29954,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1027" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -29980,7 +29980,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1028" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -30006,7 +30006,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1029" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -30032,7 +30032,7 @@
         <v>30</v>
       </c>
       <c r="G1030" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -30058,7 +30058,7 @@
         <v>30</v>
       </c>
       <c r="G1031" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -30084,7 +30084,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1032" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -30266,7 +30266,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1039" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -30292,7 +30292,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1040" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -30318,7 +30318,7 @@
         <v>28</v>
       </c>
       <c r="G1041" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -30448,7 +30448,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1046" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -30500,7 +30500,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1048" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -30526,7 +30526,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1049" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -30578,7 +30578,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1051" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -30604,7 +30604,7 @@
         <v>28</v>
       </c>
       <c r="G1052" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -30682,7 +30682,7 @@
         <v>27.5</v>
       </c>
       <c r="G1055" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -36948,7 +36948,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1296" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -36974,7 +36974,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1297" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -37026,7 +37026,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1299" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -37078,7 +37078,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1301" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -37104,7 +37104,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1302" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -37130,7 +37130,7 @@
         <v>29</v>
       </c>
       <c r="G1303" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -37156,7 +37156,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1304" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -37182,7 +37182,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1305" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -37286,7 +37286,7 @@
         <v>28</v>
       </c>
       <c r="G1309" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -37312,7 +37312,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1310" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -37338,7 +37338,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1311" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -37416,7 +37416,7 @@
         <v>28</v>
       </c>
       <c r="G1314" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -37442,7 +37442,7 @@
         <v>28</v>
       </c>
       <c r="G1315" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -37468,7 +37468,7 @@
         <v>28</v>
       </c>
       <c r="G1316" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -37832,7 +37832,7 @@
         <v>27.5</v>
       </c>
       <c r="G1330" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -38014,7 +38014,7 @@
         <v>27.5</v>
       </c>
       <c r="G1337" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -68598,7 +68598,7 @@
     </row>
     <row r="2514">
       <c r="A2514" s="1" t="n">
-        <v>45979.4653819444</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2514" t="n">
         <v>1180</v>
@@ -68619,6 +68619,32 @@
         <v>929</v>
       </c>
       <c r="H2514" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>45980.4498263889</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>70</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>2.55999994277954</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>2.55999994277954</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>2.55999994277954</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>2.55999994277954</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>937</v>
+      </c>
+      <c r="H2515" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24616146087646</t>
+    <t xml:space="preserve">1.24616158008575</t>
   </si>
   <si>
     <t xml:space="preserve">AUTME.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24544668197632</t>
+    <t xml:space="preserve">1.24544656276703</t>
   </si>
   <si>
     <t xml:space="preserve">1.24330151081085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22256803512573</t>
+    <t xml:space="preserve">1.22256815433502</t>
   </si>
   <si>
     <t xml:space="preserve">1.21541857719421</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">1.21327364444733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20683908462524</t>
+    <t xml:space="preserve">1.20683896541595</t>
   </si>
   <si>
     <t xml:space="preserve">1.2011194229126</t>
@@ -77,19 +77,19 @@
     <t xml:space="preserve">1.20040464401245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1668016910553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1946849822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25688564777374</t>
+    <t xml:space="preserve">1.16680157184601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19468486309052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25688588619232</t>
   </si>
   <si>
     <t xml:space="preserve">1.25045108795166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2468763589859</t>
+    <t xml:space="preserve">1.24687647819519</t>
   </si>
   <si>
     <t xml:space="preserve">1.25116610527039</t>
@@ -98,25 +98,25 @@
     <t xml:space="preserve">1.26475012302399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23543727397919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22542786598206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21041369438171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22113835811615</t>
+    <t xml:space="preserve">1.2354371547699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22542798519135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.210413813591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22113823890686</t>
   </si>
   <si>
     <t xml:space="preserve">1.19396996498108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22685766220093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20469439029694</t>
+    <t xml:space="preserve">1.22685790061951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20469427108765</t>
   </si>
   <si>
     <t xml:space="preserve">1.25831568241119</t>
@@ -125,43 +125,43 @@
     <t xml:space="preserve">1.26546514034271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25903058052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26903986930847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21684849262238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22828769683838</t>
+    <t xml:space="preserve">1.25903069972992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26903998851776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21684837341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22828757762909</t>
   </si>
   <si>
     <t xml:space="preserve">1.27404451370239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26689493656158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27261447906494</t>
+    <t xml:space="preserve">1.26689505577087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27261471748352</t>
   </si>
   <si>
     <t xml:space="preserve">1.27189993858337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27904903888702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26761019229889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25545608997345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26260542869568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24830627441406</t>
+    <t xml:space="preserve">1.27904915809631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26760983467102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25545585155487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26260530948639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24830639362335</t>
   </si>
   <si>
     <t xml:space="preserve">1.24902129173279</t>
@@ -170,31 +170,31 @@
     <t xml:space="preserve">1.24258661270142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23686718940735</t>
+    <t xml:space="preserve">1.23686707019806</t>
   </si>
   <si>
     <t xml:space="preserve">1.23472225666046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23400723934174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25225365161896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26176810264587</t>
+    <t xml:space="preserve">1.23400735855103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25225377082825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26176822185516</t>
   </si>
   <si>
     <t xml:space="preserve">1.26835489273071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27860140800476</t>
+    <t xml:space="preserve">1.27860116958618</t>
   </si>
   <si>
     <t xml:space="preserve">1.27640569210052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27420997619629</t>
+    <t xml:space="preserve">1.274209856987</t>
   </si>
   <si>
     <t xml:space="preserve">1.27494204044342</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">1.27128267288208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26689124107361</t>
+    <t xml:space="preserve">1.26689112186432</t>
   </si>
   <si>
     <t xml:space="preserve">1.28445637226105</t>
@@ -218,16 +218,16 @@
     <t xml:space="preserve">1.2793333530426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27347803115845</t>
+    <t xml:space="preserve">1.27347826957703</t>
   </si>
   <si>
     <t xml:space="preserve">1.27274632453918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26615941524506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28226089477539</t>
+    <t xml:space="preserve">1.26615953445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2822607755661</t>
   </si>
   <si>
     <t xml:space="preserve">1.28811597824097</t>
@@ -242,16 +242,16 @@
     <t xml:space="preserve">1.26396381855011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24127519130707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2434709072113</t>
+    <t xml:space="preserve">1.24127531051636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24347102642059</t>
   </si>
   <si>
     <t xml:space="preserve">1.22956514358521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23468840122223</t>
+    <t xml:space="preserve">1.23468852043152</t>
   </si>
   <si>
     <t xml:space="preserve">1.22663760185242</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">1.20687675476074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20760881900787</t>
+    <t xml:space="preserve">1.20760869979858</t>
   </si>
   <si>
     <t xml:space="preserve">1.18565225601196</t>
@@ -272,31 +272,31 @@
     <t xml:space="preserve">1.18784773349762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16955065727234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17101454734802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17028248310089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18931150436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22224652767181</t>
+    <t xml:space="preserve">1.16955077648163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17101442813873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17028260231018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1893116235733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22224628925323</t>
   </si>
   <si>
     <t xml:space="preserve">1.22151458263397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23981153964996</t>
+    <t xml:space="preserve">1.23981165885925</t>
   </si>
   <si>
     <t xml:space="preserve">1.23907959461212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23834800720215</t>
+    <t xml:space="preserve">1.23834776878357</t>
   </si>
   <si>
     <t xml:space="preserve">1.23542010784149</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">1.2310289144516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19736230373383</t>
+    <t xml:space="preserve">1.19736242294312</t>
   </si>
   <si>
     <t xml:space="preserve">1.2171231508255</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">1.22297823429108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23322463035583</t>
+    <t xml:space="preserve">1.23322451114655</t>
   </si>
   <si>
     <t xml:space="preserve">1.23249280452728</t>
@@ -329,22 +329,22 @@
     <t xml:space="preserve">1.28518843650818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2588404417038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30714499950409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29909420013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32324624061584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31665933132172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32763743400574</t>
+    <t xml:space="preserve">1.25884056091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30714476108551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29909408092499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32324612140656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31665945053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32763755321503</t>
   </si>
   <si>
     <t xml:space="preserve">1.30348551273346</t>
@@ -353,10 +353,10 @@
     <t xml:space="preserve">1.31592750549316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3181232213974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29763042926788</t>
+    <t xml:space="preserve">1.31812334060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29763031005859</t>
   </si>
   <si>
     <t xml:space="preserve">1.30275344848633</t>
@@ -368,22 +368,22 @@
     <t xml:space="preserve">1.28884780406952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29543483257294</t>
+    <t xml:space="preserve">1.29543471336365</t>
   </si>
   <si>
     <t xml:space="preserve">1.30055797100067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29836225509644</t>
+    <t xml:space="preserve">1.29836213588715</t>
   </si>
   <si>
     <t xml:space="preserve">1.29323923587799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29250717163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30128979682922</t>
+    <t xml:space="preserve">1.29250729084015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30128991603851</t>
   </si>
   <si>
     <t xml:space="preserve">1.3056812286377</t>
@@ -401,22 +401,22 @@
     <t xml:space="preserve">1.25518107414246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26542735099792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28006505966187</t>
+    <t xml:space="preserve">1.2654275894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28006517887115</t>
   </si>
   <si>
     <t xml:space="preserve">1.25810873508453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2500581741333</t>
+    <t xml:space="preserve">1.25005793571472</t>
   </si>
   <si>
     <t xml:space="preserve">1.24054360389709</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24639856815338</t>
+    <t xml:space="preserve">1.24639868736267</t>
   </si>
   <si>
     <t xml:space="preserve">1.24420285224915</t>
@@ -425,13 +425,13 @@
     <t xml:space="preserve">1.23615205287933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23688411712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24200713634491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23176074028015</t>
+    <t xml:space="preserve">1.23688399791718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2420072555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23176085948944</t>
   </si>
   <si>
     <t xml:space="preserve">1.20980441570282</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">1.21126806735992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2185868024826</t>
+    <t xml:space="preserve">1.21858692169189</t>
   </si>
   <si>
     <t xml:space="preserve">1.21492755413055</t>
@@ -449,19 +449,19 @@
     <t xml:space="preserve">1.19004344940186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18199276924133</t>
+    <t xml:space="preserve">1.18199265003204</t>
   </si>
   <si>
     <t xml:space="preserve">1.21419560909271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19297075271606</t>
+    <t xml:space="preserve">1.19297099113464</t>
   </si>
   <si>
     <t xml:space="preserve">1.19663047790527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.220050573349</t>
+    <t xml:space="preserve">1.22005069255829</t>
   </si>
   <si>
     <t xml:space="preserve">1.21639132499695</t>
@@ -470,34 +470,34 @@
     <t xml:space="preserve">1.25957238674164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27786934375763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28592014312744</t>
+    <t xml:space="preserve">1.27786958217621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28592026233673</t>
   </si>
   <si>
     <t xml:space="preserve">1.29470300674438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29689836502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31007242202759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32544207572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34081172943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3334926366806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33422470092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3320289850235</t>
+    <t xml:space="preserve">1.29689848423004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3100723028183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32544195652008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34081149101257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33349275588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33422482013702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33202910423279</t>
   </si>
   <si>
     <t xml:space="preserve">1.33861589431763</t>
@@ -506,10 +506,10 @@
     <t xml:space="preserve">1.33934772014618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34666657447815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34227526187897</t>
+    <t xml:space="preserve">1.34666669368744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34227538108826</t>
   </si>
   <si>
     <t xml:space="preserve">1.34007954597473</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">1.32105052471161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34593486785889</t>
+    <t xml:space="preserve">1.3459347486496</t>
   </si>
   <si>
     <t xml:space="preserve">1.36130440235138</t>
@@ -530,16 +530,16 @@
     <t xml:space="preserve">1.36057233810425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33276093006134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34959435462952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33788418769836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34373903274536</t>
+    <t xml:space="preserve">1.33276069164276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34959423542023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33788406848907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34373927116394</t>
   </si>
   <si>
     <t xml:space="preserve">1.34520280361176</t>
@@ -554,22 +554,22 @@
     <t xml:space="preserve">1.36789119243622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37667381763458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38252902030945</t>
+    <t xml:space="preserve">1.37667393684387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38252890110016</t>
   </si>
   <si>
     <t xml:space="preserve">1.39789855480194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41253614425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40668094158173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4081449508667</t>
+    <t xml:space="preserve">1.4125360250473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40668118000031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40814483165741</t>
   </si>
   <si>
     <t xml:space="preserve">1.40887677669525</t>
@@ -578,25 +578,25 @@
     <t xml:space="preserve">1.40302169322968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39277529716492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36935496330261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37886953353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.389115691185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40155780315399</t>
+    <t xml:space="preserve">1.39277541637421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3693550825119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3788697719574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38911581039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40155792236328</t>
   </si>
   <si>
     <t xml:space="preserve">1.49304342269897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47621011734009</t>
+    <t xml:space="preserve">1.47621023654938</t>
   </si>
   <si>
     <t xml:space="preserve">1.48206520080566</t>
@@ -614,34 +614,34 @@
     <t xml:space="preserve">1.45864486694336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47913765907288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4952392578125</t>
+    <t xml:space="preserve">1.47913753986359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49523913860321</t>
   </si>
   <si>
     <t xml:space="preserve">1.49084782600403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48792016506195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52744209766388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50987660884857</t>
+    <t xml:space="preserve">1.48792028427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52744221687317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50987672805786</t>
   </si>
   <si>
     <t xml:space="preserve">1.53256511688232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52963781356812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53183341026306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52817392349243</t>
+    <t xml:space="preserve">1.52963769435883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53183352947235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52817380428314</t>
   </si>
   <si>
     <t xml:space="preserve">1.51500022411346</t>
@@ -656,46 +656,46 @@
     <t xml:space="preserve">1.485724568367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47108697891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4842609167099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46376812458038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45498549938202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48499274253845</t>
+    <t xml:space="preserve">1.47108685970306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48426079750061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46376800537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45498538017273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48499286174774</t>
   </si>
   <si>
     <t xml:space="preserve">1.52085506916046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53768861293793</t>
+    <t xml:space="preserve">1.53768837451935</t>
   </si>
   <si>
     <t xml:space="preserve">1.58233344554901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63126373291016</t>
+    <t xml:space="preserve">1.63126361370087</t>
   </si>
   <si>
     <t xml:space="preserve">1.63427484035492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64857745170593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63578045368195</t>
+    <t xml:space="preserve">1.64857757091522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63578033447266</t>
   </si>
   <si>
     <t xml:space="preserve">1.66664409637451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66288042068481</t>
+    <t xml:space="preserve">1.66288030147552</t>
   </si>
   <si>
     <t xml:space="preserve">1.66137480735779</t>
@@ -710,37 +710,37 @@
     <t xml:space="preserve">1.84429883956909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9165655374527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99485433101654</t>
+    <t xml:space="preserve">1.91656541824341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99485409259796</t>
   </si>
   <si>
     <t xml:space="preserve">2.01367354393005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95345163345337</t>
+    <t xml:space="preserve">1.95345151424408</t>
   </si>
   <si>
     <t xml:space="preserve">1.98205709457397</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93011522293091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83376049995422</t>
+    <t xml:space="preserve">1.9301153421402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83376026153564</t>
   </si>
   <si>
     <t xml:space="preserve">1.90301561355591</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90452086925507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91204869747162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9353848695755</t>
+    <t xml:space="preserve">1.90452110767365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91204881668091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93538475036621</t>
   </si>
   <si>
     <t xml:space="preserve">1.92258763313293</t>
@@ -749,49 +749,49 @@
     <t xml:space="preserve">1.91581284999847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88118505477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92860996723175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92183494567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92559897899628</t>
+    <t xml:space="preserve">1.88118517398834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92860984802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.921835064888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9255987405777</t>
   </si>
   <si>
     <t xml:space="preserve">1.94065427780151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9263516664505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90376842021942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91957664489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91882383823395</t>
+    <t xml:space="preserve">1.92635142803192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90376853942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91957676410675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91882371902466</t>
   </si>
   <si>
     <t xml:space="preserve">1.93237388134003</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94366526603699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91054320335388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89021837711334</t>
+    <t xml:space="preserve">1.94366538524628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91054308414459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89021825790405</t>
   </si>
   <si>
     <t xml:space="preserve">1.90753221511841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89699327945709</t>
+    <t xml:space="preserve">1.89699339866638</t>
   </si>
   <si>
     <t xml:space="preserve">1.89473497867584</t>
@@ -806,16 +806,16 @@
     <t xml:space="preserve">1.77052700519562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79762709140778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76826870441437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7946161031723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80741333961487</t>
+    <t xml:space="preserve">1.79762697219849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76826858520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79461586475372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80741322040558</t>
   </si>
   <si>
     <t xml:space="preserve">1.83074915409088</t>
@@ -824,10 +824,10 @@
     <t xml:space="preserve">1.84881579875946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82547962665558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81042385101318</t>
+    <t xml:space="preserve">1.82547974586487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81042397022247</t>
   </si>
   <si>
     <t xml:space="preserve">1.82623255252838</t>
@@ -836,88 +836,88 @@
     <t xml:space="preserve">1.83601856231689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83902955055237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85257947444916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82171607017517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84806299209595</t>
+    <t xml:space="preserve">1.83902966976166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85257959365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82171595096588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84806287288666</t>
   </si>
   <si>
     <t xml:space="preserve">1.84655737876892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83752405643463</t>
+    <t xml:space="preserve">1.83752429485321</t>
   </si>
   <si>
     <t xml:space="preserve">1.8977462053299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91280174255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9737765789032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97151815891266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93086802959442</t>
+    <t xml:space="preserve">1.91280162334442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97377645969391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97151827812195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93086814880371</t>
   </si>
   <si>
     <t xml:space="preserve">1.93613755702972</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92108237743378</t>
+    <t xml:space="preserve">1.9210821390152</t>
   </si>
   <si>
     <t xml:space="preserve">1.88796019554138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88720738887787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89548778533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89322972297668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86914074420929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85860180854797</t>
+    <t xml:space="preserve">1.88720715045929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89548790454865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8932296037674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.869140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85860192775726</t>
   </si>
   <si>
     <t xml:space="preserve">1.85634338855743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85709631443024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85182702541351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86688232421875</t>
+    <t xml:space="preserve">1.85709619522095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85182690620422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86688220500946</t>
   </si>
   <si>
     <t xml:space="preserve">1.88494908809662</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87215161323547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87064611911774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86161315441132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88193798065186</t>
+    <t xml:space="preserve">1.87215173244476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87064623832703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86161291599274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88193774223328</t>
   </si>
   <si>
     <t xml:space="preserve">1.86763501167297</t>
@@ -926,34 +926,34 @@
     <t xml:space="preserve">1.87365734577179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86537671089172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84505188465118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84204065799713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84731042385101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84279358386993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81795191764832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82397413253784</t>
+    <t xml:space="preserve">1.86537683010101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84505200386047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84204077720642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84731030464172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84279346466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8179520368576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82397425174713</t>
   </si>
   <si>
     <t xml:space="preserve">1.82849097251892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81569373607635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82021021842957</t>
+    <t xml:space="preserve">1.81569385528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82021009922028</t>
   </si>
   <si>
     <t xml:space="preserve">1.81117689609528</t>
@@ -962,55 +962,55 @@
     <t xml:space="preserve">1.816446185112</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81418812274933</t>
+    <t xml:space="preserve">1.81418800354004</t>
   </si>
   <si>
     <t xml:space="preserve">1.83526575565338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83225464820862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82246851921082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85032117366791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89849877357483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93689036369324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91731810569763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97979867458344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96474301815033</t>
+    <t xml:space="preserve">1.83225476741791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8224686384201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85032141208649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89849889278412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93689024448395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91731822490692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97979855537415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96474313735962</t>
   </si>
   <si>
     <t xml:space="preserve">1.94667661190033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97076523303986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96775436401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96248459815979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10325360298157</t>
+    <t xml:space="preserve">1.97076511383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96775424480438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96248471736908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10325384140015</t>
   </si>
   <si>
     <t xml:space="preserve">2.04378437995911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0242121219635</t>
+    <t xml:space="preserve">2.02421236038208</t>
   </si>
   <si>
     <t xml:space="preserve">1.98732626438141</t>
@@ -1019,22 +1019,22 @@
     <t xml:space="preserve">1.99937069416046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98582088947296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99033749103546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96624863147736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99861812591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96549618244171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97603476047516</t>
+    <t xml:space="preserve">1.98582077026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99033761024475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96624851226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99861800670624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96549606323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97603487968445</t>
   </si>
   <si>
     <t xml:space="preserve">1.98280966281891</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">2.02496528625488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06260371208191</t>
+    <t xml:space="preserve">2.06260395050049</t>
   </si>
   <si>
     <t xml:space="preserve">2.07540106773376</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">2.07765960693359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09572601318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09045648574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11153435707092</t>
+    <t xml:space="preserve">2.09572625160217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09045672416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11153411865234</t>
   </si>
   <si>
     <t xml:space="preserve">2.10024261474609</t>
@@ -1076,7 +1076,7 @@
     <t xml:space="preserve">2.08669257164001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07013130187988</t>
+    <t xml:space="preserve">2.07013154029846</t>
   </si>
   <si>
     <t xml:space="preserve">2.06034564971924</t>
@@ -1085,19 +1085,19 @@
     <t xml:space="preserve">2.05959272384644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05884003639221</t>
+    <t xml:space="preserve">2.05883979797363</t>
   </si>
   <si>
     <t xml:space="preserve">2.07615375518799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08368134498596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10400676727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08518719673157</t>
+    <t xml:space="preserve">2.08368158340454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10400652885437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08518743515015</t>
   </si>
   <si>
     <t xml:space="preserve">2.13185930252075</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">2.1755199432373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16799259185791</t>
+    <t xml:space="preserve">2.16799235343933</t>
   </si>
   <si>
     <t xml:space="preserve">2.20563125610352</t>
@@ -1124,22 +1124,22 @@
     <t xml:space="preserve">2.31101989746094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36371421813965</t>
+    <t xml:space="preserve">2.36371397972107</t>
   </si>
   <si>
     <t xml:space="preserve">2.31854724884033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33360266685486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37124156951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32607507705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2884361743927</t>
+    <t xml:space="preserve">2.33360290527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37124180793762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32607531547546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28843641281128</t>
   </si>
   <si>
     <t xml:space="preserve">2.2658531665802</t>
@@ -1163,25 +1163,25 @@
     <t xml:space="preserve">2.18304800987244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43899154663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38629698753357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55190801620483</t>
+    <t xml:space="preserve">2.43899130821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38629722595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55190777778625</t>
   </si>
   <si>
     <t xml:space="preserve">2.54438018798828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61965727806091</t>
+    <t xml:space="preserve">2.61965751647949</t>
   </si>
   <si>
     <t xml:space="preserve">2.46157479286194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49168539047241</t>
+    <t xml:space="preserve">2.49168562889099</t>
   </si>
   <si>
     <t xml:space="preserve">2.46910238265991</t>
@@ -1193,25 +1193,25 @@
     <t xml:space="preserve">2.43146371841431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47663044929504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44651913642883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40888047218323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48415803909302</t>
+    <t xml:space="preserve">2.47663068771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44651937484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40888023376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4841582775116</t>
   </si>
   <si>
     <t xml:space="preserve">2.45404672622681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41640830039978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5067412853241</t>
+    <t xml:space="preserve">2.4164080619812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50674104690552</t>
   </si>
   <si>
     <t xml:space="preserve">2.5293242931366</t>
@@ -1220,19 +1220,19 @@
     <t xml:space="preserve">2.57587671279907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59139394760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58363509178162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56035923957825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50604867935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51380729675293</t>
+    <t xml:space="preserve">2.5913941860199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58363485336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56035947799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50604844093323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51380705833435</t>
   </si>
   <si>
     <t xml:space="preserve">2.52156591415405</t>
@@ -1241,13 +1241,10 @@
     <t xml:space="preserve">2.54484176635742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52932405471802</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.48277235031128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4982898235321</t>
+    <t xml:space="preserve">2.49828958511353</t>
   </si>
   <si>
     <t xml:space="preserve">2.42846179008484</t>
@@ -1277,7 +1274,7 @@
     <t xml:space="preserve">2.21897792816162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23449540138245</t>
+    <t xml:space="preserve">2.23449516296387</t>
   </si>
   <si>
     <t xml:space="preserve">2.25777125358582</t>
@@ -1295,7 +1292,7 @@
     <t xml:space="preserve">2.25001263618469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12587380409241</t>
+    <t xml:space="preserve">2.12587404251099</t>
   </si>
   <si>
     <t xml:space="preserve">2.10259819030762</t>
@@ -1304,22 +1301,22 @@
     <t xml:space="preserve">2.13363242149353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09483909606934</t>
+    <t xml:space="preserve">2.09483933448792</t>
   </si>
   <si>
     <t xml:space="preserve">2.08708071708679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07932162284851</t>
+    <t xml:space="preserve">2.07932186126709</t>
   </si>
   <si>
     <t xml:space="preserve">2.07156348228455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04052877426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14139127731323</t>
+    <t xml:space="preserve">2.0405285358429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14139151573181</t>
   </si>
   <si>
     <t xml:space="preserve">2.16466736793518</t>
@@ -1328,7 +1325,7 @@
     <t xml:space="preserve">2.14915013313293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18018484115601</t>
+    <t xml:space="preserve">2.18018460273743</t>
   </si>
   <si>
     <t xml:space="preserve">2.29656434059143</t>
@@ -1343,16 +1340,16 @@
     <t xml:space="preserve">2.02501130104065</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0094940662384</t>
+    <t xml:space="preserve">2.00949382781982</t>
   </si>
   <si>
     <t xml:space="preserve">1.97070062160492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96294188499451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93966615200043</t>
+    <t xml:space="preserve">1.9629420042038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93966591358185</t>
   </si>
   <si>
     <t xml:space="preserve">1.88535523414612</t>
@@ -1367,16 +1364,16 @@
     <t xml:space="preserve">1.86983799934387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79225134849548</t>
+    <t xml:space="preserve">1.79225146770477</t>
   </si>
   <si>
     <t xml:space="preserve">1.83880364894867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83104479312897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86207950115204</t>
+    <t xml:space="preserve">1.83104467391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86207938194275</t>
   </si>
   <si>
     <t xml:space="preserve">2.15690851211548</t>
@@ -1391,16 +1388,16 @@
     <t xml:space="preserve">2.0017352104187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97845935821533</t>
+    <t xml:space="preserve">1.97845947742462</t>
   </si>
   <si>
     <t xml:space="preserve">1.99397671222687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9241486787796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84656202793121</t>
+    <t xml:space="preserve">1.92414855957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84656190872192</t>
   </si>
   <si>
     <t xml:space="preserve">1.80776882171631</t>
@@ -1409,16 +1406,16 @@
     <t xml:space="preserve">1.75345814228058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77673411369324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74569964408875</t>
+    <t xml:space="preserve">1.77673399448395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74569952487946</t>
   </si>
   <si>
     <t xml:space="preserve">1.82328605651855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89311420917511</t>
+    <t xml:space="preserve">1.89311408996582</t>
   </si>
   <si>
     <t xml:space="preserve">1.91638994216919</t>
@@ -1430,7 +1427,7 @@
     <t xml:space="preserve">2.11035680770874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0560462474823</t>
+    <t xml:space="preserve">2.05604600906372</t>
   </si>
   <si>
     <t xml:space="preserve">2.26552987098694</t>
@@ -1442,7 +1439,7 @@
     <t xml:space="preserve">2.35087513923645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31984066963196</t>
+    <t xml:space="preserve">2.31984043121338</t>
   </si>
   <si>
     <t xml:space="preserve">2.3353579044342</t>
@@ -1451,22 +1448,22 @@
     <t xml:space="preserve">2.35863375663757</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40518569946289</t>
+    <t xml:space="preserve">2.40518593788147</t>
   </si>
   <si>
     <t xml:space="preserve">2.3819100856781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38966822624207</t>
+    <t xml:space="preserve">2.38966846466064</t>
   </si>
   <si>
     <t xml:space="preserve">2.39742732048035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41294479370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42070293426514</t>
+    <t xml:space="preserve">2.41294455528259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42070317268372</t>
   </si>
   <si>
     <t xml:space="preserve">2.36639261245728</t>
@@ -1484,111 +1481,114 @@
     <t xml:space="preserve">2.47501373291016</t>
   </si>
   <si>
+    <t xml:space="preserve">2.5526008605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54447102546692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52008318901062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49569535255432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4387903213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45504903793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47943663597107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48756623268127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50382447242737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40627312660217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43066096305847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42253160476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36562657356262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3900146484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2843337059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27620434761047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2274284362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23555779457092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25181651115417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26807498931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.357497215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32498025894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34123873710632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37375593185425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4631781578064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51195406913757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52821278572083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53634190559387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58511781692505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59324717521667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56072998046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6013765335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60950541496277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5688591003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57698845863342</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.55260062217712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5444712638855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52008318901062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49569535255432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4387903213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45504903793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47943663597107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48756623268127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50382447242737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40627288818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43066072463989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42253160476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3656268119812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3900146484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2843337059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27620434761047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2274284362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23555755615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25181651115417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26807498931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35749745368958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32498002052307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34123873710632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37375593185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4631781578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51195383071899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52821254730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53634190559387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58511805534363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59324717521667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56072998046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6013765335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60950541496277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5688591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57698845863342</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.4144024848938</t>
   </si>
   <si>
@@ -1601,7 +1601,7 @@
     <t xml:space="preserve">2.39814376831055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47130751609802</t>
+    <t xml:space="preserve">2.47130727767944</t>
   </si>
   <si>
     <t xml:space="preserve">2.44691967964172</t>
@@ -1619,7 +1619,7 @@
     <t xml:space="preserve">2.30059218406677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11361813545227</t>
+    <t xml:space="preserve">2.11361837387085</t>
   </si>
   <si>
     <t xml:space="preserve">2.18678188323975</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">2.12987685203552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08110117912292</t>
+    <t xml:space="preserve">2.08110094070435</t>
   </si>
   <si>
     <t xml:space="preserve">2.10548901557922</t>
@@ -1637,19 +1637,19 @@
     <t xml:space="preserve">2.1217474937439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.048583984375</t>
+    <t xml:space="preserve">2.04858374595642</t>
   </si>
   <si>
     <t xml:space="preserve">1.89412713050842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65837740898132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66650664806366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6258602142334</t>
+    <t xml:space="preserve">1.65837752819061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66650676727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62586009502411</t>
   </si>
   <si>
     <t xml:space="preserve">1.47140347957611</t>
@@ -1676,7 +1676,7 @@
     <t xml:space="preserve">1.4957914352417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58521378040314</t>
+    <t xml:space="preserve">1.58521366119385</t>
   </si>
   <si>
     <t xml:space="preserve">1.60147225856781</t>
@@ -1694,7 +1694,7 @@
     <t xml:space="preserve">1.5689549446106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63398957252502</t>
+    <t xml:space="preserve">1.63398945331573</t>
   </si>
   <si>
     <t xml:space="preserve">1.69089460372925</t>
@@ -1715,10 +1715,10 @@
     <t xml:space="preserve">1.67463600635529</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70715308189392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76405847072601</t>
+    <t xml:space="preserve">1.70715320110321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76405835151672</t>
   </si>
   <si>
     <t xml:space="preserve">1.73154103755951</t>
@@ -1727,25 +1727,25 @@
     <t xml:space="preserve">1.71528244018555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69902384281158</t>
+    <t xml:space="preserve">1.69902396202087</t>
   </si>
   <si>
     <t xml:space="preserve">1.6502480506897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74779975414276</t>
+    <t xml:space="preserve">1.74779963493347</t>
   </si>
   <si>
     <t xml:space="preserve">1.75592911243439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77218759059906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7884464263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82096338272095</t>
+    <t xml:space="preserve">1.77218747138977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78844630718231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82096362113953</t>
   </si>
   <si>
     <t xml:space="preserve">1.87786865234375</t>
@@ -1754,10 +1754,10 @@
     <t xml:space="preserve">1.82909286022186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80470490455627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81283402442932</t>
+    <t xml:space="preserve">1.80470478534698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81283414363861</t>
   </si>
   <si>
     <t xml:space="preserve">1.79657554626465</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">1.7803168296814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72341179847717</t>
+    <t xml:space="preserve">1.72341191768646</t>
   </si>
   <si>
     <t xml:space="preserve">1.73967039585114</t>
@@ -1775,13 +1775,13 @@
     <t xml:space="preserve">1.6827654838562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60960149765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64211881160736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57708430290222</t>
+    <t xml:space="preserve">1.60960137844086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64211869239807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57708418369293</t>
   </si>
   <si>
     <t xml:space="preserve">1.52830851078033</t>
@@ -1802,7 +1802,7 @@
     <t xml:space="preserve">1.43075704574585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42262768745422</t>
+    <t xml:space="preserve">1.42262780666351</t>
   </si>
   <si>
     <t xml:space="preserve">1.41043376922607</t>
@@ -1817,7 +1817,7 @@
     <t xml:space="preserve">1.41449844837189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36572253704071</t>
+    <t xml:space="preserve">1.36572241783142</t>
   </si>
   <si>
     <t xml:space="preserve">1.33320534229279</t>
@@ -1826,19 +1826,19 @@
     <t xml:space="preserve">1.38198125362396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35759329795837</t>
+    <t xml:space="preserve">1.35759341716766</t>
   </si>
   <si>
     <t xml:space="preserve">1.30475270748138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29255902767181</t>
+    <t xml:space="preserve">1.29255890846252</t>
   </si>
   <si>
     <t xml:space="preserve">1.3088173866272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33727014064789</t>
+    <t xml:space="preserve">1.3372700214386</t>
   </si>
   <si>
     <t xml:space="preserve">1.32507598400116</t>
@@ -1856,13 +1856,13 @@
     <t xml:space="preserve">1.39823985099792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40230429172516</t>
+    <t xml:space="preserve">1.40230441093445</t>
   </si>
   <si>
     <t xml:space="preserve">1.3860456943512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39011061191559</t>
+    <t xml:space="preserve">1.3901104927063</t>
   </si>
   <si>
     <t xml:space="preserve">1.37791657447815</t>
@@ -1874,7 +1874,7 @@
     <t xml:space="preserve">1.52017939090729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55269646644592</t>
+    <t xml:space="preserve">1.55269658565521</t>
   </si>
   <si>
     <t xml:space="preserve">1.54456722736359</t>
@@ -1883,28 +1883,28 @@
     <t xml:space="preserve">1.49172675609589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52424395084381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50798511505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51611459255219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54050254821777</t>
+    <t xml:space="preserve">1.5242440700531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50798523426056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51611471176147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54050266742706</t>
   </si>
   <si>
     <t xml:space="preserve">1.47953295707703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86973917484283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95103228092194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0729718208313</t>
+    <t xml:space="preserve">1.86973929405212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95103216171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07297158241272</t>
   </si>
   <si>
     <t xml:space="preserve">2.25994563102722</t>
@@ -1913,16 +1913,16 @@
     <t xml:space="preserve">2.24368715286255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1786527633667</t>
+    <t xml:space="preserve">2.17865252494812</t>
   </si>
   <si>
     <t xml:space="preserve">2.14613556861877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05671310424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13800597190857</t>
+    <t xml:space="preserve">2.05671286582947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13800621032715</t>
   </si>
   <si>
     <t xml:space="preserve">2.21116995811462</t>
@@ -1931,16 +1931,16 @@
     <t xml:space="preserve">2.21945142745972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2360143661499</t>
+    <t xml:space="preserve">2.23601460456848</t>
   </si>
   <si>
     <t xml:space="preserve">2.24429607391357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25257778167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20288825035095</t>
+    <t xml:space="preserve">2.25257754325867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20288848876953</t>
   </si>
   <si>
     <t xml:space="preserve">2.22773313522339</t>
@@ -1952,7 +1952,7 @@
     <t xml:space="preserve">2.17804384231567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.343674659729</t>
+    <t xml:space="preserve">2.34367442131042</t>
   </si>
   <si>
     <t xml:space="preserve">2.36023759841919</t>
@@ -1961,7 +1961,7 @@
     <t xml:space="preserve">2.36851906776428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38508224487305</t>
+    <t xml:space="preserve">2.38508200645447</t>
   </si>
   <si>
     <t xml:space="preserve">2.40164518356323</t>
@@ -1970,7 +1970,7 @@
     <t xml:space="preserve">2.45133447647095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47617888450623</t>
+    <t xml:space="preserve">2.4761791229248</t>
   </si>
   <si>
     <t xml:space="preserve">2.4844605922699</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">2.418208360672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39336347579956</t>
+    <t xml:space="preserve">2.39336371421814</t>
   </si>
   <si>
     <t xml:space="preserve">2.37680077552795</t>
@@ -1997,7 +1997,7 @@
     <t xml:space="preserve">2.42648983001709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33539319038391</t>
+    <t xml:space="preserve">2.33539295196533</t>
   </si>
   <si>
     <t xml:space="preserve">2.32711148262024</t>
@@ -2030,7 +2030,7 @@
     <t xml:space="preserve">2.12835454940796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13663601875305</t>
+    <t xml:space="preserve">2.13663625717163</t>
   </si>
   <si>
     <t xml:space="preserve">2.18632531166077</t>
@@ -2039,7 +2039,7 @@
     <t xml:space="preserve">2.08694696426392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1035099029541</t>
+    <t xml:space="preserve">2.10351014137268</t>
   </si>
   <si>
     <t xml:space="preserve">2.07038378715515</t>
@@ -2057,7 +2057,7 @@
     <t xml:space="preserve">2.26914072036743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26085925102234</t>
+    <t xml:space="preserve">2.26085901260376</t>
   </si>
   <si>
     <t xml:space="preserve">2.4099268913269</t>
@@ -2075,10 +2075,10 @@
     <t xml:space="preserve">2.50930500030518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62524652481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71634364128113</t>
+    <t xml:space="preserve">2.62524676322937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71634340286255</t>
   </si>
   <si>
     <t xml:space="preserve">2.69978022575378</t>
@@ -2096,13 +2096,13 @@
     <t xml:space="preserve">3.01447892189026</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03104162216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24636197090149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23808026313782</t>
+    <t xml:space="preserve">3.03104186058044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24636220932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2380805015564</t>
   </si>
   <si>
     <t xml:space="preserve">3.22979879379272</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">3.3043327331543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12213897705078</t>
+    <t xml:space="preserve">3.1221387386322</t>
   </si>
   <si>
     <t xml:space="preserve">3.1635468006134</t>
@@ -2132,7 +2132,7 @@
     <t xml:space="preserve">3.18010950088501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13042044639587</t>
+    <t xml:space="preserve">3.13042020797729</t>
   </si>
   <si>
     <t xml:space="preserve">3.10557556152344</t>
@@ -2144,7 +2144,7 @@
     <t xml:space="preserve">3.08901286125183</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07244944572449</t>
+    <t xml:space="preserve">3.07244968414307</t>
   </si>
   <si>
     <t xml:space="preserve">3.11385703086853</t>
@@ -2153,7 +2153,7 @@
     <t xml:space="preserve">3.08073139190674</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06416797637939</t>
+    <t xml:space="preserve">3.06416821479797</t>
   </si>
   <si>
     <t xml:space="preserve">3.254643201828</t>
@@ -2162,22 +2162,22 @@
     <t xml:space="preserve">3.09729433059692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93994498252869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02276039123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04760503768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05588674545288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15526485443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03932356834412</t>
+    <t xml:space="preserve">2.93994474411011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02276015281677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04760479927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0558865070343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15526509284973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03932332992554</t>
   </si>
   <si>
     <t xml:space="preserve">2.98963403701782</t>
@@ -2192,7 +2192,7 @@
     <t xml:space="preserve">2.97307133674622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20495438575745</t>
+    <t xml:space="preserve">3.20495414733887</t>
   </si>
   <si>
     <t xml:space="preserve">3.27948784828186</t>
@@ -18878,7 +18878,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G601" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -18904,7 +18904,7 @@
         <v>32</v>
       </c>
       <c r="G602" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -18930,7 +18930,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G603" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18956,7 +18956,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G604" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19008,7 +19008,7 @@
         <v>32</v>
       </c>
       <c r="G606" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19034,7 +19034,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G607" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19060,7 +19060,7 @@
         <v>30</v>
       </c>
       <c r="G608" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19086,7 +19086,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G609" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19112,7 +19112,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G610" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19138,7 +19138,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G611" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19164,7 +19164,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G612" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19190,7 +19190,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G613" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19216,7 +19216,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G614" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19242,7 +19242,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G615" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19268,7 +19268,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G616" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19294,7 +19294,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G617" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19320,7 +19320,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G618" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19346,7 +19346,7 @@
         <v>28</v>
       </c>
       <c r="G619" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19372,7 +19372,7 @@
         <v>28</v>
       </c>
       <c r="G620" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19398,7 +19398,7 @@
         <v>28</v>
       </c>
       <c r="G621" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19424,7 +19424,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G622" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19450,7 +19450,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G623" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19476,7 +19476,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G624" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19502,7 +19502,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G625" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19528,7 +19528,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G626" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19554,7 +19554,7 @@
         <v>29</v>
       </c>
       <c r="G627" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19580,7 +19580,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G628" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19606,7 +19606,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G629" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19632,7 +19632,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G630" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19658,7 +19658,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G631" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19684,7 +19684,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G632" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19710,7 +19710,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G633" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19736,7 +19736,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G634" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19762,7 +19762,7 @@
         <v>27.5</v>
       </c>
       <c r="G635" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19788,7 +19788,7 @@
         <v>27</v>
       </c>
       <c r="G636" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19814,7 +19814,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G637" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19840,7 +19840,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G638" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19866,7 +19866,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G639" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19892,7 +19892,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G640" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19918,7 +19918,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G641" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -19944,7 +19944,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G642" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19970,7 +19970,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G643" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19996,7 +19996,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G644" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20022,7 +20022,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G645" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20048,7 +20048,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G646" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20074,7 +20074,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G647" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20100,7 +20100,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G648" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20126,7 +20126,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G649" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20152,7 +20152,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G650" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20178,7 +20178,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G651" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20204,7 +20204,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G652" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20230,7 +20230,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G653" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20256,7 +20256,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G654" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20282,7 +20282,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G655" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20308,7 +20308,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G656" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20334,7 +20334,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G657" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20360,7 +20360,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G658" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20386,7 +20386,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G659" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20412,7 +20412,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G660" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20438,7 +20438,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G661" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20464,7 +20464,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G662" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20490,7 +20490,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G663" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -20516,7 +20516,7 @@
         <v>27.5</v>
       </c>
       <c r="G664" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20542,7 +20542,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G665" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20568,7 +20568,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G666" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20594,7 +20594,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G667" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20620,7 +20620,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G668" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20646,7 +20646,7 @@
         <v>27</v>
       </c>
       <c r="G669" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20672,7 +20672,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G670" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20698,7 +20698,7 @@
         <v>27</v>
       </c>
       <c r="G671" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20724,7 +20724,7 @@
         <v>26</v>
       </c>
       <c r="G672" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20750,7 +20750,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G673" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20776,7 +20776,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G674" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20802,7 +20802,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G675" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20828,7 +20828,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G676" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20854,7 +20854,7 @@
         <v>25</v>
       </c>
       <c r="G677" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20880,7 +20880,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G678" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20906,7 +20906,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G679" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -20932,7 +20932,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G680" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -20958,7 +20958,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G681" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -20984,7 +20984,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G682" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21010,7 +21010,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G683" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21036,7 +21036,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G684" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21062,7 +21062,7 @@
         <v>24</v>
       </c>
       <c r="G685" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21088,7 +21088,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G686" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21114,7 +21114,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G687" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21140,7 +21140,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G688" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21166,7 +21166,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G689" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21192,7 +21192,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G690" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21218,7 +21218,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G691" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21244,7 +21244,7 @@
         <v>27</v>
       </c>
       <c r="G692" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21270,7 +21270,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G693" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21296,7 +21296,7 @@
         <v>26</v>
       </c>
       <c r="G694" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21322,7 +21322,7 @@
         <v>26</v>
       </c>
       <c r="G695" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21348,7 +21348,7 @@
         <v>26</v>
       </c>
       <c r="G696" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21374,7 +21374,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G697" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21400,7 +21400,7 @@
         <v>26</v>
       </c>
       <c r="G698" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21426,7 +21426,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G699" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21452,7 +21452,7 @@
         <v>26</v>
       </c>
       <c r="G700" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21478,7 +21478,7 @@
         <v>25.5</v>
       </c>
       <c r="G701" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21504,7 +21504,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G702" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -21530,7 +21530,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G703" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21556,7 +21556,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G704" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21582,7 +21582,7 @@
         <v>26</v>
       </c>
       <c r="G705" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21608,7 +21608,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G706" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21634,7 +21634,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G707" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21660,7 +21660,7 @@
         <v>25.5</v>
       </c>
       <c r="G708" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21686,7 +21686,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G709" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21712,7 +21712,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G710" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21738,7 +21738,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G711" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21764,7 +21764,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G712" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21790,7 +21790,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G713" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21816,7 +21816,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G714" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21842,7 +21842,7 @@
         <v>24</v>
       </c>
       <c r="G715" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21868,7 +21868,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G716" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21894,7 +21894,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G717" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21920,7 +21920,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G718" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -21946,7 +21946,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G719" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -21972,7 +21972,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G720" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21998,7 +21998,7 @@
         <v>22.5</v>
       </c>
       <c r="G721" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22024,7 +22024,7 @@
         <v>23.5</v>
       </c>
       <c r="G722" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22050,7 +22050,7 @@
         <v>23.5</v>
       </c>
       <c r="G723" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22076,7 +22076,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G724" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22102,7 +22102,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G725" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22128,7 +22128,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G726" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22154,7 +22154,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G727" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22180,7 +22180,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G728" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22206,7 +22206,7 @@
         <v>25</v>
       </c>
       <c r="G729" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22232,7 +22232,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G730" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22258,7 +22258,7 @@
         <v>28</v>
       </c>
       <c r="G731" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22284,7 +22284,7 @@
         <v>28.5</v>
       </c>
       <c r="G732" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22310,7 +22310,7 @@
         <v>27.5</v>
       </c>
       <c r="G733" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22336,7 +22336,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G734" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22362,7 +22362,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G735" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22388,7 +22388,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G736" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22414,7 +22414,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G737" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22440,7 +22440,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G738" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22466,7 +22466,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G739" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -22492,7 +22492,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G740" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -22518,7 +22518,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G741" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22544,7 +22544,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G742" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22570,7 +22570,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G743" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22596,7 +22596,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G744" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22622,7 +22622,7 @@
         <v>27.5</v>
       </c>
       <c r="G745" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22648,7 +22648,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G746" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22674,7 +22674,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G747" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22700,7 +22700,7 @@
         <v>27.5</v>
       </c>
       <c r="G748" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22726,7 +22726,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G749" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22752,7 +22752,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G750" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22778,7 +22778,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G751" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22804,7 +22804,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G752" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22830,7 +22830,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G753" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22856,7 +22856,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G754" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22882,7 +22882,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G755" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22908,7 +22908,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G756" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -22934,7 +22934,7 @@
         <v>26.5</v>
       </c>
       <c r="G757" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -22960,7 +22960,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G758" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -22986,7 +22986,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G759" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23012,7 +23012,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G760" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23038,7 +23038,7 @@
         <v>27</v>
       </c>
       <c r="G761" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23064,7 +23064,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G762" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23090,7 +23090,7 @@
         <v>27</v>
       </c>
       <c r="G763" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23116,7 +23116,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G764" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23142,7 +23142,7 @@
         <v>26.5</v>
       </c>
       <c r="G765" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23168,7 +23168,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G766" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23194,7 +23194,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G767" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23220,7 +23220,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G768" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23246,7 +23246,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G769" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23272,7 +23272,7 @@
         <v>28.5</v>
       </c>
       <c r="G770" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23298,7 +23298,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G771" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23324,7 +23324,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G772" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23350,7 +23350,7 @@
         <v>28</v>
       </c>
       <c r="G773" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23376,7 +23376,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G774" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23402,7 +23402,7 @@
         <v>28</v>
       </c>
       <c r="G775" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23428,7 +23428,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G776" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23454,7 +23454,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G777" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23480,7 +23480,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G778" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -23506,7 +23506,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G779" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -23532,7 +23532,7 @@
         <v>28.5</v>
       </c>
       <c r="G780" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23558,7 +23558,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G781" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23584,7 +23584,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G782" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23610,7 +23610,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G783" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23636,7 +23636,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G784" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23662,7 +23662,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G785" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23688,7 +23688,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G786" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23714,7 +23714,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G787" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23740,7 +23740,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G788" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23766,7 +23766,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G789" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23792,7 +23792,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G790" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23818,7 +23818,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G791" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23844,7 +23844,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G792" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23870,7 +23870,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G793" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23896,7 +23896,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G794" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23922,7 +23922,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G795" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -23948,7 +23948,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G796" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -23974,7 +23974,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G797" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24000,7 +24000,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G798" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24026,7 +24026,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G799" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24052,7 +24052,7 @@
         <v>30</v>
       </c>
       <c r="G800" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24078,7 +24078,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G801" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24104,7 +24104,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G802" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24130,7 +24130,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G803" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24156,7 +24156,7 @@
         <v>31</v>
       </c>
       <c r="G804" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24182,7 +24182,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G805" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24208,7 +24208,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G806" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24234,7 +24234,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G807" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24260,7 +24260,7 @@
         <v>31</v>
       </c>
       <c r="G808" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24286,7 +24286,7 @@
         <v>31</v>
       </c>
       <c r="G809" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24312,7 +24312,7 @@
         <v>31</v>
       </c>
       <c r="G810" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24338,7 +24338,7 @@
         <v>31</v>
       </c>
       <c r="G811" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24364,7 +24364,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G812" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24390,7 +24390,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G813" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24416,7 +24416,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G814" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24442,7 +24442,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G815" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24468,7 +24468,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G816" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -24494,7 +24494,7 @@
         <v>31</v>
       </c>
       <c r="G817" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -24520,7 +24520,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G818" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24546,7 +24546,7 @@
         <v>31</v>
       </c>
       <c r="G819" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24572,7 +24572,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G820" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24598,7 +24598,7 @@
         <v>30.5</v>
       </c>
       <c r="G821" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24624,7 +24624,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G822" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24650,7 +24650,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G823" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24676,7 +24676,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G824" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24702,7 +24702,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G825" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24728,7 +24728,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G826" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24754,7 +24754,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G827" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24780,7 +24780,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G828" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24806,7 +24806,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G829" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24832,7 +24832,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G830" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24858,7 +24858,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G831" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24884,7 +24884,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G832" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24910,7 +24910,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G833" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -24936,7 +24936,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G834" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -24962,7 +24962,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G835" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -24988,7 +24988,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G836" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25014,7 +25014,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G837" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25040,7 +25040,7 @@
         <v>31</v>
       </c>
       <c r="G838" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25066,7 +25066,7 @@
         <v>31</v>
       </c>
       <c r="G839" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25092,7 +25092,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G840" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25118,7 +25118,7 @@
         <v>30</v>
       </c>
       <c r="G841" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25144,7 +25144,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G842" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25170,7 +25170,7 @@
         <v>30.5</v>
       </c>
       <c r="G843" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25196,7 +25196,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G844" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25222,7 +25222,7 @@
         <v>30.5</v>
       </c>
       <c r="G845" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25248,7 +25248,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G846" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25274,7 +25274,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G847" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25300,7 +25300,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G848" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25326,7 +25326,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G849" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25352,7 +25352,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G850" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25378,7 +25378,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G851" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25404,7 +25404,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G852" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -25430,7 +25430,7 @@
         <v>28</v>
       </c>
       <c r="G853" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -25456,7 +25456,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G854" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -25482,7 +25482,7 @@
         <v>28</v>
       </c>
       <c r="G855" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -25508,7 +25508,7 @@
         <v>27.5</v>
       </c>
       <c r="G856" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25534,7 +25534,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G857" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25560,7 +25560,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G858" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25586,7 +25586,7 @@
         <v>27.5</v>
       </c>
       <c r="G859" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25612,7 +25612,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G860" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25638,7 +25638,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G861" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25664,7 +25664,7 @@
         <v>28</v>
       </c>
       <c r="G862" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25690,7 +25690,7 @@
         <v>29</v>
       </c>
       <c r="G863" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25716,7 +25716,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G864" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25742,7 +25742,7 @@
         <v>29</v>
       </c>
       <c r="G865" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25768,7 +25768,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G866" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -25794,7 +25794,7 @@
         <v>29</v>
       </c>
       <c r="G867" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25820,7 +25820,7 @@
         <v>29</v>
       </c>
       <c r="G868" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -25846,7 +25846,7 @@
         <v>29</v>
       </c>
       <c r="G869" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -25872,7 +25872,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G870" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -25898,7 +25898,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G871" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25924,7 +25924,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G872" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -25950,7 +25950,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G873" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -25976,7 +25976,7 @@
         <v>30.5</v>
       </c>
       <c r="G874" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -26002,7 +26002,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G875" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -26028,7 +26028,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G876" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -26054,7 +26054,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G877" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -26080,7 +26080,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G878" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -26106,7 +26106,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G879" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26132,7 +26132,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G880" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -26158,7 +26158,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G881" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -26184,7 +26184,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G882" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -26210,7 +26210,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G883" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -26236,7 +26236,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G884" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -26262,7 +26262,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G885" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -26288,7 +26288,7 @@
         <v>31.5</v>
       </c>
       <c r="G886" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -26314,7 +26314,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G887" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -26340,7 +26340,7 @@
         <v>32</v>
       </c>
       <c r="G888" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -26366,7 +26366,7 @@
         <v>31.5</v>
       </c>
       <c r="G889" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -26392,7 +26392,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G890" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -26418,7 +26418,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G891" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -26444,7 +26444,7 @@
         <v>32</v>
       </c>
       <c r="G892" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -26470,7 +26470,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G893" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -26496,7 +26496,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G894" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -26522,7 +26522,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26548,7 +26548,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G896" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -26574,7 +26574,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G897" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -26600,7 +26600,7 @@
         <v>31</v>
       </c>
       <c r="G898" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -26626,7 +26626,7 @@
         <v>31</v>
       </c>
       <c r="G899" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -26652,7 +26652,7 @@
         <v>31</v>
       </c>
       <c r="G900" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -26678,7 +26678,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G901" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -26704,7 +26704,7 @@
         <v>31</v>
       </c>
       <c r="G902" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -26730,7 +26730,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G903" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -26756,7 +26756,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G904" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -26782,7 +26782,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G905" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -26808,7 +26808,7 @@
         <v>31</v>
       </c>
       <c r="G906" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -26834,7 +26834,7 @@
         <v>31</v>
       </c>
       <c r="G907" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -26860,7 +26860,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G908" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -26886,7 +26886,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G909" t="s">
-        <v>490</v>
+        <v>524</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -26912,7 +26912,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G910" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -26938,7 +26938,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G911" t="s">
-        <v>490</v>
+        <v>524</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -26964,7 +26964,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G912" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -26990,7 +26990,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G913" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -27016,7 +27016,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G914" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -27042,7 +27042,7 @@
         <v>30</v>
       </c>
       <c r="G915" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -27068,7 +27068,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G916" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -27120,7 +27120,7 @@
         <v>29</v>
       </c>
       <c r="G918" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -27172,7 +27172,7 @@
         <v>29</v>
       </c>
       <c r="G920" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -27250,7 +27250,7 @@
         <v>29</v>
       </c>
       <c r="G923" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -27276,7 +27276,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G924" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -27302,7 +27302,7 @@
         <v>29</v>
       </c>
       <c r="G925" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -27328,7 +27328,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G926" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -27354,7 +27354,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G927" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -27380,7 +27380,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G928" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -27432,7 +27432,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G930" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -27458,7 +27458,7 @@
         <v>30.5</v>
       </c>
       <c r="G931" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -27484,7 +27484,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G932" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -27588,7 +27588,7 @@
         <v>30</v>
       </c>
       <c r="G936" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -27666,7 +27666,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G939" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -27692,7 +27692,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G940" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -27718,7 +27718,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G941" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -27744,7 +27744,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G942" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -27770,7 +27770,7 @@
         <v>30</v>
       </c>
       <c r="G943" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -27796,7 +27796,7 @@
         <v>30</v>
       </c>
       <c r="G944" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -27848,7 +27848,7 @@
         <v>30</v>
       </c>
       <c r="G946" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -27874,7 +27874,7 @@
         <v>30.5</v>
       </c>
       <c r="G947" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -27900,7 +27900,7 @@
         <v>30.5</v>
       </c>
       <c r="G948" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -27926,7 +27926,7 @@
         <v>30</v>
       </c>
       <c r="G949" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -27978,7 +27978,7 @@
         <v>30</v>
       </c>
       <c r="G951" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -28030,7 +28030,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G953" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -28082,7 +28082,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G955" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -28108,7 +28108,7 @@
         <v>30</v>
       </c>
       <c r="G956" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -28134,7 +28134,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G957" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -28160,7 +28160,7 @@
         <v>30</v>
       </c>
       <c r="G958" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -28186,7 +28186,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G959" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -28212,7 +28212,7 @@
         <v>30</v>
       </c>
       <c r="G960" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -28238,7 +28238,7 @@
         <v>30</v>
       </c>
       <c r="G961" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -28264,7 +28264,7 @@
         <v>30</v>
       </c>
       <c r="G962" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -28290,7 +28290,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G963" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -28316,7 +28316,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G964" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -28342,7 +28342,7 @@
         <v>30</v>
       </c>
       <c r="G965" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -28368,7 +28368,7 @@
         <v>30</v>
       </c>
       <c r="G966" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -28420,7 +28420,7 @@
         <v>30</v>
       </c>
       <c r="G968" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -28446,7 +28446,7 @@
         <v>30</v>
       </c>
       <c r="G969" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -28524,7 +28524,7 @@
         <v>30</v>
       </c>
       <c r="G972" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -28576,7 +28576,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G974" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -28602,7 +28602,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G975" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -28654,7 +28654,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G977" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -28680,7 +28680,7 @@
         <v>31</v>
       </c>
       <c r="G978" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28706,7 +28706,7 @@
         <v>31</v>
       </c>
       <c r="G979" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -28732,7 +28732,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G980" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28758,7 +28758,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G981" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -28784,7 +28784,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G982" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -28810,7 +28810,7 @@
         <v>31</v>
       </c>
       <c r="G983" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -28836,7 +28836,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G984" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -28862,7 +28862,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G985" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28888,7 +28888,7 @@
         <v>31</v>
       </c>
       <c r="G986" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -28914,7 +28914,7 @@
         <v>31.5</v>
       </c>
       <c r="G987" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -28940,7 +28940,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G988" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -28966,7 +28966,7 @@
         <v>31.5</v>
       </c>
       <c r="G989" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -28992,7 +28992,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G990" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -29018,7 +29018,7 @@
         <v>31.5</v>
       </c>
       <c r="G991" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -29044,7 +29044,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G992" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -29070,7 +29070,7 @@
         <v>31.5</v>
       </c>
       <c r="G993" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -29096,7 +29096,7 @@
         <v>31.5</v>
       </c>
       <c r="G994" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -29122,7 +29122,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G995" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -29148,7 +29148,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G996" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -29174,7 +29174,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G997" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -29200,7 +29200,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G998" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -29226,7 +29226,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G999" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -29252,7 +29252,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1000" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -29278,7 +29278,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1001" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -29304,7 +29304,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1002" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -29330,7 +29330,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1003" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -29356,7 +29356,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1004" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -29382,7 +29382,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1005" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -29408,7 +29408,7 @@
         <v>31</v>
       </c>
       <c r="G1006" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -29434,7 +29434,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1007" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -29460,7 +29460,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1008" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -29486,7 +29486,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1009" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -29512,7 +29512,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1010" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -29538,7 +29538,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1011" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -29564,7 +29564,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1012" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -29590,7 +29590,7 @@
         <v>30.5</v>
       </c>
       <c r="G1013" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -29616,7 +29616,7 @@
         <v>30.5</v>
       </c>
       <c r="G1014" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -29668,7 +29668,7 @@
         <v>30.5</v>
       </c>
       <c r="G1016" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -29720,7 +29720,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1018" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -29746,7 +29746,7 @@
         <v>30</v>
       </c>
       <c r="G1019" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -29772,7 +29772,7 @@
         <v>30.5</v>
       </c>
       <c r="G1020" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -29798,7 +29798,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1021" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -29824,7 +29824,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1022" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -29850,7 +29850,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G1023" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -29876,7 +29876,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1024" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -29902,7 +29902,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1025" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -29928,7 +29928,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1026" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -29954,7 +29954,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1027" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -29980,7 +29980,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1028" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -30006,7 +30006,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1029" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -30032,7 +30032,7 @@
         <v>30</v>
       </c>
       <c r="G1030" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -30058,7 +30058,7 @@
         <v>30</v>
       </c>
       <c r="G1031" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -30084,7 +30084,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1032" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -30266,7 +30266,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1039" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -30292,7 +30292,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1040" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -30318,7 +30318,7 @@
         <v>28</v>
       </c>
       <c r="G1041" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -30448,7 +30448,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1046" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -30500,7 +30500,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1048" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -30526,7 +30526,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1049" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -30578,7 +30578,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1051" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -30604,7 +30604,7 @@
         <v>28</v>
       </c>
       <c r="G1052" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -30682,7 +30682,7 @@
         <v>27.5</v>
       </c>
       <c r="G1055" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -36948,7 +36948,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1296" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -36974,7 +36974,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1297" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -37026,7 +37026,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1299" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -37078,7 +37078,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1301" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -37104,7 +37104,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1302" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -37130,7 +37130,7 @@
         <v>29</v>
       </c>
       <c r="G1303" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -37156,7 +37156,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1304" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -37182,7 +37182,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1305" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -37286,7 +37286,7 @@
         <v>28</v>
       </c>
       <c r="G1309" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -37312,7 +37312,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1310" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -37338,7 +37338,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1311" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -37416,7 +37416,7 @@
         <v>28</v>
       </c>
       <c r="G1314" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -37442,7 +37442,7 @@
         <v>28</v>
       </c>
       <c r="G1315" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -37468,7 +37468,7 @@
         <v>28</v>
       </c>
       <c r="G1316" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -37832,7 +37832,7 @@
         <v>27.5</v>
       </c>
       <c r="G1330" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -38014,7 +38014,7 @@
         <v>27.5</v>
       </c>
       <c r="G1337" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -68624,7 +68624,7 @@
     </row>
     <row r="2515">
       <c r="A2515" s="1" t="n">
-        <v>45980.4498263889</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B2515" t="n">
         <v>70</v>
@@ -68645,6 +68645,32 @@
         <v>937</v>
       </c>
       <c r="H2515" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" s="1" t="n">
+        <v>45981.6576851852</v>
+      </c>
+      <c r="B2516" t="n">
+        <v>661</v>
+      </c>
+      <c r="C2516" t="n">
+        <v>2.61999988555908</v>
+      </c>
+      <c r="D2516" t="n">
+        <v>2.60500001907349</v>
+      </c>
+      <c r="E2516" t="n">
+        <v>2.60500001907349</v>
+      </c>
+      <c r="F2516" t="n">
+        <v>2.61999988555908</v>
+      </c>
+      <c r="G2516" t="s">
+        <v>906</v>
+      </c>
+      <c r="H2516" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24616158008575</t>
+    <t xml:space="preserve">1.24616146087646</t>
   </si>
   <si>
     <t xml:space="preserve">AUTME.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24544644355774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24330186843872</t>
+    <t xml:space="preserve">1.24544656276703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24330163002014</t>
   </si>
   <si>
     <t xml:space="preserve">1.22256803512573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21541857719421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22185325622559</t>
+    <t xml:space="preserve">1.2154186964035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2218531370163</t>
   </si>
   <si>
     <t xml:space="preserve">1.21470355987549</t>
@@ -68,13 +68,13 @@
     <t xml:space="preserve">1.21327364444733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20683908462524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20111954212189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20040440559387</t>
+    <t xml:space="preserve">1.20683896541595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2011194229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20040464401245</t>
   </si>
   <si>
     <t xml:space="preserve">1.16680181026459</t>
@@ -83,13 +83,13 @@
     <t xml:space="preserve">1.19468486309052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25688552856445</t>
+    <t xml:space="preserve">1.25688564777374</t>
   </si>
   <si>
     <t xml:space="preserve">1.25045108795166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24687623977661</t>
+    <t xml:space="preserve">1.24687647819519</t>
   </si>
   <si>
     <t xml:space="preserve">1.25116610527039</t>
@@ -107,22 +107,22 @@
     <t xml:space="preserve">1.210413813591</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22113811969757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19397008419037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22685790061951</t>
+    <t xml:space="preserve">1.22113823890686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19396996498108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22685778141022</t>
   </si>
   <si>
     <t xml:space="preserve">1.20469427108765</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25831580162048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26546514034271</t>
+    <t xml:space="preserve">1.2583155632019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.265465259552</t>
   </si>
   <si>
     <t xml:space="preserve">1.25903058052063</t>
@@ -134,28 +134,28 @@
     <t xml:space="preserve">1.21684849262238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22828757762909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27404475212097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26689493656158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27261483669281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27189981937408</t>
+    <t xml:space="preserve">1.22828769683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27404451370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26689505577087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27261459827423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27189970016479</t>
   </si>
   <si>
     <t xml:space="preserve">1.2790492773056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26761019229889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25545573234558</t>
+    <t xml:space="preserve">1.2676100730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25545585155487</t>
   </si>
   <si>
     <t xml:space="preserve">1.26260542869568</t>
@@ -164,40 +164,40 @@
     <t xml:space="preserve">1.24830627441406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2490211725235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24258649349213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23686683177948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23472213745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23400747776031</t>
+    <t xml:space="preserve">1.24902141094208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24258661270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23686707019806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23472225666046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23400735855103</t>
   </si>
   <si>
     <t xml:space="preserve">1.25225365161896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26176798343658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26835489273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27860128879547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27640569210052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27421021461487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27494215965271</t>
+    <t xml:space="preserve">1.26176810264587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26835513114929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27860152721405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27640581130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27421009540558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27494204044342</t>
   </si>
   <si>
     <t xml:space="preserve">1.26323187351227</t>
@@ -206,13 +206,13 @@
     <t xml:space="preserve">1.27128267288208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26689112186432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28445649147034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28079700469971</t>
+    <t xml:space="preserve">1.26689124107361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28445637226105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.280797123909</t>
   </si>
   <si>
     <t xml:space="preserve">1.2793333530426</t>
@@ -224,16 +224,16 @@
     <t xml:space="preserve">1.27274644374847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26615917682648</t>
+    <t xml:space="preserve">1.26615929603577</t>
   </si>
   <si>
     <t xml:space="preserve">1.28226089477539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28811609745026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28738415241241</t>
+    <t xml:space="preserve">1.28811585903168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28738403320312</t>
   </si>
   <si>
     <t xml:space="preserve">1.28299272060394</t>
@@ -245,13 +245,13 @@
     <t xml:space="preserve">1.24127531051636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2434709072113</t>
+    <t xml:space="preserve">1.24347102642059</t>
   </si>
   <si>
     <t xml:space="preserve">1.22956514358521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23468840122223</t>
+    <t xml:space="preserve">1.23468852043152</t>
   </si>
   <si>
     <t xml:space="preserve">1.22663760185242</t>
@@ -260,22 +260,22 @@
     <t xml:space="preserve">1.20687675476074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20760869979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18565213680267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17833340167999</t>
+    <t xml:space="preserve">1.20760881900787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18565237522125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1783332824707</t>
   </si>
   <si>
     <t xml:space="preserve">1.18784785270691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.16955065727234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17101454734802</t>
+    <t xml:space="preserve">1.16955077648163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17101442813873</t>
   </si>
   <si>
     <t xml:space="preserve">1.17028260231018</t>
@@ -284,22 +284,22 @@
     <t xml:space="preserve">1.18931150436401</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22224652767181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22151470184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23981153964996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2390798330307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23834776878357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23542010784149</t>
+    <t xml:space="preserve">1.22224628925323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22151446342468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23981165885925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23907971382141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23834788799286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23542022705078</t>
   </si>
   <si>
     <t xml:space="preserve">1.20614492893219</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">1.2310289144516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19736218452454</t>
+    <t xml:space="preserve">1.19736230373383</t>
   </si>
   <si>
     <t xml:space="preserve">1.2171231508255</t>
@@ -317,19 +317,19 @@
     <t xml:space="preserve">1.22297811508179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23322463035583</t>
+    <t xml:space="preserve">1.23322474956512</t>
   </si>
   <si>
     <t xml:space="preserve">1.23249268531799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22883331775665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28518855571747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25884079933167</t>
+    <t xml:space="preserve">1.22883343696594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2851881980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25884068012238</t>
   </si>
   <si>
     <t xml:space="preserve">1.3071448802948</t>
@@ -338,37 +338,37 @@
     <t xml:space="preserve">1.29909420013428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32324647903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31665921211243</t>
+    <t xml:space="preserve">1.32324624061584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31665933132172</t>
   </si>
   <si>
     <t xml:space="preserve">1.32763767242432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30348527431488</t>
+    <t xml:space="preserve">1.30348539352417</t>
   </si>
   <si>
     <t xml:space="preserve">1.31592750549316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31812310218811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29763031005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30275344848633</t>
+    <t xml:space="preserve">1.3181232213974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29763054847717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30275356769562</t>
   </si>
   <si>
     <t xml:space="preserve">1.29982614517212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28884792327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29543495178223</t>
+    <t xml:space="preserve">1.28884780406952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29543483257294</t>
   </si>
   <si>
     <t xml:space="preserve">1.30055809020996</t>
@@ -383,43 +383,43 @@
     <t xml:space="preserve">1.29250729084015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30128979682922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30568134784698</t>
+    <t xml:space="preserve">1.30128991603851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3056812286377</t>
   </si>
   <si>
     <t xml:space="preserve">1.26908695697784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26762318611145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24786233901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25518107414246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26542747020721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28006541728973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25810873508453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25005781650543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24054336547852</t>
+    <t xml:space="preserve">1.26762306690216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24786221981049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25518119335175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2654275894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28006517887115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25810861587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25005805492401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24054348468781</t>
   </si>
   <si>
     <t xml:space="preserve">1.24639868736267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24420297145844</t>
+    <t xml:space="preserve">1.24420285224915</t>
   </si>
   <si>
     <t xml:space="preserve">1.23615205287933</t>
@@ -428,28 +428,28 @@
     <t xml:space="preserve">1.23688399791718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24200713634491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23176085948944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20980441570282</t>
+    <t xml:space="preserve">1.2420072555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23176074028015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20980453491211</t>
   </si>
   <si>
     <t xml:space="preserve">1.21126806735992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21858704090118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21492755413055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19004333019257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18199288845062</t>
+    <t xml:space="preserve">1.21858692169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21492767333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19004344940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18199265003204</t>
   </si>
   <si>
     <t xml:space="preserve">1.214195728302</t>
@@ -461,7 +461,7 @@
     <t xml:space="preserve">1.19663035869598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22005093097687</t>
+    <t xml:space="preserve">1.22005069255829</t>
   </si>
   <si>
     <t xml:space="preserve">1.21639144420624</t>
@@ -476,19 +476,19 @@
     <t xml:space="preserve">1.28592026233673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29470300674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29689848423004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31007254123688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32544219493866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34081172943115</t>
+    <t xml:space="preserve">1.2947028875351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29689836502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31007242202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32544195652008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34081161022186</t>
   </si>
   <si>
     <t xml:space="preserve">1.3334926366806</t>
@@ -497,94 +497,94 @@
     <t xml:space="preserve">1.33422458171844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33202886581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33861589431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33934760093689</t>
+    <t xml:space="preserve">1.3320289850235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33861601352692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33934772014618</t>
   </si>
   <si>
     <t xml:space="preserve">1.34666657447815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34227514266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34007966518402</t>
+    <t xml:space="preserve">1.34227526187897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34007978439331</t>
   </si>
   <si>
     <t xml:space="preserve">1.32690572738647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32105076313019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34593462944031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36130452156067</t>
+    <t xml:space="preserve">1.3210506439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3459347486496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36130428314209</t>
   </si>
   <si>
     <t xml:space="preserve">1.36057245731354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33276069164276</t>
+    <t xml:space="preserve">1.33276081085205</t>
   </si>
   <si>
     <t xml:space="preserve">1.34959423542023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33788406848907</t>
+    <t xml:space="preserve">1.33788430690765</t>
   </si>
   <si>
     <t xml:space="preserve">1.34373915195465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34520280361176</t>
+    <t xml:space="preserve">1.34520292282104</t>
   </si>
   <si>
     <t xml:space="preserve">1.32910132408142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36349999904633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36789131164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37667405605316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38252878189087</t>
+    <t xml:space="preserve">1.36349987983704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36789119243622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37667393684387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38252890110016</t>
   </si>
   <si>
     <t xml:space="preserve">1.39789855480194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41253626346588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40668118000031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40814471244812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40887653827667</t>
+    <t xml:space="preserve">1.41253614425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40668106079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40814483165741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40887677669525</t>
   </si>
   <si>
     <t xml:space="preserve">1.40302181243896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39277565479279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36935484409332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37886965274811</t>
+    <t xml:space="preserve">1.39277529716492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36935496330261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37886953353882</t>
   </si>
   <si>
     <t xml:space="preserve">1.38911581039429</t>
@@ -593,52 +593,52 @@
     <t xml:space="preserve">1.40155792236328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49304342269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4762099981308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48206508159637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49157965183258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50328993797302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46742749214172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45864498615265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47913765907288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49523913860321</t>
+    <t xml:space="preserve">1.4930431842804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47621035575867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48206520080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49157953262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50328981876373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46742761135101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45864474773407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47913777828217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49523901939392</t>
   </si>
   <si>
     <t xml:space="preserve">1.49084782600403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48792028427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52744197845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50987660884857</t>
+    <t xml:space="preserve">1.48792040348053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52744209766388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50987684726715</t>
   </si>
   <si>
     <t xml:space="preserve">1.53256523609161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52963769435883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53183329105377</t>
+    <t xml:space="preserve">1.52963757514954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53183352947235</t>
   </si>
   <si>
     <t xml:space="preserve">1.52817380428314</t>
@@ -647,13 +647,13 @@
     <t xml:space="preserve">1.51499998569489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49963057041168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.498166680336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48572444915771</t>
+    <t xml:space="preserve">1.49963045120239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49816644191742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.485724568367</t>
   </si>
   <si>
     <t xml:space="preserve">1.47108709812164</t>
@@ -662,28 +662,28 @@
     <t xml:space="preserve">1.4842609167099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46376812458038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45498549938202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48499286174774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52085506916046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53768837451935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58233320713043</t>
+    <t xml:space="preserve">1.46376800537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45498526096344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48499274253845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52085518836975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53768849372864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58233332633972</t>
   </si>
   <si>
     <t xml:space="preserve">1.63126385211945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63427460193634</t>
+    <t xml:space="preserve">1.63427484035492</t>
   </si>
   <si>
     <t xml:space="preserve">1.64857769012451</t>
@@ -695,64 +695,64 @@
     <t xml:space="preserve">1.66664397716522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66288018226624</t>
+    <t xml:space="preserve">1.66288030147552</t>
   </si>
   <si>
     <t xml:space="preserve">1.6613746881485</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76902174949646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80816602706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84429895877838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9165655374527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99485421180725</t>
+    <t xml:space="preserve">1.76902151107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8081659078598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84429919719696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91656541824341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99485397338867</t>
   </si>
   <si>
     <t xml:space="preserve">2.01367354393005</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95345139503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98205697536469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9301153421402</t>
+    <t xml:space="preserve">1.95345175266266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9820568561554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93011546134949</t>
   </si>
   <si>
     <t xml:space="preserve">1.83376038074493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90301561355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90452110767365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9120489358902</t>
+    <t xml:space="preserve">1.9030157327652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90452098846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91204881668091</t>
   </si>
   <si>
     <t xml:space="preserve">1.93538475036621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92258810997009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91581284999847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88118493556976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92860984802246</t>
+    <t xml:space="preserve">1.92258763313293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9158126115799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88118505477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92860996723175</t>
   </si>
   <si>
     <t xml:space="preserve">1.921835064888</t>
@@ -764,40 +764,40 @@
     <t xml:space="preserve">1.94065427780151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9263516664505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90376842021942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91957640647888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91882371902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93237400054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94366538524628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91054320335388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89021837711334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90753245353699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89699351787567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89473497867584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87742137908936</t>
+    <t xml:space="preserve">1.92635154724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90376830101013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91957652568817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91882395744324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93237376213074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94366526603699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91054332256317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89021849632263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90753221511841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89699339866638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89473509788513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87742114067078</t>
   </si>
   <si>
     <t xml:space="preserve">1.86010730266571</t>
@@ -809,37 +809,37 @@
     <t xml:space="preserve">1.79762709140778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76826882362366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79461598396301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80741310119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83074903488159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84881556034088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82547986507416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81042408943176</t>
+    <t xml:space="preserve">1.76826858520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7946161031723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80741322040558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83074915409088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84881579875946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82547962665558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81042432785034</t>
   </si>
   <si>
     <t xml:space="preserve">1.82623255252838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83601868152618</t>
+    <t xml:space="preserve">1.83601856231689</t>
   </si>
   <si>
     <t xml:space="preserve">1.83902990818024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85257959365845</t>
+    <t xml:space="preserve">1.85257971286774</t>
   </si>
   <si>
     <t xml:space="preserve">1.82171583175659</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">1.84806287288666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84655725955963</t>
+    <t xml:space="preserve">1.84655737876892</t>
   </si>
   <si>
     <t xml:space="preserve">1.83752405643463</t>
@@ -857,19 +857,19 @@
     <t xml:space="preserve">1.89774596691132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91280162334442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97377622127533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97151827812195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93086802959442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93613767623901</t>
+    <t xml:space="preserve">1.91280150413513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97377645969391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97151815891266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93086838722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93613755702972</t>
   </si>
   <si>
     <t xml:space="preserve">1.9210821390152</t>
@@ -878,25 +878,25 @@
     <t xml:space="preserve">1.88796007633209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88720738887787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89548766613007</t>
+    <t xml:space="preserve">1.88720726966858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89548778533936</t>
   </si>
   <si>
     <t xml:space="preserve">1.89322936534882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86914086341858</t>
+    <t xml:space="preserve">1.86914050579071</t>
   </si>
   <si>
     <t xml:space="preserve">1.85860180854797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85634350776672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85709619522095</t>
+    <t xml:space="preserve">1.85634338855743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85709607601166</t>
   </si>
   <si>
     <t xml:space="preserve">1.85182690620422</t>
@@ -905,19 +905,19 @@
     <t xml:space="preserve">1.86688232421875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88494884967804</t>
+    <t xml:space="preserve">1.88494896888733</t>
   </si>
   <si>
     <t xml:space="preserve">1.87215185165405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87064623832703</t>
+    <t xml:space="preserve">1.87064635753632</t>
   </si>
   <si>
     <t xml:space="preserve">1.86161279678345</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88193786144257</t>
+    <t xml:space="preserve">1.88193774223328</t>
   </si>
   <si>
     <t xml:space="preserve">1.86763525009155</t>
@@ -926,19 +926,19 @@
     <t xml:space="preserve">1.87365734577179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8653769493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84505176544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84204089641571</t>
+    <t xml:space="preserve">1.86537683010101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84505200386047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84204077720642</t>
   </si>
   <si>
     <t xml:space="preserve">1.84731030464172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84279370307922</t>
+    <t xml:space="preserve">1.84279334545135</t>
   </si>
   <si>
     <t xml:space="preserve">1.81795191764832</t>
@@ -947,55 +947,55 @@
     <t xml:space="preserve">1.82397413253784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82849085330963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81569361686707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82021021842957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81117677688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81644630432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81418812274933</t>
+    <t xml:space="preserve">1.82849097251892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81569373607635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82021045684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81117689609528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81644642353058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81418800354004</t>
   </si>
   <si>
     <t xml:space="preserve">1.83526575565338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83225476741791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82246851921082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85032117366791</t>
+    <t xml:space="preserve">1.8322548866272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82246840000153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8503212928772</t>
   </si>
   <si>
     <t xml:space="preserve">1.89849889278412</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93689060211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91731822490692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97979879379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96474301815033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94667673110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97076547145844</t>
+    <t xml:space="preserve">1.93689036369324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91731834411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97979855537415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96474325656891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94667661190033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97076523303986</t>
   </si>
   <si>
     <t xml:space="preserve">1.96775412559509</t>
@@ -1007,25 +1007,25 @@
     <t xml:space="preserve">2.10325384140015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04378437995911</t>
+    <t xml:space="preserve">2.04378461837769</t>
   </si>
   <si>
     <t xml:space="preserve">2.02421236038208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98732650279999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99937081336975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98582100868225</t>
+    <t xml:space="preserve">1.98732626438141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99937057495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98582065105438</t>
   </si>
   <si>
     <t xml:space="preserve">1.99033761024475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96624863147736</t>
+    <t xml:space="preserve">1.96624886989594</t>
   </si>
   <si>
     <t xml:space="preserve">1.99861788749695</t>
@@ -1034,7 +1034,7 @@
     <t xml:space="preserve">1.96549594402313</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97603487968445</t>
+    <t xml:space="preserve">1.97603464126587</t>
   </si>
   <si>
     <t xml:space="preserve">1.98280966281891</t>
@@ -1046,37 +1046,37 @@
     <t xml:space="preserve">2.06260395050049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07540082931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08142328262329</t>
+    <t xml:space="preserve">2.07540106773376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08142304420471</t>
   </si>
   <si>
     <t xml:space="preserve">2.08217597007751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08594012260437</t>
+    <t xml:space="preserve">2.08593988418579</t>
   </si>
   <si>
     <t xml:space="preserve">2.07765936851501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09572625160217</t>
+    <t xml:space="preserve">2.09572577476501</t>
   </si>
   <si>
     <t xml:space="preserve">2.09045672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11153435707092</t>
+    <t xml:space="preserve">2.11153411865234</t>
   </si>
   <si>
     <t xml:space="preserve">2.10024261474609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08669281005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07013154029846</t>
+    <t xml:space="preserve">2.08669257164001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07013177871704</t>
   </si>
   <si>
     <t xml:space="preserve">2.06034564971924</t>
@@ -1085,19 +1085,19 @@
     <t xml:space="preserve">2.05959296226501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05884027481079</t>
+    <t xml:space="preserve">2.05884003639221</t>
   </si>
   <si>
     <t xml:space="preserve">2.07615399360657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08368158340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10400652885437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08518743515015</t>
+    <t xml:space="preserve">2.08368182182312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10400676727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08518719673157</t>
   </si>
   <si>
     <t xml:space="preserve">2.13185906410217</t>
@@ -1112,10 +1112,10 @@
     <t xml:space="preserve">2.1755199432373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16799259185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20563101768494</t>
+    <t xml:space="preserve">2.16799235343933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20563125610352</t>
   </si>
   <si>
     <t xml:space="preserve">2.22068667411804</t>
@@ -1127,19 +1127,19 @@
     <t xml:space="preserve">2.36371397972107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31854724884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33360290527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3712420463562</t>
+    <t xml:space="preserve">2.31854748725891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33360266685486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37124156951904</t>
   </si>
   <si>
     <t xml:space="preserve">2.32607507705688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28843665122986</t>
+    <t xml:space="preserve">2.28843641281128</t>
   </si>
   <si>
     <t xml:space="preserve">2.2658531665802</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">2.30349206924438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29596400260925</t>
+    <t xml:space="preserve">2.29596424102783</t>
   </si>
   <si>
     <t xml:space="preserve">2.25832533836365</t>
@@ -1163,7 +1163,7 @@
     <t xml:space="preserve">2.18304800987244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43899178504944</t>
+    <t xml:space="preserve">2.43899154663086</t>
   </si>
   <si>
     <t xml:space="preserve">2.38629722595215</t>
@@ -1178,10 +1178,10 @@
     <t xml:space="preserve">2.61965751647949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46157479286194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49168586730957</t>
+    <t xml:space="preserve">2.46157503128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49168562889099</t>
   </si>
   <si>
     <t xml:space="preserve">2.46910214424133</t>
@@ -1190,28 +1190,28 @@
     <t xml:space="preserve">2.40135264396667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43146395683289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47663044929504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44651889801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40888071060181</t>
+    <t xml:space="preserve">2.43146347999573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47663021087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44651913642883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40888047218323</t>
   </si>
   <si>
     <t xml:space="preserve">2.48415803909302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45404672622681</t>
+    <t xml:space="preserve">2.45404696464539</t>
   </si>
   <si>
     <t xml:space="preserve">2.4164080619812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50674152374268</t>
+    <t xml:space="preserve">2.50674104690552</t>
   </si>
   <si>
     <t xml:space="preserve">2.5293242931366</t>
@@ -1223,25 +1223,25 @@
     <t xml:space="preserve">2.59139394760132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5836353302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56035947799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50604867935181</t>
+    <t xml:space="preserve">2.58363485336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56035923957825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50604820251465</t>
   </si>
   <si>
     <t xml:space="preserve">2.51380729675293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52156591415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54484176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48277258872986</t>
+    <t xml:space="preserve">2.52156567573547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54484152793884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48277235031128</t>
   </si>
   <si>
     <t xml:space="preserve">2.4982898235321</t>
@@ -1265,25 +1265,25 @@
     <t xml:space="preserve">2.22673654556274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2034604549408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19570183753967</t>
+    <t xml:space="preserve">2.20346069335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19570207595825</t>
   </si>
   <si>
     <t xml:space="preserve">2.21897792816162</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23449540138245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25777149200439</t>
+    <t xml:space="preserve">2.23449516296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25777125358582</t>
   </si>
   <si>
     <t xml:space="preserve">2.1724259853363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11811518669128</t>
+    <t xml:space="preserve">2.11811494827271</t>
   </si>
   <si>
     <t xml:space="preserve">2.18794345855713</t>
@@ -1292,13 +1292,13 @@
     <t xml:space="preserve">2.25001239776611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12587380409241</t>
+    <t xml:space="preserve">2.12587404251099</t>
   </si>
   <si>
     <t xml:space="preserve">2.10259795188904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13363242149353</t>
+    <t xml:space="preserve">2.13363289833069</t>
   </si>
   <si>
     <t xml:space="preserve">2.09483933448792</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">2.07932209968567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07156348228455</t>
+    <t xml:space="preserve">2.07156324386597</t>
   </si>
   <si>
     <t xml:space="preserve">2.0405285358429</t>
@@ -1331,7 +1331,7 @@
     <t xml:space="preserve">2.29656457901001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03276991844177</t>
+    <t xml:space="preserve">2.03277015686035</t>
   </si>
   <si>
     <t xml:space="preserve">2.01725244522095</t>
@@ -1340,106 +1340,106 @@
     <t xml:space="preserve">2.02501130104065</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0094940662384</t>
+    <t xml:space="preserve">2.00949382781982</t>
   </si>
   <si>
     <t xml:space="preserve">1.97070062160492</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96294212341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93966579437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8853554725647</t>
+    <t xml:space="preserve">1.96294188499451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93966591358185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88535523414612</t>
   </si>
   <si>
     <t xml:space="preserve">1.877596616745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85432064533234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86983811855316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79225122928619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83880352973938</t>
+    <t xml:space="preserve">1.85432052612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86983799934387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79225146770477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8388032913208</t>
   </si>
   <si>
     <t xml:space="preserve">1.83104467391968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86207914352417</t>
+    <t xml:space="preserve">1.86207938194275</t>
   </si>
   <si>
     <t xml:space="preserve">2.15690851211548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06380462646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0482873916626</t>
+    <t xml:space="preserve">2.06380438804626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04828715324402</t>
   </si>
   <si>
     <t xml:space="preserve">2.0017352104187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97845935821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99397659301758</t>
+    <t xml:space="preserve">1.97845923900604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99397671222687</t>
   </si>
   <si>
     <t xml:space="preserve">1.92414855957031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84656190872192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80776870250702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75345802307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77673423290253</t>
+    <t xml:space="preserve">1.8465621471405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80776882171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75345814228058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77673375606537</t>
   </si>
   <si>
     <t xml:space="preserve">1.74569952487946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82328617572784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89311420917511</t>
+    <t xml:space="preserve">1.82328605651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89311408996582</t>
   </si>
   <si>
     <t xml:space="preserve">1.91639006137848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21121907234192</t>
+    <t xml:space="preserve">2.2112193107605</t>
   </si>
   <si>
     <t xml:space="preserve">2.11035680770874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05604600906372</t>
+    <t xml:space="preserve">2.05604577064514</t>
   </si>
   <si>
     <t xml:space="preserve">2.26552987098694</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24225401878357</t>
+    <t xml:space="preserve">2.24225378036499</t>
   </si>
   <si>
     <t xml:space="preserve">2.35087513923645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3198401927948</t>
+    <t xml:space="preserve">2.31984043121338</t>
   </si>
   <si>
     <t xml:space="preserve">2.3353579044342</t>
@@ -1454,37 +1454,37 @@
     <t xml:space="preserve">2.3819100856781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38966822624207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39742708206177</t>
+    <t xml:space="preserve">2.38966846466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39742732048035</t>
   </si>
   <si>
     <t xml:space="preserve">2.41294455528259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42070341110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36639261245728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34311676025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3741512298584</t>
+    <t xml:space="preserve">2.42070317268372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36639285087585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34311652183533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37415146827698</t>
   </si>
   <si>
     <t xml:space="preserve">2.45173788070679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47501397132874</t>
+    <t xml:space="preserve">2.47501373291016</t>
   </si>
   <si>
     <t xml:space="preserve">2.55260062217712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5444712638855</t>
+    <t xml:space="preserve">2.54447102546692</t>
   </si>
   <si>
     <t xml:space="preserve">2.52008318901062</t>
@@ -1496,7 +1496,7 @@
     <t xml:space="preserve">2.4387903213501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45504903793335</t>
+    <t xml:space="preserve">2.45504879951477</t>
   </si>
   <si>
     <t xml:space="preserve">2.47943687438965</t>
@@ -1505,25 +1505,25 @@
     <t xml:space="preserve">2.48756623268127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50382447242737</t>
+    <t xml:space="preserve">2.50382471084595</t>
   </si>
   <si>
     <t xml:space="preserve">2.40627312660217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43066072463989</t>
+    <t xml:space="preserve">2.43066120147705</t>
   </si>
   <si>
     <t xml:space="preserve">2.42253160476685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3656268119812</t>
+    <t xml:space="preserve">2.36562657356262</t>
   </si>
   <si>
     <t xml:space="preserve">2.39001441001892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2843337059021</t>
+    <t xml:space="preserve">2.28433346748352</t>
   </si>
   <si>
     <t xml:space="preserve">2.27620434761047</t>
@@ -1532,49 +1532,49 @@
     <t xml:space="preserve">2.2274284362793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23555755615234</t>
+    <t xml:space="preserve">2.23555779457092</t>
   </si>
   <si>
     <t xml:space="preserve">2.25181651115417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26807498931885</t>
+    <t xml:space="preserve">2.26807522773743</t>
   </si>
   <si>
     <t xml:space="preserve">2.357497215271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32498002052307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34123873710632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37375593185425</t>
+    <t xml:space="preserve">2.32498025894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34123849868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37375617027283</t>
   </si>
   <si>
     <t xml:space="preserve">2.4631781578064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51195383071899</t>
+    <t xml:space="preserve">2.51195406913757</t>
   </si>
   <si>
     <t xml:space="preserve">2.52821254730225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53634214401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58511757850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59324717521667</t>
+    <t xml:space="preserve">2.53634190559387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58511781692505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5932469367981</t>
   </si>
   <si>
     <t xml:space="preserve">2.56072998046875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6013765335083</t>
+    <t xml:space="preserve">2.60137629508972</t>
   </si>
   <si>
     <t xml:space="preserve">2.60950541496277</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">2.5688591003418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57698845863342</t>
+    <t xml:space="preserve">2.576988697052</t>
   </si>
   <si>
     <t xml:space="preserve">2.4144024848938</t>
@@ -1601,7 +1601,7 @@
     <t xml:space="preserve">2.47130751609802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44691967964172</t>
+    <t xml:space="preserve">2.44691944122314</t>
   </si>
   <si>
     <t xml:space="preserve">2.38188529014587</t>
@@ -1628,25 +1628,25 @@
     <t xml:space="preserve">2.08110117912292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10548901557922</t>
+    <t xml:space="preserve">2.10548877716064</t>
   </si>
   <si>
     <t xml:space="preserve">2.1217474937439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.048583984375</t>
+    <t xml:space="preserve">2.04858374595642</t>
   </si>
   <si>
     <t xml:space="preserve">1.89412713050842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65837740898132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66650664806366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6258602142334</t>
+    <t xml:space="preserve">1.65837728977203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66650676727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62586009502411</t>
   </si>
   <si>
     <t xml:space="preserve">1.47140347957611</t>
@@ -1655,28 +1655,28 @@
     <t xml:space="preserve">1.50392067432404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51205003261566</t>
+    <t xml:space="preserve">1.51204991340637</t>
   </si>
   <si>
     <t xml:space="preserve">1.61366617679596</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55676090717316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5486319065094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53237330913544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4957914352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58521378040314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60147225856781</t>
+    <t xml:space="preserve">1.55676102638245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54863166809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53237318992615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49579131603241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58521366119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60147249698639</t>
   </si>
   <si>
     <t xml:space="preserve">1.5730197429657</t>
@@ -1685,19 +1685,19 @@
     <t xml:space="preserve">1.56082582473755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58114922046661</t>
+    <t xml:space="preserve">1.58114910125732</t>
   </si>
   <si>
     <t xml:space="preserve">1.5689549446106</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63398969173431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69089460372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60553693771362</t>
+    <t xml:space="preserve">1.63398957252502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69089484214783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60553705692291</t>
   </si>
   <si>
     <t xml:space="preserve">1.62179565429688</t>
@@ -1709,13 +1709,13 @@
     <t xml:space="preserve">1.61773085594177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67463612556458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7071533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76405847072601</t>
+    <t xml:space="preserve">1.67463600635529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70715320110321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76405835151672</t>
   </si>
   <si>
     <t xml:space="preserve">1.73154103755951</t>
@@ -1724,22 +1724,22 @@
     <t xml:space="preserve">1.71528244018555</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69902384281158</t>
+    <t xml:space="preserve">1.69902396202087</t>
   </si>
   <si>
     <t xml:space="preserve">1.6502480506897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74779975414276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75592887401581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77218759059906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7884464263916</t>
+    <t xml:space="preserve">1.74779987335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75592911243439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77218747138977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78844630718231</t>
   </si>
   <si>
     <t xml:space="preserve">1.82096338272095</t>
@@ -1748,22 +1748,22 @@
     <t xml:space="preserve">1.87786841392517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82909286022186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80470490455627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81283402442932</t>
+    <t xml:space="preserve">1.82909274101257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80470502376556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81283414363861</t>
   </si>
   <si>
     <t xml:space="preserve">1.79657554626465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7803168296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72341179847717</t>
+    <t xml:space="preserve">1.78031694889069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72341191768646</t>
   </si>
   <si>
     <t xml:space="preserve">1.73967039585114</t>
@@ -1775,7 +1775,7 @@
     <t xml:space="preserve">1.60960161685944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64211881160736</t>
+    <t xml:space="preserve">1.64211893081665</t>
   </si>
   <si>
     <t xml:space="preserve">1.57708442211151</t>
@@ -1784,22 +1784,22 @@
     <t xml:space="preserve">1.52830851078033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53643798828125</t>
+    <t xml:space="preserve">1.53643774986267</t>
   </si>
   <si>
     <t xml:space="preserve">1.49985611438751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48766195774078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48359751701355</t>
+    <t xml:space="preserve">1.48766207695007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48359739780426</t>
   </si>
   <si>
     <t xml:space="preserve">1.43075704574585</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42262768745422</t>
+    <t xml:space="preserve">1.42262780666351</t>
   </si>
   <si>
     <t xml:space="preserve">1.41043376922607</t>
@@ -1808,28 +1808,28 @@
     <t xml:space="preserve">1.40636897087097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43482172489166</t>
+    <t xml:space="preserve">1.43482160568237</t>
   </si>
   <si>
     <t xml:space="preserve">1.4144983291626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36572253704071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33320534229279</t>
+    <t xml:space="preserve">1.36572241783142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33320546150208</t>
   </si>
   <si>
     <t xml:space="preserve">1.38198125362396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35759329795837</t>
+    <t xml:space="preserve">1.35759341716766</t>
   </si>
   <si>
     <t xml:space="preserve">1.30475270748138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29255878925323</t>
+    <t xml:space="preserve">1.29255890846252</t>
   </si>
   <si>
     <t xml:space="preserve">1.30881750583649</t>
@@ -1841,25 +1841,25 @@
     <t xml:space="preserve">1.32507598400116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34946405887604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37385177612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35352873802185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39823997020721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40230429172516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3860456943512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39011061191559</t>
+    <t xml:space="preserve">1.34946393966675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37385189533234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35352849960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39823985099792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40230441093445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38604581356049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3901104927063</t>
   </si>
   <si>
     <t xml:space="preserve">1.37791657447815</t>
@@ -1868,28 +1868,28 @@
     <t xml:space="preserve">1.4673388004303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.520179271698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5526967048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54456722736359</t>
+    <t xml:space="preserve">1.52017939090729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55269658565521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5445671081543</t>
   </si>
   <si>
     <t xml:space="preserve">1.49172675609589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52424395084381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50798535346985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51611459255219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54050254821777</t>
+    <t xml:space="preserve">1.5242440700531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50798523426056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51611471176147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54050266742706</t>
   </si>
   <si>
     <t xml:space="preserve">1.47953283786774</t>
@@ -1898,13 +1898,13 @@
     <t xml:space="preserve">1.86973917484283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95103204250336</t>
+    <t xml:space="preserve">1.95103216171265</t>
   </si>
   <si>
     <t xml:space="preserve">2.0729718208313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25994563102722</t>
+    <t xml:space="preserve">2.2599458694458</t>
   </si>
   <si>
     <t xml:space="preserve">2.24368715286255</t>
@@ -1916,7 +1916,7 @@
     <t xml:space="preserve">2.14613556861877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05671334266663</t>
+    <t xml:space="preserve">2.05671286582947</t>
   </si>
   <si>
     <t xml:space="preserve">2.13800597190857</t>
@@ -1928,16 +1928,16 @@
     <t xml:space="preserve">2.21945142745972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2360143661499</t>
+    <t xml:space="preserve">2.23601460456848</t>
   </si>
   <si>
     <t xml:space="preserve">2.24429607391357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25257778167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20288825035095</t>
+    <t xml:space="preserve">2.25257754325867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20288848876953</t>
   </si>
   <si>
     <t xml:space="preserve">2.22773313522339</t>
@@ -1946,10 +1946,10 @@
     <t xml:space="preserve">2.19460678100586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17804384231567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.343674659729</t>
+    <t xml:space="preserve">2.17804360389709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34367442131042</t>
   </si>
   <si>
     <t xml:space="preserve">2.36023759841919</t>
@@ -1958,7 +1958,7 @@
     <t xml:space="preserve">2.36851906776428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38508224487305</t>
+    <t xml:space="preserve">2.38508200645447</t>
   </si>
   <si>
     <t xml:space="preserve">2.40164518356323</t>
@@ -1967,19 +1967,19 @@
     <t xml:space="preserve">2.45133447647095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47617888450623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4844605922699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49274230003357</t>
+    <t xml:space="preserve">2.4761791229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48446035385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49274206161499</t>
   </si>
   <si>
     <t xml:space="preserve">2.418208360672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39336347579956</t>
+    <t xml:space="preserve">2.39336371421814</t>
   </si>
   <si>
     <t xml:space="preserve">2.37680077552795</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">2.42648983001709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33539319038391</t>
+    <t xml:space="preserve">2.33539295196533</t>
   </si>
   <si>
     <t xml:space="preserve">2.32711148262024</t>
@@ -2006,7 +2006,7 @@
     <t xml:space="preserve">2.31882977485657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31054830551147</t>
+    <t xml:space="preserve">2.31054854393005</t>
   </si>
   <si>
     <t xml:space="preserve">2.35195589065552</t>
@@ -2024,10 +2024,10 @@
     <t xml:space="preserve">2.15319919586182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12835454940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13663601875305</t>
+    <t xml:space="preserve">2.12835478782654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13663625717163</t>
   </si>
   <si>
     <t xml:space="preserve">2.18632531166077</t>
@@ -2045,7 +2045,7 @@
     <t xml:space="preserve">2.16976237297058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14491772651672</t>
+    <t xml:space="preserve">2.14491748809814</t>
   </si>
   <si>
     <t xml:space="preserve">2.16148066520691</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">2.26914072036743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26085925102234</t>
+    <t xml:space="preserve">2.26085901260376</t>
   </si>
   <si>
     <t xml:space="preserve">2.4099268913269</t>
@@ -2063,25 +2063,25 @@
     <t xml:space="preserve">2.46789741516113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50102376937866</t>
+    <t xml:space="preserve">2.50102353096008</t>
   </si>
   <si>
     <t xml:space="preserve">2.52586841583252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50930500030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62524652481079</t>
+    <t xml:space="preserve">2.50930523872375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62524676322937</t>
   </si>
   <si>
     <t xml:space="preserve">2.71634364128113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69978022575378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81572198867798</t>
+    <t xml:space="preserve">2.69978046417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81572222709656</t>
   </si>
   <si>
     <t xml:space="preserve">2.84884834289551</t>
@@ -2093,13 +2093,13 @@
     <t xml:space="preserve">3.01447892189026</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03104162216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24636197090149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23808026313782</t>
+    <t xml:space="preserve">3.03104186058044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24636220932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2380805015564</t>
   </si>
   <si>
     <t xml:space="preserve">3.22979879379272</t>
@@ -2108,10 +2108,10 @@
     <t xml:space="preserve">3.3043327331543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12213897705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1635468006134</t>
+    <t xml:space="preserve">3.1221387386322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16354656219482</t>
   </si>
   <si>
     <t xml:space="preserve">3.17182779312134</t>
@@ -2129,10 +2129,10 @@
     <t xml:space="preserve">3.18010950088501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13042044639587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10557556152344</t>
+    <t xml:space="preserve">3.13042020797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1055760383606</t>
   </si>
   <si>
     <t xml:space="preserve">3.13870191574097</t>
@@ -2141,19 +2141,19 @@
     <t xml:space="preserve">3.08901286125183</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07244944572449</t>
+    <t xml:space="preserve">3.07244920730591</t>
   </si>
   <si>
     <t xml:space="preserve">3.11385703086853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08073139190674</t>
+    <t xml:space="preserve">3.08073115348816</t>
   </si>
   <si>
     <t xml:space="preserve">3.06416797637939</t>
   </si>
   <si>
-    <t xml:space="preserve">3.254643201828</t>
+    <t xml:space="preserve">3.25464367866516</t>
   </si>
   <si>
     <t xml:space="preserve">3.09729433059692</t>
@@ -2165,22 +2165,22 @@
     <t xml:space="preserve">3.02276039123535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04760503768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05588674545288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15526485443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03932356834412</t>
+    <t xml:space="preserve">3.04760479927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0558865070343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15526461601257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03932332992554</t>
   </si>
   <si>
     <t xml:space="preserve">2.98963403701782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00619745254517</t>
+    <t xml:space="preserve">3.00619721412659</t>
   </si>
   <si>
     <t xml:space="preserve">2.98135280609131</t>
@@ -2189,13 +2189,13 @@
     <t xml:space="preserve">2.97307133674622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20495438575745</t>
+    <t xml:space="preserve">3.20495414733887</t>
   </si>
   <si>
     <t xml:space="preserve">3.27948784828186</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27120637893677</t>
+    <t xml:space="preserve">3.27120661735535</t>
   </si>
   <si>
     <t xml:space="preserve">3.29605102539062</t>
@@ -2225,13 +2225,13 @@
     <t xml:space="preserve">4.95042657852173</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01585054397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5828595161438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36477899551392</t>
+    <t xml:space="preserve">5.01585006713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58285999298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36477947235107</t>
   </si>
   <si>
     <t xml:space="preserve">5.05946683883667</t>
@@ -2240,7 +2240,7 @@
     <t xml:space="preserve">4.97223424911499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14669847488403</t>
+    <t xml:space="preserve">5.14669895172119</t>
   </si>
   <si>
     <t xml:space="preserve">5.08127450942993</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">5.19031476974487</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21212291717529</t>
+    <t xml:space="preserve">5.21212244033813</t>
   </si>
   <si>
     <t xml:space="preserve">5.27754688262939</t>
@@ -2264,22 +2264,22 @@
     <t xml:space="preserve">5.47381925582886</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53924369812012</t>
+    <t xml:space="preserve">5.53924322128296</t>
   </si>
   <si>
     <t xml:space="preserve">5.45201110839844</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43020343780518</t>
+    <t xml:space="preserve">5.43020296096802</t>
   </si>
   <si>
     <t xml:space="preserve">5.40839529037476</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3429708480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38658714294434</t>
+    <t xml:space="preserve">5.34297132492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38658761978149</t>
   </si>
   <si>
     <t xml:space="preserve">5.32116317749023</t>
@@ -2291,19 +2291,19 @@
     <t xml:space="preserve">5.99721240997314</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82591819763184</t>
+    <t xml:space="preserve">6.82591772079468</t>
   </si>
   <si>
     <t xml:space="preserve">7.32750272750854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93495798110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78230237960815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73868560791016</t>
+    <t xml:space="preserve">6.93495845794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.782301902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73868608474731</t>
   </si>
   <si>
     <t xml:space="preserve">6.67326211929321</t>
@@ -2318,7 +2318,7 @@
     <t xml:space="preserve">6.25890922546387</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32433319091797</t>
+    <t xml:space="preserve">6.32433271408081</t>
   </si>
   <si>
     <t xml:space="preserve">6.23710107803345</t>
@@ -2333,28 +2333,28 @@
     <t xml:space="preserve">6.41156530380249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62964534759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76049423217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02219104766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0658073425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04399871826172</t>
+    <t xml:space="preserve">6.62964582443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76049375534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0221905708313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06580686569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04399824142456</t>
   </si>
   <si>
     <t xml:space="preserve">7.0876145362854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45835208892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52377510070801</t>
+    <t xml:space="preserve">7.45835161209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52377557754517</t>
   </si>
   <si>
     <t xml:space="preserve">7.78547239303589</t>
@@ -2366,7 +2366,7 @@
     <t xml:space="preserve">8.19982433319092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11259365081787</t>
+    <t xml:space="preserve">8.11259269714355</t>
   </si>
   <si>
     <t xml:space="preserve">8.37428951263428</t>
@@ -68673,7 +68673,7 @@
     </row>
     <row r="2517">
       <c r="A2517" s="1" t="n">
-        <v>45982.691099537</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B2517" t="n">
         <v>3054</v>
@@ -68694,6 +68694,32 @@
         <v>892</v>
       </c>
       <c r="H2517" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" s="1" t="n">
+        <v>45985.6787962963</v>
+      </c>
+      <c r="B2518" t="n">
+        <v>1140</v>
+      </c>
+      <c r="C2518" t="n">
+        <v>2.67499995231628</v>
+      </c>
+      <c r="D2518" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="E2518" t="n">
+        <v>2.66499996185303</v>
+      </c>
+      <c r="F2518" t="n">
+        <v>2.55999994277954</v>
+      </c>
+      <c r="G2518" t="s">
+        <v>936</v>
+      </c>
+      <c r="H2518" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -53,7 +53,7 @@
     <t xml:space="preserve">1.22256815433502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2154186964035</t>
+    <t xml:space="preserve">1.21541833877563</t>
   </si>
   <si>
     <t xml:space="preserve">1.2218531370163</t>
@@ -62,388 +62,388 @@
     <t xml:space="preserve">1.21470355987549</t>
   </si>
   <si>
+    <t xml:space="preserve">1.23615229129791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21327364444733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20683908462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2011194229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20040464401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1668016910553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19468474388123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25688576698303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25045108795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24687647819519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25116610527039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26475036144257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23543727397919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22542786598206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.210413813591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22113811969757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19397008419037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22685778141022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20469439029694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25831580162048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26546537876129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25903058052063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26903986930847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21684849262238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22828769683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27404451370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26689493656158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27261459827423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27189970016479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2790492773056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26760995388031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25545573234558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26260542869568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24830615520477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24902129173279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24258673191071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23686707019806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23472225666046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23400735855103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25225365161896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26176798343658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26835513114929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27860140800476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27640581130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27420997619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27494215965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26323187351227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27128279209137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26689124107361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28445649147034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28079700469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2793333530426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27347838878632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27274644374847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26615929603577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2822607755661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28811597824097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28738391399384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28299283981323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26396381855011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24127519130707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2434709072113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22956514358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23468852043152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22663760185242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20687675476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20760881900787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18565225601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17833340167999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18784785270691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16955053806305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17101442813873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17028260231018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18931150436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22224628925323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22151446342468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23981165885925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23907959461212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23834776878357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23542022705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2061448097229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23102903366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19736230373383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21712327003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22297811508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23322463035583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23249292373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22883343696594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28518843650818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25884056091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30714499950409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29909408092499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32324635982513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31665933132172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32763755321503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30348539352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31592750549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31812310218811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29763031005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30275344848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29982614517212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28884780406952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29543495178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30055785179138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29836225509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29323923587799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29250729084015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30128979682922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30568110942841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26908695697784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26762318611145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24786221981049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25518119335175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2654275894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28006517887115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25810873508453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25005793571472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24054348468781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24639868736267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24420285224915</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.23615217208862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21327364444733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20683896541595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2011194229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20040464401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16680181026459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19468486309052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25688564777374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25045108795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24687647819519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25116622447968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26475036144257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23543727397919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22542774677277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.210413813591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22113823890686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19396996498108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22685790061951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20469439029694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25831580162048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.265465259552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25903081893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26903986930847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21684849262238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22828757762909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27404463291168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26689505577087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27261459827423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27189970016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2790492773056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2676100730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25545585155487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26260542869568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24830615520477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2490211725235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24258673191071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23686695098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23472225666046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23400735855103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25225365161896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26176798343658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26835513114929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27860128879547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27640581130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27421009540558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27494215965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26323187351227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27128267288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26689112186432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28445637226105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.280797123909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27933311462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27347826957703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27274644374847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26615929603577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28226089477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28811597824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28738403320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28299260139465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26396381855011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24127519130707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24347102642059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22956514358521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23468840122223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22663760185242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20687687397003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20760869979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18565225601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17833340167999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18784785270691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16955065727234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17101442813873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17028260231018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18931150436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22224628925323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22151446342468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23981165885925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23907971382141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23834776878357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23542022705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2061448097229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23102903366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19736218452454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21712303161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22297811508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23322474956512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23249280452728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22883343696594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28518831729889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25884056091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3071448802948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29909408092499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32324624061584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31665945053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32763755321503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30348539352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31592750549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3181232213974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29763042926788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30275356769562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29982602596283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28884792327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29543483257294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30055797100067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29836213588715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29323923587799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29250729084015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30128991603851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30568110942841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26908695697784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26762306690216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24786221981049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25518119335175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26542747020721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28006517887115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25810873508453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25005805492401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24054348468781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24639844894409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24420297145844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23615205287933</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.23688399791718</t>
   </si>
   <si>
     <t xml:space="preserve">1.24200713634491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23176097869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20980441570282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21126806735992</t>
+    <t xml:space="preserve">1.23176074028015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20980429649353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21126794815063</t>
   </si>
   <si>
     <t xml:space="preserve">1.21858692169189</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21492755413055</t>
+    <t xml:space="preserve">1.21492743492126</t>
   </si>
   <si>
     <t xml:space="preserve">1.19004356861115</t>
@@ -452,25 +452,25 @@
     <t xml:space="preserve">1.18199265003204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21419560909271</t>
+    <t xml:space="preserve">1.214195728302</t>
   </si>
   <si>
     <t xml:space="preserve">1.19297099113464</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19663047790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.220050573349</t>
+    <t xml:space="preserve">1.19663035869598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22005069255829</t>
   </si>
   <si>
     <t xml:space="preserve">1.21639132499695</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25957250595093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27786946296692</t>
+    <t xml:space="preserve">1.25957238674164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27786934375763</t>
   </si>
   <si>
     <t xml:space="preserve">1.28592026233673</t>
@@ -479,43 +479,43 @@
     <t xml:space="preserve">1.29470300674438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29689848423004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31007242202759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32544207572937</t>
+    <t xml:space="preserve">1.29689836502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31007254123688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32544219493866</t>
   </si>
   <si>
     <t xml:space="preserve">1.34081161022186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33349275588989</t>
+    <t xml:space="preserve">1.3334926366806</t>
   </si>
   <si>
     <t xml:space="preserve">1.33422470092773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3320289850235</t>
+    <t xml:space="preserve">1.33202910423279</t>
   </si>
   <si>
     <t xml:space="preserve">1.33861601352692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33934783935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34666657447815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34227526187897</t>
+    <t xml:space="preserve">1.33934760093689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34666669368744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34227538108826</t>
   </si>
   <si>
     <t xml:space="preserve">1.34007966518402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32690572738647</t>
+    <t xml:space="preserve">1.32690584659576</t>
   </si>
   <si>
     <t xml:space="preserve">1.3210506439209</t>
@@ -524,10 +524,10 @@
     <t xml:space="preserve">1.3459347486496</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36130428314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36057245731354</t>
+    <t xml:space="preserve">1.36130440235138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36057233810425</t>
   </si>
   <si>
     <t xml:space="preserve">1.33276081085205</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">1.34959423542023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33788418769836</t>
+    <t xml:space="preserve">1.33788394927979</t>
   </si>
   <si>
     <t xml:space="preserve">1.34373915195465</t>
@@ -545,67 +545,67 @@
     <t xml:space="preserve">1.34520280361176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32910132408142</t>
+    <t xml:space="preserve">1.3291015625</t>
   </si>
   <si>
     <t xml:space="preserve">1.36349987983704</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36789131164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37667381763458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38252902030945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39789867401123</t>
+    <t xml:space="preserve">1.3678914308548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37667369842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38252890110016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39789855480194</t>
   </si>
   <si>
     <t xml:space="preserve">1.41253614425659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40668129920959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40814483165741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40887665748596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40302181243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39277529716492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36935496330261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37886965274811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38911581039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40155780315399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49304342269897</t>
+    <t xml:space="preserve">1.40668106079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4081449508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40887677669525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40302169322968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39277541637421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3693550825119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37886953353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38911604881287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40155792236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49304330348969</t>
   </si>
   <si>
     <t xml:space="preserve">1.4762099981308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48206508159637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49157953262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50328981876373</t>
+    <t xml:space="preserve">1.48206520080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49157965183258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50328993797302</t>
   </si>
   <si>
     <t xml:space="preserve">1.46742749214172</t>
@@ -617,10 +617,10 @@
     <t xml:space="preserve">1.47913753986359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49523913860321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49084782600403</t>
+    <t xml:space="preserve">1.49523901939392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49084770679474</t>
   </si>
   <si>
     <t xml:space="preserve">1.48792016506195</t>
@@ -629,19 +629,19 @@
     <t xml:space="preserve">1.52744209766388</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50987684726715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53256547451019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52963757514954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53183341026306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52817380428314</t>
+    <t xml:space="preserve">1.50987660884857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53256523609161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52963745594025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53183317184448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52817392349243</t>
   </si>
   <si>
     <t xml:space="preserve">1.51499998569489</t>
@@ -650,25 +650,25 @@
     <t xml:space="preserve">1.49963045120239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49816644191742</t>
+    <t xml:space="preserve">1.49816656112671</t>
   </si>
   <si>
     <t xml:space="preserve">1.485724568367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47108697891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48426079750061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46376800537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45498549938202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48499274253845</t>
+    <t xml:space="preserve">1.47108685970306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4842609167099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46376812458038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45498514175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48499286174774</t>
   </si>
   <si>
     <t xml:space="preserve">1.52085518836975</t>
@@ -677,25 +677,25 @@
     <t xml:space="preserve">1.53768849372864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58233332633972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63126385211945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63427484035492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64857757091522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63578045368195</t>
+    <t xml:space="preserve">1.58233344554901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63126361370087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63427460193634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64857769012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63578033447266</t>
   </si>
   <si>
     <t xml:space="preserve">1.66664397716522</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66288030147552</t>
+    <t xml:space="preserve">1.6628805398941</t>
   </si>
   <si>
     <t xml:space="preserve">1.6613746881485</t>
@@ -707,13 +707,13 @@
     <t xml:space="preserve">1.8081659078598</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84429907798767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91656541824341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99485397338867</t>
+    <t xml:space="preserve">1.84429919719696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9165655374527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99485433101654</t>
   </si>
   <si>
     <t xml:space="preserve">2.01367354393005</t>
@@ -725,7 +725,7 @@
     <t xml:space="preserve">1.9820568561554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93011558055878</t>
+    <t xml:space="preserve">1.93011522293091</t>
   </si>
   <si>
     <t xml:space="preserve">1.83376038074493</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">1.9030157327652</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90452098846436</t>
+    <t xml:space="preserve">1.90452122688293</t>
   </si>
   <si>
     <t xml:space="preserve">1.91204881668091</t>
@@ -749,37 +749,37 @@
     <t xml:space="preserve">1.9158126115799</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88118505477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92860996723175</t>
+    <t xml:space="preserve">1.88118517398834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92861008644104</t>
   </si>
   <si>
     <t xml:space="preserve">1.92183494567871</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9255987405777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94065427780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92635154724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90376830101013</t>
+    <t xml:space="preserve">1.92559862136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94065451622009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92635130882263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90376842021942</t>
   </si>
   <si>
     <t xml:space="preserve">1.91957676410675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91882383823395</t>
+    <t xml:space="preserve">1.91882395744324</t>
   </si>
   <si>
     <t xml:space="preserve">1.93237364292145</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94366526603699</t>
+    <t xml:space="preserve">1.94366562366486</t>
   </si>
   <si>
     <t xml:space="preserve">1.91054308414459</t>
@@ -791,40 +791,40 @@
     <t xml:space="preserve">1.90753221511841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89699327945709</t>
+    <t xml:space="preserve">1.89699339866638</t>
   </si>
   <si>
     <t xml:space="preserve">1.89473509788513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87742137908936</t>
+    <t xml:space="preserve">1.87742114067078</t>
   </si>
   <si>
     <t xml:space="preserve">1.86010730266571</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77052688598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79762721061707</t>
+    <t xml:space="preserve">1.77052700519562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79762709140778</t>
   </si>
   <si>
     <t xml:space="preserve">1.76826882362366</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7946161031723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80741322040558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83074915409088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84881579875946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82547950744629</t>
+    <t xml:space="preserve">1.79461598396301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80741286277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83074903488159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84881567955017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82547986507416</t>
   </si>
   <si>
     <t xml:space="preserve">1.81042420864105</t>
@@ -839,13 +839,13 @@
     <t xml:space="preserve">1.83902966976166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85257971286774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82171583175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84806311130524</t>
+    <t xml:space="preserve">1.85257947444916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82171595096588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84806287288666</t>
   </si>
   <si>
     <t xml:space="preserve">1.84655737876892</t>
@@ -857,7 +857,7 @@
     <t xml:space="preserve">1.89774596691132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91280150413513</t>
+    <t xml:space="preserve">1.91280174255371</t>
   </si>
   <si>
     <t xml:space="preserve">1.97377645969391</t>
@@ -866,7 +866,7 @@
     <t xml:space="preserve">1.97151803970337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93086838722229</t>
+    <t xml:space="preserve">1.93086814880371</t>
   </si>
   <si>
     <t xml:space="preserve">1.93613755702972</t>
@@ -875,19 +875,19 @@
     <t xml:space="preserve">1.9210821390152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88796007633209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88720726966858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89548802375793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89322936534882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86914050579071</t>
+    <t xml:space="preserve">1.88795983791351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88720715045929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89548778533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8932296037674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.869140625</t>
   </si>
   <si>
     <t xml:space="preserve">1.85860192775726</t>
@@ -896,13 +896,13 @@
     <t xml:space="preserve">1.85634362697601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85709607601166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85182690620422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86688244342804</t>
+    <t xml:space="preserve">1.85709631443024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85182678699493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86688232421875</t>
   </si>
   <si>
     <t xml:space="preserve">1.88494908809662</t>
@@ -911,7 +911,7 @@
     <t xml:space="preserve">1.87215185165405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87064635753632</t>
+    <t xml:space="preserve">1.87064611911774</t>
   </si>
   <si>
     <t xml:space="preserve">1.86161291599274</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">1.88193774223328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86763501167297</t>
+    <t xml:space="preserve">1.86763489246368</t>
   </si>
   <si>
     <t xml:space="preserve">1.87365734577179</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">1.84505200386047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84204065799713</t>
+    <t xml:space="preserve">1.84204077720642</t>
   </si>
   <si>
     <t xml:space="preserve">1.84731018543243</t>
@@ -941,7 +941,7 @@
     <t xml:space="preserve">1.84279358386993</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81795191764832</t>
+    <t xml:space="preserve">1.8179520368576</t>
   </si>
   <si>
     <t xml:space="preserve">1.82397413253784</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">1.82849085330963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81569373607635</t>
+    <t xml:space="preserve">1.81569385528564</t>
   </si>
   <si>
     <t xml:space="preserve">1.82021045684814</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">1.81117689609528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81644666194916</t>
+    <t xml:space="preserve">1.81644630432129</t>
   </si>
   <si>
     <t xml:space="preserve">1.81418800354004</t>
@@ -968,13 +968,13 @@
     <t xml:space="preserve">1.83526575565338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8322548866272</t>
+    <t xml:space="preserve">1.83225464820862</t>
   </si>
   <si>
     <t xml:space="preserve">1.82246851921082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85032117366791</t>
+    <t xml:space="preserve">1.8503212928772</t>
   </si>
   <si>
     <t xml:space="preserve">1.89849889278412</t>
@@ -983,10 +983,10 @@
     <t xml:space="preserve">1.93689036369324</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91731810569763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97979831695557</t>
+    <t xml:space="preserve">1.91731834411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97979867458344</t>
   </si>
   <si>
     <t xml:space="preserve">1.96474325656891</t>
@@ -1001,10 +1001,10 @@
     <t xml:space="preserve">1.96775412559509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96248483657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10325384140015</t>
+    <t xml:space="preserve">1.96248459815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10325360298157</t>
   </si>
   <si>
     <t xml:space="preserve">2.04378437995911</t>
@@ -1016,7 +1016,7 @@
     <t xml:space="preserve">1.98732626438141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99937081336975</t>
+    <t xml:space="preserve">1.99937093257904</t>
   </si>
   <si>
     <t xml:space="preserve">1.98582065105438</t>
@@ -1025,10 +1025,10 @@
     <t xml:space="preserve">1.99033737182617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96624886989594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99861764907837</t>
+    <t xml:space="preserve">1.96624851226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99861788749695</t>
   </si>
   <si>
     <t xml:space="preserve">1.96549594402313</t>
@@ -1037,40 +1037,40 @@
     <t xml:space="preserve">1.97603464126587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98280942440033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02496528625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06260371208191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07540106773376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08142328262329</t>
+    <t xml:space="preserve">1.9828097820282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0249650478363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06260395050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07540130615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08142352104187</t>
   </si>
   <si>
     <t xml:space="preserve">2.08217597007751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08593964576721</t>
+    <t xml:space="preserve">2.08593988418579</t>
   </si>
   <si>
     <t xml:space="preserve">2.07765936851501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09572601318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09045648574829</t>
+    <t xml:space="preserve">2.09572625160217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09045672416687</t>
   </si>
   <si>
     <t xml:space="preserve">2.11153411865234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10024285316467</t>
+    <t xml:space="preserve">2.10024261474609</t>
   </si>
   <si>
     <t xml:space="preserve">2.08669257164001</t>
@@ -1079,13 +1079,13 @@
     <t xml:space="preserve">2.07013177871704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06034588813782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05959272384644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05884003639221</t>
+    <t xml:space="preserve">2.06034564971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05959296226501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05883979797363</t>
   </si>
   <si>
     <t xml:space="preserve">2.07615399360657</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">2.08368158340454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10400652885437</t>
+    <t xml:space="preserve">2.10400629043579</t>
   </si>
   <si>
     <t xml:space="preserve">2.08518719673157</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">2.13185930252075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19057559967041</t>
+    <t xml:space="preserve">2.19057583808899</t>
   </si>
   <si>
     <t xml:space="preserve">2.21315884590149</t>
@@ -1115,10 +1115,10 @@
     <t xml:space="preserve">2.16799235343933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20563125610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22068667411804</t>
+    <t xml:space="preserve">2.20563101768494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22068691253662</t>
   </si>
   <si>
     <t xml:space="preserve">2.31101989746094</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">2.31854748725891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33360266685486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37124156951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32607507705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28843641281128</t>
+    <t xml:space="preserve">2.33360290527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37124180793762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32607531547546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2884361743927</t>
   </si>
   <si>
     <t xml:space="preserve">2.2658531665802</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">2.28090858459473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30349206924438</t>
+    <t xml:space="preserve">2.30349183082581</t>
   </si>
   <si>
     <t xml:space="preserve">2.29596424102783</t>
@@ -1178,7 +1178,7 @@
     <t xml:space="preserve">2.61965751647949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46157503128052</t>
+    <t xml:space="preserve">2.46157455444336</t>
   </si>
   <si>
     <t xml:space="preserve">2.49168562889099</t>
@@ -1187,19 +1187,19 @@
     <t xml:space="preserve">2.46910238265991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40135288238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43146347999573</t>
+    <t xml:space="preserve">2.40135264396667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43146371841431</t>
   </si>
   <si>
     <t xml:space="preserve">2.47663044929504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44651913642883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40888023376465</t>
+    <t xml:space="preserve">2.44651937484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40888047218323</t>
   </si>
   <si>
     <t xml:space="preserve">2.48415780067444</t>
@@ -1211,7 +1211,7 @@
     <t xml:space="preserve">2.4164080619812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50674104690552</t>
+    <t xml:space="preserve">2.50674152374268</t>
   </si>
   <si>
     <t xml:space="preserve">2.5293242931366</t>
@@ -68728,7 +68728,7 @@
     </row>
     <row r="2519">
       <c r="A2519" s="1" t="n">
-        <v>45986.6721064815</v>
+        <v>45986.3333333333</v>
       </c>
       <c r="B2519" t="n">
         <v>4230</v>
@@ -68749,6 +68749,32 @@
         <v>936</v>
       </c>
       <c r="H2519" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2520">
+      <c r="A2520" s="1" t="n">
+        <v>45987.4763888889</v>
+      </c>
+      <c r="B2520" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2520" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="D2520" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="E2520" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="F2520" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="G2520" t="s">
+        <v>930</v>
+      </c>
+      <c r="H2520" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AUTME.MI.xlsx
+++ b/data/AUTME.MI.xlsx
@@ -38,43 +38,43 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24616169929504</t>
+    <t xml:space="preserve">1.24616158008575</t>
   </si>
   <si>
     <t xml:space="preserve">AUTME.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24544644355774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24330163002014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22256803512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21541845798492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2218531370163</t>
+    <t xml:space="preserve">1.24544656276703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24330151081085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22256815433502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21541857719421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22185325622559</t>
   </si>
   <si>
     <t xml:space="preserve">1.21470355987549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23615229129791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21327352523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20683920383453</t>
+    <t xml:space="preserve">1.23615217208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21327376365662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20683908462524</t>
   </si>
   <si>
     <t xml:space="preserve">1.2011194229126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20040464401245</t>
+    <t xml:space="preserve">1.20040452480316</t>
   </si>
   <si>
     <t xml:space="preserve">1.16680181026459</t>
@@ -86,10 +86,10 @@
     <t xml:space="preserve">1.25688576698303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25045120716095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2468763589859</t>
+    <t xml:space="preserve">1.25045132637024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24687647819519</t>
   </si>
   <si>
     <t xml:space="preserve">1.25116610527039</t>
@@ -98,40 +98,40 @@
     <t xml:space="preserve">1.26475024223328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23543727397919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22542774677277</t>
+    <t xml:space="preserve">1.2354371547699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22542786598206</t>
   </si>
   <si>
     <t xml:space="preserve">1.21041393280029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22113811969757</t>
+    <t xml:space="preserve">1.22113823890686</t>
   </si>
   <si>
     <t xml:space="preserve">1.19397008419037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22685766220093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20469439029694</t>
+    <t xml:space="preserve">1.22685790061951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20469427108765</t>
   </si>
   <si>
     <t xml:space="preserve">1.25831568241119</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26546514034271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25903069972992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26903986930847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21684849262238</t>
+    <t xml:space="preserve">1.265465259552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25903081893921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26903975009918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21684837341309</t>
   </si>
   <si>
     <t xml:space="preserve">1.22828769683838</t>
@@ -143,67 +143,67 @@
     <t xml:space="preserve">1.26689493656158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27261447906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27189993858337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2790492773056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26760983467102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25545597076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2626051902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24830639362335</t>
+    <t xml:space="preserve">1.27261471748352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27189981937408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27904915809631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2676100730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25545573234558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26260530948639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24830627441406</t>
   </si>
   <si>
     <t xml:space="preserve">1.24902129173279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24258661270142</t>
+    <t xml:space="preserve">1.24258649349213</t>
   </si>
   <si>
     <t xml:space="preserve">1.23686695098877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23472237586975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23400712013245</t>
+    <t xml:space="preserve">1.23472201824188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23400723934174</t>
   </si>
   <si>
     <t xml:space="preserve">1.25225377082825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26176810264587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26835489273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27860128879547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2764059305191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27421009540558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27494215965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26323199272156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27128279209137</t>
+    <t xml:space="preserve">1.26176798343658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26835501194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27860140800476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27640581130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27421021461487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27494204044342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26323175430298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27128267288208</t>
   </si>
   <si>
     <t xml:space="preserve">1.26689124107361</t>
@@ -218,16 +218,16 @@
     <t xml:space="preserve">1.2793333530426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27347815036774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27274632453918</t>
+    <t xml:space="preserve">1.27347826957703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2727462053299</t>
   </si>
   <si>
     <t xml:space="preserve">1.26615929603577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2822607755661</t>
+    <t xml:space="preserve">1.28226089477539</t>
   </si>
   <si>
     <t xml:space="preserve">1.28811597824097</t>
@@ -236,16 +236,16 @@
     <t xml:space="preserve">1.28738415241241</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28299272060394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26396369934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24127531051636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2434709072113</t>
+    <t xml:space="preserve">1.28299283981323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26396358013153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24127542972565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24347102642059</t>
   </si>
   <si>
     <t xml:space="preserve">1.22956514358521</t>
@@ -263,13 +263,13 @@
     <t xml:space="preserve">1.20760869979858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18565213680267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1783332824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18784773349762</t>
+    <t xml:space="preserve">1.18565237522125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17833340167999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18784785270691</t>
   </si>
   <si>
     <t xml:space="preserve">1.16955065727234</t>
@@ -281,16 +281,16 @@
     <t xml:space="preserve">1.17028260231018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18931150436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22224640846252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22151458263397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23981153964996</t>
+    <t xml:space="preserve">1.18931138515472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22224652767181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22151446342468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23981165885925</t>
   </si>
   <si>
     <t xml:space="preserve">1.23907971382141</t>
@@ -308,22 +308,22 @@
     <t xml:space="preserve">1.2310289144516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19736218452454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21712327003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22297811508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23322474956512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23249280452728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22883343696594</t>
+    <t xml:space="preserve">1.19736242294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2171231508255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22297823429108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23322463035583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23249268531799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22883331775665</t>
   </si>
   <si>
     <t xml:space="preserve">1.28518831729889</t>
@@ -332,16 +332,16 @@
     <t xml:space="preserve">1.25884068012238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3071448802948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29909408092499</t>
+    <t xml:space="preserve">1.30714499950409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2990939617157</t>
   </si>
   <si>
     <t xml:space="preserve">1.32324647903442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31665921211243</t>
+    <t xml:space="preserve">1.31665933132172</t>
   </si>
   <si>
     <t xml:space="preserve">1.32763779163361</t>
@@ -350,7 +350,7 @@
     <t xml:space="preserve">1.30348539352417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31592726707458</t>
+    <t xml:space="preserve">1.31592750549316</t>
   </si>
   <si>
     <t xml:space="preserve">1.31812310218811</t>
@@ -362,40 +362,40 @@
     <t xml:space="preserve">1.30275356769562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29982590675354</t>
+    <t xml:space="preserve">1.29982602596283</t>
   </si>
   <si>
     <t xml:space="preserve">1.2888480424881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29543507099152</t>
+    <t xml:space="preserve">1.29543483257294</t>
   </si>
   <si>
     <t xml:space="preserve">1.30055797100067</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29836213588715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2932391166687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29250729084015</t>
+    <t xml:space="preserve">1.29836225509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29323923587799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29250717163086</t>
   </si>
   <si>
     <t xml:space="preserve">1.30128979682922</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3056812286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26908695697784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26762318611145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24786221981049</t>
+    <t xml:space="preserve">1.30568110942841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26908683776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26762306690216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24786233901978</t>
   </si>
   <si>
     <t xml:space="preserve">1.25518107414246</t>
@@ -416,19 +416,22 @@
     <t xml:space="preserve">1.24054336547852</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24639868736267</t>
+    <t xml:space="preserve">1.24639856815338</t>
   </si>
   <si>
     <t xml:space="preserve">1.24420297145844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23688411712646</t>
+    <t xml:space="preserve">1.23615205287933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23688399791718</t>
   </si>
   <si>
     <t xml:space="preserve">1.2420072555542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23176097869873</t>
+    <t xml:space="preserve">1.23176074028015</t>
   </si>
   <si>
     <t xml:space="preserve">1.20980429649353</t>
@@ -437,55 +440,55 @@
     <t xml:space="preserve">1.21126806735992</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21858704090118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21492743492126</t>
+    <t xml:space="preserve">1.21858692169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21492755413055</t>
   </si>
   <si>
     <t xml:space="preserve">1.19004344940186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18199265003204</t>
+    <t xml:space="preserve">1.18199288845062</t>
   </si>
   <si>
     <t xml:space="preserve">1.214195728302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19297099113464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19663035869598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22005069255829</t>
+    <t xml:space="preserve">1.19297087192535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19663047790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22005081176758</t>
   </si>
   <si>
     <t xml:space="preserve">1.21639144420624</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25957238674164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27786958217621</t>
+    <t xml:space="preserve">1.25957226753235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27786946296692</t>
   </si>
   <si>
     <t xml:space="preserve">1.28592026233673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29470300674438</t>
+    <t xml:space="preserve">1.2947028875351</t>
   </si>
   <si>
     <t xml:space="preserve">1.29689836502075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31007242202759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32544195652008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34081161022186</t>
+    <t xml:space="preserve">1.31007254123688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32544207572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34081149101257</t>
   </si>
   <si>
     <t xml:space="preserve">1.3334926366806</t>
@@ -494,7 +497,7 @@
     <t xml:space="preserve">1.33422458171844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33202910423279</t>
+    <t xml:space="preserve">1.3320289850235</t>
   </si>
   <si>
     <t xml:space="preserve">1.33861601352692</t>
@@ -503,52 +506,52 @@
     <t xml:space="preserve">1.33934772014618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34666657447815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34227526187897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34007954597473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32690560817719</t>
+    <t xml:space="preserve">1.34666669368744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34227538108826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34007966518402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32690572738647</t>
   </si>
   <si>
     <t xml:space="preserve">1.32105076313019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3459347486496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36130452156067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36057233810425</t>
+    <t xml:space="preserve">1.34593451023102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36130440235138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36057245731354</t>
   </si>
   <si>
     <t xml:space="preserve">1.33276069164276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34959411621094</t>
+    <t xml:space="preserve">1.34959423542023</t>
   </si>
   <si>
     <t xml:space="preserve">1.33788406848907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34373915195465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34520292282104</t>
+    <t xml:space="preserve">1.34373903274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34520280361176</t>
   </si>
   <si>
     <t xml:space="preserve">1.32910144329071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36349987983704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36789119243622</t>
+    <t xml:space="preserve">1.36349999904633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36789131164551</t>
   </si>
   <si>
     <t xml:space="preserve">1.37667381763458</t>
@@ -560,13 +563,13 @@
     <t xml:space="preserve">1.39789855480194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41253626346588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40668118000031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4081449508667</t>
+    <t xml:space="preserve">1.41253614425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40668106079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40814483165741</t>
   </si>
   <si>
     <t xml:space="preserve">1.40887677669525</t>
@@ -575,76 +578,76 @@
     <t xml:space="preserve">1.40302169322968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39277517795563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3693550825119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37886965274811</t>
+    <t xml:space="preserve">1.3927755355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36935484409332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37886953353882</t>
   </si>
   <si>
     <t xml:space="preserve">1.38911592960358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40155792236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49304330348969</t>
+    <t xml:space="preserve">1.40155780315399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49304354190826</t>
   </si>
   <si>
     <t xml:space="preserve">1.47621011734009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48206532001495</t>
+    <t xml:space="preserve">1.48206508159637</t>
   </si>
   <si>
     <t xml:space="preserve">1.49157953262329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50328993797302</t>
+    <t xml:space="preserve">1.50328981876373</t>
   </si>
   <si>
     <t xml:space="preserve">1.46742749214172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45864486694336</t>
+    <t xml:space="preserve">1.45864498615265</t>
   </si>
   <si>
     <t xml:space="preserve">1.47913753986359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49523901939392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49084794521332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48792028427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5274418592453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50987648963928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53256523609161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52963757514954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53183329105377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52817368507385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51500010490417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49963045120239</t>
+    <t xml:space="preserve">1.49523913860321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49084782600403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48792016506195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52744209766388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50987660884857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5325653553009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52963769435883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53183352947235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52817392349243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51499998569489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49963057041168</t>
   </si>
   <si>
     <t xml:space="preserve">1.498166680336</t>
@@ -656,61 +659,61 @@
     <t xml:space="preserve">1.47108697891235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48426079750061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46376824378967</t>
+    <t xml:space="preserve">1.4842609167099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46376812458038</t>
   </si>
   <si>
     <t xml:space="preserve">1.45498549938202</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48499286174774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52085506916046</t>
+    <t xml:space="preserve">1.48499274253845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52085518836975</t>
   </si>
   <si>
     <t xml:space="preserve">1.53768837451935</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58233344554901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63126373291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63427472114563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64857757091522</t>
+    <t xml:space="preserve">1.58233320713043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63126385211945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63427460193634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64857769012451</t>
   </si>
   <si>
     <t xml:space="preserve">1.63578033447266</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66664433479309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66288030147552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66137480735779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76902151107788</t>
+    <t xml:space="preserve">1.66664397716522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66288018226624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6613746881485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76902174949646</t>
   </si>
   <si>
     <t xml:space="preserve">1.80816578865051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84429895877838</t>
+    <t xml:space="preserve">1.8442987203598</t>
   </si>
   <si>
     <t xml:space="preserve">1.9165655374527</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99485421180725</t>
+    <t xml:space="preserve">1.99485397338867</t>
   </si>
   <si>
     <t xml:space="preserve">2.01367354393005</t>
@@ -719,7 +722,7 @@
     <t xml:space="preserve">1.95345163345337</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98205697536469</t>
+    <t xml:space="preserve">1.98205673694611</t>
   </si>
   <si>
     <t xml:space="preserve">1.9301153421402</t>
@@ -728,16 +731,16 @@
     <t xml:space="preserve">1.83376038074493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9030157327652</t>
+    <t xml:space="preserve">1.90301561355591</t>
   </si>
   <si>
     <t xml:space="preserve">1.90452110767365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91204869747162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93538475036621</t>
+    <t xml:space="preserve">1.9120489358902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9353848695755</t>
   </si>
   <si>
     <t xml:space="preserve">1.92258787155151</t>
@@ -746,13 +749,13 @@
     <t xml:space="preserve">1.91581284999847</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88118517398834</t>
+    <t xml:space="preserve">1.88118481636047</t>
   </si>
   <si>
     <t xml:space="preserve">1.92860984802246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92183530330658</t>
+    <t xml:space="preserve">1.921835064888</t>
   </si>
   <si>
     <t xml:space="preserve">1.9255987405777</t>
@@ -761,13 +764,13 @@
     <t xml:space="preserve">1.94065427780151</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92635142803192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90376853942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91957664489746</t>
+    <t xml:space="preserve">1.9263516664505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90376842021942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91957640647888</t>
   </si>
   <si>
     <t xml:space="preserve">1.91882371902466</t>
@@ -776,82 +779,82 @@
     <t xml:space="preserve">1.93237376213074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94366562366486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91054320335388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89021837711334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90753221511841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89699327945709</t>
+    <t xml:space="preserve">1.94366538524628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9105429649353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89021813869476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90753245353699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89699351787567</t>
   </si>
   <si>
     <t xml:space="preserve">1.89473497867584</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87742114067078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86010718345642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7705272436142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79762673377991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76826882362366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79461586475372</t>
+    <t xml:space="preserve">1.87742137908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86010730266571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77052700519562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7976268529892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76826894283295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79461598396301</t>
   </si>
   <si>
     <t xml:space="preserve">1.80741310119629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8307489156723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84881567955017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82547998428345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81042397022247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82623267173767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83601856231689</t>
+    <t xml:space="preserve">1.83074915409088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84881556034088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82547962665558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81042408943176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82623243331909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83601868152618</t>
   </si>
   <si>
     <t xml:space="preserve">1.83902966976166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85257947444916</t>
+    <t xml:space="preserve">1.85257983207703</t>
   </si>
   <si>
     <t xml:space="preserve">1.82171595096588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84806275367737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84655737876892</t>
+    <t xml:space="preserve">1.84806287288666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84655725955963</t>
   </si>
   <si>
     <t xml:space="preserve">1.83752405643463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89774608612061</t>
+    <t xml:space="preserve">1.89774596691132</t>
   </si>
   <si>
     <t xml:space="preserve">1.91280162334442</t>
@@ -866,16 +869,16 @@
     <t xml:space="preserve">1.93086802959442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93613767623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92108237743378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8879599571228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88720726966858</t>
+    <t xml:space="preserve">1.93613743782043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9210821390152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88796007633209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88720738887787</t>
   </si>
   <si>
     <t xml:space="preserve">1.89548766613007</t>
@@ -887,13 +890,13 @@
     <t xml:space="preserve">1.86914074420929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85860192775726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8563437461853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85709631443024</t>
+    <t xml:space="preserve">1.85860204696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85634350776672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85709619522095</t>
   </si>
   <si>
     <t xml:space="preserve">1.85182690620422</t>
@@ -902,40 +905,40 @@
     <t xml:space="preserve">1.86688232421875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88494896888733</t>
+    <t xml:space="preserve">1.88494908809662</t>
   </si>
   <si>
     <t xml:space="preserve">1.87215185165405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87064623832703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86161279678345</t>
+    <t xml:space="preserve">1.87064647674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86161303520203</t>
   </si>
   <si>
     <t xml:space="preserve">1.88193774223328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86763501167297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8736572265625</t>
+    <t xml:space="preserve">1.86763525009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87365710735321</t>
   </si>
   <si>
     <t xml:space="preserve">1.8653769493103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84505212306976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84204053878784</t>
+    <t xml:space="preserve">1.84505176544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84204089641571</t>
   </si>
   <si>
     <t xml:space="preserve">1.84731030464172</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84279346466064</t>
+    <t xml:space="preserve">1.84279370307922</t>
   </si>
   <si>
     <t xml:space="preserve">1.81795191764832</t>
@@ -947,7 +950,7 @@
     <t xml:space="preserve">1.82849085330963</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81569373607635</t>
+    <t xml:space="preserve">1.81569385528564</t>
   </si>
   <si>
     <t xml:space="preserve">1.82021021842957</t>
@@ -956,16 +959,16 @@
     <t xml:space="preserve">1.81117701530457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81644642353058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81418824195862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83526575565338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83225452899933</t>
+    <t xml:space="preserve">1.81644630432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81418812274933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83526563644409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83225476741791</t>
   </si>
   <si>
     <t xml:space="preserve">1.82246851921082</t>
@@ -974,7 +977,7 @@
     <t xml:space="preserve">1.8503212928772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89849889278412</t>
+    <t xml:space="preserve">1.89849901199341</t>
   </si>
   <si>
     <t xml:space="preserve">1.93689036369324</t>
@@ -983,7 +986,7 @@
     <t xml:space="preserve">1.91731822490692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97979855537415</t>
+    <t xml:space="preserve">1.97979879379272</t>
   </si>
   <si>
     <t xml:space="preserve">1.96474301815033</t>
@@ -1004,31 +1007,31 @@
     <t xml:space="preserve">2.10325360298157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04378437995911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0242121219635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98732602596283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99937057495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98582053184509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99033737182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96624886989594</t>
+    <t xml:space="preserve">2.04378461837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02421236038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98732626438141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99937081336975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98582077026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99033761024475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96624863147736</t>
   </si>
   <si>
     <t xml:space="preserve">1.99861788749695</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96549570560455</t>
+    <t xml:space="preserve">1.96549594402313</t>
   </si>
   <si>
     <t xml:space="preserve">1.97603487968445</t>
@@ -1037,7 +1040,7 @@
     <t xml:space="preserve">1.98280966281891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0249650478363</t>
+    <t xml:space="preserve">2.02496528625488</t>
   </si>
   <si>
     <t xml:space="preserve">2.06260395050049</t>
@@ -1046,13 +1049,13 @@
     <t xml:space="preserve">2.07540082931519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08142352104187</t>
+    <t xml:space="preserve">2.08142328262329</t>
   </si>
   <si>
     <t xml:space="preserve">2.08217620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08594012260437</t>
+    <t xml:space="preserve">2.08593988418579</t>
   </si>
   <si>
     <t xml:space="preserve">2.07765936851501</t>
@@ -1064,7 +1067,7 @@
     <t xml:space="preserve">2.09045672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11153435707092</t>
+    <t xml:space="preserve">2.11153411865234</t>
   </si>
   <si>
     <t xml:space="preserve">2.10024261474609</t>
@@ -1076,13 +1079,13 @@
     <t xml:space="preserve">2.07013154029846</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06034588813782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05959320068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05884027481079</t>
+    <t xml:space="preserve">2.06034564971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05959296226501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05884003639221</t>
   </si>
   <si>
     <t xml:space="preserve">2.07615399360657</t>
@@ -1091,34 +1094,34 @@
     <t xml:space="preserve">2.08368134498596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10400676727295</t>
+    <t xml:space="preserve">2.10400652885437</t>
   </si>
   <si>
     <t xml:space="preserve">2.08518719673157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13185930252075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19057536125183</t>
+    <t xml:space="preserve">2.13185906410217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19057559967041</t>
   </si>
   <si>
     <t xml:space="preserve">2.21315884590149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17552018165588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16799211502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20563101768494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22068691253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31102013587952</t>
+    <t xml:space="preserve">2.1755199432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16799235343933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20563125610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22068667411804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31101989746094</t>
   </si>
   <si>
     <t xml:space="preserve">2.36371397972107</t>
@@ -1127,10 +1130,10 @@
     <t xml:space="preserve">2.31854724884033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33360314369202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37124156951904</t>
+    <t xml:space="preserve">2.33360290527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37124180793762</t>
   </si>
   <si>
     <t xml:space="preserve">2.32607507705688</t>
@@ -1148,10 +1151,10 @@
     <t xml:space="preserve">2.30349183082581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29596424102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25832557678223</t>
+    <t xml:space="preserve">2.29596400260925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25832533836365</t>
   </si>
   <si>
     <t xml:space="preserve">2.19810366630554</t>
@@ -1160,13 +1163,13 @@
     <t xml:space="preserve">2.18304800987244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43899154663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38629746437073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55190777778625</t>
+    <t xml:space="preserve">2.43899178504944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38629698753357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55190753936768</t>
   </si>
   <si>
     <t xml:space="preserve">2.5443799495697</t>
@@ -1184,19 +1187,19 @@
     <t xml:space="preserve">2.46910214424133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4013524055481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43146371841431</t>
+    <t xml:space="preserve">2.40135288238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43146395683289</t>
   </si>
   <si>
     <t xml:space="preserve">2.47663044929504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44651913642883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40888071060181</t>
+    <t xml:space="preserve">2.44651889801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40888047218323</t>
   </si>
   <si>
     <t xml:space="preserve">2.48415803909302</t>
@@ -1205,7 +1208,7 @@
     <t xml:space="preserve">2.45404672622681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41640830039978</t>
+    <t xml:space="preserve">2.4164080619812</t>
   </si>
   <si>
     <t xml:space="preserve">2.5067412853241</t>
@@ -1217,7 +1220,7 @@
     <t xml:space="preserve">2.57587671279907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59139394760132</t>
+    <t xml:space="preserve">2.5913941860199</t>
   </si>
   <si>
     <t xml:space="preserve">2.58363509178162</t>
@@ -1226,10 +1229,10 @@
     <t xml:space="preserve">2.56035923957825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50604844093323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51380705833435</t>
+    <t xml:space="preserve">2.50604867935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51380729675293</t>
   </si>
   <si>
     <t xml:space="preserve">2.52156591415405</t>
@@ -1244,16 +1247,16 @@
     <t xml:space="preserve">2.4982898235321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42846155166626</t>
+    <t xml:space="preserve">2.42846179008484</t>
   </si>
   <si>
     <t xml:space="preserve">2.32759928703308</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30432343482971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28104734420776</t>
+    <t xml:space="preserve">2.30432319641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28104710578918</t>
   </si>
   <si>
     <t xml:space="preserve">2.31208181381226</t>
@@ -1262,7 +1265,7 @@
     <t xml:space="preserve">2.22673654556274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20346069335938</t>
+    <t xml:space="preserve">2.2034604549408</t>
   </si>
   <si>
     <t xml:space="preserve">2.19570183753967</t>
@@ -1274,7 +1277,7 @@
     <t xml:space="preserve">2.23449540138245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25777125358582</t>
+    <t xml:space="preserve">2.25777149200439</t>
   </si>
   <si>
     <t xml:space="preserve">2.1724259853363</t>
@@ -1286,7 +1289,7 @@
     <t xml:space="preserve">2.18794345855713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25001239776611</t>
+    <t xml:space="preserve">2.25001263618469</t>
   </si>
   <si>
     <t xml:space="preserve">2.12587380409241</t>
@@ -1307,7 +1310,7 @@
     <t xml:space="preserve">2.07932209968567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07156348228455</t>
+    <t xml:space="preserve">2.07156324386597</t>
   </si>
   <si>
     <t xml:space="preserve">2.04052877426147</t>
@@ -1322,7 +1325,7 @@
     <t xml:space="preserve">2.14915013313293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18018436431885</t>
+    <t xml:space="preserve">2.18018460273743</t>
   </si>
   <si>
     <t xml:space="preserve">2.29656457901001</t>
@@ -1331,7 +1334,7 @@
     <t xml:space="preserve">2.03276991844177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01725268363953</t>
+    <t xml:space="preserve">2.01725244522095</t>
   </si>
   <si>
     <t xml:space="preserve">2.02501130104065</t>
@@ -1340,16 +1343,16 @@
     <t xml:space="preserve">2.0094940662384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9707008600235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9629420042038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93966603279114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88535535335541</t>
+    <t xml:space="preserve">1.97070062160492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96294212341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93966579437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8853554725647</t>
   </si>
   <si>
     <t xml:space="preserve">1.87759685516357</t>
@@ -1358,7 +1361,7 @@
     <t xml:space="preserve">1.85432064533234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86983788013458</t>
+    <t xml:space="preserve">1.86983811855316</t>
   </si>
   <si>
     <t xml:space="preserve">1.79225146770477</t>
@@ -1367,10 +1370,10 @@
     <t xml:space="preserve">1.83880352973938</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83104491233826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86207926273346</t>
+    <t xml:space="preserve">1.83104467391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86207938194275</t>
   </si>
   <si>
     <t xml:space="preserve">2.15690851211548</t>
@@ -1385,7 +1388,7 @@
     <t xml:space="preserve">2.0017352104187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97845935821533</t>
+    <t xml:space="preserve">1.97845911979675</t>
   </si>
   <si>
     <t xml:space="preserve">1.99397683143616</t>
@@ -1397,22 +1400,22 @@
     <t xml:space="preserve">1.84656190872192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80776882171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75345814228058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77673399448395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74569940567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82328593730927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89311385154724</t>
+    <t xml:space="preserve">1.80776870250702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75345802307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77673423290253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74569952487946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82328617572784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89311397075653</t>
   </si>
   <si>
     <t xml:space="preserve">1.91639006137848</t>
@@ -1427,16 +1430,16 @@
     <t xml:space="preserve">2.05604600906372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26552987098694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24225401878357</t>
+    <t xml:space="preserve">2.26553010940552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24225378036499</t>
   </si>
   <si>
     <t xml:space="preserve">2.35087513923645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31984066963196</t>
+    <t xml:space="preserve">2.3198401927948</t>
   </si>
   <si>
     <t xml:space="preserve">2.3353579044342</t>
@@ -1445,13 +1448,13 @@
     <t xml:space="preserve">2.35863375663757</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40518593788147</t>
+    <t xml:space="preserve">2.40518569946289</t>
   </si>
   <si>
     <t xml:space="preserve">2.3819100856781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38966846466064</t>
+    <t xml:space="preserve">2.38966822624207</t>
   </si>
   <si>
     <t xml:space="preserve">2.39742708206177</t>
@@ -1469,22 +1472,22 @@
     <t xml:space="preserve">2.34311676025391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3741512298584</t>
+    <t xml:space="preserve">2.37415099143982</t>
   </si>
   <si>
     <t xml:space="preserve">2.45173788070679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47501373291016</t>
+    <t xml:space="preserve">2.47501397132874</t>
   </si>
   <si>
     <t xml:space="preserve">2.55260062217712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54447102546692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5200834274292</t>
+    <t xml:space="preserve">2.5444712638855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52008318901062</t>
   </si>
   <si>
     <t xml:space="preserve">2.4956955909729</t>
@@ -1499,28 +1502,28 @@
     <t xml:space="preserve">2.47943687438965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48756623268127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50382471084595</t>
+    <t xml:space="preserve">2.4875659942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50382447242737</t>
   </si>
   <si>
     <t xml:space="preserve">2.40627312660217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43066120147705</t>
+    <t xml:space="preserve">2.43066072463989</t>
   </si>
   <si>
     <t xml:space="preserve">2.42253160476685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36562657356262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3900146484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28433346748352</t>
+    <t xml:space="preserve">2.3656268119812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39001441001892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2843337059021</t>
   </si>
   <si>
     <t xml:space="preserve">2.27620434761047</t>
@@ -1538,7 +1541,7 @@
     <t xml:space="preserve">2.26807498931885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.357497215271</t>
+    <t xml:space="preserve">2.35749745368958</t>
   </si>
   <si>
     <t xml:space="preserve">2.32498002052307</t>
@@ -1547,7 +1550,7 @@
     <t xml:space="preserve">2.34123873710632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37375593185425</t>
+    <t xml:space="preserve">2.37375617027283</t>
   </si>
   <si>
     <t xml:space="preserve">2.4631781578064</t>
@@ -1562,10 +1565,10 @@
     <t xml:space="preserve">2.53634214401245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58511781692505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5932469367981</t>
+    <t xml:space="preserve">2.58511757850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59324717521667</t>
   </si>
   <si>
     <t xml:space="preserve">2.56072998046875</t>
@@ -1580,25 +1583,22 @@
     <t xml:space="preserve">2.5688591003418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57698845863342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55260038375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41440272331238</t>
+    <t xml:space="preserve">2.57698822021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4144024848938</t>
   </si>
   <si>
     <t xml:space="preserve">2.3331093788147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34936809539795</t>
+    <t xml:space="preserve">2.34936785697937</t>
   </si>
   <si>
     <t xml:space="preserve">2.39814376831055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47130727767944</t>
+    <t xml:space="preserve">2.47130751609802</t>
   </si>
   <si>
     <t xml:space="preserve">2.44691967964172</t>
@@ -1610,13 +1610,13 @@
     <t xml:space="preserve">2.29246306419373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3087215423584</t>
+    <t xml:space="preserve">2.30872130393982</t>
   </si>
   <si>
     <t xml:space="preserve">2.30059218406677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11361837387085</t>
+    <t xml:space="preserve">2.11361813545227</t>
   </si>
   <si>
     <t xml:space="preserve">2.18678212165833</t>
@@ -1637,10 +1637,10 @@
     <t xml:space="preserve">2.048583984375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89412724971771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65837728977203</t>
+    <t xml:space="preserve">1.89412713050842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65837740898132</t>
   </si>
   <si>
     <t xml:space="preserve">1.66650664806366</t>
@@ -1649,19 +1649,19 @@
     <t xml:space="preserve">1.6258602142334</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47140347957611</t>
+    <t xml:space="preserve">1.4714035987854</t>
   </si>
   <si>
     <t xml:space="preserve">1.50392067432404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51205015182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61366641521454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55676102638245</t>
+    <t xml:space="preserve">1.51205003261566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61366629600525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55676090717316</t>
   </si>
   <si>
     <t xml:space="preserve">1.54863178730011</t>
@@ -1670,16 +1670,16 @@
     <t xml:space="preserve">1.53237330913544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49579131603241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58521366119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6014723777771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57301986217499</t>
+    <t xml:space="preserve">1.4957914352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58521378040314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60147225856781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5730197429657</t>
   </si>
   <si>
     <t xml:space="preserve">1.56082582473755</t>
@@ -1688,19 +1688,19 @@
     <t xml:space="preserve">1.58114922046661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5689549446106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63398957252502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69089460372925</t>
+    <t xml:space="preserve">1.56895506381989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63398969173431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69089448451996</t>
   </si>
   <si>
     <t xml:space="preserve">1.60553693771362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62179565429688</t>
+    <t xml:space="preserve">1.62179553508759</t>
   </si>
   <si>
     <t xml:space="preserve">1.58927834033966</t>
@@ -1712,64 +1712,64 @@
     <t xml:space="preserve">1.67463612556458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70715320110321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76405835151672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73154103755951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71528255939484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69902384281158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65024816989899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74779963493347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75592911243439</t>
+    <t xml:space="preserve">1.7071533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76405823230743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73154127597809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71528244018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69902396202087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6502480506897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74779975414276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75592887401581</t>
   </si>
   <si>
     <t xml:space="preserve">1.77218759059906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78844618797302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82096350193024</t>
+    <t xml:space="preserve">1.7884464263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82096338272095</t>
   </si>
   <si>
     <t xml:space="preserve">1.87786865234375</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82909274101257</t>
+    <t xml:space="preserve">1.82909286022186</t>
   </si>
   <si>
     <t xml:space="preserve">1.80470490455627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81283414363861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79657566547394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78031671047211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72341191768646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73967027664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6827654838562</t>
+    <t xml:space="preserve">1.81283402442932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79657554626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78031706809998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72341179847717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73967039585114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68276536464691</t>
   </si>
   <si>
     <t xml:space="preserve">1.60960149765015</t>
@@ -1778,19 +1778,19 @@
     <t xml:space="preserve">1.64211881160736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57708418369293</t>
+    <t xml:space="preserve">1.57708442211151</t>
   </si>
   <si>
     <t xml:space="preserve">1.52830851078033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53643774986267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49985599517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48766207695007</t>
+    <t xml:space="preserve">1.53643798828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49985611438751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48766195774078</t>
   </si>
   <si>
     <t xml:space="preserve">1.48359739780426</t>
@@ -1802,34 +1802,34 @@
     <t xml:space="preserve">1.42262768745422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41043388843536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40636909008026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43482160568237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41449844837189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36572241783142</t>
+    <t xml:space="preserve">1.41043376922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40636897087097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43482172489166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4144983291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36572253704071</t>
   </si>
   <si>
     <t xml:space="preserve">1.33320534229279</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38198113441467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35759329795837</t>
+    <t xml:space="preserve">1.38198125362396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35759341716766</t>
   </si>
   <si>
     <t xml:space="preserve">1.30475270748138</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29255890846252</t>
+    <t xml:space="preserve">1.29255878925323</t>
   </si>
   <si>
     <t xml:space="preserve">1.30881750583649</t>
@@ -1850,13 +1850,13 @@
     <t xml:space="preserve">1.35352861881256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39823973178864</t>
+    <t xml:space="preserve">1.39823985099792</t>
   </si>
   <si>
     <t xml:space="preserve">1.40230441093445</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3860456943512</t>
+    <t xml:space="preserve">1.38604581356049</t>
   </si>
   <si>
     <t xml:space="preserve">1.39011061191559</t>
@@ -1865,13 +1865,13 @@
     <t xml:space="preserve">1.37791657447815</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46733868122101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52017939090729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5526967048645</t>
+    <t xml:space="preserve">1.4673388004303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.520179271698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55269658565521</t>
   </si>
   <si>
     <t xml:space="preserve">1.54456722736359</t>
@@ -1889,19 +1889,19 @@
     <t xml:space="preserve">1.51611471176147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54050254821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47953295707703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86973929405212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95103216171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0729718208313</t>
+    <t xml:space="preserve">1.54050266742706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47953283786774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86973941326141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95103228092194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07297158241272</t>
   </si>
   <si>
     <t xml:space="preserve">2.25994563102722</t>
@@ -1916,7 +1916,7 @@
     <t xml:space="preserve">2.14613556861877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05671310424805</t>
+    <t xml:space="preserve">2.05671334266663</t>
   </si>
   <si>
     <t xml:space="preserve">2.13800621032715</t>
@@ -1934,10 +1934,10 @@
     <t xml:space="preserve">2.24429607391357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25257754325867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20288848876953</t>
+    <t xml:space="preserve">2.25257778167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20288825035095</t>
   </si>
   <si>
     <t xml:space="preserve">2.22773313522339</t>
@@ -1946,19 +1946,19 @@
     <t xml:space="preserve">2.19460678100586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17804360389709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34367442131042</t>
+    <t xml:space="preserve">2.17804384231567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.343674659729</t>
   </si>
   <si>
     <t xml:space="preserve">2.36023759841919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36851930618286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38508200645447</t>
+    <t xml:space="preserve">2.36851906776428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38508224487305</t>
   </si>
   <si>
     <t xml:space="preserve">2.40164518356323</t>
@@ -1976,13 +1976,13 @@
     <t xml:space="preserve">2.49274230003357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41820859909058</t>
+    <t xml:space="preserve">2.418208360672</t>
   </si>
   <si>
     <t xml:space="preserve">2.39336347579956</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37680053710938</t>
+    <t xml:space="preserve">2.37680077552795</t>
   </si>
   <si>
     <t xml:space="preserve">2.44305300712585</t>
@@ -1994,10 +1994,10 @@
     <t xml:space="preserve">2.42648983001709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33539295196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32711124420166</t>
+    <t xml:space="preserve">2.33539319038391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32711148262024</t>
   </si>
   <si>
     <t xml:space="preserve">2.30226683616638</t>
@@ -2009,7 +2009,7 @@
     <t xml:space="preserve">2.31054830551147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3519561290741</t>
+    <t xml:space="preserve">2.35195589065552</t>
   </si>
   <si>
     <t xml:space="preserve">2.29398536682129</t>
@@ -2018,19 +2018,19 @@
     <t xml:space="preserve">2.28570365905762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2774224281311</t>
+    <t xml:space="preserve">2.27742218971252</t>
   </si>
   <si>
     <t xml:space="preserve">2.15319919586182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12835478782654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13663625717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18632507324219</t>
+    <t xml:space="preserve">2.12835454940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13663601875305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18632531166077</t>
   </si>
   <si>
     <t xml:space="preserve">2.08694696426392</t>
@@ -2045,7 +2045,7 @@
     <t xml:space="preserve">2.16976237297058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14491748809814</t>
+    <t xml:space="preserve">2.14491772651672</t>
   </si>
   <si>
     <t xml:space="preserve">2.16148066520691</t>
@@ -2060,25 +2060,25 @@
     <t xml:space="preserve">2.4099268913269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46789717674255</t>
+    <t xml:space="preserve">2.46789741516113</t>
   </si>
   <si>
     <t xml:space="preserve">2.50102376937866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52586817741394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50930523872375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62524676322937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71634340286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69978046417236</t>
+    <t xml:space="preserve">2.52586841583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50930500030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62524652481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71634364128113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69978022575378</t>
   </si>
   <si>
     <t xml:space="preserve">2.81572198867798</t>
@@ -2093,13 +2093,13 @@
     <t xml:space="preserve">3.01447892189026</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03104186058044</t>
+    <t xml:space="preserve">3.03104162216187</t>
   </si>
   <si>
     <t xml:space="preserve">3.24636197090149</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23808002471924</t>
+    <t xml:space="preserve">3.23808026313782</t>
   </si>
   <si>
     <t xml:space="preserve">3.22979879379272</t>
@@ -2111,13 +2111,13 @@
     <t xml:space="preserve">3.12213897705078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16354656219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17182803153992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21323585510254</t>
+    <t xml:space="preserve">3.1635468006134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17182779312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21323561668396</t>
   </si>
   <si>
     <t xml:space="preserve">3.1883909702301</t>
@@ -2129,28 +2129,28 @@
     <t xml:space="preserve">3.18010950088501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13042020797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10557579994202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13870215415955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08901262283325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07244968414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11385726928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08073115348816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06416821479797</t>
+    <t xml:space="preserve">3.13042044639587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10557556152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13870191574097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08901286125183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07244944572449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11385703086853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08073139190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06416797637939</t>
   </si>
   <si>
     <t xml:space="preserve">3.254643201828</t>
@@ -2165,22 +2165,22 @@
     <t xml:space="preserve">3.02276039123535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04760479927063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0558865070343</t>
+    <t xml:space="preserve">3.04760503768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05588674545288</t>
   </si>
   <si>
     <t xml:space="preserve">3.15526485443115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03932332992554</t>
+    <t xml:space="preserve">3.03932356834412</t>
   </si>
   <si>
     <t xml:space="preserve">2.98963403701782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00619721412659</t>
+    <t xml:space="preserve">3.00619745254517</t>
   </si>
   <si>
     <t xml:space="preserve">2.98135280609131</t>
@@ -2225,13 +2225,13 @@
     <t xml:space="preserve">4.95042657852173</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01585006713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58285999298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36477947235107</t>
+    <t xml:space="preserve">5.01585054397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5828595161438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36477899551392</t>
   </si>
   <si>
     <t xml:space="preserve">5.05946683883667</t>
@@ -2240,7 +2240,7 @@
     <t xml:space="preserve">4.97223424911499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14669895172119</t>
+    <t xml:space="preserve">5.14669847488403</t>
   </si>
   <si>
     <t xml:space="preserve">5.08127450942993</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">5.19031476974487</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21212244033813</t>
+    <t xml:space="preserve">5.21212291717529</t>
   </si>
   <si>
     <t xml:space="preserve">5.27754688262939</t>
@@ -2264,22 +2264,22 @@
     <t xml:space="preserve">5.47381925582886</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53924322128296</t>
+    <t xml:space="preserve">5.53924369812012</t>
   </si>
   <si>
     <t xml:space="preserve">5.45201110839844</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43020296096802</t>
+    <t xml:space="preserve">5.43020343780518</t>
   </si>
   <si>
     <t xml:space="preserve">5.40839529037476</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34297132492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38658761978149</t>
+    <t xml:space="preserve">5.3429708480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38658714294434</t>
   </si>
   <si>
     <t xml:space="preserve">5.32116317749023</t>
@@ -2291,19 +2291,19 @@
     <t xml:space="preserve">5.99721240997314</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82591772079468</t>
+    <t xml:space="preserve">6.82591819763184</t>
   </si>
   <si>
     <t xml:space="preserve">7.32750272750854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93495845794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.782301902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73868608474731</t>
+    <t xml:space="preserve">6.93495798110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78230237960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73868560791016</t>
   </si>
   <si>
     <t xml:space="preserve">6.67326211929321</t>
@@ -2318,7 +2318,7 @@
     <t xml:space="preserve">6.25890922546387</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32433271408081</t>
+    <t xml:space="preserve">6.32433319091797</t>
   </si>
   <si>
     <t xml:space="preserve">6.23710107803345</t>
@@ -2333,28 +2333,28 @@
     <t xml:space="preserve">6.41156530380249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62964582443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76049375534058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0221905708313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06580686569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04399824142456</t>
+    <t xml:space="preserve">6.62964534759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76049423217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02219104766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0658073425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04399871826172</t>
   </si>
   <si>
     <t xml:space="preserve">7.0876145362854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45835161209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52377557754517</t>
+    <t xml:space="preserve">7.45835208892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52377510070801</t>
   </si>
   <si>
     <t xml:space="preserve">7.78547239303589</t>
@@ -2366,7 +2366,7 @@
     <t xml:space="preserve">8.19982433319092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11259269714355</t>
+    <t xml:space="preserve">8.11259365081787</t>
   </si>
   <si>
     <t xml:space="preserve">8.37428951263428</t>
@@ -8683,7 +8683,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G209" t="s">
-        <v>16</v>
+        <v>136</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -8709,7 +8709,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G210" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -8761,7 +8761,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G212" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -8969,7 +8969,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G220" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -9177,7 +9177,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G228" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -9203,7 +9203,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G229" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -9229,7 +9229,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G230" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -9281,7 +9281,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G232" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -9307,7 +9307,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G233" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -9333,7 +9333,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G234" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -9359,7 +9359,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G235" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -9385,7 +9385,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G236" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -9411,7 +9411,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G237" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -9489,7 +9489,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G240" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -9515,7 +9515,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G241" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -9567,7 +9567,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G243" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -9645,7 +9645,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G246" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -9671,7 +9671,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G247" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -9697,7 +9697,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G248" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -9749,7 +9749,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G250" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -9775,7 +9775,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G251" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -9853,7 +9853,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G254" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -9931,7 +9931,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G257" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -9957,7 +9957,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G258" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -9983,7 +9983,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G259" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -10009,7 +10009,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G260" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -10035,7 +10035,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G261" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -10061,7 +10061,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G262" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -10087,7 +10087,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G263" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -10113,7 +10113,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G264" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -10139,7 +10139,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G265" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -10191,7 +10191,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G267" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -10217,7 +10217,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G268" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -10243,7 +10243,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G269" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -10269,7 +10269,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G270" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -10295,7 +10295,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G271" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -10321,7 +10321,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G272" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -10347,7 +10347,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G273" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -10373,7 +10373,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G274" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -10399,7 +10399,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G275" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -10425,7 +10425,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G276" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -10451,7 +10451,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G277" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -10477,7 +10477,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G278" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -10503,7 +10503,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G279" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -10529,7 +10529,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G280" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -10555,7 +10555,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G281" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -10581,7 +10581,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G282" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -10607,7 +10607,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G283" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -10633,7 +10633,7 @@
         <v>18.6299991607666</v>
       </c>
       <c r="G284" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -10659,7 +10659,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G285" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -10685,7 +10685,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G286" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -10711,7 +10711,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G287" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -10737,7 +10737,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G288" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -10763,7 +10763,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G289" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -10789,7 +10789,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G290" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -10815,7 +10815,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G291" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -10841,7 +10841,7 @@
         <v>19.25</v>
       </c>
       <c r="G292" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -10867,7 +10867,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G293" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -10893,7 +10893,7 @@
         <v>19.0300006866455</v>
       </c>
       <c r="G294" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -10919,7 +10919,7 @@
         <v>18.7099990844727</v>
       </c>
       <c r="G295" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -10945,7 +10945,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G296" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -10971,7 +10971,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G297" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -10997,7 +10997,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G298" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -11023,7 +11023,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G299" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -11049,7 +11049,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G300" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -11075,7 +11075,7 @@
         <v>20.1700000762939</v>
       </c>
       <c r="G301" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -11101,7 +11101,7 @@
         <v>20.25</v>
       </c>
       <c r="G302" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -11127,7 +11127,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G303" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -11153,7 +11153,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G304" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -11179,7 +11179,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G305" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -11205,7 +11205,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G306" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -11231,7 +11231,7 @@
         <v>20.2099990844727</v>
       </c>
       <c r="G307" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -11257,7 +11257,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G308" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -11283,7 +11283,7 @@
         <v>20.3700008392334</v>
       </c>
       <c r="G309" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -11309,7 +11309,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G310" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -11335,7 +11335,7 @@
         <v>20.25</v>
       </c>
       <c r="G311" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -11361,7 +11361,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G312" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -11387,7 +11387,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G313" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -11413,7 +11413,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G314" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -11439,7 +11439,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G315" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -11465,7 +11465,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G316" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -11491,7 +11491,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G317" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -11517,7 +11517,7 @@
         <v>20.9300003051758</v>
       </c>
       <c r="G318" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -11543,7 +11543,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G319" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -11569,7 +11569,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G320" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -11595,7 +11595,7 @@
         <v>20.4899997711182</v>
       </c>
       <c r="G321" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -11621,7 +11621,7 @@
         <v>20.4699993133545</v>
       </c>
       <c r="G322" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -11647,7 +11647,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G323" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -11673,7 +11673,7 @@
         <v>20.25</v>
       </c>
       <c r="G324" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -11699,7 +11699,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G325" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -11725,7 +11725,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G326" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -11751,7 +11751,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G327" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -11777,7 +11777,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G328" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -11803,7 +11803,7 @@
         <v>20.25</v>
       </c>
       <c r="G329" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -11829,7 +11829,7 @@
         <v>20</v>
       </c>
       <c r="G330" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -11855,7 +11855,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G331" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -11881,7 +11881,7 @@
         <v>20.2900009155273</v>
       </c>
       <c r="G332" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -11907,7 +11907,7 @@
         <v>20.7800006866455</v>
       </c>
       <c r="G333" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -11933,7 +11933,7 @@
         <v>21.0100002288818</v>
       </c>
       <c r="G334" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -11959,7 +11959,7 @@
         <v>21.6200008392334</v>
       </c>
       <c r="G335" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -11985,7 +11985,7 @@
         <v>21.6700000762939</v>
       </c>
       <c r="G336" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -12011,7 +12011,7 @@
         <v>21.7099990844727</v>
       </c>
       <c r="G337" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -12037,7 +12037,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G338" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -12063,7 +12063,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G339" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -12089,7 +12089,7 @@
         <v>22.1399993896484</v>
       </c>
       <c r="G340" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -12115,7 +12115,7 @@
         <v>22.0900001525879</v>
       </c>
       <c r="G341" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -12141,7 +12141,7 @@
         <v>22.0699996948242</v>
       </c>
       <c r="G342" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -12167,7 +12167,7 @@
         <v>23.5</v>
       </c>
       <c r="G343" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -12193,7 +12193,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G344" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -12219,7 +12219,7 @@
         <v>24.5</v>
       </c>
       <c r="G345" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -12245,7 +12245,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G346" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -12271,7 +12271,7 @@
         <v>26.5</v>
       </c>
       <c r="G347" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -12297,7 +12297,7 @@
         <v>26.75</v>
       </c>
       <c r="G348" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -12323,7 +12323,7 @@
         <v>25.9500007629395</v>
       </c>
       <c r="G349" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -12349,7 +12349,7 @@
         <v>26.3299999237061</v>
       </c>
       <c r="G350" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -12375,7 +12375,7 @@
         <v>25.6399993896484</v>
       </c>
       <c r="G351" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -12401,7 +12401,7 @@
         <v>24.5</v>
       </c>
       <c r="G352" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -12427,7 +12427,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G353" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -12453,7 +12453,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G354" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -12479,7 +12479,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G355" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -12505,7 +12505,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G356" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -12531,7 +12531,7 @@
         <v>25.7099990844727</v>
       </c>
       <c r="G357" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -12557,7 +12557,7 @@
         <v>25.5400009155273</v>
       </c>
       <c r="G358" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -12583,7 +12583,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G359" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -12609,7 +12609,7 @@
         <v>24.9899997711182</v>
       </c>
       <c r="G360" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -12635,7 +12635,7 @@
         <v>25.6200008392334</v>
       </c>
       <c r="G361" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -12661,7 +12661,7 @@
         <v>25.5300006866455</v>
       </c>
       <c r="G362" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -12687,7 +12687,7 @@
         <v>25.5799999237061</v>
       </c>
       <c r="G363" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -12713,7 +12713,7 @@
         <v>25.7800006866455</v>
       </c>
       <c r="G364" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -12739,7 +12739,7 @@
         <v>25.5900001525879</v>
       </c>
       <c r="G365" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -12765,7 +12765,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G366" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -12791,7 +12791,7 @@
         <v>25.2900009155273</v>
       </c>
       <c r="G367" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -12817,7 +12817,7 @@
         <v>25.5</v>
       </c>
       <c r="G368" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -12843,7 +12843,7 @@
         <v>25.5799999237061</v>
       </c>
       <c r="G369" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -12869,7 +12869,7 @@
         <v>25.4899997711182</v>
       </c>
       <c r="G370" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -12895,7 +12895,7 @@
         <v>25.6700000762939</v>
       </c>
       <c r="G371" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -12921,7 +12921,7 @@
         <v>25.8199996948242</v>
       </c>
       <c r="G372" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -12947,7 +12947,7 @@
         <v>25.5400009155273</v>
       </c>
       <c r="G373" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -12973,7 +12973,7 @@
         <v>25.3799991607666</v>
       </c>
       <c r="G374" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -12999,7 +12999,7 @@
         <v>25.1100006103516</v>
       </c>
       <c r="G375" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -13025,7 +13025,7 @@
         <v>25.3400001525879</v>
       </c>
       <c r="G376" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -13051,7 +13051,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G377" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -13077,7 +13077,7 @@
         <v>25.1700000762939</v>
       </c>
       <c r="G378" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -13103,7 +13103,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G379" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -13129,7 +13129,7 @@
         <v>24.7099990844727</v>
       </c>
       <c r="G380" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -13155,7 +13155,7 @@
         <v>23.5200004577637</v>
       </c>
       <c r="G381" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -13181,7 +13181,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G382" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -13207,7 +13207,7 @@
         <v>23.4899997711182</v>
       </c>
       <c r="G383" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -13233,7 +13233,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G384" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -13259,7 +13259,7 @@
         <v>24.0100002288818</v>
       </c>
       <c r="G385" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -13285,7 +13285,7 @@
         <v>24.3199996948242</v>
       </c>
       <c r="G386" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -13311,7 +13311,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G387" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -13337,7 +13337,7 @@
         <v>24.25</v>
       </c>
       <c r="G388" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -13363,7 +13363,7 @@
         <v>24.0499992370605</v>
       </c>
       <c r="G389" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -13389,7 +13389,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G390" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -13415,7 +13415,7 @@
         <v>24.2600002288818</v>
       </c>
       <c r="G391" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -13441,7 +13441,7 @@
         <v>24.0499992370605</v>
       </c>
       <c r="G392" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -13467,7 +13467,7 @@
         <v>24.3899993896484</v>
       </c>
       <c r="G393" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -13493,7 +13493,7 @@
         <v>24.4300003051758</v>
       </c>
       <c r="G394" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -13519,7 +13519,7 @@
         <v>24.5</v>
       </c>
       <c r="G395" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -13545,7 +13545,7 @@
         <v>24.5</v>
       </c>
       <c r="G396" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -13571,7 +13571,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G397" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -13597,7 +13597,7 @@
         <v>24.6100006103516</v>
       </c>
       <c r="G398" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -13623,7 +13623,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G399" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -13649,7 +13649,7 @@
         <v>24.5499992370605</v>
       </c>
       <c r="G400" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -13675,7 +13675,7 @@
         <v>24.5300006866455</v>
       </c>
       <c r="G401" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -13701,7 +13701,7 @@
         <v>24.4099998474121</v>
       </c>
       <c r="G402" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -13727,7 +13727,7 @@
         <v>25.2099990844727</v>
       </c>
       <c r="G403" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -13753,7 +13753,7 @@
         <v>25.4099998474121</v>
       </c>
       <c r="G404" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -13779,7 +13779,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G405" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -13805,7 +13805,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G406" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -13831,7 +13831,7 @@
         <v>26.1900005340576</v>
       </c>
       <c r="G407" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -13857,7 +13857,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G408" t="s">
-        <v>283</v>
+        <v>284</v>
       